--- a/data/workout_log.xlsx
+++ b/data/workout_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H199"/>
+  <dimension ref="A1:H242"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6486,6 +6486,1342 @@
         <v>37.5</v>
       </c>
     </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-02-08 12:00:00</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Deadlift</t>
+        </is>
+      </c>
+      <c r="C200" t="n">
+        <v>70</v>
+      </c>
+      <c r="D200" t="n">
+        <v>6</v>
+      </c>
+      <c r="E200" t="n">
+        <v>420</v>
+      </c>
+      <c r="F200" t="n">
+        <v>6</v>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>Warm up/Primer</t>
+        </is>
+      </c>
+      <c r="H200" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-02-08 12:00:00</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Deadlift</t>
+        </is>
+      </c>
+      <c r="C201" t="n">
+        <v>90</v>
+      </c>
+      <c r="D201" t="n">
+        <v>5</v>
+      </c>
+      <c r="E201" t="n">
+        <v>450</v>
+      </c>
+      <c r="F201" t="n">
+        <v>7</v>
+      </c>
+      <c r="G201" t="inlineStr"/>
+      <c r="H201" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-02-08 12:00:00</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Deadlift</t>
+        </is>
+      </c>
+      <c r="C202" t="n">
+        <v>120</v>
+      </c>
+      <c r="D202" t="n">
+        <v>5</v>
+      </c>
+      <c r="E202" t="n">
+        <v>600</v>
+      </c>
+      <c r="F202" t="n">
+        <v>8</v>
+      </c>
+      <c r="G202" t="inlineStr"/>
+      <c r="H202" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-02-08 12:00:00</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Deadlift</t>
+        </is>
+      </c>
+      <c r="C203" t="n">
+        <v>120</v>
+      </c>
+      <c r="D203" t="n">
+        <v>5</v>
+      </c>
+      <c r="E203" t="n">
+        <v>600</v>
+      </c>
+      <c r="F203" t="n">
+        <v>8</v>
+      </c>
+      <c r="G203" t="inlineStr"/>
+      <c r="H203" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-02-08 12:00:00</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Deadlift</t>
+        </is>
+      </c>
+      <c r="C204" t="n">
+        <v>120</v>
+      </c>
+      <c r="D204" t="n">
+        <v>5</v>
+      </c>
+      <c r="E204" t="n">
+        <v>600</v>
+      </c>
+      <c r="F204" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G204" t="inlineStr"/>
+      <c r="H204" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-02-08 12:00:00</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Deadlift</t>
+        </is>
+      </c>
+      <c r="C205" t="n">
+        <v>120</v>
+      </c>
+      <c r="D205" t="n">
+        <v>5</v>
+      </c>
+      <c r="E205" t="n">
+        <v>600</v>
+      </c>
+      <c r="F205" t="n">
+        <v>9</v>
+      </c>
+      <c r="G205" t="inlineStr"/>
+      <c r="H205" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-02-08 12:00:00</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Deadlift</t>
+        </is>
+      </c>
+      <c r="C206" t="n">
+        <v>120</v>
+      </c>
+      <c r="D206" t="n">
+        <v>5</v>
+      </c>
+      <c r="E206" t="n">
+        <v>600</v>
+      </c>
+      <c r="F206" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G206" t="inlineStr"/>
+      <c r="H206" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-02-08 12:00:00</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>BTN Press</t>
+        </is>
+      </c>
+      <c r="C207" t="n">
+        <v>20</v>
+      </c>
+      <c r="D207" t="n">
+        <v>12</v>
+      </c>
+      <c r="E207" t="n">
+        <v>240</v>
+      </c>
+      <c r="F207" t="n">
+        <v>6</v>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>Thoracic extension focus</t>
+        </is>
+      </c>
+      <c r="H207" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-02-08 12:00:00</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Overhead Press</t>
+        </is>
+      </c>
+      <c r="C208" t="n">
+        <v>30</v>
+      </c>
+      <c r="D208" t="n">
+        <v>10</v>
+      </c>
+      <c r="E208" t="n">
+        <v>300</v>
+      </c>
+      <c r="F208" t="n">
+        <v>6</v>
+      </c>
+      <c r="G208" t="inlineStr"/>
+      <c r="H208" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-02-08 12:00:00</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Overhead Press</t>
+        </is>
+      </c>
+      <c r="C209" t="n">
+        <v>35</v>
+      </c>
+      <c r="D209" t="n">
+        <v>10</v>
+      </c>
+      <c r="E209" t="n">
+        <v>350</v>
+      </c>
+      <c r="F209" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="G209" t="inlineStr"/>
+      <c r="H209" t="n">
+        <v>46.66666666666666</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-02-08 12:00:00</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Overhead Press</t>
+        </is>
+      </c>
+      <c r="C210" t="n">
+        <v>35</v>
+      </c>
+      <c r="D210" t="n">
+        <v>10</v>
+      </c>
+      <c r="E210" t="n">
+        <v>350</v>
+      </c>
+      <c r="F210" t="n">
+        <v>8</v>
+      </c>
+      <c r="G210" t="inlineStr"/>
+      <c r="H210" t="n">
+        <v>46.66666666666666</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-02-08 12:00:00</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Overhead Press</t>
+        </is>
+      </c>
+      <c r="C211" t="n">
+        <v>35</v>
+      </c>
+      <c r="D211" t="n">
+        <v>10</v>
+      </c>
+      <c r="E211" t="n">
+        <v>350</v>
+      </c>
+      <c r="F211" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G211" t="inlineStr"/>
+      <c r="H211" t="n">
+        <v>46.66666666666666</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-02-08 12:00:00</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Bicep Curl</t>
+        </is>
+      </c>
+      <c r="C212" t="n">
+        <v>22</v>
+      </c>
+      <c r="D212" t="n">
+        <v>8</v>
+      </c>
+      <c r="E212" t="n">
+        <v>176</v>
+      </c>
+      <c r="F212" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>Superset A</t>
+        </is>
+      </c>
+      <c r="H212" t="n">
+        <v>27.86666666666667</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-02-08 12:00:00</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Tricep Extension</t>
+        </is>
+      </c>
+      <c r="C213" t="n">
+        <v>22</v>
+      </c>
+      <c r="D213" t="n">
+        <v>12</v>
+      </c>
+      <c r="E213" t="n">
+        <v>264</v>
+      </c>
+      <c r="F213" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>Superset B</t>
+        </is>
+      </c>
+      <c r="H213" t="n">
+        <v>30.8</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2026-02-08 12:00:00</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Bicep Curl</t>
+        </is>
+      </c>
+      <c r="C214" t="n">
+        <v>22</v>
+      </c>
+      <c r="D214" t="n">
+        <v>8</v>
+      </c>
+      <c r="E214" t="n">
+        <v>176</v>
+      </c>
+      <c r="F214" t="n">
+        <v>8</v>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>Superset A</t>
+        </is>
+      </c>
+      <c r="H214" t="n">
+        <v>27.86666666666667</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2026-02-08 12:00:00</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Tricep Extension</t>
+        </is>
+      </c>
+      <c r="C215" t="n">
+        <v>22</v>
+      </c>
+      <c r="D215" t="n">
+        <v>12</v>
+      </c>
+      <c r="E215" t="n">
+        <v>264</v>
+      </c>
+      <c r="F215" t="n">
+        <v>8</v>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>Superset B</t>
+        </is>
+      </c>
+      <c r="H215" t="n">
+        <v>30.8</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2026-02-08 12:00:00</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Bicep Curl</t>
+        </is>
+      </c>
+      <c r="C216" t="n">
+        <v>22</v>
+      </c>
+      <c r="D216" t="n">
+        <v>8</v>
+      </c>
+      <c r="E216" t="n">
+        <v>176</v>
+      </c>
+      <c r="F216" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>Superset A</t>
+        </is>
+      </c>
+      <c r="H216" t="n">
+        <v>27.86666666666667</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2026-02-08 12:00:00</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Tricep Extension</t>
+        </is>
+      </c>
+      <c r="C217" t="n">
+        <v>22</v>
+      </c>
+      <c r="D217" t="n">
+        <v>12</v>
+      </c>
+      <c r="E217" t="n">
+        <v>264</v>
+      </c>
+      <c r="F217" t="n">
+        <v>8</v>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>Superset B</t>
+        </is>
+      </c>
+      <c r="H217" t="n">
+        <v>30.8</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2026-02-08 12:00:00</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Assisted Pull-up</t>
+        </is>
+      </c>
+      <c r="C218" t="n">
+        <v>25</v>
+      </c>
+      <c r="D218" t="n">
+        <v>8</v>
+      </c>
+      <c r="E218" t="n">
+        <v>200</v>
+      </c>
+      <c r="F218" t="n">
+        <v>8</v>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>Superset C</t>
+        </is>
+      </c>
+      <c r="H218" t="n">
+        <v>31.66666666666666</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2026-02-08 12:00:00</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Assisted Dip</t>
+        </is>
+      </c>
+      <c r="C219" t="n">
+        <v>25</v>
+      </c>
+      <c r="D219" t="n">
+        <v>8</v>
+      </c>
+      <c r="E219" t="n">
+        <v>200</v>
+      </c>
+      <c r="F219" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>Superset D</t>
+        </is>
+      </c>
+      <c r="H219" t="n">
+        <v>31.66666666666666</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2026-02-08 12:00:00</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Assisted Pull-up</t>
+        </is>
+      </c>
+      <c r="C220" t="n">
+        <v>25</v>
+      </c>
+      <c r="D220" t="n">
+        <v>8</v>
+      </c>
+      <c r="E220" t="n">
+        <v>200</v>
+      </c>
+      <c r="F220" t="n">
+        <v>8</v>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>Superset C</t>
+        </is>
+      </c>
+      <c r="H220" t="n">
+        <v>31.66666666666666</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2026-02-08 12:00:00</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Assisted Dip</t>
+        </is>
+      </c>
+      <c r="C221" t="n">
+        <v>25</v>
+      </c>
+      <c r="D221" t="n">
+        <v>8</v>
+      </c>
+      <c r="E221" t="n">
+        <v>200</v>
+      </c>
+      <c r="F221" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>Superset D</t>
+        </is>
+      </c>
+      <c r="H221" t="n">
+        <v>31.66666666666666</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2026-02-08 12:00:00</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Assisted Pull-up</t>
+        </is>
+      </c>
+      <c r="C222" t="n">
+        <v>25</v>
+      </c>
+      <c r="D222" t="n">
+        <v>8</v>
+      </c>
+      <c r="E222" t="n">
+        <v>200</v>
+      </c>
+      <c r="F222" t="n">
+        <v>9</v>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>Superset C</t>
+        </is>
+      </c>
+      <c r="H222" t="n">
+        <v>31.66666666666666</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2026-02-08 12:00:00</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Assisted Dip</t>
+        </is>
+      </c>
+      <c r="C223" t="n">
+        <v>25</v>
+      </c>
+      <c r="D223" t="n">
+        <v>8</v>
+      </c>
+      <c r="E223" t="n">
+        <v>200</v>
+      </c>
+      <c r="F223" t="n">
+        <v>9</v>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>Superset D</t>
+        </is>
+      </c>
+      <c r="H223" t="n">
+        <v>31.66666666666666</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2026-02-10 21:00:00</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Back Squat</t>
+        </is>
+      </c>
+      <c r="C224" t="n">
+        <v>70</v>
+      </c>
+      <c r="D224" t="n">
+        <v>6</v>
+      </c>
+      <c r="E224" t="n">
+        <v>420</v>
+      </c>
+      <c r="F224" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>Warm-up</t>
+        </is>
+      </c>
+      <c r="H224" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2026-02-10 21:00:00</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Back Squat</t>
+        </is>
+      </c>
+      <c r="C225" t="n">
+        <v>85</v>
+      </c>
+      <c r="D225" t="n">
+        <v>12</v>
+      </c>
+      <c r="E225" t="n">
+        <v>1020</v>
+      </c>
+      <c r="F225" t="n">
+        <v>8</v>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>Working set 1</t>
+        </is>
+      </c>
+      <c r="H225" t="n">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2026-02-10 21:00:00</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Back Squat</t>
+        </is>
+      </c>
+      <c r="C226" t="n">
+        <v>85</v>
+      </c>
+      <c r="D226" t="n">
+        <v>12</v>
+      </c>
+      <c r="E226" t="n">
+        <v>1020</v>
+      </c>
+      <c r="F226" t="n">
+        <v>9</v>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>Working set 2</t>
+        </is>
+      </c>
+      <c r="H226" t="n">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2026-02-10 21:00:00</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Back Squat</t>
+        </is>
+      </c>
+      <c r="C227" t="n">
+        <v>85</v>
+      </c>
+      <c r="D227" t="n">
+        <v>10</v>
+      </c>
+      <c r="E227" t="n">
+        <v>850</v>
+      </c>
+      <c r="F227" t="n">
+        <v>10</v>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>Failed 11th rep</t>
+        </is>
+      </c>
+      <c r="H227" t="n">
+        <v>113.3333333333333</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2026-02-10 21:00:00</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>BTN Press</t>
+        </is>
+      </c>
+      <c r="C228" t="n">
+        <v>30</v>
+      </c>
+      <c r="D228" t="n">
+        <v>6</v>
+      </c>
+      <c r="E228" t="n">
+        <v>180</v>
+      </c>
+      <c r="F228" t="n">
+        <v>6</v>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>Mobility check</t>
+        </is>
+      </c>
+      <c r="H228" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2026-02-10 21:00:00</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Standing OHP</t>
+        </is>
+      </c>
+      <c r="C229" t="n">
+        <v>30</v>
+      </c>
+      <c r="D229" t="n">
+        <v>8</v>
+      </c>
+      <c r="E229" t="n">
+        <v>240</v>
+      </c>
+      <c r="F229" t="n">
+        <v>6</v>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>Warm-up</t>
+        </is>
+      </c>
+      <c r="H229" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2026-02-10 21:00:00</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Standing OHP</t>
+        </is>
+      </c>
+      <c r="C230" t="n">
+        <v>40</v>
+      </c>
+      <c r="D230" t="n">
+        <v>8</v>
+      </c>
+      <c r="E230" t="n">
+        <v>320</v>
+      </c>
+      <c r="F230" t="n">
+        <v>8</v>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>Working set 1</t>
+        </is>
+      </c>
+      <c r="H230" t="n">
+        <v>50.66666666666666</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2026-02-10 21:00:00</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Standing OHP</t>
+        </is>
+      </c>
+      <c r="C231" t="n">
+        <v>40</v>
+      </c>
+      <c r="D231" t="n">
+        <v>8</v>
+      </c>
+      <c r="E231" t="n">
+        <v>320</v>
+      </c>
+      <c r="F231" t="n">
+        <v>9</v>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>Working set 2</t>
+        </is>
+      </c>
+      <c r="H231" t="n">
+        <v>50.66666666666666</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2026-02-10 21:00:00</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Standing OHP</t>
+        </is>
+      </c>
+      <c r="C232" t="n">
+        <v>40</v>
+      </c>
+      <c r="D232" t="n">
+        <v>7</v>
+      </c>
+      <c r="E232" t="n">
+        <v>280</v>
+      </c>
+      <c r="F232" t="n">
+        <v>10</v>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>Failed 8th rep</t>
+        </is>
+      </c>
+      <c r="H232" t="n">
+        <v>49.33333333333334</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2026-02-10 21:00:00</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Bent Over Row</t>
+        </is>
+      </c>
+      <c r="C233" t="n">
+        <v>40</v>
+      </c>
+      <c r="D233" t="n">
+        <v>12</v>
+      </c>
+      <c r="E233" t="n">
+        <v>480</v>
+      </c>
+      <c r="F233" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>Back set 1</t>
+        </is>
+      </c>
+      <c r="H233" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2026-02-10 21:00:00</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Bent Over Row</t>
+        </is>
+      </c>
+      <c r="C234" t="n">
+        <v>40</v>
+      </c>
+      <c r="D234" t="n">
+        <v>12</v>
+      </c>
+      <c r="E234" t="n">
+        <v>480</v>
+      </c>
+      <c r="F234" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>Back set 2</t>
+        </is>
+      </c>
+      <c r="H234" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2026-02-10 21:00:00</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Bent Over Row</t>
+        </is>
+      </c>
+      <c r="C235" t="n">
+        <v>40</v>
+      </c>
+      <c r="D235" t="n">
+        <v>12</v>
+      </c>
+      <c r="E235" t="n">
+        <v>480</v>
+      </c>
+      <c r="F235" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>Back set 3</t>
+        </is>
+      </c>
+      <c r="H235" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2026-02-10 21:00:00</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Bent Over Row</t>
+        </is>
+      </c>
+      <c r="C236" t="n">
+        <v>40</v>
+      </c>
+      <c r="D236" t="n">
+        <v>12</v>
+      </c>
+      <c r="E236" t="n">
+        <v>480</v>
+      </c>
+      <c r="F236" t="n">
+        <v>9</v>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>Back set 4</t>
+        </is>
+      </c>
+      <c r="H236" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2026-02-10 21:00:00</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Assisted Pullups</t>
+        </is>
+      </c>
+      <c r="C237" t="n">
+        <v>60</v>
+      </c>
+      <c r="D237" t="n">
+        <v>10</v>
+      </c>
+      <c r="E237" t="n">
+        <v>600</v>
+      </c>
+      <c r="F237" t="n">
+        <v>8</v>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>Superset A1</t>
+        </is>
+      </c>
+      <c r="H237" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2026-02-10 21:00:00</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Assisted Dips</t>
+        </is>
+      </c>
+      <c r="C238" t="n">
+        <v>60</v>
+      </c>
+      <c r="D238" t="n">
+        <v>10</v>
+      </c>
+      <c r="E238" t="n">
+        <v>600</v>
+      </c>
+      <c r="F238" t="n">
+        <v>7</v>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>Superset B1</t>
+        </is>
+      </c>
+      <c r="H238" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2026-02-10 21:00:00</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Assisted Pullups</t>
+        </is>
+      </c>
+      <c r="C239" t="n">
+        <v>60</v>
+      </c>
+      <c r="D239" t="n">
+        <v>10</v>
+      </c>
+      <c r="E239" t="n">
+        <v>600</v>
+      </c>
+      <c r="F239" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>Superset A2</t>
+        </is>
+      </c>
+      <c r="H239" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2026-02-10 21:00:00</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Assisted Dips</t>
+        </is>
+      </c>
+      <c r="C240" t="n">
+        <v>60</v>
+      </c>
+      <c r="D240" t="n">
+        <v>10</v>
+      </c>
+      <c r="E240" t="n">
+        <v>600</v>
+      </c>
+      <c r="F240" t="n">
+        <v>8</v>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>Superset B2</t>
+        </is>
+      </c>
+      <c r="H240" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2026-02-10 21:00:00</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Assisted Pullups</t>
+        </is>
+      </c>
+      <c r="C241" t="n">
+        <v>60</v>
+      </c>
+      <c r="D241" t="n">
+        <v>10</v>
+      </c>
+      <c r="E241" t="n">
+        <v>600</v>
+      </c>
+      <c r="F241" t="n">
+        <v>9</v>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>Superset A3</t>
+        </is>
+      </c>
+      <c r="H241" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2026-02-10 21:00:00</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Assisted Dips</t>
+        </is>
+      </c>
+      <c r="C242" t="n">
+        <v>60</v>
+      </c>
+      <c r="D242" t="n">
+        <v>10</v>
+      </c>
+      <c r="E242" t="n">
+        <v>600</v>
+      </c>
+      <c r="F242" t="n">
+        <v>9</v>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>Superset B3</t>
+        </is>
+      </c>
+      <c r="H242" t="n">
+        <v>80</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/workout_log.xlsx
+++ b/data/workout_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H271"/>
+  <dimension ref="A1:H293"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8750,6 +8750,622 @@
         <v>34</v>
       </c>
     </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-02-22 14:00:00</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Squat</t>
+        </is>
+      </c>
+      <c r="C272" t="n">
+        <v>20</v>
+      </c>
+      <c r="D272" t="n">
+        <v>12</v>
+      </c>
+      <c r="E272" t="n">
+        <v>240</v>
+      </c>
+      <c r="F272" t="n">
+        <v>3</v>
+      </c>
+      <c r="G272" t="inlineStr"/>
+      <c r="H272" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-02-22 14:00:00</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Squat</t>
+        </is>
+      </c>
+      <c r="C273" t="n">
+        <v>60</v>
+      </c>
+      <c r="D273" t="n">
+        <v>8</v>
+      </c>
+      <c r="E273" t="n">
+        <v>480</v>
+      </c>
+      <c r="F273" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="G273" t="inlineStr"/>
+      <c r="H273" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-02-22 14:00:00</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Squat</t>
+        </is>
+      </c>
+      <c r="C274" t="n">
+        <v>100</v>
+      </c>
+      <c r="D274" t="n">
+        <v>2</v>
+      </c>
+      <c r="E274" t="n">
+        <v>200</v>
+      </c>
+      <c r="F274" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G274" t="inlineStr"/>
+      <c r="H274" t="n">
+        <v>106.6666666666667</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-02-22 14:00:00</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Squat</t>
+        </is>
+      </c>
+      <c r="C275" t="n">
+        <v>100</v>
+      </c>
+      <c r="D275" t="n">
+        <v>5</v>
+      </c>
+      <c r="E275" t="n">
+        <v>500</v>
+      </c>
+      <c r="F275" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="G275" t="inlineStr"/>
+      <c r="H275" t="n">
+        <v>116.6666666666667</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-02-22 14:00:00</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Squat</t>
+        </is>
+      </c>
+      <c r="C276" t="n">
+        <v>60</v>
+      </c>
+      <c r="D276" t="n">
+        <v>20</v>
+      </c>
+      <c r="E276" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F276" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="G276" t="inlineStr"/>
+      <c r="H276" t="n">
+        <v>99.99999999999999</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-02-22 14:00:00</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Squat</t>
+        </is>
+      </c>
+      <c r="C277" t="n">
+        <v>90</v>
+      </c>
+      <c r="D277" t="n">
+        <v>8</v>
+      </c>
+      <c r="E277" t="n">
+        <v>720</v>
+      </c>
+      <c r="F277" t="n">
+        <v>8</v>
+      </c>
+      <c r="G277" t="inlineStr"/>
+      <c r="H277" t="n">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-02-22 14:00:00</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Squat</t>
+        </is>
+      </c>
+      <c r="C278" t="n">
+        <v>110</v>
+      </c>
+      <c r="D278" t="n">
+        <v>1</v>
+      </c>
+      <c r="E278" t="n">
+        <v>110</v>
+      </c>
+      <c r="F278" t="n">
+        <v>8</v>
+      </c>
+      <c r="G278" t="inlineStr"/>
+      <c r="H278" t="n">
+        <v>113.6666666666667</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-02-22 14:00:00</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>BTN Press</t>
+        </is>
+      </c>
+      <c r="C279" t="n">
+        <v>30</v>
+      </c>
+      <c r="D279" t="n">
+        <v>8</v>
+      </c>
+      <c r="E279" t="n">
+        <v>240</v>
+      </c>
+      <c r="F279" t="n">
+        <v>7</v>
+      </c>
+      <c r="G279" t="inlineStr"/>
+      <c r="H279" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-02-22 14:00:00</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>OHP</t>
+        </is>
+      </c>
+      <c r="C280" t="n">
+        <v>40</v>
+      </c>
+      <c r="D280" t="n">
+        <v>8</v>
+      </c>
+      <c r="E280" t="n">
+        <v>320</v>
+      </c>
+      <c r="F280" t="n">
+        <v>8</v>
+      </c>
+      <c r="G280" t="inlineStr"/>
+      <c r="H280" t="n">
+        <v>50.66666666666666</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-02-22 14:00:00</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>OHP</t>
+        </is>
+      </c>
+      <c r="C281" t="n">
+        <v>40</v>
+      </c>
+      <c r="D281" t="n">
+        <v>6</v>
+      </c>
+      <c r="E281" t="n">
+        <v>240</v>
+      </c>
+      <c r="F281" t="n">
+        <v>10</v>
+      </c>
+      <c r="G281" t="inlineStr"/>
+      <c r="H281" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>2026-02-22 14:00:00</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>OHP</t>
+        </is>
+      </c>
+      <c r="C282" t="n">
+        <v>30</v>
+      </c>
+      <c r="D282" t="n">
+        <v>13</v>
+      </c>
+      <c r="E282" t="n">
+        <v>390</v>
+      </c>
+      <c r="F282" t="n">
+        <v>10</v>
+      </c>
+      <c r="G282" t="inlineStr"/>
+      <c r="H282" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>2026-02-22 14:00:00</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Barbell Row</t>
+        </is>
+      </c>
+      <c r="C283" t="n">
+        <v>30</v>
+      </c>
+      <c r="D283" t="n">
+        <v>20</v>
+      </c>
+      <c r="E283" t="n">
+        <v>600</v>
+      </c>
+      <c r="F283" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G283" t="inlineStr"/>
+      <c r="H283" t="n">
+        <v>49.99999999999999</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>2026-02-22 14:00:00</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Barbell Row</t>
+        </is>
+      </c>
+      <c r="C284" t="n">
+        <v>40</v>
+      </c>
+      <c r="D284" t="n">
+        <v>12</v>
+      </c>
+      <c r="E284" t="n">
+        <v>480</v>
+      </c>
+      <c r="F284" t="n">
+        <v>7</v>
+      </c>
+      <c r="G284" t="inlineStr"/>
+      <c r="H284" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>2026-02-22 14:00:00</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Barbell Row</t>
+        </is>
+      </c>
+      <c r="C285" t="n">
+        <v>40</v>
+      </c>
+      <c r="D285" t="n">
+        <v>12</v>
+      </c>
+      <c r="E285" t="n">
+        <v>480</v>
+      </c>
+      <c r="F285" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="G285" t="inlineStr"/>
+      <c r="H285" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>2026-02-22 14:00:00</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Barbell Row</t>
+        </is>
+      </c>
+      <c r="C286" t="n">
+        <v>40</v>
+      </c>
+      <c r="D286" t="n">
+        <v>12</v>
+      </c>
+      <c r="E286" t="n">
+        <v>480</v>
+      </c>
+      <c r="F286" t="n">
+        <v>8</v>
+      </c>
+      <c r="G286" t="inlineStr"/>
+      <c r="H286" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>2026-02-22 14:00:00</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Barbell Row</t>
+        </is>
+      </c>
+      <c r="C287" t="n">
+        <v>40</v>
+      </c>
+      <c r="D287" t="n">
+        <v>12</v>
+      </c>
+      <c r="E287" t="n">
+        <v>480</v>
+      </c>
+      <c r="F287" t="n">
+        <v>9</v>
+      </c>
+      <c r="G287" t="inlineStr"/>
+      <c r="H287" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>2026-02-22 14:00:00</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Assisted Pullup</t>
+        </is>
+      </c>
+      <c r="C288" t="n">
+        <v>60</v>
+      </c>
+      <c r="D288" t="n">
+        <v>8</v>
+      </c>
+      <c r="E288" t="n">
+        <v>480</v>
+      </c>
+      <c r="F288" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="G288" t="inlineStr"/>
+      <c r="H288" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>2026-02-22 14:00:00</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Assisted Dip</t>
+        </is>
+      </c>
+      <c r="C289" t="n">
+        <v>60</v>
+      </c>
+      <c r="D289" t="n">
+        <v>8</v>
+      </c>
+      <c r="E289" t="n">
+        <v>480</v>
+      </c>
+      <c r="F289" t="n">
+        <v>7</v>
+      </c>
+      <c r="G289" t="inlineStr"/>
+      <c r="H289" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2026-02-22 14:00:00</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Assisted Pullup</t>
+        </is>
+      </c>
+      <c r="C290" t="n">
+        <v>60</v>
+      </c>
+      <c r="D290" t="n">
+        <v>8</v>
+      </c>
+      <c r="E290" t="n">
+        <v>480</v>
+      </c>
+      <c r="F290" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G290" t="inlineStr"/>
+      <c r="H290" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2026-02-22 14:00:00</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Assisted Dip</t>
+        </is>
+      </c>
+      <c r="C291" t="n">
+        <v>60</v>
+      </c>
+      <c r="D291" t="n">
+        <v>8</v>
+      </c>
+      <c r="E291" t="n">
+        <v>480</v>
+      </c>
+      <c r="F291" t="n">
+        <v>8</v>
+      </c>
+      <c r="G291" t="inlineStr"/>
+      <c r="H291" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2026-02-22 14:00:00</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Assisted Pullup</t>
+        </is>
+      </c>
+      <c r="C292" t="n">
+        <v>60</v>
+      </c>
+      <c r="D292" t="n">
+        <v>8</v>
+      </c>
+      <c r="E292" t="n">
+        <v>480</v>
+      </c>
+      <c r="F292" t="n">
+        <v>9</v>
+      </c>
+      <c r="G292" t="inlineStr"/>
+      <c r="H292" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2026-02-22 14:00:00</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Assisted Dip</t>
+        </is>
+      </c>
+      <c r="C293" t="n">
+        <v>60</v>
+      </c>
+      <c r="D293" t="n">
+        <v>8</v>
+      </c>
+      <c r="E293" t="n">
+        <v>480</v>
+      </c>
+      <c r="F293" t="n">
+        <v>9</v>
+      </c>
+      <c r="G293" t="inlineStr"/>
+      <c r="H293" t="n">
+        <v>76</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/workout_log.xlsx
+++ b/data/workout_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H293"/>
+  <dimension ref="A1:H307"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6613,401 +6613,449 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2026-01-26 21:38:00</t>
+          <t>2026-02-25 20:30:00</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Run</t>
+          <t>Squats</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D200" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E200" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="F200" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>5 mins at 5:00/km pace</t>
+          <t>Warm-up</t>
         </is>
       </c>
       <c r="H200" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2026-01-26 21:38:00</t>
+          <t>2026-02-25 20:30:00</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Standing Overhead Press</t>
+          <t>Squats</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="D201" t="n">
         <v>8</v>
       </c>
       <c r="E201" t="n">
-        <v>240</v>
+        <v>480</v>
       </c>
       <c r="F201" t="n">
         <v>6</v>
       </c>
-      <c r="G201" t="inlineStr"/>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>Working set</t>
+        </is>
+      </c>
       <c r="H201" t="n">
-        <v>38</v>
+        <v>76</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2026-01-26 21:38:00</t>
+          <t>2026-02-25 20:30:00</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Standing Overhead Press</t>
+          <t>Squats</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>30</v>
+        <v>110</v>
       </c>
       <c r="D202" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E202" t="n">
-        <v>240</v>
+        <v>330</v>
       </c>
       <c r="F202" t="n">
-        <v>6</v>
-      </c>
-      <c r="G202" t="inlineStr"/>
+        <v>7.5</v>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>Heavy triple</t>
+        </is>
+      </c>
       <c r="H202" t="n">
-        <v>38</v>
+        <v>121</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2026-01-26 21:38:00</t>
+          <t>2026-02-25 20:30:00</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Standing Overhead Press</t>
+          <t>Squats</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="D203" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E203" t="n">
-        <v>240</v>
+        <v>1400</v>
       </c>
       <c r="F203" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="G203" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>3-minute set; endurance diagnostic</t>
+        </is>
+      </c>
       <c r="H203" t="n">
-        <v>38</v>
+        <v>116.6666666666667</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2026-01-26 21:38:00</t>
+          <t>2026-02-25 20:30:00</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Standing Overhead Press</t>
+          <t>Squats</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="D204" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E204" t="n">
-        <v>240</v>
+        <v>960</v>
       </c>
       <c r="F204" t="n">
-        <v>8</v>
-      </c>
-      <c r="G204" t="inlineStr"/>
+        <v>8.5</v>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>150s; Track: Pain - Dancing with the Dead</t>
+        </is>
+      </c>
       <c r="H204" t="n">
-        <v>38</v>
+        <v>112</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2026-01-26 21:38:00</t>
+          <t>2026-02-25 20:30:00</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Bent over barbell row</t>
+          <t>Deadlift</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="D205" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E205" t="n">
-        <v>450</v>
+        <v>600</v>
       </c>
       <c r="F205" t="n">
-        <v>4</v>
-      </c>
-      <c r="G205" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>Technical set</t>
+        </is>
+      </c>
       <c r="H205" t="n">
-        <v>45</v>
+        <v>80</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2026-01-26 21:38:00</t>
+          <t>2026-02-25 20:30:00</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Bent over barbell row</t>
+          <t>Deadlift</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>30</v>
+        <v>110</v>
       </c>
       <c r="D206" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E206" t="n">
-        <v>450</v>
+        <v>550</v>
       </c>
       <c r="F206" t="n">
-        <v>5</v>
-      </c>
-      <c r="G206" t="inlineStr"/>
+        <v>6.5</v>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>Working set</t>
+        </is>
+      </c>
       <c r="H206" t="n">
-        <v>45</v>
+        <v>128.3333333333333</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2026-01-26 21:38:00</t>
+          <t>2026-02-25 20:30:00</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Bent over barbell row</t>
+          <t>Deadlift</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>30</v>
+        <v>140</v>
       </c>
       <c r="D207" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E207" t="n">
-        <v>450</v>
+        <v>140</v>
       </c>
       <c r="F207" t="n">
-        <v>6</v>
-      </c>
-      <c r="G207" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>Heavy single</t>
+        </is>
+      </c>
       <c r="H207" t="n">
-        <v>45</v>
+        <v>144.6666666666667</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2026-01-26 21:38:00</t>
+          <t>2026-02-25 20:30:00</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Bent over barbell row</t>
+          <t>Deadlift</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>30</v>
+        <v>160</v>
       </c>
       <c r="D208" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E208" t="n">
-        <v>450</v>
+        <v>160</v>
       </c>
       <c r="F208" t="n">
-        <v>8</v>
-      </c>
-      <c r="G208" t="inlineStr"/>
+        <v>8.5</v>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>Heavy single; Track: Arch Enemy - War Eternal</t>
+        </is>
+      </c>
       <c r="H208" t="n">
-        <v>45</v>
+        <v>165.3333333333333</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2026-01-26 21:38:00</t>
+          <t>2026-02-25 20:30:00</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>RDL</t>
+          <t>Deadlift</t>
         </is>
       </c>
       <c r="C209" t="n">
-        <v>30</v>
+        <v>170</v>
       </c>
       <c r="D209" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E209" t="n">
-        <v>450</v>
+        <v>170</v>
       </c>
       <c r="F209" t="n">
-        <v>4</v>
-      </c>
-      <c r="G209" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>Top Single; Track: Rammstein - Deutschland</t>
+        </is>
+      </c>
       <c r="H209" t="n">
-        <v>45</v>
+        <v>175.6666666666667</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2026-01-26 21:38:00</t>
+          <t>2026-02-25 20:30:00</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>RDL</t>
+          <t>Overhead Press</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="D210" t="n">
         <v>10</v>
       </c>
       <c r="E210" t="n">
-        <v>700</v>
+        <v>300</v>
       </c>
       <c r="F210" t="n">
-        <v>6</v>
-      </c>
-      <c r="G210" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
       <c r="H210" t="n">
-        <v>93.33333333333333</v>
+        <v>40</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2026-01-26 21:38:00</t>
+          <t>2026-02-25 20:30:00</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>RDL</t>
+          <t>Overhead Press</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="D211" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E211" t="n">
-        <v>700</v>
+        <v>120</v>
       </c>
       <c r="F211" t="n">
         <v>7</v>
       </c>
-      <c r="G211" t="inlineStr"/>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>Strength set</t>
+        </is>
+      </c>
       <c r="H211" t="n">
-        <v>93.33333333333333</v>
+        <v>44</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2026-01-26 21:38:00</t>
+          <t>2026-02-25 20:30:00</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>RDL</t>
+          <t>Overhead Press</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="D212" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E212" t="n">
-        <v>700</v>
+        <v>100</v>
       </c>
       <c r="F212" t="n">
-        <v>8</v>
-      </c>
-      <c r="G212" t="inlineStr"/>
+        <v>9.5</v>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>Top Double</t>
+        </is>
+      </c>
       <c r="H212" t="n">
-        <v>93.33333333333333</v>
+        <v>53.33333333333334</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2026-01-26 21:38:00</t>
+          <t>2026-02-25 20:30:00</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Cable Tricep Pushdown</t>
+          <t>Overhead Press</t>
         </is>
       </c>
       <c r="C213" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="D213" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E213" t="n">
-        <v>460</v>
+        <v>400</v>
       </c>
       <c r="F213" t="n">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Superset A</t>
+          <t>Back-off volume</t>
         </is>
       </c>
       <c r="H213" t="n">
-        <v>38.33333333333333</v>
+        <v>53.33333333333333</v>
       </c>
     </row>
     <row r="214">
@@ -7018,28 +7066,28 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Cable Bicep Curl</t>
+          <t>Run</t>
         </is>
       </c>
       <c r="C214" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="D214" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E214" t="n">
-        <v>460</v>
+        <v>0</v>
       </c>
       <c r="F214" t="n">
         <v>7</v>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Superset B</t>
+          <t>5 mins at 5:00/km pace</t>
         </is>
       </c>
       <c r="H214" t="n">
-        <v>38.33333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="215">
@@ -7050,28 +7098,24 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Cable Tricep Pushdown</t>
+          <t>Standing Overhead Press</t>
         </is>
       </c>
       <c r="C215" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D215" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E215" t="n">
-        <v>460</v>
+        <v>240</v>
       </c>
       <c r="F215" t="n">
-        <v>9</v>
-      </c>
-      <c r="G215" t="inlineStr">
-        <is>
-          <t>Superset A</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="G215" t="inlineStr"/>
       <c r="H215" t="n">
-        <v>38.33333333333333</v>
+        <v>38</v>
       </c>
     </row>
     <row r="216">
@@ -7082,28 +7126,24 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Cable Bicep Curl</t>
+          <t>Standing Overhead Press</t>
         </is>
       </c>
       <c r="C216" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D216" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E216" t="n">
-        <v>276</v>
+        <v>240</v>
       </c>
       <c r="F216" t="n">
-        <v>10</v>
-      </c>
-      <c r="G216" t="inlineStr">
-        <is>
-          <t>Superset B - failure at 12</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="G216" t="inlineStr"/>
       <c r="H216" t="n">
-        <v>32.2</v>
+        <v>38</v>
       </c>
     </row>
     <row r="217">
@@ -7114,24 +7154,24 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Kettlebell Swings</t>
+          <t>Standing Overhead Press</t>
         </is>
       </c>
       <c r="C217" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D217" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E217" t="n">
         <v>240</v>
       </c>
       <c r="F217" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="G217" t="inlineStr"/>
       <c r="H217" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
     </row>
     <row r="218">
@@ -7142,24 +7182,24 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Kettlebell Swings</t>
+          <t>Standing Overhead Press</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D218" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E218" t="n">
         <v>240</v>
       </c>
       <c r="F218" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="G218" t="inlineStr"/>
       <c r="H218" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
     </row>
     <row r="219">
@@ -7170,1558 +7210,1506 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Kettlebell Swings</t>
+          <t>Bent over barbell row</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D219" t="n">
         <v>15</v>
       </c>
       <c r="E219" t="n">
-        <v>300</v>
+        <v>450</v>
       </c>
       <c r="F219" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G219" t="inlineStr"/>
       <c r="H219" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2026-01-27 21:00:00</t>
+          <t>2026-01-26 21:38:00</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Incline DB Press</t>
+          <t>Bent over barbell row</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D220" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E220" t="n">
-        <v>360</v>
+        <v>450</v>
       </c>
       <c r="F220" t="n">
         <v>5</v>
       </c>
-      <c r="G220" t="inlineStr">
-        <is>
-          <t>18kg each hand</t>
-        </is>
-      </c>
+      <c r="G220" t="inlineStr"/>
       <c r="H220" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2026-01-27 21:00:00</t>
+          <t>2026-01-26 21:38:00</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Incline DB Press</t>
+          <t>Bent over barbell row</t>
         </is>
       </c>
       <c r="C221" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="D221" t="n">
+        <v>15</v>
+      </c>
+      <c r="E221" t="n">
+        <v>450</v>
+      </c>
+      <c r="F221" t="n">
         <v>6</v>
       </c>
-      <c r="E221" t="n">
-        <v>264</v>
-      </c>
-      <c r="F221" t="n">
-        <v>7</v>
-      </c>
-      <c r="G221" t="inlineStr">
-        <is>
-          <t>22kg each hand</t>
-        </is>
-      </c>
+      <c r="G221" t="inlineStr"/>
       <c r="H221" t="n">
-        <v>52.8</v>
+        <v>45</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2026-01-27 21:00:00</t>
+          <t>2026-01-26 21:38:00</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Incline DB Press</t>
+          <t>Bent over barbell row</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="D222" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E222" t="n">
-        <v>264</v>
+        <v>450</v>
       </c>
       <c r="F222" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="G222" t="inlineStr">
-        <is>
-          <t>22kg each hand</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="G222" t="inlineStr"/>
       <c r="H222" t="n">
-        <v>52.8</v>
+        <v>45</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2026-01-27 21:00:00</t>
+          <t>2026-01-26 21:38:00</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Incline DB Press</t>
+          <t>RDL</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="D223" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E223" t="n">
-        <v>264</v>
+        <v>450</v>
       </c>
       <c r="F223" t="n">
-        <v>8</v>
-      </c>
-      <c r="G223" t="inlineStr">
-        <is>
-          <t>22kg each hand</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="G223" t="inlineStr"/>
       <c r="H223" t="n">
-        <v>52.8</v>
+        <v>45</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2026-01-27 21:00:00</t>
+          <t>2026-01-26 21:38:00</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Deadlift</t>
+          <t>RDL</t>
         </is>
       </c>
       <c r="C224" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="D224" t="n">
         <v>10</v>
       </c>
       <c r="E224" t="n">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="F224" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G224" t="inlineStr"/>
       <c r="H224" t="n">
-        <v>80</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2026-01-27 21:00:00</t>
+          <t>2026-01-26 21:38:00</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Deadlift</t>
+          <t>RDL</t>
         </is>
       </c>
       <c r="C225" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="D225" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E225" t="n">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="F225" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G225" t="inlineStr"/>
       <c r="H225" t="n">
-        <v>120</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2026-01-27 21:00:00</t>
+          <t>2026-01-26 21:38:00</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Deadlift</t>
+          <t>RDL</t>
         </is>
       </c>
       <c r="C226" t="n">
-        <v>130</v>
+        <v>70</v>
       </c>
       <c r="D226" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E226" t="n">
-        <v>650</v>
+        <v>700</v>
       </c>
       <c r="F226" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G226" t="inlineStr"/>
       <c r="H226" t="n">
-        <v>151.6666666666667</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2026-01-27 21:00:00</t>
+          <t>2026-01-26 21:38:00</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Deadlift</t>
+          <t>Cable Tricep Pushdown</t>
         </is>
       </c>
       <c r="C227" t="n">
-        <v>140</v>
+        <v>23</v>
       </c>
       <c r="D227" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E227" t="n">
-        <v>140</v>
+        <v>460</v>
       </c>
       <c r="F227" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Failed on second rep</t>
+          <t>Superset A</t>
         </is>
       </c>
       <c r="H227" t="n">
-        <v>144.6666666666667</v>
+        <v>38.33333333333333</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2026-01-27 21:00:00</t>
+          <t>2026-01-26 21:38:00</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Deadlift</t>
+          <t>Cable Bicep Curl</t>
         </is>
       </c>
       <c r="C228" t="n">
-        <v>130</v>
+        <v>23</v>
       </c>
       <c r="D228" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="E228" t="n">
-        <v>260</v>
+        <v>460</v>
       </c>
       <c r="F228" t="n">
-        <v>8</v>
-      </c>
-      <c r="G228" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>Superset B</t>
+        </is>
+      </c>
       <c r="H228" t="n">
-        <v>138.6666666666667</v>
+        <v>38.33333333333333</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>2026-01-27 21:00:00</t>
+          <t>2026-01-26 21:38:00</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Deadlift</t>
+          <t>Cable Tricep Pushdown</t>
         </is>
       </c>
       <c r="C229" t="n">
-        <v>100</v>
+        <v>23</v>
       </c>
       <c r="D229" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E229" t="n">
-        <v>500</v>
+        <v>460</v>
       </c>
       <c r="F229" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="G229" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>Superset A</t>
+        </is>
+      </c>
       <c r="H229" t="n">
-        <v>116.6666666666667</v>
+        <v>38.33333333333333</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>2026-01-27 21:00:00</t>
+          <t>2026-01-26 21:38:00</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Deadlift</t>
+          <t>Cable Bicep Curl</t>
         </is>
       </c>
       <c r="C230" t="n">
-        <v>100</v>
+        <v>23</v>
       </c>
       <c r="D230" t="n">
+        <v>12</v>
+      </c>
+      <c r="E230" t="n">
+        <v>276</v>
+      </c>
+      <c r="F230" t="n">
         <v>10</v>
       </c>
-      <c r="E230" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F230" t="n">
-        <v>9</v>
-      </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Finisher set</t>
+          <t>Superset B - failure at 12</t>
         </is>
       </c>
       <c r="H230" t="n">
-        <v>133.3333333333333</v>
+        <v>32.2</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>2026-01-27 21:00:00</t>
+          <t>2026-01-26 21:38:00</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Behind the Neck Press</t>
+          <t>Kettlebell Swings</t>
         </is>
       </c>
       <c r="C231" t="n">
         <v>20</v>
       </c>
       <c r="D231" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E231" t="n">
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="F231" t="n">
-        <v>8</v>
-      </c>
-      <c r="G231" t="inlineStr">
-        <is>
-          <t>Superset Part 1</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="G231" t="inlineStr"/>
       <c r="H231" t="n">
-        <v>26.66666666666666</v>
+        <v>28</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>2026-01-27 21:00:00</t>
+          <t>2026-01-26 21:38:00</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Overhead Press</t>
+          <t>Kettlebell Swings</t>
         </is>
       </c>
       <c r="C232" t="n">
         <v>20</v>
       </c>
       <c r="D232" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E232" t="n">
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="F232" t="n">
-        <v>9</v>
-      </c>
-      <c r="G232" t="inlineStr">
-        <is>
-          <t>Superset Part 2</t>
-        </is>
-      </c>
+        <v>7.5</v>
+      </c>
+      <c r="G232" t="inlineStr"/>
       <c r="H232" t="n">
-        <v>26.66666666666666</v>
+        <v>28</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>2026-01-27 21:00:00</t>
+          <t>2026-01-26 21:38:00</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Overhead Press</t>
+          <t>Kettlebell Swings</t>
         </is>
       </c>
       <c r="C233" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D233" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E233" t="n">
-        <v>180</v>
+        <v>300</v>
       </c>
       <c r="F233" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G233" t="inlineStr"/>
       <c r="H233" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>2026-01-27 21:00:00</t>
+          <t>2026-02-22 14:00:00</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Overhead Press</t>
+          <t>Squat</t>
         </is>
       </c>
       <c r="C234" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="D234" t="n">
+        <v>12</v>
+      </c>
+      <c r="E234" t="n">
+        <v>240</v>
+      </c>
+      <c r="F234" t="n">
         <v>3</v>
-      </c>
-      <c r="E234" t="n">
-        <v>120</v>
-      </c>
-      <c r="F234" t="n">
-        <v>8</v>
       </c>
       <c r="G234" t="inlineStr"/>
       <c r="H234" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>2026-01-27 21:00:00</t>
+          <t>2026-02-22 14:00:00</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Overhead Press</t>
+          <t>Squat</t>
         </is>
       </c>
       <c r="C235" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="D235" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E235" t="n">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="F235" t="n">
-        <v>8</v>
+        <v>5.5</v>
       </c>
       <c r="G235" t="inlineStr"/>
       <c r="H235" t="n">
-        <v>44</v>
+        <v>76</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>2026-01-27 21:00:00</t>
+          <t>2026-02-22 14:00:00</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Overhead Press</t>
+          <t>Squat</t>
         </is>
       </c>
       <c r="C236" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="D236" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E236" t="n">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="F236" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="G236" t="inlineStr"/>
       <c r="H236" t="n">
-        <v>44</v>
+        <v>106.6666666666667</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>2026-01-27 21:00:00</t>
+          <t>2026-02-22 14:00:00</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Overhead Press</t>
+          <t>Squat</t>
         </is>
       </c>
       <c r="C237" t="n">
-        <v>45</v>
+        <v>100</v>
       </c>
       <c r="D237" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E237" t="n">
-        <v>45</v>
+        <v>500</v>
       </c>
       <c r="F237" t="n">
         <v>7.5</v>
       </c>
       <c r="G237" t="inlineStr"/>
       <c r="H237" t="n">
-        <v>46.50000000000001</v>
+        <v>116.6666666666667</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>2026-01-27 21:00:00</t>
+          <t>2026-02-22 14:00:00</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Front Squat</t>
+          <t>Squat</t>
         </is>
       </c>
       <c r="C238" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="D238" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E238" t="n">
-        <v>270</v>
+        <v>1200</v>
       </c>
       <c r="F238" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="G238" t="inlineStr"/>
       <c r="H238" t="n">
-        <v>54</v>
+        <v>99.99999999999999</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>2026-01-27 21:00:00</t>
+          <t>2026-02-22 14:00:00</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Bicep Curl</t>
+          <t>Squat</t>
         </is>
       </c>
       <c r="C239" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="D239" t="n">
         <v>8</v>
       </c>
       <c r="E239" t="n">
-        <v>400</v>
+        <v>720</v>
       </c>
       <c r="F239" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="G239" t="inlineStr">
-        <is>
-          <t>25kg each hand</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="G239" t="inlineStr"/>
       <c r="H239" t="n">
-        <v>63.33333333333333</v>
+        <v>114</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>2026-01-27 21:00:00</t>
+          <t>2026-02-22 14:00:00</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Overhead Tricep Ext</t>
+          <t>Squat</t>
         </is>
       </c>
       <c r="C240" t="n">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="D240" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E240" t="n">
-        <v>400</v>
+        <v>110</v>
       </c>
       <c r="F240" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="G240" t="inlineStr">
-        <is>
-          <t>25kg each hand</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="G240" t="inlineStr"/>
       <c r="H240" t="n">
-        <v>63.33333333333333</v>
+        <v>113.6666666666667</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>2026-01-27 21:00:00</t>
+          <t>2026-02-22 14:00:00</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Bicep Curl</t>
+          <t>BTN Press</t>
         </is>
       </c>
       <c r="C241" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="D241" t="n">
         <v>8</v>
       </c>
       <c r="E241" t="n">
-        <v>400</v>
+        <v>240</v>
       </c>
       <c r="F241" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="G241" t="inlineStr">
-        <is>
-          <t>25kg each hand</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="G241" t="inlineStr"/>
       <c r="H241" t="n">
-        <v>63.33333333333333</v>
+        <v>38</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>2026-01-27 21:00:00</t>
+          <t>2026-02-22 14:00:00</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Overhead Tricep Ext</t>
+          <t>OHP</t>
         </is>
       </c>
       <c r="C242" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="D242" t="n">
         <v>8</v>
       </c>
       <c r="E242" t="n">
-        <v>400</v>
+        <v>320</v>
       </c>
       <c r="F242" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="G242" t="inlineStr">
-        <is>
-          <t>25kg each hand</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="G242" t="inlineStr"/>
       <c r="H242" t="n">
-        <v>63.33333333333333</v>
+        <v>50.66666666666666</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>2026-01-27 21:00:00</t>
+          <t>2026-02-22 14:00:00</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Bicep Curl</t>
+          <t>OHP</t>
         </is>
       </c>
       <c r="C243" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="D243" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E243" t="n">
-        <v>400</v>
+        <v>240</v>
       </c>
       <c r="F243" t="n">
-        <v>9</v>
-      </c>
-      <c r="G243" t="inlineStr">
-        <is>
-          <t>25kg each hand</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="G243" t="inlineStr"/>
       <c r="H243" t="n">
-        <v>63.33333333333333</v>
+        <v>48</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>2026-01-27 21:00:00</t>
+          <t>2026-02-22 14:00:00</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Overhead Tricep Ext</t>
+          <t>OHP</t>
         </is>
       </c>
       <c r="C244" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="D244" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E244" t="n">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="F244" t="n">
-        <v>9</v>
-      </c>
-      <c r="G244" t="inlineStr">
-        <is>
-          <t>25kg each hand</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="G244" t="inlineStr"/>
       <c r="H244" t="n">
-        <v>63.33333333333333</v>
+        <v>43</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>2026-01-31 21:00:00</t>
+          <t>2026-02-22 14:00:00</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Bench Press</t>
+          <t>Barbell Row</t>
         </is>
       </c>
       <c r="C245" t="n">
+        <v>30</v>
+      </c>
+      <c r="D245" t="n">
         <v>20</v>
       </c>
-      <c r="D245" t="n">
-        <v>12</v>
-      </c>
       <c r="E245" t="n">
-        <v>240</v>
+        <v>600</v>
       </c>
       <c r="F245" t="n">
-        <v>4</v>
-      </c>
-      <c r="G245" t="inlineStr">
-        <is>
-          <t>Warm up</t>
-        </is>
-      </c>
+        <v>6.5</v>
+      </c>
+      <c r="G245" t="inlineStr"/>
       <c r="H245" t="n">
-        <v>28</v>
+        <v>49.99999999999999</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>2026-01-31 21:00:00</t>
+          <t>2026-02-22 14:00:00</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Bench Press</t>
+          <t>Barbell Row</t>
         </is>
       </c>
       <c r="C246" t="n">
         <v>40</v>
       </c>
       <c r="D246" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E246" t="n">
-        <v>320</v>
+        <v>480</v>
       </c>
       <c r="F246" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G246" t="inlineStr"/>
       <c r="H246" t="n">
-        <v>50.66666666666666</v>
+        <v>56</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>2026-01-31 21:00:00</t>
+          <t>2026-02-22 14:00:00</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Bench Press</t>
+          <t>Barbell Row</t>
         </is>
       </c>
       <c r="C247" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="D247" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E247" t="n">
-        <v>400</v>
+        <v>480</v>
       </c>
       <c r="F247" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="G247" t="inlineStr"/>
       <c r="H247" t="n">
-        <v>63.33333333333333</v>
+        <v>56</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>2026-01-31 21:00:00</t>
+          <t>2026-02-22 14:00:00</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Bench Press</t>
+          <t>Barbell Row</t>
         </is>
       </c>
       <c r="C248" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="D248" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E248" t="n">
-        <v>180</v>
+        <v>480</v>
       </c>
       <c r="F248" t="n">
         <v>8</v>
       </c>
       <c r="G248" t="inlineStr"/>
       <c r="H248" t="n">
-        <v>66</v>
+        <v>56</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>2026-01-31 21:00:00</t>
+          <t>2026-02-22 14:00:00</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Bench Press</t>
+          <t>Barbell Row</t>
         </is>
       </c>
       <c r="C249" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="D249" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E249" t="n">
-        <v>180</v>
+        <v>480</v>
       </c>
       <c r="F249" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G249" t="inlineStr"/>
       <c r="H249" t="n">
-        <v>66</v>
+        <v>56</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>2026-01-31 21:00:00</t>
+          <t>2026-02-22 14:00:00</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Bench Press</t>
+          <t>Assisted Pullup</t>
         </is>
       </c>
       <c r="C250" t="n">
         <v>60</v>
       </c>
       <c r="D250" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E250" t="n">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="F250" t="n">
-        <v>9</v>
-      </c>
-      <c r="G250" t="inlineStr">
-        <is>
-          <t>Fatigue visible</t>
-        </is>
-      </c>
+        <v>7.5</v>
+      </c>
+      <c r="G250" t="inlineStr"/>
       <c r="H250" t="n">
-        <v>64</v>
+        <v>76</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>2026-01-31 21:00:00</t>
+          <t>2026-02-22 14:00:00</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Bench Press</t>
+          <t>Assisted Dip</t>
         </is>
       </c>
       <c r="C251" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="D251" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E251" t="n">
-        <v>600</v>
+        <v>480</v>
       </c>
       <c r="F251" t="n">
-        <v>8</v>
-      </c>
-      <c r="G251" t="inlineStr">
-        <is>
-          <t>Back-off</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="G251" t="inlineStr"/>
       <c r="H251" t="n">
-        <v>60</v>
+        <v>76</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>2026-01-31 21:00:00</t>
+          <t>2026-02-22 14:00:00</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Bicep Curl</t>
+          <t>Assisted Pullup</t>
         </is>
       </c>
       <c r="C252" t="n">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="D252" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E252" t="n">
-        <v>160</v>
+        <v>480</v>
       </c>
       <c r="F252" t="n">
-        <v>7</v>
-      </c>
-      <c r="G252" t="inlineStr">
-        <is>
-          <t>Superset</t>
-        </is>
-      </c>
+        <v>8.5</v>
+      </c>
+      <c r="G252" t="inlineStr"/>
       <c r="H252" t="n">
-        <v>21.33333333333333</v>
+        <v>76</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>2026-01-31 21:00:00</t>
+          <t>2026-02-22 14:00:00</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Chest Fly</t>
+          <t>Assisted Dip</t>
         </is>
       </c>
       <c r="C253" t="n">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="D253" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E253" t="n">
-        <v>160</v>
+        <v>480</v>
       </c>
       <c r="F253" t="n">
-        <v>7</v>
-      </c>
-      <c r="G253" t="inlineStr">
-        <is>
-          <t>Superset</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="G253" t="inlineStr"/>
       <c r="H253" t="n">
-        <v>21.33333333333333</v>
+        <v>76</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>2026-01-31 21:00:00</t>
+          <t>2026-02-22 14:00:00</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Bicep Curl</t>
+          <t>Assisted Pullup</t>
         </is>
       </c>
       <c r="C254" t="n">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="D254" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E254" t="n">
-        <v>160</v>
+        <v>480</v>
       </c>
       <c r="F254" t="n">
-        <v>8</v>
-      </c>
-      <c r="G254" t="inlineStr">
-        <is>
-          <t>Superset</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="G254" t="inlineStr"/>
       <c r="H254" t="n">
-        <v>21.33333333333333</v>
+        <v>76</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>2026-01-31 21:00:00</t>
+          <t>2026-02-22 14:00:00</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Chest Fly</t>
+          <t>Assisted Dip</t>
         </is>
       </c>
       <c r="C255" t="n">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="D255" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E255" t="n">
-        <v>160</v>
+        <v>480</v>
       </c>
       <c r="F255" t="n">
-        <v>8</v>
-      </c>
-      <c r="G255" t="inlineStr">
-        <is>
-          <t>Superset</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="G255" t="inlineStr"/>
       <c r="H255" t="n">
-        <v>21.33333333333333</v>
+        <v>76</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>2026-01-31 21:00:00</t>
+          <t>2026-01-27 21:00:00</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Bicep Curl</t>
+          <t>Incline DB Press</t>
         </is>
       </c>
       <c r="C256" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="D256" t="n">
         <v>10</v>
       </c>
       <c r="E256" t="n">
-        <v>160</v>
+        <v>360</v>
       </c>
       <c r="F256" t="n">
-        <v>8.5</v>
+        <v>5</v>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Superset</t>
+          <t>18kg each hand</t>
         </is>
       </c>
       <c r="H256" t="n">
-        <v>21.33333333333333</v>
+        <v>48</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>2026-01-31 21:00:00</t>
+          <t>2026-01-27 21:00:00</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Chest Fly</t>
+          <t>Incline DB Press</t>
         </is>
       </c>
       <c r="C257" t="n">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="D257" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E257" t="n">
-        <v>160</v>
+        <v>264</v>
       </c>
       <c r="F257" t="n">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Superset</t>
+          <t>22kg each hand</t>
         </is>
       </c>
       <c r="H257" t="n">
-        <v>21.33333333333333</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>2026-01-31 21:00:00</t>
+          <t>2026-01-27 21:00:00</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Rear Delt Fly</t>
+          <t>Incline DB Press</t>
         </is>
       </c>
       <c r="C258" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="D258" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E258" t="n">
-        <v>80</v>
+        <v>264</v>
       </c>
       <c r="F258" t="n">
-        <v>8</v>
-      </c>
-      <c r="G258" t="inlineStr"/>
+        <v>7.5</v>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>22kg each hand</t>
+        </is>
+      </c>
       <c r="H258" t="n">
-        <v>10.66666666666667</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>2026-01-31 21:00:00</t>
+          <t>2026-01-27 21:00:00</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Rear Delt Fly</t>
+          <t>Incline DB Press</t>
         </is>
       </c>
       <c r="C259" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="D259" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E259" t="n">
-        <v>96</v>
+        <v>264</v>
       </c>
       <c r="F259" t="n">
-        <v>7</v>
-      </c>
-      <c r="G259" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>22kg each hand</t>
+        </is>
+      </c>
       <c r="H259" t="n">
-        <v>11.2</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>2026-01-31 21:00:00</t>
+          <t>2026-01-27 21:00:00</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Rear Delt Fly</t>
+          <t>Deadlift</t>
         </is>
       </c>
       <c r="C260" t="n">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="D260" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E260" t="n">
-        <v>96</v>
+        <v>600</v>
       </c>
       <c r="F260" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G260" t="inlineStr"/>
       <c r="H260" t="n">
-        <v>11.2</v>
+        <v>80</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>2026-01-31 21:00:00</t>
+          <t>2026-01-27 21:00:00</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Assisted Dip</t>
+          <t>Deadlift</t>
         </is>
       </c>
       <c r="C261" t="n">
-        <v>58</v>
+        <v>100</v>
       </c>
       <c r="D261" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E261" t="n">
-        <v>580</v>
+        <v>600</v>
       </c>
       <c r="F261" t="n">
-        <v>7</v>
-      </c>
-      <c r="G261" t="inlineStr">
-        <is>
-          <t>Bodyweight 85kg</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="G261" t="inlineStr"/>
       <c r="H261" t="n">
-        <v>77.33333333333333</v>
+        <v>120</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>2026-01-31 21:00:00</t>
+          <t>2026-01-27 21:00:00</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Assisted Pullup</t>
+          <t>Deadlift</t>
         </is>
       </c>
       <c r="C262" t="n">
-        <v>58</v>
+        <v>130</v>
       </c>
       <c r="D262" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E262" t="n">
-        <v>580</v>
+        <v>650</v>
       </c>
       <c r="F262" t="n">
         <v>7</v>
       </c>
-      <c r="G262" t="inlineStr">
-        <is>
-          <t>Bodyweight 85kg</t>
-        </is>
-      </c>
+      <c r="G262" t="inlineStr"/>
       <c r="H262" t="n">
-        <v>77.33333333333333</v>
+        <v>151.6666666666667</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>2026-01-31 21:00:00</t>
+          <t>2026-01-27 21:00:00</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Assisted Dip</t>
+          <t>Deadlift</t>
         </is>
       </c>
       <c r="C263" t="n">
-        <v>58</v>
+        <v>140</v>
       </c>
       <c r="D263" t="n">
+        <v>1</v>
+      </c>
+      <c r="E263" t="n">
+        <v>140</v>
+      </c>
+      <c r="F263" t="n">
         <v>10</v>
       </c>
-      <c r="E263" t="n">
-        <v>580</v>
-      </c>
-      <c r="F263" t="n">
-        <v>8</v>
-      </c>
-      <c r="G263" t="inlineStr"/>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>Failed on second rep</t>
+        </is>
+      </c>
       <c r="H263" t="n">
-        <v>77.33333333333333</v>
+        <v>144.6666666666667</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>2026-01-31 21:00:00</t>
+          <t>2026-01-27 21:00:00</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Assisted Pullup</t>
+          <t>Deadlift</t>
         </is>
       </c>
       <c r="C264" t="n">
-        <v>58</v>
+        <v>130</v>
       </c>
       <c r="D264" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E264" t="n">
-        <v>580</v>
+        <v>260</v>
       </c>
       <c r="F264" t="n">
         <v>8</v>
       </c>
       <c r="G264" t="inlineStr"/>
       <c r="H264" t="n">
-        <v>77.33333333333333</v>
+        <v>138.6666666666667</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>2026-01-31 21:00:00</t>
+          <t>2026-01-27 21:00:00</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Assisted Dip</t>
+          <t>Deadlift</t>
         </is>
       </c>
       <c r="C265" t="n">
-        <v>58</v>
+        <v>100</v>
       </c>
       <c r="D265" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E265" t="n">
-        <v>464</v>
+        <v>500</v>
       </c>
       <c r="F265" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="G265" t="inlineStr"/>
       <c r="H265" t="n">
-        <v>73.46666666666667</v>
+        <v>116.6666666666667</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>2026-01-31 21:00:00</t>
+          <t>2026-01-27 21:00:00</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Assisted Pullup</t>
+          <t>Deadlift</t>
         </is>
       </c>
       <c r="C266" t="n">
-        <v>58</v>
+        <v>100</v>
       </c>
       <c r="D266" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E266" t="n">
-        <v>464</v>
+        <v>1000</v>
       </c>
       <c r="F266" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="G266" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>Finisher set</t>
+        </is>
+      </c>
       <c r="H266" t="n">
-        <v>73.46666666666667</v>
+        <v>133.3333333333333</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>2026-01-31 21:00:00</t>
+          <t>2026-01-27 21:00:00</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Seated Row</t>
+          <t>Behind the Neck Press</t>
         </is>
       </c>
       <c r="C267" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="D267" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E267" t="n">
-        <v>360</v>
+        <v>200</v>
       </c>
       <c r="F267" t="n">
-        <v>7</v>
-      </c>
-      <c r="G267" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>Superset Part 1</t>
+        </is>
+      </c>
       <c r="H267" t="n">
-        <v>57</v>
+        <v>26.66666666666666</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>2026-01-31 21:00:00</t>
+          <t>2026-01-27 21:00:00</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Seated Row</t>
+          <t>Overhead Press</t>
         </is>
       </c>
       <c r="C268" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="D268" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E268" t="n">
-        <v>360</v>
+        <v>200</v>
       </c>
       <c r="F268" t="n">
-        <v>8</v>
-      </c>
-      <c r="G268" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>Superset Part 2</t>
+        </is>
+      </c>
       <c r="H268" t="n">
-        <v>57</v>
+        <v>26.66666666666666</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>2026-01-31 21:00:00</t>
+          <t>2026-01-27 21:00:00</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Seated Row</t>
+          <t>Overhead Press</t>
         </is>
       </c>
       <c r="C269" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="D269" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E269" t="n">
-        <v>360</v>
+        <v>180</v>
       </c>
       <c r="F269" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G269" t="inlineStr"/>
       <c r="H269" t="n">
-        <v>57</v>
+        <v>36</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>2026-01-31 21:00:00</t>
+          <t>2026-01-27 21:00:00</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>BTN Standing Press</t>
+          <t>Overhead Press</t>
         </is>
       </c>
       <c r="C270" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="D270" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E270" t="n">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="F270" t="n">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="G270" t="inlineStr"/>
       <c r="H270" t="n">
-        <v>26.66666666666666</v>
+        <v>44</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>2026-01-31 21:00:00</t>
+          <t>2026-01-27 21:00:00</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -8730,640 +8718,1100 @@
         </is>
       </c>
       <c r="C271" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D271" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E271" t="n">
         <v>120</v>
       </c>
       <c r="F271" t="n">
-        <v>10</v>
-      </c>
-      <c r="G271" t="inlineStr">
-        <is>
-          <t>Failed reps</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="G271" t="inlineStr"/>
       <c r="H271" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>2026-02-22 14:00:00</t>
+          <t>2026-01-27 21:00:00</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Squat</t>
+          <t>Overhead Press</t>
         </is>
       </c>
       <c r="C272" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="D272" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E272" t="n">
-        <v>240</v>
+        <v>120</v>
       </c>
       <c r="F272" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G272" t="inlineStr"/>
       <c r="H272" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>2026-02-22 14:00:00</t>
+          <t>2026-01-27 21:00:00</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Squat</t>
+          <t>Overhead Press</t>
         </is>
       </c>
       <c r="C273" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="D273" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E273" t="n">
-        <v>480</v>
+        <v>45</v>
       </c>
       <c r="F273" t="n">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="G273" t="inlineStr"/>
       <c r="H273" t="n">
-        <v>76</v>
+        <v>46.50000000000001</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>2026-02-22 14:00:00</t>
+          <t>2026-01-27 21:00:00</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Squat</t>
+          <t>Front Squat</t>
         </is>
       </c>
       <c r="C274" t="n">
-        <v>100</v>
+        <v>45</v>
       </c>
       <c r="D274" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E274" t="n">
-        <v>200</v>
+        <v>270</v>
       </c>
       <c r="F274" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="G274" t="inlineStr"/>
       <c r="H274" t="n">
-        <v>106.6666666666667</v>
+        <v>54</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>2026-02-22 14:00:00</t>
+          <t>2026-01-27 21:00:00</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Squat</t>
+          <t>Bicep Curl</t>
         </is>
       </c>
       <c r="C275" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="D275" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E275" t="n">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="F275" t="n">
         <v>7.5</v>
       </c>
-      <c r="G275" t="inlineStr"/>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>25kg each hand</t>
+        </is>
+      </c>
       <c r="H275" t="n">
-        <v>116.6666666666667</v>
+        <v>63.33333333333333</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>2026-02-22 14:00:00</t>
+          <t>2026-01-27 21:00:00</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Squat</t>
+          <t>Overhead Tricep Ext</t>
         </is>
       </c>
       <c r="C276" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="D276" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E276" t="n">
-        <v>1200</v>
+        <v>400</v>
       </c>
       <c r="F276" t="n">
         <v>7.5</v>
       </c>
-      <c r="G276" t="inlineStr"/>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>25kg each hand</t>
+        </is>
+      </c>
       <c r="H276" t="n">
-        <v>99.99999999999999</v>
+        <v>63.33333333333333</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>2026-02-22 14:00:00</t>
+          <t>2026-01-27 21:00:00</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Squat</t>
+          <t>Bicep Curl</t>
         </is>
       </c>
       <c r="C277" t="n">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="D277" t="n">
         <v>8</v>
       </c>
       <c r="E277" t="n">
-        <v>720</v>
+        <v>400</v>
       </c>
       <c r="F277" t="n">
-        <v>8</v>
-      </c>
-      <c r="G277" t="inlineStr"/>
+        <v>8.5</v>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>25kg each hand</t>
+        </is>
+      </c>
       <c r="H277" t="n">
-        <v>114</v>
+        <v>63.33333333333333</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>2026-02-22 14:00:00</t>
+          <t>2026-01-27 21:00:00</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Squat</t>
+          <t>Overhead Tricep Ext</t>
         </is>
       </c>
       <c r="C278" t="n">
-        <v>110</v>
+        <v>50</v>
       </c>
       <c r="D278" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E278" t="n">
-        <v>110</v>
+        <v>400</v>
       </c>
       <c r="F278" t="n">
-        <v>8</v>
-      </c>
-      <c r="G278" t="inlineStr"/>
+        <v>8.5</v>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>25kg each hand</t>
+        </is>
+      </c>
       <c r="H278" t="n">
-        <v>113.6666666666667</v>
+        <v>63.33333333333333</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>2026-02-22 14:00:00</t>
+          <t>2026-01-27 21:00:00</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>BTN Press</t>
+          <t>Bicep Curl</t>
         </is>
       </c>
       <c r="C279" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="D279" t="n">
         <v>8</v>
       </c>
       <c r="E279" t="n">
-        <v>240</v>
+        <v>400</v>
       </c>
       <c r="F279" t="n">
-        <v>7</v>
-      </c>
-      <c r="G279" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>25kg each hand</t>
+        </is>
+      </c>
       <c r="H279" t="n">
-        <v>38</v>
+        <v>63.33333333333333</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>2026-02-22 14:00:00</t>
+          <t>2026-01-27 21:00:00</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>OHP</t>
+          <t>Overhead Tricep Ext</t>
         </is>
       </c>
       <c r="C280" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D280" t="n">
         <v>8</v>
       </c>
       <c r="E280" t="n">
-        <v>320</v>
+        <v>400</v>
       </c>
       <c r="F280" t="n">
-        <v>8</v>
-      </c>
-      <c r="G280" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>25kg each hand</t>
+        </is>
+      </c>
       <c r="H280" t="n">
-        <v>50.66666666666666</v>
+        <v>63.33333333333333</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>2026-02-22 14:00:00</t>
+          <t>2026-01-31 21:00:00</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>OHP</t>
+          <t>Bench Press</t>
         </is>
       </c>
       <c r="C281" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="D281" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E281" t="n">
         <v>240</v>
       </c>
       <c r="F281" t="n">
-        <v>10</v>
-      </c>
-      <c r="G281" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>Warm up</t>
+        </is>
+      </c>
       <c r="H281" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>2026-02-22 14:00:00</t>
+          <t>2026-01-31 21:00:00</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>OHP</t>
+          <t>Bench Press</t>
         </is>
       </c>
       <c r="C282" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D282" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E282" t="n">
-        <v>390</v>
+        <v>320</v>
       </c>
       <c r="F282" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G282" t="inlineStr"/>
       <c r="H282" t="n">
-        <v>43</v>
+        <v>50.66666666666666</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>2026-02-22 14:00:00</t>
+          <t>2026-01-31 21:00:00</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Barbell Row</t>
+          <t>Bench Press</t>
         </is>
       </c>
       <c r="C283" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="D283" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E283" t="n">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="F283" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="G283" t="inlineStr"/>
       <c r="H283" t="n">
-        <v>49.99999999999999</v>
+        <v>63.33333333333333</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>2026-02-22 14:00:00</t>
+          <t>2026-01-31 21:00:00</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Barbell Row</t>
+          <t>Bench Press</t>
         </is>
       </c>
       <c r="C284" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="D284" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E284" t="n">
-        <v>480</v>
+        <v>180</v>
       </c>
       <c r="F284" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G284" t="inlineStr"/>
       <c r="H284" t="n">
-        <v>56</v>
+        <v>66</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>2026-02-22 14:00:00</t>
+          <t>2026-01-31 21:00:00</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Barbell Row</t>
+          <t>Bench Press</t>
         </is>
       </c>
       <c r="C285" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="D285" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E285" t="n">
-        <v>480</v>
+        <v>180</v>
       </c>
       <c r="F285" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="G285" t="inlineStr"/>
       <c r="H285" t="n">
-        <v>56</v>
+        <v>66</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>2026-02-22 14:00:00</t>
+          <t>2026-01-31 21:00:00</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Barbell Row</t>
+          <t>Bench Press</t>
         </is>
       </c>
       <c r="C286" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="D286" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E286" t="n">
-        <v>480</v>
+        <v>120</v>
       </c>
       <c r="F286" t="n">
-        <v>8</v>
-      </c>
-      <c r="G286" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>Fatigue visible</t>
+        </is>
+      </c>
       <c r="H286" t="n">
-        <v>56</v>
+        <v>64</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>2026-02-22 14:00:00</t>
+          <t>2026-01-31 21:00:00</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Barbell Row</t>
+          <t>Bench Press</t>
         </is>
       </c>
       <c r="C287" t="n">
         <v>40</v>
       </c>
       <c r="D287" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E287" t="n">
-        <v>480</v>
+        <v>600</v>
       </c>
       <c r="F287" t="n">
-        <v>9</v>
-      </c>
-      <c r="G287" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>Back-off</t>
+        </is>
+      </c>
       <c r="H287" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>2026-02-22 14:00:00</t>
+          <t>2026-01-31 21:00:00</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Assisted Pullup</t>
+          <t>Bicep Curl</t>
         </is>
       </c>
       <c r="C288" t="n">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="D288" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E288" t="n">
-        <v>480</v>
+        <v>160</v>
       </c>
       <c r="F288" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="G288" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>Superset</t>
+        </is>
+      </c>
       <c r="H288" t="n">
-        <v>76</v>
+        <v>21.33333333333333</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>2026-02-22 14:00:00</t>
+          <t>2026-01-31 21:00:00</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Assisted Dip</t>
+          <t>Chest Fly</t>
         </is>
       </c>
       <c r="C289" t="n">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="D289" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E289" t="n">
-        <v>480</v>
+        <v>160</v>
       </c>
       <c r="F289" t="n">
         <v>7</v>
       </c>
-      <c r="G289" t="inlineStr"/>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>Superset</t>
+        </is>
+      </c>
       <c r="H289" t="n">
-        <v>76</v>
+        <v>21.33333333333333</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>2026-02-22 14:00:00</t>
+          <t>2026-01-31 21:00:00</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Assisted Pullup</t>
+          <t>Bicep Curl</t>
         </is>
       </c>
       <c r="C290" t="n">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="D290" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E290" t="n">
-        <v>480</v>
+        <v>160</v>
       </c>
       <c r="F290" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="G290" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>Superset</t>
+        </is>
+      </c>
       <c r="H290" t="n">
-        <v>76</v>
+        <v>21.33333333333333</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>2026-02-22 14:00:00</t>
+          <t>2026-01-31 21:00:00</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Assisted Dip</t>
+          <t>Chest Fly</t>
         </is>
       </c>
       <c r="C291" t="n">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="D291" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E291" t="n">
-        <v>480</v>
+        <v>160</v>
       </c>
       <c r="F291" t="n">
         <v>8</v>
       </c>
-      <c r="G291" t="inlineStr"/>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>Superset</t>
+        </is>
+      </c>
       <c r="H291" t="n">
-        <v>76</v>
+        <v>21.33333333333333</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>2026-02-22 14:00:00</t>
+          <t>2026-01-31 21:00:00</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Assisted Pullup</t>
+          <t>Bicep Curl</t>
         </is>
       </c>
       <c r="C292" t="n">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="D292" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E292" t="n">
-        <v>480</v>
+        <v>160</v>
       </c>
       <c r="F292" t="n">
-        <v>9</v>
-      </c>
-      <c r="G292" t="inlineStr"/>
+        <v>8.5</v>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>Superset</t>
+        </is>
+      </c>
       <c r="H292" t="n">
-        <v>76</v>
+        <v>21.33333333333333</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>2026-02-22 14:00:00</t>
+          <t>2026-01-31 21:00:00</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
+          <t>Chest Fly</t>
+        </is>
+      </c>
+      <c r="C293" t="n">
+        <v>16</v>
+      </c>
+      <c r="D293" t="n">
+        <v>10</v>
+      </c>
+      <c r="E293" t="n">
+        <v>160</v>
+      </c>
+      <c r="F293" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>Superset</t>
+        </is>
+      </c>
+      <c r="H293" t="n">
+        <v>21.33333333333333</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2026-01-31 21:00:00</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Rear Delt Fly</t>
+        </is>
+      </c>
+      <c r="C294" t="n">
+        <v>8</v>
+      </c>
+      <c r="D294" t="n">
+        <v>10</v>
+      </c>
+      <c r="E294" t="n">
+        <v>80</v>
+      </c>
+      <c r="F294" t="n">
+        <v>8</v>
+      </c>
+      <c r="G294" t="inlineStr"/>
+      <c r="H294" t="n">
+        <v>10.66666666666667</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2026-01-31 21:00:00</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Rear Delt Fly</t>
+        </is>
+      </c>
+      <c r="C295" t="n">
+        <v>8</v>
+      </c>
+      <c r="D295" t="n">
+        <v>12</v>
+      </c>
+      <c r="E295" t="n">
+        <v>96</v>
+      </c>
+      <c r="F295" t="n">
+        <v>7</v>
+      </c>
+      <c r="G295" t="inlineStr"/>
+      <c r="H295" t="n">
+        <v>11.2</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2026-01-31 21:00:00</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Rear Delt Fly</t>
+        </is>
+      </c>
+      <c r="C296" t="n">
+        <v>8</v>
+      </c>
+      <c r="D296" t="n">
+        <v>12</v>
+      </c>
+      <c r="E296" t="n">
+        <v>96</v>
+      </c>
+      <c r="F296" t="n">
+        <v>8</v>
+      </c>
+      <c r="G296" t="inlineStr"/>
+      <c r="H296" t="n">
+        <v>11.2</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>2026-01-31 21:00:00</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
           <t>Assisted Dip</t>
         </is>
       </c>
-      <c r="C293" t="n">
-        <v>60</v>
-      </c>
-      <c r="D293" t="n">
-        <v>8</v>
-      </c>
-      <c r="E293" t="n">
-        <v>480</v>
-      </c>
-      <c r="F293" t="n">
-        <v>9</v>
-      </c>
-      <c r="G293" t="inlineStr"/>
-      <c r="H293" t="n">
-        <v>76</v>
+      <c r="C297" t="n">
+        <v>58</v>
+      </c>
+      <c r="D297" t="n">
+        <v>10</v>
+      </c>
+      <c r="E297" t="n">
+        <v>580</v>
+      </c>
+      <c r="F297" t="n">
+        <v>7</v>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>Bodyweight 85kg</t>
+        </is>
+      </c>
+      <c r="H297" t="n">
+        <v>77.33333333333333</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>2026-01-31 21:00:00</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Assisted Pullup</t>
+        </is>
+      </c>
+      <c r="C298" t="n">
+        <v>58</v>
+      </c>
+      <c r="D298" t="n">
+        <v>10</v>
+      </c>
+      <c r="E298" t="n">
+        <v>580</v>
+      </c>
+      <c r="F298" t="n">
+        <v>7</v>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>Bodyweight 85kg</t>
+        </is>
+      </c>
+      <c r="H298" t="n">
+        <v>77.33333333333333</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>2026-01-31 21:00:00</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Assisted Dip</t>
+        </is>
+      </c>
+      <c r="C299" t="n">
+        <v>58</v>
+      </c>
+      <c r="D299" t="n">
+        <v>10</v>
+      </c>
+      <c r="E299" t="n">
+        <v>580</v>
+      </c>
+      <c r="F299" t="n">
+        <v>8</v>
+      </c>
+      <c r="G299" t="inlineStr"/>
+      <c r="H299" t="n">
+        <v>77.33333333333333</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>2026-01-31 21:00:00</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Assisted Pullup</t>
+        </is>
+      </c>
+      <c r="C300" t="n">
+        <v>58</v>
+      </c>
+      <c r="D300" t="n">
+        <v>10</v>
+      </c>
+      <c r="E300" t="n">
+        <v>580</v>
+      </c>
+      <c r="F300" t="n">
+        <v>8</v>
+      </c>
+      <c r="G300" t="inlineStr"/>
+      <c r="H300" t="n">
+        <v>77.33333333333333</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>2026-01-31 21:00:00</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Assisted Dip</t>
+        </is>
+      </c>
+      <c r="C301" t="n">
+        <v>58</v>
+      </c>
+      <c r="D301" t="n">
+        <v>8</v>
+      </c>
+      <c r="E301" t="n">
+        <v>464</v>
+      </c>
+      <c r="F301" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G301" t="inlineStr"/>
+      <c r="H301" t="n">
+        <v>73.46666666666667</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>2026-01-31 21:00:00</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Assisted Pullup</t>
+        </is>
+      </c>
+      <c r="C302" t="n">
+        <v>58</v>
+      </c>
+      <c r="D302" t="n">
+        <v>8</v>
+      </c>
+      <c r="E302" t="n">
+        <v>464</v>
+      </c>
+      <c r="F302" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G302" t="inlineStr"/>
+      <c r="H302" t="n">
+        <v>73.46666666666667</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>2026-01-31 21:00:00</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Seated Row</t>
+        </is>
+      </c>
+      <c r="C303" t="n">
+        <v>45</v>
+      </c>
+      <c r="D303" t="n">
+        <v>8</v>
+      </c>
+      <c r="E303" t="n">
+        <v>360</v>
+      </c>
+      <c r="F303" t="n">
+        <v>7</v>
+      </c>
+      <c r="G303" t="inlineStr"/>
+      <c r="H303" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>2026-01-31 21:00:00</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Seated Row</t>
+        </is>
+      </c>
+      <c r="C304" t="n">
+        <v>45</v>
+      </c>
+      <c r="D304" t="n">
+        <v>8</v>
+      </c>
+      <c r="E304" t="n">
+        <v>360</v>
+      </c>
+      <c r="F304" t="n">
+        <v>8</v>
+      </c>
+      <c r="G304" t="inlineStr"/>
+      <c r="H304" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>2026-01-31 21:00:00</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Seated Row</t>
+        </is>
+      </c>
+      <c r="C305" t="n">
+        <v>45</v>
+      </c>
+      <c r="D305" t="n">
+        <v>8</v>
+      </c>
+      <c r="E305" t="n">
+        <v>360</v>
+      </c>
+      <c r="F305" t="n">
+        <v>8</v>
+      </c>
+      <c r="G305" t="inlineStr"/>
+      <c r="H305" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>2026-01-31 21:00:00</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>BTN Standing Press</t>
+        </is>
+      </c>
+      <c r="C306" t="n">
+        <v>20</v>
+      </c>
+      <c r="D306" t="n">
+        <v>10</v>
+      </c>
+      <c r="E306" t="n">
+        <v>200</v>
+      </c>
+      <c r="F306" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="G306" t="inlineStr"/>
+      <c r="H306" t="n">
+        <v>26.66666666666666</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>2026-01-31 21:00:00</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Overhead Press</t>
+        </is>
+      </c>
+      <c r="C307" t="n">
+        <v>30</v>
+      </c>
+      <c r="D307" t="n">
+        <v>4</v>
+      </c>
+      <c r="E307" t="n">
+        <v>120</v>
+      </c>
+      <c r="F307" t="n">
+        <v>10</v>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>Failed reps</t>
+        </is>
+      </c>
+      <c r="H307" t="n">
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/data/workout_log.xlsx
+++ b/data/workout_log.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="984" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1071" uniqueCount="295">
   <si>
     <t>Timestamp</t>
   </si>
@@ -91,6 +91,93 @@
     <t>2026-03-05 21:00:00</t>
   </si>
   <si>
+    <t>2026-03-07 11:30:00</t>
+  </si>
+  <si>
+    <t>2026-03-07 11:35:00</t>
+  </si>
+  <si>
+    <t>2026-03-07 11:42:00</t>
+  </si>
+  <si>
+    <t>2026-03-07 11:50:00</t>
+  </si>
+  <si>
+    <t>2026-03-07 11:58:00</t>
+  </si>
+  <si>
+    <t>2026-03-07 12:05:00</t>
+  </si>
+  <si>
+    <t>2026-03-07 12:10:00</t>
+  </si>
+  <si>
+    <t>2026-03-07 12:15:00</t>
+  </si>
+  <si>
+    <t>2026-03-07 12:22:00</t>
+  </si>
+  <si>
+    <t>2026-03-07 12:28:00</t>
+  </si>
+  <si>
+    <t>2026-03-07 12:35:00</t>
+  </si>
+  <si>
+    <t>2026-03-07 12:40:00</t>
+  </si>
+  <si>
+    <t>2026-03-07 12:44:00</t>
+  </si>
+  <si>
+    <t>2026-03-07 12:48:00</t>
+  </si>
+  <si>
+    <t>2026-03-07 12:55:00</t>
+  </si>
+  <si>
+    <t>2026-03-07 12:58:00</t>
+  </si>
+  <si>
+    <t>2026-03-07 13:02:00</t>
+  </si>
+  <si>
+    <t>2026-03-07 13:06:00</t>
+  </si>
+  <si>
+    <t>2026-03-07 13:12:00</t>
+  </si>
+  <si>
+    <t>2026-03-07 13:18:00</t>
+  </si>
+  <si>
+    <t>2026-03-07 13:22:00</t>
+  </si>
+  <si>
+    <t>2026-03-07 13:26:00</t>
+  </si>
+  <si>
+    <t>2026-03-07 13:30:00</t>
+  </si>
+  <si>
+    <t>2026-03-07 13:38:00</t>
+  </si>
+  <si>
+    <t>2026-03-07 13:42:00</t>
+  </si>
+  <si>
+    <t>2026-03-07 13:46:00</t>
+  </si>
+  <si>
+    <t>2026-03-07 13:50:00</t>
+  </si>
+  <si>
+    <t>2026-03-07 13:54:00</t>
+  </si>
+  <si>
+    <t>2026-03-07 13:58:00</t>
+  </si>
+  <si>
     <t>Overhead Press</t>
   </si>
   <si>
@@ -253,6 +340,27 @@
     <t>Lat Pulldown</t>
   </si>
   <si>
+    <t>Incline Bench Press</t>
+  </si>
+  <si>
+    <t>Flat Bench Press</t>
+  </si>
+  <si>
+    <t>Pause Bench Press</t>
+  </si>
+  <si>
+    <t>Machine Chest Press</t>
+  </si>
+  <si>
+    <t>Unloaded Back Extension</t>
+  </si>
+  <si>
+    <t>Weighted Back Extension</t>
+  </si>
+  <si>
+    <t>Machine Rows</t>
+  </si>
+  <si>
     <t>Warm-up. Run: 2.75km in 12:30 prior.</t>
   </si>
   <si>
@@ -713,6 +821,84 @@
   </si>
   <si>
     <t>High-rep burner finisher</t>
+  </si>
+  <si>
+    <t>Incremental build</t>
+  </si>
+  <si>
+    <t>High RIR</t>
+  </si>
+  <si>
+    <t>Focus on dead-stop force</t>
+  </si>
+  <si>
+    <t>Successful heavy single</t>
+  </si>
+  <si>
+    <t>Failed at start of concentric</t>
+  </si>
+  <si>
+    <t>Asymmetric load error (L:23.75, R:22.5); 2s lockout lag</t>
+  </si>
+  <si>
+    <t>Symmetrical recalibration</t>
+  </si>
+  <si>
+    <t>Metabolic flush</t>
+  </si>
+  <si>
+    <t>Fixed path hypertrophy</t>
+  </si>
+  <si>
+    <t>Technical proficiency improved</t>
+  </si>
+  <si>
+    <t>Failure on 7th rep</t>
+  </si>
+  <si>
+    <t>Posterior chain recovery</t>
+  </si>
+  <si>
+    <t>High intensity spinal stability</t>
+  </si>
+  <si>
+    <t>Improved work capacity</t>
+  </si>
+  <si>
+    <t>Significant lumbar pump</t>
+  </si>
+  <si>
+    <t>Vertical pull intro</t>
+  </si>
+  <si>
+    <t>Lat focus</t>
+  </si>
+  <si>
+    <t>Neuromuscular facilitation</t>
+  </si>
+  <si>
+    <t>Steady state performance</t>
+  </si>
+  <si>
+    <t>Peripheral fatigue setting in</t>
+  </si>
+  <si>
+    <t>Horizontal pull focus</t>
+  </si>
+  <si>
+    <t>Optimized seat position</t>
+  </si>
+  <si>
+    <t>Accumulated intra-set fatigue</t>
+  </si>
+  <si>
+    <t>Volume accumulation</t>
+  </si>
+  <si>
+    <t>End of back volume</t>
+  </si>
+  <si>
+    <t>Final terminal set</t>
   </si>
 </sst>
 </file>
@@ -1070,7 +1256,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H370"/>
+  <dimension ref="A1:H399"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1104,7 +1290,7 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="C2">
         <v>30</v>
@@ -1119,7 +1305,7 @@
         <v>4</v>
       </c>
       <c r="G2" t="s">
-        <v>79</v>
+        <v>115</v>
       </c>
       <c r="H2">
         <v>40</v>
@@ -1130,7 +1316,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="C3">
         <v>30</v>
@@ -1153,7 +1339,7 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="C4">
         <v>30</v>
@@ -1176,7 +1362,7 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="C5">
         <v>30</v>
@@ -1199,7 +1385,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="C6">
         <v>60</v>
@@ -1214,7 +1400,7 @@
         <v>5</v>
       </c>
       <c r="G6" t="s">
-        <v>80</v>
+        <v>116</v>
       </c>
       <c r="H6">
         <v>76</v>
@@ -1225,7 +1411,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="C7">
         <v>100</v>
@@ -1240,7 +1426,7 @@
         <v>6</v>
       </c>
       <c r="G7" t="s">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="H7">
         <v>110</v>
@@ -1251,7 +1437,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="C8">
         <v>100</v>
@@ -1274,7 +1460,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="C9">
         <v>100</v>
@@ -1297,7 +1483,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="C10">
         <v>32</v>
@@ -1312,7 +1498,7 @@
         <v>3</v>
       </c>
       <c r="G10" t="s">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="H10">
         <v>44.8</v>
@@ -1323,7 +1509,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="C11">
         <v>40</v>
@@ -1338,7 +1524,7 @@
         <v>5.5</v>
       </c>
       <c r="G11" t="s">
-        <v>83</v>
+        <v>119</v>
       </c>
       <c r="H11">
         <v>50.66666666666666</v>
@@ -1349,7 +1535,7 @@
         <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="C12">
         <v>40</v>
@@ -1372,7 +1558,7 @@
         <v>8</v>
       </c>
       <c r="B13" t="s">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="C13">
         <v>40</v>
@@ -1387,7 +1573,7 @@
         <v>9</v>
       </c>
       <c r="G13" t="s">
-        <v>84</v>
+        <v>120</v>
       </c>
       <c r="H13">
         <v>48</v>
@@ -1398,7 +1584,7 @@
         <v>8</v>
       </c>
       <c r="B14" t="s">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="C14">
         <v>20</v>
@@ -1421,7 +1607,7 @@
         <v>8</v>
       </c>
       <c r="B15" t="s">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="C15">
         <v>20</v>
@@ -1444,7 +1630,7 @@
         <v>8</v>
       </c>
       <c r="B16" t="s">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="C16">
         <v>20</v>
@@ -1467,7 +1653,7 @@
         <v>8</v>
       </c>
       <c r="B17" t="s">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="C17">
         <v>20</v>
@@ -1482,7 +1668,7 @@
         <v>8</v>
       </c>
       <c r="G17" t="s">
-        <v>85</v>
+        <v>121</v>
       </c>
       <c r="H17">
         <v>26.66666666666666</v>
@@ -1493,7 +1679,7 @@
         <v>8</v>
       </c>
       <c r="B18" t="s">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="C18">
         <v>20</v>
@@ -1508,7 +1694,7 @@
         <v>8</v>
       </c>
       <c r="G18" t="s">
-        <v>86</v>
+        <v>122</v>
       </c>
       <c r="H18">
         <v>26.66666666666666</v>
@@ -1519,7 +1705,7 @@
         <v>8</v>
       </c>
       <c r="B19" t="s">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="C19">
         <v>20</v>
@@ -1534,7 +1720,7 @@
         <v>8</v>
       </c>
       <c r="G19" t="s">
-        <v>85</v>
+        <v>121</v>
       </c>
       <c r="H19">
         <v>25.33333333333333</v>
@@ -1545,7 +1731,7 @@
         <v>8</v>
       </c>
       <c r="B20" t="s">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="C20">
         <v>20</v>
@@ -1560,7 +1746,7 @@
         <v>8</v>
       </c>
       <c r="G20" t="s">
-        <v>86</v>
+        <v>122</v>
       </c>
       <c r="H20">
         <v>25.33333333333333</v>
@@ -1571,7 +1757,7 @@
         <v>9</v>
       </c>
       <c r="B21" t="s">
-        <v>32</v>
+        <v>61</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -1586,7 +1772,7 @@
         <v>7</v>
       </c>
       <c r="G21" t="s">
-        <v>87</v>
+        <v>123</v>
       </c>
       <c r="H21">
         <v>0</v>
@@ -1597,7 +1783,7 @@
         <v>9</v>
       </c>
       <c r="B22" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="C22">
         <v>30</v>
@@ -1620,7 +1806,7 @@
         <v>9</v>
       </c>
       <c r="B23" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="C23">
         <v>30</v>
@@ -1643,7 +1829,7 @@
         <v>9</v>
       </c>
       <c r="B24" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="C24">
         <v>30</v>
@@ -1666,7 +1852,7 @@
         <v>9</v>
       </c>
       <c r="B25" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="C25">
         <v>30</v>
@@ -1689,7 +1875,7 @@
         <v>9</v>
       </c>
       <c r="B26" t="s">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="C26">
         <v>30</v>
@@ -1712,7 +1898,7 @@
         <v>9</v>
       </c>
       <c r="B27" t="s">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="C27">
         <v>30</v>
@@ -1735,7 +1921,7 @@
         <v>9</v>
       </c>
       <c r="B28" t="s">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="C28">
         <v>30</v>
@@ -1758,7 +1944,7 @@
         <v>9</v>
       </c>
       <c r="B29" t="s">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="C29">
         <v>30</v>
@@ -1781,7 +1967,7 @@
         <v>9</v>
       </c>
       <c r="B30" t="s">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="C30">
         <v>30</v>
@@ -1804,7 +1990,7 @@
         <v>9</v>
       </c>
       <c r="B31" t="s">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="C31">
         <v>70</v>
@@ -1827,7 +2013,7 @@
         <v>9</v>
       </c>
       <c r="B32" t="s">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="C32">
         <v>70</v>
@@ -1850,7 +2036,7 @@
         <v>9</v>
       </c>
       <c r="B33" t="s">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="C33">
         <v>70</v>
@@ -1873,7 +2059,7 @@
         <v>9</v>
       </c>
       <c r="B34" t="s">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="C34">
         <v>23</v>
@@ -1888,7 +2074,7 @@
         <v>7</v>
       </c>
       <c r="G34" t="s">
-        <v>85</v>
+        <v>121</v>
       </c>
       <c r="H34">
         <v>38.33333333333333</v>
@@ -1899,7 +2085,7 @@
         <v>9</v>
       </c>
       <c r="B35" t="s">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="C35">
         <v>23</v>
@@ -1914,7 +2100,7 @@
         <v>7</v>
       </c>
       <c r="G35" t="s">
-        <v>86</v>
+        <v>122</v>
       </c>
       <c r="H35">
         <v>38.33333333333333</v>
@@ -1925,7 +2111,7 @@
         <v>9</v>
       </c>
       <c r="B36" t="s">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="C36">
         <v>23</v>
@@ -1940,7 +2126,7 @@
         <v>9</v>
       </c>
       <c r="G36" t="s">
-        <v>85</v>
+        <v>121</v>
       </c>
       <c r="H36">
         <v>38.33333333333333</v>
@@ -1951,7 +2137,7 @@
         <v>9</v>
       </c>
       <c r="B37" t="s">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="C37">
         <v>23</v>
@@ -1966,7 +2152,7 @@
         <v>10</v>
       </c>
       <c r="G37" t="s">
-        <v>88</v>
+        <v>124</v>
       </c>
       <c r="H37">
         <v>32.2</v>
@@ -1977,7 +2163,7 @@
         <v>9</v>
       </c>
       <c r="B38" t="s">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="C38">
         <v>20</v>
@@ -2000,7 +2186,7 @@
         <v>9</v>
       </c>
       <c r="B39" t="s">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="C39">
         <v>20</v>
@@ -2023,7 +2209,7 @@
         <v>9</v>
       </c>
       <c r="B40" t="s">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="C40">
         <v>20</v>
@@ -2046,7 +2232,7 @@
         <v>10</v>
       </c>
       <c r="B41" t="s">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="C41">
         <v>36</v>
@@ -2061,7 +2247,7 @@
         <v>5</v>
       </c>
       <c r="G41" t="s">
-        <v>89</v>
+        <v>125</v>
       </c>
       <c r="H41">
         <v>48</v>
@@ -2072,7 +2258,7 @@
         <v>10</v>
       </c>
       <c r="B42" t="s">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="C42">
         <v>44</v>
@@ -2087,7 +2273,7 @@
         <v>7</v>
       </c>
       <c r="G42" t="s">
-        <v>90</v>
+        <v>126</v>
       </c>
       <c r="H42">
         <v>52.8</v>
@@ -2098,7 +2284,7 @@
         <v>10</v>
       </c>
       <c r="B43" t="s">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="C43">
         <v>44</v>
@@ -2113,7 +2299,7 @@
         <v>7.5</v>
       </c>
       <c r="G43" t="s">
-        <v>90</v>
+        <v>126</v>
       </c>
       <c r="H43">
         <v>52.8</v>
@@ -2124,7 +2310,7 @@
         <v>10</v>
       </c>
       <c r="B44" t="s">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="C44">
         <v>44</v>
@@ -2139,7 +2325,7 @@
         <v>8</v>
       </c>
       <c r="G44" t="s">
-        <v>90</v>
+        <v>126</v>
       </c>
       <c r="H44">
         <v>52.8</v>
@@ -2150,7 +2336,7 @@
         <v>10</v>
       </c>
       <c r="B45" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="C45">
         <v>60</v>
@@ -2173,7 +2359,7 @@
         <v>10</v>
       </c>
       <c r="B46" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="C46">
         <v>100</v>
@@ -2196,7 +2382,7 @@
         <v>10</v>
       </c>
       <c r="B47" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="C47">
         <v>130</v>
@@ -2219,7 +2405,7 @@
         <v>10</v>
       </c>
       <c r="B48" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="C48">
         <v>140</v>
@@ -2234,7 +2420,7 @@
         <v>10</v>
       </c>
       <c r="G48" t="s">
-        <v>91</v>
+        <v>127</v>
       </c>
       <c r="H48">
         <v>144.6666666666667</v>
@@ -2245,7 +2431,7 @@
         <v>10</v>
       </c>
       <c r="B49" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="C49">
         <v>130</v>
@@ -2268,7 +2454,7 @@
         <v>10</v>
       </c>
       <c r="B50" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="C50">
         <v>100</v>
@@ -2291,7 +2477,7 @@
         <v>10</v>
       </c>
       <c r="B51" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="C51">
         <v>100</v>
@@ -2306,7 +2492,7 @@
         <v>9</v>
       </c>
       <c r="G51" t="s">
-        <v>92</v>
+        <v>128</v>
       </c>
       <c r="H51">
         <v>133.3333333333333</v>
@@ -2317,7 +2503,7 @@
         <v>10</v>
       </c>
       <c r="B52" t="s">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="C52">
         <v>20</v>
@@ -2332,7 +2518,7 @@
         <v>8</v>
       </c>
       <c r="G52" t="s">
-        <v>93</v>
+        <v>129</v>
       </c>
       <c r="H52">
         <v>26.66666666666666</v>
@@ -2343,7 +2529,7 @@
         <v>10</v>
       </c>
       <c r="B53" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="C53">
         <v>20</v>
@@ -2358,7 +2544,7 @@
         <v>9</v>
       </c>
       <c r="G53" t="s">
-        <v>94</v>
+        <v>130</v>
       </c>
       <c r="H53">
         <v>26.66666666666666</v>
@@ -2369,7 +2555,7 @@
         <v>10</v>
       </c>
       <c r="B54" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="C54">
         <v>30</v>
@@ -2392,7 +2578,7 @@
         <v>10</v>
       </c>
       <c r="B55" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="C55">
         <v>40</v>
@@ -2415,7 +2601,7 @@
         <v>10</v>
       </c>
       <c r="B56" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="C56">
         <v>40</v>
@@ -2438,7 +2624,7 @@
         <v>10</v>
       </c>
       <c r="B57" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="C57">
         <v>40</v>
@@ -2461,7 +2647,7 @@
         <v>10</v>
       </c>
       <c r="B58" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="C58">
         <v>45</v>
@@ -2484,7 +2670,7 @@
         <v>10</v>
       </c>
       <c r="B59" t="s">
-        <v>41</v>
+        <v>70</v>
       </c>
       <c r="C59">
         <v>45</v>
@@ -2507,7 +2693,7 @@
         <v>10</v>
       </c>
       <c r="B60" t="s">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="C60">
         <v>50</v>
@@ -2522,7 +2708,7 @@
         <v>7.5</v>
       </c>
       <c r="G60" t="s">
-        <v>95</v>
+        <v>131</v>
       </c>
       <c r="H60">
         <v>63.33333333333333</v>
@@ -2533,7 +2719,7 @@
         <v>10</v>
       </c>
       <c r="B61" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="C61">
         <v>50</v>
@@ -2548,7 +2734,7 @@
         <v>7.5</v>
       </c>
       <c r="G61" t="s">
-        <v>95</v>
+        <v>131</v>
       </c>
       <c r="H61">
         <v>63.33333333333333</v>
@@ -2559,7 +2745,7 @@
         <v>10</v>
       </c>
       <c r="B62" t="s">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="C62">
         <v>50</v>
@@ -2574,7 +2760,7 @@
         <v>8.5</v>
       </c>
       <c r="G62" t="s">
-        <v>95</v>
+        <v>131</v>
       </c>
       <c r="H62">
         <v>63.33333333333333</v>
@@ -2585,7 +2771,7 @@
         <v>10</v>
       </c>
       <c r="B63" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="C63">
         <v>50</v>
@@ -2600,7 +2786,7 @@
         <v>8.5</v>
       </c>
       <c r="G63" t="s">
-        <v>95</v>
+        <v>131</v>
       </c>
       <c r="H63">
         <v>63.33333333333333</v>
@@ -2611,7 +2797,7 @@
         <v>10</v>
       </c>
       <c r="B64" t="s">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="C64">
         <v>50</v>
@@ -2626,7 +2812,7 @@
         <v>9</v>
       </c>
       <c r="G64" t="s">
-        <v>95</v>
+        <v>131</v>
       </c>
       <c r="H64">
         <v>63.33333333333333</v>
@@ -2637,7 +2823,7 @@
         <v>10</v>
       </c>
       <c r="B65" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="C65">
         <v>50</v>
@@ -2652,7 +2838,7 @@
         <v>9</v>
       </c>
       <c r="G65" t="s">
-        <v>95</v>
+        <v>131</v>
       </c>
       <c r="H65">
         <v>63.33333333333333</v>
@@ -2663,7 +2849,7 @@
         <v>11</v>
       </c>
       <c r="B66" t="s">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="C66">
         <v>60</v>
@@ -2686,7 +2872,7 @@
         <v>11</v>
       </c>
       <c r="B67" t="s">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="C67">
         <v>100</v>
@@ -2709,7 +2895,7 @@
         <v>11</v>
       </c>
       <c r="B68" t="s">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="C68">
         <v>100</v>
@@ -2732,7 +2918,7 @@
         <v>11</v>
       </c>
       <c r="B69" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="C69">
         <v>60</v>
@@ -2755,7 +2941,7 @@
         <v>11</v>
       </c>
       <c r="B70" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="C70">
         <v>100</v>
@@ -2778,7 +2964,7 @@
         <v>11</v>
       </c>
       <c r="B71" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="C71">
         <v>80</v>
@@ -2801,7 +2987,7 @@
         <v>11</v>
       </c>
       <c r="B72" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="C72">
         <v>80</v>
@@ -2824,7 +3010,7 @@
         <v>11</v>
       </c>
       <c r="B73" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="C73">
         <v>20</v>
@@ -2847,7 +3033,7 @@
         <v>11</v>
       </c>
       <c r="B74" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="C74">
         <v>30</v>
@@ -2870,7 +3056,7 @@
         <v>11</v>
       </c>
       <c r="B75" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="C75">
         <v>35</v>
@@ -2893,7 +3079,7 @@
         <v>11</v>
       </c>
       <c r="B76" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="C76">
         <v>35</v>
@@ -2908,7 +3094,7 @@
         <v>10</v>
       </c>
       <c r="G76" t="s">
-        <v>96</v>
+        <v>132</v>
       </c>
       <c r="H76">
         <v>43.16666666666667</v>
@@ -2919,7 +3105,7 @@
         <v>11</v>
       </c>
       <c r="B77" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="C77">
         <v>30</v>
@@ -2942,7 +3128,7 @@
         <v>11</v>
       </c>
       <c r="B78" t="s">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="C78">
         <v>30</v>
@@ -2965,7 +3151,7 @@
         <v>11</v>
       </c>
       <c r="B79" t="s">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="C79">
         <v>50</v>
@@ -2988,7 +3174,7 @@
         <v>11</v>
       </c>
       <c r="B80" t="s">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="C80">
         <v>40</v>
@@ -3011,7 +3197,7 @@
         <v>11</v>
       </c>
       <c r="B81" t="s">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="C81">
         <v>22</v>
@@ -3034,7 +3220,7 @@
         <v>11</v>
       </c>
       <c r="B82" t="s">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="C82">
         <v>22</v>
@@ -3057,7 +3243,7 @@
         <v>11</v>
       </c>
       <c r="B83" t="s">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="C83">
         <v>22</v>
@@ -3080,7 +3266,7 @@
         <v>12</v>
       </c>
       <c r="B84" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="C84">
         <v>20</v>
@@ -3095,7 +3281,7 @@
         <v>4</v>
       </c>
       <c r="G84" t="s">
-        <v>97</v>
+        <v>133</v>
       </c>
       <c r="H84">
         <v>28</v>
@@ -3106,7 +3292,7 @@
         <v>12</v>
       </c>
       <c r="B85" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="C85">
         <v>40</v>
@@ -3129,7 +3315,7 @@
         <v>12</v>
       </c>
       <c r="B86" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="C86">
         <v>50</v>
@@ -3152,7 +3338,7 @@
         <v>12</v>
       </c>
       <c r="B87" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="C87">
         <v>60</v>
@@ -3175,7 +3361,7 @@
         <v>12</v>
       </c>
       <c r="B88" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="C88">
         <v>60</v>
@@ -3198,7 +3384,7 @@
         <v>12</v>
       </c>
       <c r="B89" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="C89">
         <v>60</v>
@@ -3213,7 +3399,7 @@
         <v>9</v>
       </c>
       <c r="G89" t="s">
-        <v>98</v>
+        <v>134</v>
       </c>
       <c r="H89">
         <v>64</v>
@@ -3224,7 +3410,7 @@
         <v>12</v>
       </c>
       <c r="B90" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="C90">
         <v>40</v>
@@ -3239,7 +3425,7 @@
         <v>8</v>
       </c>
       <c r="G90" t="s">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="H90">
         <v>60</v>
@@ -3250,7 +3436,7 @@
         <v>12</v>
       </c>
       <c r="B91" t="s">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="C91">
         <v>16</v>
@@ -3265,7 +3451,7 @@
         <v>7</v>
       </c>
       <c r="G91" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="H91">
         <v>21.33333333333333</v>
@@ -3276,7 +3462,7 @@
         <v>12</v>
       </c>
       <c r="B92" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="C92">
         <v>16</v>
@@ -3291,7 +3477,7 @@
         <v>7</v>
       </c>
       <c r="G92" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="H92">
         <v>21.33333333333333</v>
@@ -3302,7 +3488,7 @@
         <v>12</v>
       </c>
       <c r="B93" t="s">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="C93">
         <v>16</v>
@@ -3317,7 +3503,7 @@
         <v>8</v>
       </c>
       <c r="G93" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="H93">
         <v>21.33333333333333</v>
@@ -3328,7 +3514,7 @@
         <v>12</v>
       </c>
       <c r="B94" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="C94">
         <v>16</v>
@@ -3343,7 +3529,7 @@
         <v>8</v>
       </c>
       <c r="G94" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="H94">
         <v>21.33333333333333</v>
@@ -3354,7 +3540,7 @@
         <v>12</v>
       </c>
       <c r="B95" t="s">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="C95">
         <v>16</v>
@@ -3369,7 +3555,7 @@
         <v>8.5</v>
       </c>
       <c r="G95" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="H95">
         <v>21.33333333333333</v>
@@ -3380,7 +3566,7 @@
         <v>12</v>
       </c>
       <c r="B96" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="C96">
         <v>16</v>
@@ -3395,7 +3581,7 @@
         <v>8.5</v>
       </c>
       <c r="G96" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="H96">
         <v>21.33333333333333</v>
@@ -3406,7 +3592,7 @@
         <v>12</v>
       </c>
       <c r="B97" t="s">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="C97">
         <v>8</v>
@@ -3429,7 +3615,7 @@
         <v>12</v>
       </c>
       <c r="B98" t="s">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="C98">
         <v>8</v>
@@ -3452,7 +3638,7 @@
         <v>12</v>
       </c>
       <c r="B99" t="s">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="C99">
         <v>8</v>
@@ -3475,7 +3661,7 @@
         <v>12</v>
       </c>
       <c r="B100" t="s">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="C100">
         <v>58</v>
@@ -3490,7 +3676,7 @@
         <v>7</v>
       </c>
       <c r="G100" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="H100">
         <v>77.33333333333333</v>
@@ -3501,7 +3687,7 @@
         <v>12</v>
       </c>
       <c r="B101" t="s">
-        <v>52</v>
+        <v>81</v>
       </c>
       <c r="C101">
         <v>58</v>
@@ -3516,7 +3702,7 @@
         <v>7</v>
       </c>
       <c r="G101" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="H101">
         <v>77.33333333333333</v>
@@ -3527,7 +3713,7 @@
         <v>12</v>
       </c>
       <c r="B102" t="s">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="C102">
         <v>58</v>
@@ -3550,7 +3736,7 @@
         <v>12</v>
       </c>
       <c r="B103" t="s">
-        <v>52</v>
+        <v>81</v>
       </c>
       <c r="C103">
         <v>58</v>
@@ -3573,7 +3759,7 @@
         <v>12</v>
       </c>
       <c r="B104" t="s">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="C104">
         <v>58</v>
@@ -3596,7 +3782,7 @@
         <v>12</v>
       </c>
       <c r="B105" t="s">
-        <v>52</v>
+        <v>81</v>
       </c>
       <c r="C105">
         <v>58</v>
@@ -3619,7 +3805,7 @@
         <v>12</v>
       </c>
       <c r="B106" t="s">
-        <v>53</v>
+        <v>82</v>
       </c>
       <c r="C106">
         <v>45</v>
@@ -3642,7 +3828,7 @@
         <v>12</v>
       </c>
       <c r="B107" t="s">
-        <v>53</v>
+        <v>82</v>
       </c>
       <c r="C107">
         <v>45</v>
@@ -3665,7 +3851,7 @@
         <v>12</v>
       </c>
       <c r="B108" t="s">
-        <v>53</v>
+        <v>82</v>
       </c>
       <c r="C108">
         <v>45</v>
@@ -3688,7 +3874,7 @@
         <v>12</v>
       </c>
       <c r="B109" t="s">
-        <v>54</v>
+        <v>83</v>
       </c>
       <c r="C109">
         <v>20</v>
@@ -3711,7 +3897,7 @@
         <v>12</v>
       </c>
       <c r="B110" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="C110">
         <v>30</v>
@@ -3726,7 +3912,7 @@
         <v>10</v>
       </c>
       <c r="G110" t="s">
-        <v>102</v>
+        <v>138</v>
       </c>
       <c r="H110">
         <v>34</v>
@@ -3737,7 +3923,7 @@
         <v>13</v>
       </c>
       <c r="B111" t="s">
-        <v>55</v>
+        <v>84</v>
       </c>
       <c r="C111">
         <v>20</v>
@@ -3752,7 +3938,7 @@
         <v>3</v>
       </c>
       <c r="G111" t="s">
-        <v>103</v>
+        <v>139</v>
       </c>
       <c r="H111">
         <v>25.33333333333333</v>
@@ -3763,7 +3949,7 @@
         <v>13</v>
       </c>
       <c r="B112" t="s">
-        <v>56</v>
+        <v>85</v>
       </c>
       <c r="C112">
         <v>60</v>
@@ -3778,7 +3964,7 @@
         <v>5</v>
       </c>
       <c r="G112" t="s">
-        <v>104</v>
+        <v>140</v>
       </c>
       <c r="H112">
         <v>66</v>
@@ -3789,7 +3975,7 @@
         <v>13</v>
       </c>
       <c r="B113" t="s">
-        <v>55</v>
+        <v>84</v>
       </c>
       <c r="C113">
         <v>80</v>
@@ -3804,7 +3990,7 @@
         <v>7</v>
       </c>
       <c r="G113" t="s">
-        <v>105</v>
+        <v>141</v>
       </c>
       <c r="H113">
         <v>88</v>
@@ -3815,7 +4001,7 @@
         <v>13</v>
       </c>
       <c r="B114" t="s">
-        <v>55</v>
+        <v>84</v>
       </c>
       <c r="C114">
         <v>90</v>
@@ -3830,7 +4016,7 @@
         <v>7</v>
       </c>
       <c r="G114" t="s">
-        <v>106</v>
+        <v>142</v>
       </c>
       <c r="H114">
         <v>93.00000000000001</v>
@@ -3841,7 +4027,7 @@
         <v>13</v>
       </c>
       <c r="B115" t="s">
-        <v>55</v>
+        <v>84</v>
       </c>
       <c r="C115">
         <v>90</v>
@@ -3856,7 +4042,7 @@
         <v>7.5</v>
       </c>
       <c r="G115" t="s">
-        <v>107</v>
+        <v>143</v>
       </c>
       <c r="H115">
         <v>99.00000000000001</v>
@@ -3867,7 +4053,7 @@
         <v>13</v>
       </c>
       <c r="B116" t="s">
-        <v>55</v>
+        <v>84</v>
       </c>
       <c r="C116">
         <v>100</v>
@@ -3882,7 +4068,7 @@
         <v>8.5</v>
       </c>
       <c r="G116" t="s">
-        <v>108</v>
+        <v>144</v>
       </c>
       <c r="H116">
         <v>110</v>
@@ -3893,7 +4079,7 @@
         <v>13</v>
       </c>
       <c r="B117" t="s">
-        <v>55</v>
+        <v>84</v>
       </c>
       <c r="C117">
         <v>110</v>
@@ -3908,7 +4094,7 @@
         <v>9</v>
       </c>
       <c r="G117" t="s">
-        <v>109</v>
+        <v>145</v>
       </c>
       <c r="H117">
         <v>113.6666666666667</v>
@@ -3919,7 +4105,7 @@
         <v>13</v>
       </c>
       <c r="B118" t="s">
-        <v>57</v>
+        <v>86</v>
       </c>
       <c r="C118">
         <v>20</v>
@@ -3934,7 +4120,7 @@
         <v>5</v>
       </c>
       <c r="G118" t="s">
-        <v>110</v>
+        <v>146</v>
       </c>
       <c r="H118">
         <v>28</v>
@@ -3945,7 +4131,7 @@
         <v>13</v>
       </c>
       <c r="B119" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="C119">
         <v>30</v>
@@ -3960,7 +4146,7 @@
         <v>6</v>
       </c>
       <c r="G119" t="s">
-        <v>111</v>
+        <v>147</v>
       </c>
       <c r="H119">
         <v>36</v>
@@ -3971,7 +4157,7 @@
         <v>13</v>
       </c>
       <c r="B120" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="C120">
         <v>40</v>
@@ -3986,7 +4172,7 @@
         <v>7.5</v>
       </c>
       <c r="G120" t="s">
-        <v>112</v>
+        <v>148</v>
       </c>
       <c r="H120">
         <v>45.33333333333333</v>
@@ -3997,7 +4183,7 @@
         <v>13</v>
       </c>
       <c r="B121" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="C121">
         <v>45</v>
@@ -4012,7 +4198,7 @@
         <v>8.5</v>
       </c>
       <c r="G121" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="H121">
         <v>49.50000000000001</v>
@@ -4023,7 +4209,7 @@
         <v>13</v>
       </c>
       <c r="B122" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="C122">
         <v>50</v>
@@ -4038,7 +4224,7 @@
         <v>10</v>
       </c>
       <c r="G122" t="s">
-        <v>114</v>
+        <v>150</v>
       </c>
       <c r="H122">
         <v>50</v>
@@ -4049,7 +4235,7 @@
         <v>13</v>
       </c>
       <c r="B123" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="C123">
         <v>70</v>
@@ -4064,7 +4250,7 @@
         <v>6</v>
       </c>
       <c r="G123" t="s">
-        <v>115</v>
+        <v>151</v>
       </c>
       <c r="H123">
         <v>77</v>
@@ -4075,7 +4261,7 @@
         <v>13</v>
       </c>
       <c r="B124" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="C124">
         <v>120</v>
@@ -4090,7 +4276,7 @@
         <v>8.5</v>
       </c>
       <c r="G124" t="s">
-        <v>116</v>
+        <v>152</v>
       </c>
       <c r="H124">
         <v>124</v>
@@ -4101,7 +4287,7 @@
         <v>13</v>
       </c>
       <c r="B125" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="C125">
         <v>120</v>
@@ -4116,7 +4302,7 @@
         <v>9.5</v>
       </c>
       <c r="G125" t="s">
-        <v>117</v>
+        <v>153</v>
       </c>
       <c r="H125">
         <v>124</v>
@@ -4127,7 +4313,7 @@
         <v>13</v>
       </c>
       <c r="B126" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="C126">
         <v>120</v>
@@ -4142,7 +4328,7 @@
         <v>9.5</v>
       </c>
       <c r="G126" t="s">
-        <v>118</v>
+        <v>154</v>
       </c>
       <c r="H126">
         <v>124</v>
@@ -4153,7 +4339,7 @@
         <v>13</v>
       </c>
       <c r="B127" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="C127">
         <v>120</v>
@@ -4168,7 +4354,7 @@
         <v>9.5</v>
       </c>
       <c r="G127" t="s">
-        <v>119</v>
+        <v>155</v>
       </c>
       <c r="H127">
         <v>124</v>
@@ -4179,7 +4365,7 @@
         <v>13</v>
       </c>
       <c r="B128" t="s">
-        <v>58</v>
+        <v>87</v>
       </c>
       <c r="C128">
         <v>20</v>
@@ -4194,7 +4380,7 @@
         <v>6.5</v>
       </c>
       <c r="G128" t="s">
-        <v>120</v>
+        <v>156</v>
       </c>
       <c r="H128">
         <v>26.66666666666666</v>
@@ -4205,7 +4391,7 @@
         <v>13</v>
       </c>
       <c r="B129" t="s">
-        <v>59</v>
+        <v>88</v>
       </c>
       <c r="C129">
         <v>20</v>
@@ -4220,7 +4406,7 @@
         <v>6.5</v>
       </c>
       <c r="G129" t="s">
-        <v>121</v>
+        <v>157</v>
       </c>
       <c r="H129">
         <v>26.66666666666666</v>
@@ -4231,7 +4417,7 @@
         <v>13</v>
       </c>
       <c r="B130" t="s">
-        <v>58</v>
+        <v>87</v>
       </c>
       <c r="C130">
         <v>20</v>
@@ -4246,7 +4432,7 @@
         <v>8</v>
       </c>
       <c r="G130" t="s">
-        <v>122</v>
+        <v>158</v>
       </c>
       <c r="H130">
         <v>26.66666666666666</v>
@@ -4257,7 +4443,7 @@
         <v>13</v>
       </c>
       <c r="B131" t="s">
-        <v>59</v>
+        <v>88</v>
       </c>
       <c r="C131">
         <v>20</v>
@@ -4272,7 +4458,7 @@
         <v>8</v>
       </c>
       <c r="G131" t="s">
-        <v>123</v>
+        <v>159</v>
       </c>
       <c r="H131">
         <v>26.66666666666666</v>
@@ -4283,7 +4469,7 @@
         <v>13</v>
       </c>
       <c r="B132" t="s">
-        <v>58</v>
+        <v>87</v>
       </c>
       <c r="C132">
         <v>20</v>
@@ -4298,7 +4484,7 @@
         <v>8.5</v>
       </c>
       <c r="G132" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="H132">
         <v>26.66666666666666</v>
@@ -4309,7 +4495,7 @@
         <v>13</v>
       </c>
       <c r="B133" t="s">
-        <v>59</v>
+        <v>88</v>
       </c>
       <c r="C133">
         <v>20</v>
@@ -4324,7 +4510,7 @@
         <v>8.5</v>
       </c>
       <c r="G133" t="s">
-        <v>125</v>
+        <v>161</v>
       </c>
       <c r="H133">
         <v>26.66666666666666</v>
@@ -4335,7 +4521,7 @@
         <v>14</v>
       </c>
       <c r="B134" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="C134">
         <v>20</v>
@@ -4350,7 +4536,7 @@
         <v>3</v>
       </c>
       <c r="G134" t="s">
-        <v>103</v>
+        <v>139</v>
       </c>
       <c r="H134">
         <v>25.33333333333333</v>
@@ -4361,7 +4547,7 @@
         <v>14</v>
       </c>
       <c r="B135" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="C135">
         <v>60</v>
@@ -4376,7 +4562,7 @@
         <v>6</v>
       </c>
       <c r="G135" t="s">
-        <v>126</v>
+        <v>162</v>
       </c>
       <c r="H135">
         <v>72</v>
@@ -4387,7 +4573,7 @@
         <v>14</v>
       </c>
       <c r="B136" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="C136">
         <v>80</v>
@@ -4402,7 +4588,7 @@
         <v>7</v>
       </c>
       <c r="G136" t="s">
-        <v>127</v>
+        <v>163</v>
       </c>
       <c r="H136">
         <v>88</v>
@@ -4413,7 +4599,7 @@
         <v>14</v>
       </c>
       <c r="B137" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="C137">
         <v>100</v>
@@ -4428,7 +4614,7 @@
         <v>7</v>
       </c>
       <c r="G137" t="s">
-        <v>128</v>
+        <v>164</v>
       </c>
       <c r="H137">
         <v>103.3333333333333</v>
@@ -4439,7 +4625,7 @@
         <v>14</v>
       </c>
       <c r="B138" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="C138">
         <v>70</v>
@@ -4454,7 +4640,7 @@
         <v>8</v>
       </c>
       <c r="G138" t="s">
-        <v>129</v>
+        <v>165</v>
       </c>
       <c r="H138">
         <v>98</v>
@@ -4465,7 +4651,7 @@
         <v>14</v>
       </c>
       <c r="B139" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="C139">
         <v>80</v>
@@ -4480,7 +4666,7 @@
         <v>8.5</v>
       </c>
       <c r="G139" t="s">
-        <v>130</v>
+        <v>166</v>
       </c>
       <c r="H139">
         <v>101.3333333333333</v>
@@ -4491,7 +4677,7 @@
         <v>14</v>
       </c>
       <c r="B140" t="s">
-        <v>57</v>
+        <v>86</v>
       </c>
       <c r="C140">
         <v>20</v>
@@ -4506,7 +4692,7 @@
         <v>5</v>
       </c>
       <c r="G140" t="s">
-        <v>131</v>
+        <v>167</v>
       </c>
       <c r="H140">
         <v>28</v>
@@ -4517,7 +4703,7 @@
         <v>14</v>
       </c>
       <c r="B141" t="s">
-        <v>57</v>
+        <v>86</v>
       </c>
       <c r="C141">
         <v>30</v>
@@ -4532,7 +4718,7 @@
         <v>7</v>
       </c>
       <c r="G141" t="s">
-        <v>105</v>
+        <v>141</v>
       </c>
       <c r="H141">
         <v>38</v>
@@ -4543,7 +4729,7 @@
         <v>14</v>
       </c>
       <c r="B142" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="C142">
         <v>40</v>
@@ -4558,7 +4744,7 @@
         <v>8</v>
       </c>
       <c r="G142" t="s">
-        <v>132</v>
+        <v>168</v>
       </c>
       <c r="H142">
         <v>48</v>
@@ -4569,7 +4755,7 @@
         <v>14</v>
       </c>
       <c r="B143" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="C143">
         <v>40</v>
@@ -4584,7 +4770,7 @@
         <v>9</v>
       </c>
       <c r="G143" t="s">
-        <v>133</v>
+        <v>169</v>
       </c>
       <c r="H143">
         <v>48</v>
@@ -4595,7 +4781,7 @@
         <v>14</v>
       </c>
       <c r="B144" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="C144">
         <v>30</v>
@@ -4610,7 +4796,7 @@
         <v>9</v>
       </c>
       <c r="G144" t="s">
-        <v>134</v>
+        <v>170</v>
       </c>
       <c r="H144">
         <v>42</v>
@@ -4621,7 +4807,7 @@
         <v>14</v>
       </c>
       <c r="B145" t="s">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="C145">
         <v>30</v>
@@ -4636,7 +4822,7 @@
         <v>7</v>
       </c>
       <c r="G145" t="s">
-        <v>135</v>
+        <v>171</v>
       </c>
       <c r="H145">
         <v>45</v>
@@ -4647,7 +4833,7 @@
         <v>14</v>
       </c>
       <c r="B146" t="s">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="C146">
         <v>50</v>
@@ -4662,7 +4848,7 @@
         <v>7.5</v>
       </c>
       <c r="G146" t="s">
-        <v>105</v>
+        <v>141</v>
       </c>
       <c r="H146">
         <v>63.33333333333333</v>
@@ -4673,7 +4859,7 @@
         <v>14</v>
       </c>
       <c r="B147" t="s">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="C147">
         <v>50</v>
@@ -4688,7 +4874,7 @@
         <v>8</v>
       </c>
       <c r="G147" t="s">
-        <v>105</v>
+        <v>141</v>
       </c>
       <c r="H147">
         <v>63.33333333333333</v>
@@ -4699,7 +4885,7 @@
         <v>14</v>
       </c>
       <c r="B148" t="s">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="C148">
         <v>50</v>
@@ -4714,7 +4900,7 @@
         <v>8.5</v>
       </c>
       <c r="G148" t="s">
-        <v>136</v>
+        <v>172</v>
       </c>
       <c r="H148">
         <v>63.33333333333333</v>
@@ -4725,7 +4911,7 @@
         <v>14</v>
       </c>
       <c r="B149" t="s">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="C149">
         <v>50</v>
@@ -4740,7 +4926,7 @@
         <v>9.5</v>
       </c>
       <c r="G149" t="s">
-        <v>137</v>
+        <v>173</v>
       </c>
       <c r="H149">
         <v>63.33333333333333</v>
@@ -4751,7 +4937,7 @@
         <v>14</v>
       </c>
       <c r="B150" t="s">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="C150">
         <v>40</v>
@@ -4766,7 +4952,7 @@
         <v>8</v>
       </c>
       <c r="G150" t="s">
-        <v>134</v>
+        <v>170</v>
       </c>
       <c r="H150">
         <v>56</v>
@@ -4777,7 +4963,7 @@
         <v>14</v>
       </c>
       <c r="B151" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="C151">
         <v>70</v>
@@ -4792,7 +4978,7 @@
         <v>6</v>
       </c>
       <c r="G151" t="s">
-        <v>138</v>
+        <v>174</v>
       </c>
       <c r="H151">
         <v>84</v>
@@ -4803,7 +4989,7 @@
         <v>14</v>
       </c>
       <c r="B152" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="C152">
         <v>120</v>
@@ -4818,7 +5004,7 @@
         <v>6</v>
       </c>
       <c r="G152" t="s">
-        <v>139</v>
+        <v>175</v>
       </c>
       <c r="H152">
         <v>124</v>
@@ -4829,7 +5015,7 @@
         <v>14</v>
       </c>
       <c r="B153" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="C153">
         <v>120</v>
@@ -4844,7 +5030,7 @@
         <v>8</v>
       </c>
       <c r="G153" t="s">
-        <v>140</v>
+        <v>176</v>
       </c>
       <c r="H153">
         <v>140</v>
@@ -4855,7 +5041,7 @@
         <v>14</v>
       </c>
       <c r="B154" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="C154">
         <v>130</v>
@@ -4870,7 +5056,7 @@
         <v>8.5</v>
       </c>
       <c r="G154" t="s">
-        <v>141</v>
+        <v>177</v>
       </c>
       <c r="H154">
         <v>151.6666666666667</v>
@@ -4881,7 +5067,7 @@
         <v>14</v>
       </c>
       <c r="B155" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="C155">
         <v>130</v>
@@ -4896,7 +5082,7 @@
         <v>9</v>
       </c>
       <c r="G155" t="s">
-        <v>142</v>
+        <v>178</v>
       </c>
       <c r="H155">
         <v>151.6666666666667</v>
@@ -4907,7 +5093,7 @@
         <v>15</v>
       </c>
       <c r="B156" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="C156">
         <v>20</v>
@@ -4922,7 +5108,7 @@
         <v>4</v>
       </c>
       <c r="G156" t="s">
-        <v>103</v>
+        <v>139</v>
       </c>
       <c r="H156">
         <v>28</v>
@@ -4933,7 +5119,7 @@
         <v>15</v>
       </c>
       <c r="B157" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="C157">
         <v>40</v>
@@ -4956,7 +5142,7 @@
         <v>15</v>
       </c>
       <c r="B158" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="C158">
         <v>60</v>
@@ -4971,7 +5157,7 @@
         <v>6.5</v>
       </c>
       <c r="G158" t="s">
-        <v>143</v>
+        <v>179</v>
       </c>
       <c r="H158">
         <v>62.00000000000001</v>
@@ -4982,7 +5168,7 @@
         <v>15</v>
       </c>
       <c r="B159" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="C159">
         <v>70</v>
@@ -4997,7 +5183,7 @@
         <v>8.5</v>
       </c>
       <c r="G159" t="s">
-        <v>144</v>
+        <v>180</v>
       </c>
       <c r="H159">
         <v>72.33333333333334</v>
@@ -5008,7 +5194,7 @@
         <v>15</v>
       </c>
       <c r="B160" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="C160">
         <v>65</v>
@@ -5023,7 +5209,7 @@
         <v>8</v>
       </c>
       <c r="G160" t="s">
-        <v>145</v>
+        <v>181</v>
       </c>
       <c r="H160">
         <v>67.16666666666667</v>
@@ -5034,7 +5220,7 @@
         <v>15</v>
       </c>
       <c r="B161" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="C161">
         <v>60</v>
@@ -5057,7 +5243,7 @@
         <v>15</v>
       </c>
       <c r="B162" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="C162">
         <v>60</v>
@@ -5072,7 +5258,7 @@
         <v>9</v>
       </c>
       <c r="G162" t="s">
-        <v>146</v>
+        <v>182</v>
       </c>
       <c r="H162">
         <v>66</v>
@@ -5083,7 +5269,7 @@
         <v>15</v>
       </c>
       <c r="B163" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="C163">
         <v>45</v>
@@ -5098,7 +5284,7 @@
         <v>8</v>
       </c>
       <c r="G163" t="s">
-        <v>147</v>
+        <v>183</v>
       </c>
       <c r="H163">
         <v>62.99999999999999</v>
@@ -5109,7 +5295,7 @@
         <v>15</v>
       </c>
       <c r="B164" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="C164">
         <v>45</v>
@@ -5132,7 +5318,7 @@
         <v>15</v>
       </c>
       <c r="B165" t="s">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="C165">
         <v>20</v>
@@ -5147,7 +5333,7 @@
         <v>7</v>
       </c>
       <c r="G165" t="s">
-        <v>120</v>
+        <v>156</v>
       </c>
       <c r="H165">
         <v>26.66666666666666</v>
@@ -5158,7 +5344,7 @@
         <v>15</v>
       </c>
       <c r="B166" t="s">
-        <v>62</v>
+        <v>91</v>
       </c>
       <c r="C166">
         <v>20</v>
@@ -5173,7 +5359,7 @@
         <v>6</v>
       </c>
       <c r="G166" t="s">
-        <v>122</v>
+        <v>158</v>
       </c>
       <c r="H166">
         <v>28</v>
@@ -5184,7 +5370,7 @@
         <v>15</v>
       </c>
       <c r="B167" t="s">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="C167">
         <v>20</v>
@@ -5199,7 +5385,7 @@
         <v>7</v>
       </c>
       <c r="G167" t="s">
-        <v>121</v>
+        <v>157</v>
       </c>
       <c r="H167">
         <v>28</v>
@@ -5210,7 +5396,7 @@
         <v>15</v>
       </c>
       <c r="B168" t="s">
-        <v>62</v>
+        <v>91</v>
       </c>
       <c r="C168">
         <v>20</v>
@@ -5225,7 +5411,7 @@
         <v>7</v>
       </c>
       <c r="G168" t="s">
-        <v>123</v>
+        <v>159</v>
       </c>
       <c r="H168">
         <v>30</v>
@@ -5236,7 +5422,7 @@
         <v>15</v>
       </c>
       <c r="B169" t="s">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="C169">
         <v>22.5</v>
@@ -5251,7 +5437,7 @@
         <v>7.5</v>
       </c>
       <c r="G169" t="s">
-        <v>148</v>
+        <v>184</v>
       </c>
       <c r="H169">
         <v>30</v>
@@ -5262,7 +5448,7 @@
         <v>15</v>
       </c>
       <c r="B170" t="s">
-        <v>62</v>
+        <v>91</v>
       </c>
       <c r="C170">
         <v>22.5</v>
@@ -5277,7 +5463,7 @@
         <v>7</v>
       </c>
       <c r="G170" t="s">
-        <v>149</v>
+        <v>185</v>
       </c>
       <c r="H170">
         <v>31.5</v>
@@ -5288,7 +5474,7 @@
         <v>15</v>
       </c>
       <c r="B171" t="s">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="C171">
         <v>25</v>
@@ -5303,7 +5489,7 @@
         <v>8</v>
       </c>
       <c r="G171" t="s">
-        <v>150</v>
+        <v>186</v>
       </c>
       <c r="H171">
         <v>31.66666666666666</v>
@@ -5314,7 +5500,7 @@
         <v>15</v>
       </c>
       <c r="B172" t="s">
-        <v>62</v>
+        <v>91</v>
       </c>
       <c r="C172">
         <v>25</v>
@@ -5329,7 +5515,7 @@
         <v>7.5</v>
       </c>
       <c r="G172" t="s">
-        <v>151</v>
+        <v>187</v>
       </c>
       <c r="H172">
         <v>35</v>
@@ -5340,7 +5526,7 @@
         <v>15</v>
       </c>
       <c r="B173" t="s">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="C173">
         <v>25</v>
@@ -5355,7 +5541,7 @@
         <v>8</v>
       </c>
       <c r="G173" t="s">
-        <v>152</v>
+        <v>188</v>
       </c>
       <c r="H173">
         <v>31.66666666666666</v>
@@ -5366,7 +5552,7 @@
         <v>15</v>
       </c>
       <c r="B174" t="s">
-        <v>62</v>
+        <v>91</v>
       </c>
       <c r="C174">
         <v>25</v>
@@ -5381,7 +5567,7 @@
         <v>8</v>
       </c>
       <c r="G174" t="s">
-        <v>153</v>
+        <v>189</v>
       </c>
       <c r="H174">
         <v>37.5</v>
@@ -5392,7 +5578,7 @@
         <v>15</v>
       </c>
       <c r="B175" t="s">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="C175">
         <v>40</v>
@@ -5407,7 +5593,7 @@
         <v>7.5</v>
       </c>
       <c r="G175" t="s">
-        <v>154</v>
+        <v>190</v>
       </c>
       <c r="H175">
         <v>50.66666666666666</v>
@@ -5418,7 +5604,7 @@
         <v>15</v>
       </c>
       <c r="B176" t="s">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="C176">
         <v>40</v>
@@ -5433,7 +5619,7 @@
         <v>8.5</v>
       </c>
       <c r="G176" t="s">
-        <v>154</v>
+        <v>190</v>
       </c>
       <c r="H176">
         <v>50.66666666666666</v>
@@ -5444,7 +5630,7 @@
         <v>15</v>
       </c>
       <c r="B177" t="s">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="C177">
         <v>40</v>
@@ -5459,7 +5645,7 @@
         <v>9</v>
       </c>
       <c r="G177" t="s">
-        <v>154</v>
+        <v>190</v>
       </c>
       <c r="H177">
         <v>48</v>
@@ -5470,7 +5656,7 @@
         <v>15</v>
       </c>
       <c r="B178" t="s">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="C178">
         <v>22</v>
@@ -5485,7 +5671,7 @@
         <v>7</v>
       </c>
       <c r="G178" t="s">
-        <v>155</v>
+        <v>191</v>
       </c>
       <c r="H178">
         <v>27.86666666666667</v>
@@ -5496,7 +5682,7 @@
         <v>15</v>
       </c>
       <c r="B179" t="s">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="C179">
         <v>22</v>
@@ -5519,7 +5705,7 @@
         <v>15</v>
       </c>
       <c r="B180" t="s">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="C180">
         <v>22</v>
@@ -5534,7 +5720,7 @@
         <v>8.5</v>
       </c>
       <c r="G180" t="s">
-        <v>156</v>
+        <v>192</v>
       </c>
       <c r="H180">
         <v>27.86666666666667</v>
@@ -5545,7 +5731,7 @@
         <v>16</v>
       </c>
       <c r="B181" t="s">
-        <v>64</v>
+        <v>93</v>
       </c>
       <c r="C181">
         <v>20</v>
@@ -5568,7 +5754,7 @@
         <v>16</v>
       </c>
       <c r="B182" t="s">
-        <v>64</v>
+        <v>93</v>
       </c>
       <c r="C182">
         <v>22</v>
@@ -5591,7 +5777,7 @@
         <v>16</v>
       </c>
       <c r="B183" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="C183">
         <v>20</v>
@@ -5606,7 +5792,7 @@
         <v>4</v>
       </c>
       <c r="G183" t="s">
-        <v>103</v>
+        <v>139</v>
       </c>
       <c r="H183">
         <v>25.33333333333333</v>
@@ -5617,7 +5803,7 @@
         <v>16</v>
       </c>
       <c r="B184" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="C184">
         <v>60</v>
@@ -5640,7 +5826,7 @@
         <v>16</v>
       </c>
       <c r="B185" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="C185">
         <v>80</v>
@@ -5663,7 +5849,7 @@
         <v>16</v>
       </c>
       <c r="B186" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="C186">
         <v>100</v>
@@ -5686,7 +5872,7 @@
         <v>16</v>
       </c>
       <c r="B187" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="C187">
         <v>110</v>
@@ -5709,7 +5895,7 @@
         <v>16</v>
       </c>
       <c r="B188" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="C188">
         <v>120</v>
@@ -5724,7 +5910,7 @@
         <v>8.5</v>
       </c>
       <c r="G188" t="s">
-        <v>157</v>
+        <v>193</v>
       </c>
       <c r="H188">
         <v>124</v>
@@ -5735,7 +5921,7 @@
         <v>16</v>
       </c>
       <c r="B189" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="C189">
         <v>80</v>
@@ -5750,7 +5936,7 @@
         <v>7.5</v>
       </c>
       <c r="G189" t="s">
-        <v>158</v>
+        <v>194</v>
       </c>
       <c r="H189">
         <v>112</v>
@@ -5761,7 +5947,7 @@
         <v>16</v>
       </c>
       <c r="B190" t="s">
-        <v>65</v>
+        <v>94</v>
       </c>
       <c r="C190">
         <v>-30</v>
@@ -5776,7 +5962,7 @@
         <v>6</v>
       </c>
       <c r="G190" t="s">
-        <v>159</v>
+        <v>195</v>
       </c>
       <c r="H190">
         <v>-38</v>
@@ -5787,7 +5973,7 @@
         <v>16</v>
       </c>
       <c r="B191" t="s">
-        <v>66</v>
+        <v>95</v>
       </c>
       <c r="C191">
         <v>-30</v>
@@ -5802,7 +5988,7 @@
         <v>6</v>
       </c>
       <c r="G191" t="s">
-        <v>159</v>
+        <v>195</v>
       </c>
       <c r="H191">
         <v>-38</v>
@@ -5813,7 +5999,7 @@
         <v>16</v>
       </c>
       <c r="B192" t="s">
-        <v>65</v>
+        <v>94</v>
       </c>
       <c r="C192">
         <v>-25</v>
@@ -5828,7 +6014,7 @@
         <v>7.5</v>
       </c>
       <c r="G192" t="s">
-        <v>160</v>
+        <v>196</v>
       </c>
       <c r="H192">
         <v>-33.33333333333333</v>
@@ -5839,7 +6025,7 @@
         <v>16</v>
       </c>
       <c r="B193" t="s">
-        <v>66</v>
+        <v>95</v>
       </c>
       <c r="C193">
         <v>-25</v>
@@ -5854,7 +6040,7 @@
         <v>7.5</v>
       </c>
       <c r="G193" t="s">
-        <v>160</v>
+        <v>196</v>
       </c>
       <c r="H193">
         <v>-33.33333333333333</v>
@@ -5865,7 +6051,7 @@
         <v>16</v>
       </c>
       <c r="B194" t="s">
-        <v>65</v>
+        <v>94</v>
       </c>
       <c r="C194">
         <v>-20</v>
@@ -5880,7 +6066,7 @@
         <v>8</v>
       </c>
       <c r="G194" t="s">
-        <v>161</v>
+        <v>197</v>
       </c>
       <c r="H194">
         <v>-25.33333333333333</v>
@@ -5891,7 +6077,7 @@
         <v>16</v>
       </c>
       <c r="B195" t="s">
-        <v>66</v>
+        <v>95</v>
       </c>
       <c r="C195">
         <v>-20</v>
@@ -5906,7 +6092,7 @@
         <v>8</v>
       </c>
       <c r="G195" t="s">
-        <v>161</v>
+        <v>197</v>
       </c>
       <c r="H195">
         <v>-25.33333333333333</v>
@@ -5917,7 +6103,7 @@
         <v>16</v>
       </c>
       <c r="B196" t="s">
-        <v>67</v>
+        <v>96</v>
       </c>
       <c r="C196">
         <v>35</v>
@@ -5932,7 +6118,7 @@
         <v>7</v>
       </c>
       <c r="G196" t="s">
-        <v>162</v>
+        <v>198</v>
       </c>
       <c r="H196">
         <v>52.5</v>
@@ -5943,7 +6129,7 @@
         <v>16</v>
       </c>
       <c r="B197" t="s">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="C197">
         <v>25</v>
@@ -5958,7 +6144,7 @@
         <v>7</v>
       </c>
       <c r="G197" t="s">
-        <v>162</v>
+        <v>198</v>
       </c>
       <c r="H197">
         <v>37.5</v>
@@ -5969,7 +6155,7 @@
         <v>16</v>
       </c>
       <c r="B198" t="s">
-        <v>67</v>
+        <v>96</v>
       </c>
       <c r="C198">
         <v>35</v>
@@ -5984,7 +6170,7 @@
         <v>7</v>
       </c>
       <c r="G198" t="s">
-        <v>163</v>
+        <v>199</v>
       </c>
       <c r="H198">
         <v>52.5</v>
@@ -5995,7 +6181,7 @@
         <v>16</v>
       </c>
       <c r="B199" t="s">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="C199">
         <v>25</v>
@@ -6010,7 +6196,7 @@
         <v>7</v>
       </c>
       <c r="G199" t="s">
-        <v>163</v>
+        <v>199</v>
       </c>
       <c r="H199">
         <v>37.5</v>
@@ -6021,7 +6207,7 @@
         <v>17</v>
       </c>
       <c r="B200" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="C200">
         <v>70</v>
@@ -6036,7 +6222,7 @@
         <v>6</v>
       </c>
       <c r="G200" t="s">
-        <v>164</v>
+        <v>200</v>
       </c>
       <c r="H200">
         <v>84</v>
@@ -6047,7 +6233,7 @@
         <v>17</v>
       </c>
       <c r="B201" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="C201">
         <v>90</v>
@@ -6070,7 +6256,7 @@
         <v>17</v>
       </c>
       <c r="B202" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="C202">
         <v>120</v>
@@ -6093,7 +6279,7 @@
         <v>17</v>
       </c>
       <c r="B203" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="C203">
         <v>120</v>
@@ -6116,7 +6302,7 @@
         <v>17</v>
       </c>
       <c r="B204" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="C204">
         <v>120</v>
@@ -6139,7 +6325,7 @@
         <v>17</v>
       </c>
       <c r="B205" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="C205">
         <v>120</v>
@@ -6162,7 +6348,7 @@
         <v>17</v>
       </c>
       <c r="B206" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="C206">
         <v>120</v>
@@ -6185,7 +6371,7 @@
         <v>17</v>
       </c>
       <c r="B207" t="s">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="C207">
         <v>20</v>
@@ -6200,7 +6386,7 @@
         <v>6</v>
       </c>
       <c r="G207" t="s">
-        <v>165</v>
+        <v>201</v>
       </c>
       <c r="H207">
         <v>28</v>
@@ -6211,7 +6397,7 @@
         <v>17</v>
       </c>
       <c r="B208" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="C208">
         <v>30</v>
@@ -6234,7 +6420,7 @@
         <v>17</v>
       </c>
       <c r="B209" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="C209">
         <v>35</v>
@@ -6257,7 +6443,7 @@
         <v>17</v>
       </c>
       <c r="B210" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="C210">
         <v>35</v>
@@ -6280,7 +6466,7 @@
         <v>17</v>
       </c>
       <c r="B211" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="C211">
         <v>35</v>
@@ -6303,7 +6489,7 @@
         <v>17</v>
       </c>
       <c r="B212" t="s">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="C212">
         <v>22</v>
@@ -6318,7 +6504,7 @@
         <v>7.5</v>
       </c>
       <c r="G212" t="s">
-        <v>85</v>
+        <v>121</v>
       </c>
       <c r="H212">
         <v>27.86666666666667</v>
@@ -6329,7 +6515,7 @@
         <v>17</v>
       </c>
       <c r="B213" t="s">
-        <v>62</v>
+        <v>91</v>
       </c>
       <c r="C213">
         <v>22</v>
@@ -6344,7 +6530,7 @@
         <v>7.5</v>
       </c>
       <c r="G213" t="s">
-        <v>86</v>
+        <v>122</v>
       </c>
       <c r="H213">
         <v>30.8</v>
@@ -6355,7 +6541,7 @@
         <v>17</v>
       </c>
       <c r="B214" t="s">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="C214">
         <v>22</v>
@@ -6370,7 +6556,7 @@
         <v>8</v>
       </c>
       <c r="G214" t="s">
-        <v>85</v>
+        <v>121</v>
       </c>
       <c r="H214">
         <v>27.86666666666667</v>
@@ -6381,7 +6567,7 @@
         <v>17</v>
       </c>
       <c r="B215" t="s">
-        <v>62</v>
+        <v>91</v>
       </c>
       <c r="C215">
         <v>22</v>
@@ -6396,7 +6582,7 @@
         <v>8</v>
       </c>
       <c r="G215" t="s">
-        <v>86</v>
+        <v>122</v>
       </c>
       <c r="H215">
         <v>30.8</v>
@@ -6407,7 +6593,7 @@
         <v>17</v>
       </c>
       <c r="B216" t="s">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="C216">
         <v>22</v>
@@ -6422,7 +6608,7 @@
         <v>8.5</v>
       </c>
       <c r="G216" t="s">
-        <v>85</v>
+        <v>121</v>
       </c>
       <c r="H216">
         <v>27.86666666666667</v>
@@ -6433,7 +6619,7 @@
         <v>17</v>
       </c>
       <c r="B217" t="s">
-        <v>62</v>
+        <v>91</v>
       </c>
       <c r="C217">
         <v>22</v>
@@ -6448,7 +6634,7 @@
         <v>8</v>
       </c>
       <c r="G217" t="s">
-        <v>86</v>
+        <v>122</v>
       </c>
       <c r="H217">
         <v>30.8</v>
@@ -6459,7 +6645,7 @@
         <v>17</v>
       </c>
       <c r="B218" t="s">
-        <v>69</v>
+        <v>98</v>
       </c>
       <c r="C218">
         <v>25</v>
@@ -6474,7 +6660,7 @@
         <v>8</v>
       </c>
       <c r="G218" t="s">
-        <v>166</v>
+        <v>202</v>
       </c>
       <c r="H218">
         <v>31.66666666666666</v>
@@ -6485,7 +6671,7 @@
         <v>17</v>
       </c>
       <c r="B219" t="s">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="C219">
         <v>25</v>
@@ -6500,7 +6686,7 @@
         <v>6.5</v>
       </c>
       <c r="G219" t="s">
-        <v>167</v>
+        <v>203</v>
       </c>
       <c r="H219">
         <v>31.66666666666666</v>
@@ -6511,7 +6697,7 @@
         <v>17</v>
       </c>
       <c r="B220" t="s">
-        <v>69</v>
+        <v>98</v>
       </c>
       <c r="C220">
         <v>25</v>
@@ -6526,7 +6712,7 @@
         <v>8</v>
       </c>
       <c r="G220" t="s">
-        <v>166</v>
+        <v>202</v>
       </c>
       <c r="H220">
         <v>31.66666666666666</v>
@@ -6537,7 +6723,7 @@
         <v>17</v>
       </c>
       <c r="B221" t="s">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="C221">
         <v>25</v>
@@ -6552,7 +6738,7 @@
         <v>7.5</v>
       </c>
       <c r="G221" t="s">
-        <v>167</v>
+        <v>203</v>
       </c>
       <c r="H221">
         <v>31.66666666666666</v>
@@ -6563,7 +6749,7 @@
         <v>17</v>
       </c>
       <c r="B222" t="s">
-        <v>69</v>
+        <v>98</v>
       </c>
       <c r="C222">
         <v>25</v>
@@ -6578,7 +6764,7 @@
         <v>9</v>
       </c>
       <c r="G222" t="s">
-        <v>166</v>
+        <v>202</v>
       </c>
       <c r="H222">
         <v>31.66666666666666</v>
@@ -6589,7 +6775,7 @@
         <v>17</v>
       </c>
       <c r="B223" t="s">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="C223">
         <v>25</v>
@@ -6604,7 +6790,7 @@
         <v>9</v>
       </c>
       <c r="G223" t="s">
-        <v>167</v>
+        <v>203</v>
       </c>
       <c r="H223">
         <v>31.66666666666666</v>
@@ -6615,7 +6801,7 @@
         <v>18</v>
       </c>
       <c r="B224" t="s">
-        <v>55</v>
+        <v>84</v>
       </c>
       <c r="C224">
         <v>70</v>
@@ -6630,7 +6816,7 @@
         <v>6.5</v>
       </c>
       <c r="G224" t="s">
-        <v>103</v>
+        <v>139</v>
       </c>
       <c r="H224">
         <v>84</v>
@@ -6641,7 +6827,7 @@
         <v>18</v>
       </c>
       <c r="B225" t="s">
-        <v>55</v>
+        <v>84</v>
       </c>
       <c r="C225">
         <v>85</v>
@@ -6656,7 +6842,7 @@
         <v>8</v>
       </c>
       <c r="G225" t="s">
-        <v>168</v>
+        <v>204</v>
       </c>
       <c r="H225">
         <v>119</v>
@@ -6667,7 +6853,7 @@
         <v>18</v>
       </c>
       <c r="B226" t="s">
-        <v>55</v>
+        <v>84</v>
       </c>
       <c r="C226">
         <v>85</v>
@@ -6682,7 +6868,7 @@
         <v>9</v>
       </c>
       <c r="G226" t="s">
-        <v>169</v>
+        <v>205</v>
       </c>
       <c r="H226">
         <v>119</v>
@@ -6693,7 +6879,7 @@
         <v>18</v>
       </c>
       <c r="B227" t="s">
-        <v>55</v>
+        <v>84</v>
       </c>
       <c r="C227">
         <v>85</v>
@@ -6708,7 +6894,7 @@
         <v>10</v>
       </c>
       <c r="G227" t="s">
-        <v>170</v>
+        <v>206</v>
       </c>
       <c r="H227">
         <v>113.3333333333333</v>
@@ -6719,7 +6905,7 @@
         <v>18</v>
       </c>
       <c r="B228" t="s">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="C228">
         <v>30</v>
@@ -6734,7 +6920,7 @@
         <v>6</v>
       </c>
       <c r="G228" t="s">
-        <v>171</v>
+        <v>207</v>
       </c>
       <c r="H228">
         <v>36</v>
@@ -6745,7 +6931,7 @@
         <v>18</v>
       </c>
       <c r="B229" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="C229">
         <v>30</v>
@@ -6760,7 +6946,7 @@
         <v>6</v>
       </c>
       <c r="G229" t="s">
-        <v>103</v>
+        <v>139</v>
       </c>
       <c r="H229">
         <v>38</v>
@@ -6771,7 +6957,7 @@
         <v>18</v>
       </c>
       <c r="B230" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="C230">
         <v>40</v>
@@ -6786,7 +6972,7 @@
         <v>8</v>
       </c>
       <c r="G230" t="s">
-        <v>168</v>
+        <v>204</v>
       </c>
       <c r="H230">
         <v>50.66666666666666</v>
@@ -6797,7 +6983,7 @@
         <v>18</v>
       </c>
       <c r="B231" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="C231">
         <v>40</v>
@@ -6812,7 +6998,7 @@
         <v>9</v>
       </c>
       <c r="G231" t="s">
-        <v>169</v>
+        <v>205</v>
       </c>
       <c r="H231">
         <v>50.66666666666666</v>
@@ -6823,7 +7009,7 @@
         <v>18</v>
       </c>
       <c r="B232" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="C232">
         <v>40</v>
@@ -6838,7 +7024,7 @@
         <v>10</v>
       </c>
       <c r="G232" t="s">
-        <v>96</v>
+        <v>132</v>
       </c>
       <c r="H232">
         <v>49.33333333333334</v>
@@ -6849,7 +7035,7 @@
         <v>18</v>
       </c>
       <c r="B233" t="s">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="C233">
         <v>40</v>
@@ -6864,7 +7050,7 @@
         <v>6.5</v>
       </c>
       <c r="G233" t="s">
-        <v>172</v>
+        <v>208</v>
       </c>
       <c r="H233">
         <v>56</v>
@@ -6875,7 +7061,7 @@
         <v>18</v>
       </c>
       <c r="B234" t="s">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="C234">
         <v>40</v>
@@ -6890,7 +7076,7 @@
         <v>6.5</v>
       </c>
       <c r="G234" t="s">
-        <v>173</v>
+        <v>209</v>
       </c>
       <c r="H234">
         <v>56</v>
@@ -6901,7 +7087,7 @@
         <v>18</v>
       </c>
       <c r="B235" t="s">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="C235">
         <v>40</v>
@@ -6916,7 +7102,7 @@
         <v>7.5</v>
       </c>
       <c r="G235" t="s">
-        <v>174</v>
+        <v>210</v>
       </c>
       <c r="H235">
         <v>56</v>
@@ -6927,7 +7113,7 @@
         <v>18</v>
       </c>
       <c r="B236" t="s">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="C236">
         <v>40</v>
@@ -6942,7 +7128,7 @@
         <v>9</v>
       </c>
       <c r="G236" t="s">
-        <v>175</v>
+        <v>211</v>
       </c>
       <c r="H236">
         <v>56</v>
@@ -6953,7 +7139,7 @@
         <v>18</v>
       </c>
       <c r="B237" t="s">
-        <v>66</v>
+        <v>95</v>
       </c>
       <c r="C237">
         <v>60</v>
@@ -6968,7 +7154,7 @@
         <v>8</v>
       </c>
       <c r="G237" t="s">
-        <v>120</v>
+        <v>156</v>
       </c>
       <c r="H237">
         <v>80</v>
@@ -6979,7 +7165,7 @@
         <v>18</v>
       </c>
       <c r="B238" t="s">
-        <v>65</v>
+        <v>94</v>
       </c>
       <c r="C238">
         <v>60</v>
@@ -6994,7 +7180,7 @@
         <v>7</v>
       </c>
       <c r="G238" t="s">
-        <v>122</v>
+        <v>158</v>
       </c>
       <c r="H238">
         <v>80</v>
@@ -7005,7 +7191,7 @@
         <v>18</v>
       </c>
       <c r="B239" t="s">
-        <v>66</v>
+        <v>95</v>
       </c>
       <c r="C239">
         <v>60</v>
@@ -7020,7 +7206,7 @@
         <v>8.5</v>
       </c>
       <c r="G239" t="s">
-        <v>121</v>
+        <v>157</v>
       </c>
       <c r="H239">
         <v>80</v>
@@ -7031,7 +7217,7 @@
         <v>18</v>
       </c>
       <c r="B240" t="s">
-        <v>65</v>
+        <v>94</v>
       </c>
       <c r="C240">
         <v>60</v>
@@ -7046,7 +7232,7 @@
         <v>8</v>
       </c>
       <c r="G240" t="s">
-        <v>123</v>
+        <v>159</v>
       </c>
       <c r="H240">
         <v>80</v>
@@ -7057,7 +7243,7 @@
         <v>18</v>
       </c>
       <c r="B241" t="s">
-        <v>66</v>
+        <v>95</v>
       </c>
       <c r="C241">
         <v>60</v>
@@ -7072,7 +7258,7 @@
         <v>9</v>
       </c>
       <c r="G241" t="s">
-        <v>148</v>
+        <v>184</v>
       </c>
       <c r="H241">
         <v>80</v>
@@ -7083,7 +7269,7 @@
         <v>18</v>
       </c>
       <c r="B242" t="s">
-        <v>65</v>
+        <v>94</v>
       </c>
       <c r="C242">
         <v>60</v>
@@ -7098,7 +7284,7 @@
         <v>9</v>
       </c>
       <c r="G242" t="s">
-        <v>149</v>
+        <v>185</v>
       </c>
       <c r="H242">
         <v>80</v>
@@ -7109,7 +7295,7 @@
         <v>19</v>
       </c>
       <c r="B243" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="C243">
         <v>60</v>
@@ -7124,7 +7310,7 @@
         <v>4</v>
       </c>
       <c r="G243" t="s">
-        <v>103</v>
+        <v>139</v>
       </c>
       <c r="H243">
         <v>76</v>
@@ -7135,7 +7321,7 @@
         <v>19</v>
       </c>
       <c r="B244" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="C244">
         <v>100</v>
@@ -7150,7 +7336,7 @@
         <v>6</v>
       </c>
       <c r="G244" t="s">
-        <v>103</v>
+        <v>139</v>
       </c>
       <c r="H244">
         <v>116.6666666666667</v>
@@ -7161,7 +7347,7 @@
         <v>19</v>
       </c>
       <c r="B245" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="C245">
         <v>130</v>
@@ -7176,7 +7362,7 @@
         <v>7</v>
       </c>
       <c r="G245" t="s">
-        <v>176</v>
+        <v>212</v>
       </c>
       <c r="H245">
         <v>134.3333333333333</v>
@@ -7187,7 +7373,7 @@
         <v>19</v>
       </c>
       <c r="B246" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="C246">
         <v>150</v>
@@ -7202,7 +7388,7 @@
         <v>8.5</v>
       </c>
       <c r="G246" t="s">
-        <v>177</v>
+        <v>213</v>
       </c>
       <c r="H246">
         <v>155</v>
@@ -7213,7 +7399,7 @@
         <v>19</v>
       </c>
       <c r="B247" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="C247">
         <v>120</v>
@@ -7228,7 +7414,7 @@
         <v>7.5</v>
       </c>
       <c r="G247" t="s">
-        <v>178</v>
+        <v>214</v>
       </c>
       <c r="H247">
         <v>140</v>
@@ -7239,7 +7425,7 @@
         <v>19</v>
       </c>
       <c r="B248" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="C248">
         <v>120</v>
@@ -7254,7 +7440,7 @@
         <v>7.5</v>
       </c>
       <c r="G248" t="s">
-        <v>179</v>
+        <v>215</v>
       </c>
       <c r="H248">
         <v>140</v>
@@ -7265,7 +7451,7 @@
         <v>19</v>
       </c>
       <c r="B249" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="C249">
         <v>120</v>
@@ -7280,7 +7466,7 @@
         <v>8</v>
       </c>
       <c r="G249" t="s">
-        <v>180</v>
+        <v>216</v>
       </c>
       <c r="H249">
         <v>140</v>
@@ -7291,7 +7477,7 @@
         <v>19</v>
       </c>
       <c r="B250" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="C250">
         <v>120</v>
@@ -7306,7 +7492,7 @@
         <v>8.5</v>
       </c>
       <c r="G250" t="s">
-        <v>181</v>
+        <v>217</v>
       </c>
       <c r="H250">
         <v>140</v>
@@ -7317,7 +7503,7 @@
         <v>19</v>
       </c>
       <c r="B251" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="C251">
         <v>120</v>
@@ -7332,7 +7518,7 @@
         <v>9</v>
       </c>
       <c r="G251" t="s">
-        <v>182</v>
+        <v>218</v>
       </c>
       <c r="H251">
         <v>140</v>
@@ -7343,7 +7529,7 @@
         <v>19</v>
       </c>
       <c r="B252" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="C252">
         <v>40</v>
@@ -7358,7 +7544,7 @@
         <v>5</v>
       </c>
       <c r="G252" t="s">
-        <v>183</v>
+        <v>219</v>
       </c>
       <c r="H252">
         <v>50.66666666666666</v>
@@ -7369,7 +7555,7 @@
         <v>19</v>
       </c>
       <c r="B253" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="C253">
         <v>50</v>
@@ -7384,7 +7570,7 @@
         <v>6</v>
       </c>
       <c r="G253" t="s">
-        <v>184</v>
+        <v>220</v>
       </c>
       <c r="H253">
         <v>58.33333333333334</v>
@@ -7395,7 +7581,7 @@
         <v>19</v>
       </c>
       <c r="B254" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="C254">
         <v>60</v>
@@ -7410,7 +7596,7 @@
         <v>7</v>
       </c>
       <c r="G254" t="s">
-        <v>185</v>
+        <v>221</v>
       </c>
       <c r="H254">
         <v>70</v>
@@ -7421,7 +7607,7 @@
         <v>19</v>
       </c>
       <c r="B255" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="C255">
         <v>60</v>
@@ -7436,7 +7622,7 @@
         <v>8</v>
       </c>
       <c r="G255" t="s">
-        <v>186</v>
+        <v>222</v>
       </c>
       <c r="H255">
         <v>70</v>
@@ -7447,7 +7633,7 @@
         <v>19</v>
       </c>
       <c r="B256" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="C256">
         <v>60</v>
@@ -7462,7 +7648,7 @@
         <v>8.5</v>
       </c>
       <c r="G256" t="s">
-        <v>187</v>
+        <v>223</v>
       </c>
       <c r="H256">
         <v>70</v>
@@ -7473,7 +7659,7 @@
         <v>19</v>
       </c>
       <c r="B257" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="C257">
         <v>60</v>
@@ -7488,7 +7674,7 @@
         <v>8.5</v>
       </c>
       <c r="G257" t="s">
-        <v>188</v>
+        <v>224</v>
       </c>
       <c r="H257">
         <v>70</v>
@@ -7499,7 +7685,7 @@
         <v>19</v>
       </c>
       <c r="B258" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="C258">
         <v>60</v>
@@ -7514,7 +7700,7 @@
         <v>8</v>
       </c>
       <c r="G258" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="H258">
         <v>70</v>
@@ -7525,7 +7711,7 @@
         <v>19</v>
       </c>
       <c r="B259" t="s">
-        <v>70</v>
+        <v>99</v>
       </c>
       <c r="C259">
         <v>40</v>
@@ -7540,7 +7726,7 @@
         <v>5</v>
       </c>
       <c r="G259" t="s">
-        <v>190</v>
+        <v>226</v>
       </c>
       <c r="H259">
         <v>53.33333333333333</v>
@@ -7551,7 +7737,7 @@
         <v>19</v>
       </c>
       <c r="B260" t="s">
-        <v>70</v>
+        <v>99</v>
       </c>
       <c r="C260">
         <v>50</v>
@@ -7566,7 +7752,7 @@
         <v>7</v>
       </c>
       <c r="G260" t="s">
-        <v>191</v>
+        <v>227</v>
       </c>
       <c r="H260">
         <v>63.33333333333333</v>
@@ -7577,7 +7763,7 @@
         <v>19</v>
       </c>
       <c r="B261" t="s">
-        <v>70</v>
+        <v>99</v>
       </c>
       <c r="C261">
         <v>50</v>
@@ -7592,7 +7778,7 @@
         <v>7</v>
       </c>
       <c r="G261" t="s">
-        <v>192</v>
+        <v>228</v>
       </c>
       <c r="H261">
         <v>63.33333333333333</v>
@@ -7603,7 +7789,7 @@
         <v>19</v>
       </c>
       <c r="B262" t="s">
-        <v>70</v>
+        <v>99</v>
       </c>
       <c r="C262">
         <v>50</v>
@@ -7618,7 +7804,7 @@
         <v>7.5</v>
       </c>
       <c r="G262" t="s">
-        <v>193</v>
+        <v>229</v>
       </c>
       <c r="H262">
         <v>63.33333333333333</v>
@@ -7629,7 +7815,7 @@
         <v>19</v>
       </c>
       <c r="B263" t="s">
-        <v>70</v>
+        <v>99</v>
       </c>
       <c r="C263">
         <v>50</v>
@@ -7644,7 +7830,7 @@
         <v>8</v>
       </c>
       <c r="G263" t="s">
-        <v>194</v>
+        <v>230</v>
       </c>
       <c r="H263">
         <v>66.66666666666666</v>
@@ -7655,7 +7841,7 @@
         <v>19</v>
       </c>
       <c r="B264" t="s">
-        <v>71</v>
+        <v>100</v>
       </c>
       <c r="C264">
         <v>20</v>
@@ -7670,7 +7856,7 @@
         <v>7</v>
       </c>
       <c r="G264" t="s">
-        <v>120</v>
+        <v>156</v>
       </c>
       <c r="H264">
         <v>26.66666666666666</v>
@@ -7681,7 +7867,7 @@
         <v>19</v>
       </c>
       <c r="B265" t="s">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="C265">
         <v>20</v>
@@ -7696,7 +7882,7 @@
         <v>7</v>
       </c>
       <c r="G265" t="s">
-        <v>121</v>
+        <v>157</v>
       </c>
       <c r="H265">
         <v>28</v>
@@ -7707,7 +7893,7 @@
         <v>19</v>
       </c>
       <c r="B266" t="s">
-        <v>71</v>
+        <v>100</v>
       </c>
       <c r="C266">
         <v>25</v>
@@ -7722,7 +7908,7 @@
         <v>8.5</v>
       </c>
       <c r="G266" t="s">
-        <v>195</v>
+        <v>231</v>
       </c>
       <c r="H266">
         <v>31.66666666666666</v>
@@ -7733,7 +7919,7 @@
         <v>19</v>
       </c>
       <c r="B267" t="s">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="C267">
         <v>25</v>
@@ -7748,7 +7934,7 @@
         <v>7.5</v>
       </c>
       <c r="G267" t="s">
-        <v>123</v>
+        <v>159</v>
       </c>
       <c r="H267">
         <v>33.33333333333333</v>
@@ -7759,7 +7945,7 @@
         <v>19</v>
       </c>
       <c r="B268" t="s">
-        <v>71</v>
+        <v>100</v>
       </c>
       <c r="C268">
         <v>25</v>
@@ -7774,7 +7960,7 @@
         <v>8.5</v>
       </c>
       <c r="G268" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="H268">
         <v>31.66666666666666</v>
@@ -7785,7 +7971,7 @@
         <v>19</v>
       </c>
       <c r="B269" t="s">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="C269">
         <v>25</v>
@@ -7800,7 +7986,7 @@
         <v>8</v>
       </c>
       <c r="G269" t="s">
-        <v>125</v>
+        <v>161</v>
       </c>
       <c r="H269">
         <v>35</v>
@@ -7811,7 +7997,7 @@
         <v>19</v>
       </c>
       <c r="B270" t="s">
-        <v>71</v>
+        <v>100</v>
       </c>
       <c r="C270">
         <v>25</v>
@@ -7826,7 +8012,7 @@
         <v>9</v>
       </c>
       <c r="G270" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="H270">
         <v>31.66666666666666</v>
@@ -7837,7 +8023,7 @@
         <v>19</v>
       </c>
       <c r="B271" t="s">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="C271">
         <v>25</v>
@@ -7852,7 +8038,7 @@
         <v>9</v>
       </c>
       <c r="G271" t="s">
-        <v>197</v>
+        <v>233</v>
       </c>
       <c r="H271">
         <v>37.5</v>
@@ -7863,7 +8049,7 @@
         <v>20</v>
       </c>
       <c r="B272" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="C272">
         <v>20</v>
@@ -7886,7 +8072,7 @@
         <v>20</v>
       </c>
       <c r="B273" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="C273">
         <v>60</v>
@@ -7909,7 +8095,7 @@
         <v>20</v>
       </c>
       <c r="B274" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="C274">
         <v>100</v>
@@ -7932,7 +8118,7 @@
         <v>20</v>
       </c>
       <c r="B275" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="C275">
         <v>100</v>
@@ -7955,7 +8141,7 @@
         <v>20</v>
       </c>
       <c r="B276" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="C276">
         <v>60</v>
@@ -7978,7 +8164,7 @@
         <v>20</v>
       </c>
       <c r="B277" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="C277">
         <v>90</v>
@@ -8001,7 +8187,7 @@
         <v>20</v>
       </c>
       <c r="B278" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="C278">
         <v>110</v>
@@ -8024,7 +8210,7 @@
         <v>20</v>
       </c>
       <c r="B279" t="s">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="C279">
         <v>30</v>
@@ -8047,7 +8233,7 @@
         <v>20</v>
       </c>
       <c r="B280" t="s">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="C280">
         <v>40</v>
@@ -8070,7 +8256,7 @@
         <v>20</v>
       </c>
       <c r="B281" t="s">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="C281">
         <v>40</v>
@@ -8093,7 +8279,7 @@
         <v>20</v>
       </c>
       <c r="B282" t="s">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="C282">
         <v>30</v>
@@ -8116,7 +8302,7 @@
         <v>20</v>
       </c>
       <c r="B283" t="s">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="C283">
         <v>30</v>
@@ -8139,7 +8325,7 @@
         <v>20</v>
       </c>
       <c r="B284" t="s">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="C284">
         <v>40</v>
@@ -8162,7 +8348,7 @@
         <v>20</v>
       </c>
       <c r="B285" t="s">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="C285">
         <v>40</v>
@@ -8185,7 +8371,7 @@
         <v>20</v>
       </c>
       <c r="B286" t="s">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="C286">
         <v>40</v>
@@ -8208,7 +8394,7 @@
         <v>20</v>
       </c>
       <c r="B287" t="s">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="C287">
         <v>40</v>
@@ -8231,7 +8417,7 @@
         <v>20</v>
       </c>
       <c r="B288" t="s">
-        <v>52</v>
+        <v>81</v>
       </c>
       <c r="C288">
         <v>60</v>
@@ -8254,7 +8440,7 @@
         <v>20</v>
       </c>
       <c r="B289" t="s">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="C289">
         <v>60</v>
@@ -8277,7 +8463,7 @@
         <v>20</v>
       </c>
       <c r="B290" t="s">
-        <v>52</v>
+        <v>81</v>
       </c>
       <c r="C290">
         <v>60</v>
@@ -8300,7 +8486,7 @@
         <v>20</v>
       </c>
       <c r="B291" t="s">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="C291">
         <v>60</v>
@@ -8323,7 +8509,7 @@
         <v>20</v>
       </c>
       <c r="B292" t="s">
-        <v>52</v>
+        <v>81</v>
       </c>
       <c r="C292">
         <v>60</v>
@@ -8346,7 +8532,7 @@
         <v>20</v>
       </c>
       <c r="B293" t="s">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="C293">
         <v>60</v>
@@ -8369,7 +8555,7 @@
         <v>21</v>
       </c>
       <c r="B294" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="C294">
         <v>20</v>
@@ -8384,7 +8570,7 @@
         <v>3</v>
       </c>
       <c r="G294" t="s">
-        <v>103</v>
+        <v>139</v>
       </c>
       <c r="H294">
         <v>28</v>
@@ -8395,7 +8581,7 @@
         <v>21</v>
       </c>
       <c r="B295" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="C295">
         <v>60</v>
@@ -8410,7 +8596,7 @@
         <v>6</v>
       </c>
       <c r="G295" t="s">
-        <v>105</v>
+        <v>141</v>
       </c>
       <c r="H295">
         <v>76</v>
@@ -8421,7 +8607,7 @@
         <v>21</v>
       </c>
       <c r="B296" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="C296">
         <v>110</v>
@@ -8436,7 +8622,7 @@
         <v>7.5</v>
       </c>
       <c r="G296" t="s">
-        <v>127</v>
+        <v>163</v>
       </c>
       <c r="H296">
         <v>121</v>
@@ -8447,7 +8633,7 @@
         <v>21</v>
       </c>
       <c r="B297" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="C297">
         <v>70</v>
@@ -8462,7 +8648,7 @@
         <v>8</v>
       </c>
       <c r="G297" t="s">
-        <v>198</v>
+        <v>234</v>
       </c>
       <c r="H297">
         <v>116.6666666666667</v>
@@ -8473,7 +8659,7 @@
         <v>21</v>
       </c>
       <c r="B298" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="C298">
         <v>80</v>
@@ -8488,7 +8674,7 @@
         <v>8.5</v>
       </c>
       <c r="G298" t="s">
-        <v>199</v>
+        <v>235</v>
       </c>
       <c r="H298">
         <v>112</v>
@@ -8499,7 +8685,7 @@
         <v>21</v>
       </c>
       <c r="B299" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="C299">
         <v>60</v>
@@ -8514,7 +8700,7 @@
         <v>5</v>
       </c>
       <c r="G299" t="s">
-        <v>200</v>
+        <v>236</v>
       </c>
       <c r="H299">
         <v>80</v>
@@ -8525,7 +8711,7 @@
         <v>21</v>
       </c>
       <c r="B300" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="C300">
         <v>110</v>
@@ -8540,7 +8726,7 @@
         <v>6.5</v>
       </c>
       <c r="G300" t="s">
-        <v>105</v>
+        <v>141</v>
       </c>
       <c r="H300">
         <v>128.3333333333333</v>
@@ -8551,7 +8737,7 @@
         <v>21</v>
       </c>
       <c r="B301" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="C301">
         <v>140</v>
@@ -8566,7 +8752,7 @@
         <v>7</v>
       </c>
       <c r="G301" t="s">
-        <v>106</v>
+        <v>142</v>
       </c>
       <c r="H301">
         <v>144.6666666666667</v>
@@ -8577,7 +8763,7 @@
         <v>21</v>
       </c>
       <c r="B302" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="C302">
         <v>160</v>
@@ -8592,7 +8778,7 @@
         <v>8.5</v>
       </c>
       <c r="G302" t="s">
-        <v>201</v>
+        <v>237</v>
       </c>
       <c r="H302">
         <v>165.3333333333333</v>
@@ -8603,7 +8789,7 @@
         <v>21</v>
       </c>
       <c r="B303" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="C303">
         <v>170</v>
@@ -8618,7 +8804,7 @@
         <v>9</v>
       </c>
       <c r="G303" t="s">
-        <v>202</v>
+        <v>238</v>
       </c>
       <c r="H303">
         <v>175.6666666666667</v>
@@ -8629,7 +8815,7 @@
         <v>21</v>
       </c>
       <c r="B304" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="C304">
         <v>30</v>
@@ -8644,7 +8830,7 @@
         <v>7</v>
       </c>
       <c r="G304" t="s">
-        <v>203</v>
+        <v>239</v>
       </c>
       <c r="H304">
         <v>40</v>
@@ -8655,7 +8841,7 @@
         <v>21</v>
       </c>
       <c r="B305" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="C305">
         <v>40</v>
@@ -8670,7 +8856,7 @@
         <v>7</v>
       </c>
       <c r="G305" t="s">
-        <v>204</v>
+        <v>240</v>
       </c>
       <c r="H305">
         <v>44</v>
@@ -8681,7 +8867,7 @@
         <v>21</v>
       </c>
       <c r="B306" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="C306">
         <v>50</v>
@@ -8696,7 +8882,7 @@
         <v>9.5</v>
       </c>
       <c r="G306" t="s">
-        <v>205</v>
+        <v>241</v>
       </c>
       <c r="H306">
         <v>53.33333333333334</v>
@@ -8707,7 +8893,7 @@
         <v>21</v>
       </c>
       <c r="B307" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="C307">
         <v>40</v>
@@ -8722,7 +8908,7 @@
         <v>8.5</v>
       </c>
       <c r="G307" t="s">
-        <v>134</v>
+        <v>170</v>
       </c>
       <c r="H307">
         <v>53.33333333333333</v>
@@ -8733,7 +8919,7 @@
         <v>22</v>
       </c>
       <c r="B308" t="s">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="C308">
         <v>70</v>
@@ -8756,7 +8942,7 @@
         <v>22</v>
       </c>
       <c r="B309" t="s">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="C309">
         <v>120</v>
@@ -8779,7 +8965,7 @@
         <v>22</v>
       </c>
       <c r="B310" t="s">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="C310">
         <v>140</v>
@@ -8802,7 +8988,7 @@
         <v>22</v>
       </c>
       <c r="B311" t="s">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="C311">
         <v>140</v>
@@ -8825,7 +9011,7 @@
         <v>22</v>
       </c>
       <c r="B312" t="s">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="C312">
         <v>120</v>
@@ -8848,7 +9034,7 @@
         <v>22</v>
       </c>
       <c r="B313" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="C313">
         <v>20</v>
@@ -8871,7 +9057,7 @@
         <v>22</v>
       </c>
       <c r="B314" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="C314">
         <v>40</v>
@@ -8894,7 +9080,7 @@
         <v>22</v>
       </c>
       <c r="B315" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="C315">
         <v>60</v>
@@ -8917,7 +9103,7 @@
         <v>22</v>
       </c>
       <c r="B316" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="C316">
         <v>70</v>
@@ -8940,7 +9126,7 @@
         <v>22</v>
       </c>
       <c r="B317" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="C317">
         <v>80</v>
@@ -8963,7 +9149,7 @@
         <v>22</v>
       </c>
       <c r="B318" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="C318">
         <v>75</v>
@@ -8986,7 +9172,7 @@
         <v>22</v>
       </c>
       <c r="B319" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="C319">
         <v>60</v>
@@ -9009,7 +9195,7 @@
         <v>22</v>
       </c>
       <c r="B320" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="C320">
         <v>60</v>
@@ -9032,7 +9218,7 @@
         <v>22</v>
       </c>
       <c r="B321" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="C321">
         <v>60</v>
@@ -9055,7 +9241,7 @@
         <v>22</v>
       </c>
       <c r="B322" t="s">
-        <v>69</v>
+        <v>98</v>
       </c>
       <c r="C322">
         <v>65</v>
@@ -9078,7 +9264,7 @@
         <v>22</v>
       </c>
       <c r="B323" t="s">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="C323">
         <v>65</v>
@@ -9101,7 +9287,7 @@
         <v>22</v>
       </c>
       <c r="B324" t="s">
-        <v>69</v>
+        <v>98</v>
       </c>
       <c r="C324">
         <v>65</v>
@@ -9124,7 +9310,7 @@
         <v>22</v>
       </c>
       <c r="B325" t="s">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="C325">
         <v>65</v>
@@ -9147,7 +9333,7 @@
         <v>22</v>
       </c>
       <c r="B326" t="s">
-        <v>69</v>
+        <v>98</v>
       </c>
       <c r="C326">
         <v>65</v>
@@ -9170,7 +9356,7 @@
         <v>22</v>
       </c>
       <c r="B327" t="s">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="C327">
         <v>65</v>
@@ -9193,7 +9379,7 @@
         <v>22</v>
       </c>
       <c r="B328" t="s">
-        <v>69</v>
+        <v>98</v>
       </c>
       <c r="C328">
         <v>65</v>
@@ -9216,7 +9402,7 @@
         <v>22</v>
       </c>
       <c r="B329" t="s">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="C329">
         <v>65</v>
@@ -9239,7 +9425,7 @@
         <v>23</v>
       </c>
       <c r="B330" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="C330">
         <v>20</v>
@@ -9254,7 +9440,7 @@
         <v>3</v>
       </c>
       <c r="G330" t="s">
-        <v>103</v>
+        <v>139</v>
       </c>
       <c r="H330">
         <v>25.33333333333333</v>
@@ -9265,7 +9451,7 @@
         <v>23</v>
       </c>
       <c r="B331" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="C331">
         <v>70</v>
@@ -9280,7 +9466,7 @@
         <v>6</v>
       </c>
       <c r="G331" t="s">
-        <v>206</v>
+        <v>242</v>
       </c>
       <c r="H331">
         <v>81.66666666666667</v>
@@ -9291,7 +9477,7 @@
         <v>23</v>
       </c>
       <c r="B332" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="C332">
         <v>90</v>
@@ -9306,7 +9492,7 @@
         <v>6</v>
       </c>
       <c r="G332" t="s">
-        <v>145</v>
+        <v>181</v>
       </c>
       <c r="H332">
         <v>93.00000000000001</v>
@@ -9317,7 +9503,7 @@
         <v>23</v>
       </c>
       <c r="B333" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="C333">
         <v>120</v>
@@ -9332,7 +9518,7 @@
         <v>7.5</v>
       </c>
       <c r="G333" t="s">
-        <v>145</v>
+        <v>181</v>
       </c>
       <c r="H333">
         <v>124</v>
@@ -9343,7 +9529,7 @@
         <v>23</v>
       </c>
       <c r="B334" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="C334">
         <v>140</v>
@@ -9358,7 +9544,7 @@
         <v>10</v>
       </c>
       <c r="G334" t="s">
-        <v>207</v>
+        <v>243</v>
       </c>
       <c r="H334">
         <v>140</v>
@@ -9369,7 +9555,7 @@
         <v>23</v>
       </c>
       <c r="B335" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="C335">
         <v>80</v>
@@ -9384,7 +9570,7 @@
         <v>8.5</v>
       </c>
       <c r="G335" t="s">
-        <v>208</v>
+        <v>244</v>
       </c>
       <c r="H335">
         <v>133.3333333333333</v>
@@ -9395,7 +9581,7 @@
         <v>23</v>
       </c>
       <c r="B336" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="C336">
         <v>80</v>
@@ -9410,7 +9596,7 @@
         <v>10</v>
       </c>
       <c r="G336" t="s">
-        <v>209</v>
+        <v>245</v>
       </c>
       <c r="H336">
         <v>101.3333333333333</v>
@@ -9421,7 +9607,7 @@
         <v>23</v>
       </c>
       <c r="B337" t="s">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="C337">
         <v>20</v>
@@ -9436,7 +9622,7 @@
         <v>4</v>
       </c>
       <c r="G337" t="s">
-        <v>103</v>
+        <v>139</v>
       </c>
       <c r="H337">
         <v>25.33333333333333</v>
@@ -9447,7 +9633,7 @@
         <v>23</v>
       </c>
       <c r="B338" t="s">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="C338">
         <v>40</v>
@@ -9462,7 +9648,7 @@
         <v>6</v>
       </c>
       <c r="G338" t="s">
-        <v>203</v>
+        <v>239</v>
       </c>
       <c r="H338">
         <v>50.66666666666666</v>
@@ -9473,7 +9659,7 @@
         <v>23</v>
       </c>
       <c r="B339" t="s">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="C339">
         <v>60</v>
@@ -9488,7 +9674,7 @@
         <v>7</v>
       </c>
       <c r="G339" t="s">
-        <v>210</v>
+        <v>246</v>
       </c>
       <c r="H339">
         <v>66</v>
@@ -9499,7 +9685,7 @@
         <v>23</v>
       </c>
       <c r="B340" t="s">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="C340">
         <v>70</v>
@@ -9514,7 +9700,7 @@
         <v>8.5</v>
       </c>
       <c r="G340" t="s">
-        <v>127</v>
+        <v>163</v>
       </c>
       <c r="H340">
         <v>77</v>
@@ -9525,7 +9711,7 @@
         <v>23</v>
       </c>
       <c r="B341" t="s">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="C341">
         <v>75</v>
@@ -9540,7 +9726,7 @@
         <v>8.75</v>
       </c>
       <c r="G341" t="s">
-        <v>211</v>
+        <v>247</v>
       </c>
       <c r="H341">
         <v>77.50000000000001</v>
@@ -9551,7 +9737,7 @@
         <v>23</v>
       </c>
       <c r="B342" t="s">
-        <v>77</v>
+        <v>106</v>
       </c>
       <c r="C342">
         <v>50</v>
@@ -9566,7 +9752,7 @@
         <v>8</v>
       </c>
       <c r="G342" t="s">
-        <v>212</v>
+        <v>248</v>
       </c>
       <c r="H342">
         <v>66.66666666666666</v>
@@ -9577,7 +9763,7 @@
         <v>23</v>
       </c>
       <c r="B343" t="s">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="C343">
         <v>40</v>
@@ -9592,7 +9778,7 @@
         <v>6</v>
       </c>
       <c r="G343" t="s">
-        <v>213</v>
+        <v>249</v>
       </c>
       <c r="H343">
         <v>50.66666666666666</v>
@@ -9603,7 +9789,7 @@
         <v>23</v>
       </c>
       <c r="B344" t="s">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="C344">
         <v>50</v>
@@ -9618,7 +9804,7 @@
         <v>6.5</v>
       </c>
       <c r="G344" t="s">
-        <v>214</v>
+        <v>250</v>
       </c>
       <c r="H344">
         <v>63.33333333333333</v>
@@ -9629,7 +9815,7 @@
         <v>23</v>
       </c>
       <c r="B345" t="s">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="C345">
         <v>63</v>
@@ -9644,7 +9830,7 @@
         <v>8</v>
       </c>
       <c r="G345" t="s">
-        <v>215</v>
+        <v>251</v>
       </c>
       <c r="H345">
         <v>75.59999999999999</v>
@@ -9655,7 +9841,7 @@
         <v>23</v>
       </c>
       <c r="B346" t="s">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="C346">
         <v>63</v>
@@ -9670,7 +9856,7 @@
         <v>8.5</v>
       </c>
       <c r="G346" t="s">
-        <v>216</v>
+        <v>252</v>
       </c>
       <c r="H346">
         <v>75.59999999999999</v>
@@ -9681,7 +9867,7 @@
         <v>23</v>
       </c>
       <c r="B347" t="s">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="C347">
         <v>11</v>
@@ -9696,7 +9882,7 @@
         <v>5</v>
       </c>
       <c r="G347" t="s">
-        <v>120</v>
+        <v>156</v>
       </c>
       <c r="H347">
         <v>16.5</v>
@@ -9707,7 +9893,7 @@
         <v>23</v>
       </c>
       <c r="B348" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="C348">
         <v>32</v>
@@ -9722,7 +9908,7 @@
         <v>5</v>
       </c>
       <c r="G348" t="s">
-        <v>122</v>
+        <v>158</v>
       </c>
       <c r="H348">
         <v>48</v>
@@ -9733,7 +9919,7 @@
         <v>23</v>
       </c>
       <c r="B349" t="s">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="C349">
         <v>33</v>
@@ -9748,7 +9934,7 @@
         <v>7</v>
       </c>
       <c r="G349" t="s">
-        <v>121</v>
+        <v>157</v>
       </c>
       <c r="H349">
         <v>49.5</v>
@@ -9759,7 +9945,7 @@
         <v>23</v>
       </c>
       <c r="B350" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="C350">
         <v>59</v>
@@ -9774,7 +9960,7 @@
         <v>8</v>
       </c>
       <c r="G350" t="s">
-        <v>123</v>
+        <v>159</v>
       </c>
       <c r="H350">
         <v>82.59999999999999</v>
@@ -9785,7 +9971,7 @@
         <v>23</v>
       </c>
       <c r="B351" t="s">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="C351">
         <v>39</v>
@@ -9800,7 +9986,7 @@
         <v>9</v>
       </c>
       <c r="G351" t="s">
-        <v>148</v>
+        <v>184</v>
       </c>
       <c r="H351">
         <v>58.5</v>
@@ -9811,7 +9997,7 @@
         <v>23</v>
       </c>
       <c r="B352" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="C352">
         <v>66</v>
@@ -9826,7 +10012,7 @@
         <v>9</v>
       </c>
       <c r="G352" t="s">
-        <v>149</v>
+        <v>185</v>
       </c>
       <c r="H352">
         <v>92.39999999999999</v>
@@ -9837,7 +10023,7 @@
         <v>24</v>
       </c>
       <c r="B353" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="C353">
         <v>70</v>
@@ -9852,7 +10038,7 @@
         <v>6</v>
       </c>
       <c r="G353" t="s">
-        <v>97</v>
+        <v>133</v>
       </c>
       <c r="H353">
         <v>81.66666666666667</v>
@@ -9863,7 +10049,7 @@
         <v>24</v>
       </c>
       <c r="B354" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="C354">
         <v>120</v>
@@ -9878,7 +10064,7 @@
         <v>6</v>
       </c>
       <c r="G354" t="s">
-        <v>217</v>
+        <v>253</v>
       </c>
       <c r="H354">
         <v>124</v>
@@ -9889,7 +10075,7 @@
         <v>24</v>
       </c>
       <c r="B355" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="C355">
         <v>140</v>
@@ -9904,7 +10090,7 @@
         <v>6.5</v>
       </c>
       <c r="G355" t="s">
-        <v>218</v>
+        <v>254</v>
       </c>
       <c r="H355">
         <v>144.6666666666667</v>
@@ -9915,7 +10101,7 @@
         <v>24</v>
       </c>
       <c r="B356" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="C356">
         <v>160</v>
@@ -9930,7 +10116,7 @@
         <v>8.5</v>
       </c>
       <c r="G356" t="s">
-        <v>106</v>
+        <v>142</v>
       </c>
       <c r="H356">
         <v>165.3333333333333</v>
@@ -9941,7 +10127,7 @@
         <v>24</v>
       </c>
       <c r="B357" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="C357">
         <v>140</v>
@@ -9956,7 +10142,7 @@
         <v>8.5</v>
       </c>
       <c r="G357" t="s">
-        <v>219</v>
+        <v>255</v>
       </c>
       <c r="H357">
         <v>163.3333333333333</v>
@@ -9967,7 +10153,7 @@
         <v>24</v>
       </c>
       <c r="B358" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="C358">
         <v>140</v>
@@ -9982,7 +10168,7 @@
         <v>9</v>
       </c>
       <c r="G358" t="s">
-        <v>220</v>
+        <v>256</v>
       </c>
       <c r="H358">
         <v>163.3333333333333</v>
@@ -9993,7 +10179,7 @@
         <v>24</v>
       </c>
       <c r="B359" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="C359">
         <v>120</v>
@@ -10008,7 +10194,7 @@
         <v>9</v>
       </c>
       <c r="G359" t="s">
-        <v>221</v>
+        <v>257</v>
       </c>
       <c r="H359">
         <v>144</v>
@@ -10019,7 +10205,7 @@
         <v>24</v>
       </c>
       <c r="B360" t="s">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="C360">
         <v>30</v>
@@ -10034,7 +10220,7 @@
         <v>6</v>
       </c>
       <c r="G360" t="s">
-        <v>222</v>
+        <v>258</v>
       </c>
       <c r="H360">
         <v>38</v>
@@ -10045,7 +10231,7 @@
         <v>24</v>
       </c>
       <c r="B361" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="C361">
         <v>40</v>
@@ -10060,7 +10246,7 @@
         <v>7</v>
       </c>
       <c r="G361" t="s">
-        <v>223</v>
+        <v>259</v>
       </c>
       <c r="H361">
         <v>48</v>
@@ -10071,7 +10257,7 @@
         <v>24</v>
       </c>
       <c r="B362" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="C362">
         <v>50</v>
@@ -10086,7 +10272,7 @@
         <v>8</v>
       </c>
       <c r="G362" t="s">
-        <v>224</v>
+        <v>260</v>
       </c>
       <c r="H362">
         <v>53.33333333333334</v>
@@ -10097,7 +10283,7 @@
         <v>24</v>
       </c>
       <c r="B363" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="C363">
         <v>55</v>
@@ -10112,7 +10298,7 @@
         <v>10</v>
       </c>
       <c r="G363" t="s">
-        <v>225</v>
+        <v>261</v>
       </c>
       <c r="H363">
         <v>56.83333333333334</v>
@@ -10123,7 +10309,7 @@
         <v>24</v>
       </c>
       <c r="B364" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="C364">
         <v>45</v>
@@ -10138,7 +10324,7 @@
         <v>9</v>
       </c>
       <c r="G364" t="s">
-        <v>226</v>
+        <v>262</v>
       </c>
       <c r="H364">
         <v>52.5</v>
@@ -10149,7 +10335,7 @@
         <v>24</v>
       </c>
       <c r="B365" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="C365">
         <v>45</v>
@@ -10164,7 +10350,7 @@
         <v>9.5</v>
       </c>
       <c r="G365" t="s">
-        <v>227</v>
+        <v>263</v>
       </c>
       <c r="H365">
         <v>52.5</v>
@@ -10175,7 +10361,7 @@
         <v>24</v>
       </c>
       <c r="B366" t="s">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="C366">
         <v>45</v>
@@ -10190,7 +10376,7 @@
         <v>7</v>
       </c>
       <c r="G366" t="s">
-        <v>228</v>
+        <v>264</v>
       </c>
       <c r="H366">
         <v>57</v>
@@ -10201,7 +10387,7 @@
         <v>24</v>
       </c>
       <c r="B367" t="s">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="C367">
         <v>50</v>
@@ -10216,7 +10402,7 @@
         <v>8</v>
       </c>
       <c r="G367" t="s">
-        <v>229</v>
+        <v>265</v>
       </c>
       <c r="H367">
         <v>63.33333333333333</v>
@@ -10227,7 +10413,7 @@
         <v>24</v>
       </c>
       <c r="B368" t="s">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="C368">
         <v>50</v>
@@ -10242,7 +10428,7 @@
         <v>8</v>
       </c>
       <c r="G368" t="s">
-        <v>230</v>
+        <v>266</v>
       </c>
       <c r="H368">
         <v>63.33333333333333</v>
@@ -10253,7 +10439,7 @@
         <v>24</v>
       </c>
       <c r="B369" t="s">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="C369">
         <v>50</v>
@@ -10268,7 +10454,7 @@
         <v>8</v>
       </c>
       <c r="G369" t="s">
-        <v>231</v>
+        <v>267</v>
       </c>
       <c r="H369">
         <v>63.33333333333333</v>
@@ -10279,7 +10465,7 @@
         <v>24</v>
       </c>
       <c r="B370" t="s">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="C370">
         <v>40</v>
@@ -10294,10 +10480,764 @@
         <v>8.5</v>
       </c>
       <c r="G370" t="s">
-        <v>232</v>
+        <v>268</v>
       </c>
       <c r="H370">
         <v>60</v>
+      </c>
+    </row>
+    <row r="371" spans="1:8">
+      <c r="A371" t="s">
+        <v>25</v>
+      </c>
+      <c r="B371" t="s">
+        <v>108</v>
+      </c>
+      <c r="C371">
+        <v>20</v>
+      </c>
+      <c r="D371">
+        <v>8</v>
+      </c>
+      <c r="E371">
+        <v>160</v>
+      </c>
+      <c r="F371">
+        <v>5</v>
+      </c>
+      <c r="G371" t="s">
+        <v>133</v>
+      </c>
+      <c r="H371">
+        <v>25.33333333333333</v>
+      </c>
+    </row>
+    <row r="372" spans="1:8">
+      <c r="A372" t="s">
+        <v>26</v>
+      </c>
+      <c r="B372" t="s">
+        <v>108</v>
+      </c>
+      <c r="C372">
+        <v>40</v>
+      </c>
+      <c r="D372">
+        <v>5</v>
+      </c>
+      <c r="E372">
+        <v>200</v>
+      </c>
+      <c r="F372">
+        <v>6</v>
+      </c>
+      <c r="G372" t="s">
+        <v>269</v>
+      </c>
+      <c r="H372">
+        <v>46.66666666666667</v>
+      </c>
+    </row>
+    <row r="373" spans="1:8">
+      <c r="A373" t="s">
+        <v>27</v>
+      </c>
+      <c r="B373" t="s">
+        <v>108</v>
+      </c>
+      <c r="C373">
+        <v>50</v>
+      </c>
+      <c r="D373">
+        <v>6</v>
+      </c>
+      <c r="E373">
+        <v>300</v>
+      </c>
+      <c r="F373">
+        <v>7</v>
+      </c>
+      <c r="G373" t="s">
+        <v>141</v>
+      </c>
+      <c r="H373">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="374" spans="1:8">
+      <c r="A374" t="s">
+        <v>28</v>
+      </c>
+      <c r="B374" t="s">
+        <v>109</v>
+      </c>
+      <c r="C374">
+        <v>50</v>
+      </c>
+      <c r="D374">
+        <v>8</v>
+      </c>
+      <c r="E374">
+        <v>400</v>
+      </c>
+      <c r="F374">
+        <v>6.5</v>
+      </c>
+      <c r="G374" t="s">
+        <v>270</v>
+      </c>
+      <c r="H374">
+        <v>63.33333333333333</v>
+      </c>
+    </row>
+    <row r="375" spans="1:8">
+      <c r="A375" t="s">
+        <v>29</v>
+      </c>
+      <c r="B375" t="s">
+        <v>110</v>
+      </c>
+      <c r="C375">
+        <v>60</v>
+      </c>
+      <c r="D375">
+        <v>3</v>
+      </c>
+      <c r="E375">
+        <v>180</v>
+      </c>
+      <c r="F375">
+        <v>7</v>
+      </c>
+      <c r="G375" t="s">
+        <v>271</v>
+      </c>
+      <c r="H375">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="376" spans="1:8">
+      <c r="A376" t="s">
+        <v>30</v>
+      </c>
+      <c r="B376" t="s">
+        <v>110</v>
+      </c>
+      <c r="C376">
+        <v>70</v>
+      </c>
+      <c r="D376">
+        <v>1</v>
+      </c>
+      <c r="E376">
+        <v>70</v>
+      </c>
+      <c r="F376">
+        <v>7.75</v>
+      </c>
+      <c r="G376" t="s">
+        <v>142</v>
+      </c>
+      <c r="H376">
+        <v>72.33333333333334</v>
+      </c>
+    </row>
+    <row r="377" spans="1:8">
+      <c r="A377" t="s">
+        <v>31</v>
+      </c>
+      <c r="B377" t="s">
+        <v>110</v>
+      </c>
+      <c r="C377">
+        <v>75</v>
+      </c>
+      <c r="D377">
+        <v>1</v>
+      </c>
+      <c r="E377">
+        <v>75</v>
+      </c>
+      <c r="F377">
+        <v>8</v>
+      </c>
+      <c r="G377" t="s">
+        <v>272</v>
+      </c>
+      <c r="H377">
+        <v>77.50000000000001</v>
+      </c>
+    </row>
+    <row r="378" spans="1:8">
+      <c r="A378" t="s">
+        <v>32</v>
+      </c>
+      <c r="B378" t="s">
+        <v>110</v>
+      </c>
+      <c r="C378">
+        <v>77.5</v>
+      </c>
+      <c r="D378">
+        <v>0</v>
+      </c>
+      <c r="E378">
+        <v>0</v>
+      </c>
+      <c r="F378">
+        <v>10</v>
+      </c>
+      <c r="G378" t="s">
+        <v>273</v>
+      </c>
+      <c r="H378">
+        <v>77.5</v>
+      </c>
+    </row>
+    <row r="379" spans="1:8">
+      <c r="A379" t="s">
+        <v>33</v>
+      </c>
+      <c r="B379" t="s">
+        <v>109</v>
+      </c>
+      <c r="C379">
+        <v>66.25</v>
+      </c>
+      <c r="D379">
+        <v>5</v>
+      </c>
+      <c r="E379">
+        <v>331.25</v>
+      </c>
+      <c r="F379">
+        <v>9</v>
+      </c>
+      <c r="G379" t="s">
+        <v>274</v>
+      </c>
+      <c r="H379">
+        <v>77.29166666666667</v>
+      </c>
+    </row>
+    <row r="380" spans="1:8">
+      <c r="A380" t="s">
+        <v>34</v>
+      </c>
+      <c r="B380" t="s">
+        <v>109</v>
+      </c>
+      <c r="C380">
+        <v>60</v>
+      </c>
+      <c r="D380">
+        <v>5</v>
+      </c>
+      <c r="E380">
+        <v>300</v>
+      </c>
+      <c r="F380">
+        <v>8.25</v>
+      </c>
+      <c r="G380" t="s">
+        <v>275</v>
+      </c>
+      <c r="H380">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="381" spans="1:8">
+      <c r="A381" t="s">
+        <v>35</v>
+      </c>
+      <c r="B381" t="s">
+        <v>111</v>
+      </c>
+      <c r="C381">
+        <v>30</v>
+      </c>
+      <c r="D381">
+        <v>12</v>
+      </c>
+      <c r="E381">
+        <v>360</v>
+      </c>
+      <c r="F381">
+        <v>6</v>
+      </c>
+      <c r="G381" t="s">
+        <v>276</v>
+      </c>
+      <c r="H381">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="382" spans="1:8">
+      <c r="A382" t="s">
+        <v>36</v>
+      </c>
+      <c r="B382" t="s">
+        <v>111</v>
+      </c>
+      <c r="C382">
+        <v>50</v>
+      </c>
+      <c r="D382">
+        <v>8</v>
+      </c>
+      <c r="E382">
+        <v>400</v>
+      </c>
+      <c r="F382">
+        <v>8.5</v>
+      </c>
+      <c r="G382" t="s">
+        <v>277</v>
+      </c>
+      <c r="H382">
+        <v>63.33333333333333</v>
+      </c>
+    </row>
+    <row r="383" spans="1:8">
+      <c r="A383" t="s">
+        <v>37</v>
+      </c>
+      <c r="B383" t="s">
+        <v>111</v>
+      </c>
+      <c r="C383">
+        <v>50</v>
+      </c>
+      <c r="D383">
+        <v>8</v>
+      </c>
+      <c r="E383">
+        <v>400</v>
+      </c>
+      <c r="F383">
+        <v>8</v>
+      </c>
+      <c r="G383" t="s">
+        <v>278</v>
+      </c>
+      <c r="H383">
+        <v>63.33333333333333</v>
+      </c>
+    </row>
+    <row r="384" spans="1:8">
+      <c r="A384" t="s">
+        <v>38</v>
+      </c>
+      <c r="B384" t="s">
+        <v>111</v>
+      </c>
+      <c r="C384">
+        <v>50</v>
+      </c>
+      <c r="D384">
+        <v>6</v>
+      </c>
+      <c r="E384">
+        <v>300</v>
+      </c>
+      <c r="F384">
+        <v>10</v>
+      </c>
+      <c r="G384" t="s">
+        <v>279</v>
+      </c>
+      <c r="H384">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="385" spans="1:8">
+      <c r="A385" t="s">
+        <v>39</v>
+      </c>
+      <c r="B385" t="s">
+        <v>112</v>
+      </c>
+      <c r="C385">
+        <v>0</v>
+      </c>
+      <c r="D385">
+        <v>10</v>
+      </c>
+      <c r="E385">
+        <v>0</v>
+      </c>
+      <c r="F385">
+        <v>6</v>
+      </c>
+      <c r="G385" t="s">
+        <v>280</v>
+      </c>
+      <c r="H385">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="386" spans="1:8">
+      <c r="A386" t="s">
+        <v>40</v>
+      </c>
+      <c r="B386" t="s">
+        <v>113</v>
+      </c>
+      <c r="C386">
+        <v>25</v>
+      </c>
+      <c r="D386">
+        <v>6</v>
+      </c>
+      <c r="E386">
+        <v>150</v>
+      </c>
+      <c r="F386">
+        <v>8</v>
+      </c>
+      <c r="G386" t="s">
+        <v>281</v>
+      </c>
+      <c r="H386">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="387" spans="1:8">
+      <c r="A387" t="s">
+        <v>41</v>
+      </c>
+      <c r="B387" t="s">
+        <v>113</v>
+      </c>
+      <c r="C387">
+        <v>25</v>
+      </c>
+      <c r="D387">
+        <v>8</v>
+      </c>
+      <c r="E387">
+        <v>200</v>
+      </c>
+      <c r="F387">
+        <v>8</v>
+      </c>
+      <c r="G387" t="s">
+        <v>282</v>
+      </c>
+      <c r="H387">
+        <v>31.66666666666666</v>
+      </c>
+    </row>
+    <row r="388" spans="1:8">
+      <c r="A388" t="s">
+        <v>42</v>
+      </c>
+      <c r="B388" t="s">
+        <v>113</v>
+      </c>
+      <c r="C388">
+        <v>25</v>
+      </c>
+      <c r="D388">
+        <v>8</v>
+      </c>
+      <c r="E388">
+        <v>200</v>
+      </c>
+      <c r="F388">
+        <v>8.5</v>
+      </c>
+      <c r="G388" t="s">
+        <v>283</v>
+      </c>
+      <c r="H388">
+        <v>31.66666666666666</v>
+      </c>
+    </row>
+    <row r="389" spans="1:8">
+      <c r="A389" t="s">
+        <v>43</v>
+      </c>
+      <c r="B389" t="s">
+        <v>107</v>
+      </c>
+      <c r="C389">
+        <v>45</v>
+      </c>
+      <c r="D389">
+        <v>12</v>
+      </c>
+      <c r="E389">
+        <v>540</v>
+      </c>
+      <c r="F389">
+        <v>6.5</v>
+      </c>
+      <c r="G389" t="s">
+        <v>284</v>
+      </c>
+      <c r="H389">
+        <v>62.99999999999999</v>
+      </c>
+    </row>
+    <row r="390" spans="1:8">
+      <c r="A390" t="s">
+        <v>44</v>
+      </c>
+      <c r="B390" t="s">
+        <v>107</v>
+      </c>
+      <c r="C390">
+        <v>60</v>
+      </c>
+      <c r="D390">
+        <v>8</v>
+      </c>
+      <c r="E390">
+        <v>480</v>
+      </c>
+      <c r="F390">
+        <v>8</v>
+      </c>
+      <c r="G390" t="s">
+        <v>285</v>
+      </c>
+      <c r="H390">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="391" spans="1:8">
+      <c r="A391" t="s">
+        <v>45</v>
+      </c>
+      <c r="B391" t="s">
+        <v>107</v>
+      </c>
+      <c r="C391">
+        <v>60</v>
+      </c>
+      <c r="D391">
+        <v>8</v>
+      </c>
+      <c r="E391">
+        <v>480</v>
+      </c>
+      <c r="F391">
+        <v>7.5</v>
+      </c>
+      <c r="G391" t="s">
+        <v>286</v>
+      </c>
+      <c r="H391">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="392" spans="1:8">
+      <c r="A392" t="s">
+        <v>46</v>
+      </c>
+      <c r="B392" t="s">
+        <v>107</v>
+      </c>
+      <c r="C392">
+        <v>60</v>
+      </c>
+      <c r="D392">
+        <v>8</v>
+      </c>
+      <c r="E392">
+        <v>480</v>
+      </c>
+      <c r="F392">
+        <v>7.5</v>
+      </c>
+      <c r="G392" t="s">
+        <v>287</v>
+      </c>
+      <c r="H392">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="393" spans="1:8">
+      <c r="A393" t="s">
+        <v>47</v>
+      </c>
+      <c r="B393" t="s">
+        <v>107</v>
+      </c>
+      <c r="C393">
+        <v>60</v>
+      </c>
+      <c r="D393">
+        <v>8</v>
+      </c>
+      <c r="E393">
+        <v>480</v>
+      </c>
+      <c r="F393">
+        <v>9</v>
+      </c>
+      <c r="G393" t="s">
+        <v>288</v>
+      </c>
+      <c r="H393">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="394" spans="1:8">
+      <c r="A394" t="s">
+        <v>48</v>
+      </c>
+      <c r="B394" t="s">
+        <v>114</v>
+      </c>
+      <c r="C394">
+        <v>40</v>
+      </c>
+      <c r="D394">
+        <v>10</v>
+      </c>
+      <c r="E394">
+        <v>400</v>
+      </c>
+      <c r="F394">
+        <v>8</v>
+      </c>
+      <c r="G394" t="s">
+        <v>289</v>
+      </c>
+      <c r="H394">
+        <v>53.33333333333333</v>
+      </c>
+    </row>
+    <row r="395" spans="1:8">
+      <c r="A395" t="s">
+        <v>49</v>
+      </c>
+      <c r="B395" t="s">
+        <v>114</v>
+      </c>
+      <c r="C395">
+        <v>40</v>
+      </c>
+      <c r="D395">
+        <v>12</v>
+      </c>
+      <c r="E395">
+        <v>480</v>
+      </c>
+      <c r="F395">
+        <v>7.5</v>
+      </c>
+      <c r="G395" t="s">
+        <v>290</v>
+      </c>
+      <c r="H395">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="396" spans="1:8">
+      <c r="A396" t="s">
+        <v>50</v>
+      </c>
+      <c r="B396" t="s">
+        <v>114</v>
+      </c>
+      <c r="C396">
+        <v>40</v>
+      </c>
+      <c r="D396">
+        <v>12</v>
+      </c>
+      <c r="E396">
+        <v>480</v>
+      </c>
+      <c r="F396">
+        <v>8</v>
+      </c>
+      <c r="G396" t="s">
+        <v>291</v>
+      </c>
+      <c r="H396">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="397" spans="1:8">
+      <c r="A397" t="s">
+        <v>51</v>
+      </c>
+      <c r="B397" t="s">
+        <v>114</v>
+      </c>
+      <c r="C397">
+        <v>40</v>
+      </c>
+      <c r="D397">
+        <v>12</v>
+      </c>
+      <c r="E397">
+        <v>480</v>
+      </c>
+      <c r="F397">
+        <v>8</v>
+      </c>
+      <c r="G397" t="s">
+        <v>292</v>
+      </c>
+      <c r="H397">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="398" spans="1:8">
+      <c r="A398" t="s">
+        <v>52</v>
+      </c>
+      <c r="B398" t="s">
+        <v>114</v>
+      </c>
+      <c r="C398">
+        <v>40</v>
+      </c>
+      <c r="D398">
+        <v>12</v>
+      </c>
+      <c r="E398">
+        <v>480</v>
+      </c>
+      <c r="F398">
+        <v>8.5</v>
+      </c>
+      <c r="G398" t="s">
+        <v>293</v>
+      </c>
+      <c r="H398">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="399" spans="1:8">
+      <c r="A399" t="s">
+        <v>53</v>
+      </c>
+      <c r="B399" t="s">
+        <v>114</v>
+      </c>
+      <c r="C399">
+        <v>40</v>
+      </c>
+      <c r="D399">
+        <v>12</v>
+      </c>
+      <c r="E399">
+        <v>480</v>
+      </c>
+      <c r="F399">
+        <v>9</v>
+      </c>
+      <c r="G399" t="s">
+        <v>294</v>
+      </c>
+      <c r="H399">
+        <v>56</v>
       </c>
     </row>
   </sheetData>

--- a/data/workout_log.xlsx
+++ b/data/workout_log.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1071" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1134" uniqueCount="336">
   <si>
     <t>Timestamp</t>
   </si>
@@ -178,6 +178,60 @@
     <t>2026-03-07 13:58:00</t>
   </si>
   <si>
+    <t>2026-03-08 16:00:00</t>
+  </si>
+  <si>
+    <t>2026-03-08 16:10:00</t>
+  </si>
+  <si>
+    <t>2026-03-08 16:20:00</t>
+  </si>
+  <si>
+    <t>2026-03-08 16:30:00</t>
+  </si>
+  <si>
+    <t>2026-03-08 16:40:00</t>
+  </si>
+  <si>
+    <t>2026-03-08 16:50:00</t>
+  </si>
+  <si>
+    <t>2026-03-08 17:00:00</t>
+  </si>
+  <si>
+    <t>2026-03-08 17:05:00</t>
+  </si>
+  <si>
+    <t>2026-03-08 17:10:00</t>
+  </si>
+  <si>
+    <t>2026-03-08 17:15:00</t>
+  </si>
+  <si>
+    <t>2026-03-08 17:20:00</t>
+  </si>
+  <si>
+    <t>2026-03-08 17:25:00</t>
+  </si>
+  <si>
+    <t>2026-03-08 17:30:00</t>
+  </si>
+  <si>
+    <t>2026-03-08 17:35:00</t>
+  </si>
+  <si>
+    <t>2026-03-08 17:40:00</t>
+  </si>
+  <si>
+    <t>2026-03-08 17:45:00</t>
+  </si>
+  <si>
+    <t>2026-03-08 17:50:00</t>
+  </si>
+  <si>
+    <t>2026-03-08 17:55:00</t>
+  </si>
+  <si>
     <t>Overhead Press</t>
   </si>
   <si>
@@ -361,6 +415,12 @@
     <t>Machine Rows</t>
   </si>
   <si>
+    <t>EZ Bar Curl</t>
+  </si>
+  <si>
+    <t>EZ Bar Skullcrusher</t>
+  </si>
+  <si>
     <t>Warm-up. Run: 2.75km in 12:30 prior.</t>
   </si>
   <si>
@@ -899,6 +959,69 @@
   </si>
   <si>
     <t>Final terminal set</t>
+  </si>
+  <si>
+    <t>Technical warmup</t>
+  </si>
+  <si>
+    <t>Focus on bar path</t>
+  </si>
+  <si>
+    <t>High-intensity single</t>
+  </si>
+  <si>
+    <t>Heavy volume</t>
+  </si>
+  <si>
+    <t>Failed 5th rep</t>
+  </si>
+  <si>
+    <t>Brace compromised</t>
+  </si>
+  <si>
+    <t>High-rep accessory</t>
+  </si>
+  <si>
+    <t>Stable torso</t>
+  </si>
+  <si>
+    <t>Maintaining hinge</t>
+  </si>
+  <si>
+    <t>Fatigue summation</t>
+  </si>
+  <si>
+    <t>Mobility focus</t>
+  </si>
+  <si>
+    <t>Technical transition</t>
+  </si>
+  <si>
+    <t>Pushing head through window</t>
+  </si>
+  <si>
+    <t>Failed 9th + 2 partials</t>
+  </si>
+  <si>
+    <t>Final high-effort OHP</t>
+  </si>
+  <si>
+    <t>Superset 1A</t>
+  </si>
+  <si>
+    <t>Superset 1B</t>
+  </si>
+  <si>
+    <t>Superset 2A</t>
+  </si>
+  <si>
+    <t>Superset 2B</t>
+  </si>
+  <si>
+    <t>Superset 3A</t>
+  </si>
+  <si>
+    <t>Superset 3B</t>
   </si>
 </sst>
 </file>
@@ -1256,7 +1379,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H399"/>
+  <dimension ref="A1:H420"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1290,7 +1413,7 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="C2">
         <v>30</v>
@@ -1305,7 +1428,7 @@
         <v>4</v>
       </c>
       <c r="G2" t="s">
-        <v>115</v>
+        <v>135</v>
       </c>
       <c r="H2">
         <v>40</v>
@@ -1316,7 +1439,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="C3">
         <v>30</v>
@@ -1339,7 +1462,7 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="C4">
         <v>30</v>
@@ -1362,7 +1485,7 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="C5">
         <v>30</v>
@@ -1385,7 +1508,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="C6">
         <v>60</v>
@@ -1400,7 +1523,7 @@
         <v>5</v>
       </c>
       <c r="G6" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="H6">
         <v>76</v>
@@ -1411,7 +1534,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="C7">
         <v>100</v>
@@ -1426,7 +1549,7 @@
         <v>6</v>
       </c>
       <c r="G7" t="s">
-        <v>117</v>
+        <v>137</v>
       </c>
       <c r="H7">
         <v>110</v>
@@ -1437,7 +1560,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="C8">
         <v>100</v>
@@ -1460,7 +1583,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="C9">
         <v>100</v>
@@ -1483,7 +1606,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="C10">
         <v>32</v>
@@ -1498,7 +1621,7 @@
         <v>3</v>
       </c>
       <c r="G10" t="s">
-        <v>118</v>
+        <v>138</v>
       </c>
       <c r="H10">
         <v>44.8</v>
@@ -1509,7 +1632,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="C11">
         <v>40</v>
@@ -1524,7 +1647,7 @@
         <v>5.5</v>
       </c>
       <c r="G11" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="H11">
         <v>50.66666666666666</v>
@@ -1535,7 +1658,7 @@
         <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="C12">
         <v>40</v>
@@ -1558,7 +1681,7 @@
         <v>8</v>
       </c>
       <c r="B13" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="C13">
         <v>40</v>
@@ -1573,7 +1696,7 @@
         <v>9</v>
       </c>
       <c r="G13" t="s">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="H13">
         <v>48</v>
@@ -1584,7 +1707,7 @@
         <v>8</v>
       </c>
       <c r="B14" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="C14">
         <v>20</v>
@@ -1607,7 +1730,7 @@
         <v>8</v>
       </c>
       <c r="B15" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="C15">
         <v>20</v>
@@ -1630,7 +1753,7 @@
         <v>8</v>
       </c>
       <c r="B16" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="C16">
         <v>20</v>
@@ -1653,7 +1776,7 @@
         <v>8</v>
       </c>
       <c r="B17" t="s">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="C17">
         <v>20</v>
@@ -1668,7 +1791,7 @@
         <v>8</v>
       </c>
       <c r="G17" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="H17">
         <v>26.66666666666666</v>
@@ -1679,7 +1802,7 @@
         <v>8</v>
       </c>
       <c r="B18" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="C18">
         <v>20</v>
@@ -1694,7 +1817,7 @@
         <v>8</v>
       </c>
       <c r="G18" t="s">
-        <v>122</v>
+        <v>142</v>
       </c>
       <c r="H18">
         <v>26.66666666666666</v>
@@ -1705,7 +1828,7 @@
         <v>8</v>
       </c>
       <c r="B19" t="s">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="C19">
         <v>20</v>
@@ -1720,7 +1843,7 @@
         <v>8</v>
       </c>
       <c r="G19" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="H19">
         <v>25.33333333333333</v>
@@ -1731,7 +1854,7 @@
         <v>8</v>
       </c>
       <c r="B20" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="C20">
         <v>20</v>
@@ -1746,7 +1869,7 @@
         <v>8</v>
       </c>
       <c r="G20" t="s">
-        <v>122</v>
+        <v>142</v>
       </c>
       <c r="H20">
         <v>25.33333333333333</v>
@@ -1757,7 +1880,7 @@
         <v>9</v>
       </c>
       <c r="B21" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -1772,7 +1895,7 @@
         <v>7</v>
       </c>
       <c r="G21" t="s">
-        <v>123</v>
+        <v>143</v>
       </c>
       <c r="H21">
         <v>0</v>
@@ -1783,7 +1906,7 @@
         <v>9</v>
       </c>
       <c r="B22" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="C22">
         <v>30</v>
@@ -1806,7 +1929,7 @@
         <v>9</v>
       </c>
       <c r="B23" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="C23">
         <v>30</v>
@@ -1829,7 +1952,7 @@
         <v>9</v>
       </c>
       <c r="B24" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="C24">
         <v>30</v>
@@ -1852,7 +1975,7 @@
         <v>9</v>
       </c>
       <c r="B25" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="C25">
         <v>30</v>
@@ -1875,7 +1998,7 @@
         <v>9</v>
       </c>
       <c r="B26" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="C26">
         <v>30</v>
@@ -1898,7 +2021,7 @@
         <v>9</v>
       </c>
       <c r="B27" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="C27">
         <v>30</v>
@@ -1921,7 +2044,7 @@
         <v>9</v>
       </c>
       <c r="B28" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="C28">
         <v>30</v>
@@ -1944,7 +2067,7 @@
         <v>9</v>
       </c>
       <c r="B29" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="C29">
         <v>30</v>
@@ -1967,7 +2090,7 @@
         <v>9</v>
       </c>
       <c r="B30" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="C30">
         <v>30</v>
@@ -1990,7 +2113,7 @@
         <v>9</v>
       </c>
       <c r="B31" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="C31">
         <v>70</v>
@@ -2013,7 +2136,7 @@
         <v>9</v>
       </c>
       <c r="B32" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="C32">
         <v>70</v>
@@ -2036,7 +2159,7 @@
         <v>9</v>
       </c>
       <c r="B33" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="C33">
         <v>70</v>
@@ -2059,7 +2182,7 @@
         <v>9</v>
       </c>
       <c r="B34" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="C34">
         <v>23</v>
@@ -2074,7 +2197,7 @@
         <v>7</v>
       </c>
       <c r="G34" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="H34">
         <v>38.33333333333333</v>
@@ -2085,7 +2208,7 @@
         <v>9</v>
       </c>
       <c r="B35" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="C35">
         <v>23</v>
@@ -2100,7 +2223,7 @@
         <v>7</v>
       </c>
       <c r="G35" t="s">
-        <v>122</v>
+        <v>142</v>
       </c>
       <c r="H35">
         <v>38.33333333333333</v>
@@ -2111,7 +2234,7 @@
         <v>9</v>
       </c>
       <c r="B36" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="C36">
         <v>23</v>
@@ -2126,7 +2249,7 @@
         <v>9</v>
       </c>
       <c r="G36" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="H36">
         <v>38.33333333333333</v>
@@ -2137,7 +2260,7 @@
         <v>9</v>
       </c>
       <c r="B37" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="C37">
         <v>23</v>
@@ -2152,7 +2275,7 @@
         <v>10</v>
       </c>
       <c r="G37" t="s">
-        <v>124</v>
+        <v>144</v>
       </c>
       <c r="H37">
         <v>32.2</v>
@@ -2163,7 +2286,7 @@
         <v>9</v>
       </c>
       <c r="B38" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="C38">
         <v>20</v>
@@ -2186,7 +2309,7 @@
         <v>9</v>
       </c>
       <c r="B39" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="C39">
         <v>20</v>
@@ -2209,7 +2332,7 @@
         <v>9</v>
       </c>
       <c r="B40" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="C40">
         <v>20</v>
@@ -2232,7 +2355,7 @@
         <v>10</v>
       </c>
       <c r="B41" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="C41">
         <v>36</v>
@@ -2247,7 +2370,7 @@
         <v>5</v>
       </c>
       <c r="G41" t="s">
-        <v>125</v>
+        <v>145</v>
       </c>
       <c r="H41">
         <v>48</v>
@@ -2258,7 +2381,7 @@
         <v>10</v>
       </c>
       <c r="B42" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="C42">
         <v>44</v>
@@ -2273,7 +2396,7 @@
         <v>7</v>
       </c>
       <c r="G42" t="s">
-        <v>126</v>
+        <v>146</v>
       </c>
       <c r="H42">
         <v>52.8</v>
@@ -2284,7 +2407,7 @@
         <v>10</v>
       </c>
       <c r="B43" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="C43">
         <v>44</v>
@@ -2299,7 +2422,7 @@
         <v>7.5</v>
       </c>
       <c r="G43" t="s">
-        <v>126</v>
+        <v>146</v>
       </c>
       <c r="H43">
         <v>52.8</v>
@@ -2310,7 +2433,7 @@
         <v>10</v>
       </c>
       <c r="B44" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="C44">
         <v>44</v>
@@ -2325,7 +2448,7 @@
         <v>8</v>
       </c>
       <c r="G44" t="s">
-        <v>126</v>
+        <v>146</v>
       </c>
       <c r="H44">
         <v>52.8</v>
@@ -2336,7 +2459,7 @@
         <v>10</v>
       </c>
       <c r="B45" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="C45">
         <v>60</v>
@@ -2359,7 +2482,7 @@
         <v>10</v>
       </c>
       <c r="B46" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="C46">
         <v>100</v>
@@ -2382,7 +2505,7 @@
         <v>10</v>
       </c>
       <c r="B47" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="C47">
         <v>130</v>
@@ -2405,7 +2528,7 @@
         <v>10</v>
       </c>
       <c r="B48" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="C48">
         <v>140</v>
@@ -2420,7 +2543,7 @@
         <v>10</v>
       </c>
       <c r="G48" t="s">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="H48">
         <v>144.6666666666667</v>
@@ -2431,7 +2554,7 @@
         <v>10</v>
       </c>
       <c r="B49" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="C49">
         <v>130</v>
@@ -2454,7 +2577,7 @@
         <v>10</v>
       </c>
       <c r="B50" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="C50">
         <v>100</v>
@@ -2477,7 +2600,7 @@
         <v>10</v>
       </c>
       <c r="B51" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="C51">
         <v>100</v>
@@ -2492,7 +2615,7 @@
         <v>9</v>
       </c>
       <c r="G51" t="s">
-        <v>128</v>
+        <v>148</v>
       </c>
       <c r="H51">
         <v>133.3333333333333</v>
@@ -2503,7 +2626,7 @@
         <v>10</v>
       </c>
       <c r="B52" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="C52">
         <v>20</v>
@@ -2518,7 +2641,7 @@
         <v>8</v>
       </c>
       <c r="G52" t="s">
-        <v>129</v>
+        <v>149</v>
       </c>
       <c r="H52">
         <v>26.66666666666666</v>
@@ -2529,7 +2652,7 @@
         <v>10</v>
       </c>
       <c r="B53" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="C53">
         <v>20</v>
@@ -2544,7 +2667,7 @@
         <v>9</v>
       </c>
       <c r="G53" t="s">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="H53">
         <v>26.66666666666666</v>
@@ -2555,7 +2678,7 @@
         <v>10</v>
       </c>
       <c r="B54" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="C54">
         <v>30</v>
@@ -2578,7 +2701,7 @@
         <v>10</v>
       </c>
       <c r="B55" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="C55">
         <v>40</v>
@@ -2601,7 +2724,7 @@
         <v>10</v>
       </c>
       <c r="B56" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="C56">
         <v>40</v>
@@ -2624,7 +2747,7 @@
         <v>10</v>
       </c>
       <c r="B57" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="C57">
         <v>40</v>
@@ -2647,7 +2770,7 @@
         <v>10</v>
       </c>
       <c r="B58" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="C58">
         <v>45</v>
@@ -2670,7 +2793,7 @@
         <v>10</v>
       </c>
       <c r="B59" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="C59">
         <v>45</v>
@@ -2693,7 +2816,7 @@
         <v>10</v>
       </c>
       <c r="B60" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="C60">
         <v>50</v>
@@ -2708,7 +2831,7 @@
         <v>7.5</v>
       </c>
       <c r="G60" t="s">
-        <v>131</v>
+        <v>151</v>
       </c>
       <c r="H60">
         <v>63.33333333333333</v>
@@ -2719,7 +2842,7 @@
         <v>10</v>
       </c>
       <c r="B61" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="C61">
         <v>50</v>
@@ -2734,7 +2857,7 @@
         <v>7.5</v>
       </c>
       <c r="G61" t="s">
-        <v>131</v>
+        <v>151</v>
       </c>
       <c r="H61">
         <v>63.33333333333333</v>
@@ -2745,7 +2868,7 @@
         <v>10</v>
       </c>
       <c r="B62" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="C62">
         <v>50</v>
@@ -2760,7 +2883,7 @@
         <v>8.5</v>
       </c>
       <c r="G62" t="s">
-        <v>131</v>
+        <v>151</v>
       </c>
       <c r="H62">
         <v>63.33333333333333</v>
@@ -2771,7 +2894,7 @@
         <v>10</v>
       </c>
       <c r="B63" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="C63">
         <v>50</v>
@@ -2786,7 +2909,7 @@
         <v>8.5</v>
       </c>
       <c r="G63" t="s">
-        <v>131</v>
+        <v>151</v>
       </c>
       <c r="H63">
         <v>63.33333333333333</v>
@@ -2797,7 +2920,7 @@
         <v>10</v>
       </c>
       <c r="B64" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="C64">
         <v>50</v>
@@ -2812,7 +2935,7 @@
         <v>9</v>
       </c>
       <c r="G64" t="s">
-        <v>131</v>
+        <v>151</v>
       </c>
       <c r="H64">
         <v>63.33333333333333</v>
@@ -2823,7 +2946,7 @@
         <v>10</v>
       </c>
       <c r="B65" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="C65">
         <v>50</v>
@@ -2838,7 +2961,7 @@
         <v>9</v>
       </c>
       <c r="G65" t="s">
-        <v>131</v>
+        <v>151</v>
       </c>
       <c r="H65">
         <v>63.33333333333333</v>
@@ -2849,7 +2972,7 @@
         <v>11</v>
       </c>
       <c r="B66" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="C66">
         <v>60</v>
@@ -2872,7 +2995,7 @@
         <v>11</v>
       </c>
       <c r="B67" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="C67">
         <v>100</v>
@@ -2895,7 +3018,7 @@
         <v>11</v>
       </c>
       <c r="B68" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="C68">
         <v>100</v>
@@ -2918,7 +3041,7 @@
         <v>11</v>
       </c>
       <c r="B69" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="C69">
         <v>60</v>
@@ -2941,7 +3064,7 @@
         <v>11</v>
       </c>
       <c r="B70" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="C70">
         <v>100</v>
@@ -2964,7 +3087,7 @@
         <v>11</v>
       </c>
       <c r="B71" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="C71">
         <v>80</v>
@@ -2987,7 +3110,7 @@
         <v>11</v>
       </c>
       <c r="B72" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="C72">
         <v>80</v>
@@ -3010,7 +3133,7 @@
         <v>11</v>
       </c>
       <c r="B73" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="C73">
         <v>20</v>
@@ -3033,7 +3156,7 @@
         <v>11</v>
       </c>
       <c r="B74" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="C74">
         <v>30</v>
@@ -3056,7 +3179,7 @@
         <v>11</v>
       </c>
       <c r="B75" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="C75">
         <v>35</v>
@@ -3079,7 +3202,7 @@
         <v>11</v>
       </c>
       <c r="B76" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="C76">
         <v>35</v>
@@ -3094,7 +3217,7 @@
         <v>10</v>
       </c>
       <c r="G76" t="s">
-        <v>132</v>
+        <v>152</v>
       </c>
       <c r="H76">
         <v>43.16666666666667</v>
@@ -3105,7 +3228,7 @@
         <v>11</v>
       </c>
       <c r="B77" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="C77">
         <v>30</v>
@@ -3128,7 +3251,7 @@
         <v>11</v>
       </c>
       <c r="B78" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="C78">
         <v>30</v>
@@ -3151,7 +3274,7 @@
         <v>11</v>
       </c>
       <c r="B79" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="C79">
         <v>50</v>
@@ -3174,7 +3297,7 @@
         <v>11</v>
       </c>
       <c r="B80" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="C80">
         <v>40</v>
@@ -3197,7 +3320,7 @@
         <v>11</v>
       </c>
       <c r="B81" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="C81">
         <v>22</v>
@@ -3220,7 +3343,7 @@
         <v>11</v>
       </c>
       <c r="B82" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="C82">
         <v>22</v>
@@ -3243,7 +3366,7 @@
         <v>11</v>
       </c>
       <c r="B83" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="C83">
         <v>22</v>
@@ -3266,7 +3389,7 @@
         <v>12</v>
       </c>
       <c r="B84" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="C84">
         <v>20</v>
@@ -3281,7 +3404,7 @@
         <v>4</v>
       </c>
       <c r="G84" t="s">
-        <v>133</v>
+        <v>153</v>
       </c>
       <c r="H84">
         <v>28</v>
@@ -3292,7 +3415,7 @@
         <v>12</v>
       </c>
       <c r="B85" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="C85">
         <v>40</v>
@@ -3315,7 +3438,7 @@
         <v>12</v>
       </c>
       <c r="B86" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="C86">
         <v>50</v>
@@ -3338,7 +3461,7 @@
         <v>12</v>
       </c>
       <c r="B87" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="C87">
         <v>60</v>
@@ -3361,7 +3484,7 @@
         <v>12</v>
       </c>
       <c r="B88" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="C88">
         <v>60</v>
@@ -3384,7 +3507,7 @@
         <v>12</v>
       </c>
       <c r="B89" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="C89">
         <v>60</v>
@@ -3399,7 +3522,7 @@
         <v>9</v>
       </c>
       <c r="G89" t="s">
-        <v>134</v>
+        <v>154</v>
       </c>
       <c r="H89">
         <v>64</v>
@@ -3410,7 +3533,7 @@
         <v>12</v>
       </c>
       <c r="B90" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="C90">
         <v>40</v>
@@ -3425,7 +3548,7 @@
         <v>8</v>
       </c>
       <c r="G90" t="s">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="H90">
         <v>60</v>
@@ -3436,7 +3559,7 @@
         <v>12</v>
       </c>
       <c r="B91" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="C91">
         <v>16</v>
@@ -3451,7 +3574,7 @@
         <v>7</v>
       </c>
       <c r="G91" t="s">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="H91">
         <v>21.33333333333333</v>
@@ -3462,7 +3585,7 @@
         <v>12</v>
       </c>
       <c r="B92" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="C92">
         <v>16</v>
@@ -3477,7 +3600,7 @@
         <v>7</v>
       </c>
       <c r="G92" t="s">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="H92">
         <v>21.33333333333333</v>
@@ -3488,7 +3611,7 @@
         <v>12</v>
       </c>
       <c r="B93" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="C93">
         <v>16</v>
@@ -3503,7 +3626,7 @@
         <v>8</v>
       </c>
       <c r="G93" t="s">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="H93">
         <v>21.33333333333333</v>
@@ -3514,7 +3637,7 @@
         <v>12</v>
       </c>
       <c r="B94" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="C94">
         <v>16</v>
@@ -3529,7 +3652,7 @@
         <v>8</v>
       </c>
       <c r="G94" t="s">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="H94">
         <v>21.33333333333333</v>
@@ -3540,7 +3663,7 @@
         <v>12</v>
       </c>
       <c r="B95" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="C95">
         <v>16</v>
@@ -3555,7 +3678,7 @@
         <v>8.5</v>
       </c>
       <c r="G95" t="s">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="H95">
         <v>21.33333333333333</v>
@@ -3566,7 +3689,7 @@
         <v>12</v>
       </c>
       <c r="B96" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="C96">
         <v>16</v>
@@ -3581,7 +3704,7 @@
         <v>8.5</v>
       </c>
       <c r="G96" t="s">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="H96">
         <v>21.33333333333333</v>
@@ -3592,7 +3715,7 @@
         <v>12</v>
       </c>
       <c r="B97" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="C97">
         <v>8</v>
@@ -3615,7 +3738,7 @@
         <v>12</v>
       </c>
       <c r="B98" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="C98">
         <v>8</v>
@@ -3638,7 +3761,7 @@
         <v>12</v>
       </c>
       <c r="B99" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="C99">
         <v>8</v>
@@ -3661,7 +3784,7 @@
         <v>12</v>
       </c>
       <c r="B100" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="C100">
         <v>58</v>
@@ -3676,7 +3799,7 @@
         <v>7</v>
       </c>
       <c r="G100" t="s">
-        <v>137</v>
+        <v>157</v>
       </c>
       <c r="H100">
         <v>77.33333333333333</v>
@@ -3687,7 +3810,7 @@
         <v>12</v>
       </c>
       <c r="B101" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="C101">
         <v>58</v>
@@ -3702,7 +3825,7 @@
         <v>7</v>
       </c>
       <c r="G101" t="s">
-        <v>137</v>
+        <v>157</v>
       </c>
       <c r="H101">
         <v>77.33333333333333</v>
@@ -3713,7 +3836,7 @@
         <v>12</v>
       </c>
       <c r="B102" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="C102">
         <v>58</v>
@@ -3736,7 +3859,7 @@
         <v>12</v>
       </c>
       <c r="B103" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="C103">
         <v>58</v>
@@ -3759,7 +3882,7 @@
         <v>12</v>
       </c>
       <c r="B104" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="C104">
         <v>58</v>
@@ -3782,7 +3905,7 @@
         <v>12</v>
       </c>
       <c r="B105" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="C105">
         <v>58</v>
@@ -3805,7 +3928,7 @@
         <v>12</v>
       </c>
       <c r="B106" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="C106">
         <v>45</v>
@@ -3828,7 +3951,7 @@
         <v>12</v>
       </c>
       <c r="B107" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="C107">
         <v>45</v>
@@ -3851,7 +3974,7 @@
         <v>12</v>
       </c>
       <c r="B108" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="C108">
         <v>45</v>
@@ -3874,7 +3997,7 @@
         <v>12</v>
       </c>
       <c r="B109" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="C109">
         <v>20</v>
@@ -3897,7 +4020,7 @@
         <v>12</v>
       </c>
       <c r="B110" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="C110">
         <v>30</v>
@@ -3912,7 +4035,7 @@
         <v>10</v>
       </c>
       <c r="G110" t="s">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="H110">
         <v>34</v>
@@ -3923,7 +4046,7 @@
         <v>13</v>
       </c>
       <c r="B111" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="C111">
         <v>20</v>
@@ -3938,7 +4061,7 @@
         <v>3</v>
       </c>
       <c r="G111" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="H111">
         <v>25.33333333333333</v>
@@ -3949,7 +4072,7 @@
         <v>13</v>
       </c>
       <c r="B112" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="C112">
         <v>60</v>
@@ -3964,7 +4087,7 @@
         <v>5</v>
       </c>
       <c r="G112" t="s">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="H112">
         <v>66</v>
@@ -3975,7 +4098,7 @@
         <v>13</v>
       </c>
       <c r="B113" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="C113">
         <v>80</v>
@@ -3990,7 +4113,7 @@
         <v>7</v>
       </c>
       <c r="G113" t="s">
-        <v>141</v>
+        <v>161</v>
       </c>
       <c r="H113">
         <v>88</v>
@@ -4001,7 +4124,7 @@
         <v>13</v>
       </c>
       <c r="B114" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="C114">
         <v>90</v>
@@ -4016,7 +4139,7 @@
         <v>7</v>
       </c>
       <c r="G114" t="s">
-        <v>142</v>
+        <v>162</v>
       </c>
       <c r="H114">
         <v>93.00000000000001</v>
@@ -4027,7 +4150,7 @@
         <v>13</v>
       </c>
       <c r="B115" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="C115">
         <v>90</v>
@@ -4042,7 +4165,7 @@
         <v>7.5</v>
       </c>
       <c r="G115" t="s">
-        <v>143</v>
+        <v>163</v>
       </c>
       <c r="H115">
         <v>99.00000000000001</v>
@@ -4053,7 +4176,7 @@
         <v>13</v>
       </c>
       <c r="B116" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="C116">
         <v>100</v>
@@ -4068,7 +4191,7 @@
         <v>8.5</v>
       </c>
       <c r="G116" t="s">
-        <v>144</v>
+        <v>164</v>
       </c>
       <c r="H116">
         <v>110</v>
@@ -4079,7 +4202,7 @@
         <v>13</v>
       </c>
       <c r="B117" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="C117">
         <v>110</v>
@@ -4094,7 +4217,7 @@
         <v>9</v>
       </c>
       <c r="G117" t="s">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="H117">
         <v>113.6666666666667</v>
@@ -4105,7 +4228,7 @@
         <v>13</v>
       </c>
       <c r="B118" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="C118">
         <v>20</v>
@@ -4120,7 +4243,7 @@
         <v>5</v>
       </c>
       <c r="G118" t="s">
-        <v>146</v>
+        <v>166</v>
       </c>
       <c r="H118">
         <v>28</v>
@@ -4131,7 +4254,7 @@
         <v>13</v>
       </c>
       <c r="B119" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="C119">
         <v>30</v>
@@ -4146,7 +4269,7 @@
         <v>6</v>
       </c>
       <c r="G119" t="s">
-        <v>147</v>
+        <v>167</v>
       </c>
       <c r="H119">
         <v>36</v>
@@ -4157,7 +4280,7 @@
         <v>13</v>
       </c>
       <c r="B120" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="C120">
         <v>40</v>
@@ -4172,7 +4295,7 @@
         <v>7.5</v>
       </c>
       <c r="G120" t="s">
-        <v>148</v>
+        <v>168</v>
       </c>
       <c r="H120">
         <v>45.33333333333333</v>
@@ -4183,7 +4306,7 @@
         <v>13</v>
       </c>
       <c r="B121" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="C121">
         <v>45</v>
@@ -4198,7 +4321,7 @@
         <v>8.5</v>
       </c>
       <c r="G121" t="s">
-        <v>149</v>
+        <v>169</v>
       </c>
       <c r="H121">
         <v>49.50000000000001</v>
@@ -4209,7 +4332,7 @@
         <v>13</v>
       </c>
       <c r="B122" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="C122">
         <v>50</v>
@@ -4224,7 +4347,7 @@
         <v>10</v>
       </c>
       <c r="G122" t="s">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="H122">
         <v>50</v>
@@ -4235,7 +4358,7 @@
         <v>13</v>
       </c>
       <c r="B123" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="C123">
         <v>70</v>
@@ -4250,7 +4373,7 @@
         <v>6</v>
       </c>
       <c r="G123" t="s">
-        <v>151</v>
+        <v>171</v>
       </c>
       <c r="H123">
         <v>77</v>
@@ -4261,7 +4384,7 @@
         <v>13</v>
       </c>
       <c r="B124" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="C124">
         <v>120</v>
@@ -4276,7 +4399,7 @@
         <v>8.5</v>
       </c>
       <c r="G124" t="s">
-        <v>152</v>
+        <v>172</v>
       </c>
       <c r="H124">
         <v>124</v>
@@ -4287,7 +4410,7 @@
         <v>13</v>
       </c>
       <c r="B125" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="C125">
         <v>120</v>
@@ -4302,7 +4425,7 @@
         <v>9.5</v>
       </c>
       <c r="G125" t="s">
-        <v>153</v>
+        <v>173</v>
       </c>
       <c r="H125">
         <v>124</v>
@@ -4313,7 +4436,7 @@
         <v>13</v>
       </c>
       <c r="B126" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="C126">
         <v>120</v>
@@ -4328,7 +4451,7 @@
         <v>9.5</v>
       </c>
       <c r="G126" t="s">
-        <v>154</v>
+        <v>174</v>
       </c>
       <c r="H126">
         <v>124</v>
@@ -4339,7 +4462,7 @@
         <v>13</v>
       </c>
       <c r="B127" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="C127">
         <v>120</v>
@@ -4354,7 +4477,7 @@
         <v>9.5</v>
       </c>
       <c r="G127" t="s">
-        <v>155</v>
+        <v>175</v>
       </c>
       <c r="H127">
         <v>124</v>
@@ -4365,7 +4488,7 @@
         <v>13</v>
       </c>
       <c r="B128" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="C128">
         <v>20</v>
@@ -4380,7 +4503,7 @@
         <v>6.5</v>
       </c>
       <c r="G128" t="s">
-        <v>156</v>
+        <v>176</v>
       </c>
       <c r="H128">
         <v>26.66666666666666</v>
@@ -4391,7 +4514,7 @@
         <v>13</v>
       </c>
       <c r="B129" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="C129">
         <v>20</v>
@@ -4406,7 +4529,7 @@
         <v>6.5</v>
       </c>
       <c r="G129" t="s">
-        <v>157</v>
+        <v>177</v>
       </c>
       <c r="H129">
         <v>26.66666666666666</v>
@@ -4417,7 +4540,7 @@
         <v>13</v>
       </c>
       <c r="B130" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="C130">
         <v>20</v>
@@ -4432,7 +4555,7 @@
         <v>8</v>
       </c>
       <c r="G130" t="s">
-        <v>158</v>
+        <v>178</v>
       </c>
       <c r="H130">
         <v>26.66666666666666</v>
@@ -4443,7 +4566,7 @@
         <v>13</v>
       </c>
       <c r="B131" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="C131">
         <v>20</v>
@@ -4458,7 +4581,7 @@
         <v>8</v>
       </c>
       <c r="G131" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="H131">
         <v>26.66666666666666</v>
@@ -4469,7 +4592,7 @@
         <v>13</v>
       </c>
       <c r="B132" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="C132">
         <v>20</v>
@@ -4484,7 +4607,7 @@
         <v>8.5</v>
       </c>
       <c r="G132" t="s">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="H132">
         <v>26.66666666666666</v>
@@ -4495,7 +4618,7 @@
         <v>13</v>
       </c>
       <c r="B133" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="C133">
         <v>20</v>
@@ -4510,7 +4633,7 @@
         <v>8.5</v>
       </c>
       <c r="G133" t="s">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="H133">
         <v>26.66666666666666</v>
@@ -4521,7 +4644,7 @@
         <v>14</v>
       </c>
       <c r="B134" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="C134">
         <v>20</v>
@@ -4536,7 +4659,7 @@
         <v>3</v>
       </c>
       <c r="G134" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="H134">
         <v>25.33333333333333</v>
@@ -4547,7 +4670,7 @@
         <v>14</v>
       </c>
       <c r="B135" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="C135">
         <v>60</v>
@@ -4562,7 +4685,7 @@
         <v>6</v>
       </c>
       <c r="G135" t="s">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="H135">
         <v>72</v>
@@ -4573,7 +4696,7 @@
         <v>14</v>
       </c>
       <c r="B136" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="C136">
         <v>80</v>
@@ -4588,7 +4711,7 @@
         <v>7</v>
       </c>
       <c r="G136" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="H136">
         <v>88</v>
@@ -4599,7 +4722,7 @@
         <v>14</v>
       </c>
       <c r="B137" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="C137">
         <v>100</v>
@@ -4614,7 +4737,7 @@
         <v>7</v>
       </c>
       <c r="G137" t="s">
-        <v>164</v>
+        <v>184</v>
       </c>
       <c r="H137">
         <v>103.3333333333333</v>
@@ -4625,7 +4748,7 @@
         <v>14</v>
       </c>
       <c r="B138" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="C138">
         <v>70</v>
@@ -4640,7 +4763,7 @@
         <v>8</v>
       </c>
       <c r="G138" t="s">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="H138">
         <v>98</v>
@@ -4651,7 +4774,7 @@
         <v>14</v>
       </c>
       <c r="B139" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="C139">
         <v>80</v>
@@ -4666,7 +4789,7 @@
         <v>8.5</v>
       </c>
       <c r="G139" t="s">
-        <v>166</v>
+        <v>186</v>
       </c>
       <c r="H139">
         <v>101.3333333333333</v>
@@ -4677,7 +4800,7 @@
         <v>14</v>
       </c>
       <c r="B140" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="C140">
         <v>20</v>
@@ -4692,7 +4815,7 @@
         <v>5</v>
       </c>
       <c r="G140" t="s">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="H140">
         <v>28</v>
@@ -4703,7 +4826,7 @@
         <v>14</v>
       </c>
       <c r="B141" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="C141">
         <v>30</v>
@@ -4718,7 +4841,7 @@
         <v>7</v>
       </c>
       <c r="G141" t="s">
-        <v>141</v>
+        <v>161</v>
       </c>
       <c r="H141">
         <v>38</v>
@@ -4729,7 +4852,7 @@
         <v>14</v>
       </c>
       <c r="B142" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="C142">
         <v>40</v>
@@ -4744,7 +4867,7 @@
         <v>8</v>
       </c>
       <c r="G142" t="s">
-        <v>168</v>
+        <v>188</v>
       </c>
       <c r="H142">
         <v>48</v>
@@ -4755,7 +4878,7 @@
         <v>14</v>
       </c>
       <c r="B143" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="C143">
         <v>40</v>
@@ -4770,7 +4893,7 @@
         <v>9</v>
       </c>
       <c r="G143" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="H143">
         <v>48</v>
@@ -4781,7 +4904,7 @@
         <v>14</v>
       </c>
       <c r="B144" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="C144">
         <v>30</v>
@@ -4796,7 +4919,7 @@
         <v>9</v>
       </c>
       <c r="G144" t="s">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="H144">
         <v>42</v>
@@ -4807,7 +4930,7 @@
         <v>14</v>
       </c>
       <c r="B145" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="C145">
         <v>30</v>
@@ -4822,7 +4945,7 @@
         <v>7</v>
       </c>
       <c r="G145" t="s">
-        <v>171</v>
+        <v>191</v>
       </c>
       <c r="H145">
         <v>45</v>
@@ -4833,7 +4956,7 @@
         <v>14</v>
       </c>
       <c r="B146" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="C146">
         <v>50</v>
@@ -4848,7 +4971,7 @@
         <v>7.5</v>
       </c>
       <c r="G146" t="s">
-        <v>141</v>
+        <v>161</v>
       </c>
       <c r="H146">
         <v>63.33333333333333</v>
@@ -4859,7 +4982,7 @@
         <v>14</v>
       </c>
       <c r="B147" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="C147">
         <v>50</v>
@@ -4874,7 +4997,7 @@
         <v>8</v>
       </c>
       <c r="G147" t="s">
-        <v>141</v>
+        <v>161</v>
       </c>
       <c r="H147">
         <v>63.33333333333333</v>
@@ -4885,7 +5008,7 @@
         <v>14</v>
       </c>
       <c r="B148" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="C148">
         <v>50</v>
@@ -4900,7 +5023,7 @@
         <v>8.5</v>
       </c>
       <c r="G148" t="s">
-        <v>172</v>
+        <v>192</v>
       </c>
       <c r="H148">
         <v>63.33333333333333</v>
@@ -4911,7 +5034,7 @@
         <v>14</v>
       </c>
       <c r="B149" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="C149">
         <v>50</v>
@@ -4926,7 +5049,7 @@
         <v>9.5</v>
       </c>
       <c r="G149" t="s">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="H149">
         <v>63.33333333333333</v>
@@ -4937,7 +5060,7 @@
         <v>14</v>
       </c>
       <c r="B150" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="C150">
         <v>40</v>
@@ -4952,7 +5075,7 @@
         <v>8</v>
       </c>
       <c r="G150" t="s">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="H150">
         <v>56</v>
@@ -4963,7 +5086,7 @@
         <v>14</v>
       </c>
       <c r="B151" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="C151">
         <v>70</v>
@@ -4978,7 +5101,7 @@
         <v>6</v>
       </c>
       <c r="G151" t="s">
-        <v>174</v>
+        <v>194</v>
       </c>
       <c r="H151">
         <v>84</v>
@@ -4989,7 +5112,7 @@
         <v>14</v>
       </c>
       <c r="B152" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="C152">
         <v>120</v>
@@ -5004,7 +5127,7 @@
         <v>6</v>
       </c>
       <c r="G152" t="s">
-        <v>175</v>
+        <v>195</v>
       </c>
       <c r="H152">
         <v>124</v>
@@ -5015,7 +5138,7 @@
         <v>14</v>
       </c>
       <c r="B153" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="C153">
         <v>120</v>
@@ -5030,7 +5153,7 @@
         <v>8</v>
       </c>
       <c r="G153" t="s">
-        <v>176</v>
+        <v>196</v>
       </c>
       <c r="H153">
         <v>140</v>
@@ -5041,7 +5164,7 @@
         <v>14</v>
       </c>
       <c r="B154" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="C154">
         <v>130</v>
@@ -5056,7 +5179,7 @@
         <v>8.5</v>
       </c>
       <c r="G154" t="s">
-        <v>177</v>
+        <v>197</v>
       </c>
       <c r="H154">
         <v>151.6666666666667</v>
@@ -5067,7 +5190,7 @@
         <v>14</v>
       </c>
       <c r="B155" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="C155">
         <v>130</v>
@@ -5082,7 +5205,7 @@
         <v>9</v>
       </c>
       <c r="G155" t="s">
-        <v>178</v>
+        <v>198</v>
       </c>
       <c r="H155">
         <v>151.6666666666667</v>
@@ -5093,7 +5216,7 @@
         <v>15</v>
       </c>
       <c r="B156" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="C156">
         <v>20</v>
@@ -5108,7 +5231,7 @@
         <v>4</v>
       </c>
       <c r="G156" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="H156">
         <v>28</v>
@@ -5119,7 +5242,7 @@
         <v>15</v>
       </c>
       <c r="B157" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="C157">
         <v>40</v>
@@ -5142,7 +5265,7 @@
         <v>15</v>
       </c>
       <c r="B158" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="C158">
         <v>60</v>
@@ -5157,7 +5280,7 @@
         <v>6.5</v>
       </c>
       <c r="G158" t="s">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="H158">
         <v>62.00000000000001</v>
@@ -5168,7 +5291,7 @@
         <v>15</v>
       </c>
       <c r="B159" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="C159">
         <v>70</v>
@@ -5183,7 +5306,7 @@
         <v>8.5</v>
       </c>
       <c r="G159" t="s">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="H159">
         <v>72.33333333333334</v>
@@ -5194,7 +5317,7 @@
         <v>15</v>
       </c>
       <c r="B160" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="C160">
         <v>65</v>
@@ -5209,7 +5332,7 @@
         <v>8</v>
       </c>
       <c r="G160" t="s">
-        <v>181</v>
+        <v>201</v>
       </c>
       <c r="H160">
         <v>67.16666666666667</v>
@@ -5220,7 +5343,7 @@
         <v>15</v>
       </c>
       <c r="B161" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="C161">
         <v>60</v>
@@ -5243,7 +5366,7 @@
         <v>15</v>
       </c>
       <c r="B162" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="C162">
         <v>60</v>
@@ -5258,7 +5381,7 @@
         <v>9</v>
       </c>
       <c r="G162" t="s">
-        <v>182</v>
+        <v>202</v>
       </c>
       <c r="H162">
         <v>66</v>
@@ -5269,7 +5392,7 @@
         <v>15</v>
       </c>
       <c r="B163" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="C163">
         <v>45</v>
@@ -5284,7 +5407,7 @@
         <v>8</v>
       </c>
       <c r="G163" t="s">
-        <v>183</v>
+        <v>203</v>
       </c>
       <c r="H163">
         <v>62.99999999999999</v>
@@ -5295,7 +5418,7 @@
         <v>15</v>
       </c>
       <c r="B164" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="C164">
         <v>45</v>
@@ -5318,7 +5441,7 @@
         <v>15</v>
       </c>
       <c r="B165" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="C165">
         <v>20</v>
@@ -5333,7 +5456,7 @@
         <v>7</v>
       </c>
       <c r="G165" t="s">
-        <v>156</v>
+        <v>176</v>
       </c>
       <c r="H165">
         <v>26.66666666666666</v>
@@ -5344,7 +5467,7 @@
         <v>15</v>
       </c>
       <c r="B166" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="C166">
         <v>20</v>
@@ -5359,7 +5482,7 @@
         <v>6</v>
       </c>
       <c r="G166" t="s">
-        <v>158</v>
+        <v>178</v>
       </c>
       <c r="H166">
         <v>28</v>
@@ -5370,7 +5493,7 @@
         <v>15</v>
       </c>
       <c r="B167" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="C167">
         <v>20</v>
@@ -5385,7 +5508,7 @@
         <v>7</v>
       </c>
       <c r="G167" t="s">
-        <v>157</v>
+        <v>177</v>
       </c>
       <c r="H167">
         <v>28</v>
@@ -5396,7 +5519,7 @@
         <v>15</v>
       </c>
       <c r="B168" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="C168">
         <v>20</v>
@@ -5411,7 +5534,7 @@
         <v>7</v>
       </c>
       <c r="G168" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="H168">
         <v>30</v>
@@ -5422,7 +5545,7 @@
         <v>15</v>
       </c>
       <c r="B169" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="C169">
         <v>22.5</v>
@@ -5437,7 +5560,7 @@
         <v>7.5</v>
       </c>
       <c r="G169" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
       <c r="H169">
         <v>30</v>
@@ -5448,7 +5571,7 @@
         <v>15</v>
       </c>
       <c r="B170" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="C170">
         <v>22.5</v>
@@ -5463,7 +5586,7 @@
         <v>7</v>
       </c>
       <c r="G170" t="s">
-        <v>185</v>
+        <v>205</v>
       </c>
       <c r="H170">
         <v>31.5</v>
@@ -5474,7 +5597,7 @@
         <v>15</v>
       </c>
       <c r="B171" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="C171">
         <v>25</v>
@@ -5489,7 +5612,7 @@
         <v>8</v>
       </c>
       <c r="G171" t="s">
-        <v>186</v>
+        <v>206</v>
       </c>
       <c r="H171">
         <v>31.66666666666666</v>
@@ -5500,7 +5623,7 @@
         <v>15</v>
       </c>
       <c r="B172" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="C172">
         <v>25</v>
@@ -5515,7 +5638,7 @@
         <v>7.5</v>
       </c>
       <c r="G172" t="s">
-        <v>187</v>
+        <v>207</v>
       </c>
       <c r="H172">
         <v>35</v>
@@ -5526,7 +5649,7 @@
         <v>15</v>
       </c>
       <c r="B173" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="C173">
         <v>25</v>
@@ -5541,7 +5664,7 @@
         <v>8</v>
       </c>
       <c r="G173" t="s">
-        <v>188</v>
+        <v>208</v>
       </c>
       <c r="H173">
         <v>31.66666666666666</v>
@@ -5552,7 +5675,7 @@
         <v>15</v>
       </c>
       <c r="B174" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="C174">
         <v>25</v>
@@ -5567,7 +5690,7 @@
         <v>8</v>
       </c>
       <c r="G174" t="s">
-        <v>189</v>
+        <v>209</v>
       </c>
       <c r="H174">
         <v>37.5</v>
@@ -5578,7 +5701,7 @@
         <v>15</v>
       </c>
       <c r="B175" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="C175">
         <v>40</v>
@@ -5593,7 +5716,7 @@
         <v>7.5</v>
       </c>
       <c r="G175" t="s">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="H175">
         <v>50.66666666666666</v>
@@ -5604,7 +5727,7 @@
         <v>15</v>
       </c>
       <c r="B176" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="C176">
         <v>40</v>
@@ -5619,7 +5742,7 @@
         <v>8.5</v>
       </c>
       <c r="G176" t="s">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="H176">
         <v>50.66666666666666</v>
@@ -5630,7 +5753,7 @@
         <v>15</v>
       </c>
       <c r="B177" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="C177">
         <v>40</v>
@@ -5645,7 +5768,7 @@
         <v>9</v>
       </c>
       <c r="G177" t="s">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="H177">
         <v>48</v>
@@ -5656,7 +5779,7 @@
         <v>15</v>
       </c>
       <c r="B178" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="C178">
         <v>22</v>
@@ -5671,7 +5794,7 @@
         <v>7</v>
       </c>
       <c r="G178" t="s">
-        <v>191</v>
+        <v>211</v>
       </c>
       <c r="H178">
         <v>27.86666666666667</v>
@@ -5682,7 +5805,7 @@
         <v>15</v>
       </c>
       <c r="B179" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="C179">
         <v>22</v>
@@ -5705,7 +5828,7 @@
         <v>15</v>
       </c>
       <c r="B180" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="C180">
         <v>22</v>
@@ -5720,7 +5843,7 @@
         <v>8.5</v>
       </c>
       <c r="G180" t="s">
-        <v>192</v>
+        <v>212</v>
       </c>
       <c r="H180">
         <v>27.86666666666667</v>
@@ -5731,7 +5854,7 @@
         <v>16</v>
       </c>
       <c r="B181" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="C181">
         <v>20</v>
@@ -5754,7 +5877,7 @@
         <v>16</v>
       </c>
       <c r="B182" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="C182">
         <v>22</v>
@@ -5777,7 +5900,7 @@
         <v>16</v>
       </c>
       <c r="B183" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="C183">
         <v>20</v>
@@ -5792,7 +5915,7 @@
         <v>4</v>
       </c>
       <c r="G183" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="H183">
         <v>25.33333333333333</v>
@@ -5803,7 +5926,7 @@
         <v>16</v>
       </c>
       <c r="B184" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="C184">
         <v>60</v>
@@ -5826,7 +5949,7 @@
         <v>16</v>
       </c>
       <c r="B185" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="C185">
         <v>80</v>
@@ -5849,7 +5972,7 @@
         <v>16</v>
       </c>
       <c r="B186" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="C186">
         <v>100</v>
@@ -5872,7 +5995,7 @@
         <v>16</v>
       </c>
       <c r="B187" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="C187">
         <v>110</v>
@@ -5895,7 +6018,7 @@
         <v>16</v>
       </c>
       <c r="B188" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="C188">
         <v>120</v>
@@ -5910,7 +6033,7 @@
         <v>8.5</v>
       </c>
       <c r="G188" t="s">
-        <v>193</v>
+        <v>213</v>
       </c>
       <c r="H188">
         <v>124</v>
@@ -5921,7 +6044,7 @@
         <v>16</v>
       </c>
       <c r="B189" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="C189">
         <v>80</v>
@@ -5936,7 +6059,7 @@
         <v>7.5</v>
       </c>
       <c r="G189" t="s">
-        <v>194</v>
+        <v>214</v>
       </c>
       <c r="H189">
         <v>112</v>
@@ -5947,7 +6070,7 @@
         <v>16</v>
       </c>
       <c r="B190" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="C190">
         <v>-30</v>
@@ -5962,7 +6085,7 @@
         <v>6</v>
       </c>
       <c r="G190" t="s">
-        <v>195</v>
+        <v>215</v>
       </c>
       <c r="H190">
         <v>-38</v>
@@ -5973,7 +6096,7 @@
         <v>16</v>
       </c>
       <c r="B191" t="s">
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="C191">
         <v>-30</v>
@@ -5988,7 +6111,7 @@
         <v>6</v>
       </c>
       <c r="G191" t="s">
-        <v>195</v>
+        <v>215</v>
       </c>
       <c r="H191">
         <v>-38</v>
@@ -5999,7 +6122,7 @@
         <v>16</v>
       </c>
       <c r="B192" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="C192">
         <v>-25</v>
@@ -6014,7 +6137,7 @@
         <v>7.5</v>
       </c>
       <c r="G192" t="s">
-        <v>196</v>
+        <v>216</v>
       </c>
       <c r="H192">
         <v>-33.33333333333333</v>
@@ -6025,7 +6148,7 @@
         <v>16</v>
       </c>
       <c r="B193" t="s">
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="C193">
         <v>-25</v>
@@ -6040,7 +6163,7 @@
         <v>7.5</v>
       </c>
       <c r="G193" t="s">
-        <v>196</v>
+        <v>216</v>
       </c>
       <c r="H193">
         <v>-33.33333333333333</v>
@@ -6051,7 +6174,7 @@
         <v>16</v>
       </c>
       <c r="B194" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="C194">
         <v>-20</v>
@@ -6066,7 +6189,7 @@
         <v>8</v>
       </c>
       <c r="G194" t="s">
-        <v>197</v>
+        <v>217</v>
       </c>
       <c r="H194">
         <v>-25.33333333333333</v>
@@ -6077,7 +6200,7 @@
         <v>16</v>
       </c>
       <c r="B195" t="s">
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="C195">
         <v>-20</v>
@@ -6092,7 +6215,7 @@
         <v>8</v>
       </c>
       <c r="G195" t="s">
-        <v>197</v>
+        <v>217</v>
       </c>
       <c r="H195">
         <v>-25.33333333333333</v>
@@ -6103,7 +6226,7 @@
         <v>16</v>
       </c>
       <c r="B196" t="s">
-        <v>96</v>
+        <v>114</v>
       </c>
       <c r="C196">
         <v>35</v>
@@ -6118,7 +6241,7 @@
         <v>7</v>
       </c>
       <c r="G196" t="s">
-        <v>198</v>
+        <v>218</v>
       </c>
       <c r="H196">
         <v>52.5</v>
@@ -6129,7 +6252,7 @@
         <v>16</v>
       </c>
       <c r="B197" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="C197">
         <v>25</v>
@@ -6144,7 +6267,7 @@
         <v>7</v>
       </c>
       <c r="G197" t="s">
-        <v>198</v>
+        <v>218</v>
       </c>
       <c r="H197">
         <v>37.5</v>
@@ -6155,7 +6278,7 @@
         <v>16</v>
       </c>
       <c r="B198" t="s">
-        <v>96</v>
+        <v>114</v>
       </c>
       <c r="C198">
         <v>35</v>
@@ -6170,7 +6293,7 @@
         <v>7</v>
       </c>
       <c r="G198" t="s">
-        <v>199</v>
+        <v>219</v>
       </c>
       <c r="H198">
         <v>52.5</v>
@@ -6181,7 +6304,7 @@
         <v>16</v>
       </c>
       <c r="B199" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="C199">
         <v>25</v>
@@ -6196,7 +6319,7 @@
         <v>7</v>
       </c>
       <c r="G199" t="s">
-        <v>199</v>
+        <v>219</v>
       </c>
       <c r="H199">
         <v>37.5</v>
@@ -6207,7 +6330,7 @@
         <v>17</v>
       </c>
       <c r="B200" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="C200">
         <v>70</v>
@@ -6222,7 +6345,7 @@
         <v>6</v>
       </c>
       <c r="G200" t="s">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="H200">
         <v>84</v>
@@ -6233,7 +6356,7 @@
         <v>17</v>
       </c>
       <c r="B201" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="C201">
         <v>90</v>
@@ -6256,7 +6379,7 @@
         <v>17</v>
       </c>
       <c r="B202" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="C202">
         <v>120</v>
@@ -6279,7 +6402,7 @@
         <v>17</v>
       </c>
       <c r="B203" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="C203">
         <v>120</v>
@@ -6302,7 +6425,7 @@
         <v>17</v>
       </c>
       <c r="B204" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="C204">
         <v>120</v>
@@ -6325,7 +6448,7 @@
         <v>17</v>
       </c>
       <c r="B205" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="C205">
         <v>120</v>
@@ -6348,7 +6471,7 @@
         <v>17</v>
       </c>
       <c r="B206" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="C206">
         <v>120</v>
@@ -6371,7 +6494,7 @@
         <v>17</v>
       </c>
       <c r="B207" t="s">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="C207">
         <v>20</v>
@@ -6386,7 +6509,7 @@
         <v>6</v>
       </c>
       <c r="G207" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
       <c r="H207">
         <v>28</v>
@@ -6397,7 +6520,7 @@
         <v>17</v>
       </c>
       <c r="B208" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="C208">
         <v>30</v>
@@ -6420,7 +6543,7 @@
         <v>17</v>
       </c>
       <c r="B209" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="C209">
         <v>35</v>
@@ -6443,7 +6566,7 @@
         <v>17</v>
       </c>
       <c r="B210" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="C210">
         <v>35</v>
@@ -6466,7 +6589,7 @@
         <v>17</v>
       </c>
       <c r="B211" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="C211">
         <v>35</v>
@@ -6489,7 +6612,7 @@
         <v>17</v>
       </c>
       <c r="B212" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="C212">
         <v>22</v>
@@ -6504,7 +6627,7 @@
         <v>7.5</v>
       </c>
       <c r="G212" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="H212">
         <v>27.86666666666667</v>
@@ -6515,7 +6638,7 @@
         <v>17</v>
       </c>
       <c r="B213" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="C213">
         <v>22</v>
@@ -6530,7 +6653,7 @@
         <v>7.5</v>
       </c>
       <c r="G213" t="s">
-        <v>122</v>
+        <v>142</v>
       </c>
       <c r="H213">
         <v>30.8</v>
@@ -6541,7 +6664,7 @@
         <v>17</v>
       </c>
       <c r="B214" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="C214">
         <v>22</v>
@@ -6556,7 +6679,7 @@
         <v>8</v>
       </c>
       <c r="G214" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="H214">
         <v>27.86666666666667</v>
@@ -6567,7 +6690,7 @@
         <v>17</v>
       </c>
       <c r="B215" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="C215">
         <v>22</v>
@@ -6582,7 +6705,7 @@
         <v>8</v>
       </c>
       <c r="G215" t="s">
-        <v>122</v>
+        <v>142</v>
       </c>
       <c r="H215">
         <v>30.8</v>
@@ -6593,7 +6716,7 @@
         <v>17</v>
       </c>
       <c r="B216" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="C216">
         <v>22</v>
@@ -6608,7 +6731,7 @@
         <v>8.5</v>
       </c>
       <c r="G216" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="H216">
         <v>27.86666666666667</v>
@@ -6619,7 +6742,7 @@
         <v>17</v>
       </c>
       <c r="B217" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="C217">
         <v>22</v>
@@ -6634,7 +6757,7 @@
         <v>8</v>
       </c>
       <c r="G217" t="s">
-        <v>122</v>
+        <v>142</v>
       </c>
       <c r="H217">
         <v>30.8</v>
@@ -6645,7 +6768,7 @@
         <v>17</v>
       </c>
       <c r="B218" t="s">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="C218">
         <v>25</v>
@@ -6660,7 +6783,7 @@
         <v>8</v>
       </c>
       <c r="G218" t="s">
-        <v>202</v>
+        <v>222</v>
       </c>
       <c r="H218">
         <v>31.66666666666666</v>
@@ -6671,7 +6794,7 @@
         <v>17</v>
       </c>
       <c r="B219" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="C219">
         <v>25</v>
@@ -6686,7 +6809,7 @@
         <v>6.5</v>
       </c>
       <c r="G219" t="s">
-        <v>203</v>
+        <v>223</v>
       </c>
       <c r="H219">
         <v>31.66666666666666</v>
@@ -6697,7 +6820,7 @@
         <v>17</v>
       </c>
       <c r="B220" t="s">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="C220">
         <v>25</v>
@@ -6712,7 +6835,7 @@
         <v>8</v>
       </c>
       <c r="G220" t="s">
-        <v>202</v>
+        <v>222</v>
       </c>
       <c r="H220">
         <v>31.66666666666666</v>
@@ -6723,7 +6846,7 @@
         <v>17</v>
       </c>
       <c r="B221" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="C221">
         <v>25</v>
@@ -6738,7 +6861,7 @@
         <v>7.5</v>
       </c>
       <c r="G221" t="s">
-        <v>203</v>
+        <v>223</v>
       </c>
       <c r="H221">
         <v>31.66666666666666</v>
@@ -6749,7 +6872,7 @@
         <v>17</v>
       </c>
       <c r="B222" t="s">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="C222">
         <v>25</v>
@@ -6764,7 +6887,7 @@
         <v>9</v>
       </c>
       <c r="G222" t="s">
-        <v>202</v>
+        <v>222</v>
       </c>
       <c r="H222">
         <v>31.66666666666666</v>
@@ -6775,7 +6898,7 @@
         <v>17</v>
       </c>
       <c r="B223" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="C223">
         <v>25</v>
@@ -6790,7 +6913,7 @@
         <v>9</v>
       </c>
       <c r="G223" t="s">
-        <v>203</v>
+        <v>223</v>
       </c>
       <c r="H223">
         <v>31.66666666666666</v>
@@ -6801,7 +6924,7 @@
         <v>18</v>
       </c>
       <c r="B224" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="C224">
         <v>70</v>
@@ -6816,7 +6939,7 @@
         <v>6.5</v>
       </c>
       <c r="G224" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="H224">
         <v>84</v>
@@ -6827,7 +6950,7 @@
         <v>18</v>
       </c>
       <c r="B225" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="C225">
         <v>85</v>
@@ -6842,7 +6965,7 @@
         <v>8</v>
       </c>
       <c r="G225" t="s">
-        <v>204</v>
+        <v>224</v>
       </c>
       <c r="H225">
         <v>119</v>
@@ -6853,7 +6976,7 @@
         <v>18</v>
       </c>
       <c r="B226" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="C226">
         <v>85</v>
@@ -6868,7 +6991,7 @@
         <v>9</v>
       </c>
       <c r="G226" t="s">
-        <v>205</v>
+        <v>225</v>
       </c>
       <c r="H226">
         <v>119</v>
@@ -6879,7 +7002,7 @@
         <v>18</v>
       </c>
       <c r="B227" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="C227">
         <v>85</v>
@@ -6894,7 +7017,7 @@
         <v>10</v>
       </c>
       <c r="G227" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="H227">
         <v>113.3333333333333</v>
@@ -6905,7 +7028,7 @@
         <v>18</v>
       </c>
       <c r="B228" t="s">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="C228">
         <v>30</v>
@@ -6920,7 +7043,7 @@
         <v>6</v>
       </c>
       <c r="G228" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="H228">
         <v>36</v>
@@ -6931,7 +7054,7 @@
         <v>18</v>
       </c>
       <c r="B229" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="C229">
         <v>30</v>
@@ -6946,7 +7069,7 @@
         <v>6</v>
       </c>
       <c r="G229" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="H229">
         <v>38</v>
@@ -6957,7 +7080,7 @@
         <v>18</v>
       </c>
       <c r="B230" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="C230">
         <v>40</v>
@@ -6972,7 +7095,7 @@
         <v>8</v>
       </c>
       <c r="G230" t="s">
-        <v>204</v>
+        <v>224</v>
       </c>
       <c r="H230">
         <v>50.66666666666666</v>
@@ -6983,7 +7106,7 @@
         <v>18</v>
       </c>
       <c r="B231" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="C231">
         <v>40</v>
@@ -6998,7 +7121,7 @@
         <v>9</v>
       </c>
       <c r="G231" t="s">
-        <v>205</v>
+        <v>225</v>
       </c>
       <c r="H231">
         <v>50.66666666666666</v>
@@ -7009,7 +7132,7 @@
         <v>18</v>
       </c>
       <c r="B232" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="C232">
         <v>40</v>
@@ -7024,7 +7147,7 @@
         <v>10</v>
       </c>
       <c r="G232" t="s">
-        <v>132</v>
+        <v>152</v>
       </c>
       <c r="H232">
         <v>49.33333333333334</v>
@@ -7035,7 +7158,7 @@
         <v>18</v>
       </c>
       <c r="B233" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="C233">
         <v>40</v>
@@ -7050,7 +7173,7 @@
         <v>6.5</v>
       </c>
       <c r="G233" t="s">
-        <v>208</v>
+        <v>228</v>
       </c>
       <c r="H233">
         <v>56</v>
@@ -7061,7 +7184,7 @@
         <v>18</v>
       </c>
       <c r="B234" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="C234">
         <v>40</v>
@@ -7076,7 +7199,7 @@
         <v>6.5</v>
       </c>
       <c r="G234" t="s">
-        <v>209</v>
+        <v>229</v>
       </c>
       <c r="H234">
         <v>56</v>
@@ -7087,7 +7210,7 @@
         <v>18</v>
       </c>
       <c r="B235" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="C235">
         <v>40</v>
@@ -7102,7 +7225,7 @@
         <v>7.5</v>
       </c>
       <c r="G235" t="s">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="H235">
         <v>56</v>
@@ -7113,7 +7236,7 @@
         <v>18</v>
       </c>
       <c r="B236" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="C236">
         <v>40</v>
@@ -7128,7 +7251,7 @@
         <v>9</v>
       </c>
       <c r="G236" t="s">
-        <v>211</v>
+        <v>231</v>
       </c>
       <c r="H236">
         <v>56</v>
@@ -7139,7 +7262,7 @@
         <v>18</v>
       </c>
       <c r="B237" t="s">
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="C237">
         <v>60</v>
@@ -7154,7 +7277,7 @@
         <v>8</v>
       </c>
       <c r="G237" t="s">
-        <v>156</v>
+        <v>176</v>
       </c>
       <c r="H237">
         <v>80</v>
@@ -7165,7 +7288,7 @@
         <v>18</v>
       </c>
       <c r="B238" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="C238">
         <v>60</v>
@@ -7180,7 +7303,7 @@
         <v>7</v>
       </c>
       <c r="G238" t="s">
-        <v>158</v>
+        <v>178</v>
       </c>
       <c r="H238">
         <v>80</v>
@@ -7191,7 +7314,7 @@
         <v>18</v>
       </c>
       <c r="B239" t="s">
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="C239">
         <v>60</v>
@@ -7206,7 +7329,7 @@
         <v>8.5</v>
       </c>
       <c r="G239" t="s">
-        <v>157</v>
+        <v>177</v>
       </c>
       <c r="H239">
         <v>80</v>
@@ -7217,7 +7340,7 @@
         <v>18</v>
       </c>
       <c r="B240" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="C240">
         <v>60</v>
@@ -7232,7 +7355,7 @@
         <v>8</v>
       </c>
       <c r="G240" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="H240">
         <v>80</v>
@@ -7243,7 +7366,7 @@
         <v>18</v>
       </c>
       <c r="B241" t="s">
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="C241">
         <v>60</v>
@@ -7258,7 +7381,7 @@
         <v>9</v>
       </c>
       <c r="G241" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
       <c r="H241">
         <v>80</v>
@@ -7269,7 +7392,7 @@
         <v>18</v>
       </c>
       <c r="B242" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="C242">
         <v>60</v>
@@ -7284,7 +7407,7 @@
         <v>9</v>
       </c>
       <c r="G242" t="s">
-        <v>185</v>
+        <v>205</v>
       </c>
       <c r="H242">
         <v>80</v>
@@ -7295,7 +7418,7 @@
         <v>19</v>
       </c>
       <c r="B243" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="C243">
         <v>60</v>
@@ -7310,7 +7433,7 @@
         <v>4</v>
       </c>
       <c r="G243" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="H243">
         <v>76</v>
@@ -7321,7 +7444,7 @@
         <v>19</v>
       </c>
       <c r="B244" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="C244">
         <v>100</v>
@@ -7336,7 +7459,7 @@
         <v>6</v>
       </c>
       <c r="G244" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="H244">
         <v>116.6666666666667</v>
@@ -7347,7 +7470,7 @@
         <v>19</v>
       </c>
       <c r="B245" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="C245">
         <v>130</v>
@@ -7362,7 +7485,7 @@
         <v>7</v>
       </c>
       <c r="G245" t="s">
-        <v>212</v>
+        <v>232</v>
       </c>
       <c r="H245">
         <v>134.3333333333333</v>
@@ -7373,7 +7496,7 @@
         <v>19</v>
       </c>
       <c r="B246" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="C246">
         <v>150</v>
@@ -7388,7 +7511,7 @@
         <v>8.5</v>
       </c>
       <c r="G246" t="s">
-        <v>213</v>
+        <v>233</v>
       </c>
       <c r="H246">
         <v>155</v>
@@ -7399,7 +7522,7 @@
         <v>19</v>
       </c>
       <c r="B247" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="C247">
         <v>120</v>
@@ -7414,7 +7537,7 @@
         <v>7.5</v>
       </c>
       <c r="G247" t="s">
-        <v>214</v>
+        <v>234</v>
       </c>
       <c r="H247">
         <v>140</v>
@@ -7425,7 +7548,7 @@
         <v>19</v>
       </c>
       <c r="B248" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="C248">
         <v>120</v>
@@ -7440,7 +7563,7 @@
         <v>7.5</v>
       </c>
       <c r="G248" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="H248">
         <v>140</v>
@@ -7451,7 +7574,7 @@
         <v>19</v>
       </c>
       <c r="B249" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="C249">
         <v>120</v>
@@ -7466,7 +7589,7 @@
         <v>8</v>
       </c>
       <c r="G249" t="s">
-        <v>216</v>
+        <v>236</v>
       </c>
       <c r="H249">
         <v>140</v>
@@ -7477,7 +7600,7 @@
         <v>19</v>
       </c>
       <c r="B250" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="C250">
         <v>120</v>
@@ -7492,7 +7615,7 @@
         <v>8.5</v>
       </c>
       <c r="G250" t="s">
-        <v>217</v>
+        <v>237</v>
       </c>
       <c r="H250">
         <v>140</v>
@@ -7503,7 +7626,7 @@
         <v>19</v>
       </c>
       <c r="B251" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="C251">
         <v>120</v>
@@ -7518,7 +7641,7 @@
         <v>9</v>
       </c>
       <c r="G251" t="s">
-        <v>218</v>
+        <v>238</v>
       </c>
       <c r="H251">
         <v>140</v>
@@ -7529,7 +7652,7 @@
         <v>19</v>
       </c>
       <c r="B252" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="C252">
         <v>40</v>
@@ -7544,7 +7667,7 @@
         <v>5</v>
       </c>
       <c r="G252" t="s">
-        <v>219</v>
+        <v>239</v>
       </c>
       <c r="H252">
         <v>50.66666666666666</v>
@@ -7555,7 +7678,7 @@
         <v>19</v>
       </c>
       <c r="B253" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="C253">
         <v>50</v>
@@ -7570,7 +7693,7 @@
         <v>6</v>
       </c>
       <c r="G253" t="s">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="H253">
         <v>58.33333333333334</v>
@@ -7581,7 +7704,7 @@
         <v>19</v>
       </c>
       <c r="B254" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="C254">
         <v>60</v>
@@ -7596,7 +7719,7 @@
         <v>7</v>
       </c>
       <c r="G254" t="s">
-        <v>221</v>
+        <v>241</v>
       </c>
       <c r="H254">
         <v>70</v>
@@ -7607,7 +7730,7 @@
         <v>19</v>
       </c>
       <c r="B255" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="C255">
         <v>60</v>
@@ -7622,7 +7745,7 @@
         <v>8</v>
       </c>
       <c r="G255" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="H255">
         <v>70</v>
@@ -7633,7 +7756,7 @@
         <v>19</v>
       </c>
       <c r="B256" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="C256">
         <v>60</v>
@@ -7648,7 +7771,7 @@
         <v>8.5</v>
       </c>
       <c r="G256" t="s">
-        <v>223</v>
+        <v>243</v>
       </c>
       <c r="H256">
         <v>70</v>
@@ -7659,7 +7782,7 @@
         <v>19</v>
       </c>
       <c r="B257" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="C257">
         <v>60</v>
@@ -7674,7 +7797,7 @@
         <v>8.5</v>
       </c>
       <c r="G257" t="s">
-        <v>224</v>
+        <v>244</v>
       </c>
       <c r="H257">
         <v>70</v>
@@ -7685,7 +7808,7 @@
         <v>19</v>
       </c>
       <c r="B258" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="C258">
         <v>60</v>
@@ -7700,7 +7823,7 @@
         <v>8</v>
       </c>
       <c r="G258" t="s">
-        <v>225</v>
+        <v>245</v>
       </c>
       <c r="H258">
         <v>70</v>
@@ -7711,7 +7834,7 @@
         <v>19</v>
       </c>
       <c r="B259" t="s">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="C259">
         <v>40</v>
@@ -7726,7 +7849,7 @@
         <v>5</v>
       </c>
       <c r="G259" t="s">
-        <v>226</v>
+        <v>246</v>
       </c>
       <c r="H259">
         <v>53.33333333333333</v>
@@ -7737,7 +7860,7 @@
         <v>19</v>
       </c>
       <c r="B260" t="s">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="C260">
         <v>50</v>
@@ -7752,7 +7875,7 @@
         <v>7</v>
       </c>
       <c r="G260" t="s">
-        <v>227</v>
+        <v>247</v>
       </c>
       <c r="H260">
         <v>63.33333333333333</v>
@@ -7763,7 +7886,7 @@
         <v>19</v>
       </c>
       <c r="B261" t="s">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="C261">
         <v>50</v>
@@ -7778,7 +7901,7 @@
         <v>7</v>
       </c>
       <c r="G261" t="s">
-        <v>228</v>
+        <v>248</v>
       </c>
       <c r="H261">
         <v>63.33333333333333</v>
@@ -7789,7 +7912,7 @@
         <v>19</v>
       </c>
       <c r="B262" t="s">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="C262">
         <v>50</v>
@@ -7804,7 +7927,7 @@
         <v>7.5</v>
       </c>
       <c r="G262" t="s">
-        <v>229</v>
+        <v>249</v>
       </c>
       <c r="H262">
         <v>63.33333333333333</v>
@@ -7815,7 +7938,7 @@
         <v>19</v>
       </c>
       <c r="B263" t="s">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="C263">
         <v>50</v>
@@ -7830,7 +7953,7 @@
         <v>8</v>
       </c>
       <c r="G263" t="s">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="H263">
         <v>66.66666666666666</v>
@@ -7841,7 +7964,7 @@
         <v>19</v>
       </c>
       <c r="B264" t="s">
-        <v>100</v>
+        <v>118</v>
       </c>
       <c r="C264">
         <v>20</v>
@@ -7856,7 +7979,7 @@
         <v>7</v>
       </c>
       <c r="G264" t="s">
-        <v>156</v>
+        <v>176</v>
       </c>
       <c r="H264">
         <v>26.66666666666666</v>
@@ -7867,7 +7990,7 @@
         <v>19</v>
       </c>
       <c r="B265" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="C265">
         <v>20</v>
@@ -7882,7 +8005,7 @@
         <v>7</v>
       </c>
       <c r="G265" t="s">
-        <v>157</v>
+        <v>177</v>
       </c>
       <c r="H265">
         <v>28</v>
@@ -7893,7 +8016,7 @@
         <v>19</v>
       </c>
       <c r="B266" t="s">
-        <v>100</v>
+        <v>118</v>
       </c>
       <c r="C266">
         <v>25</v>
@@ -7908,7 +8031,7 @@
         <v>8.5</v>
       </c>
       <c r="G266" t="s">
-        <v>231</v>
+        <v>251</v>
       </c>
       <c r="H266">
         <v>31.66666666666666</v>
@@ -7919,7 +8042,7 @@
         <v>19</v>
       </c>
       <c r="B267" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="C267">
         <v>25</v>
@@ -7934,7 +8057,7 @@
         <v>7.5</v>
       </c>
       <c r="G267" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="H267">
         <v>33.33333333333333</v>
@@ -7945,7 +8068,7 @@
         <v>19</v>
       </c>
       <c r="B268" t="s">
-        <v>100</v>
+        <v>118</v>
       </c>
       <c r="C268">
         <v>25</v>
@@ -7960,7 +8083,7 @@
         <v>8.5</v>
       </c>
       <c r="G268" t="s">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="H268">
         <v>31.66666666666666</v>
@@ -7971,7 +8094,7 @@
         <v>19</v>
       </c>
       <c r="B269" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="C269">
         <v>25</v>
@@ -7986,7 +8109,7 @@
         <v>8</v>
       </c>
       <c r="G269" t="s">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="H269">
         <v>35</v>
@@ -7997,7 +8120,7 @@
         <v>19</v>
       </c>
       <c r="B270" t="s">
-        <v>100</v>
+        <v>118</v>
       </c>
       <c r="C270">
         <v>25</v>
@@ -8012,7 +8135,7 @@
         <v>9</v>
       </c>
       <c r="G270" t="s">
-        <v>232</v>
+        <v>252</v>
       </c>
       <c r="H270">
         <v>31.66666666666666</v>
@@ -8023,7 +8146,7 @@
         <v>19</v>
       </c>
       <c r="B271" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="C271">
         <v>25</v>
@@ -8038,7 +8161,7 @@
         <v>9</v>
       </c>
       <c r="G271" t="s">
-        <v>233</v>
+        <v>253</v>
       </c>
       <c r="H271">
         <v>37.5</v>
@@ -8049,7 +8172,7 @@
         <v>20</v>
       </c>
       <c r="B272" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="C272">
         <v>20</v>
@@ -8072,7 +8195,7 @@
         <v>20</v>
       </c>
       <c r="B273" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="C273">
         <v>60</v>
@@ -8095,7 +8218,7 @@
         <v>20</v>
       </c>
       <c r="B274" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="C274">
         <v>100</v>
@@ -8118,7 +8241,7 @@
         <v>20</v>
       </c>
       <c r="B275" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="C275">
         <v>100</v>
@@ -8141,7 +8264,7 @@
         <v>20</v>
       </c>
       <c r="B276" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="C276">
         <v>60</v>
@@ -8164,7 +8287,7 @@
         <v>20</v>
       </c>
       <c r="B277" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="C277">
         <v>90</v>
@@ -8187,7 +8310,7 @@
         <v>20</v>
       </c>
       <c r="B278" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="C278">
         <v>110</v>
@@ -8210,7 +8333,7 @@
         <v>20</v>
       </c>
       <c r="B279" t="s">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="C279">
         <v>30</v>
@@ -8233,7 +8356,7 @@
         <v>20</v>
       </c>
       <c r="B280" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="C280">
         <v>40</v>
@@ -8256,7 +8379,7 @@
         <v>20</v>
       </c>
       <c r="B281" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="C281">
         <v>40</v>
@@ -8279,7 +8402,7 @@
         <v>20</v>
       </c>
       <c r="B282" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="C282">
         <v>30</v>
@@ -8302,7 +8425,7 @@
         <v>20</v>
       </c>
       <c r="B283" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="C283">
         <v>30</v>
@@ -8325,7 +8448,7 @@
         <v>20</v>
       </c>
       <c r="B284" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="C284">
         <v>40</v>
@@ -8348,7 +8471,7 @@
         <v>20</v>
       </c>
       <c r="B285" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="C285">
         <v>40</v>
@@ -8371,7 +8494,7 @@
         <v>20</v>
       </c>
       <c r="B286" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="C286">
         <v>40</v>
@@ -8394,7 +8517,7 @@
         <v>20</v>
       </c>
       <c r="B287" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="C287">
         <v>40</v>
@@ -8417,7 +8540,7 @@
         <v>20</v>
       </c>
       <c r="B288" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="C288">
         <v>60</v>
@@ -8440,7 +8563,7 @@
         <v>20</v>
       </c>
       <c r="B289" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="C289">
         <v>60</v>
@@ -8463,7 +8586,7 @@
         <v>20</v>
       </c>
       <c r="B290" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="C290">
         <v>60</v>
@@ -8486,7 +8609,7 @@
         <v>20</v>
       </c>
       <c r="B291" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="C291">
         <v>60</v>
@@ -8509,7 +8632,7 @@
         <v>20</v>
       </c>
       <c r="B292" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="C292">
         <v>60</v>
@@ -8532,7 +8655,7 @@
         <v>20</v>
       </c>
       <c r="B293" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="C293">
         <v>60</v>
@@ -8555,7 +8678,7 @@
         <v>21</v>
       </c>
       <c r="B294" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="C294">
         <v>20</v>
@@ -8570,7 +8693,7 @@
         <v>3</v>
       </c>
       <c r="G294" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="H294">
         <v>28</v>
@@ -8581,7 +8704,7 @@
         <v>21</v>
       </c>
       <c r="B295" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="C295">
         <v>60</v>
@@ -8596,7 +8719,7 @@
         <v>6</v>
       </c>
       <c r="G295" t="s">
-        <v>141</v>
+        <v>161</v>
       </c>
       <c r="H295">
         <v>76</v>
@@ -8607,7 +8730,7 @@
         <v>21</v>
       </c>
       <c r="B296" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="C296">
         <v>110</v>
@@ -8622,7 +8745,7 @@
         <v>7.5</v>
       </c>
       <c r="G296" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="H296">
         <v>121</v>
@@ -8633,7 +8756,7 @@
         <v>21</v>
       </c>
       <c r="B297" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="C297">
         <v>70</v>
@@ -8648,7 +8771,7 @@
         <v>8</v>
       </c>
       <c r="G297" t="s">
-        <v>234</v>
+        <v>254</v>
       </c>
       <c r="H297">
         <v>116.6666666666667</v>
@@ -8659,7 +8782,7 @@
         <v>21</v>
       </c>
       <c r="B298" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="C298">
         <v>80</v>
@@ -8674,7 +8797,7 @@
         <v>8.5</v>
       </c>
       <c r="G298" t="s">
-        <v>235</v>
+        <v>255</v>
       </c>
       <c r="H298">
         <v>112</v>
@@ -8685,7 +8808,7 @@
         <v>21</v>
       </c>
       <c r="B299" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="C299">
         <v>60</v>
@@ -8700,7 +8823,7 @@
         <v>5</v>
       </c>
       <c r="G299" t="s">
-        <v>236</v>
+        <v>256</v>
       </c>
       <c r="H299">
         <v>80</v>
@@ -8711,7 +8834,7 @@
         <v>21</v>
       </c>
       <c r="B300" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="C300">
         <v>110</v>
@@ -8726,7 +8849,7 @@
         <v>6.5</v>
       </c>
       <c r="G300" t="s">
-        <v>141</v>
+        <v>161</v>
       </c>
       <c r="H300">
         <v>128.3333333333333</v>
@@ -8737,7 +8860,7 @@
         <v>21</v>
       </c>
       <c r="B301" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="C301">
         <v>140</v>
@@ -8752,7 +8875,7 @@
         <v>7</v>
       </c>
       <c r="G301" t="s">
-        <v>142</v>
+        <v>162</v>
       </c>
       <c r="H301">
         <v>144.6666666666667</v>
@@ -8763,7 +8886,7 @@
         <v>21</v>
       </c>
       <c r="B302" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="C302">
         <v>160</v>
@@ -8778,7 +8901,7 @@
         <v>8.5</v>
       </c>
       <c r="G302" t="s">
-        <v>237</v>
+        <v>257</v>
       </c>
       <c r="H302">
         <v>165.3333333333333</v>
@@ -8789,7 +8912,7 @@
         <v>21</v>
       </c>
       <c r="B303" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="C303">
         <v>170</v>
@@ -8804,7 +8927,7 @@
         <v>9</v>
       </c>
       <c r="G303" t="s">
-        <v>238</v>
+        <v>258</v>
       </c>
       <c r="H303">
         <v>175.6666666666667</v>
@@ -8815,7 +8938,7 @@
         <v>21</v>
       </c>
       <c r="B304" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="C304">
         <v>30</v>
@@ -8830,7 +8953,7 @@
         <v>7</v>
       </c>
       <c r="G304" t="s">
-        <v>239</v>
+        <v>259</v>
       </c>
       <c r="H304">
         <v>40</v>
@@ -8841,7 +8964,7 @@
         <v>21</v>
       </c>
       <c r="B305" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="C305">
         <v>40</v>
@@ -8856,7 +8979,7 @@
         <v>7</v>
       </c>
       <c r="G305" t="s">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="H305">
         <v>44</v>
@@ -8867,7 +8990,7 @@
         <v>21</v>
       </c>
       <c r="B306" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="C306">
         <v>50</v>
@@ -8882,7 +9005,7 @@
         <v>9.5</v>
       </c>
       <c r="G306" t="s">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="H306">
         <v>53.33333333333334</v>
@@ -8893,7 +9016,7 @@
         <v>21</v>
       </c>
       <c r="B307" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="C307">
         <v>40</v>
@@ -8908,7 +9031,7 @@
         <v>8.5</v>
       </c>
       <c r="G307" t="s">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="H307">
         <v>53.33333333333333</v>
@@ -8919,7 +9042,7 @@
         <v>22</v>
       </c>
       <c r="B308" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="C308">
         <v>70</v>
@@ -8942,7 +9065,7 @@
         <v>22</v>
       </c>
       <c r="B309" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="C309">
         <v>120</v>
@@ -8965,7 +9088,7 @@
         <v>22</v>
       </c>
       <c r="B310" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="C310">
         <v>140</v>
@@ -8988,7 +9111,7 @@
         <v>22</v>
       </c>
       <c r="B311" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="C311">
         <v>140</v>
@@ -9011,7 +9134,7 @@
         <v>22</v>
       </c>
       <c r="B312" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="C312">
         <v>120</v>
@@ -9034,7 +9157,7 @@
         <v>22</v>
       </c>
       <c r="B313" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="C313">
         <v>20</v>
@@ -9057,7 +9180,7 @@
         <v>22</v>
       </c>
       <c r="B314" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="C314">
         <v>40</v>
@@ -9080,7 +9203,7 @@
         <v>22</v>
       </c>
       <c r="B315" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="C315">
         <v>60</v>
@@ -9103,7 +9226,7 @@
         <v>22</v>
       </c>
       <c r="B316" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="C316">
         <v>70</v>
@@ -9126,7 +9249,7 @@
         <v>22</v>
       </c>
       <c r="B317" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="C317">
         <v>80</v>
@@ -9149,7 +9272,7 @@
         <v>22</v>
       </c>
       <c r="B318" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="C318">
         <v>75</v>
@@ -9172,7 +9295,7 @@
         <v>22</v>
       </c>
       <c r="B319" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="C319">
         <v>60</v>
@@ -9195,7 +9318,7 @@
         <v>22</v>
       </c>
       <c r="B320" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="C320">
         <v>60</v>
@@ -9218,7 +9341,7 @@
         <v>22</v>
       </c>
       <c r="B321" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="C321">
         <v>60</v>
@@ -9241,7 +9364,7 @@
         <v>22</v>
       </c>
       <c r="B322" t="s">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="C322">
         <v>65</v>
@@ -9264,7 +9387,7 @@
         <v>22</v>
       </c>
       <c r="B323" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="C323">
         <v>65</v>
@@ -9287,7 +9410,7 @@
         <v>22</v>
       </c>
       <c r="B324" t="s">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="C324">
         <v>65</v>
@@ -9310,7 +9433,7 @@
         <v>22</v>
       </c>
       <c r="B325" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="C325">
         <v>65</v>
@@ -9333,7 +9456,7 @@
         <v>22</v>
       </c>
       <c r="B326" t="s">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="C326">
         <v>65</v>
@@ -9356,7 +9479,7 @@
         <v>22</v>
       </c>
       <c r="B327" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="C327">
         <v>65</v>
@@ -9379,7 +9502,7 @@
         <v>22</v>
       </c>
       <c r="B328" t="s">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="C328">
         <v>65</v>
@@ -9402,7 +9525,7 @@
         <v>22</v>
       </c>
       <c r="B329" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="C329">
         <v>65</v>
@@ -9425,7 +9548,7 @@
         <v>23</v>
       </c>
       <c r="B330" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="C330">
         <v>20</v>
@@ -9440,7 +9563,7 @@
         <v>3</v>
       </c>
       <c r="G330" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="H330">
         <v>25.33333333333333</v>
@@ -9451,7 +9574,7 @@
         <v>23</v>
       </c>
       <c r="B331" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="C331">
         <v>70</v>
@@ -9466,7 +9589,7 @@
         <v>6</v>
       </c>
       <c r="G331" t="s">
-        <v>242</v>
+        <v>262</v>
       </c>
       <c r="H331">
         <v>81.66666666666667</v>
@@ -9477,7 +9600,7 @@
         <v>23</v>
       </c>
       <c r="B332" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="C332">
         <v>90</v>
@@ -9492,7 +9615,7 @@
         <v>6</v>
       </c>
       <c r="G332" t="s">
-        <v>181</v>
+        <v>201</v>
       </c>
       <c r="H332">
         <v>93.00000000000001</v>
@@ -9503,7 +9626,7 @@
         <v>23</v>
       </c>
       <c r="B333" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="C333">
         <v>120</v>
@@ -9518,7 +9641,7 @@
         <v>7.5</v>
       </c>
       <c r="G333" t="s">
-        <v>181</v>
+        <v>201</v>
       </c>
       <c r="H333">
         <v>124</v>
@@ -9529,7 +9652,7 @@
         <v>23</v>
       </c>
       <c r="B334" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="C334">
         <v>140</v>
@@ -9544,7 +9667,7 @@
         <v>10</v>
       </c>
       <c r="G334" t="s">
-        <v>243</v>
+        <v>263</v>
       </c>
       <c r="H334">
         <v>140</v>
@@ -9555,7 +9678,7 @@
         <v>23</v>
       </c>
       <c r="B335" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="C335">
         <v>80</v>
@@ -9570,7 +9693,7 @@
         <v>8.5</v>
       </c>
       <c r="G335" t="s">
-        <v>244</v>
+        <v>264</v>
       </c>
       <c r="H335">
         <v>133.3333333333333</v>
@@ -9581,7 +9704,7 @@
         <v>23</v>
       </c>
       <c r="B336" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="C336">
         <v>80</v>
@@ -9596,7 +9719,7 @@
         <v>10</v>
       </c>
       <c r="G336" t="s">
-        <v>245</v>
+        <v>265</v>
       </c>
       <c r="H336">
         <v>101.3333333333333</v>
@@ -9607,7 +9730,7 @@
         <v>23</v>
       </c>
       <c r="B337" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="C337">
         <v>20</v>
@@ -9622,7 +9745,7 @@
         <v>4</v>
       </c>
       <c r="G337" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="H337">
         <v>25.33333333333333</v>
@@ -9633,7 +9756,7 @@
         <v>23</v>
       </c>
       <c r="B338" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="C338">
         <v>40</v>
@@ -9648,7 +9771,7 @@
         <v>6</v>
       </c>
       <c r="G338" t="s">
-        <v>239</v>
+        <v>259</v>
       </c>
       <c r="H338">
         <v>50.66666666666666</v>
@@ -9659,7 +9782,7 @@
         <v>23</v>
       </c>
       <c r="B339" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="C339">
         <v>60</v>
@@ -9674,7 +9797,7 @@
         <v>7</v>
       </c>
       <c r="G339" t="s">
-        <v>246</v>
+        <v>266</v>
       </c>
       <c r="H339">
         <v>66</v>
@@ -9685,7 +9808,7 @@
         <v>23</v>
       </c>
       <c r="B340" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="C340">
         <v>70</v>
@@ -9700,7 +9823,7 @@
         <v>8.5</v>
       </c>
       <c r="G340" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="H340">
         <v>77</v>
@@ -9711,7 +9834,7 @@
         <v>23</v>
       </c>
       <c r="B341" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="C341">
         <v>75</v>
@@ -9726,7 +9849,7 @@
         <v>8.75</v>
       </c>
       <c r="G341" t="s">
-        <v>247</v>
+        <v>267</v>
       </c>
       <c r="H341">
         <v>77.50000000000001</v>
@@ -9737,7 +9860,7 @@
         <v>23</v>
       </c>
       <c r="B342" t="s">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="C342">
         <v>50</v>
@@ -9752,7 +9875,7 @@
         <v>8</v>
       </c>
       <c r="G342" t="s">
-        <v>248</v>
+        <v>268</v>
       </c>
       <c r="H342">
         <v>66.66666666666666</v>
@@ -9763,7 +9886,7 @@
         <v>23</v>
       </c>
       <c r="B343" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="C343">
         <v>40</v>
@@ -9778,7 +9901,7 @@
         <v>6</v>
       </c>
       <c r="G343" t="s">
-        <v>249</v>
+        <v>269</v>
       </c>
       <c r="H343">
         <v>50.66666666666666</v>
@@ -9789,7 +9912,7 @@
         <v>23</v>
       </c>
       <c r="B344" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="C344">
         <v>50</v>
@@ -9804,7 +9927,7 @@
         <v>6.5</v>
       </c>
       <c r="G344" t="s">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="H344">
         <v>63.33333333333333</v>
@@ -9815,7 +9938,7 @@
         <v>23</v>
       </c>
       <c r="B345" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="C345">
         <v>63</v>
@@ -9830,7 +9953,7 @@
         <v>8</v>
       </c>
       <c r="G345" t="s">
-        <v>251</v>
+        <v>271</v>
       </c>
       <c r="H345">
         <v>75.59999999999999</v>
@@ -9841,7 +9964,7 @@
         <v>23</v>
       </c>
       <c r="B346" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="C346">
         <v>63</v>
@@ -9856,7 +9979,7 @@
         <v>8.5</v>
       </c>
       <c r="G346" t="s">
-        <v>252</v>
+        <v>272</v>
       </c>
       <c r="H346">
         <v>75.59999999999999</v>
@@ -9867,7 +9990,7 @@
         <v>23</v>
       </c>
       <c r="B347" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="C347">
         <v>11</v>
@@ -9882,7 +10005,7 @@
         <v>5</v>
       </c>
       <c r="G347" t="s">
-        <v>156</v>
+        <v>176</v>
       </c>
       <c r="H347">
         <v>16.5</v>
@@ -9893,7 +10016,7 @@
         <v>23</v>
       </c>
       <c r="B348" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="C348">
         <v>32</v>
@@ -9908,7 +10031,7 @@
         <v>5</v>
       </c>
       <c r="G348" t="s">
-        <v>158</v>
+        <v>178</v>
       </c>
       <c r="H348">
         <v>48</v>
@@ -9919,7 +10042,7 @@
         <v>23</v>
       </c>
       <c r="B349" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="C349">
         <v>33</v>
@@ -9934,7 +10057,7 @@
         <v>7</v>
       </c>
       <c r="G349" t="s">
-        <v>157</v>
+        <v>177</v>
       </c>
       <c r="H349">
         <v>49.5</v>
@@ -9945,7 +10068,7 @@
         <v>23</v>
       </c>
       <c r="B350" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="C350">
         <v>59</v>
@@ -9960,7 +10083,7 @@
         <v>8</v>
       </c>
       <c r="G350" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="H350">
         <v>82.59999999999999</v>
@@ -9971,7 +10094,7 @@
         <v>23</v>
       </c>
       <c r="B351" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="C351">
         <v>39</v>
@@ -9986,7 +10109,7 @@
         <v>9</v>
       </c>
       <c r="G351" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
       <c r="H351">
         <v>58.5</v>
@@ -9997,7 +10120,7 @@
         <v>23</v>
       </c>
       <c r="B352" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="C352">
         <v>66</v>
@@ -10012,7 +10135,7 @@
         <v>9</v>
       </c>
       <c r="G352" t="s">
-        <v>185</v>
+        <v>205</v>
       </c>
       <c r="H352">
         <v>92.39999999999999</v>
@@ -10023,7 +10146,7 @@
         <v>24</v>
       </c>
       <c r="B353" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="C353">
         <v>70</v>
@@ -10038,7 +10161,7 @@
         <v>6</v>
       </c>
       <c r="G353" t="s">
-        <v>133</v>
+        <v>153</v>
       </c>
       <c r="H353">
         <v>81.66666666666667</v>
@@ -10049,7 +10172,7 @@
         <v>24</v>
       </c>
       <c r="B354" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="C354">
         <v>120</v>
@@ -10064,7 +10187,7 @@
         <v>6</v>
       </c>
       <c r="G354" t="s">
-        <v>253</v>
+        <v>273</v>
       </c>
       <c r="H354">
         <v>124</v>
@@ -10075,7 +10198,7 @@
         <v>24</v>
       </c>
       <c r="B355" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="C355">
         <v>140</v>
@@ -10090,7 +10213,7 @@
         <v>6.5</v>
       </c>
       <c r="G355" t="s">
-        <v>254</v>
+        <v>274</v>
       </c>
       <c r="H355">
         <v>144.6666666666667</v>
@@ -10101,7 +10224,7 @@
         <v>24</v>
       </c>
       <c r="B356" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="C356">
         <v>160</v>
@@ -10116,7 +10239,7 @@
         <v>8.5</v>
       </c>
       <c r="G356" t="s">
-        <v>142</v>
+        <v>162</v>
       </c>
       <c r="H356">
         <v>165.3333333333333</v>
@@ -10127,7 +10250,7 @@
         <v>24</v>
       </c>
       <c r="B357" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="C357">
         <v>140</v>
@@ -10142,7 +10265,7 @@
         <v>8.5</v>
       </c>
       <c r="G357" t="s">
-        <v>255</v>
+        <v>275</v>
       </c>
       <c r="H357">
         <v>163.3333333333333</v>
@@ -10153,7 +10276,7 @@
         <v>24</v>
       </c>
       <c r="B358" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="C358">
         <v>140</v>
@@ -10168,7 +10291,7 @@
         <v>9</v>
       </c>
       <c r="G358" t="s">
-        <v>256</v>
+        <v>276</v>
       </c>
       <c r="H358">
         <v>163.3333333333333</v>
@@ -10179,7 +10302,7 @@
         <v>24</v>
       </c>
       <c r="B359" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="C359">
         <v>120</v>
@@ -10194,7 +10317,7 @@
         <v>9</v>
       </c>
       <c r="G359" t="s">
-        <v>257</v>
+        <v>277</v>
       </c>
       <c r="H359">
         <v>144</v>
@@ -10205,7 +10328,7 @@
         <v>24</v>
       </c>
       <c r="B360" t="s">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="C360">
         <v>30</v>
@@ -10220,7 +10343,7 @@
         <v>6</v>
       </c>
       <c r="G360" t="s">
-        <v>258</v>
+        <v>278</v>
       </c>
       <c r="H360">
         <v>38</v>
@@ -10231,7 +10354,7 @@
         <v>24</v>
       </c>
       <c r="B361" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="C361">
         <v>40</v>
@@ -10246,7 +10369,7 @@
         <v>7</v>
       </c>
       <c r="G361" t="s">
-        <v>259</v>
+        <v>279</v>
       </c>
       <c r="H361">
         <v>48</v>
@@ -10257,7 +10380,7 @@
         <v>24</v>
       </c>
       <c r="B362" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="C362">
         <v>50</v>
@@ -10272,7 +10395,7 @@
         <v>8</v>
       </c>
       <c r="G362" t="s">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="H362">
         <v>53.33333333333334</v>
@@ -10283,7 +10406,7 @@
         <v>24</v>
       </c>
       <c r="B363" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="C363">
         <v>55</v>
@@ -10298,7 +10421,7 @@
         <v>10</v>
       </c>
       <c r="G363" t="s">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="H363">
         <v>56.83333333333334</v>
@@ -10309,7 +10432,7 @@
         <v>24</v>
       </c>
       <c r="B364" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="C364">
         <v>45</v>
@@ -10324,7 +10447,7 @@
         <v>9</v>
       </c>
       <c r="G364" t="s">
-        <v>262</v>
+        <v>282</v>
       </c>
       <c r="H364">
         <v>52.5</v>
@@ -10335,7 +10458,7 @@
         <v>24</v>
       </c>
       <c r="B365" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="C365">
         <v>45</v>
@@ -10350,7 +10473,7 @@
         <v>9.5</v>
       </c>
       <c r="G365" t="s">
-        <v>263</v>
+        <v>283</v>
       </c>
       <c r="H365">
         <v>52.5</v>
@@ -10361,7 +10484,7 @@
         <v>24</v>
       </c>
       <c r="B366" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="C366">
         <v>45</v>
@@ -10376,7 +10499,7 @@
         <v>7</v>
       </c>
       <c r="G366" t="s">
-        <v>264</v>
+        <v>284</v>
       </c>
       <c r="H366">
         <v>57</v>
@@ -10387,7 +10510,7 @@
         <v>24</v>
       </c>
       <c r="B367" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="C367">
         <v>50</v>
@@ -10402,7 +10525,7 @@
         <v>8</v>
       </c>
       <c r="G367" t="s">
-        <v>265</v>
+        <v>285</v>
       </c>
       <c r="H367">
         <v>63.33333333333333</v>
@@ -10413,7 +10536,7 @@
         <v>24</v>
       </c>
       <c r="B368" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="C368">
         <v>50</v>
@@ -10428,7 +10551,7 @@
         <v>8</v>
       </c>
       <c r="G368" t="s">
-        <v>266</v>
+        <v>286</v>
       </c>
       <c r="H368">
         <v>63.33333333333333</v>
@@ -10439,7 +10562,7 @@
         <v>24</v>
       </c>
       <c r="B369" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="C369">
         <v>50</v>
@@ -10454,7 +10577,7 @@
         <v>8</v>
       </c>
       <c r="G369" t="s">
-        <v>267</v>
+        <v>287</v>
       </c>
       <c r="H369">
         <v>63.33333333333333</v>
@@ -10465,7 +10588,7 @@
         <v>24</v>
       </c>
       <c r="B370" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="C370">
         <v>40</v>
@@ -10480,7 +10603,7 @@
         <v>8.5</v>
       </c>
       <c r="G370" t="s">
-        <v>268</v>
+        <v>288</v>
       </c>
       <c r="H370">
         <v>60</v>
@@ -10491,7 +10614,7 @@
         <v>25</v>
       </c>
       <c r="B371" t="s">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="C371">
         <v>20</v>
@@ -10506,7 +10629,7 @@
         <v>5</v>
       </c>
       <c r="G371" t="s">
-        <v>133</v>
+        <v>153</v>
       </c>
       <c r="H371">
         <v>25.33333333333333</v>
@@ -10517,7 +10640,7 @@
         <v>26</v>
       </c>
       <c r="B372" t="s">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="C372">
         <v>40</v>
@@ -10532,7 +10655,7 @@
         <v>6</v>
       </c>
       <c r="G372" t="s">
-        <v>269</v>
+        <v>289</v>
       </c>
       <c r="H372">
         <v>46.66666666666667</v>
@@ -10543,7 +10666,7 @@
         <v>27</v>
       </c>
       <c r="B373" t="s">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="C373">
         <v>50</v>
@@ -10558,7 +10681,7 @@
         <v>7</v>
       </c>
       <c r="G373" t="s">
-        <v>141</v>
+        <v>161</v>
       </c>
       <c r="H373">
         <v>60</v>
@@ -10569,7 +10692,7 @@
         <v>28</v>
       </c>
       <c r="B374" t="s">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="C374">
         <v>50</v>
@@ -10584,7 +10707,7 @@
         <v>6.5</v>
       </c>
       <c r="G374" t="s">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="H374">
         <v>63.33333333333333</v>
@@ -10595,7 +10718,7 @@
         <v>29</v>
       </c>
       <c r="B375" t="s">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="C375">
         <v>60</v>
@@ -10610,7 +10733,7 @@
         <v>7</v>
       </c>
       <c r="G375" t="s">
-        <v>271</v>
+        <v>291</v>
       </c>
       <c r="H375">
         <v>66</v>
@@ -10621,7 +10744,7 @@
         <v>30</v>
       </c>
       <c r="B376" t="s">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="C376">
         <v>70</v>
@@ -10636,7 +10759,7 @@
         <v>7.75</v>
       </c>
       <c r="G376" t="s">
-        <v>142</v>
+        <v>162</v>
       </c>
       <c r="H376">
         <v>72.33333333333334</v>
@@ -10647,7 +10770,7 @@
         <v>31</v>
       </c>
       <c r="B377" t="s">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="C377">
         <v>75</v>
@@ -10662,7 +10785,7 @@
         <v>8</v>
       </c>
       <c r="G377" t="s">
-        <v>272</v>
+        <v>292</v>
       </c>
       <c r="H377">
         <v>77.50000000000001</v>
@@ -10673,7 +10796,7 @@
         <v>32</v>
       </c>
       <c r="B378" t="s">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="C378">
         <v>77.5</v>
@@ -10688,7 +10811,7 @@
         <v>10</v>
       </c>
       <c r="G378" t="s">
-        <v>273</v>
+        <v>293</v>
       </c>
       <c r="H378">
         <v>77.5</v>
@@ -10699,7 +10822,7 @@
         <v>33</v>
       </c>
       <c r="B379" t="s">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="C379">
         <v>66.25</v>
@@ -10714,7 +10837,7 @@
         <v>9</v>
       </c>
       <c r="G379" t="s">
-        <v>274</v>
+        <v>294</v>
       </c>
       <c r="H379">
         <v>77.29166666666667</v>
@@ -10725,7 +10848,7 @@
         <v>34</v>
       </c>
       <c r="B380" t="s">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="C380">
         <v>60</v>
@@ -10740,7 +10863,7 @@
         <v>8.25</v>
       </c>
       <c r="G380" t="s">
-        <v>275</v>
+        <v>295</v>
       </c>
       <c r="H380">
         <v>70</v>
@@ -10751,7 +10874,7 @@
         <v>35</v>
       </c>
       <c r="B381" t="s">
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="C381">
         <v>30</v>
@@ -10766,7 +10889,7 @@
         <v>6</v>
       </c>
       <c r="G381" t="s">
-        <v>276</v>
+        <v>296</v>
       </c>
       <c r="H381">
         <v>42</v>
@@ -10777,7 +10900,7 @@
         <v>36</v>
       </c>
       <c r="B382" t="s">
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="C382">
         <v>50</v>
@@ -10792,7 +10915,7 @@
         <v>8.5</v>
       </c>
       <c r="G382" t="s">
-        <v>277</v>
+        <v>297</v>
       </c>
       <c r="H382">
         <v>63.33333333333333</v>
@@ -10803,7 +10926,7 @@
         <v>37</v>
       </c>
       <c r="B383" t="s">
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="C383">
         <v>50</v>
@@ -10818,7 +10941,7 @@
         <v>8</v>
       </c>
       <c r="G383" t="s">
-        <v>278</v>
+        <v>298</v>
       </c>
       <c r="H383">
         <v>63.33333333333333</v>
@@ -10829,7 +10952,7 @@
         <v>38</v>
       </c>
       <c r="B384" t="s">
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="C384">
         <v>50</v>
@@ -10844,7 +10967,7 @@
         <v>10</v>
       </c>
       <c r="G384" t="s">
-        <v>279</v>
+        <v>299</v>
       </c>
       <c r="H384">
         <v>60</v>
@@ -10855,7 +10978,7 @@
         <v>39</v>
       </c>
       <c r="B385" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="C385">
         <v>0</v>
@@ -10870,7 +10993,7 @@
         <v>6</v>
       </c>
       <c r="G385" t="s">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="H385">
         <v>0</v>
@@ -10881,7 +11004,7 @@
         <v>40</v>
       </c>
       <c r="B386" t="s">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="C386">
         <v>25</v>
@@ -10896,7 +11019,7 @@
         <v>8</v>
       </c>
       <c r="G386" t="s">
-        <v>281</v>
+        <v>301</v>
       </c>
       <c r="H386">
         <v>30</v>
@@ -10907,7 +11030,7 @@
         <v>41</v>
       </c>
       <c r="B387" t="s">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="C387">
         <v>25</v>
@@ -10922,7 +11045,7 @@
         <v>8</v>
       </c>
       <c r="G387" t="s">
-        <v>282</v>
+        <v>302</v>
       </c>
       <c r="H387">
         <v>31.66666666666666</v>
@@ -10933,7 +11056,7 @@
         <v>42</v>
       </c>
       <c r="B388" t="s">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="C388">
         <v>25</v>
@@ -10948,7 +11071,7 @@
         <v>8.5</v>
       </c>
       <c r="G388" t="s">
-        <v>283</v>
+        <v>303</v>
       </c>
       <c r="H388">
         <v>31.66666666666666</v>
@@ -10959,7 +11082,7 @@
         <v>43</v>
       </c>
       <c r="B389" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="C389">
         <v>45</v>
@@ -10974,7 +11097,7 @@
         <v>6.5</v>
       </c>
       <c r="G389" t="s">
-        <v>284</v>
+        <v>304</v>
       </c>
       <c r="H389">
         <v>62.99999999999999</v>
@@ -10985,7 +11108,7 @@
         <v>44</v>
       </c>
       <c r="B390" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="C390">
         <v>60</v>
@@ -11000,7 +11123,7 @@
         <v>8</v>
       </c>
       <c r="G390" t="s">
-        <v>285</v>
+        <v>305</v>
       </c>
       <c r="H390">
         <v>76</v>
@@ -11011,7 +11134,7 @@
         <v>45</v>
       </c>
       <c r="B391" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="C391">
         <v>60</v>
@@ -11026,7 +11149,7 @@
         <v>7.5</v>
       </c>
       <c r="G391" t="s">
-        <v>286</v>
+        <v>306</v>
       </c>
       <c r="H391">
         <v>76</v>
@@ -11037,7 +11160,7 @@
         <v>46</v>
       </c>
       <c r="B392" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="C392">
         <v>60</v>
@@ -11052,7 +11175,7 @@
         <v>7.5</v>
       </c>
       <c r="G392" t="s">
-        <v>287</v>
+        <v>307</v>
       </c>
       <c r="H392">
         <v>76</v>
@@ -11063,7 +11186,7 @@
         <v>47</v>
       </c>
       <c r="B393" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="C393">
         <v>60</v>
@@ -11078,7 +11201,7 @@
         <v>9</v>
       </c>
       <c r="G393" t="s">
-        <v>288</v>
+        <v>308</v>
       </c>
       <c r="H393">
         <v>76</v>
@@ -11089,7 +11212,7 @@
         <v>48</v>
       </c>
       <c r="B394" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="C394">
         <v>40</v>
@@ -11104,7 +11227,7 @@
         <v>8</v>
       </c>
       <c r="G394" t="s">
-        <v>289</v>
+        <v>309</v>
       </c>
       <c r="H394">
         <v>53.33333333333333</v>
@@ -11115,7 +11238,7 @@
         <v>49</v>
       </c>
       <c r="B395" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="C395">
         <v>40</v>
@@ -11130,7 +11253,7 @@
         <v>7.5</v>
       </c>
       <c r="G395" t="s">
-        <v>290</v>
+        <v>310</v>
       </c>
       <c r="H395">
         <v>56</v>
@@ -11141,7 +11264,7 @@
         <v>50</v>
       </c>
       <c r="B396" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="C396">
         <v>40</v>
@@ -11156,7 +11279,7 @@
         <v>8</v>
       </c>
       <c r="G396" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="H396">
         <v>56</v>
@@ -11167,7 +11290,7 @@
         <v>51</v>
       </c>
       <c r="B397" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="C397">
         <v>40</v>
@@ -11182,7 +11305,7 @@
         <v>8</v>
       </c>
       <c r="G397" t="s">
-        <v>292</v>
+        <v>312</v>
       </c>
       <c r="H397">
         <v>56</v>
@@ -11193,7 +11316,7 @@
         <v>52</v>
       </c>
       <c r="B398" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="C398">
         <v>40</v>
@@ -11208,7 +11331,7 @@
         <v>8.5</v>
       </c>
       <c r="G398" t="s">
-        <v>293</v>
+        <v>313</v>
       </c>
       <c r="H398">
         <v>56</v>
@@ -11219,7 +11342,7 @@
         <v>53</v>
       </c>
       <c r="B399" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="C399">
         <v>40</v>
@@ -11234,10 +11357,556 @@
         <v>9</v>
       </c>
       <c r="G399" t="s">
-        <v>294</v>
+        <v>314</v>
       </c>
       <c r="H399">
         <v>56</v>
+      </c>
+    </row>
+    <row r="400" spans="1:8">
+      <c r="A400" t="s">
+        <v>54</v>
+      </c>
+      <c r="B400" t="s">
+        <v>102</v>
+      </c>
+      <c r="C400">
+        <v>20</v>
+      </c>
+      <c r="D400">
+        <v>8</v>
+      </c>
+      <c r="E400">
+        <v>160</v>
+      </c>
+      <c r="F400">
+        <v>5</v>
+      </c>
+      <c r="G400" t="s">
+        <v>315</v>
+      </c>
+      <c r="H400">
+        <v>25.33333333333333</v>
+      </c>
+    </row>
+    <row r="401" spans="1:8">
+      <c r="A401" t="s">
+        <v>55</v>
+      </c>
+      <c r="B401" t="s">
+        <v>102</v>
+      </c>
+      <c r="C401">
+        <v>70</v>
+      </c>
+      <c r="D401">
+        <v>5</v>
+      </c>
+      <c r="E401">
+        <v>350</v>
+      </c>
+      <c r="F401">
+        <v>6</v>
+      </c>
+      <c r="G401" t="s">
+        <v>316</v>
+      </c>
+      <c r="H401">
+        <v>81.66666666666667</v>
+      </c>
+    </row>
+    <row r="402" spans="1:8">
+      <c r="A402" t="s">
+        <v>56</v>
+      </c>
+      <c r="B402" t="s">
+        <v>102</v>
+      </c>
+      <c r="C402">
+        <v>120</v>
+      </c>
+      <c r="D402">
+        <v>1</v>
+      </c>
+      <c r="E402">
+        <v>120</v>
+      </c>
+      <c r="F402">
+        <v>7.5</v>
+      </c>
+      <c r="G402" t="s">
+        <v>317</v>
+      </c>
+      <c r="H402">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="403" spans="1:8">
+      <c r="A403" t="s">
+        <v>57</v>
+      </c>
+      <c r="B403" t="s">
+        <v>102</v>
+      </c>
+      <c r="C403">
+        <v>110</v>
+      </c>
+      <c r="D403">
+        <v>5</v>
+      </c>
+      <c r="E403">
+        <v>550</v>
+      </c>
+      <c r="F403">
+        <v>8.5</v>
+      </c>
+      <c r="G403" t="s">
+        <v>318</v>
+      </c>
+      <c r="H403">
+        <v>128.3333333333333</v>
+      </c>
+    </row>
+    <row r="404" spans="1:8">
+      <c r="A404" t="s">
+        <v>58</v>
+      </c>
+      <c r="B404" t="s">
+        <v>102</v>
+      </c>
+      <c r="C404">
+        <v>110</v>
+      </c>
+      <c r="D404">
+        <v>4</v>
+      </c>
+      <c r="E404">
+        <v>440</v>
+      </c>
+      <c r="F404">
+        <v>10</v>
+      </c>
+      <c r="G404" t="s">
+        <v>319</v>
+      </c>
+      <c r="H404">
+        <v>124.6666666666667</v>
+      </c>
+    </row>
+    <row r="405" spans="1:8">
+      <c r="A405" t="s">
+        <v>59</v>
+      </c>
+      <c r="B405" t="s">
+        <v>102</v>
+      </c>
+      <c r="C405">
+        <v>100</v>
+      </c>
+      <c r="D405">
+        <v>3</v>
+      </c>
+      <c r="E405">
+        <v>300</v>
+      </c>
+      <c r="F405">
+        <v>9.5</v>
+      </c>
+      <c r="G405" t="s">
+        <v>320</v>
+      </c>
+      <c r="H405">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="406" spans="1:8">
+      <c r="A406" t="s">
+        <v>60</v>
+      </c>
+      <c r="B406" t="s">
+        <v>121</v>
+      </c>
+      <c r="C406">
+        <v>40</v>
+      </c>
+      <c r="D406">
+        <v>15</v>
+      </c>
+      <c r="E406">
+        <v>600</v>
+      </c>
+      <c r="F406">
+        <v>6</v>
+      </c>
+      <c r="G406" t="s">
+        <v>321</v>
+      </c>
+      <c r="H406">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="407" spans="1:8">
+      <c r="A407" t="s">
+        <v>61</v>
+      </c>
+      <c r="B407" t="s">
+        <v>121</v>
+      </c>
+      <c r="C407">
+        <v>50</v>
+      </c>
+      <c r="D407">
+        <v>12</v>
+      </c>
+      <c r="E407">
+        <v>600</v>
+      </c>
+      <c r="F407">
+        <v>7</v>
+      </c>
+      <c r="G407" t="s">
+        <v>322</v>
+      </c>
+      <c r="H407">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="408" spans="1:8">
+      <c r="A408" t="s">
+        <v>62</v>
+      </c>
+      <c r="B408" t="s">
+        <v>121</v>
+      </c>
+      <c r="C408">
+        <v>50</v>
+      </c>
+      <c r="D408">
+        <v>12</v>
+      </c>
+      <c r="E408">
+        <v>600</v>
+      </c>
+      <c r="F408">
+        <v>7.5</v>
+      </c>
+      <c r="G408" t="s">
+        <v>323</v>
+      </c>
+      <c r="H408">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="409" spans="1:8">
+      <c r="A409" t="s">
+        <v>63</v>
+      </c>
+      <c r="B409" t="s">
+        <v>121</v>
+      </c>
+      <c r="C409">
+        <v>50</v>
+      </c>
+      <c r="D409">
+        <v>12</v>
+      </c>
+      <c r="E409">
+        <v>600</v>
+      </c>
+      <c r="F409">
+        <v>8.5</v>
+      </c>
+      <c r="G409" t="s">
+        <v>324</v>
+      </c>
+      <c r="H409">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="410" spans="1:8">
+      <c r="A410" t="s">
+        <v>64</v>
+      </c>
+      <c r="B410" t="s">
+        <v>101</v>
+      </c>
+      <c r="C410">
+        <v>30</v>
+      </c>
+      <c r="D410">
+        <v>10</v>
+      </c>
+      <c r="E410">
+        <v>300</v>
+      </c>
+      <c r="F410">
+        <v>6</v>
+      </c>
+      <c r="G410" t="s">
+        <v>325</v>
+      </c>
+      <c r="H410">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="411" spans="1:8">
+      <c r="A411" t="s">
+        <v>65</v>
+      </c>
+      <c r="B411" t="s">
+        <v>73</v>
+      </c>
+      <c r="C411">
+        <v>30</v>
+      </c>
+      <c r="D411">
+        <v>10</v>
+      </c>
+      <c r="E411">
+        <v>300</v>
+      </c>
+      <c r="F411">
+        <v>6.5</v>
+      </c>
+      <c r="G411" t="s">
+        <v>326</v>
+      </c>
+      <c r="H411">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="412" spans="1:8">
+      <c r="A412" t="s">
+        <v>66</v>
+      </c>
+      <c r="B412" t="s">
+        <v>73</v>
+      </c>
+      <c r="C412">
+        <v>40</v>
+      </c>
+      <c r="D412">
+        <v>10</v>
+      </c>
+      <c r="E412">
+        <v>400</v>
+      </c>
+      <c r="F412">
+        <v>8.5</v>
+      </c>
+      <c r="G412" t="s">
+        <v>327</v>
+      </c>
+      <c r="H412">
+        <v>53.33333333333333</v>
+      </c>
+    </row>
+    <row r="413" spans="1:8">
+      <c r="A413" t="s">
+        <v>67</v>
+      </c>
+      <c r="B413" t="s">
+        <v>73</v>
+      </c>
+      <c r="C413">
+        <v>40</v>
+      </c>
+      <c r="D413">
+        <v>8</v>
+      </c>
+      <c r="E413">
+        <v>320</v>
+      </c>
+      <c r="F413">
+        <v>10</v>
+      </c>
+      <c r="G413" t="s">
+        <v>328</v>
+      </c>
+      <c r="H413">
+        <v>50.66666666666666</v>
+      </c>
+    </row>
+    <row r="414" spans="1:8">
+      <c r="A414" t="s">
+        <v>68</v>
+      </c>
+      <c r="B414" t="s">
+        <v>73</v>
+      </c>
+      <c r="C414">
+        <v>40</v>
+      </c>
+      <c r="D414">
+        <v>8</v>
+      </c>
+      <c r="E414">
+        <v>320</v>
+      </c>
+      <c r="F414">
+        <v>9</v>
+      </c>
+      <c r="G414" t="s">
+        <v>329</v>
+      </c>
+      <c r="H414">
+        <v>50.66666666666666</v>
+      </c>
+    </row>
+    <row r="415" spans="1:8">
+      <c r="A415" t="s">
+        <v>69</v>
+      </c>
+      <c r="B415" t="s">
+        <v>133</v>
+      </c>
+      <c r="C415">
+        <v>30</v>
+      </c>
+      <c r="D415">
+        <v>5</v>
+      </c>
+      <c r="E415">
+        <v>150</v>
+      </c>
+      <c r="F415">
+        <v>8</v>
+      </c>
+      <c r="G415" t="s">
+        <v>330</v>
+      </c>
+      <c r="H415">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="416" spans="1:8">
+      <c r="A416" t="s">
+        <v>69</v>
+      </c>
+      <c r="B416" t="s">
+        <v>134</v>
+      </c>
+      <c r="C416">
+        <v>30</v>
+      </c>
+      <c r="D416">
+        <v>12</v>
+      </c>
+      <c r="E416">
+        <v>360</v>
+      </c>
+      <c r="F416">
+        <v>8</v>
+      </c>
+      <c r="G416" t="s">
+        <v>331</v>
+      </c>
+      <c r="H416">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="417" spans="1:8">
+      <c r="A417" t="s">
+        <v>70</v>
+      </c>
+      <c r="B417" t="s">
+        <v>133</v>
+      </c>
+      <c r="C417">
+        <v>30</v>
+      </c>
+      <c r="D417">
+        <v>6</v>
+      </c>
+      <c r="E417">
+        <v>180</v>
+      </c>
+      <c r="F417">
+        <v>8.5</v>
+      </c>
+      <c r="G417" t="s">
+        <v>332</v>
+      </c>
+      <c r="H417">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="418" spans="1:8">
+      <c r="A418" t="s">
+        <v>70</v>
+      </c>
+      <c r="B418" t="s">
+        <v>134</v>
+      </c>
+      <c r="C418">
+        <v>30</v>
+      </c>
+      <c r="D418">
+        <v>12</v>
+      </c>
+      <c r="E418">
+        <v>360</v>
+      </c>
+      <c r="F418">
+        <v>8.5</v>
+      </c>
+      <c r="G418" t="s">
+        <v>333</v>
+      </c>
+      <c r="H418">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="419" spans="1:8">
+      <c r="A419" t="s">
+        <v>71</v>
+      </c>
+      <c r="B419" t="s">
+        <v>133</v>
+      </c>
+      <c r="C419">
+        <v>30</v>
+      </c>
+      <c r="D419">
+        <v>6</v>
+      </c>
+      <c r="E419">
+        <v>180</v>
+      </c>
+      <c r="F419">
+        <v>9</v>
+      </c>
+      <c r="G419" t="s">
+        <v>334</v>
+      </c>
+      <c r="H419">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="420" spans="1:8">
+      <c r="A420" t="s">
+        <v>71</v>
+      </c>
+      <c r="B420" t="s">
+        <v>134</v>
+      </c>
+      <c r="C420">
+        <v>30</v>
+      </c>
+      <c r="D420">
+        <v>12</v>
+      </c>
+      <c r="E420">
+        <v>360</v>
+      </c>
+      <c r="F420">
+        <v>9</v>
+      </c>
+      <c r="G420" t="s">
+        <v>335</v>
+      </c>
+      <c r="H420">
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/data/workout_log.xlsx
+++ b/data/workout_log.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1134" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1204" uniqueCount="359">
   <si>
     <t>Timestamp</t>
   </si>
@@ -40,6 +40,9 @@
     <t>e1RM</t>
   </si>
   <si>
+    <t>RPE</t>
+  </si>
+  <si>
     <t>2026-01-25 10:00:00</t>
   </si>
   <si>
@@ -232,6 +235,9 @@
     <t>2026-03-08 17:55:00</t>
   </si>
   <si>
+    <t>2026-03-11 19:15:00</t>
+  </si>
+  <si>
     <t>Overhead Press</t>
   </si>
   <si>
@@ -421,6 +427,9 @@
     <t>EZ Bar Skullcrusher</t>
   </si>
   <si>
+    <t>Skullcrusher</t>
+  </si>
+  <si>
     <t>Warm-up. Run: 2.75km in 12:30 prior.</t>
   </si>
   <si>
@@ -1022,6 +1031,66 @@
   </si>
   <si>
     <t>Superset 3B</t>
+  </si>
+  <si>
+    <t>Warm-up set</t>
+  </si>
+  <si>
+    <t>Ramping up</t>
+  </si>
+  <si>
+    <t>Heavy triple; testing bracing</t>
+  </si>
+  <si>
+    <t>High-volume endurance set; target milestone</t>
+  </si>
+  <si>
+    <t>Front-loaded stability</t>
+  </si>
+  <si>
+    <t>Vertical bar path focus</t>
+  </si>
+  <si>
+    <t>Volume at intensity</t>
+  </si>
+  <si>
+    <t>High fatigue accumulation</t>
+  </si>
+  <si>
+    <t>Final press set</t>
+  </si>
+  <si>
+    <t>Horizontal pull</t>
+  </si>
+  <si>
+    <t>Controlled pull</t>
+  </si>
+  <si>
+    <t>Strict mechanics</t>
+  </si>
+  <si>
+    <t>Repeat set</t>
+  </si>
+  <si>
+    <t>Fatigue manifesting</t>
+  </si>
+  <si>
+    <t>Rowing volume accumulation</t>
+  </si>
+  <si>
+    <t>Controlled eccentric</t>
+  </si>
+  <si>
+    <t>Stopped; tendon soreness</t>
+  </si>
+  <si>
+    <t>Triceps stretch</t>
+  </si>
+  <si>
+    <t>Stability focus</t>
+  </si>
+  <si>
+    <t>Final set of session</t>
   </si>
 </sst>
 </file>
@@ -1379,10 +1448,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H420"/>
+  <dimension ref="A1:I443"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1407,13 +1476,16 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C2">
         <v>30</v>
@@ -1428,18 +1500,18 @@
         <v>4</v>
       </c>
       <c r="G2" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="H2">
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C3">
         <v>30</v>
@@ -1457,12 +1529,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C4">
         <v>30</v>
@@ -1480,12 +1552,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C5">
         <v>30</v>
@@ -1503,12 +1575,12 @@
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C6">
         <v>60</v>
@@ -1523,18 +1595,18 @@
         <v>5</v>
       </c>
       <c r="G6" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="H6">
         <v>76</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C7">
         <v>100</v>
@@ -1549,18 +1621,18 @@
         <v>6</v>
       </c>
       <c r="G7" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="H7">
         <v>110</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C8">
         <v>100</v>
@@ -1578,12 +1650,12 @@
         <v>110</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C9">
         <v>100</v>
@@ -1601,12 +1673,12 @@
         <v>110</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C10">
         <v>32</v>
@@ -1621,18 +1693,18 @@
         <v>3</v>
       </c>
       <c r="G10" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="H10">
         <v>44.8</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C11">
         <v>40</v>
@@ -1647,18 +1719,18 @@
         <v>5.5</v>
       </c>
       <c r="G11" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="H11">
         <v>50.66666666666666</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C12">
         <v>40</v>
@@ -1676,12 +1748,12 @@
         <v>50.66666666666666</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C13">
         <v>40</v>
@@ -1696,18 +1768,18 @@
         <v>9</v>
       </c>
       <c r="G13" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="H13">
         <v>48</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B14" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C14">
         <v>20</v>
@@ -1725,12 +1797,12 @@
         <v>26.66666666666666</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B15" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C15">
         <v>20</v>
@@ -1748,12 +1820,12 @@
         <v>26.66666666666666</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B16" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C16">
         <v>20</v>
@@ -1773,10 +1845,10 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B17" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C17">
         <v>20</v>
@@ -1791,7 +1863,7 @@
         <v>8</v>
       </c>
       <c r="G17" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="H17">
         <v>26.66666666666666</v>
@@ -1799,10 +1871,10 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B18" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C18">
         <v>20</v>
@@ -1817,7 +1889,7 @@
         <v>8</v>
       </c>
       <c r="G18" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="H18">
         <v>26.66666666666666</v>
@@ -1825,10 +1897,10 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B19" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C19">
         <v>20</v>
@@ -1843,7 +1915,7 @@
         <v>8</v>
       </c>
       <c r="G19" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="H19">
         <v>25.33333333333333</v>
@@ -1851,10 +1923,10 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B20" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C20">
         <v>20</v>
@@ -1869,7 +1941,7 @@
         <v>8</v>
       </c>
       <c r="G20" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="H20">
         <v>25.33333333333333</v>
@@ -1877,10 +1949,10 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B21" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -1895,7 +1967,7 @@
         <v>7</v>
       </c>
       <c r="G21" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="H21">
         <v>0</v>
@@ -1903,10 +1975,10 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B22" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C22">
         <v>30</v>
@@ -1926,10 +1998,10 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B23" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C23">
         <v>30</v>
@@ -1949,10 +2021,10 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B24" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C24">
         <v>30</v>
@@ -1972,10 +2044,10 @@
     </row>
     <row r="25" spans="1:8">
       <c r="A25" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B25" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C25">
         <v>30</v>
@@ -1995,10 +2067,10 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B26" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C26">
         <v>30</v>
@@ -2018,10 +2090,10 @@
     </row>
     <row r="27" spans="1:8">
       <c r="A27" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B27" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C27">
         <v>30</v>
@@ -2041,10 +2113,10 @@
     </row>
     <row r="28" spans="1:8">
       <c r="A28" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B28" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C28">
         <v>30</v>
@@ -2064,10 +2136,10 @@
     </row>
     <row r="29" spans="1:8">
       <c r="A29" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B29" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C29">
         <v>30</v>
@@ -2087,10 +2159,10 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B30" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C30">
         <v>30</v>
@@ -2110,10 +2182,10 @@
     </row>
     <row r="31" spans="1:8">
       <c r="A31" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B31" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C31">
         <v>70</v>
@@ -2133,10 +2205,10 @@
     </row>
     <row r="32" spans="1:8">
       <c r="A32" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B32" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C32">
         <v>70</v>
@@ -2156,10 +2228,10 @@
     </row>
     <row r="33" spans="1:8">
       <c r="A33" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B33" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C33">
         <v>70</v>
@@ -2179,10 +2251,10 @@
     </row>
     <row r="34" spans="1:8">
       <c r="A34" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B34" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C34">
         <v>23</v>
@@ -2197,7 +2269,7 @@
         <v>7</v>
       </c>
       <c r="G34" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="H34">
         <v>38.33333333333333</v>
@@ -2205,10 +2277,10 @@
     </row>
     <row r="35" spans="1:8">
       <c r="A35" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B35" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C35">
         <v>23</v>
@@ -2223,7 +2295,7 @@
         <v>7</v>
       </c>
       <c r="G35" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="H35">
         <v>38.33333333333333</v>
@@ -2231,10 +2303,10 @@
     </row>
     <row r="36" spans="1:8">
       <c r="A36" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B36" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C36">
         <v>23</v>
@@ -2249,7 +2321,7 @@
         <v>9</v>
       </c>
       <c r="G36" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="H36">
         <v>38.33333333333333</v>
@@ -2257,10 +2329,10 @@
     </row>
     <row r="37" spans="1:8">
       <c r="A37" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B37" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C37">
         <v>23</v>
@@ -2275,7 +2347,7 @@
         <v>10</v>
       </c>
       <c r="G37" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="H37">
         <v>32.2</v>
@@ -2283,10 +2355,10 @@
     </row>
     <row r="38" spans="1:8">
       <c r="A38" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B38" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C38">
         <v>20</v>
@@ -2306,10 +2378,10 @@
     </row>
     <row r="39" spans="1:8">
       <c r="A39" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B39" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C39">
         <v>20</v>
@@ -2329,10 +2401,10 @@
     </row>
     <row r="40" spans="1:8">
       <c r="A40" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B40" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C40">
         <v>20</v>
@@ -2352,10 +2424,10 @@
     </row>
     <row r="41" spans="1:8">
       <c r="A41" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B41" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C41">
         <v>36</v>
@@ -2370,7 +2442,7 @@
         <v>5</v>
       </c>
       <c r="G41" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="H41">
         <v>48</v>
@@ -2378,10 +2450,10 @@
     </row>
     <row r="42" spans="1:8">
       <c r="A42" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B42" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C42">
         <v>44</v>
@@ -2396,7 +2468,7 @@
         <v>7</v>
       </c>
       <c r="G42" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="H42">
         <v>52.8</v>
@@ -2404,10 +2476,10 @@
     </row>
     <row r="43" spans="1:8">
       <c r="A43" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B43" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C43">
         <v>44</v>
@@ -2422,7 +2494,7 @@
         <v>7.5</v>
       </c>
       <c r="G43" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="H43">
         <v>52.8</v>
@@ -2430,10 +2502,10 @@
     </row>
     <row r="44" spans="1:8">
       <c r="A44" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B44" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C44">
         <v>44</v>
@@ -2448,7 +2520,7 @@
         <v>8</v>
       </c>
       <c r="G44" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="H44">
         <v>52.8</v>
@@ -2456,10 +2528,10 @@
     </row>
     <row r="45" spans="1:8">
       <c r="A45" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B45" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C45">
         <v>60</v>
@@ -2479,10 +2551,10 @@
     </row>
     <row r="46" spans="1:8">
       <c r="A46" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B46" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C46">
         <v>100</v>
@@ -2502,10 +2574,10 @@
     </row>
     <row r="47" spans="1:8">
       <c r="A47" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B47" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C47">
         <v>130</v>
@@ -2525,10 +2597,10 @@
     </row>
     <row r="48" spans="1:8">
       <c r="A48" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B48" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C48">
         <v>140</v>
@@ -2543,7 +2615,7 @@
         <v>10</v>
       </c>
       <c r="G48" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="H48">
         <v>144.6666666666667</v>
@@ -2551,10 +2623,10 @@
     </row>
     <row r="49" spans="1:8">
       <c r="A49" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B49" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C49">
         <v>130</v>
@@ -2574,10 +2646,10 @@
     </row>
     <row r="50" spans="1:8">
       <c r="A50" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B50" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C50">
         <v>100</v>
@@ -2597,10 +2669,10 @@
     </row>
     <row r="51" spans="1:8">
       <c r="A51" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B51" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C51">
         <v>100</v>
@@ -2615,7 +2687,7 @@
         <v>9</v>
       </c>
       <c r="G51" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="H51">
         <v>133.3333333333333</v>
@@ -2623,10 +2695,10 @@
     </row>
     <row r="52" spans="1:8">
       <c r="A52" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B52" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C52">
         <v>20</v>
@@ -2641,7 +2713,7 @@
         <v>8</v>
       </c>
       <c r="G52" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="H52">
         <v>26.66666666666666</v>
@@ -2649,10 +2721,10 @@
     </row>
     <row r="53" spans="1:8">
       <c r="A53" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B53" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C53">
         <v>20</v>
@@ -2667,7 +2739,7 @@
         <v>9</v>
       </c>
       <c r="G53" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="H53">
         <v>26.66666666666666</v>
@@ -2675,10 +2747,10 @@
     </row>
     <row r="54" spans="1:8">
       <c r="A54" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B54" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C54">
         <v>30</v>
@@ -2698,10 +2770,10 @@
     </row>
     <row r="55" spans="1:8">
       <c r="A55" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B55" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C55">
         <v>40</v>
@@ -2721,10 +2793,10 @@
     </row>
     <row r="56" spans="1:8">
       <c r="A56" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B56" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C56">
         <v>40</v>
@@ -2744,10 +2816,10 @@
     </row>
     <row r="57" spans="1:8">
       <c r="A57" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B57" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C57">
         <v>40</v>
@@ -2767,10 +2839,10 @@
     </row>
     <row r="58" spans="1:8">
       <c r="A58" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B58" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C58">
         <v>45</v>
@@ -2790,10 +2862,10 @@
     </row>
     <row r="59" spans="1:8">
       <c r="A59" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B59" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C59">
         <v>45</v>
@@ -2813,10 +2885,10 @@
     </row>
     <row r="60" spans="1:8">
       <c r="A60" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B60" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C60">
         <v>50</v>
@@ -2831,7 +2903,7 @@
         <v>7.5</v>
       </c>
       <c r="G60" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="H60">
         <v>63.33333333333333</v>
@@ -2839,10 +2911,10 @@
     </row>
     <row r="61" spans="1:8">
       <c r="A61" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B61" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C61">
         <v>50</v>
@@ -2857,7 +2929,7 @@
         <v>7.5</v>
       </c>
       <c r="G61" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="H61">
         <v>63.33333333333333</v>
@@ -2865,10 +2937,10 @@
     </row>
     <row r="62" spans="1:8">
       <c r="A62" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B62" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C62">
         <v>50</v>
@@ -2883,7 +2955,7 @@
         <v>8.5</v>
       </c>
       <c r="G62" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="H62">
         <v>63.33333333333333</v>
@@ -2891,10 +2963,10 @@
     </row>
     <row r="63" spans="1:8">
       <c r="A63" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B63" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C63">
         <v>50</v>
@@ -2909,7 +2981,7 @@
         <v>8.5</v>
       </c>
       <c r="G63" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="H63">
         <v>63.33333333333333</v>
@@ -2917,10 +2989,10 @@
     </row>
     <row r="64" spans="1:8">
       <c r="A64" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B64" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C64">
         <v>50</v>
@@ -2935,7 +3007,7 @@
         <v>9</v>
       </c>
       <c r="G64" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="H64">
         <v>63.33333333333333</v>
@@ -2943,10 +3015,10 @@
     </row>
     <row r="65" spans="1:8">
       <c r="A65" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B65" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C65">
         <v>50</v>
@@ -2961,7 +3033,7 @@
         <v>9</v>
       </c>
       <c r="G65" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="H65">
         <v>63.33333333333333</v>
@@ -2969,10 +3041,10 @@
     </row>
     <row r="66" spans="1:8">
       <c r="A66" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B66" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C66">
         <v>60</v>
@@ -2992,10 +3064,10 @@
     </row>
     <row r="67" spans="1:8">
       <c r="A67" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B67" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C67">
         <v>100</v>
@@ -3015,10 +3087,10 @@
     </row>
     <row r="68" spans="1:8">
       <c r="A68" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B68" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C68">
         <v>100</v>
@@ -3038,10 +3110,10 @@
     </row>
     <row r="69" spans="1:8">
       <c r="A69" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B69" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C69">
         <v>60</v>
@@ -3061,10 +3133,10 @@
     </row>
     <row r="70" spans="1:8">
       <c r="A70" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B70" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C70">
         <v>100</v>
@@ -3084,10 +3156,10 @@
     </row>
     <row r="71" spans="1:8">
       <c r="A71" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B71" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C71">
         <v>80</v>
@@ -3107,10 +3179,10 @@
     </row>
     <row r="72" spans="1:8">
       <c r="A72" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B72" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C72">
         <v>80</v>
@@ -3130,10 +3202,10 @@
     </row>
     <row r="73" spans="1:8">
       <c r="A73" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B73" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C73">
         <v>20</v>
@@ -3153,10 +3225,10 @@
     </row>
     <row r="74" spans="1:8">
       <c r="A74" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B74" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C74">
         <v>30</v>
@@ -3176,10 +3248,10 @@
     </row>
     <row r="75" spans="1:8">
       <c r="A75" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B75" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C75">
         <v>35</v>
@@ -3199,10 +3271,10 @@
     </row>
     <row r="76" spans="1:8">
       <c r="A76" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B76" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C76">
         <v>35</v>
@@ -3217,7 +3289,7 @@
         <v>10</v>
       </c>
       <c r="G76" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="H76">
         <v>43.16666666666667</v>
@@ -3225,10 +3297,10 @@
     </row>
     <row r="77" spans="1:8">
       <c r="A77" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B77" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C77">
         <v>30</v>
@@ -3248,10 +3320,10 @@
     </row>
     <row r="78" spans="1:8">
       <c r="A78" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B78" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C78">
         <v>30</v>
@@ -3271,10 +3343,10 @@
     </row>
     <row r="79" spans="1:8">
       <c r="A79" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B79" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C79">
         <v>50</v>
@@ -3294,10 +3366,10 @@
     </row>
     <row r="80" spans="1:8">
       <c r="A80" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B80" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C80">
         <v>40</v>
@@ -3317,10 +3389,10 @@
     </row>
     <row r="81" spans="1:8">
       <c r="A81" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B81" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C81">
         <v>22</v>
@@ -3340,10 +3412,10 @@
     </row>
     <row r="82" spans="1:8">
       <c r="A82" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B82" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C82">
         <v>22</v>
@@ -3363,10 +3435,10 @@
     </row>
     <row r="83" spans="1:8">
       <c r="A83" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B83" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C83">
         <v>22</v>
@@ -3386,10 +3458,10 @@
     </row>
     <row r="84" spans="1:8">
       <c r="A84" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B84" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C84">
         <v>20</v>
@@ -3404,7 +3476,7 @@
         <v>4</v>
       </c>
       <c r="G84" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="H84">
         <v>28</v>
@@ -3412,10 +3484,10 @@
     </row>
     <row r="85" spans="1:8">
       <c r="A85" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B85" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C85">
         <v>40</v>
@@ -3435,10 +3507,10 @@
     </row>
     <row r="86" spans="1:8">
       <c r="A86" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B86" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C86">
         <v>50</v>
@@ -3458,10 +3530,10 @@
     </row>
     <row r="87" spans="1:8">
       <c r="A87" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B87" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C87">
         <v>60</v>
@@ -3481,10 +3553,10 @@
     </row>
     <row r="88" spans="1:8">
       <c r="A88" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B88" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C88">
         <v>60</v>
@@ -3504,10 +3576,10 @@
     </row>
     <row r="89" spans="1:8">
       <c r="A89" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B89" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C89">
         <v>60</v>
@@ -3522,7 +3594,7 @@
         <v>9</v>
       </c>
       <c r="G89" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="H89">
         <v>64</v>
@@ -3530,10 +3602,10 @@
     </row>
     <row r="90" spans="1:8">
       <c r="A90" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B90" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C90">
         <v>40</v>
@@ -3548,7 +3620,7 @@
         <v>8</v>
       </c>
       <c r="G90" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="H90">
         <v>60</v>
@@ -3556,10 +3628,10 @@
     </row>
     <row r="91" spans="1:8">
       <c r="A91" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B91" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C91">
         <v>16</v>
@@ -3574,7 +3646,7 @@
         <v>7</v>
       </c>
       <c r="G91" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="H91">
         <v>21.33333333333333</v>
@@ -3582,10 +3654,10 @@
     </row>
     <row r="92" spans="1:8">
       <c r="A92" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B92" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C92">
         <v>16</v>
@@ -3600,7 +3672,7 @@
         <v>7</v>
       </c>
       <c r="G92" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="H92">
         <v>21.33333333333333</v>
@@ -3608,10 +3680,10 @@
     </row>
     <row r="93" spans="1:8">
       <c r="A93" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B93" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C93">
         <v>16</v>
@@ -3626,7 +3698,7 @@
         <v>8</v>
       </c>
       <c r="G93" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="H93">
         <v>21.33333333333333</v>
@@ -3634,10 +3706,10 @@
     </row>
     <row r="94" spans="1:8">
       <c r="A94" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B94" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C94">
         <v>16</v>
@@ -3652,7 +3724,7 @@
         <v>8</v>
       </c>
       <c r="G94" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="H94">
         <v>21.33333333333333</v>
@@ -3660,10 +3732,10 @@
     </row>
     <row r="95" spans="1:8">
       <c r="A95" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B95" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C95">
         <v>16</v>
@@ -3678,7 +3750,7 @@
         <v>8.5</v>
       </c>
       <c r="G95" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="H95">
         <v>21.33333333333333</v>
@@ -3686,10 +3758,10 @@
     </row>
     <row r="96" spans="1:8">
       <c r="A96" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B96" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C96">
         <v>16</v>
@@ -3704,7 +3776,7 @@
         <v>8.5</v>
       </c>
       <c r="G96" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="H96">
         <v>21.33333333333333</v>
@@ -3712,10 +3784,10 @@
     </row>
     <row r="97" spans="1:8">
       <c r="A97" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B97" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C97">
         <v>8</v>
@@ -3735,10 +3807,10 @@
     </row>
     <row r="98" spans="1:8">
       <c r="A98" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B98" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C98">
         <v>8</v>
@@ -3758,10 +3830,10 @@
     </row>
     <row r="99" spans="1:8">
       <c r="A99" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B99" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C99">
         <v>8</v>
@@ -3781,10 +3853,10 @@
     </row>
     <row r="100" spans="1:8">
       <c r="A100" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B100" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C100">
         <v>58</v>
@@ -3799,7 +3871,7 @@
         <v>7</v>
       </c>
       <c r="G100" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="H100">
         <v>77.33333333333333</v>
@@ -3807,10 +3879,10 @@
     </row>
     <row r="101" spans="1:8">
       <c r="A101" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B101" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C101">
         <v>58</v>
@@ -3825,7 +3897,7 @@
         <v>7</v>
       </c>
       <c r="G101" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="H101">
         <v>77.33333333333333</v>
@@ -3833,10 +3905,10 @@
     </row>
     <row r="102" spans="1:8">
       <c r="A102" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B102" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C102">
         <v>58</v>
@@ -3856,10 +3928,10 @@
     </row>
     <row r="103" spans="1:8">
       <c r="A103" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B103" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C103">
         <v>58</v>
@@ -3879,10 +3951,10 @@
     </row>
     <row r="104" spans="1:8">
       <c r="A104" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B104" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C104">
         <v>58</v>
@@ -3902,10 +3974,10 @@
     </row>
     <row r="105" spans="1:8">
       <c r="A105" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B105" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C105">
         <v>58</v>
@@ -3925,10 +3997,10 @@
     </row>
     <row r="106" spans="1:8">
       <c r="A106" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B106" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C106">
         <v>45</v>
@@ -3948,10 +4020,10 @@
     </row>
     <row r="107" spans="1:8">
       <c r="A107" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B107" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C107">
         <v>45</v>
@@ -3971,10 +4043,10 @@
     </row>
     <row r="108" spans="1:8">
       <c r="A108" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B108" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C108">
         <v>45</v>
@@ -3994,10 +4066,10 @@
     </row>
     <row r="109" spans="1:8">
       <c r="A109" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B109" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C109">
         <v>20</v>
@@ -4017,10 +4089,10 @@
     </row>
     <row r="110" spans="1:8">
       <c r="A110" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B110" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C110">
         <v>30</v>
@@ -4035,7 +4107,7 @@
         <v>10</v>
       </c>
       <c r="G110" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="H110">
         <v>34</v>
@@ -4043,10 +4115,10 @@
     </row>
     <row r="111" spans="1:8">
       <c r="A111" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B111" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C111">
         <v>20</v>
@@ -4061,7 +4133,7 @@
         <v>3</v>
       </c>
       <c r="G111" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="H111">
         <v>25.33333333333333</v>
@@ -4069,10 +4141,10 @@
     </row>
     <row r="112" spans="1:8">
       <c r="A112" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B112" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C112">
         <v>60</v>
@@ -4087,7 +4159,7 @@
         <v>5</v>
       </c>
       <c r="G112" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="H112">
         <v>66</v>
@@ -4095,10 +4167,10 @@
     </row>
     <row r="113" spans="1:8">
       <c r="A113" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B113" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C113">
         <v>80</v>
@@ -4113,7 +4185,7 @@
         <v>7</v>
       </c>
       <c r="G113" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="H113">
         <v>88</v>
@@ -4121,10 +4193,10 @@
     </row>
     <row r="114" spans="1:8">
       <c r="A114" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B114" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C114">
         <v>90</v>
@@ -4139,7 +4211,7 @@
         <v>7</v>
       </c>
       <c r="G114" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="H114">
         <v>93.00000000000001</v>
@@ -4147,10 +4219,10 @@
     </row>
     <row r="115" spans="1:8">
       <c r="A115" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B115" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C115">
         <v>90</v>
@@ -4165,7 +4237,7 @@
         <v>7.5</v>
       </c>
       <c r="G115" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="H115">
         <v>99.00000000000001</v>
@@ -4173,10 +4245,10 @@
     </row>
     <row r="116" spans="1:8">
       <c r="A116" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B116" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C116">
         <v>100</v>
@@ -4191,7 +4263,7 @@
         <v>8.5</v>
       </c>
       <c r="G116" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="H116">
         <v>110</v>
@@ -4199,10 +4271,10 @@
     </row>
     <row r="117" spans="1:8">
       <c r="A117" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B117" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C117">
         <v>110</v>
@@ -4217,7 +4289,7 @@
         <v>9</v>
       </c>
       <c r="G117" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="H117">
         <v>113.6666666666667</v>
@@ -4225,10 +4297,10 @@
     </row>
     <row r="118" spans="1:8">
       <c r="A118" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B118" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C118">
         <v>20</v>
@@ -4243,7 +4315,7 @@
         <v>5</v>
       </c>
       <c r="G118" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="H118">
         <v>28</v>
@@ -4251,10 +4323,10 @@
     </row>
     <row r="119" spans="1:8">
       <c r="A119" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B119" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C119">
         <v>30</v>
@@ -4269,7 +4341,7 @@
         <v>6</v>
       </c>
       <c r="G119" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="H119">
         <v>36</v>
@@ -4277,10 +4349,10 @@
     </row>
     <row r="120" spans="1:8">
       <c r="A120" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B120" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C120">
         <v>40</v>
@@ -4295,7 +4367,7 @@
         <v>7.5</v>
       </c>
       <c r="G120" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="H120">
         <v>45.33333333333333</v>
@@ -4303,10 +4375,10 @@
     </row>
     <row r="121" spans="1:8">
       <c r="A121" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B121" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C121">
         <v>45</v>
@@ -4321,7 +4393,7 @@
         <v>8.5</v>
       </c>
       <c r="G121" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="H121">
         <v>49.50000000000001</v>
@@ -4329,10 +4401,10 @@
     </row>
     <row r="122" spans="1:8">
       <c r="A122" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B122" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C122">
         <v>50</v>
@@ -4347,7 +4419,7 @@
         <v>10</v>
       </c>
       <c r="G122" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="H122">
         <v>50</v>
@@ -4355,10 +4427,10 @@
     </row>
     <row r="123" spans="1:8">
       <c r="A123" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B123" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C123">
         <v>70</v>
@@ -4373,7 +4445,7 @@
         <v>6</v>
       </c>
       <c r="G123" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="H123">
         <v>77</v>
@@ -4381,10 +4453,10 @@
     </row>
     <row r="124" spans="1:8">
       <c r="A124" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B124" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C124">
         <v>120</v>
@@ -4399,7 +4471,7 @@
         <v>8.5</v>
       </c>
       <c r="G124" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H124">
         <v>124</v>
@@ -4407,10 +4479,10 @@
     </row>
     <row r="125" spans="1:8">
       <c r="A125" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B125" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C125">
         <v>120</v>
@@ -4425,7 +4497,7 @@
         <v>9.5</v>
       </c>
       <c r="G125" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="H125">
         <v>124</v>
@@ -4433,10 +4505,10 @@
     </row>
     <row r="126" spans="1:8">
       <c r="A126" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B126" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C126">
         <v>120</v>
@@ -4451,7 +4523,7 @@
         <v>9.5</v>
       </c>
       <c r="G126" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="H126">
         <v>124</v>
@@ -4459,10 +4531,10 @@
     </row>
     <row r="127" spans="1:8">
       <c r="A127" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B127" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C127">
         <v>120</v>
@@ -4477,7 +4549,7 @@
         <v>9.5</v>
       </c>
       <c r="G127" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H127">
         <v>124</v>
@@ -4485,10 +4557,10 @@
     </row>
     <row r="128" spans="1:8">
       <c r="A128" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B128" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C128">
         <v>20</v>
@@ -4503,7 +4575,7 @@
         <v>6.5</v>
       </c>
       <c r="G128" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="H128">
         <v>26.66666666666666</v>
@@ -4511,10 +4583,10 @@
     </row>
     <row r="129" spans="1:8">
       <c r="A129" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B129" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C129">
         <v>20</v>
@@ -4529,7 +4601,7 @@
         <v>6.5</v>
       </c>
       <c r="G129" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H129">
         <v>26.66666666666666</v>
@@ -4537,10 +4609,10 @@
     </row>
     <row r="130" spans="1:8">
       <c r="A130" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B130" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C130">
         <v>20</v>
@@ -4555,7 +4627,7 @@
         <v>8</v>
       </c>
       <c r="G130" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="H130">
         <v>26.66666666666666</v>
@@ -4563,10 +4635,10 @@
     </row>
     <row r="131" spans="1:8">
       <c r="A131" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B131" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C131">
         <v>20</v>
@@ -4581,7 +4653,7 @@
         <v>8</v>
       </c>
       <c r="G131" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="H131">
         <v>26.66666666666666</v>
@@ -4589,10 +4661,10 @@
     </row>
     <row r="132" spans="1:8">
       <c r="A132" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B132" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C132">
         <v>20</v>
@@ -4607,7 +4679,7 @@
         <v>8.5</v>
       </c>
       <c r="G132" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="H132">
         <v>26.66666666666666</v>
@@ -4615,10 +4687,10 @@
     </row>
     <row r="133" spans="1:8">
       <c r="A133" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B133" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C133">
         <v>20</v>
@@ -4633,7 +4705,7 @@
         <v>8.5</v>
       </c>
       <c r="G133" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="H133">
         <v>26.66666666666666</v>
@@ -4641,10 +4713,10 @@
     </row>
     <row r="134" spans="1:8">
       <c r="A134" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B134" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C134">
         <v>20</v>
@@ -4659,7 +4731,7 @@
         <v>3</v>
       </c>
       <c r="G134" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="H134">
         <v>25.33333333333333</v>
@@ -4667,10 +4739,10 @@
     </row>
     <row r="135" spans="1:8">
       <c r="A135" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B135" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C135">
         <v>60</v>
@@ -4685,7 +4757,7 @@
         <v>6</v>
       </c>
       <c r="G135" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="H135">
         <v>72</v>
@@ -4693,10 +4765,10 @@
     </row>
     <row r="136" spans="1:8">
       <c r="A136" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B136" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C136">
         <v>80</v>
@@ -4711,7 +4783,7 @@
         <v>7</v>
       </c>
       <c r="G136" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="H136">
         <v>88</v>
@@ -4719,10 +4791,10 @@
     </row>
     <row r="137" spans="1:8">
       <c r="A137" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B137" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C137">
         <v>100</v>
@@ -4737,7 +4809,7 @@
         <v>7</v>
       </c>
       <c r="G137" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="H137">
         <v>103.3333333333333</v>
@@ -4745,10 +4817,10 @@
     </row>
     <row r="138" spans="1:8">
       <c r="A138" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B138" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C138">
         <v>70</v>
@@ -4763,7 +4835,7 @@
         <v>8</v>
       </c>
       <c r="G138" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="H138">
         <v>98</v>
@@ -4771,10 +4843,10 @@
     </row>
     <row r="139" spans="1:8">
       <c r="A139" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B139" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C139">
         <v>80</v>
@@ -4789,7 +4861,7 @@
         <v>8.5</v>
       </c>
       <c r="G139" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="H139">
         <v>101.3333333333333</v>
@@ -4797,10 +4869,10 @@
     </row>
     <row r="140" spans="1:8">
       <c r="A140" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B140" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C140">
         <v>20</v>
@@ -4815,7 +4887,7 @@
         <v>5</v>
       </c>
       <c r="G140" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="H140">
         <v>28</v>
@@ -4823,10 +4895,10 @@
     </row>
     <row r="141" spans="1:8">
       <c r="A141" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B141" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C141">
         <v>30</v>
@@ -4841,7 +4913,7 @@
         <v>7</v>
       </c>
       <c r="G141" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="H141">
         <v>38</v>
@@ -4849,10 +4921,10 @@
     </row>
     <row r="142" spans="1:8">
       <c r="A142" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B142" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C142">
         <v>40</v>
@@ -4867,7 +4939,7 @@
         <v>8</v>
       </c>
       <c r="G142" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="H142">
         <v>48</v>
@@ -4875,10 +4947,10 @@
     </row>
     <row r="143" spans="1:8">
       <c r="A143" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B143" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C143">
         <v>40</v>
@@ -4893,7 +4965,7 @@
         <v>9</v>
       </c>
       <c r="G143" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="H143">
         <v>48</v>
@@ -4901,10 +4973,10 @@
     </row>
     <row r="144" spans="1:8">
       <c r="A144" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B144" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C144">
         <v>30</v>
@@ -4919,7 +4991,7 @@
         <v>9</v>
       </c>
       <c r="G144" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="H144">
         <v>42</v>
@@ -4927,10 +4999,10 @@
     </row>
     <row r="145" spans="1:8">
       <c r="A145" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B145" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C145">
         <v>30</v>
@@ -4945,7 +5017,7 @@
         <v>7</v>
       </c>
       <c r="G145" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="H145">
         <v>45</v>
@@ -4953,10 +5025,10 @@
     </row>
     <row r="146" spans="1:8">
       <c r="A146" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B146" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C146">
         <v>50</v>
@@ -4971,7 +5043,7 @@
         <v>7.5</v>
       </c>
       <c r="G146" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="H146">
         <v>63.33333333333333</v>
@@ -4979,10 +5051,10 @@
     </row>
     <row r="147" spans="1:8">
       <c r="A147" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B147" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C147">
         <v>50</v>
@@ -4997,7 +5069,7 @@
         <v>8</v>
       </c>
       <c r="G147" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="H147">
         <v>63.33333333333333</v>
@@ -5005,10 +5077,10 @@
     </row>
     <row r="148" spans="1:8">
       <c r="A148" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B148" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C148">
         <v>50</v>
@@ -5023,7 +5095,7 @@
         <v>8.5</v>
       </c>
       <c r="G148" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="H148">
         <v>63.33333333333333</v>
@@ -5031,10 +5103,10 @@
     </row>
     <row r="149" spans="1:8">
       <c r="A149" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B149" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C149">
         <v>50</v>
@@ -5049,7 +5121,7 @@
         <v>9.5</v>
       </c>
       <c r="G149" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="H149">
         <v>63.33333333333333</v>
@@ -5057,10 +5129,10 @@
     </row>
     <row r="150" spans="1:8">
       <c r="A150" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B150" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C150">
         <v>40</v>
@@ -5075,7 +5147,7 @@
         <v>8</v>
       </c>
       <c r="G150" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="H150">
         <v>56</v>
@@ -5083,10 +5155,10 @@
     </row>
     <row r="151" spans="1:8">
       <c r="A151" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B151" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C151">
         <v>70</v>
@@ -5101,7 +5173,7 @@
         <v>6</v>
       </c>
       <c r="G151" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="H151">
         <v>84</v>
@@ -5109,10 +5181,10 @@
     </row>
     <row r="152" spans="1:8">
       <c r="A152" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B152" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C152">
         <v>120</v>
@@ -5127,7 +5199,7 @@
         <v>6</v>
       </c>
       <c r="G152" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="H152">
         <v>124</v>
@@ -5135,10 +5207,10 @@
     </row>
     <row r="153" spans="1:8">
       <c r="A153" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B153" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C153">
         <v>120</v>
@@ -5153,7 +5225,7 @@
         <v>8</v>
       </c>
       <c r="G153" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="H153">
         <v>140</v>
@@ -5161,10 +5233,10 @@
     </row>
     <row r="154" spans="1:8">
       <c r="A154" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B154" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C154">
         <v>130</v>
@@ -5179,7 +5251,7 @@
         <v>8.5</v>
       </c>
       <c r="G154" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="H154">
         <v>151.6666666666667</v>
@@ -5187,10 +5259,10 @@
     </row>
     <row r="155" spans="1:8">
       <c r="A155" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B155" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C155">
         <v>130</v>
@@ -5205,7 +5277,7 @@
         <v>9</v>
       </c>
       <c r="G155" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="H155">
         <v>151.6666666666667</v>
@@ -5213,10 +5285,10 @@
     </row>
     <row r="156" spans="1:8">
       <c r="A156" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B156" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C156">
         <v>20</v>
@@ -5231,7 +5303,7 @@
         <v>4</v>
       </c>
       <c r="G156" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="H156">
         <v>28</v>
@@ -5239,10 +5311,10 @@
     </row>
     <row r="157" spans="1:8">
       <c r="A157" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B157" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C157">
         <v>40</v>
@@ -5262,10 +5334,10 @@
     </row>
     <row r="158" spans="1:8">
       <c r="A158" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B158" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C158">
         <v>60</v>
@@ -5280,7 +5352,7 @@
         <v>6.5</v>
       </c>
       <c r="G158" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="H158">
         <v>62.00000000000001</v>
@@ -5288,10 +5360,10 @@
     </row>
     <row r="159" spans="1:8">
       <c r="A159" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B159" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C159">
         <v>70</v>
@@ -5306,7 +5378,7 @@
         <v>8.5</v>
       </c>
       <c r="G159" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="H159">
         <v>72.33333333333334</v>
@@ -5314,10 +5386,10 @@
     </row>
     <row r="160" spans="1:8">
       <c r="A160" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B160" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C160">
         <v>65</v>
@@ -5332,7 +5404,7 @@
         <v>8</v>
       </c>
       <c r="G160" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="H160">
         <v>67.16666666666667</v>
@@ -5340,10 +5412,10 @@
     </row>
     <row r="161" spans="1:8">
       <c r="A161" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B161" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C161">
         <v>60</v>
@@ -5363,10 +5435,10 @@
     </row>
     <row r="162" spans="1:8">
       <c r="A162" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B162" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C162">
         <v>60</v>
@@ -5381,7 +5453,7 @@
         <v>9</v>
       </c>
       <c r="G162" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="H162">
         <v>66</v>
@@ -5389,10 +5461,10 @@
     </row>
     <row r="163" spans="1:8">
       <c r="A163" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B163" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C163">
         <v>45</v>
@@ -5407,7 +5479,7 @@
         <v>8</v>
       </c>
       <c r="G163" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="H163">
         <v>62.99999999999999</v>
@@ -5415,10 +5487,10 @@
     </row>
     <row r="164" spans="1:8">
       <c r="A164" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B164" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C164">
         <v>45</v>
@@ -5438,10 +5510,10 @@
     </row>
     <row r="165" spans="1:8">
       <c r="A165" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B165" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C165">
         <v>20</v>
@@ -5456,7 +5528,7 @@
         <v>7</v>
       </c>
       <c r="G165" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="H165">
         <v>26.66666666666666</v>
@@ -5464,10 +5536,10 @@
     </row>
     <row r="166" spans="1:8">
       <c r="A166" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B166" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C166">
         <v>20</v>
@@ -5482,7 +5554,7 @@
         <v>6</v>
       </c>
       <c r="G166" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="H166">
         <v>28</v>
@@ -5490,10 +5562,10 @@
     </row>
     <row r="167" spans="1:8">
       <c r="A167" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B167" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C167">
         <v>20</v>
@@ -5508,7 +5580,7 @@
         <v>7</v>
       </c>
       <c r="G167" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H167">
         <v>28</v>
@@ -5516,10 +5588,10 @@
     </row>
     <row r="168" spans="1:8">
       <c r="A168" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B168" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C168">
         <v>20</v>
@@ -5534,7 +5606,7 @@
         <v>7</v>
       </c>
       <c r="G168" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="H168">
         <v>30</v>
@@ -5542,10 +5614,10 @@
     </row>
     <row r="169" spans="1:8">
       <c r="A169" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B169" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C169">
         <v>22.5</v>
@@ -5560,7 +5632,7 @@
         <v>7.5</v>
       </c>
       <c r="G169" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="H169">
         <v>30</v>
@@ -5568,10 +5640,10 @@
     </row>
     <row r="170" spans="1:8">
       <c r="A170" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B170" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C170">
         <v>22.5</v>
@@ -5586,7 +5658,7 @@
         <v>7</v>
       </c>
       <c r="G170" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="H170">
         <v>31.5</v>
@@ -5594,10 +5666,10 @@
     </row>
     <row r="171" spans="1:8">
       <c r="A171" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B171" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C171">
         <v>25</v>
@@ -5612,7 +5684,7 @@
         <v>8</v>
       </c>
       <c r="G171" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="H171">
         <v>31.66666666666666</v>
@@ -5620,10 +5692,10 @@
     </row>
     <row r="172" spans="1:8">
       <c r="A172" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B172" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C172">
         <v>25</v>
@@ -5638,7 +5710,7 @@
         <v>7.5</v>
       </c>
       <c r="G172" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="H172">
         <v>35</v>
@@ -5646,10 +5718,10 @@
     </row>
     <row r="173" spans="1:8">
       <c r="A173" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B173" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C173">
         <v>25</v>
@@ -5664,7 +5736,7 @@
         <v>8</v>
       </c>
       <c r="G173" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="H173">
         <v>31.66666666666666</v>
@@ -5672,10 +5744,10 @@
     </row>
     <row r="174" spans="1:8">
       <c r="A174" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B174" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C174">
         <v>25</v>
@@ -5690,7 +5762,7 @@
         <v>8</v>
       </c>
       <c r="G174" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="H174">
         <v>37.5</v>
@@ -5698,10 +5770,10 @@
     </row>
     <row r="175" spans="1:8">
       <c r="A175" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B175" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C175">
         <v>40</v>
@@ -5716,7 +5788,7 @@
         <v>7.5</v>
       </c>
       <c r="G175" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="H175">
         <v>50.66666666666666</v>
@@ -5724,10 +5796,10 @@
     </row>
     <row r="176" spans="1:8">
       <c r="A176" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B176" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C176">
         <v>40</v>
@@ -5742,7 +5814,7 @@
         <v>8.5</v>
       </c>
       <c r="G176" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="H176">
         <v>50.66666666666666</v>
@@ -5750,10 +5822,10 @@
     </row>
     <row r="177" spans="1:8">
       <c r="A177" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B177" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C177">
         <v>40</v>
@@ -5768,7 +5840,7 @@
         <v>9</v>
       </c>
       <c r="G177" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="H177">
         <v>48</v>
@@ -5776,10 +5848,10 @@
     </row>
     <row r="178" spans="1:8">
       <c r="A178" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B178" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C178">
         <v>22</v>
@@ -5794,7 +5866,7 @@
         <v>7</v>
       </c>
       <c r="G178" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="H178">
         <v>27.86666666666667</v>
@@ -5802,10 +5874,10 @@
     </row>
     <row r="179" spans="1:8">
       <c r="A179" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B179" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C179">
         <v>22</v>
@@ -5825,10 +5897,10 @@
     </row>
     <row r="180" spans="1:8">
       <c r="A180" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B180" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C180">
         <v>22</v>
@@ -5843,7 +5915,7 @@
         <v>8.5</v>
       </c>
       <c r="G180" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="H180">
         <v>27.86666666666667</v>
@@ -5851,10 +5923,10 @@
     </row>
     <row r="181" spans="1:8">
       <c r="A181" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B181" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C181">
         <v>20</v>
@@ -5874,10 +5946,10 @@
     </row>
     <row r="182" spans="1:8">
       <c r="A182" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B182" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C182">
         <v>22</v>
@@ -5897,10 +5969,10 @@
     </row>
     <row r="183" spans="1:8">
       <c r="A183" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B183" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C183">
         <v>20</v>
@@ -5915,7 +5987,7 @@
         <v>4</v>
       </c>
       <c r="G183" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="H183">
         <v>25.33333333333333</v>
@@ -5923,10 +5995,10 @@
     </row>
     <row r="184" spans="1:8">
       <c r="A184" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B184" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C184">
         <v>60</v>
@@ -5946,10 +6018,10 @@
     </row>
     <row r="185" spans="1:8">
       <c r="A185" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B185" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C185">
         <v>80</v>
@@ -5969,10 +6041,10 @@
     </row>
     <row r="186" spans="1:8">
       <c r="A186" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B186" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C186">
         <v>100</v>
@@ -5992,10 +6064,10 @@
     </row>
     <row r="187" spans="1:8">
       <c r="A187" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B187" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C187">
         <v>110</v>
@@ -6015,10 +6087,10 @@
     </row>
     <row r="188" spans="1:8">
       <c r="A188" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B188" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C188">
         <v>120</v>
@@ -6033,7 +6105,7 @@
         <v>8.5</v>
       </c>
       <c r="G188" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="H188">
         <v>124</v>
@@ -6041,10 +6113,10 @@
     </row>
     <row r="189" spans="1:8">
       <c r="A189" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B189" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C189">
         <v>80</v>
@@ -6059,7 +6131,7 @@
         <v>7.5</v>
       </c>
       <c r="G189" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="H189">
         <v>112</v>
@@ -6067,10 +6139,10 @@
     </row>
     <row r="190" spans="1:8">
       <c r="A190" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B190" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C190">
         <v>-30</v>
@@ -6085,7 +6157,7 @@
         <v>6</v>
       </c>
       <c r="G190" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="H190">
         <v>-38</v>
@@ -6093,10 +6165,10 @@
     </row>
     <row r="191" spans="1:8">
       <c r="A191" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B191" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C191">
         <v>-30</v>
@@ -6111,7 +6183,7 @@
         <v>6</v>
       </c>
       <c r="G191" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="H191">
         <v>-38</v>
@@ -6119,10 +6191,10 @@
     </row>
     <row r="192" spans="1:8">
       <c r="A192" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B192" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C192">
         <v>-25</v>
@@ -6137,7 +6209,7 @@
         <v>7.5</v>
       </c>
       <c r="G192" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="H192">
         <v>-33.33333333333333</v>
@@ -6145,10 +6217,10 @@
     </row>
     <row r="193" spans="1:8">
       <c r="A193" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B193" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C193">
         <v>-25</v>
@@ -6163,7 +6235,7 @@
         <v>7.5</v>
       </c>
       <c r="G193" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="H193">
         <v>-33.33333333333333</v>
@@ -6171,10 +6243,10 @@
     </row>
     <row r="194" spans="1:8">
       <c r="A194" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B194" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C194">
         <v>-20</v>
@@ -6189,7 +6261,7 @@
         <v>8</v>
       </c>
       <c r="G194" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="H194">
         <v>-25.33333333333333</v>
@@ -6197,10 +6269,10 @@
     </row>
     <row r="195" spans="1:8">
       <c r="A195" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B195" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C195">
         <v>-20</v>
@@ -6215,7 +6287,7 @@
         <v>8</v>
       </c>
       <c r="G195" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="H195">
         <v>-25.33333333333333</v>
@@ -6223,10 +6295,10 @@
     </row>
     <row r="196" spans="1:8">
       <c r="A196" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B196" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C196">
         <v>35</v>
@@ -6241,7 +6313,7 @@
         <v>7</v>
       </c>
       <c r="G196" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="H196">
         <v>52.5</v>
@@ -6249,10 +6321,10 @@
     </row>
     <row r="197" spans="1:8">
       <c r="A197" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B197" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C197">
         <v>25</v>
@@ -6267,7 +6339,7 @@
         <v>7</v>
       </c>
       <c r="G197" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="H197">
         <v>37.5</v>
@@ -6275,10 +6347,10 @@
     </row>
     <row r="198" spans="1:8">
       <c r="A198" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B198" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C198">
         <v>35</v>
@@ -6293,7 +6365,7 @@
         <v>7</v>
       </c>
       <c r="G198" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="H198">
         <v>52.5</v>
@@ -6301,10 +6373,10 @@
     </row>
     <row r="199" spans="1:8">
       <c r="A199" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B199" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C199">
         <v>25</v>
@@ -6319,7 +6391,7 @@
         <v>7</v>
       </c>
       <c r="G199" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="H199">
         <v>37.5</v>
@@ -6327,10 +6399,10 @@
     </row>
     <row r="200" spans="1:8">
       <c r="A200" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B200" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C200">
         <v>70</v>
@@ -6345,7 +6417,7 @@
         <v>6</v>
       </c>
       <c r="G200" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="H200">
         <v>84</v>
@@ -6353,10 +6425,10 @@
     </row>
     <row r="201" spans="1:8">
       <c r="A201" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B201" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C201">
         <v>90</v>
@@ -6376,10 +6448,10 @@
     </row>
     <row r="202" spans="1:8">
       <c r="A202" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B202" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C202">
         <v>120</v>
@@ -6399,10 +6471,10 @@
     </row>
     <row r="203" spans="1:8">
       <c r="A203" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B203" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C203">
         <v>120</v>
@@ -6422,10 +6494,10 @@
     </row>
     <row r="204" spans="1:8">
       <c r="A204" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B204" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C204">
         <v>120</v>
@@ -6445,10 +6517,10 @@
     </row>
     <row r="205" spans="1:8">
       <c r="A205" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B205" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C205">
         <v>120</v>
@@ -6468,10 +6540,10 @@
     </row>
     <row r="206" spans="1:8">
       <c r="A206" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B206" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C206">
         <v>120</v>
@@ -6491,10 +6563,10 @@
     </row>
     <row r="207" spans="1:8">
       <c r="A207" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B207" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C207">
         <v>20</v>
@@ -6509,7 +6581,7 @@
         <v>6</v>
       </c>
       <c r="G207" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="H207">
         <v>28</v>
@@ -6517,10 +6589,10 @@
     </row>
     <row r="208" spans="1:8">
       <c r="A208" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B208" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C208">
         <v>30</v>
@@ -6540,10 +6612,10 @@
     </row>
     <row r="209" spans="1:8">
       <c r="A209" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B209" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C209">
         <v>35</v>
@@ -6563,10 +6635,10 @@
     </row>
     <row r="210" spans="1:8">
       <c r="A210" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B210" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C210">
         <v>35</v>
@@ -6586,10 +6658,10 @@
     </row>
     <row r="211" spans="1:8">
       <c r="A211" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B211" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C211">
         <v>35</v>
@@ -6609,10 +6681,10 @@
     </row>
     <row r="212" spans="1:8">
       <c r="A212" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B212" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C212">
         <v>22</v>
@@ -6627,7 +6699,7 @@
         <v>7.5</v>
       </c>
       <c r="G212" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="H212">
         <v>27.86666666666667</v>
@@ -6635,10 +6707,10 @@
     </row>
     <row r="213" spans="1:8">
       <c r="A213" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B213" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C213">
         <v>22</v>
@@ -6653,7 +6725,7 @@
         <v>7.5</v>
       </c>
       <c r="G213" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="H213">
         <v>30.8</v>
@@ -6661,10 +6733,10 @@
     </row>
     <row r="214" spans="1:8">
       <c r="A214" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B214" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C214">
         <v>22</v>
@@ -6679,7 +6751,7 @@
         <v>8</v>
       </c>
       <c r="G214" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="H214">
         <v>27.86666666666667</v>
@@ -6687,10 +6759,10 @@
     </row>
     <row r="215" spans="1:8">
       <c r="A215" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B215" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C215">
         <v>22</v>
@@ -6705,7 +6777,7 @@
         <v>8</v>
       </c>
       <c r="G215" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="H215">
         <v>30.8</v>
@@ -6713,10 +6785,10 @@
     </row>
     <row r="216" spans="1:8">
       <c r="A216" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B216" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C216">
         <v>22</v>
@@ -6731,7 +6803,7 @@
         <v>8.5</v>
       </c>
       <c r="G216" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="H216">
         <v>27.86666666666667</v>
@@ -6739,10 +6811,10 @@
     </row>
     <row r="217" spans="1:8">
       <c r="A217" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B217" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C217">
         <v>22</v>
@@ -6757,7 +6829,7 @@
         <v>8</v>
       </c>
       <c r="G217" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="H217">
         <v>30.8</v>
@@ -6765,10 +6837,10 @@
     </row>
     <row r="218" spans="1:8">
       <c r="A218" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B218" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C218">
         <v>25</v>
@@ -6783,7 +6855,7 @@
         <v>8</v>
       </c>
       <c r="G218" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="H218">
         <v>31.66666666666666</v>
@@ -6791,10 +6863,10 @@
     </row>
     <row r="219" spans="1:8">
       <c r="A219" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B219" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C219">
         <v>25</v>
@@ -6809,7 +6881,7 @@
         <v>6.5</v>
       </c>
       <c r="G219" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="H219">
         <v>31.66666666666666</v>
@@ -6817,10 +6889,10 @@
     </row>
     <row r="220" spans="1:8">
       <c r="A220" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B220" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C220">
         <v>25</v>
@@ -6835,7 +6907,7 @@
         <v>8</v>
       </c>
       <c r="G220" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="H220">
         <v>31.66666666666666</v>
@@ -6843,10 +6915,10 @@
     </row>
     <row r="221" spans="1:8">
       <c r="A221" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B221" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C221">
         <v>25</v>
@@ -6861,7 +6933,7 @@
         <v>7.5</v>
       </c>
       <c r="G221" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="H221">
         <v>31.66666666666666</v>
@@ -6869,10 +6941,10 @@
     </row>
     <row r="222" spans="1:8">
       <c r="A222" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B222" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C222">
         <v>25</v>
@@ -6887,7 +6959,7 @@
         <v>9</v>
       </c>
       <c r="G222" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="H222">
         <v>31.66666666666666</v>
@@ -6895,10 +6967,10 @@
     </row>
     <row r="223" spans="1:8">
       <c r="A223" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B223" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C223">
         <v>25</v>
@@ -6913,7 +6985,7 @@
         <v>9</v>
       </c>
       <c r="G223" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="H223">
         <v>31.66666666666666</v>
@@ -6921,10 +6993,10 @@
     </row>
     <row r="224" spans="1:8">
       <c r="A224" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B224" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C224">
         <v>70</v>
@@ -6939,7 +7011,7 @@
         <v>6.5</v>
       </c>
       <c r="G224" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="H224">
         <v>84</v>
@@ -6947,10 +7019,10 @@
     </row>
     <row r="225" spans="1:8">
       <c r="A225" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B225" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C225">
         <v>85</v>
@@ -6965,7 +7037,7 @@
         <v>8</v>
       </c>
       <c r="G225" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="H225">
         <v>119</v>
@@ -6973,10 +7045,10 @@
     </row>
     <row r="226" spans="1:8">
       <c r="A226" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B226" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C226">
         <v>85</v>
@@ -6991,7 +7063,7 @@
         <v>9</v>
       </c>
       <c r="G226" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="H226">
         <v>119</v>
@@ -6999,10 +7071,10 @@
     </row>
     <row r="227" spans="1:8">
       <c r="A227" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B227" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C227">
         <v>85</v>
@@ -7017,7 +7089,7 @@
         <v>10</v>
       </c>
       <c r="G227" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="H227">
         <v>113.3333333333333</v>
@@ -7025,10 +7097,10 @@
     </row>
     <row r="228" spans="1:8">
       <c r="A228" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B228" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C228">
         <v>30</v>
@@ -7043,7 +7115,7 @@
         <v>6</v>
       </c>
       <c r="G228" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="H228">
         <v>36</v>
@@ -7051,10 +7123,10 @@
     </row>
     <row r="229" spans="1:8">
       <c r="A229" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B229" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C229">
         <v>30</v>
@@ -7069,7 +7141,7 @@
         <v>6</v>
       </c>
       <c r="G229" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="H229">
         <v>38</v>
@@ -7077,10 +7149,10 @@
     </row>
     <row r="230" spans="1:8">
       <c r="A230" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B230" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C230">
         <v>40</v>
@@ -7095,7 +7167,7 @@
         <v>8</v>
       </c>
       <c r="G230" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="H230">
         <v>50.66666666666666</v>
@@ -7103,10 +7175,10 @@
     </row>
     <row r="231" spans="1:8">
       <c r="A231" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B231" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C231">
         <v>40</v>
@@ -7121,7 +7193,7 @@
         <v>9</v>
       </c>
       <c r="G231" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="H231">
         <v>50.66666666666666</v>
@@ -7129,10 +7201,10 @@
     </row>
     <row r="232" spans="1:8">
       <c r="A232" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B232" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C232">
         <v>40</v>
@@ -7147,7 +7219,7 @@
         <v>10</v>
       </c>
       <c r="G232" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="H232">
         <v>49.33333333333334</v>
@@ -7155,10 +7227,10 @@
     </row>
     <row r="233" spans="1:8">
       <c r="A233" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B233" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C233">
         <v>40</v>
@@ -7173,7 +7245,7 @@
         <v>6.5</v>
       </c>
       <c r="G233" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="H233">
         <v>56</v>
@@ -7181,10 +7253,10 @@
     </row>
     <row r="234" spans="1:8">
       <c r="A234" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B234" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C234">
         <v>40</v>
@@ -7199,7 +7271,7 @@
         <v>6.5</v>
       </c>
       <c r="G234" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="H234">
         <v>56</v>
@@ -7207,10 +7279,10 @@
     </row>
     <row r="235" spans="1:8">
       <c r="A235" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B235" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C235">
         <v>40</v>
@@ -7225,7 +7297,7 @@
         <v>7.5</v>
       </c>
       <c r="G235" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="H235">
         <v>56</v>
@@ -7233,10 +7305,10 @@
     </row>
     <row r="236" spans="1:8">
       <c r="A236" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B236" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C236">
         <v>40</v>
@@ -7251,7 +7323,7 @@
         <v>9</v>
       </c>
       <c r="G236" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="H236">
         <v>56</v>
@@ -7259,10 +7331,10 @@
     </row>
     <row r="237" spans="1:8">
       <c r="A237" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B237" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C237">
         <v>60</v>
@@ -7277,7 +7349,7 @@
         <v>8</v>
       </c>
       <c r="G237" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="H237">
         <v>80</v>
@@ -7285,10 +7357,10 @@
     </row>
     <row r="238" spans="1:8">
       <c r="A238" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B238" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C238">
         <v>60</v>
@@ -7303,7 +7375,7 @@
         <v>7</v>
       </c>
       <c r="G238" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="H238">
         <v>80</v>
@@ -7311,10 +7383,10 @@
     </row>
     <row r="239" spans="1:8">
       <c r="A239" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B239" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C239">
         <v>60</v>
@@ -7329,7 +7401,7 @@
         <v>8.5</v>
       </c>
       <c r="G239" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H239">
         <v>80</v>
@@ -7337,10 +7409,10 @@
     </row>
     <row r="240" spans="1:8">
       <c r="A240" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B240" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C240">
         <v>60</v>
@@ -7355,7 +7427,7 @@
         <v>8</v>
       </c>
       <c r="G240" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="H240">
         <v>80</v>
@@ -7363,10 +7435,10 @@
     </row>
     <row r="241" spans="1:8">
       <c r="A241" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B241" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C241">
         <v>60</v>
@@ -7381,7 +7453,7 @@
         <v>9</v>
       </c>
       <c r="G241" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="H241">
         <v>80</v>
@@ -7389,10 +7461,10 @@
     </row>
     <row r="242" spans="1:8">
       <c r="A242" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B242" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C242">
         <v>60</v>
@@ -7407,7 +7479,7 @@
         <v>9</v>
       </c>
       <c r="G242" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="H242">
         <v>80</v>
@@ -7415,10 +7487,10 @@
     </row>
     <row r="243" spans="1:8">
       <c r="A243" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B243" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C243">
         <v>60</v>
@@ -7433,7 +7505,7 @@
         <v>4</v>
       </c>
       <c r="G243" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="H243">
         <v>76</v>
@@ -7441,10 +7513,10 @@
     </row>
     <row r="244" spans="1:8">
       <c r="A244" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B244" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C244">
         <v>100</v>
@@ -7459,7 +7531,7 @@
         <v>6</v>
       </c>
       <c r="G244" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="H244">
         <v>116.6666666666667</v>
@@ -7467,10 +7539,10 @@
     </row>
     <row r="245" spans="1:8">
       <c r="A245" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B245" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C245">
         <v>130</v>
@@ -7485,7 +7557,7 @@
         <v>7</v>
       </c>
       <c r="G245" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="H245">
         <v>134.3333333333333</v>
@@ -7493,10 +7565,10 @@
     </row>
     <row r="246" spans="1:8">
       <c r="A246" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B246" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C246">
         <v>150</v>
@@ -7511,7 +7583,7 @@
         <v>8.5</v>
       </c>
       <c r="G246" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="H246">
         <v>155</v>
@@ -7519,10 +7591,10 @@
     </row>
     <row r="247" spans="1:8">
       <c r="A247" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B247" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C247">
         <v>120</v>
@@ -7537,7 +7609,7 @@
         <v>7.5</v>
       </c>
       <c r="G247" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="H247">
         <v>140</v>
@@ -7545,10 +7617,10 @@
     </row>
     <row r="248" spans="1:8">
       <c r="A248" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B248" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C248">
         <v>120</v>
@@ -7563,7 +7635,7 @@
         <v>7.5</v>
       </c>
       <c r="G248" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="H248">
         <v>140</v>
@@ -7571,10 +7643,10 @@
     </row>
     <row r="249" spans="1:8">
       <c r="A249" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B249" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C249">
         <v>120</v>
@@ -7589,7 +7661,7 @@
         <v>8</v>
       </c>
       <c r="G249" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="H249">
         <v>140</v>
@@ -7597,10 +7669,10 @@
     </row>
     <row r="250" spans="1:8">
       <c r="A250" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B250" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C250">
         <v>120</v>
@@ -7615,7 +7687,7 @@
         <v>8.5</v>
       </c>
       <c r="G250" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="H250">
         <v>140</v>
@@ -7623,10 +7695,10 @@
     </row>
     <row r="251" spans="1:8">
       <c r="A251" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B251" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C251">
         <v>120</v>
@@ -7641,7 +7713,7 @@
         <v>9</v>
       </c>
       <c r="G251" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="H251">
         <v>140</v>
@@ -7649,10 +7721,10 @@
     </row>
     <row r="252" spans="1:8">
       <c r="A252" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B252" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C252">
         <v>40</v>
@@ -7667,7 +7739,7 @@
         <v>5</v>
       </c>
       <c r="G252" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="H252">
         <v>50.66666666666666</v>
@@ -7675,10 +7747,10 @@
     </row>
     <row r="253" spans="1:8">
       <c r="A253" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B253" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C253">
         <v>50</v>
@@ -7693,7 +7765,7 @@
         <v>6</v>
       </c>
       <c r="G253" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="H253">
         <v>58.33333333333334</v>
@@ -7701,10 +7773,10 @@
     </row>
     <row r="254" spans="1:8">
       <c r="A254" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B254" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C254">
         <v>60</v>
@@ -7719,7 +7791,7 @@
         <v>7</v>
       </c>
       <c r="G254" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="H254">
         <v>70</v>
@@ -7727,10 +7799,10 @@
     </row>
     <row r="255" spans="1:8">
       <c r="A255" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B255" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C255">
         <v>60</v>
@@ -7745,7 +7817,7 @@
         <v>8</v>
       </c>
       <c r="G255" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="H255">
         <v>70</v>
@@ -7753,10 +7825,10 @@
     </row>
     <row r="256" spans="1:8">
       <c r="A256" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B256" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C256">
         <v>60</v>
@@ -7771,7 +7843,7 @@
         <v>8.5</v>
       </c>
       <c r="G256" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="H256">
         <v>70</v>
@@ -7779,10 +7851,10 @@
     </row>
     <row r="257" spans="1:8">
       <c r="A257" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B257" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C257">
         <v>60</v>
@@ -7797,7 +7869,7 @@
         <v>8.5</v>
       </c>
       <c r="G257" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="H257">
         <v>70</v>
@@ -7805,10 +7877,10 @@
     </row>
     <row r="258" spans="1:8">
       <c r="A258" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B258" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C258">
         <v>60</v>
@@ -7823,7 +7895,7 @@
         <v>8</v>
       </c>
       <c r="G258" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="H258">
         <v>70</v>
@@ -7831,10 +7903,10 @@
     </row>
     <row r="259" spans="1:8">
       <c r="A259" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B259" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C259">
         <v>40</v>
@@ -7849,7 +7921,7 @@
         <v>5</v>
       </c>
       <c r="G259" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="H259">
         <v>53.33333333333333</v>
@@ -7857,10 +7929,10 @@
     </row>
     <row r="260" spans="1:8">
       <c r="A260" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B260" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C260">
         <v>50</v>
@@ -7875,7 +7947,7 @@
         <v>7</v>
       </c>
       <c r="G260" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="H260">
         <v>63.33333333333333</v>
@@ -7883,10 +7955,10 @@
     </row>
     <row r="261" spans="1:8">
       <c r="A261" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B261" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C261">
         <v>50</v>
@@ -7901,7 +7973,7 @@
         <v>7</v>
       </c>
       <c r="G261" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="H261">
         <v>63.33333333333333</v>
@@ -7909,10 +7981,10 @@
     </row>
     <row r="262" spans="1:8">
       <c r="A262" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B262" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C262">
         <v>50</v>
@@ -7927,7 +7999,7 @@
         <v>7.5</v>
       </c>
       <c r="G262" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="H262">
         <v>63.33333333333333</v>
@@ -7935,10 +8007,10 @@
     </row>
     <row r="263" spans="1:8">
       <c r="A263" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B263" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C263">
         <v>50</v>
@@ -7953,7 +8025,7 @@
         <v>8</v>
       </c>
       <c r="G263" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="H263">
         <v>66.66666666666666</v>
@@ -7961,10 +8033,10 @@
     </row>
     <row r="264" spans="1:8">
       <c r="A264" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B264" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C264">
         <v>20</v>
@@ -7979,7 +8051,7 @@
         <v>7</v>
       </c>
       <c r="G264" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="H264">
         <v>26.66666666666666</v>
@@ -7987,10 +8059,10 @@
     </row>
     <row r="265" spans="1:8">
       <c r="A265" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B265" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C265">
         <v>20</v>
@@ -8005,7 +8077,7 @@
         <v>7</v>
       </c>
       <c r="G265" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H265">
         <v>28</v>
@@ -8013,10 +8085,10 @@
     </row>
     <row r="266" spans="1:8">
       <c r="A266" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B266" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C266">
         <v>25</v>
@@ -8031,7 +8103,7 @@
         <v>8.5</v>
       </c>
       <c r="G266" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="H266">
         <v>31.66666666666666</v>
@@ -8039,10 +8111,10 @@
     </row>
     <row r="267" spans="1:8">
       <c r="A267" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B267" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C267">
         <v>25</v>
@@ -8057,7 +8129,7 @@
         <v>7.5</v>
       </c>
       <c r="G267" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="H267">
         <v>33.33333333333333</v>
@@ -8065,10 +8137,10 @@
     </row>
     <row r="268" spans="1:8">
       <c r="A268" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B268" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C268">
         <v>25</v>
@@ -8083,7 +8155,7 @@
         <v>8.5</v>
       </c>
       <c r="G268" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="H268">
         <v>31.66666666666666</v>
@@ -8091,10 +8163,10 @@
     </row>
     <row r="269" spans="1:8">
       <c r="A269" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B269" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C269">
         <v>25</v>
@@ -8109,7 +8181,7 @@
         <v>8</v>
       </c>
       <c r="G269" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="H269">
         <v>35</v>
@@ -8117,10 +8189,10 @@
     </row>
     <row r="270" spans="1:8">
       <c r="A270" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B270" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C270">
         <v>25</v>
@@ -8135,7 +8207,7 @@
         <v>9</v>
       </c>
       <c r="G270" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="H270">
         <v>31.66666666666666</v>
@@ -8143,10 +8215,10 @@
     </row>
     <row r="271" spans="1:8">
       <c r="A271" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B271" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C271">
         <v>25</v>
@@ -8161,7 +8233,7 @@
         <v>9</v>
       </c>
       <c r="G271" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="H271">
         <v>37.5</v>
@@ -8169,10 +8241,10 @@
     </row>
     <row r="272" spans="1:8">
       <c r="A272" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B272" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C272">
         <v>20</v>
@@ -8192,10 +8264,10 @@
     </row>
     <row r="273" spans="1:8">
       <c r="A273" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B273" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C273">
         <v>60</v>
@@ -8215,10 +8287,10 @@
     </row>
     <row r="274" spans="1:8">
       <c r="A274" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B274" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C274">
         <v>100</v>
@@ -8238,10 +8310,10 @@
     </row>
     <row r="275" spans="1:8">
       <c r="A275" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B275" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C275">
         <v>100</v>
@@ -8261,10 +8333,10 @@
     </row>
     <row r="276" spans="1:8">
       <c r="A276" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B276" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C276">
         <v>60</v>
@@ -8284,10 +8356,10 @@
     </row>
     <row r="277" spans="1:8">
       <c r="A277" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B277" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C277">
         <v>90</v>
@@ -8307,10 +8379,10 @@
     </row>
     <row r="278" spans="1:8">
       <c r="A278" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B278" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C278">
         <v>110</v>
@@ -8330,10 +8402,10 @@
     </row>
     <row r="279" spans="1:8">
       <c r="A279" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B279" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C279">
         <v>30</v>
@@ -8353,10 +8425,10 @@
     </row>
     <row r="280" spans="1:8">
       <c r="A280" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B280" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C280">
         <v>40</v>
@@ -8376,10 +8448,10 @@
     </row>
     <row r="281" spans="1:8">
       <c r="A281" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B281" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C281">
         <v>40</v>
@@ -8399,10 +8471,10 @@
     </row>
     <row r="282" spans="1:8">
       <c r="A282" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B282" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C282">
         <v>30</v>
@@ -8422,10 +8494,10 @@
     </row>
     <row r="283" spans="1:8">
       <c r="A283" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B283" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C283">
         <v>30</v>
@@ -8445,10 +8517,10 @@
     </row>
     <row r="284" spans="1:8">
       <c r="A284" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B284" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C284">
         <v>40</v>
@@ -8468,10 +8540,10 @@
     </row>
     <row r="285" spans="1:8">
       <c r="A285" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B285" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C285">
         <v>40</v>
@@ -8491,10 +8563,10 @@
     </row>
     <row r="286" spans="1:8">
       <c r="A286" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B286" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C286">
         <v>40</v>
@@ -8514,10 +8586,10 @@
     </row>
     <row r="287" spans="1:8">
       <c r="A287" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B287" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C287">
         <v>40</v>
@@ -8537,10 +8609,10 @@
     </row>
     <row r="288" spans="1:8">
       <c r="A288" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B288" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C288">
         <v>60</v>
@@ -8560,10 +8632,10 @@
     </row>
     <row r="289" spans="1:8">
       <c r="A289" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B289" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C289">
         <v>60</v>
@@ -8583,10 +8655,10 @@
     </row>
     <row r="290" spans="1:8">
       <c r="A290" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B290" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C290">
         <v>60</v>
@@ -8606,10 +8678,10 @@
     </row>
     <row r="291" spans="1:8">
       <c r="A291" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B291" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C291">
         <v>60</v>
@@ -8629,10 +8701,10 @@
     </row>
     <row r="292" spans="1:8">
       <c r="A292" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B292" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C292">
         <v>60</v>
@@ -8652,10 +8724,10 @@
     </row>
     <row r="293" spans="1:8">
       <c r="A293" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B293" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C293">
         <v>60</v>
@@ -8675,10 +8747,10 @@
     </row>
     <row r="294" spans="1:8">
       <c r="A294" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B294" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C294">
         <v>20</v>
@@ -8693,7 +8765,7 @@
         <v>3</v>
       </c>
       <c r="G294" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="H294">
         <v>28</v>
@@ -8701,10 +8773,10 @@
     </row>
     <row r="295" spans="1:8">
       <c r="A295" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B295" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C295">
         <v>60</v>
@@ -8719,7 +8791,7 @@
         <v>6</v>
       </c>
       <c r="G295" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="H295">
         <v>76</v>
@@ -8727,10 +8799,10 @@
     </row>
     <row r="296" spans="1:8">
       <c r="A296" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B296" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C296">
         <v>110</v>
@@ -8745,7 +8817,7 @@
         <v>7.5</v>
       </c>
       <c r="G296" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="H296">
         <v>121</v>
@@ -8753,10 +8825,10 @@
     </row>
     <row r="297" spans="1:8">
       <c r="A297" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B297" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C297">
         <v>70</v>
@@ -8771,7 +8843,7 @@
         <v>8</v>
       </c>
       <c r="G297" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="H297">
         <v>116.6666666666667</v>
@@ -8779,10 +8851,10 @@
     </row>
     <row r="298" spans="1:8">
       <c r="A298" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B298" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C298">
         <v>80</v>
@@ -8797,7 +8869,7 @@
         <v>8.5</v>
       </c>
       <c r="G298" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H298">
         <v>112</v>
@@ -8805,10 +8877,10 @@
     </row>
     <row r="299" spans="1:8">
       <c r="A299" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B299" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C299">
         <v>60</v>
@@ -8823,7 +8895,7 @@
         <v>5</v>
       </c>
       <c r="G299" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="H299">
         <v>80</v>
@@ -8831,10 +8903,10 @@
     </row>
     <row r="300" spans="1:8">
       <c r="A300" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B300" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C300">
         <v>110</v>
@@ -8849,7 +8921,7 @@
         <v>6.5</v>
       </c>
       <c r="G300" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="H300">
         <v>128.3333333333333</v>
@@ -8857,10 +8929,10 @@
     </row>
     <row r="301" spans="1:8">
       <c r="A301" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B301" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C301">
         <v>140</v>
@@ -8875,7 +8947,7 @@
         <v>7</v>
       </c>
       <c r="G301" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="H301">
         <v>144.6666666666667</v>
@@ -8883,10 +8955,10 @@
     </row>
     <row r="302" spans="1:8">
       <c r="A302" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B302" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C302">
         <v>160</v>
@@ -8901,7 +8973,7 @@
         <v>8.5</v>
       </c>
       <c r="G302" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="H302">
         <v>165.3333333333333</v>
@@ -8909,10 +8981,10 @@
     </row>
     <row r="303" spans="1:8">
       <c r="A303" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B303" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C303">
         <v>170</v>
@@ -8927,7 +8999,7 @@
         <v>9</v>
       </c>
       <c r="G303" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="H303">
         <v>175.6666666666667</v>
@@ -8935,10 +9007,10 @@
     </row>
     <row r="304" spans="1:8">
       <c r="A304" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B304" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C304">
         <v>30</v>
@@ -8953,7 +9025,7 @@
         <v>7</v>
       </c>
       <c r="G304" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="H304">
         <v>40</v>
@@ -8961,10 +9033,10 @@
     </row>
     <row r="305" spans="1:8">
       <c r="A305" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B305" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C305">
         <v>40</v>
@@ -8979,7 +9051,7 @@
         <v>7</v>
       </c>
       <c r="G305" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="H305">
         <v>44</v>
@@ -8987,10 +9059,10 @@
     </row>
     <row r="306" spans="1:8">
       <c r="A306" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B306" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C306">
         <v>50</v>
@@ -9005,7 +9077,7 @@
         <v>9.5</v>
       </c>
       <c r="G306" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="H306">
         <v>53.33333333333334</v>
@@ -9013,10 +9085,10 @@
     </row>
     <row r="307" spans="1:8">
       <c r="A307" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B307" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C307">
         <v>40</v>
@@ -9031,7 +9103,7 @@
         <v>8.5</v>
       </c>
       <c r="G307" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="H307">
         <v>53.33333333333333</v>
@@ -9039,10 +9111,10 @@
     </row>
     <row r="308" spans="1:8">
       <c r="A308" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B308" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C308">
         <v>70</v>
@@ -9062,10 +9134,10 @@
     </row>
     <row r="309" spans="1:8">
       <c r="A309" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B309" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C309">
         <v>120</v>
@@ -9085,10 +9157,10 @@
     </row>
     <row r="310" spans="1:8">
       <c r="A310" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B310" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C310">
         <v>140</v>
@@ -9108,10 +9180,10 @@
     </row>
     <row r="311" spans="1:8">
       <c r="A311" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B311" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C311">
         <v>140</v>
@@ -9131,10 +9203,10 @@
     </row>
     <row r="312" spans="1:8">
       <c r="A312" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B312" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C312">
         <v>120</v>
@@ -9154,10 +9226,10 @@
     </row>
     <row r="313" spans="1:8">
       <c r="A313" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B313" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C313">
         <v>20</v>
@@ -9177,10 +9249,10 @@
     </row>
     <row r="314" spans="1:8">
       <c r="A314" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B314" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C314">
         <v>40</v>
@@ -9200,10 +9272,10 @@
     </row>
     <row r="315" spans="1:8">
       <c r="A315" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B315" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C315">
         <v>60</v>
@@ -9223,10 +9295,10 @@
     </row>
     <row r="316" spans="1:8">
       <c r="A316" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B316" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C316">
         <v>70</v>
@@ -9246,10 +9318,10 @@
     </row>
     <row r="317" spans="1:8">
       <c r="A317" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B317" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C317">
         <v>80</v>
@@ -9269,10 +9341,10 @@
     </row>
     <row r="318" spans="1:8">
       <c r="A318" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B318" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C318">
         <v>75</v>
@@ -9292,10 +9364,10 @@
     </row>
     <row r="319" spans="1:8">
       <c r="A319" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B319" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C319">
         <v>60</v>
@@ -9315,10 +9387,10 @@
     </row>
     <row r="320" spans="1:8">
       <c r="A320" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B320" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C320">
         <v>60</v>
@@ -9338,10 +9410,10 @@
     </row>
     <row r="321" spans="1:8">
       <c r="A321" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B321" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C321">
         <v>60</v>
@@ -9361,10 +9433,10 @@
     </row>
     <row r="322" spans="1:8">
       <c r="A322" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B322" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C322">
         <v>65</v>
@@ -9384,10 +9456,10 @@
     </row>
     <row r="323" spans="1:8">
       <c r="A323" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B323" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C323">
         <v>65</v>
@@ -9407,10 +9479,10 @@
     </row>
     <row r="324" spans="1:8">
       <c r="A324" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B324" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C324">
         <v>65</v>
@@ -9430,10 +9502,10 @@
     </row>
     <row r="325" spans="1:8">
       <c r="A325" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B325" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C325">
         <v>65</v>
@@ -9453,10 +9525,10 @@
     </row>
     <row r="326" spans="1:8">
       <c r="A326" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B326" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C326">
         <v>65</v>
@@ -9476,10 +9548,10 @@
     </row>
     <row r="327" spans="1:8">
       <c r="A327" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B327" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C327">
         <v>65</v>
@@ -9499,10 +9571,10 @@
     </row>
     <row r="328" spans="1:8">
       <c r="A328" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B328" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C328">
         <v>65</v>
@@ -9522,10 +9594,10 @@
     </row>
     <row r="329" spans="1:8">
       <c r="A329" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B329" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C329">
         <v>65</v>
@@ -9545,10 +9617,10 @@
     </row>
     <row r="330" spans="1:8">
       <c r="A330" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B330" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C330">
         <v>20</v>
@@ -9563,7 +9635,7 @@
         <v>3</v>
       </c>
       <c r="G330" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="H330">
         <v>25.33333333333333</v>
@@ -9571,10 +9643,10 @@
     </row>
     <row r="331" spans="1:8">
       <c r="A331" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B331" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C331">
         <v>70</v>
@@ -9589,7 +9661,7 @@
         <v>6</v>
       </c>
       <c r="G331" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="H331">
         <v>81.66666666666667</v>
@@ -9597,10 +9669,10 @@
     </row>
     <row r="332" spans="1:8">
       <c r="A332" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B332" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C332">
         <v>90</v>
@@ -9615,7 +9687,7 @@
         <v>6</v>
       </c>
       <c r="G332" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="H332">
         <v>93.00000000000001</v>
@@ -9623,10 +9695,10 @@
     </row>
     <row r="333" spans="1:8">
       <c r="A333" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B333" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C333">
         <v>120</v>
@@ -9641,7 +9713,7 @@
         <v>7.5</v>
       </c>
       <c r="G333" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="H333">
         <v>124</v>
@@ -9649,10 +9721,10 @@
     </row>
     <row r="334" spans="1:8">
       <c r="A334" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B334" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C334">
         <v>140</v>
@@ -9667,7 +9739,7 @@
         <v>10</v>
       </c>
       <c r="G334" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="H334">
         <v>140</v>
@@ -9675,10 +9747,10 @@
     </row>
     <row r="335" spans="1:8">
       <c r="A335" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B335" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C335">
         <v>80</v>
@@ -9693,7 +9765,7 @@
         <v>8.5</v>
       </c>
       <c r="G335" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="H335">
         <v>133.3333333333333</v>
@@ -9701,10 +9773,10 @@
     </row>
     <row r="336" spans="1:8">
       <c r="A336" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B336" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C336">
         <v>80</v>
@@ -9719,7 +9791,7 @@
         <v>10</v>
       </c>
       <c r="G336" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="H336">
         <v>101.3333333333333</v>
@@ -9727,10 +9799,10 @@
     </row>
     <row r="337" spans="1:8">
       <c r="A337" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B337" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C337">
         <v>20</v>
@@ -9745,7 +9817,7 @@
         <v>4</v>
       </c>
       <c r="G337" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="H337">
         <v>25.33333333333333</v>
@@ -9753,10 +9825,10 @@
     </row>
     <row r="338" spans="1:8">
       <c r="A338" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B338" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C338">
         <v>40</v>
@@ -9771,7 +9843,7 @@
         <v>6</v>
       </c>
       <c r="G338" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="H338">
         <v>50.66666666666666</v>
@@ -9779,10 +9851,10 @@
     </row>
     <row r="339" spans="1:8">
       <c r="A339" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B339" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C339">
         <v>60</v>
@@ -9797,7 +9869,7 @@
         <v>7</v>
       </c>
       <c r="G339" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="H339">
         <v>66</v>
@@ -9805,10 +9877,10 @@
     </row>
     <row r="340" spans="1:8">
       <c r="A340" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B340" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C340">
         <v>70</v>
@@ -9823,7 +9895,7 @@
         <v>8.5</v>
       </c>
       <c r="G340" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="H340">
         <v>77</v>
@@ -9831,10 +9903,10 @@
     </row>
     <row r="341" spans="1:8">
       <c r="A341" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B341" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C341">
         <v>75</v>
@@ -9849,7 +9921,7 @@
         <v>8.75</v>
       </c>
       <c r="G341" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="H341">
         <v>77.50000000000001</v>
@@ -9857,10 +9929,10 @@
     </row>
     <row r="342" spans="1:8">
       <c r="A342" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B342" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C342">
         <v>50</v>
@@ -9875,7 +9947,7 @@
         <v>8</v>
       </c>
       <c r="G342" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H342">
         <v>66.66666666666666</v>
@@ -9883,10 +9955,10 @@
     </row>
     <row r="343" spans="1:8">
       <c r="A343" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B343" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C343">
         <v>40</v>
@@ -9901,7 +9973,7 @@
         <v>6</v>
       </c>
       <c r="G343" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="H343">
         <v>50.66666666666666</v>
@@ -9909,10 +9981,10 @@
     </row>
     <row r="344" spans="1:8">
       <c r="A344" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B344" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C344">
         <v>50</v>
@@ -9927,7 +9999,7 @@
         <v>6.5</v>
       </c>
       <c r="G344" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="H344">
         <v>63.33333333333333</v>
@@ -9935,10 +10007,10 @@
     </row>
     <row r="345" spans="1:8">
       <c r="A345" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B345" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C345">
         <v>63</v>
@@ -9953,7 +10025,7 @@
         <v>8</v>
       </c>
       <c r="G345" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="H345">
         <v>75.59999999999999</v>
@@ -9961,10 +10033,10 @@
     </row>
     <row r="346" spans="1:8">
       <c r="A346" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B346" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C346">
         <v>63</v>
@@ -9979,7 +10051,7 @@
         <v>8.5</v>
       </c>
       <c r="G346" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="H346">
         <v>75.59999999999999</v>
@@ -9987,10 +10059,10 @@
     </row>
     <row r="347" spans="1:8">
       <c r="A347" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B347" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C347">
         <v>11</v>
@@ -10005,7 +10077,7 @@
         <v>5</v>
       </c>
       <c r="G347" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="H347">
         <v>16.5</v>
@@ -10013,10 +10085,10 @@
     </row>
     <row r="348" spans="1:8">
       <c r="A348" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B348" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C348">
         <v>32</v>
@@ -10031,7 +10103,7 @@
         <v>5</v>
       </c>
       <c r="G348" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="H348">
         <v>48</v>
@@ -10039,10 +10111,10 @@
     </row>
     <row r="349" spans="1:8">
       <c r="A349" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B349" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C349">
         <v>33</v>
@@ -10057,7 +10129,7 @@
         <v>7</v>
       </c>
       <c r="G349" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H349">
         <v>49.5</v>
@@ -10065,10 +10137,10 @@
     </row>
     <row r="350" spans="1:8">
       <c r="A350" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B350" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C350">
         <v>59</v>
@@ -10083,7 +10155,7 @@
         <v>8</v>
       </c>
       <c r="G350" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="H350">
         <v>82.59999999999999</v>
@@ -10091,10 +10163,10 @@
     </row>
     <row r="351" spans="1:8">
       <c r="A351" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B351" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C351">
         <v>39</v>
@@ -10109,7 +10181,7 @@
         <v>9</v>
       </c>
       <c r="G351" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="H351">
         <v>58.5</v>
@@ -10117,10 +10189,10 @@
     </row>
     <row r="352" spans="1:8">
       <c r="A352" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B352" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C352">
         <v>66</v>
@@ -10135,7 +10207,7 @@
         <v>9</v>
       </c>
       <c r="G352" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="H352">
         <v>92.39999999999999</v>
@@ -10143,10 +10215,10 @@
     </row>
     <row r="353" spans="1:8">
       <c r="A353" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B353" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C353">
         <v>70</v>
@@ -10161,7 +10233,7 @@
         <v>6</v>
       </c>
       <c r="G353" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="H353">
         <v>81.66666666666667</v>
@@ -10169,10 +10241,10 @@
     </row>
     <row r="354" spans="1:8">
       <c r="A354" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B354" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C354">
         <v>120</v>
@@ -10187,7 +10259,7 @@
         <v>6</v>
       </c>
       <c r="G354" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="H354">
         <v>124</v>
@@ -10195,10 +10267,10 @@
     </row>
     <row r="355" spans="1:8">
       <c r="A355" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B355" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C355">
         <v>140</v>
@@ -10213,7 +10285,7 @@
         <v>6.5</v>
       </c>
       <c r="G355" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="H355">
         <v>144.6666666666667</v>
@@ -10221,10 +10293,10 @@
     </row>
     <row r="356" spans="1:8">
       <c r="A356" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B356" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C356">
         <v>160</v>
@@ -10239,7 +10311,7 @@
         <v>8.5</v>
       </c>
       <c r="G356" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="H356">
         <v>165.3333333333333</v>
@@ -10247,10 +10319,10 @@
     </row>
     <row r="357" spans="1:8">
       <c r="A357" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B357" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C357">
         <v>140</v>
@@ -10265,7 +10337,7 @@
         <v>8.5</v>
       </c>
       <c r="G357" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="H357">
         <v>163.3333333333333</v>
@@ -10273,10 +10345,10 @@
     </row>
     <row r="358" spans="1:8">
       <c r="A358" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B358" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C358">
         <v>140</v>
@@ -10291,7 +10363,7 @@
         <v>9</v>
       </c>
       <c r="G358" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="H358">
         <v>163.3333333333333</v>
@@ -10299,10 +10371,10 @@
     </row>
     <row r="359" spans="1:8">
       <c r="A359" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B359" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C359">
         <v>120</v>
@@ -10317,7 +10389,7 @@
         <v>9</v>
       </c>
       <c r="G359" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="H359">
         <v>144</v>
@@ -10325,10 +10397,10 @@
     </row>
     <row r="360" spans="1:8">
       <c r="A360" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B360" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C360">
         <v>30</v>
@@ -10343,7 +10415,7 @@
         <v>6</v>
       </c>
       <c r="G360" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="H360">
         <v>38</v>
@@ -10351,10 +10423,10 @@
     </row>
     <row r="361" spans="1:8">
       <c r="A361" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B361" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C361">
         <v>40</v>
@@ -10369,7 +10441,7 @@
         <v>7</v>
       </c>
       <c r="G361" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="H361">
         <v>48</v>
@@ -10377,10 +10449,10 @@
     </row>
     <row r="362" spans="1:8">
       <c r="A362" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B362" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C362">
         <v>50</v>
@@ -10395,7 +10467,7 @@
         <v>8</v>
       </c>
       <c r="G362" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="H362">
         <v>53.33333333333334</v>
@@ -10403,10 +10475,10 @@
     </row>
     <row r="363" spans="1:8">
       <c r="A363" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B363" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C363">
         <v>55</v>
@@ -10421,7 +10493,7 @@
         <v>10</v>
       </c>
       <c r="G363" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="H363">
         <v>56.83333333333334</v>
@@ -10429,10 +10501,10 @@
     </row>
     <row r="364" spans="1:8">
       <c r="A364" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B364" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C364">
         <v>45</v>
@@ -10447,7 +10519,7 @@
         <v>9</v>
       </c>
       <c r="G364" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="H364">
         <v>52.5</v>
@@ -10455,10 +10527,10 @@
     </row>
     <row r="365" spans="1:8">
       <c r="A365" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B365" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C365">
         <v>45</v>
@@ -10473,7 +10545,7 @@
         <v>9.5</v>
       </c>
       <c r="G365" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="H365">
         <v>52.5</v>
@@ -10481,10 +10553,10 @@
     </row>
     <row r="366" spans="1:8">
       <c r="A366" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B366" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C366">
         <v>45</v>
@@ -10499,7 +10571,7 @@
         <v>7</v>
       </c>
       <c r="G366" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="H366">
         <v>57</v>
@@ -10507,10 +10579,10 @@
     </row>
     <row r="367" spans="1:8">
       <c r="A367" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B367" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C367">
         <v>50</v>
@@ -10525,7 +10597,7 @@
         <v>8</v>
       </c>
       <c r="G367" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="H367">
         <v>63.33333333333333</v>
@@ -10533,10 +10605,10 @@
     </row>
     <row r="368" spans="1:8">
       <c r="A368" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B368" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C368">
         <v>50</v>
@@ -10551,7 +10623,7 @@
         <v>8</v>
       </c>
       <c r="G368" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="H368">
         <v>63.33333333333333</v>
@@ -10559,10 +10631,10 @@
     </row>
     <row r="369" spans="1:8">
       <c r="A369" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B369" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C369">
         <v>50</v>
@@ -10577,7 +10649,7 @@
         <v>8</v>
       </c>
       <c r="G369" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="H369">
         <v>63.33333333333333</v>
@@ -10585,10 +10657,10 @@
     </row>
     <row r="370" spans="1:8">
       <c r="A370" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B370" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C370">
         <v>40</v>
@@ -10603,7 +10675,7 @@
         <v>8.5</v>
       </c>
       <c r="G370" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="H370">
         <v>60</v>
@@ -10611,10 +10683,10 @@
     </row>
     <row r="371" spans="1:8">
       <c r="A371" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B371" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C371">
         <v>20</v>
@@ -10629,7 +10701,7 @@
         <v>5</v>
       </c>
       <c r="G371" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="H371">
         <v>25.33333333333333</v>
@@ -10637,10 +10709,10 @@
     </row>
     <row r="372" spans="1:8">
       <c r="A372" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B372" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C372">
         <v>40</v>
@@ -10655,7 +10727,7 @@
         <v>6</v>
       </c>
       <c r="G372" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="H372">
         <v>46.66666666666667</v>
@@ -10663,10 +10735,10 @@
     </row>
     <row r="373" spans="1:8">
       <c r="A373" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B373" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C373">
         <v>50</v>
@@ -10681,7 +10753,7 @@
         <v>7</v>
       </c>
       <c r="G373" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="H373">
         <v>60</v>
@@ -10689,10 +10761,10 @@
     </row>
     <row r="374" spans="1:8">
       <c r="A374" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B374" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C374">
         <v>50</v>
@@ -10707,7 +10779,7 @@
         <v>6.5</v>
       </c>
       <c r="G374" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="H374">
         <v>63.33333333333333</v>
@@ -10715,10 +10787,10 @@
     </row>
     <row r="375" spans="1:8">
       <c r="A375" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B375" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C375">
         <v>60</v>
@@ -10733,7 +10805,7 @@
         <v>7</v>
       </c>
       <c r="G375" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="H375">
         <v>66</v>
@@ -10741,10 +10813,10 @@
     </row>
     <row r="376" spans="1:8">
       <c r="A376" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B376" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C376">
         <v>70</v>
@@ -10759,7 +10831,7 @@
         <v>7.75</v>
       </c>
       <c r="G376" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="H376">
         <v>72.33333333333334</v>
@@ -10767,10 +10839,10 @@
     </row>
     <row r="377" spans="1:8">
       <c r="A377" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B377" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C377">
         <v>75</v>
@@ -10785,7 +10857,7 @@
         <v>8</v>
       </c>
       <c r="G377" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="H377">
         <v>77.50000000000001</v>
@@ -10793,10 +10865,10 @@
     </row>
     <row r="378" spans="1:8">
       <c r="A378" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B378" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C378">
         <v>77.5</v>
@@ -10811,7 +10883,7 @@
         <v>10</v>
       </c>
       <c r="G378" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="H378">
         <v>77.5</v>
@@ -10819,10 +10891,10 @@
     </row>
     <row r="379" spans="1:8">
       <c r="A379" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B379" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C379">
         <v>66.25</v>
@@ -10837,7 +10909,7 @@
         <v>9</v>
       </c>
       <c r="G379" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="H379">
         <v>77.29166666666667</v>
@@ -10845,10 +10917,10 @@
     </row>
     <row r="380" spans="1:8">
       <c r="A380" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B380" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C380">
         <v>60</v>
@@ -10863,7 +10935,7 @@
         <v>8.25</v>
       </c>
       <c r="G380" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="H380">
         <v>70</v>
@@ -10871,10 +10943,10 @@
     </row>
     <row r="381" spans="1:8">
       <c r="A381" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B381" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C381">
         <v>30</v>
@@ -10889,7 +10961,7 @@
         <v>6</v>
       </c>
       <c r="G381" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="H381">
         <v>42</v>
@@ -10897,10 +10969,10 @@
     </row>
     <row r="382" spans="1:8">
       <c r="A382" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B382" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C382">
         <v>50</v>
@@ -10915,7 +10987,7 @@
         <v>8.5</v>
       </c>
       <c r="G382" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="H382">
         <v>63.33333333333333</v>
@@ -10923,10 +10995,10 @@
     </row>
     <row r="383" spans="1:8">
       <c r="A383" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B383" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C383">
         <v>50</v>
@@ -10941,7 +11013,7 @@
         <v>8</v>
       </c>
       <c r="G383" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="H383">
         <v>63.33333333333333</v>
@@ -10949,10 +11021,10 @@
     </row>
     <row r="384" spans="1:8">
       <c r="A384" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B384" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C384">
         <v>50</v>
@@ -10967,7 +11039,7 @@
         <v>10</v>
       </c>
       <c r="G384" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="H384">
         <v>60</v>
@@ -10975,10 +11047,10 @@
     </row>
     <row r="385" spans="1:8">
       <c r="A385" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B385" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C385">
         <v>0</v>
@@ -10993,7 +11065,7 @@
         <v>6</v>
       </c>
       <c r="G385" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="H385">
         <v>0</v>
@@ -11001,10 +11073,10 @@
     </row>
     <row r="386" spans="1:8">
       <c r="A386" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B386" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C386">
         <v>25</v>
@@ -11019,7 +11091,7 @@
         <v>8</v>
       </c>
       <c r="G386" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="H386">
         <v>30</v>
@@ -11027,10 +11099,10 @@
     </row>
     <row r="387" spans="1:8">
       <c r="A387" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B387" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C387">
         <v>25</v>
@@ -11045,7 +11117,7 @@
         <v>8</v>
       </c>
       <c r="G387" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="H387">
         <v>31.66666666666666</v>
@@ -11053,10 +11125,10 @@
     </row>
     <row r="388" spans="1:8">
       <c r="A388" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B388" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C388">
         <v>25</v>
@@ -11071,7 +11143,7 @@
         <v>8.5</v>
       </c>
       <c r="G388" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="H388">
         <v>31.66666666666666</v>
@@ -11079,10 +11151,10 @@
     </row>
     <row r="389" spans="1:8">
       <c r="A389" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B389" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C389">
         <v>45</v>
@@ -11097,7 +11169,7 @@
         <v>6.5</v>
       </c>
       <c r="G389" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H389">
         <v>62.99999999999999</v>
@@ -11105,10 +11177,10 @@
     </row>
     <row r="390" spans="1:8">
       <c r="A390" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B390" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C390">
         <v>60</v>
@@ -11123,7 +11195,7 @@
         <v>8</v>
       </c>
       <c r="G390" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="H390">
         <v>76</v>
@@ -11131,10 +11203,10 @@
     </row>
     <row r="391" spans="1:8">
       <c r="A391" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B391" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C391">
         <v>60</v>
@@ -11149,7 +11221,7 @@
         <v>7.5</v>
       </c>
       <c r="G391" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H391">
         <v>76</v>
@@ -11157,10 +11229,10 @@
     </row>
     <row r="392" spans="1:8">
       <c r="A392" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B392" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C392">
         <v>60</v>
@@ -11175,7 +11247,7 @@
         <v>7.5</v>
       </c>
       <c r="G392" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="H392">
         <v>76</v>
@@ -11183,10 +11255,10 @@
     </row>
     <row r="393" spans="1:8">
       <c r="A393" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B393" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C393">
         <v>60</v>
@@ -11201,7 +11273,7 @@
         <v>9</v>
       </c>
       <c r="G393" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="H393">
         <v>76</v>
@@ -11209,10 +11281,10 @@
     </row>
     <row r="394" spans="1:8">
       <c r="A394" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B394" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C394">
         <v>40</v>
@@ -11227,7 +11299,7 @@
         <v>8</v>
       </c>
       <c r="G394" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="H394">
         <v>53.33333333333333</v>
@@ -11235,10 +11307,10 @@
     </row>
     <row r="395" spans="1:8">
       <c r="A395" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B395" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C395">
         <v>40</v>
@@ -11253,7 +11325,7 @@
         <v>7.5</v>
       </c>
       <c r="G395" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="H395">
         <v>56</v>
@@ -11261,10 +11333,10 @@
     </row>
     <row r="396" spans="1:8">
       <c r="A396" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B396" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C396">
         <v>40</v>
@@ -11279,7 +11351,7 @@
         <v>8</v>
       </c>
       <c r="G396" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="H396">
         <v>56</v>
@@ -11287,10 +11359,10 @@
     </row>
     <row r="397" spans="1:8">
       <c r="A397" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B397" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C397">
         <v>40</v>
@@ -11305,7 +11377,7 @@
         <v>8</v>
       </c>
       <c r="G397" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="H397">
         <v>56</v>
@@ -11313,10 +11385,10 @@
     </row>
     <row r="398" spans="1:8">
       <c r="A398" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B398" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C398">
         <v>40</v>
@@ -11331,7 +11403,7 @@
         <v>8.5</v>
       </c>
       <c r="G398" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="H398">
         <v>56</v>
@@ -11339,10 +11411,10 @@
     </row>
     <row r="399" spans="1:8">
       <c r="A399" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B399" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C399">
         <v>40</v>
@@ -11357,7 +11429,7 @@
         <v>9</v>
       </c>
       <c r="G399" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="H399">
         <v>56</v>
@@ -11365,10 +11437,10 @@
     </row>
     <row r="400" spans="1:8">
       <c r="A400" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B400" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C400">
         <v>20</v>
@@ -11383,7 +11455,7 @@
         <v>5</v>
       </c>
       <c r="G400" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="H400">
         <v>25.33333333333333</v>
@@ -11391,10 +11463,10 @@
     </row>
     <row r="401" spans="1:8">
       <c r="A401" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B401" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C401">
         <v>70</v>
@@ -11409,7 +11481,7 @@
         <v>6</v>
       </c>
       <c r="G401" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="H401">
         <v>81.66666666666667</v>
@@ -11417,10 +11489,10 @@
     </row>
     <row r="402" spans="1:8">
       <c r="A402" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B402" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C402">
         <v>120</v>
@@ -11435,7 +11507,7 @@
         <v>7.5</v>
       </c>
       <c r="G402" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="H402">
         <v>124</v>
@@ -11443,10 +11515,10 @@
     </row>
     <row r="403" spans="1:8">
       <c r="A403" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B403" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C403">
         <v>110</v>
@@ -11461,7 +11533,7 @@
         <v>8.5</v>
       </c>
       <c r="G403" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="H403">
         <v>128.3333333333333</v>
@@ -11469,10 +11541,10 @@
     </row>
     <row r="404" spans="1:8">
       <c r="A404" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B404" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C404">
         <v>110</v>
@@ -11487,7 +11559,7 @@
         <v>10</v>
       </c>
       <c r="G404" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="H404">
         <v>124.6666666666667</v>
@@ -11495,10 +11567,10 @@
     </row>
     <row r="405" spans="1:8">
       <c r="A405" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B405" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C405">
         <v>100</v>
@@ -11513,7 +11585,7 @@
         <v>9.5</v>
       </c>
       <c r="G405" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="H405">
         <v>110</v>
@@ -11521,10 +11593,10 @@
     </row>
     <row r="406" spans="1:8">
       <c r="A406" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B406" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C406">
         <v>40</v>
@@ -11539,7 +11611,7 @@
         <v>6</v>
       </c>
       <c r="G406" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="H406">
         <v>60</v>
@@ -11547,10 +11619,10 @@
     </row>
     <row r="407" spans="1:8">
       <c r="A407" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B407" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C407">
         <v>50</v>
@@ -11565,7 +11637,7 @@
         <v>7</v>
       </c>
       <c r="G407" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="H407">
         <v>70</v>
@@ -11573,10 +11645,10 @@
     </row>
     <row r="408" spans="1:8">
       <c r="A408" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B408" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C408">
         <v>50</v>
@@ -11591,7 +11663,7 @@
         <v>7.5</v>
       </c>
       <c r="G408" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="H408">
         <v>70</v>
@@ -11599,10 +11671,10 @@
     </row>
     <row r="409" spans="1:8">
       <c r="A409" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B409" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C409">
         <v>50</v>
@@ -11617,7 +11689,7 @@
         <v>8.5</v>
       </c>
       <c r="G409" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="H409">
         <v>70</v>
@@ -11625,10 +11697,10 @@
     </row>
     <row r="410" spans="1:8">
       <c r="A410" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B410" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C410">
         <v>30</v>
@@ -11643,7 +11715,7 @@
         <v>6</v>
       </c>
       <c r="G410" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="H410">
         <v>40</v>
@@ -11651,10 +11723,10 @@
     </row>
     <row r="411" spans="1:8">
       <c r="A411" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B411" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C411">
         <v>30</v>
@@ -11669,7 +11741,7 @@
         <v>6.5</v>
       </c>
       <c r="G411" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="H411">
         <v>40</v>
@@ -11677,10 +11749,10 @@
     </row>
     <row r="412" spans="1:8">
       <c r="A412" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B412" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C412">
         <v>40</v>
@@ -11695,7 +11767,7 @@
         <v>8.5</v>
       </c>
       <c r="G412" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="H412">
         <v>53.33333333333333</v>
@@ -11703,10 +11775,10 @@
     </row>
     <row r="413" spans="1:8">
       <c r="A413" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B413" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C413">
         <v>40</v>
@@ -11721,7 +11793,7 @@
         <v>10</v>
       </c>
       <c r="G413" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="H413">
         <v>50.66666666666666</v>
@@ -11729,10 +11801,10 @@
     </row>
     <row r="414" spans="1:8">
       <c r="A414" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B414" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C414">
         <v>40</v>
@@ -11747,7 +11819,7 @@
         <v>9</v>
       </c>
       <c r="G414" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="H414">
         <v>50.66666666666666</v>
@@ -11755,10 +11827,10 @@
     </row>
     <row r="415" spans="1:8">
       <c r="A415" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B415" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C415">
         <v>30</v>
@@ -11773,7 +11845,7 @@
         <v>8</v>
       </c>
       <c r="G415" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="H415">
         <v>35</v>
@@ -11781,10 +11853,10 @@
     </row>
     <row r="416" spans="1:8">
       <c r="A416" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B416" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C416">
         <v>30</v>
@@ -11799,18 +11871,18 @@
         <v>8</v>
       </c>
       <c r="G416" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="H416">
         <v>42</v>
       </c>
     </row>
-    <row r="417" spans="1:8">
+    <row r="417" spans="1:9">
       <c r="A417" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B417" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C417">
         <v>30</v>
@@ -11825,18 +11897,18 @@
         <v>8.5</v>
       </c>
       <c r="G417" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="H417">
         <v>36</v>
       </c>
     </row>
-    <row r="418" spans="1:8">
+    <row r="418" spans="1:9">
       <c r="A418" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B418" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C418">
         <v>30</v>
@@ -11851,18 +11923,18 @@
         <v>8.5</v>
       </c>
       <c r="G418" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="H418">
         <v>42</v>
       </c>
     </row>
-    <row r="419" spans="1:8">
+    <row r="419" spans="1:9">
       <c r="A419" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B419" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C419">
         <v>30</v>
@@ -11877,18 +11949,18 @@
         <v>9</v>
       </c>
       <c r="G419" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="H419">
         <v>36</v>
       </c>
     </row>
-    <row r="420" spans="1:8">
+    <row r="420" spans="1:9">
       <c r="A420" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B420" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C420">
         <v>30</v>
@@ -11903,10 +11975,608 @@
         <v>9</v>
       </c>
       <c r="G420" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="H420">
         <v>42</v>
+      </c>
+    </row>
+    <row r="421" spans="1:9">
+      <c r="A421" t="s">
+        <v>73</v>
+      </c>
+      <c r="B421" t="s">
+        <v>109</v>
+      </c>
+      <c r="C421">
+        <v>20</v>
+      </c>
+      <c r="D421">
+        <v>8</v>
+      </c>
+      <c r="E421">
+        <v>160</v>
+      </c>
+      <c r="G421" t="s">
+        <v>339</v>
+      </c>
+      <c r="H421">
+        <v>25.33333333333333</v>
+      </c>
+      <c r="I421">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="422" spans="1:9">
+      <c r="A422" t="s">
+        <v>73</v>
+      </c>
+      <c r="B422" t="s">
+        <v>109</v>
+      </c>
+      <c r="C422">
+        <v>70</v>
+      </c>
+      <c r="D422">
+        <v>5</v>
+      </c>
+      <c r="E422">
+        <v>350</v>
+      </c>
+      <c r="G422" t="s">
+        <v>340</v>
+      </c>
+      <c r="H422">
+        <v>81.66666666666667</v>
+      </c>
+      <c r="I422">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="423" spans="1:9">
+      <c r="A423" t="s">
+        <v>73</v>
+      </c>
+      <c r="B423" t="s">
+        <v>109</v>
+      </c>
+      <c r="C423">
+        <v>120</v>
+      </c>
+      <c r="D423">
+        <v>3</v>
+      </c>
+      <c r="E423">
+        <v>360</v>
+      </c>
+      <c r="G423" t="s">
+        <v>341</v>
+      </c>
+      <c r="H423">
+        <v>132</v>
+      </c>
+      <c r="I423">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="424" spans="1:9">
+      <c r="A424" t="s">
+        <v>73</v>
+      </c>
+      <c r="B424" t="s">
+        <v>109</v>
+      </c>
+      <c r="C424">
+        <v>90</v>
+      </c>
+      <c r="D424">
+        <v>20</v>
+      </c>
+      <c r="E424">
+        <v>1800</v>
+      </c>
+      <c r="G424" t="s">
+        <v>342</v>
+      </c>
+      <c r="H424">
+        <v>150</v>
+      </c>
+      <c r="I424">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="425" spans="1:9">
+      <c r="A425" t="s">
+        <v>73</v>
+      </c>
+      <c r="B425" t="s">
+        <v>89</v>
+      </c>
+      <c r="C425">
+        <v>30</v>
+      </c>
+      <c r="D425">
+        <v>8</v>
+      </c>
+      <c r="E425">
+        <v>240</v>
+      </c>
+      <c r="G425" t="s">
+        <v>224</v>
+      </c>
+      <c r="H425">
+        <v>38</v>
+      </c>
+      <c r="I425">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="426" spans="1:9">
+      <c r="A426" t="s">
+        <v>73</v>
+      </c>
+      <c r="B426" t="s">
+        <v>74</v>
+      </c>
+      <c r="C426">
+        <v>40</v>
+      </c>
+      <c r="D426">
+        <v>3</v>
+      </c>
+      <c r="E426">
+        <v>120</v>
+      </c>
+      <c r="G426" t="s">
+        <v>343</v>
+      </c>
+      <c r="H426">
+        <v>44</v>
+      </c>
+      <c r="I426">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="427" spans="1:9">
+      <c r="A427" t="s">
+        <v>73</v>
+      </c>
+      <c r="B427" t="s">
+        <v>74</v>
+      </c>
+      <c r="C427">
+        <v>45</v>
+      </c>
+      <c r="D427">
+        <v>3</v>
+      </c>
+      <c r="E427">
+        <v>135</v>
+      </c>
+      <c r="G427" t="s">
+        <v>344</v>
+      </c>
+      <c r="H427">
+        <v>49.50000000000001</v>
+      </c>
+      <c r="I427">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="428" spans="1:9">
+      <c r="A428" t="s">
+        <v>73</v>
+      </c>
+      <c r="B428" t="s">
+        <v>74</v>
+      </c>
+      <c r="C428">
+        <v>45</v>
+      </c>
+      <c r="D428">
+        <v>8</v>
+      </c>
+      <c r="E428">
+        <v>360</v>
+      </c>
+      <c r="G428" t="s">
+        <v>345</v>
+      </c>
+      <c r="H428">
+        <v>57</v>
+      </c>
+      <c r="I428">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="429" spans="1:9">
+      <c r="A429" t="s">
+        <v>73</v>
+      </c>
+      <c r="B429" t="s">
+        <v>74</v>
+      </c>
+      <c r="C429">
+        <v>45</v>
+      </c>
+      <c r="D429">
+        <v>8</v>
+      </c>
+      <c r="E429">
+        <v>360</v>
+      </c>
+      <c r="G429" t="s">
+        <v>346</v>
+      </c>
+      <c r="H429">
+        <v>57</v>
+      </c>
+      <c r="I429">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="430" spans="1:9">
+      <c r="A430" t="s">
+        <v>73</v>
+      </c>
+      <c r="B430" t="s">
+        <v>74</v>
+      </c>
+      <c r="C430">
+        <v>45</v>
+      </c>
+      <c r="D430">
+        <v>8</v>
+      </c>
+      <c r="E430">
+        <v>360</v>
+      </c>
+      <c r="G430" t="s">
+        <v>347</v>
+      </c>
+      <c r="H430">
+        <v>57</v>
+      </c>
+      <c r="I430">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="431" spans="1:9">
+      <c r="A431" t="s">
+        <v>73</v>
+      </c>
+      <c r="B431" t="s">
+        <v>123</v>
+      </c>
+      <c r="C431">
+        <v>40</v>
+      </c>
+      <c r="D431">
+        <v>12</v>
+      </c>
+      <c r="E431">
+        <v>480</v>
+      </c>
+      <c r="G431" t="s">
+        <v>348</v>
+      </c>
+      <c r="H431">
+        <v>56</v>
+      </c>
+      <c r="I431">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="432" spans="1:9">
+      <c r="A432" t="s">
+        <v>73</v>
+      </c>
+      <c r="B432" t="s">
+        <v>123</v>
+      </c>
+      <c r="C432">
+        <v>50</v>
+      </c>
+      <c r="D432">
+        <v>6</v>
+      </c>
+      <c r="E432">
+        <v>300</v>
+      </c>
+      <c r="G432" t="s">
+        <v>349</v>
+      </c>
+      <c r="H432">
+        <v>60</v>
+      </c>
+      <c r="I432">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="433" spans="1:9">
+      <c r="A433" t="s">
+        <v>73</v>
+      </c>
+      <c r="B433" t="s">
+        <v>123</v>
+      </c>
+      <c r="C433">
+        <v>60</v>
+      </c>
+      <c r="D433">
+        <v>6</v>
+      </c>
+      <c r="E433">
+        <v>360</v>
+      </c>
+      <c r="G433" t="s">
+        <v>350</v>
+      </c>
+      <c r="H433">
+        <v>72</v>
+      </c>
+      <c r="I433">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="434" spans="1:9">
+      <c r="A434" t="s">
+        <v>73</v>
+      </c>
+      <c r="B434" t="s">
+        <v>123</v>
+      </c>
+      <c r="C434">
+        <v>60</v>
+      </c>
+      <c r="D434">
+        <v>6</v>
+      </c>
+      <c r="E434">
+        <v>360</v>
+      </c>
+      <c r="G434" t="s">
+        <v>351</v>
+      </c>
+      <c r="H434">
+        <v>72</v>
+      </c>
+      <c r="I434">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="435" spans="1:9">
+      <c r="A435" t="s">
+        <v>73</v>
+      </c>
+      <c r="B435" t="s">
+        <v>123</v>
+      </c>
+      <c r="C435">
+        <v>60</v>
+      </c>
+      <c r="D435">
+        <v>6</v>
+      </c>
+      <c r="E435">
+        <v>360</v>
+      </c>
+      <c r="G435" t="s">
+        <v>352</v>
+      </c>
+      <c r="H435">
+        <v>72</v>
+      </c>
+      <c r="I435">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="436" spans="1:9">
+      <c r="A436" t="s">
+        <v>73</v>
+      </c>
+      <c r="B436" t="s">
+        <v>123</v>
+      </c>
+      <c r="C436">
+        <v>60</v>
+      </c>
+      <c r="D436">
+        <v>6</v>
+      </c>
+      <c r="E436">
+        <v>360</v>
+      </c>
+      <c r="G436" t="s">
+        <v>353</v>
+      </c>
+      <c r="H436">
+        <v>72</v>
+      </c>
+      <c r="I436">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="437" spans="1:9">
+      <c r="A437" t="s">
+        <v>73</v>
+      </c>
+      <c r="B437" t="s">
+        <v>91</v>
+      </c>
+      <c r="C437">
+        <v>20</v>
+      </c>
+      <c r="D437">
+        <v>8</v>
+      </c>
+      <c r="E437">
+        <v>160</v>
+      </c>
+      <c r="G437" t="s">
+        <v>354</v>
+      </c>
+      <c r="H437">
+        <v>25.33333333333333</v>
+      </c>
+      <c r="I437">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="438" spans="1:9">
+      <c r="A438" t="s">
+        <v>73</v>
+      </c>
+      <c r="B438" t="s">
+        <v>91</v>
+      </c>
+      <c r="C438">
+        <v>30</v>
+      </c>
+      <c r="D438">
+        <v>5</v>
+      </c>
+      <c r="E438">
+        <v>150</v>
+      </c>
+      <c r="G438" t="s">
+        <v>355</v>
+      </c>
+      <c r="H438">
+        <v>35</v>
+      </c>
+      <c r="I438">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="439" spans="1:9">
+      <c r="A439" t="s">
+        <v>73</v>
+      </c>
+      <c r="B439" t="s">
+        <v>137</v>
+      </c>
+      <c r="C439">
+        <v>20</v>
+      </c>
+      <c r="D439">
+        <v>12</v>
+      </c>
+      <c r="E439">
+        <v>240</v>
+      </c>
+      <c r="G439" t="s">
+        <v>356</v>
+      </c>
+      <c r="H439">
+        <v>28</v>
+      </c>
+      <c r="I439">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="440" spans="1:9">
+      <c r="A440" t="s">
+        <v>73</v>
+      </c>
+      <c r="B440" t="s">
+        <v>137</v>
+      </c>
+      <c r="C440">
+        <v>30</v>
+      </c>
+      <c r="D440">
+        <v>8</v>
+      </c>
+      <c r="E440">
+        <v>240</v>
+      </c>
+      <c r="G440" t="s">
+        <v>357</v>
+      </c>
+      <c r="H440">
+        <v>38</v>
+      </c>
+      <c r="I440">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="441" spans="1:9">
+      <c r="A441" t="s">
+        <v>73</v>
+      </c>
+      <c r="B441" t="s">
+        <v>137</v>
+      </c>
+      <c r="C441">
+        <v>40</v>
+      </c>
+      <c r="D441">
+        <v>3</v>
+      </c>
+      <c r="E441">
+        <v>120</v>
+      </c>
+      <c r="G441" t="s">
+        <v>186</v>
+      </c>
+      <c r="H441">
+        <v>44</v>
+      </c>
+      <c r="I441">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="442" spans="1:9">
+      <c r="A442" t="s">
+        <v>73</v>
+      </c>
+      <c r="B442" t="s">
+        <v>137</v>
+      </c>
+      <c r="C442">
+        <v>30</v>
+      </c>
+      <c r="D442">
+        <v>8</v>
+      </c>
+      <c r="E442">
+        <v>240</v>
+      </c>
+      <c r="G442" t="s">
+        <v>315</v>
+      </c>
+      <c r="H442">
+        <v>38</v>
+      </c>
+      <c r="I442">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="443" spans="1:9">
+      <c r="A443" t="s">
+        <v>73</v>
+      </c>
+      <c r="B443" t="s">
+        <v>137</v>
+      </c>
+      <c r="C443">
+        <v>30</v>
+      </c>
+      <c r="D443">
+        <v>8</v>
+      </c>
+      <c r="E443">
+        <v>240</v>
+      </c>
+      <c r="G443" t="s">
+        <v>358</v>
+      </c>
+      <c r="H443">
+        <v>38</v>
+      </c>
+      <c r="I443">
+        <v>8.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/workout_log.xlsx
+++ b/data/workout_log.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1204" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1246" uniqueCount="373">
   <si>
     <t>Timestamp</t>
   </si>
@@ -238,6 +238,9 @@
     <t>2026-03-11 19:15:00</t>
   </si>
   <si>
+    <t>2026-03-14 09:00:00</t>
+  </si>
+  <si>
     <t>Overhead Press</t>
   </si>
   <si>
@@ -1091,6 +1094,45 @@
   </si>
   <si>
     <t>Final set of session</t>
+  </si>
+  <si>
+    <t>Progressive warm-up / initial working set</t>
+  </si>
+  <si>
+    <t>Heavy single; testing top-end stability</t>
+  </si>
+  <si>
+    <t>Heavy triple; significant intensity increase</t>
+  </si>
+  <si>
+    <t>Volume back-off; building capacity for the 20-rep goal</t>
+  </si>
+  <si>
+    <t>Volume accumulation; repeating the high-rep effort</t>
+  </si>
+  <si>
+    <t>Initial set; focusing on overhead mobility</t>
+  </si>
+  <si>
+    <t>Standard OHP; smooth bar path</t>
+  </si>
+  <si>
+    <t>Submaximal single; focus on explosive concentric</t>
+  </si>
+  <si>
+    <t>Incremental single; technical build-up</t>
+  </si>
+  <si>
+    <t>Heavy technical single; focus on core rigidity</t>
+  </si>
+  <si>
+    <t>Failed attempt; technical breakdown at sticking point</t>
+  </si>
+  <si>
+    <t>Back-off set for volume post-failure</t>
+  </si>
+  <si>
+    <t>Final high-effort volume set</t>
   </si>
 </sst>
 </file>
@@ -1448,7 +1490,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I443"/>
+  <dimension ref="A1:I457"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -1485,7 +1527,7 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C2">
         <v>30</v>
@@ -1500,7 +1542,7 @@
         <v>4</v>
       </c>
       <c r="G2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H2">
         <v>40</v>
@@ -1511,7 +1553,7 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C3">
         <v>30</v>
@@ -1534,7 +1576,7 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C4">
         <v>30</v>
@@ -1557,7 +1599,7 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C5">
         <v>30</v>
@@ -1580,7 +1622,7 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C6">
         <v>60</v>
@@ -1595,7 +1637,7 @@
         <v>5</v>
       </c>
       <c r="G6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H6">
         <v>76</v>
@@ -1606,7 +1648,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C7">
         <v>100</v>
@@ -1621,7 +1663,7 @@
         <v>6</v>
       </c>
       <c r="G7" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H7">
         <v>110</v>
@@ -1632,7 +1674,7 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C8">
         <v>100</v>
@@ -1655,7 +1697,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C9">
         <v>100</v>
@@ -1678,7 +1720,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C10">
         <v>32</v>
@@ -1693,7 +1735,7 @@
         <v>3</v>
       </c>
       <c r="G10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H10">
         <v>44.8</v>
@@ -1704,7 +1746,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C11">
         <v>40</v>
@@ -1719,7 +1761,7 @@
         <v>5.5</v>
       </c>
       <c r="G11" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H11">
         <v>50.66666666666666</v>
@@ -1730,7 +1772,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C12">
         <v>40</v>
@@ -1753,7 +1795,7 @@
         <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C13">
         <v>40</v>
@@ -1768,7 +1810,7 @@
         <v>9</v>
       </c>
       <c r="G13" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H13">
         <v>48</v>
@@ -1779,7 +1821,7 @@
         <v>9</v>
       </c>
       <c r="B14" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C14">
         <v>20</v>
@@ -1802,7 +1844,7 @@
         <v>9</v>
       </c>
       <c r="B15" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C15">
         <v>20</v>
@@ -1825,7 +1867,7 @@
         <v>9</v>
       </c>
       <c r="B16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C16">
         <v>20</v>
@@ -1848,7 +1890,7 @@
         <v>9</v>
       </c>
       <c r="B17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C17">
         <v>20</v>
@@ -1863,7 +1905,7 @@
         <v>8</v>
       </c>
       <c r="G17" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H17">
         <v>26.66666666666666</v>
@@ -1874,7 +1916,7 @@
         <v>9</v>
       </c>
       <c r="B18" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C18">
         <v>20</v>
@@ -1889,7 +1931,7 @@
         <v>8</v>
       </c>
       <c r="G18" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H18">
         <v>26.66666666666666</v>
@@ -1900,7 +1942,7 @@
         <v>9</v>
       </c>
       <c r="B19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C19">
         <v>20</v>
@@ -1915,7 +1957,7 @@
         <v>8</v>
       </c>
       <c r="G19" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H19">
         <v>25.33333333333333</v>
@@ -1926,7 +1968,7 @@
         <v>9</v>
       </c>
       <c r="B20" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C20">
         <v>20</v>
@@ -1941,7 +1983,7 @@
         <v>8</v>
       </c>
       <c r="G20" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H20">
         <v>25.33333333333333</v>
@@ -1952,7 +1994,7 @@
         <v>10</v>
       </c>
       <c r="B21" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -1967,7 +2009,7 @@
         <v>7</v>
       </c>
       <c r="G21" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H21">
         <v>0</v>
@@ -1978,7 +2020,7 @@
         <v>10</v>
       </c>
       <c r="B22" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C22">
         <v>30</v>
@@ -2001,7 +2043,7 @@
         <v>10</v>
       </c>
       <c r="B23" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C23">
         <v>30</v>
@@ -2024,7 +2066,7 @@
         <v>10</v>
       </c>
       <c r="B24" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C24">
         <v>30</v>
@@ -2047,7 +2089,7 @@
         <v>10</v>
       </c>
       <c r="B25" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C25">
         <v>30</v>
@@ -2070,7 +2112,7 @@
         <v>10</v>
       </c>
       <c r="B26" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C26">
         <v>30</v>
@@ -2093,7 +2135,7 @@
         <v>10</v>
       </c>
       <c r="B27" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C27">
         <v>30</v>
@@ -2116,7 +2158,7 @@
         <v>10</v>
       </c>
       <c r="B28" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C28">
         <v>30</v>
@@ -2139,7 +2181,7 @@
         <v>10</v>
       </c>
       <c r="B29" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C29">
         <v>30</v>
@@ -2162,7 +2204,7 @@
         <v>10</v>
       </c>
       <c r="B30" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C30">
         <v>30</v>
@@ -2185,7 +2227,7 @@
         <v>10</v>
       </c>
       <c r="B31" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C31">
         <v>70</v>
@@ -2208,7 +2250,7 @@
         <v>10</v>
       </c>
       <c r="B32" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C32">
         <v>70</v>
@@ -2231,7 +2273,7 @@
         <v>10</v>
       </c>
       <c r="B33" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C33">
         <v>70</v>
@@ -2254,7 +2296,7 @@
         <v>10</v>
       </c>
       <c r="B34" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C34">
         <v>23</v>
@@ -2269,7 +2311,7 @@
         <v>7</v>
       </c>
       <c r="G34" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H34">
         <v>38.33333333333333</v>
@@ -2280,7 +2322,7 @@
         <v>10</v>
       </c>
       <c r="B35" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C35">
         <v>23</v>
@@ -2295,7 +2337,7 @@
         <v>7</v>
       </c>
       <c r="G35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H35">
         <v>38.33333333333333</v>
@@ -2306,7 +2348,7 @@
         <v>10</v>
       </c>
       <c r="B36" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C36">
         <v>23</v>
@@ -2321,7 +2363,7 @@
         <v>9</v>
       </c>
       <c r="G36" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H36">
         <v>38.33333333333333</v>
@@ -2332,7 +2374,7 @@
         <v>10</v>
       </c>
       <c r="B37" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C37">
         <v>23</v>
@@ -2347,7 +2389,7 @@
         <v>10</v>
       </c>
       <c r="G37" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H37">
         <v>32.2</v>
@@ -2358,7 +2400,7 @@
         <v>10</v>
       </c>
       <c r="B38" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C38">
         <v>20</v>
@@ -2381,7 +2423,7 @@
         <v>10</v>
       </c>
       <c r="B39" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C39">
         <v>20</v>
@@ -2404,7 +2446,7 @@
         <v>10</v>
       </c>
       <c r="B40" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C40">
         <v>20</v>
@@ -2427,7 +2469,7 @@
         <v>11</v>
       </c>
       <c r="B41" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C41">
         <v>36</v>
@@ -2442,7 +2484,7 @@
         <v>5</v>
       </c>
       <c r="G41" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H41">
         <v>48</v>
@@ -2453,7 +2495,7 @@
         <v>11</v>
       </c>
       <c r="B42" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C42">
         <v>44</v>
@@ -2468,7 +2510,7 @@
         <v>7</v>
       </c>
       <c r="G42" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H42">
         <v>52.8</v>
@@ -2479,7 +2521,7 @@
         <v>11</v>
       </c>
       <c r="B43" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C43">
         <v>44</v>
@@ -2494,7 +2536,7 @@
         <v>7.5</v>
       </c>
       <c r="G43" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H43">
         <v>52.8</v>
@@ -2505,7 +2547,7 @@
         <v>11</v>
       </c>
       <c r="B44" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C44">
         <v>44</v>
@@ -2520,7 +2562,7 @@
         <v>8</v>
       </c>
       <c r="G44" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H44">
         <v>52.8</v>
@@ -2531,7 +2573,7 @@
         <v>11</v>
       </c>
       <c r="B45" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C45">
         <v>60</v>
@@ -2554,7 +2596,7 @@
         <v>11</v>
       </c>
       <c r="B46" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C46">
         <v>100</v>
@@ -2577,7 +2619,7 @@
         <v>11</v>
       </c>
       <c r="B47" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C47">
         <v>130</v>
@@ -2600,7 +2642,7 @@
         <v>11</v>
       </c>
       <c r="B48" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C48">
         <v>140</v>
@@ -2615,7 +2657,7 @@
         <v>10</v>
       </c>
       <c r="G48" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H48">
         <v>144.6666666666667</v>
@@ -2626,7 +2668,7 @@
         <v>11</v>
       </c>
       <c r="B49" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C49">
         <v>130</v>
@@ -2649,7 +2691,7 @@
         <v>11</v>
       </c>
       <c r="B50" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C50">
         <v>100</v>
@@ -2672,7 +2714,7 @@
         <v>11</v>
       </c>
       <c r="B51" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C51">
         <v>100</v>
@@ -2687,7 +2729,7 @@
         <v>9</v>
       </c>
       <c r="G51" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H51">
         <v>133.3333333333333</v>
@@ -2698,7 +2740,7 @@
         <v>11</v>
       </c>
       <c r="B52" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C52">
         <v>20</v>
@@ -2713,7 +2755,7 @@
         <v>8</v>
       </c>
       <c r="G52" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H52">
         <v>26.66666666666666</v>
@@ -2724,7 +2766,7 @@
         <v>11</v>
       </c>
       <c r="B53" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C53">
         <v>20</v>
@@ -2739,7 +2781,7 @@
         <v>9</v>
       </c>
       <c r="G53" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H53">
         <v>26.66666666666666</v>
@@ -2750,7 +2792,7 @@
         <v>11</v>
       </c>
       <c r="B54" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C54">
         <v>30</v>
@@ -2773,7 +2815,7 @@
         <v>11</v>
       </c>
       <c r="B55" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C55">
         <v>40</v>
@@ -2796,7 +2838,7 @@
         <v>11</v>
       </c>
       <c r="B56" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C56">
         <v>40</v>
@@ -2819,7 +2861,7 @@
         <v>11</v>
       </c>
       <c r="B57" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C57">
         <v>40</v>
@@ -2842,7 +2884,7 @@
         <v>11</v>
       </c>
       <c r="B58" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C58">
         <v>45</v>
@@ -2865,7 +2907,7 @@
         <v>11</v>
       </c>
       <c r="B59" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C59">
         <v>45</v>
@@ -2888,7 +2930,7 @@
         <v>11</v>
       </c>
       <c r="B60" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C60">
         <v>50</v>
@@ -2903,7 +2945,7 @@
         <v>7.5</v>
       </c>
       <c r="G60" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H60">
         <v>63.33333333333333</v>
@@ -2914,7 +2956,7 @@
         <v>11</v>
       </c>
       <c r="B61" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C61">
         <v>50</v>
@@ -2929,7 +2971,7 @@
         <v>7.5</v>
       </c>
       <c r="G61" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H61">
         <v>63.33333333333333</v>
@@ -2940,7 +2982,7 @@
         <v>11</v>
       </c>
       <c r="B62" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C62">
         <v>50</v>
@@ -2955,7 +2997,7 @@
         <v>8.5</v>
       </c>
       <c r="G62" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H62">
         <v>63.33333333333333</v>
@@ -2966,7 +3008,7 @@
         <v>11</v>
       </c>
       <c r="B63" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C63">
         <v>50</v>
@@ -2981,7 +3023,7 @@
         <v>8.5</v>
       </c>
       <c r="G63" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H63">
         <v>63.33333333333333</v>
@@ -2992,7 +3034,7 @@
         <v>11</v>
       </c>
       <c r="B64" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C64">
         <v>50</v>
@@ -3007,7 +3049,7 @@
         <v>9</v>
       </c>
       <c r="G64" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H64">
         <v>63.33333333333333</v>
@@ -3018,7 +3060,7 @@
         <v>11</v>
       </c>
       <c r="B65" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C65">
         <v>50</v>
@@ -3033,7 +3075,7 @@
         <v>9</v>
       </c>
       <c r="G65" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H65">
         <v>63.33333333333333</v>
@@ -3044,7 +3086,7 @@
         <v>12</v>
       </c>
       <c r="B66" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C66">
         <v>60</v>
@@ -3067,7 +3109,7 @@
         <v>12</v>
       </c>
       <c r="B67" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C67">
         <v>100</v>
@@ -3090,7 +3132,7 @@
         <v>12</v>
       </c>
       <c r="B68" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C68">
         <v>100</v>
@@ -3113,7 +3155,7 @@
         <v>12</v>
       </c>
       <c r="B69" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C69">
         <v>60</v>
@@ -3136,7 +3178,7 @@
         <v>12</v>
       </c>
       <c r="B70" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C70">
         <v>100</v>
@@ -3159,7 +3201,7 @@
         <v>12</v>
       </c>
       <c r="B71" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C71">
         <v>80</v>
@@ -3182,7 +3224,7 @@
         <v>12</v>
       </c>
       <c r="B72" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C72">
         <v>80</v>
@@ -3205,7 +3247,7 @@
         <v>12</v>
       </c>
       <c r="B73" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C73">
         <v>20</v>
@@ -3228,7 +3270,7 @@
         <v>12</v>
       </c>
       <c r="B74" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C74">
         <v>30</v>
@@ -3251,7 +3293,7 @@
         <v>12</v>
       </c>
       <c r="B75" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C75">
         <v>35</v>
@@ -3274,7 +3316,7 @@
         <v>12</v>
       </c>
       <c r="B76" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C76">
         <v>35</v>
@@ -3289,7 +3331,7 @@
         <v>10</v>
       </c>
       <c r="G76" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H76">
         <v>43.16666666666667</v>
@@ -3300,7 +3342,7 @@
         <v>12</v>
       </c>
       <c r="B77" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C77">
         <v>30</v>
@@ -3323,7 +3365,7 @@
         <v>12</v>
       </c>
       <c r="B78" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C78">
         <v>30</v>
@@ -3346,7 +3388,7 @@
         <v>12</v>
       </c>
       <c r="B79" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C79">
         <v>50</v>
@@ -3369,7 +3411,7 @@
         <v>12</v>
       </c>
       <c r="B80" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C80">
         <v>40</v>
@@ -3392,7 +3434,7 @@
         <v>12</v>
       </c>
       <c r="B81" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C81">
         <v>22</v>
@@ -3415,7 +3457,7 @@
         <v>12</v>
       </c>
       <c r="B82" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C82">
         <v>22</v>
@@ -3438,7 +3480,7 @@
         <v>12</v>
       </c>
       <c r="B83" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C83">
         <v>22</v>
@@ -3461,7 +3503,7 @@
         <v>13</v>
       </c>
       <c r="B84" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C84">
         <v>20</v>
@@ -3476,7 +3518,7 @@
         <v>4</v>
       </c>
       <c r="G84" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H84">
         <v>28</v>
@@ -3487,7 +3529,7 @@
         <v>13</v>
       </c>
       <c r="B85" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C85">
         <v>40</v>
@@ -3510,7 +3552,7 @@
         <v>13</v>
       </c>
       <c r="B86" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C86">
         <v>50</v>
@@ -3533,7 +3575,7 @@
         <v>13</v>
       </c>
       <c r="B87" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C87">
         <v>60</v>
@@ -3556,7 +3598,7 @@
         <v>13</v>
       </c>
       <c r="B88" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C88">
         <v>60</v>
@@ -3579,7 +3621,7 @@
         <v>13</v>
       </c>
       <c r="B89" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C89">
         <v>60</v>
@@ -3594,7 +3636,7 @@
         <v>9</v>
       </c>
       <c r="G89" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H89">
         <v>64</v>
@@ -3605,7 +3647,7 @@
         <v>13</v>
       </c>
       <c r="B90" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C90">
         <v>40</v>
@@ -3620,7 +3662,7 @@
         <v>8</v>
       </c>
       <c r="G90" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H90">
         <v>60</v>
@@ -3631,7 +3673,7 @@
         <v>13</v>
       </c>
       <c r="B91" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C91">
         <v>16</v>
@@ -3646,7 +3688,7 @@
         <v>7</v>
       </c>
       <c r="G91" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H91">
         <v>21.33333333333333</v>
@@ -3657,7 +3699,7 @@
         <v>13</v>
       </c>
       <c r="B92" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C92">
         <v>16</v>
@@ -3672,7 +3714,7 @@
         <v>7</v>
       </c>
       <c r="G92" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H92">
         <v>21.33333333333333</v>
@@ -3683,7 +3725,7 @@
         <v>13</v>
       </c>
       <c r="B93" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C93">
         <v>16</v>
@@ -3698,7 +3740,7 @@
         <v>8</v>
       </c>
       <c r="G93" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H93">
         <v>21.33333333333333</v>
@@ -3709,7 +3751,7 @@
         <v>13</v>
       </c>
       <c r="B94" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C94">
         <v>16</v>
@@ -3724,7 +3766,7 @@
         <v>8</v>
       </c>
       <c r="G94" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H94">
         <v>21.33333333333333</v>
@@ -3735,7 +3777,7 @@
         <v>13</v>
       </c>
       <c r="B95" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C95">
         <v>16</v>
@@ -3750,7 +3792,7 @@
         <v>8.5</v>
       </c>
       <c r="G95" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H95">
         <v>21.33333333333333</v>
@@ -3761,7 +3803,7 @@
         <v>13</v>
       </c>
       <c r="B96" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C96">
         <v>16</v>
@@ -3776,7 +3818,7 @@
         <v>8.5</v>
       </c>
       <c r="G96" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H96">
         <v>21.33333333333333</v>
@@ -3787,7 +3829,7 @@
         <v>13</v>
       </c>
       <c r="B97" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C97">
         <v>8</v>
@@ -3810,7 +3852,7 @@
         <v>13</v>
       </c>
       <c r="B98" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C98">
         <v>8</v>
@@ -3833,7 +3875,7 @@
         <v>13</v>
       </c>
       <c r="B99" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C99">
         <v>8</v>
@@ -3856,7 +3898,7 @@
         <v>13</v>
       </c>
       <c r="B100" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C100">
         <v>58</v>
@@ -3871,7 +3913,7 @@
         <v>7</v>
       </c>
       <c r="G100" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H100">
         <v>77.33333333333333</v>
@@ -3882,7 +3924,7 @@
         <v>13</v>
       </c>
       <c r="B101" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C101">
         <v>58</v>
@@ -3897,7 +3939,7 @@
         <v>7</v>
       </c>
       <c r="G101" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H101">
         <v>77.33333333333333</v>
@@ -3908,7 +3950,7 @@
         <v>13</v>
       </c>
       <c r="B102" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C102">
         <v>58</v>
@@ -3931,7 +3973,7 @@
         <v>13</v>
       </c>
       <c r="B103" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C103">
         <v>58</v>
@@ -3954,7 +3996,7 @@
         <v>13</v>
       </c>
       <c r="B104" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C104">
         <v>58</v>
@@ -3977,7 +4019,7 @@
         <v>13</v>
       </c>
       <c r="B105" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C105">
         <v>58</v>
@@ -4000,7 +4042,7 @@
         <v>13</v>
       </c>
       <c r="B106" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C106">
         <v>45</v>
@@ -4023,7 +4065,7 @@
         <v>13</v>
       </c>
       <c r="B107" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C107">
         <v>45</v>
@@ -4046,7 +4088,7 @@
         <v>13</v>
       </c>
       <c r="B108" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C108">
         <v>45</v>
@@ -4069,7 +4111,7 @@
         <v>13</v>
       </c>
       <c r="B109" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C109">
         <v>20</v>
@@ -4092,7 +4134,7 @@
         <v>13</v>
       </c>
       <c r="B110" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C110">
         <v>30</v>
@@ -4107,7 +4149,7 @@
         <v>10</v>
       </c>
       <c r="G110" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H110">
         <v>34</v>
@@ -4118,7 +4160,7 @@
         <v>14</v>
       </c>
       <c r="B111" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C111">
         <v>20</v>
@@ -4133,7 +4175,7 @@
         <v>3</v>
       </c>
       <c r="G111" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H111">
         <v>25.33333333333333</v>
@@ -4144,7 +4186,7 @@
         <v>14</v>
       </c>
       <c r="B112" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C112">
         <v>60</v>
@@ -4159,7 +4201,7 @@
         <v>5</v>
       </c>
       <c r="G112" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H112">
         <v>66</v>
@@ -4170,7 +4212,7 @@
         <v>14</v>
       </c>
       <c r="B113" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C113">
         <v>80</v>
@@ -4185,7 +4227,7 @@
         <v>7</v>
       </c>
       <c r="G113" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H113">
         <v>88</v>
@@ -4196,7 +4238,7 @@
         <v>14</v>
       </c>
       <c r="B114" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C114">
         <v>90</v>
@@ -4211,7 +4253,7 @@
         <v>7</v>
       </c>
       <c r="G114" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H114">
         <v>93.00000000000001</v>
@@ -4222,7 +4264,7 @@
         <v>14</v>
       </c>
       <c r="B115" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C115">
         <v>90</v>
@@ -4237,7 +4279,7 @@
         <v>7.5</v>
       </c>
       <c r="G115" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H115">
         <v>99.00000000000001</v>
@@ -4248,7 +4290,7 @@
         <v>14</v>
       </c>
       <c r="B116" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C116">
         <v>100</v>
@@ -4263,7 +4305,7 @@
         <v>8.5</v>
       </c>
       <c r="G116" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H116">
         <v>110</v>
@@ -4274,7 +4316,7 @@
         <v>14</v>
       </c>
       <c r="B117" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C117">
         <v>110</v>
@@ -4289,7 +4331,7 @@
         <v>9</v>
       </c>
       <c r="G117" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H117">
         <v>113.6666666666667</v>
@@ -4300,7 +4342,7 @@
         <v>14</v>
       </c>
       <c r="B118" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C118">
         <v>20</v>
@@ -4315,7 +4357,7 @@
         <v>5</v>
       </c>
       <c r="G118" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H118">
         <v>28</v>
@@ -4326,7 +4368,7 @@
         <v>14</v>
       </c>
       <c r="B119" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C119">
         <v>30</v>
@@ -4341,7 +4383,7 @@
         <v>6</v>
       </c>
       <c r="G119" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H119">
         <v>36</v>
@@ -4352,7 +4394,7 @@
         <v>14</v>
       </c>
       <c r="B120" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C120">
         <v>40</v>
@@ -4367,7 +4409,7 @@
         <v>7.5</v>
       </c>
       <c r="G120" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H120">
         <v>45.33333333333333</v>
@@ -4378,7 +4420,7 @@
         <v>14</v>
       </c>
       <c r="B121" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C121">
         <v>45</v>
@@ -4393,7 +4435,7 @@
         <v>8.5</v>
       </c>
       <c r="G121" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H121">
         <v>49.50000000000001</v>
@@ -4404,7 +4446,7 @@
         <v>14</v>
       </c>
       <c r="B122" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C122">
         <v>50</v>
@@ -4419,7 +4461,7 @@
         <v>10</v>
       </c>
       <c r="G122" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H122">
         <v>50</v>
@@ -4430,7 +4472,7 @@
         <v>14</v>
       </c>
       <c r="B123" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C123">
         <v>70</v>
@@ -4445,7 +4487,7 @@
         <v>6</v>
       </c>
       <c r="G123" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H123">
         <v>77</v>
@@ -4456,7 +4498,7 @@
         <v>14</v>
       </c>
       <c r="B124" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C124">
         <v>120</v>
@@ -4471,7 +4513,7 @@
         <v>8.5</v>
       </c>
       <c r="G124" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H124">
         <v>124</v>
@@ -4482,7 +4524,7 @@
         <v>14</v>
       </c>
       <c r="B125" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C125">
         <v>120</v>
@@ -4497,7 +4539,7 @@
         <v>9.5</v>
       </c>
       <c r="G125" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H125">
         <v>124</v>
@@ -4508,7 +4550,7 @@
         <v>14</v>
       </c>
       <c r="B126" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C126">
         <v>120</v>
@@ -4523,7 +4565,7 @@
         <v>9.5</v>
       </c>
       <c r="G126" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H126">
         <v>124</v>
@@ -4534,7 +4576,7 @@
         <v>14</v>
       </c>
       <c r="B127" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C127">
         <v>120</v>
@@ -4549,7 +4591,7 @@
         <v>9.5</v>
       </c>
       <c r="G127" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H127">
         <v>124</v>
@@ -4560,7 +4602,7 @@
         <v>14</v>
       </c>
       <c r="B128" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C128">
         <v>20</v>
@@ -4575,7 +4617,7 @@
         <v>6.5</v>
       </c>
       <c r="G128" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H128">
         <v>26.66666666666666</v>
@@ -4586,7 +4628,7 @@
         <v>14</v>
       </c>
       <c r="B129" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C129">
         <v>20</v>
@@ -4601,7 +4643,7 @@
         <v>6.5</v>
       </c>
       <c r="G129" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H129">
         <v>26.66666666666666</v>
@@ -4612,7 +4654,7 @@
         <v>14</v>
       </c>
       <c r="B130" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C130">
         <v>20</v>
@@ -4627,7 +4669,7 @@
         <v>8</v>
       </c>
       <c r="G130" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H130">
         <v>26.66666666666666</v>
@@ -4638,7 +4680,7 @@
         <v>14</v>
       </c>
       <c r="B131" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C131">
         <v>20</v>
@@ -4653,7 +4695,7 @@
         <v>8</v>
       </c>
       <c r="G131" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H131">
         <v>26.66666666666666</v>
@@ -4664,7 +4706,7 @@
         <v>14</v>
       </c>
       <c r="B132" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C132">
         <v>20</v>
@@ -4679,7 +4721,7 @@
         <v>8.5</v>
       </c>
       <c r="G132" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H132">
         <v>26.66666666666666</v>
@@ -4690,7 +4732,7 @@
         <v>14</v>
       </c>
       <c r="B133" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C133">
         <v>20</v>
@@ -4705,7 +4747,7 @@
         <v>8.5</v>
       </c>
       <c r="G133" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H133">
         <v>26.66666666666666</v>
@@ -4716,7 +4758,7 @@
         <v>15</v>
       </c>
       <c r="B134" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C134">
         <v>20</v>
@@ -4731,7 +4773,7 @@
         <v>3</v>
       </c>
       <c r="G134" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H134">
         <v>25.33333333333333</v>
@@ -4742,7 +4784,7 @@
         <v>15</v>
       </c>
       <c r="B135" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C135">
         <v>60</v>
@@ -4757,7 +4799,7 @@
         <v>6</v>
       </c>
       <c r="G135" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H135">
         <v>72</v>
@@ -4768,7 +4810,7 @@
         <v>15</v>
       </c>
       <c r="B136" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C136">
         <v>80</v>
@@ -4783,7 +4825,7 @@
         <v>7</v>
       </c>
       <c r="G136" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H136">
         <v>88</v>
@@ -4794,7 +4836,7 @@
         <v>15</v>
       </c>
       <c r="B137" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C137">
         <v>100</v>
@@ -4809,7 +4851,7 @@
         <v>7</v>
       </c>
       <c r="G137" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H137">
         <v>103.3333333333333</v>
@@ -4820,7 +4862,7 @@
         <v>15</v>
       </c>
       <c r="B138" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C138">
         <v>70</v>
@@ -4835,7 +4877,7 @@
         <v>8</v>
       </c>
       <c r="G138" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H138">
         <v>98</v>
@@ -4846,7 +4888,7 @@
         <v>15</v>
       </c>
       <c r="B139" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C139">
         <v>80</v>
@@ -4861,7 +4903,7 @@
         <v>8.5</v>
       </c>
       <c r="G139" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H139">
         <v>101.3333333333333</v>
@@ -4872,7 +4914,7 @@
         <v>15</v>
       </c>
       <c r="B140" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C140">
         <v>20</v>
@@ -4887,7 +4929,7 @@
         <v>5</v>
       </c>
       <c r="G140" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H140">
         <v>28</v>
@@ -4898,7 +4940,7 @@
         <v>15</v>
       </c>
       <c r="B141" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C141">
         <v>30</v>
@@ -4913,7 +4955,7 @@
         <v>7</v>
       </c>
       <c r="G141" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H141">
         <v>38</v>
@@ -4924,7 +4966,7 @@
         <v>15</v>
       </c>
       <c r="B142" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C142">
         <v>40</v>
@@ -4939,7 +4981,7 @@
         <v>8</v>
       </c>
       <c r="G142" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H142">
         <v>48</v>
@@ -4950,7 +4992,7 @@
         <v>15</v>
       </c>
       <c r="B143" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C143">
         <v>40</v>
@@ -4965,7 +5007,7 @@
         <v>9</v>
       </c>
       <c r="G143" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H143">
         <v>48</v>
@@ -4976,7 +5018,7 @@
         <v>15</v>
       </c>
       <c r="B144" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C144">
         <v>30</v>
@@ -4991,7 +5033,7 @@
         <v>9</v>
       </c>
       <c r="G144" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H144">
         <v>42</v>
@@ -5002,7 +5044,7 @@
         <v>15</v>
       </c>
       <c r="B145" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C145">
         <v>30</v>
@@ -5017,7 +5059,7 @@
         <v>7</v>
       </c>
       <c r="G145" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H145">
         <v>45</v>
@@ -5028,7 +5070,7 @@
         <v>15</v>
       </c>
       <c r="B146" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C146">
         <v>50</v>
@@ -5043,7 +5085,7 @@
         <v>7.5</v>
       </c>
       <c r="G146" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H146">
         <v>63.33333333333333</v>
@@ -5054,7 +5096,7 @@
         <v>15</v>
       </c>
       <c r="B147" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C147">
         <v>50</v>
@@ -5069,7 +5111,7 @@
         <v>8</v>
       </c>
       <c r="G147" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H147">
         <v>63.33333333333333</v>
@@ -5080,7 +5122,7 @@
         <v>15</v>
       </c>
       <c r="B148" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C148">
         <v>50</v>
@@ -5095,7 +5137,7 @@
         <v>8.5</v>
       </c>
       <c r="G148" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H148">
         <v>63.33333333333333</v>
@@ -5106,7 +5148,7 @@
         <v>15</v>
       </c>
       <c r="B149" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C149">
         <v>50</v>
@@ -5121,7 +5163,7 @@
         <v>9.5</v>
       </c>
       <c r="G149" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H149">
         <v>63.33333333333333</v>
@@ -5132,7 +5174,7 @@
         <v>15</v>
       </c>
       <c r="B150" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C150">
         <v>40</v>
@@ -5147,7 +5189,7 @@
         <v>8</v>
       </c>
       <c r="G150" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H150">
         <v>56</v>
@@ -5158,7 +5200,7 @@
         <v>15</v>
       </c>
       <c r="B151" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C151">
         <v>70</v>
@@ -5173,7 +5215,7 @@
         <v>6</v>
       </c>
       <c r="G151" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H151">
         <v>84</v>
@@ -5184,7 +5226,7 @@
         <v>15</v>
       </c>
       <c r="B152" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C152">
         <v>120</v>
@@ -5199,7 +5241,7 @@
         <v>6</v>
       </c>
       <c r="G152" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H152">
         <v>124</v>
@@ -5210,7 +5252,7 @@
         <v>15</v>
       </c>
       <c r="B153" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C153">
         <v>120</v>
@@ -5225,7 +5267,7 @@
         <v>8</v>
       </c>
       <c r="G153" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H153">
         <v>140</v>
@@ -5236,7 +5278,7 @@
         <v>15</v>
       </c>
       <c r="B154" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C154">
         <v>130</v>
@@ -5251,7 +5293,7 @@
         <v>8.5</v>
       </c>
       <c r="G154" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H154">
         <v>151.6666666666667</v>
@@ -5262,7 +5304,7 @@
         <v>15</v>
       </c>
       <c r="B155" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C155">
         <v>130</v>
@@ -5277,7 +5319,7 @@
         <v>9</v>
       </c>
       <c r="G155" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H155">
         <v>151.6666666666667</v>
@@ -5288,7 +5330,7 @@
         <v>16</v>
       </c>
       <c r="B156" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C156">
         <v>20</v>
@@ -5303,7 +5345,7 @@
         <v>4</v>
       </c>
       <c r="G156" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H156">
         <v>28</v>
@@ -5314,7 +5356,7 @@
         <v>16</v>
       </c>
       <c r="B157" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C157">
         <v>40</v>
@@ -5337,7 +5379,7 @@
         <v>16</v>
       </c>
       <c r="B158" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C158">
         <v>60</v>
@@ -5352,7 +5394,7 @@
         <v>6.5</v>
       </c>
       <c r="G158" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H158">
         <v>62.00000000000001</v>
@@ -5363,7 +5405,7 @@
         <v>16</v>
       </c>
       <c r="B159" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C159">
         <v>70</v>
@@ -5378,7 +5420,7 @@
         <v>8.5</v>
       </c>
       <c r="G159" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H159">
         <v>72.33333333333334</v>
@@ -5389,7 +5431,7 @@
         <v>16</v>
       </c>
       <c r="B160" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C160">
         <v>65</v>
@@ -5404,7 +5446,7 @@
         <v>8</v>
       </c>
       <c r="G160" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H160">
         <v>67.16666666666667</v>
@@ -5415,7 +5457,7 @@
         <v>16</v>
       </c>
       <c r="B161" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C161">
         <v>60</v>
@@ -5438,7 +5480,7 @@
         <v>16</v>
       </c>
       <c r="B162" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C162">
         <v>60</v>
@@ -5453,7 +5495,7 @@
         <v>9</v>
       </c>
       <c r="G162" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H162">
         <v>66</v>
@@ -5464,7 +5506,7 @@
         <v>16</v>
       </c>
       <c r="B163" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C163">
         <v>45</v>
@@ -5479,7 +5521,7 @@
         <v>8</v>
       </c>
       <c r="G163" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H163">
         <v>62.99999999999999</v>
@@ -5490,7 +5532,7 @@
         <v>16</v>
       </c>
       <c r="B164" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C164">
         <v>45</v>
@@ -5513,7 +5555,7 @@
         <v>16</v>
       </c>
       <c r="B165" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C165">
         <v>20</v>
@@ -5528,7 +5570,7 @@
         <v>7</v>
       </c>
       <c r="G165" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H165">
         <v>26.66666666666666</v>
@@ -5539,7 +5581,7 @@
         <v>16</v>
       </c>
       <c r="B166" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C166">
         <v>20</v>
@@ -5554,7 +5596,7 @@
         <v>6</v>
       </c>
       <c r="G166" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H166">
         <v>28</v>
@@ -5565,7 +5607,7 @@
         <v>16</v>
       </c>
       <c r="B167" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C167">
         <v>20</v>
@@ -5580,7 +5622,7 @@
         <v>7</v>
       </c>
       <c r="G167" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H167">
         <v>28</v>
@@ -5591,7 +5633,7 @@
         <v>16</v>
       </c>
       <c r="B168" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C168">
         <v>20</v>
@@ -5606,7 +5648,7 @@
         <v>7</v>
       </c>
       <c r="G168" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H168">
         <v>30</v>
@@ -5617,7 +5659,7 @@
         <v>16</v>
       </c>
       <c r="B169" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C169">
         <v>22.5</v>
@@ -5632,7 +5674,7 @@
         <v>7.5</v>
       </c>
       <c r="G169" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H169">
         <v>30</v>
@@ -5643,7 +5685,7 @@
         <v>16</v>
       </c>
       <c r="B170" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C170">
         <v>22.5</v>
@@ -5658,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="G170" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H170">
         <v>31.5</v>
@@ -5669,7 +5711,7 @@
         <v>16</v>
       </c>
       <c r="B171" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C171">
         <v>25</v>
@@ -5684,7 +5726,7 @@
         <v>8</v>
       </c>
       <c r="G171" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H171">
         <v>31.66666666666666</v>
@@ -5695,7 +5737,7 @@
         <v>16</v>
       </c>
       <c r="B172" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C172">
         <v>25</v>
@@ -5710,7 +5752,7 @@
         <v>7.5</v>
       </c>
       <c r="G172" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H172">
         <v>35</v>
@@ -5721,7 +5763,7 @@
         <v>16</v>
       </c>
       <c r="B173" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C173">
         <v>25</v>
@@ -5736,7 +5778,7 @@
         <v>8</v>
       </c>
       <c r="G173" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H173">
         <v>31.66666666666666</v>
@@ -5747,7 +5789,7 @@
         <v>16</v>
       </c>
       <c r="B174" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C174">
         <v>25</v>
@@ -5762,7 +5804,7 @@
         <v>8</v>
       </c>
       <c r="G174" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H174">
         <v>37.5</v>
@@ -5773,7 +5815,7 @@
         <v>16</v>
       </c>
       <c r="B175" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C175">
         <v>40</v>
@@ -5788,7 +5830,7 @@
         <v>7.5</v>
       </c>
       <c r="G175" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H175">
         <v>50.66666666666666</v>
@@ -5799,7 +5841,7 @@
         <v>16</v>
       </c>
       <c r="B176" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C176">
         <v>40</v>
@@ -5814,7 +5856,7 @@
         <v>8.5</v>
       </c>
       <c r="G176" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H176">
         <v>50.66666666666666</v>
@@ -5825,7 +5867,7 @@
         <v>16</v>
       </c>
       <c r="B177" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C177">
         <v>40</v>
@@ -5840,7 +5882,7 @@
         <v>9</v>
       </c>
       <c r="G177" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H177">
         <v>48</v>
@@ -5851,7 +5893,7 @@
         <v>16</v>
       </c>
       <c r="B178" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C178">
         <v>22</v>
@@ -5866,7 +5908,7 @@
         <v>7</v>
       </c>
       <c r="G178" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H178">
         <v>27.86666666666667</v>
@@ -5877,7 +5919,7 @@
         <v>16</v>
       </c>
       <c r="B179" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C179">
         <v>22</v>
@@ -5900,7 +5942,7 @@
         <v>16</v>
       </c>
       <c r="B180" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C180">
         <v>22</v>
@@ -5915,7 +5957,7 @@
         <v>8.5</v>
       </c>
       <c r="G180" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H180">
         <v>27.86666666666667</v>
@@ -5926,7 +5968,7 @@
         <v>17</v>
       </c>
       <c r="B181" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C181">
         <v>20</v>
@@ -5949,7 +5991,7 @@
         <v>17</v>
       </c>
       <c r="B182" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C182">
         <v>22</v>
@@ -5972,7 +6014,7 @@
         <v>17</v>
       </c>
       <c r="B183" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C183">
         <v>20</v>
@@ -5987,7 +6029,7 @@
         <v>4</v>
       </c>
       <c r="G183" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H183">
         <v>25.33333333333333</v>
@@ -5998,7 +6040,7 @@
         <v>17</v>
       </c>
       <c r="B184" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C184">
         <v>60</v>
@@ -6021,7 +6063,7 @@
         <v>17</v>
       </c>
       <c r="B185" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C185">
         <v>80</v>
@@ -6044,7 +6086,7 @@
         <v>17</v>
       </c>
       <c r="B186" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C186">
         <v>100</v>
@@ -6067,7 +6109,7 @@
         <v>17</v>
       </c>
       <c r="B187" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C187">
         <v>110</v>
@@ -6090,7 +6132,7 @@
         <v>17</v>
       </c>
       <c r="B188" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C188">
         <v>120</v>
@@ -6105,7 +6147,7 @@
         <v>8.5</v>
       </c>
       <c r="G188" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H188">
         <v>124</v>
@@ -6116,7 +6158,7 @@
         <v>17</v>
       </c>
       <c r="B189" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C189">
         <v>80</v>
@@ -6131,7 +6173,7 @@
         <v>7.5</v>
       </c>
       <c r="G189" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H189">
         <v>112</v>
@@ -6142,7 +6184,7 @@
         <v>17</v>
       </c>
       <c r="B190" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C190">
         <v>-30</v>
@@ -6157,7 +6199,7 @@
         <v>6</v>
       </c>
       <c r="G190" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H190">
         <v>-38</v>
@@ -6168,7 +6210,7 @@
         <v>17</v>
       </c>
       <c r="B191" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C191">
         <v>-30</v>
@@ -6183,7 +6225,7 @@
         <v>6</v>
       </c>
       <c r="G191" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H191">
         <v>-38</v>
@@ -6194,7 +6236,7 @@
         <v>17</v>
       </c>
       <c r="B192" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C192">
         <v>-25</v>
@@ -6209,7 +6251,7 @@
         <v>7.5</v>
       </c>
       <c r="G192" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H192">
         <v>-33.33333333333333</v>
@@ -6220,7 +6262,7 @@
         <v>17</v>
       </c>
       <c r="B193" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C193">
         <v>-25</v>
@@ -6235,7 +6277,7 @@
         <v>7.5</v>
       </c>
       <c r="G193" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H193">
         <v>-33.33333333333333</v>
@@ -6246,7 +6288,7 @@
         <v>17</v>
       </c>
       <c r="B194" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C194">
         <v>-20</v>
@@ -6261,7 +6303,7 @@
         <v>8</v>
       </c>
       <c r="G194" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H194">
         <v>-25.33333333333333</v>
@@ -6272,7 +6314,7 @@
         <v>17</v>
       </c>
       <c r="B195" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C195">
         <v>-20</v>
@@ -6287,7 +6329,7 @@
         <v>8</v>
       </c>
       <c r="G195" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H195">
         <v>-25.33333333333333</v>
@@ -6298,7 +6340,7 @@
         <v>17</v>
       </c>
       <c r="B196" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C196">
         <v>35</v>
@@ -6313,7 +6355,7 @@
         <v>7</v>
       </c>
       <c r="G196" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H196">
         <v>52.5</v>
@@ -6324,7 +6366,7 @@
         <v>17</v>
       </c>
       <c r="B197" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C197">
         <v>25</v>
@@ -6339,7 +6381,7 @@
         <v>7</v>
       </c>
       <c r="G197" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H197">
         <v>37.5</v>
@@ -6350,7 +6392,7 @@
         <v>17</v>
       </c>
       <c r="B198" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C198">
         <v>35</v>
@@ -6365,7 +6407,7 @@
         <v>7</v>
       </c>
       <c r="G198" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H198">
         <v>52.5</v>
@@ -6376,7 +6418,7 @@
         <v>17</v>
       </c>
       <c r="B199" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C199">
         <v>25</v>
@@ -6391,7 +6433,7 @@
         <v>7</v>
       </c>
       <c r="G199" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H199">
         <v>37.5</v>
@@ -6402,7 +6444,7 @@
         <v>18</v>
       </c>
       <c r="B200" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C200">
         <v>70</v>
@@ -6417,7 +6459,7 @@
         <v>6</v>
       </c>
       <c r="G200" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H200">
         <v>84</v>
@@ -6428,7 +6470,7 @@
         <v>18</v>
       </c>
       <c r="B201" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C201">
         <v>90</v>
@@ -6451,7 +6493,7 @@
         <v>18</v>
       </c>
       <c r="B202" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C202">
         <v>120</v>
@@ -6474,7 +6516,7 @@
         <v>18</v>
       </c>
       <c r="B203" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C203">
         <v>120</v>
@@ -6497,7 +6539,7 @@
         <v>18</v>
       </c>
       <c r="B204" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C204">
         <v>120</v>
@@ -6520,7 +6562,7 @@
         <v>18</v>
       </c>
       <c r="B205" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C205">
         <v>120</v>
@@ -6543,7 +6585,7 @@
         <v>18</v>
       </c>
       <c r="B206" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C206">
         <v>120</v>
@@ -6566,7 +6608,7 @@
         <v>18</v>
       </c>
       <c r="B207" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C207">
         <v>20</v>
@@ -6581,7 +6623,7 @@
         <v>6</v>
       </c>
       <c r="G207" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H207">
         <v>28</v>
@@ -6592,7 +6634,7 @@
         <v>18</v>
       </c>
       <c r="B208" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C208">
         <v>30</v>
@@ -6615,7 +6657,7 @@
         <v>18</v>
       </c>
       <c r="B209" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C209">
         <v>35</v>
@@ -6638,7 +6680,7 @@
         <v>18</v>
       </c>
       <c r="B210" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C210">
         <v>35</v>
@@ -6661,7 +6703,7 @@
         <v>18</v>
       </c>
       <c r="B211" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C211">
         <v>35</v>
@@ -6684,7 +6726,7 @@
         <v>18</v>
       </c>
       <c r="B212" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C212">
         <v>22</v>
@@ -6699,7 +6741,7 @@
         <v>7.5</v>
       </c>
       <c r="G212" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H212">
         <v>27.86666666666667</v>
@@ -6710,7 +6752,7 @@
         <v>18</v>
       </c>
       <c r="B213" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C213">
         <v>22</v>
@@ -6725,7 +6767,7 @@
         <v>7.5</v>
       </c>
       <c r="G213" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H213">
         <v>30.8</v>
@@ -6736,7 +6778,7 @@
         <v>18</v>
       </c>
       <c r="B214" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C214">
         <v>22</v>
@@ -6751,7 +6793,7 @@
         <v>8</v>
       </c>
       <c r="G214" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H214">
         <v>27.86666666666667</v>
@@ -6762,7 +6804,7 @@
         <v>18</v>
       </c>
       <c r="B215" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C215">
         <v>22</v>
@@ -6777,7 +6819,7 @@
         <v>8</v>
       </c>
       <c r="G215" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H215">
         <v>30.8</v>
@@ -6788,7 +6830,7 @@
         <v>18</v>
       </c>
       <c r="B216" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C216">
         <v>22</v>
@@ -6803,7 +6845,7 @@
         <v>8.5</v>
       </c>
       <c r="G216" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H216">
         <v>27.86666666666667</v>
@@ -6814,7 +6856,7 @@
         <v>18</v>
       </c>
       <c r="B217" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C217">
         <v>22</v>
@@ -6829,7 +6871,7 @@
         <v>8</v>
       </c>
       <c r="G217" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H217">
         <v>30.8</v>
@@ -6840,7 +6882,7 @@
         <v>18</v>
       </c>
       <c r="B218" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C218">
         <v>25</v>
@@ -6855,7 +6897,7 @@
         <v>8</v>
       </c>
       <c r="G218" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H218">
         <v>31.66666666666666</v>
@@ -6866,7 +6908,7 @@
         <v>18</v>
       </c>
       <c r="B219" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C219">
         <v>25</v>
@@ -6881,7 +6923,7 @@
         <v>6.5</v>
       </c>
       <c r="G219" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H219">
         <v>31.66666666666666</v>
@@ -6892,7 +6934,7 @@
         <v>18</v>
       </c>
       <c r="B220" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C220">
         <v>25</v>
@@ -6907,7 +6949,7 @@
         <v>8</v>
       </c>
       <c r="G220" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H220">
         <v>31.66666666666666</v>
@@ -6918,7 +6960,7 @@
         <v>18</v>
       </c>
       <c r="B221" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C221">
         <v>25</v>
@@ -6933,7 +6975,7 @@
         <v>7.5</v>
       </c>
       <c r="G221" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H221">
         <v>31.66666666666666</v>
@@ -6944,7 +6986,7 @@
         <v>18</v>
       </c>
       <c r="B222" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C222">
         <v>25</v>
@@ -6959,7 +7001,7 @@
         <v>9</v>
       </c>
       <c r="G222" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H222">
         <v>31.66666666666666</v>
@@ -6970,7 +7012,7 @@
         <v>18</v>
       </c>
       <c r="B223" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C223">
         <v>25</v>
@@ -6985,7 +7027,7 @@
         <v>9</v>
       </c>
       <c r="G223" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H223">
         <v>31.66666666666666</v>
@@ -6996,7 +7038,7 @@
         <v>19</v>
       </c>
       <c r="B224" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C224">
         <v>70</v>
@@ -7011,7 +7053,7 @@
         <v>6.5</v>
       </c>
       <c r="G224" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H224">
         <v>84</v>
@@ -7022,7 +7064,7 @@
         <v>19</v>
       </c>
       <c r="B225" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C225">
         <v>85</v>
@@ -7037,7 +7079,7 @@
         <v>8</v>
       </c>
       <c r="G225" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H225">
         <v>119</v>
@@ -7048,7 +7090,7 @@
         <v>19</v>
       </c>
       <c r="B226" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C226">
         <v>85</v>
@@ -7063,7 +7105,7 @@
         <v>9</v>
       </c>
       <c r="G226" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H226">
         <v>119</v>
@@ -7074,7 +7116,7 @@
         <v>19</v>
       </c>
       <c r="B227" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C227">
         <v>85</v>
@@ -7089,7 +7131,7 @@
         <v>10</v>
       </c>
       <c r="G227" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H227">
         <v>113.3333333333333</v>
@@ -7100,7 +7142,7 @@
         <v>19</v>
       </c>
       <c r="B228" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C228">
         <v>30</v>
@@ -7115,7 +7157,7 @@
         <v>6</v>
       </c>
       <c r="G228" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H228">
         <v>36</v>
@@ -7126,7 +7168,7 @@
         <v>19</v>
       </c>
       <c r="B229" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C229">
         <v>30</v>
@@ -7141,7 +7183,7 @@
         <v>6</v>
       </c>
       <c r="G229" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H229">
         <v>38</v>
@@ -7152,7 +7194,7 @@
         <v>19</v>
       </c>
       <c r="B230" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C230">
         <v>40</v>
@@ -7167,7 +7209,7 @@
         <v>8</v>
       </c>
       <c r="G230" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H230">
         <v>50.66666666666666</v>
@@ -7178,7 +7220,7 @@
         <v>19</v>
       </c>
       <c r="B231" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C231">
         <v>40</v>
@@ -7193,7 +7235,7 @@
         <v>9</v>
       </c>
       <c r="G231" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H231">
         <v>50.66666666666666</v>
@@ -7204,7 +7246,7 @@
         <v>19</v>
       </c>
       <c r="B232" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C232">
         <v>40</v>
@@ -7219,7 +7261,7 @@
         <v>10</v>
       </c>
       <c r="G232" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H232">
         <v>49.33333333333334</v>
@@ -7230,7 +7272,7 @@
         <v>19</v>
       </c>
       <c r="B233" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C233">
         <v>40</v>
@@ -7245,7 +7287,7 @@
         <v>6.5</v>
       </c>
       <c r="G233" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H233">
         <v>56</v>
@@ -7256,7 +7298,7 @@
         <v>19</v>
       </c>
       <c r="B234" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C234">
         <v>40</v>
@@ -7271,7 +7313,7 @@
         <v>6.5</v>
       </c>
       <c r="G234" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H234">
         <v>56</v>
@@ -7282,7 +7324,7 @@
         <v>19</v>
       </c>
       <c r="B235" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C235">
         <v>40</v>
@@ -7297,7 +7339,7 @@
         <v>7.5</v>
       </c>
       <c r="G235" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H235">
         <v>56</v>
@@ -7308,7 +7350,7 @@
         <v>19</v>
       </c>
       <c r="B236" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C236">
         <v>40</v>
@@ -7323,7 +7365,7 @@
         <v>9</v>
       </c>
       <c r="G236" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H236">
         <v>56</v>
@@ -7334,7 +7376,7 @@
         <v>19</v>
       </c>
       <c r="B237" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C237">
         <v>60</v>
@@ -7349,7 +7391,7 @@
         <v>8</v>
       </c>
       <c r="G237" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H237">
         <v>80</v>
@@ -7360,7 +7402,7 @@
         <v>19</v>
       </c>
       <c r="B238" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C238">
         <v>60</v>
@@ -7375,7 +7417,7 @@
         <v>7</v>
       </c>
       <c r="G238" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H238">
         <v>80</v>
@@ -7386,7 +7428,7 @@
         <v>19</v>
       </c>
       <c r="B239" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C239">
         <v>60</v>
@@ -7401,7 +7443,7 @@
         <v>8.5</v>
       </c>
       <c r="G239" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H239">
         <v>80</v>
@@ -7412,7 +7454,7 @@
         <v>19</v>
       </c>
       <c r="B240" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C240">
         <v>60</v>
@@ -7427,7 +7469,7 @@
         <v>8</v>
       </c>
       <c r="G240" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H240">
         <v>80</v>
@@ -7438,7 +7480,7 @@
         <v>19</v>
       </c>
       <c r="B241" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C241">
         <v>60</v>
@@ -7453,7 +7495,7 @@
         <v>9</v>
       </c>
       <c r="G241" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H241">
         <v>80</v>
@@ -7464,7 +7506,7 @@
         <v>19</v>
       </c>
       <c r="B242" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C242">
         <v>60</v>
@@ -7479,7 +7521,7 @@
         <v>9</v>
       </c>
       <c r="G242" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H242">
         <v>80</v>
@@ -7490,7 +7532,7 @@
         <v>20</v>
       </c>
       <c r="B243" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C243">
         <v>60</v>
@@ -7505,7 +7547,7 @@
         <v>4</v>
       </c>
       <c r="G243" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H243">
         <v>76</v>
@@ -7516,7 +7558,7 @@
         <v>20</v>
       </c>
       <c r="B244" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C244">
         <v>100</v>
@@ -7531,7 +7573,7 @@
         <v>6</v>
       </c>
       <c r="G244" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H244">
         <v>116.6666666666667</v>
@@ -7542,7 +7584,7 @@
         <v>20</v>
       </c>
       <c r="B245" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C245">
         <v>130</v>
@@ -7557,7 +7599,7 @@
         <v>7</v>
       </c>
       <c r="G245" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H245">
         <v>134.3333333333333</v>
@@ -7568,7 +7610,7 @@
         <v>20</v>
       </c>
       <c r="B246" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C246">
         <v>150</v>
@@ -7583,7 +7625,7 @@
         <v>8.5</v>
       </c>
       <c r="G246" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H246">
         <v>155</v>
@@ -7594,7 +7636,7 @@
         <v>20</v>
       </c>
       <c r="B247" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C247">
         <v>120</v>
@@ -7609,7 +7651,7 @@
         <v>7.5</v>
       </c>
       <c r="G247" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H247">
         <v>140</v>
@@ -7620,7 +7662,7 @@
         <v>20</v>
       </c>
       <c r="B248" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C248">
         <v>120</v>
@@ -7635,7 +7677,7 @@
         <v>7.5</v>
       </c>
       <c r="G248" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H248">
         <v>140</v>
@@ -7646,7 +7688,7 @@
         <v>20</v>
       </c>
       <c r="B249" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C249">
         <v>120</v>
@@ -7661,7 +7703,7 @@
         <v>8</v>
       </c>
       <c r="G249" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H249">
         <v>140</v>
@@ -7672,7 +7714,7 @@
         <v>20</v>
       </c>
       <c r="B250" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C250">
         <v>120</v>
@@ -7687,7 +7729,7 @@
         <v>8.5</v>
       </c>
       <c r="G250" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H250">
         <v>140</v>
@@ -7698,7 +7740,7 @@
         <v>20</v>
       </c>
       <c r="B251" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C251">
         <v>120</v>
@@ -7713,7 +7755,7 @@
         <v>9</v>
       </c>
       <c r="G251" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H251">
         <v>140</v>
@@ -7724,7 +7766,7 @@
         <v>20</v>
       </c>
       <c r="B252" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C252">
         <v>40</v>
@@ -7739,7 +7781,7 @@
         <v>5</v>
       </c>
       <c r="G252" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H252">
         <v>50.66666666666666</v>
@@ -7750,7 +7792,7 @@
         <v>20</v>
       </c>
       <c r="B253" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C253">
         <v>50</v>
@@ -7765,7 +7807,7 @@
         <v>6</v>
       </c>
       <c r="G253" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H253">
         <v>58.33333333333334</v>
@@ -7776,7 +7818,7 @@
         <v>20</v>
       </c>
       <c r="B254" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C254">
         <v>60</v>
@@ -7791,7 +7833,7 @@
         <v>7</v>
       </c>
       <c r="G254" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H254">
         <v>70</v>
@@ -7802,7 +7844,7 @@
         <v>20</v>
       </c>
       <c r="B255" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C255">
         <v>60</v>
@@ -7817,7 +7859,7 @@
         <v>8</v>
       </c>
       <c r="G255" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H255">
         <v>70</v>
@@ -7828,7 +7870,7 @@
         <v>20</v>
       </c>
       <c r="B256" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C256">
         <v>60</v>
@@ -7843,7 +7885,7 @@
         <v>8.5</v>
       </c>
       <c r="G256" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H256">
         <v>70</v>
@@ -7854,7 +7896,7 @@
         <v>20</v>
       </c>
       <c r="B257" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C257">
         <v>60</v>
@@ -7869,7 +7911,7 @@
         <v>8.5</v>
       </c>
       <c r="G257" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H257">
         <v>70</v>
@@ -7880,7 +7922,7 @@
         <v>20</v>
       </c>
       <c r="B258" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C258">
         <v>60</v>
@@ -7895,7 +7937,7 @@
         <v>8</v>
       </c>
       <c r="G258" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H258">
         <v>70</v>
@@ -7906,7 +7948,7 @@
         <v>20</v>
       </c>
       <c r="B259" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C259">
         <v>40</v>
@@ -7921,7 +7963,7 @@
         <v>5</v>
       </c>
       <c r="G259" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H259">
         <v>53.33333333333333</v>
@@ -7932,7 +7974,7 @@
         <v>20</v>
       </c>
       <c r="B260" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C260">
         <v>50</v>
@@ -7947,7 +7989,7 @@
         <v>7</v>
       </c>
       <c r="G260" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H260">
         <v>63.33333333333333</v>
@@ -7958,7 +8000,7 @@
         <v>20</v>
       </c>
       <c r="B261" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C261">
         <v>50</v>
@@ -7973,7 +8015,7 @@
         <v>7</v>
       </c>
       <c r="G261" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H261">
         <v>63.33333333333333</v>
@@ -7984,7 +8026,7 @@
         <v>20</v>
       </c>
       <c r="B262" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C262">
         <v>50</v>
@@ -7999,7 +8041,7 @@
         <v>7.5</v>
       </c>
       <c r="G262" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H262">
         <v>63.33333333333333</v>
@@ -8010,7 +8052,7 @@
         <v>20</v>
       </c>
       <c r="B263" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C263">
         <v>50</v>
@@ -8025,7 +8067,7 @@
         <v>8</v>
       </c>
       <c r="G263" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H263">
         <v>66.66666666666666</v>
@@ -8036,7 +8078,7 @@
         <v>20</v>
       </c>
       <c r="B264" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C264">
         <v>20</v>
@@ -8051,7 +8093,7 @@
         <v>7</v>
       </c>
       <c r="G264" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H264">
         <v>26.66666666666666</v>
@@ -8062,7 +8104,7 @@
         <v>20</v>
       </c>
       <c r="B265" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C265">
         <v>20</v>
@@ -8077,7 +8119,7 @@
         <v>7</v>
       </c>
       <c r="G265" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H265">
         <v>28</v>
@@ -8088,7 +8130,7 @@
         <v>20</v>
       </c>
       <c r="B266" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C266">
         <v>25</v>
@@ -8103,7 +8145,7 @@
         <v>8.5</v>
       </c>
       <c r="G266" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H266">
         <v>31.66666666666666</v>
@@ -8114,7 +8156,7 @@
         <v>20</v>
       </c>
       <c r="B267" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C267">
         <v>25</v>
@@ -8129,7 +8171,7 @@
         <v>7.5</v>
       </c>
       <c r="G267" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H267">
         <v>33.33333333333333</v>
@@ -8140,7 +8182,7 @@
         <v>20</v>
       </c>
       <c r="B268" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C268">
         <v>25</v>
@@ -8155,7 +8197,7 @@
         <v>8.5</v>
       </c>
       <c r="G268" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H268">
         <v>31.66666666666666</v>
@@ -8166,7 +8208,7 @@
         <v>20</v>
       </c>
       <c r="B269" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C269">
         <v>25</v>
@@ -8181,7 +8223,7 @@
         <v>8</v>
       </c>
       <c r="G269" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H269">
         <v>35</v>
@@ -8192,7 +8234,7 @@
         <v>20</v>
       </c>
       <c r="B270" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C270">
         <v>25</v>
@@ -8207,7 +8249,7 @@
         <v>9</v>
       </c>
       <c r="G270" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H270">
         <v>31.66666666666666</v>
@@ -8218,7 +8260,7 @@
         <v>20</v>
       </c>
       <c r="B271" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C271">
         <v>25</v>
@@ -8233,7 +8275,7 @@
         <v>9</v>
       </c>
       <c r="G271" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H271">
         <v>37.5</v>
@@ -8244,7 +8286,7 @@
         <v>21</v>
       </c>
       <c r="B272" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C272">
         <v>20</v>
@@ -8267,7 +8309,7 @@
         <v>21</v>
       </c>
       <c r="B273" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C273">
         <v>60</v>
@@ -8290,7 +8332,7 @@
         <v>21</v>
       </c>
       <c r="B274" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C274">
         <v>100</v>
@@ -8313,7 +8355,7 @@
         <v>21</v>
       </c>
       <c r="B275" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C275">
         <v>100</v>
@@ -8336,7 +8378,7 @@
         <v>21</v>
       </c>
       <c r="B276" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C276">
         <v>60</v>
@@ -8359,7 +8401,7 @@
         <v>21</v>
       </c>
       <c r="B277" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C277">
         <v>90</v>
@@ -8382,7 +8424,7 @@
         <v>21</v>
       </c>
       <c r="B278" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C278">
         <v>110</v>
@@ -8405,7 +8447,7 @@
         <v>21</v>
       </c>
       <c r="B279" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C279">
         <v>30</v>
@@ -8428,7 +8470,7 @@
         <v>21</v>
       </c>
       <c r="B280" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C280">
         <v>40</v>
@@ -8451,7 +8493,7 @@
         <v>21</v>
       </c>
       <c r="B281" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C281">
         <v>40</v>
@@ -8474,7 +8516,7 @@
         <v>21</v>
       </c>
       <c r="B282" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C282">
         <v>30</v>
@@ -8497,7 +8539,7 @@
         <v>21</v>
       </c>
       <c r="B283" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C283">
         <v>30</v>
@@ -8520,7 +8562,7 @@
         <v>21</v>
       </c>
       <c r="B284" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C284">
         <v>40</v>
@@ -8543,7 +8585,7 @@
         <v>21</v>
       </c>
       <c r="B285" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C285">
         <v>40</v>
@@ -8566,7 +8608,7 @@
         <v>21</v>
       </c>
       <c r="B286" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C286">
         <v>40</v>
@@ -8589,7 +8631,7 @@
         <v>21</v>
       </c>
       <c r="B287" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C287">
         <v>40</v>
@@ -8612,7 +8654,7 @@
         <v>21</v>
       </c>
       <c r="B288" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C288">
         <v>60</v>
@@ -8635,7 +8677,7 @@
         <v>21</v>
       </c>
       <c r="B289" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C289">
         <v>60</v>
@@ -8658,7 +8700,7 @@
         <v>21</v>
       </c>
       <c r="B290" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C290">
         <v>60</v>
@@ -8681,7 +8723,7 @@
         <v>21</v>
       </c>
       <c r="B291" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C291">
         <v>60</v>
@@ -8704,7 +8746,7 @@
         <v>21</v>
       </c>
       <c r="B292" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C292">
         <v>60</v>
@@ -8727,7 +8769,7 @@
         <v>21</v>
       </c>
       <c r="B293" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C293">
         <v>60</v>
@@ -8750,7 +8792,7 @@
         <v>22</v>
       </c>
       <c r="B294" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C294">
         <v>20</v>
@@ -8765,7 +8807,7 @@
         <v>3</v>
       </c>
       <c r="G294" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H294">
         <v>28</v>
@@ -8776,7 +8818,7 @@
         <v>22</v>
       </c>
       <c r="B295" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C295">
         <v>60</v>
@@ -8791,7 +8833,7 @@
         <v>6</v>
       </c>
       <c r="G295" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H295">
         <v>76</v>
@@ -8802,7 +8844,7 @@
         <v>22</v>
       </c>
       <c r="B296" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C296">
         <v>110</v>
@@ -8817,7 +8859,7 @@
         <v>7.5</v>
       </c>
       <c r="G296" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H296">
         <v>121</v>
@@ -8828,7 +8870,7 @@
         <v>22</v>
       </c>
       <c r="B297" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C297">
         <v>70</v>
@@ -8843,7 +8885,7 @@
         <v>8</v>
       </c>
       <c r="G297" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H297">
         <v>116.6666666666667</v>
@@ -8854,7 +8896,7 @@
         <v>22</v>
       </c>
       <c r="B298" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C298">
         <v>80</v>
@@ -8869,7 +8911,7 @@
         <v>8.5</v>
       </c>
       <c r="G298" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H298">
         <v>112</v>
@@ -8880,7 +8922,7 @@
         <v>22</v>
       </c>
       <c r="B299" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C299">
         <v>60</v>
@@ -8895,7 +8937,7 @@
         <v>5</v>
       </c>
       <c r="G299" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H299">
         <v>80</v>
@@ -8906,7 +8948,7 @@
         <v>22</v>
       </c>
       <c r="B300" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C300">
         <v>110</v>
@@ -8921,7 +8963,7 @@
         <v>6.5</v>
       </c>
       <c r="G300" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H300">
         <v>128.3333333333333</v>
@@ -8932,7 +8974,7 @@
         <v>22</v>
       </c>
       <c r="B301" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C301">
         <v>140</v>
@@ -8947,7 +8989,7 @@
         <v>7</v>
       </c>
       <c r="G301" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H301">
         <v>144.6666666666667</v>
@@ -8958,7 +9000,7 @@
         <v>22</v>
       </c>
       <c r="B302" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C302">
         <v>160</v>
@@ -8973,7 +9015,7 @@
         <v>8.5</v>
       </c>
       <c r="G302" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H302">
         <v>165.3333333333333</v>
@@ -8984,7 +9026,7 @@
         <v>22</v>
       </c>
       <c r="B303" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C303">
         <v>170</v>
@@ -8999,7 +9041,7 @@
         <v>9</v>
       </c>
       <c r="G303" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H303">
         <v>175.6666666666667</v>
@@ -9010,7 +9052,7 @@
         <v>22</v>
       </c>
       <c r="B304" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C304">
         <v>30</v>
@@ -9025,7 +9067,7 @@
         <v>7</v>
       </c>
       <c r="G304" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H304">
         <v>40</v>
@@ -9036,7 +9078,7 @@
         <v>22</v>
       </c>
       <c r="B305" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C305">
         <v>40</v>
@@ -9051,7 +9093,7 @@
         <v>7</v>
       </c>
       <c r="G305" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H305">
         <v>44</v>
@@ -9062,7 +9104,7 @@
         <v>22</v>
       </c>
       <c r="B306" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C306">
         <v>50</v>
@@ -9077,7 +9119,7 @@
         <v>9.5</v>
       </c>
       <c r="G306" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H306">
         <v>53.33333333333334</v>
@@ -9088,7 +9130,7 @@
         <v>22</v>
       </c>
       <c r="B307" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C307">
         <v>40</v>
@@ -9103,7 +9145,7 @@
         <v>8.5</v>
       </c>
       <c r="G307" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H307">
         <v>53.33333333333333</v>
@@ -9114,7 +9156,7 @@
         <v>23</v>
       </c>
       <c r="B308" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C308">
         <v>70</v>
@@ -9137,7 +9179,7 @@
         <v>23</v>
       </c>
       <c r="B309" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C309">
         <v>120</v>
@@ -9160,7 +9202,7 @@
         <v>23</v>
       </c>
       <c r="B310" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C310">
         <v>140</v>
@@ -9183,7 +9225,7 @@
         <v>23</v>
       </c>
       <c r="B311" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C311">
         <v>140</v>
@@ -9206,7 +9248,7 @@
         <v>23</v>
       </c>
       <c r="B312" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C312">
         <v>120</v>
@@ -9229,7 +9271,7 @@
         <v>23</v>
       </c>
       <c r="B313" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C313">
         <v>20</v>
@@ -9252,7 +9294,7 @@
         <v>23</v>
       </c>
       <c r="B314" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C314">
         <v>40</v>
@@ -9275,7 +9317,7 @@
         <v>23</v>
       </c>
       <c r="B315" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C315">
         <v>60</v>
@@ -9298,7 +9340,7 @@
         <v>23</v>
       </c>
       <c r="B316" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C316">
         <v>70</v>
@@ -9321,7 +9363,7 @@
         <v>23</v>
       </c>
       <c r="B317" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C317">
         <v>80</v>
@@ -9344,7 +9386,7 @@
         <v>23</v>
       </c>
       <c r="B318" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C318">
         <v>75</v>
@@ -9367,7 +9409,7 @@
         <v>23</v>
       </c>
       <c r="B319" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C319">
         <v>60</v>
@@ -9390,7 +9432,7 @@
         <v>23</v>
       </c>
       <c r="B320" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C320">
         <v>60</v>
@@ -9413,7 +9455,7 @@
         <v>23</v>
       </c>
       <c r="B321" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C321">
         <v>60</v>
@@ -9436,7 +9478,7 @@
         <v>23</v>
       </c>
       <c r="B322" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C322">
         <v>65</v>
@@ -9459,7 +9501,7 @@
         <v>23</v>
       </c>
       <c r="B323" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C323">
         <v>65</v>
@@ -9482,7 +9524,7 @@
         <v>23</v>
       </c>
       <c r="B324" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C324">
         <v>65</v>
@@ -9505,7 +9547,7 @@
         <v>23</v>
       </c>
       <c r="B325" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C325">
         <v>65</v>
@@ -9528,7 +9570,7 @@
         <v>23</v>
       </c>
       <c r="B326" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C326">
         <v>65</v>
@@ -9551,7 +9593,7 @@
         <v>23</v>
       </c>
       <c r="B327" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C327">
         <v>65</v>
@@ -9574,7 +9616,7 @@
         <v>23</v>
       </c>
       <c r="B328" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C328">
         <v>65</v>
@@ -9597,7 +9639,7 @@
         <v>23</v>
       </c>
       <c r="B329" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C329">
         <v>65</v>
@@ -9620,7 +9662,7 @@
         <v>24</v>
       </c>
       <c r="B330" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C330">
         <v>20</v>
@@ -9635,7 +9677,7 @@
         <v>3</v>
       </c>
       <c r="G330" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H330">
         <v>25.33333333333333</v>
@@ -9646,7 +9688,7 @@
         <v>24</v>
       </c>
       <c r="B331" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C331">
         <v>70</v>
@@ -9661,7 +9703,7 @@
         <v>6</v>
       </c>
       <c r="G331" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H331">
         <v>81.66666666666667</v>
@@ -9672,7 +9714,7 @@
         <v>24</v>
       </c>
       <c r="B332" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C332">
         <v>90</v>
@@ -9687,7 +9729,7 @@
         <v>6</v>
       </c>
       <c r="G332" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H332">
         <v>93.00000000000001</v>
@@ -9698,7 +9740,7 @@
         <v>24</v>
       </c>
       <c r="B333" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C333">
         <v>120</v>
@@ -9713,7 +9755,7 @@
         <v>7.5</v>
       </c>
       <c r="G333" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H333">
         <v>124</v>
@@ -9724,7 +9766,7 @@
         <v>24</v>
       </c>
       <c r="B334" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C334">
         <v>140</v>
@@ -9739,7 +9781,7 @@
         <v>10</v>
       </c>
       <c r="G334" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H334">
         <v>140</v>
@@ -9750,7 +9792,7 @@
         <v>24</v>
       </c>
       <c r="B335" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C335">
         <v>80</v>
@@ -9765,7 +9807,7 @@
         <v>8.5</v>
       </c>
       <c r="G335" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H335">
         <v>133.3333333333333</v>
@@ -9776,7 +9818,7 @@
         <v>24</v>
       </c>
       <c r="B336" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C336">
         <v>80</v>
@@ -9791,7 +9833,7 @@
         <v>10</v>
       </c>
       <c r="G336" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H336">
         <v>101.3333333333333</v>
@@ -9802,7 +9844,7 @@
         <v>24</v>
       </c>
       <c r="B337" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C337">
         <v>20</v>
@@ -9817,7 +9859,7 @@
         <v>4</v>
       </c>
       <c r="G337" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H337">
         <v>25.33333333333333</v>
@@ -9828,7 +9870,7 @@
         <v>24</v>
       </c>
       <c r="B338" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C338">
         <v>40</v>
@@ -9843,7 +9885,7 @@
         <v>6</v>
       </c>
       <c r="G338" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H338">
         <v>50.66666666666666</v>
@@ -9854,7 +9896,7 @@
         <v>24</v>
       </c>
       <c r="B339" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C339">
         <v>60</v>
@@ -9869,7 +9911,7 @@
         <v>7</v>
       </c>
       <c r="G339" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H339">
         <v>66</v>
@@ -9880,7 +9922,7 @@
         <v>24</v>
       </c>
       <c r="B340" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C340">
         <v>70</v>
@@ -9895,7 +9937,7 @@
         <v>8.5</v>
       </c>
       <c r="G340" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H340">
         <v>77</v>
@@ -9906,7 +9948,7 @@
         <v>24</v>
       </c>
       <c r="B341" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C341">
         <v>75</v>
@@ -9921,7 +9963,7 @@
         <v>8.75</v>
       </c>
       <c r="G341" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H341">
         <v>77.50000000000001</v>
@@ -9932,7 +9974,7 @@
         <v>24</v>
       </c>
       <c r="B342" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C342">
         <v>50</v>
@@ -9947,7 +9989,7 @@
         <v>8</v>
       </c>
       <c r="G342" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H342">
         <v>66.66666666666666</v>
@@ -9958,7 +10000,7 @@
         <v>24</v>
       </c>
       <c r="B343" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C343">
         <v>40</v>
@@ -9973,7 +10015,7 @@
         <v>6</v>
       </c>
       <c r="G343" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H343">
         <v>50.66666666666666</v>
@@ -9984,7 +10026,7 @@
         <v>24</v>
       </c>
       <c r="B344" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C344">
         <v>50</v>
@@ -9999,7 +10041,7 @@
         <v>6.5</v>
       </c>
       <c r="G344" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H344">
         <v>63.33333333333333</v>
@@ -10010,7 +10052,7 @@
         <v>24</v>
       </c>
       <c r="B345" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C345">
         <v>63</v>
@@ -10025,7 +10067,7 @@
         <v>8</v>
       </c>
       <c r="G345" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H345">
         <v>75.59999999999999</v>
@@ -10036,7 +10078,7 @@
         <v>24</v>
       </c>
       <c r="B346" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C346">
         <v>63</v>
@@ -10051,7 +10093,7 @@
         <v>8.5</v>
       </c>
       <c r="G346" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H346">
         <v>75.59999999999999</v>
@@ -10062,7 +10104,7 @@
         <v>24</v>
       </c>
       <c r="B347" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C347">
         <v>11</v>
@@ -10077,7 +10119,7 @@
         <v>5</v>
       </c>
       <c r="G347" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H347">
         <v>16.5</v>
@@ -10088,7 +10130,7 @@
         <v>24</v>
       </c>
       <c r="B348" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C348">
         <v>32</v>
@@ -10103,7 +10145,7 @@
         <v>5</v>
       </c>
       <c r="G348" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H348">
         <v>48</v>
@@ -10114,7 +10156,7 @@
         <v>24</v>
       </c>
       <c r="B349" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C349">
         <v>33</v>
@@ -10129,7 +10171,7 @@
         <v>7</v>
       </c>
       <c r="G349" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H349">
         <v>49.5</v>
@@ -10140,7 +10182,7 @@
         <v>24</v>
       </c>
       <c r="B350" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C350">
         <v>59</v>
@@ -10155,7 +10197,7 @@
         <v>8</v>
       </c>
       <c r="G350" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H350">
         <v>82.59999999999999</v>
@@ -10166,7 +10208,7 @@
         <v>24</v>
       </c>
       <c r="B351" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C351">
         <v>39</v>
@@ -10181,7 +10223,7 @@
         <v>9</v>
       </c>
       <c r="G351" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H351">
         <v>58.5</v>
@@ -10192,7 +10234,7 @@
         <v>24</v>
       </c>
       <c r="B352" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C352">
         <v>66</v>
@@ -10207,7 +10249,7 @@
         <v>9</v>
       </c>
       <c r="G352" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H352">
         <v>92.39999999999999</v>
@@ -10218,7 +10260,7 @@
         <v>25</v>
       </c>
       <c r="B353" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C353">
         <v>70</v>
@@ -10233,7 +10275,7 @@
         <v>6</v>
       </c>
       <c r="G353" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H353">
         <v>81.66666666666667</v>
@@ -10244,7 +10286,7 @@
         <v>25</v>
       </c>
       <c r="B354" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C354">
         <v>120</v>
@@ -10259,7 +10301,7 @@
         <v>6</v>
       </c>
       <c r="G354" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H354">
         <v>124</v>
@@ -10270,7 +10312,7 @@
         <v>25</v>
       </c>
       <c r="B355" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C355">
         <v>140</v>
@@ -10285,7 +10327,7 @@
         <v>6.5</v>
       </c>
       <c r="G355" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H355">
         <v>144.6666666666667</v>
@@ -10296,7 +10338,7 @@
         <v>25</v>
       </c>
       <c r="B356" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C356">
         <v>160</v>
@@ -10311,7 +10353,7 @@
         <v>8.5</v>
       </c>
       <c r="G356" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H356">
         <v>165.3333333333333</v>
@@ -10322,7 +10364,7 @@
         <v>25</v>
       </c>
       <c r="B357" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C357">
         <v>140</v>
@@ -10337,7 +10379,7 @@
         <v>8.5</v>
       </c>
       <c r="G357" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H357">
         <v>163.3333333333333</v>
@@ -10348,7 +10390,7 @@
         <v>25</v>
       </c>
       <c r="B358" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C358">
         <v>140</v>
@@ -10363,7 +10405,7 @@
         <v>9</v>
       </c>
       <c r="G358" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H358">
         <v>163.3333333333333</v>
@@ -10374,7 +10416,7 @@
         <v>25</v>
       </c>
       <c r="B359" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C359">
         <v>120</v>
@@ -10389,7 +10431,7 @@
         <v>9</v>
       </c>
       <c r="G359" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H359">
         <v>144</v>
@@ -10400,7 +10442,7 @@
         <v>25</v>
       </c>
       <c r="B360" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C360">
         <v>30</v>
@@ -10415,7 +10457,7 @@
         <v>6</v>
       </c>
       <c r="G360" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H360">
         <v>38</v>
@@ -10426,7 +10468,7 @@
         <v>25</v>
       </c>
       <c r="B361" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C361">
         <v>40</v>
@@ -10441,7 +10483,7 @@
         <v>7</v>
       </c>
       <c r="G361" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H361">
         <v>48</v>
@@ -10452,7 +10494,7 @@
         <v>25</v>
       </c>
       <c r="B362" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C362">
         <v>50</v>
@@ -10467,7 +10509,7 @@
         <v>8</v>
       </c>
       <c r="G362" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H362">
         <v>53.33333333333334</v>
@@ -10478,7 +10520,7 @@
         <v>25</v>
       </c>
       <c r="B363" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C363">
         <v>55</v>
@@ -10493,7 +10535,7 @@
         <v>10</v>
       </c>
       <c r="G363" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H363">
         <v>56.83333333333334</v>
@@ -10504,7 +10546,7 @@
         <v>25</v>
       </c>
       <c r="B364" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C364">
         <v>45</v>
@@ -10519,7 +10561,7 @@
         <v>9</v>
       </c>
       <c r="G364" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H364">
         <v>52.5</v>
@@ -10530,7 +10572,7 @@
         <v>25</v>
       </c>
       <c r="B365" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C365">
         <v>45</v>
@@ -10545,7 +10587,7 @@
         <v>9.5</v>
       </c>
       <c r="G365" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H365">
         <v>52.5</v>
@@ -10556,7 +10598,7 @@
         <v>25</v>
       </c>
       <c r="B366" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C366">
         <v>45</v>
@@ -10571,7 +10613,7 @@
         <v>7</v>
       </c>
       <c r="G366" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H366">
         <v>57</v>
@@ -10582,7 +10624,7 @@
         <v>25</v>
       </c>
       <c r="B367" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C367">
         <v>50</v>
@@ -10597,7 +10639,7 @@
         <v>8</v>
       </c>
       <c r="G367" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H367">
         <v>63.33333333333333</v>
@@ -10608,7 +10650,7 @@
         <v>25</v>
       </c>
       <c r="B368" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C368">
         <v>50</v>
@@ -10623,7 +10665,7 @@
         <v>8</v>
       </c>
       <c r="G368" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H368">
         <v>63.33333333333333</v>
@@ -10634,7 +10676,7 @@
         <v>25</v>
       </c>
       <c r="B369" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C369">
         <v>50</v>
@@ -10649,7 +10691,7 @@
         <v>8</v>
       </c>
       <c r="G369" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H369">
         <v>63.33333333333333</v>
@@ -10660,7 +10702,7 @@
         <v>25</v>
       </c>
       <c r="B370" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C370">
         <v>40</v>
@@ -10675,7 +10717,7 @@
         <v>8.5</v>
       </c>
       <c r="G370" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H370">
         <v>60</v>
@@ -10686,7 +10728,7 @@
         <v>26</v>
       </c>
       <c r="B371" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C371">
         <v>20</v>
@@ -10701,7 +10743,7 @@
         <v>5</v>
       </c>
       <c r="G371" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H371">
         <v>25.33333333333333</v>
@@ -10712,7 +10754,7 @@
         <v>27</v>
       </c>
       <c r="B372" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C372">
         <v>40</v>
@@ -10727,7 +10769,7 @@
         <v>6</v>
       </c>
       <c r="G372" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H372">
         <v>46.66666666666667</v>
@@ -10738,7 +10780,7 @@
         <v>28</v>
       </c>
       <c r="B373" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C373">
         <v>50</v>
@@ -10753,7 +10795,7 @@
         <v>7</v>
       </c>
       <c r="G373" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H373">
         <v>60</v>
@@ -10764,7 +10806,7 @@
         <v>29</v>
       </c>
       <c r="B374" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C374">
         <v>50</v>
@@ -10779,7 +10821,7 @@
         <v>6.5</v>
       </c>
       <c r="G374" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H374">
         <v>63.33333333333333</v>
@@ -10790,7 +10832,7 @@
         <v>30</v>
       </c>
       <c r="B375" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C375">
         <v>60</v>
@@ -10805,7 +10847,7 @@
         <v>7</v>
       </c>
       <c r="G375" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H375">
         <v>66</v>
@@ -10816,7 +10858,7 @@
         <v>31</v>
       </c>
       <c r="B376" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C376">
         <v>70</v>
@@ -10831,7 +10873,7 @@
         <v>7.75</v>
       </c>
       <c r="G376" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H376">
         <v>72.33333333333334</v>
@@ -10842,7 +10884,7 @@
         <v>32</v>
       </c>
       <c r="B377" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C377">
         <v>75</v>
@@ -10857,7 +10899,7 @@
         <v>8</v>
       </c>
       <c r="G377" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H377">
         <v>77.50000000000001</v>
@@ -10868,7 +10910,7 @@
         <v>33</v>
       </c>
       <c r="B378" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C378">
         <v>77.5</v>
@@ -10883,7 +10925,7 @@
         <v>10</v>
       </c>
       <c r="G378" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H378">
         <v>77.5</v>
@@ -10894,7 +10936,7 @@
         <v>34</v>
       </c>
       <c r="B379" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C379">
         <v>66.25</v>
@@ -10909,7 +10951,7 @@
         <v>9</v>
       </c>
       <c r="G379" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H379">
         <v>77.29166666666667</v>
@@ -10920,7 +10962,7 @@
         <v>35</v>
       </c>
       <c r="B380" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C380">
         <v>60</v>
@@ -10935,7 +10977,7 @@
         <v>8.25</v>
       </c>
       <c r="G380" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H380">
         <v>70</v>
@@ -10946,7 +10988,7 @@
         <v>36</v>
       </c>
       <c r="B381" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C381">
         <v>30</v>
@@ -10961,7 +11003,7 @@
         <v>6</v>
       </c>
       <c r="G381" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H381">
         <v>42</v>
@@ -10972,7 +11014,7 @@
         <v>37</v>
       </c>
       <c r="B382" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C382">
         <v>50</v>
@@ -10987,7 +11029,7 @@
         <v>8.5</v>
       </c>
       <c r="G382" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H382">
         <v>63.33333333333333</v>
@@ -10998,7 +11040,7 @@
         <v>38</v>
       </c>
       <c r="B383" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C383">
         <v>50</v>
@@ -11013,7 +11055,7 @@
         <v>8</v>
       </c>
       <c r="G383" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H383">
         <v>63.33333333333333</v>
@@ -11024,7 +11066,7 @@
         <v>39</v>
       </c>
       <c r="B384" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C384">
         <v>50</v>
@@ -11039,7 +11081,7 @@
         <v>10</v>
       </c>
       <c r="G384" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H384">
         <v>60</v>
@@ -11050,7 +11092,7 @@
         <v>40</v>
       </c>
       <c r="B385" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C385">
         <v>0</v>
@@ -11065,7 +11107,7 @@
         <v>6</v>
       </c>
       <c r="G385" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H385">
         <v>0</v>
@@ -11076,7 +11118,7 @@
         <v>41</v>
       </c>
       <c r="B386" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C386">
         <v>25</v>
@@ -11091,7 +11133,7 @@
         <v>8</v>
       </c>
       <c r="G386" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H386">
         <v>30</v>
@@ -11102,7 +11144,7 @@
         <v>42</v>
       </c>
       <c r="B387" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C387">
         <v>25</v>
@@ -11117,7 +11159,7 @@
         <v>8</v>
       </c>
       <c r="G387" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H387">
         <v>31.66666666666666</v>
@@ -11128,7 +11170,7 @@
         <v>43</v>
       </c>
       <c r="B388" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C388">
         <v>25</v>
@@ -11143,7 +11185,7 @@
         <v>8.5</v>
       </c>
       <c r="G388" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H388">
         <v>31.66666666666666</v>
@@ -11154,7 +11196,7 @@
         <v>44</v>
       </c>
       <c r="B389" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C389">
         <v>45</v>
@@ -11169,7 +11211,7 @@
         <v>6.5</v>
       </c>
       <c r="G389" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H389">
         <v>62.99999999999999</v>
@@ -11180,7 +11222,7 @@
         <v>45</v>
       </c>
       <c r="B390" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C390">
         <v>60</v>
@@ -11195,7 +11237,7 @@
         <v>8</v>
       </c>
       <c r="G390" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H390">
         <v>76</v>
@@ -11206,7 +11248,7 @@
         <v>46</v>
       </c>
       <c r="B391" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C391">
         <v>60</v>
@@ -11221,7 +11263,7 @@
         <v>7.5</v>
       </c>
       <c r="G391" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H391">
         <v>76</v>
@@ -11232,7 +11274,7 @@
         <v>47</v>
       </c>
       <c r="B392" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C392">
         <v>60</v>
@@ -11247,7 +11289,7 @@
         <v>7.5</v>
       </c>
       <c r="G392" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H392">
         <v>76</v>
@@ -11258,7 +11300,7 @@
         <v>48</v>
       </c>
       <c r="B393" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C393">
         <v>60</v>
@@ -11273,7 +11315,7 @@
         <v>9</v>
       </c>
       <c r="G393" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H393">
         <v>76</v>
@@ -11284,7 +11326,7 @@
         <v>49</v>
       </c>
       <c r="B394" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C394">
         <v>40</v>
@@ -11299,7 +11341,7 @@
         <v>8</v>
       </c>
       <c r="G394" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H394">
         <v>53.33333333333333</v>
@@ -11310,7 +11352,7 @@
         <v>50</v>
       </c>
       <c r="B395" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C395">
         <v>40</v>
@@ -11325,7 +11367,7 @@
         <v>7.5</v>
       </c>
       <c r="G395" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H395">
         <v>56</v>
@@ -11336,7 +11378,7 @@
         <v>51</v>
       </c>
       <c r="B396" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C396">
         <v>40</v>
@@ -11351,7 +11393,7 @@
         <v>8</v>
       </c>
       <c r="G396" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H396">
         <v>56</v>
@@ -11362,7 +11404,7 @@
         <v>52</v>
       </c>
       <c r="B397" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C397">
         <v>40</v>
@@ -11377,7 +11419,7 @@
         <v>8</v>
       </c>
       <c r="G397" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H397">
         <v>56</v>
@@ -11388,7 +11430,7 @@
         <v>53</v>
       </c>
       <c r="B398" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C398">
         <v>40</v>
@@ -11403,7 +11445,7 @@
         <v>8.5</v>
       </c>
       <c r="G398" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H398">
         <v>56</v>
@@ -11414,7 +11456,7 @@
         <v>54</v>
       </c>
       <c r="B399" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C399">
         <v>40</v>
@@ -11429,7 +11471,7 @@
         <v>9</v>
       </c>
       <c r="G399" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H399">
         <v>56</v>
@@ -11440,7 +11482,7 @@
         <v>55</v>
       </c>
       <c r="B400" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C400">
         <v>20</v>
@@ -11455,7 +11497,7 @@
         <v>5</v>
       </c>
       <c r="G400" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H400">
         <v>25.33333333333333</v>
@@ -11466,7 +11508,7 @@
         <v>56</v>
       </c>
       <c r="B401" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C401">
         <v>70</v>
@@ -11481,7 +11523,7 @@
         <v>6</v>
       </c>
       <c r="G401" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H401">
         <v>81.66666666666667</v>
@@ -11492,7 +11534,7 @@
         <v>57</v>
       </c>
       <c r="B402" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C402">
         <v>120</v>
@@ -11507,7 +11549,7 @@
         <v>7.5</v>
       </c>
       <c r="G402" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H402">
         <v>124</v>
@@ -11518,7 +11560,7 @@
         <v>58</v>
       </c>
       <c r="B403" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C403">
         <v>110</v>
@@ -11533,7 +11575,7 @@
         <v>8.5</v>
       </c>
       <c r="G403" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H403">
         <v>128.3333333333333</v>
@@ -11544,7 +11586,7 @@
         <v>59</v>
       </c>
       <c r="B404" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C404">
         <v>110</v>
@@ -11559,7 +11601,7 @@
         <v>10</v>
       </c>
       <c r="G404" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H404">
         <v>124.6666666666667</v>
@@ -11570,7 +11612,7 @@
         <v>60</v>
       </c>
       <c r="B405" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C405">
         <v>100</v>
@@ -11585,7 +11627,7 @@
         <v>9.5</v>
       </c>
       <c r="G405" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H405">
         <v>110</v>
@@ -11596,7 +11638,7 @@
         <v>61</v>
       </c>
       <c r="B406" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C406">
         <v>40</v>
@@ -11611,7 +11653,7 @@
         <v>6</v>
       </c>
       <c r="G406" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H406">
         <v>60</v>
@@ -11622,7 +11664,7 @@
         <v>62</v>
       </c>
       <c r="B407" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C407">
         <v>50</v>
@@ -11637,7 +11679,7 @@
         <v>7</v>
       </c>
       <c r="G407" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H407">
         <v>70</v>
@@ -11648,7 +11690,7 @@
         <v>63</v>
       </c>
       <c r="B408" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C408">
         <v>50</v>
@@ -11663,7 +11705,7 @@
         <v>7.5</v>
       </c>
       <c r="G408" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H408">
         <v>70</v>
@@ -11674,7 +11716,7 @@
         <v>64</v>
       </c>
       <c r="B409" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C409">
         <v>50</v>
@@ -11689,7 +11731,7 @@
         <v>8.5</v>
       </c>
       <c r="G409" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H409">
         <v>70</v>
@@ -11700,7 +11742,7 @@
         <v>65</v>
       </c>
       <c r="B410" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C410">
         <v>30</v>
@@ -11715,7 +11757,7 @@
         <v>6</v>
       </c>
       <c r="G410" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H410">
         <v>40</v>
@@ -11726,7 +11768,7 @@
         <v>66</v>
       </c>
       <c r="B411" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C411">
         <v>30</v>
@@ -11741,7 +11783,7 @@
         <v>6.5</v>
       </c>
       <c r="G411" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H411">
         <v>40</v>
@@ -11752,7 +11794,7 @@
         <v>67</v>
       </c>
       <c r="B412" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C412">
         <v>40</v>
@@ -11767,7 +11809,7 @@
         <v>8.5</v>
       </c>
       <c r="G412" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H412">
         <v>53.33333333333333</v>
@@ -11778,7 +11820,7 @@
         <v>68</v>
       </c>
       <c r="B413" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C413">
         <v>40</v>
@@ -11793,7 +11835,7 @@
         <v>10</v>
       </c>
       <c r="G413" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H413">
         <v>50.66666666666666</v>
@@ -11804,7 +11846,7 @@
         <v>69</v>
       </c>
       <c r="B414" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C414">
         <v>40</v>
@@ -11819,7 +11861,7 @@
         <v>9</v>
       </c>
       <c r="G414" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H414">
         <v>50.66666666666666</v>
@@ -11830,7 +11872,7 @@
         <v>70</v>
       </c>
       <c r="B415" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C415">
         <v>30</v>
@@ -11845,7 +11887,7 @@
         <v>8</v>
       </c>
       <c r="G415" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H415">
         <v>35</v>
@@ -11856,7 +11898,7 @@
         <v>70</v>
       </c>
       <c r="B416" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C416">
         <v>30</v>
@@ -11871,7 +11913,7 @@
         <v>8</v>
       </c>
       <c r="G416" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H416">
         <v>42</v>
@@ -11882,7 +11924,7 @@
         <v>71</v>
       </c>
       <c r="B417" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C417">
         <v>30</v>
@@ -11897,7 +11939,7 @@
         <v>8.5</v>
       </c>
       <c r="G417" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H417">
         <v>36</v>
@@ -11908,7 +11950,7 @@
         <v>71</v>
       </c>
       <c r="B418" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C418">
         <v>30</v>
@@ -11923,7 +11965,7 @@
         <v>8.5</v>
       </c>
       <c r="G418" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H418">
         <v>42</v>
@@ -11934,7 +11976,7 @@
         <v>72</v>
       </c>
       <c r="B419" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C419">
         <v>30</v>
@@ -11949,7 +11991,7 @@
         <v>9</v>
       </c>
       <c r="G419" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H419">
         <v>36</v>
@@ -11960,7 +12002,7 @@
         <v>72</v>
       </c>
       <c r="B420" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C420">
         <v>30</v>
@@ -11975,7 +12017,7 @@
         <v>9</v>
       </c>
       <c r="G420" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H420">
         <v>42</v>
@@ -11986,7 +12028,7 @@
         <v>73</v>
       </c>
       <c r="B421" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C421">
         <v>20</v>
@@ -11998,7 +12040,7 @@
         <v>160</v>
       </c>
       <c r="G421" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H421">
         <v>25.33333333333333</v>
@@ -12012,7 +12054,7 @@
         <v>73</v>
       </c>
       <c r="B422" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C422">
         <v>70</v>
@@ -12024,7 +12066,7 @@
         <v>350</v>
       </c>
       <c r="G422" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H422">
         <v>81.66666666666667</v>
@@ -12038,7 +12080,7 @@
         <v>73</v>
       </c>
       <c r="B423" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C423">
         <v>120</v>
@@ -12050,7 +12092,7 @@
         <v>360</v>
       </c>
       <c r="G423" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H423">
         <v>132</v>
@@ -12064,7 +12106,7 @@
         <v>73</v>
       </c>
       <c r="B424" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C424">
         <v>90</v>
@@ -12076,7 +12118,7 @@
         <v>1800</v>
       </c>
       <c r="G424" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H424">
         <v>150</v>
@@ -12090,7 +12132,7 @@
         <v>73</v>
       </c>
       <c r="B425" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C425">
         <v>30</v>
@@ -12102,7 +12144,7 @@
         <v>240</v>
       </c>
       <c r="G425" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H425">
         <v>38</v>
@@ -12116,7 +12158,7 @@
         <v>73</v>
       </c>
       <c r="B426" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C426">
         <v>40</v>
@@ -12128,7 +12170,7 @@
         <v>120</v>
       </c>
       <c r="G426" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H426">
         <v>44</v>
@@ -12142,7 +12184,7 @@
         <v>73</v>
       </c>
       <c r="B427" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C427">
         <v>45</v>
@@ -12154,7 +12196,7 @@
         <v>135</v>
       </c>
       <c r="G427" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H427">
         <v>49.50000000000001</v>
@@ -12168,7 +12210,7 @@
         <v>73</v>
       </c>
       <c r="B428" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C428">
         <v>45</v>
@@ -12180,7 +12222,7 @@
         <v>360</v>
       </c>
       <c r="G428" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H428">
         <v>57</v>
@@ -12194,7 +12236,7 @@
         <v>73</v>
       </c>
       <c r="B429" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C429">
         <v>45</v>
@@ -12206,7 +12248,7 @@
         <v>360</v>
       </c>
       <c r="G429" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H429">
         <v>57</v>
@@ -12220,7 +12262,7 @@
         <v>73</v>
       </c>
       <c r="B430" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C430">
         <v>45</v>
@@ -12232,7 +12274,7 @@
         <v>360</v>
       </c>
       <c r="G430" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H430">
         <v>57</v>
@@ -12246,7 +12288,7 @@
         <v>73</v>
       </c>
       <c r="B431" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C431">
         <v>40</v>
@@ -12258,7 +12300,7 @@
         <v>480</v>
       </c>
       <c r="G431" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H431">
         <v>56</v>
@@ -12272,7 +12314,7 @@
         <v>73</v>
       </c>
       <c r="B432" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C432">
         <v>50</v>
@@ -12284,7 +12326,7 @@
         <v>300</v>
       </c>
       <c r="G432" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H432">
         <v>60</v>
@@ -12298,7 +12340,7 @@
         <v>73</v>
       </c>
       <c r="B433" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C433">
         <v>60</v>
@@ -12310,7 +12352,7 @@
         <v>360</v>
       </c>
       <c r="G433" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H433">
         <v>72</v>
@@ -12324,7 +12366,7 @@
         <v>73</v>
       </c>
       <c r="B434" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C434">
         <v>60</v>
@@ -12336,7 +12378,7 @@
         <v>360</v>
       </c>
       <c r="G434" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H434">
         <v>72</v>
@@ -12350,7 +12392,7 @@
         <v>73</v>
       </c>
       <c r="B435" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C435">
         <v>60</v>
@@ -12362,7 +12404,7 @@
         <v>360</v>
       </c>
       <c r="G435" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H435">
         <v>72</v>
@@ -12376,7 +12418,7 @@
         <v>73</v>
       </c>
       <c r="B436" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C436">
         <v>60</v>
@@ -12388,7 +12430,7 @@
         <v>360</v>
       </c>
       <c r="G436" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H436">
         <v>72</v>
@@ -12402,7 +12444,7 @@
         <v>73</v>
       </c>
       <c r="B437" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C437">
         <v>20</v>
@@ -12414,7 +12456,7 @@
         <v>160</v>
       </c>
       <c r="G437" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H437">
         <v>25.33333333333333</v>
@@ -12428,7 +12470,7 @@
         <v>73</v>
       </c>
       <c r="B438" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C438">
         <v>30</v>
@@ -12440,7 +12482,7 @@
         <v>150</v>
       </c>
       <c r="G438" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H438">
         <v>35</v>
@@ -12454,7 +12496,7 @@
         <v>73</v>
       </c>
       <c r="B439" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C439">
         <v>20</v>
@@ -12466,7 +12508,7 @@
         <v>240</v>
       </c>
       <c r="G439" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H439">
         <v>28</v>
@@ -12480,7 +12522,7 @@
         <v>73</v>
       </c>
       <c r="B440" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C440">
         <v>30</v>
@@ -12492,7 +12534,7 @@
         <v>240</v>
       </c>
       <c r="G440" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H440">
         <v>38</v>
@@ -12506,7 +12548,7 @@
         <v>73</v>
       </c>
       <c r="B441" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C441">
         <v>40</v>
@@ -12518,7 +12560,7 @@
         <v>120</v>
       </c>
       <c r="G441" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H441">
         <v>44</v>
@@ -12532,7 +12574,7 @@
         <v>73</v>
       </c>
       <c r="B442" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C442">
         <v>30</v>
@@ -12544,7 +12586,7 @@
         <v>240</v>
       </c>
       <c r="G442" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H442">
         <v>38</v>
@@ -12558,7 +12600,7 @@
         <v>73</v>
       </c>
       <c r="B443" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C443">
         <v>30</v>
@@ -12570,13 +12612,377 @@
         <v>240</v>
       </c>
       <c r="G443" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H443">
         <v>38</v>
       </c>
       <c r="I443">
         <v>8.5</v>
+      </c>
+    </row>
+    <row r="444" spans="1:9">
+      <c r="A444" t="s">
+        <v>74</v>
+      </c>
+      <c r="B444" t="s">
+        <v>110</v>
+      </c>
+      <c r="C444">
+        <v>20</v>
+      </c>
+      <c r="D444">
+        <v>8</v>
+      </c>
+      <c r="E444">
+        <v>160</v>
+      </c>
+      <c r="F444">
+        <v>4</v>
+      </c>
+      <c r="G444" t="s">
+        <v>340</v>
+      </c>
+      <c r="H444">
+        <v>25.33333333333333</v>
+      </c>
+    </row>
+    <row r="445" spans="1:9">
+      <c r="A445" t="s">
+        <v>74</v>
+      </c>
+      <c r="B445" t="s">
+        <v>110</v>
+      </c>
+      <c r="C445">
+        <v>70</v>
+      </c>
+      <c r="D445">
+        <v>6</v>
+      </c>
+      <c r="E445">
+        <v>420</v>
+      </c>
+      <c r="F445">
+        <v>6</v>
+      </c>
+      <c r="G445" t="s">
+        <v>360</v>
+      </c>
+      <c r="H445">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="446" spans="1:9">
+      <c r="A446" t="s">
+        <v>74</v>
+      </c>
+      <c r="B446" t="s">
+        <v>110</v>
+      </c>
+      <c r="C446">
+        <v>110</v>
+      </c>
+      <c r="D446">
+        <v>1</v>
+      </c>
+      <c r="E446">
+        <v>110</v>
+      </c>
+      <c r="F446">
+        <v>7</v>
+      </c>
+      <c r="G446" t="s">
+        <v>361</v>
+      </c>
+      <c r="H446">
+        <v>113.6666666666667</v>
+      </c>
+    </row>
+    <row r="447" spans="1:9">
+      <c r="A447" t="s">
+        <v>74</v>
+      </c>
+      <c r="B447" t="s">
+        <v>110</v>
+      </c>
+      <c r="C447">
+        <v>110</v>
+      </c>
+      <c r="D447">
+        <v>3</v>
+      </c>
+      <c r="E447">
+        <v>330</v>
+      </c>
+      <c r="F447">
+        <v>8.5</v>
+      </c>
+      <c r="G447" t="s">
+        <v>362</v>
+      </c>
+      <c r="H447">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="448" spans="1:9">
+      <c r="A448" t="s">
+        <v>74</v>
+      </c>
+      <c r="B448" t="s">
+        <v>110</v>
+      </c>
+      <c r="C448">
+        <v>90</v>
+      </c>
+      <c r="D448">
+        <v>10</v>
+      </c>
+      <c r="E448">
+        <v>900</v>
+      </c>
+      <c r="F448">
+        <v>8</v>
+      </c>
+      <c r="G448" t="s">
+        <v>363</v>
+      </c>
+      <c r="H448">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="449" spans="1:8">
+      <c r="A449" t="s">
+        <v>74</v>
+      </c>
+      <c r="B449" t="s">
+        <v>110</v>
+      </c>
+      <c r="C449">
+        <v>90</v>
+      </c>
+      <c r="D449">
+        <v>10</v>
+      </c>
+      <c r="E449">
+        <v>900</v>
+      </c>
+      <c r="F449">
+        <v>8.5</v>
+      </c>
+      <c r="G449" t="s">
+        <v>364</v>
+      </c>
+      <c r="H449">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="450" spans="1:8">
+      <c r="A450" t="s">
+        <v>74</v>
+      </c>
+      <c r="B450" t="s">
+        <v>90</v>
+      </c>
+      <c r="C450">
+        <v>30</v>
+      </c>
+      <c r="D450">
+        <v>8</v>
+      </c>
+      <c r="E450">
+        <v>240</v>
+      </c>
+      <c r="F450">
+        <v>5.5</v>
+      </c>
+      <c r="G450" t="s">
+        <v>365</v>
+      </c>
+      <c r="H450">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="451" spans="1:8">
+      <c r="A451" t="s">
+        <v>74</v>
+      </c>
+      <c r="B451" t="s">
+        <v>83</v>
+      </c>
+      <c r="C451">
+        <v>40</v>
+      </c>
+      <c r="D451">
+        <v>8</v>
+      </c>
+      <c r="E451">
+        <v>320</v>
+      </c>
+      <c r="F451">
+        <v>6</v>
+      </c>
+      <c r="G451" t="s">
+        <v>366</v>
+      </c>
+      <c r="H451">
+        <v>50.66666666666666</v>
+      </c>
+    </row>
+    <row r="452" spans="1:8">
+      <c r="A452" t="s">
+        <v>74</v>
+      </c>
+      <c r="B452" t="s">
+        <v>83</v>
+      </c>
+      <c r="C452">
+        <v>45</v>
+      </c>
+      <c r="D452">
+        <v>1</v>
+      </c>
+      <c r="E452">
+        <v>45</v>
+      </c>
+      <c r="F452">
+        <v>6</v>
+      </c>
+      <c r="G452" t="s">
+        <v>367</v>
+      </c>
+      <c r="H452">
+        <v>46.50000000000001</v>
+      </c>
+    </row>
+    <row r="453" spans="1:8">
+      <c r="A453" t="s">
+        <v>74</v>
+      </c>
+      <c r="B453" t="s">
+        <v>83</v>
+      </c>
+      <c r="C453">
+        <v>50</v>
+      </c>
+      <c r="D453">
+        <v>1</v>
+      </c>
+      <c r="E453">
+        <v>50</v>
+      </c>
+      <c r="F453">
+        <v>6.5</v>
+      </c>
+      <c r="G453" t="s">
+        <v>368</v>
+      </c>
+      <c r="H453">
+        <v>51.66666666666667</v>
+      </c>
+    </row>
+    <row r="454" spans="1:8">
+      <c r="A454" t="s">
+        <v>74</v>
+      </c>
+      <c r="B454" t="s">
+        <v>83</v>
+      </c>
+      <c r="C454">
+        <v>55</v>
+      </c>
+      <c r="D454">
+        <v>1</v>
+      </c>
+      <c r="E454">
+        <v>55</v>
+      </c>
+      <c r="F454">
+        <v>7</v>
+      </c>
+      <c r="G454" t="s">
+        <v>369</v>
+      </c>
+      <c r="H454">
+        <v>56.83333333333334</v>
+      </c>
+    </row>
+    <row r="455" spans="1:8">
+      <c r="A455" t="s">
+        <v>74</v>
+      </c>
+      <c r="B455" t="s">
+        <v>83</v>
+      </c>
+      <c r="C455">
+        <v>60</v>
+      </c>
+      <c r="D455">
+        <v>0</v>
+      </c>
+      <c r="E455">
+        <v>0</v>
+      </c>
+      <c r="F455">
+        <v>10</v>
+      </c>
+      <c r="G455" t="s">
+        <v>370</v>
+      </c>
+      <c r="H455">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="456" spans="1:8">
+      <c r="A456" t="s">
+        <v>74</v>
+      </c>
+      <c r="B456" t="s">
+        <v>83</v>
+      </c>
+      <c r="C456">
+        <v>50</v>
+      </c>
+      <c r="D456">
+        <v>6</v>
+      </c>
+      <c r="E456">
+        <v>300</v>
+      </c>
+      <c r="F456">
+        <v>8</v>
+      </c>
+      <c r="G456" t="s">
+        <v>371</v>
+      </c>
+      <c r="H456">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="457" spans="1:8">
+      <c r="A457" t="s">
+        <v>74</v>
+      </c>
+      <c r="B457" t="s">
+        <v>83</v>
+      </c>
+      <c r="C457">
+        <v>50</v>
+      </c>
+      <c r="D457">
+        <v>6</v>
+      </c>
+      <c r="E457">
+        <v>300</v>
+      </c>
+      <c r="F457">
+        <v>9</v>
+      </c>
+      <c r="G457" t="s">
+        <v>372</v>
+      </c>
+      <c r="H457">
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/data/workout_log.xlsx
+++ b/data/workout_log.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1246" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1318" uniqueCount="398">
   <si>
     <t>Timestamp</t>
   </si>
@@ -241,6 +241,9 @@
     <t>2026-03-14 09:00:00</t>
   </si>
   <si>
+    <t>2026-03-22</t>
+  </si>
+  <si>
     <t>Overhead Press</t>
   </si>
   <si>
@@ -433,6 +436,12 @@
     <t>Skullcrusher</t>
   </si>
   <si>
+    <t>Tricep Ext</t>
+  </si>
+  <si>
+    <t>DB Pullover</t>
+  </si>
+  <si>
     <t>Warm-up. Run: 2.75km in 12:30 prior.</t>
   </si>
   <si>
@@ -1133,6 +1142,72 @@
   </si>
   <si>
     <t>Final high-effort volume set</t>
+  </si>
+  <si>
+    <t>Mobilising</t>
+  </si>
+  <si>
+    <t>Warmup</t>
+  </si>
+  <si>
+    <t>Skill</t>
+  </si>
+  <si>
+    <t>Heavy double</t>
+  </si>
+  <si>
+    <t>Back-off 1</t>
+  </si>
+  <si>
+    <t>5s grind; God rep</t>
+  </si>
+  <si>
+    <t>Mobility</t>
+  </si>
+  <si>
+    <t>Transition</t>
+  </si>
+  <si>
+    <t>Max grind</t>
+  </si>
+  <si>
+    <t>Volume 1</t>
+  </si>
+  <si>
+    <t>Volume 2</t>
+  </si>
+  <si>
+    <t>Absolute failure</t>
+  </si>
+  <si>
+    <t>High volume pull</t>
+  </si>
+  <si>
+    <t>Heavy Triple</t>
+  </si>
+  <si>
+    <t>Set 1</t>
+  </si>
+  <si>
+    <t>Set 2</t>
+  </si>
+  <si>
+    <t>Set 3</t>
+  </si>
+  <si>
+    <t>Finisher SS</t>
+  </si>
+  <si>
+    <t>Expansion</t>
+  </si>
+  <si>
+    <t>Stretch</t>
+  </si>
+  <si>
+    <t>Tension</t>
+  </si>
+  <si>
+    <t>Final Century Rep</t>
   </si>
 </sst>
 </file>
@@ -1490,7 +1565,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I457"/>
+  <dimension ref="A1:I481"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -1527,7 +1602,7 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C2">
         <v>30</v>
@@ -1542,7 +1617,7 @@
         <v>4</v>
       </c>
       <c r="G2" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="H2">
         <v>40</v>
@@ -1553,7 +1628,7 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C3">
         <v>30</v>
@@ -1576,7 +1651,7 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C4">
         <v>30</v>
@@ -1599,7 +1674,7 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C5">
         <v>30</v>
@@ -1622,7 +1697,7 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C6">
         <v>60</v>
@@ -1637,7 +1712,7 @@
         <v>5</v>
       </c>
       <c r="G6" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="H6">
         <v>76</v>
@@ -1648,7 +1723,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C7">
         <v>100</v>
@@ -1663,7 +1738,7 @@
         <v>6</v>
       </c>
       <c r="G7" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="H7">
         <v>110</v>
@@ -1674,7 +1749,7 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C8">
         <v>100</v>
@@ -1697,7 +1772,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C9">
         <v>100</v>
@@ -1720,7 +1795,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C10">
         <v>32</v>
@@ -1735,7 +1810,7 @@
         <v>3</v>
       </c>
       <c r="G10" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="H10">
         <v>44.8</v>
@@ -1746,7 +1821,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C11">
         <v>40</v>
@@ -1761,7 +1836,7 @@
         <v>5.5</v>
       </c>
       <c r="G11" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="H11">
         <v>50.66666666666666</v>
@@ -1772,7 +1847,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C12">
         <v>40</v>
@@ -1795,7 +1870,7 @@
         <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C13">
         <v>40</v>
@@ -1810,7 +1885,7 @@
         <v>9</v>
       </c>
       <c r="G13" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="H13">
         <v>48</v>
@@ -1821,7 +1896,7 @@
         <v>9</v>
       </c>
       <c r="B14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C14">
         <v>20</v>
@@ -1844,7 +1919,7 @@
         <v>9</v>
       </c>
       <c r="B15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C15">
         <v>20</v>
@@ -1867,7 +1942,7 @@
         <v>9</v>
       </c>
       <c r="B16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C16">
         <v>20</v>
@@ -1890,7 +1965,7 @@
         <v>9</v>
       </c>
       <c r="B17" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C17">
         <v>20</v>
@@ -1905,7 +1980,7 @@
         <v>8</v>
       </c>
       <c r="G17" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="H17">
         <v>26.66666666666666</v>
@@ -1916,7 +1991,7 @@
         <v>9</v>
       </c>
       <c r="B18" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C18">
         <v>20</v>
@@ -1931,7 +2006,7 @@
         <v>8</v>
       </c>
       <c r="G18" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="H18">
         <v>26.66666666666666</v>
@@ -1942,7 +2017,7 @@
         <v>9</v>
       </c>
       <c r="B19" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C19">
         <v>20</v>
@@ -1957,7 +2032,7 @@
         <v>8</v>
       </c>
       <c r="G19" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="H19">
         <v>25.33333333333333</v>
@@ -1968,7 +2043,7 @@
         <v>9</v>
       </c>
       <c r="B20" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C20">
         <v>20</v>
@@ -1983,7 +2058,7 @@
         <v>8</v>
       </c>
       <c r="G20" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="H20">
         <v>25.33333333333333</v>
@@ -1994,7 +2069,7 @@
         <v>10</v>
       </c>
       <c r="B21" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -2009,7 +2084,7 @@
         <v>7</v>
       </c>
       <c r="G21" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="H21">
         <v>0</v>
@@ -2020,7 +2095,7 @@
         <v>10</v>
       </c>
       <c r="B22" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C22">
         <v>30</v>
@@ -2043,7 +2118,7 @@
         <v>10</v>
       </c>
       <c r="B23" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C23">
         <v>30</v>
@@ -2066,7 +2141,7 @@
         <v>10</v>
       </c>
       <c r="B24" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C24">
         <v>30</v>
@@ -2089,7 +2164,7 @@
         <v>10</v>
       </c>
       <c r="B25" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C25">
         <v>30</v>
@@ -2112,7 +2187,7 @@
         <v>10</v>
       </c>
       <c r="B26" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C26">
         <v>30</v>
@@ -2135,7 +2210,7 @@
         <v>10</v>
       </c>
       <c r="B27" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C27">
         <v>30</v>
@@ -2158,7 +2233,7 @@
         <v>10</v>
       </c>
       <c r="B28" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C28">
         <v>30</v>
@@ -2181,7 +2256,7 @@
         <v>10</v>
       </c>
       <c r="B29" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C29">
         <v>30</v>
@@ -2204,7 +2279,7 @@
         <v>10</v>
       </c>
       <c r="B30" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C30">
         <v>30</v>
@@ -2227,7 +2302,7 @@
         <v>10</v>
       </c>
       <c r="B31" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C31">
         <v>70</v>
@@ -2250,7 +2325,7 @@
         <v>10</v>
       </c>
       <c r="B32" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C32">
         <v>70</v>
@@ -2273,7 +2348,7 @@
         <v>10</v>
       </c>
       <c r="B33" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C33">
         <v>70</v>
@@ -2296,7 +2371,7 @@
         <v>10</v>
       </c>
       <c r="B34" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C34">
         <v>23</v>
@@ -2311,7 +2386,7 @@
         <v>7</v>
       </c>
       <c r="G34" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="H34">
         <v>38.33333333333333</v>
@@ -2322,7 +2397,7 @@
         <v>10</v>
       </c>
       <c r="B35" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C35">
         <v>23</v>
@@ -2337,7 +2412,7 @@
         <v>7</v>
       </c>
       <c r="G35" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="H35">
         <v>38.33333333333333</v>
@@ -2348,7 +2423,7 @@
         <v>10</v>
       </c>
       <c r="B36" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C36">
         <v>23</v>
@@ -2363,7 +2438,7 @@
         <v>9</v>
       </c>
       <c r="G36" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="H36">
         <v>38.33333333333333</v>
@@ -2374,7 +2449,7 @@
         <v>10</v>
       </c>
       <c r="B37" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C37">
         <v>23</v>
@@ -2389,7 +2464,7 @@
         <v>10</v>
       </c>
       <c r="G37" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="H37">
         <v>32.2</v>
@@ -2400,7 +2475,7 @@
         <v>10</v>
       </c>
       <c r="B38" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C38">
         <v>20</v>
@@ -2423,7 +2498,7 @@
         <v>10</v>
       </c>
       <c r="B39" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C39">
         <v>20</v>
@@ -2446,7 +2521,7 @@
         <v>10</v>
       </c>
       <c r="B40" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C40">
         <v>20</v>
@@ -2469,7 +2544,7 @@
         <v>11</v>
       </c>
       <c r="B41" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C41">
         <v>36</v>
@@ -2484,7 +2559,7 @@
         <v>5</v>
       </c>
       <c r="G41" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="H41">
         <v>48</v>
@@ -2495,7 +2570,7 @@
         <v>11</v>
       </c>
       <c r="B42" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C42">
         <v>44</v>
@@ -2510,7 +2585,7 @@
         <v>7</v>
       </c>
       <c r="G42" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="H42">
         <v>52.8</v>
@@ -2521,7 +2596,7 @@
         <v>11</v>
       </c>
       <c r="B43" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C43">
         <v>44</v>
@@ -2536,7 +2611,7 @@
         <v>7.5</v>
       </c>
       <c r="G43" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="H43">
         <v>52.8</v>
@@ -2547,7 +2622,7 @@
         <v>11</v>
       </c>
       <c r="B44" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C44">
         <v>44</v>
@@ -2562,7 +2637,7 @@
         <v>8</v>
       </c>
       <c r="G44" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="H44">
         <v>52.8</v>
@@ -2573,7 +2648,7 @@
         <v>11</v>
       </c>
       <c r="B45" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C45">
         <v>60</v>
@@ -2596,7 +2671,7 @@
         <v>11</v>
       </c>
       <c r="B46" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C46">
         <v>100</v>
@@ -2619,7 +2694,7 @@
         <v>11</v>
       </c>
       <c r="B47" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C47">
         <v>130</v>
@@ -2642,7 +2717,7 @@
         <v>11</v>
       </c>
       <c r="B48" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C48">
         <v>140</v>
@@ -2657,7 +2732,7 @@
         <v>10</v>
       </c>
       <c r="G48" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="H48">
         <v>144.6666666666667</v>
@@ -2668,7 +2743,7 @@
         <v>11</v>
       </c>
       <c r="B49" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C49">
         <v>130</v>
@@ -2691,7 +2766,7 @@
         <v>11</v>
       </c>
       <c r="B50" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C50">
         <v>100</v>
@@ -2714,7 +2789,7 @@
         <v>11</v>
       </c>
       <c r="B51" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C51">
         <v>100</v>
@@ -2729,7 +2804,7 @@
         <v>9</v>
       </c>
       <c r="G51" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="H51">
         <v>133.3333333333333</v>
@@ -2740,7 +2815,7 @@
         <v>11</v>
       </c>
       <c r="B52" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C52">
         <v>20</v>
@@ -2755,7 +2830,7 @@
         <v>8</v>
       </c>
       <c r="G52" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="H52">
         <v>26.66666666666666</v>
@@ -2766,7 +2841,7 @@
         <v>11</v>
       </c>
       <c r="B53" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C53">
         <v>20</v>
@@ -2781,7 +2856,7 @@
         <v>9</v>
       </c>
       <c r="G53" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="H53">
         <v>26.66666666666666</v>
@@ -2792,7 +2867,7 @@
         <v>11</v>
       </c>
       <c r="B54" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C54">
         <v>30</v>
@@ -2815,7 +2890,7 @@
         <v>11</v>
       </c>
       <c r="B55" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C55">
         <v>40</v>
@@ -2838,7 +2913,7 @@
         <v>11</v>
       </c>
       <c r="B56" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C56">
         <v>40</v>
@@ -2861,7 +2936,7 @@
         <v>11</v>
       </c>
       <c r="B57" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C57">
         <v>40</v>
@@ -2884,7 +2959,7 @@
         <v>11</v>
       </c>
       <c r="B58" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C58">
         <v>45</v>
@@ -2907,7 +2982,7 @@
         <v>11</v>
       </c>
       <c r="B59" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C59">
         <v>45</v>
@@ -2930,7 +3005,7 @@
         <v>11</v>
       </c>
       <c r="B60" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C60">
         <v>50</v>
@@ -2945,7 +3020,7 @@
         <v>7.5</v>
       </c>
       <c r="G60" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="H60">
         <v>63.33333333333333</v>
@@ -2956,7 +3031,7 @@
         <v>11</v>
       </c>
       <c r="B61" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C61">
         <v>50</v>
@@ -2971,7 +3046,7 @@
         <v>7.5</v>
       </c>
       <c r="G61" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="H61">
         <v>63.33333333333333</v>
@@ -2982,7 +3057,7 @@
         <v>11</v>
       </c>
       <c r="B62" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C62">
         <v>50</v>
@@ -2997,7 +3072,7 @@
         <v>8.5</v>
       </c>
       <c r="G62" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="H62">
         <v>63.33333333333333</v>
@@ -3008,7 +3083,7 @@
         <v>11</v>
       </c>
       <c r="B63" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C63">
         <v>50</v>
@@ -3023,7 +3098,7 @@
         <v>8.5</v>
       </c>
       <c r="G63" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="H63">
         <v>63.33333333333333</v>
@@ -3034,7 +3109,7 @@
         <v>11</v>
       </c>
       <c r="B64" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C64">
         <v>50</v>
@@ -3049,7 +3124,7 @@
         <v>9</v>
       </c>
       <c r="G64" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="H64">
         <v>63.33333333333333</v>
@@ -3060,7 +3135,7 @@
         <v>11</v>
       </c>
       <c r="B65" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C65">
         <v>50</v>
@@ -3075,7 +3150,7 @@
         <v>9</v>
       </c>
       <c r="G65" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="H65">
         <v>63.33333333333333</v>
@@ -3086,7 +3161,7 @@
         <v>12</v>
       </c>
       <c r="B66" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C66">
         <v>60</v>
@@ -3109,7 +3184,7 @@
         <v>12</v>
       </c>
       <c r="B67" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C67">
         <v>100</v>
@@ -3132,7 +3207,7 @@
         <v>12</v>
       </c>
       <c r="B68" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C68">
         <v>100</v>
@@ -3155,7 +3230,7 @@
         <v>12</v>
       </c>
       <c r="B69" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C69">
         <v>60</v>
@@ -3178,7 +3253,7 @@
         <v>12</v>
       </c>
       <c r="B70" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C70">
         <v>100</v>
@@ -3201,7 +3276,7 @@
         <v>12</v>
       </c>
       <c r="B71" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C71">
         <v>80</v>
@@ -3224,7 +3299,7 @@
         <v>12</v>
       </c>
       <c r="B72" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C72">
         <v>80</v>
@@ -3247,7 +3322,7 @@
         <v>12</v>
       </c>
       <c r="B73" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C73">
         <v>20</v>
@@ -3270,7 +3345,7 @@
         <v>12</v>
       </c>
       <c r="B74" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C74">
         <v>30</v>
@@ -3293,7 +3368,7 @@
         <v>12</v>
       </c>
       <c r="B75" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C75">
         <v>35</v>
@@ -3316,7 +3391,7 @@
         <v>12</v>
       </c>
       <c r="B76" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C76">
         <v>35</v>
@@ -3331,7 +3406,7 @@
         <v>10</v>
       </c>
       <c r="G76" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="H76">
         <v>43.16666666666667</v>
@@ -3342,7 +3417,7 @@
         <v>12</v>
       </c>
       <c r="B77" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C77">
         <v>30</v>
@@ -3365,7 +3440,7 @@
         <v>12</v>
       </c>
       <c r="B78" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C78">
         <v>30</v>
@@ -3388,7 +3463,7 @@
         <v>12</v>
       </c>
       <c r="B79" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C79">
         <v>50</v>
@@ -3411,7 +3486,7 @@
         <v>12</v>
       </c>
       <c r="B80" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C80">
         <v>40</v>
@@ -3434,7 +3509,7 @@
         <v>12</v>
       </c>
       <c r="B81" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C81">
         <v>22</v>
@@ -3457,7 +3532,7 @@
         <v>12</v>
       </c>
       <c r="B82" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C82">
         <v>22</v>
@@ -3480,7 +3555,7 @@
         <v>12</v>
       </c>
       <c r="B83" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C83">
         <v>22</v>
@@ -3503,7 +3578,7 @@
         <v>13</v>
       </c>
       <c r="B84" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C84">
         <v>20</v>
@@ -3518,7 +3593,7 @@
         <v>4</v>
       </c>
       <c r="G84" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="H84">
         <v>28</v>
@@ -3529,7 +3604,7 @@
         <v>13</v>
       </c>
       <c r="B85" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C85">
         <v>40</v>
@@ -3552,7 +3627,7 @@
         <v>13</v>
       </c>
       <c r="B86" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C86">
         <v>50</v>
@@ -3575,7 +3650,7 @@
         <v>13</v>
       </c>
       <c r="B87" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C87">
         <v>60</v>
@@ -3598,7 +3673,7 @@
         <v>13</v>
       </c>
       <c r="B88" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C88">
         <v>60</v>
@@ -3621,7 +3696,7 @@
         <v>13</v>
       </c>
       <c r="B89" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C89">
         <v>60</v>
@@ -3636,7 +3711,7 @@
         <v>9</v>
       </c>
       <c r="G89" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="H89">
         <v>64</v>
@@ -3647,7 +3722,7 @@
         <v>13</v>
       </c>
       <c r="B90" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C90">
         <v>40</v>
@@ -3662,7 +3737,7 @@
         <v>8</v>
       </c>
       <c r="G90" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="H90">
         <v>60</v>
@@ -3673,7 +3748,7 @@
         <v>13</v>
       </c>
       <c r="B91" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C91">
         <v>16</v>
@@ -3688,7 +3763,7 @@
         <v>7</v>
       </c>
       <c r="G91" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="H91">
         <v>21.33333333333333</v>
@@ -3699,7 +3774,7 @@
         <v>13</v>
       </c>
       <c r="B92" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C92">
         <v>16</v>
@@ -3714,7 +3789,7 @@
         <v>7</v>
       </c>
       <c r="G92" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="H92">
         <v>21.33333333333333</v>
@@ -3725,7 +3800,7 @@
         <v>13</v>
       </c>
       <c r="B93" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C93">
         <v>16</v>
@@ -3740,7 +3815,7 @@
         <v>8</v>
       </c>
       <c r="G93" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="H93">
         <v>21.33333333333333</v>
@@ -3751,7 +3826,7 @@
         <v>13</v>
       </c>
       <c r="B94" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C94">
         <v>16</v>
@@ -3766,7 +3841,7 @@
         <v>8</v>
       </c>
       <c r="G94" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="H94">
         <v>21.33333333333333</v>
@@ -3777,7 +3852,7 @@
         <v>13</v>
       </c>
       <c r="B95" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C95">
         <v>16</v>
@@ -3792,7 +3867,7 @@
         <v>8.5</v>
       </c>
       <c r="G95" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="H95">
         <v>21.33333333333333</v>
@@ -3803,7 +3878,7 @@
         <v>13</v>
       </c>
       <c r="B96" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C96">
         <v>16</v>
@@ -3818,7 +3893,7 @@
         <v>8.5</v>
       </c>
       <c r="G96" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="H96">
         <v>21.33333333333333</v>
@@ -3829,7 +3904,7 @@
         <v>13</v>
       </c>
       <c r="B97" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C97">
         <v>8</v>
@@ -3852,7 +3927,7 @@
         <v>13</v>
       </c>
       <c r="B98" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C98">
         <v>8</v>
@@ -3875,7 +3950,7 @@
         <v>13</v>
       </c>
       <c r="B99" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C99">
         <v>8</v>
@@ -3898,7 +3973,7 @@
         <v>13</v>
       </c>
       <c r="B100" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C100">
         <v>58</v>
@@ -3913,7 +3988,7 @@
         <v>7</v>
       </c>
       <c r="G100" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="H100">
         <v>77.33333333333333</v>
@@ -3924,7 +3999,7 @@
         <v>13</v>
       </c>
       <c r="B101" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C101">
         <v>58</v>
@@ -3939,7 +4014,7 @@
         <v>7</v>
       </c>
       <c r="G101" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="H101">
         <v>77.33333333333333</v>
@@ -3950,7 +4025,7 @@
         <v>13</v>
       </c>
       <c r="B102" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C102">
         <v>58</v>
@@ -3973,7 +4048,7 @@
         <v>13</v>
       </c>
       <c r="B103" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C103">
         <v>58</v>
@@ -3996,7 +4071,7 @@
         <v>13</v>
       </c>
       <c r="B104" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C104">
         <v>58</v>
@@ -4019,7 +4094,7 @@
         <v>13</v>
       </c>
       <c r="B105" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C105">
         <v>58</v>
@@ -4042,7 +4117,7 @@
         <v>13</v>
       </c>
       <c r="B106" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C106">
         <v>45</v>
@@ -4065,7 +4140,7 @@
         <v>13</v>
       </c>
       <c r="B107" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C107">
         <v>45</v>
@@ -4088,7 +4163,7 @@
         <v>13</v>
       </c>
       <c r="B108" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C108">
         <v>45</v>
@@ -4111,7 +4186,7 @@
         <v>13</v>
       </c>
       <c r="B109" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C109">
         <v>20</v>
@@ -4134,7 +4209,7 @@
         <v>13</v>
       </c>
       <c r="B110" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C110">
         <v>30</v>
@@ -4149,7 +4224,7 @@
         <v>10</v>
       </c>
       <c r="G110" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="H110">
         <v>34</v>
@@ -4160,7 +4235,7 @@
         <v>14</v>
       </c>
       <c r="B111" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C111">
         <v>20</v>
@@ -4175,7 +4250,7 @@
         <v>3</v>
       </c>
       <c r="G111" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="H111">
         <v>25.33333333333333</v>
@@ -4186,7 +4261,7 @@
         <v>14</v>
       </c>
       <c r="B112" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C112">
         <v>60</v>
@@ -4201,7 +4276,7 @@
         <v>5</v>
       </c>
       <c r="G112" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="H112">
         <v>66</v>
@@ -4212,7 +4287,7 @@
         <v>14</v>
       </c>
       <c r="B113" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C113">
         <v>80</v>
@@ -4227,7 +4302,7 @@
         <v>7</v>
       </c>
       <c r="G113" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="H113">
         <v>88</v>
@@ -4238,7 +4313,7 @@
         <v>14</v>
       </c>
       <c r="B114" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C114">
         <v>90</v>
@@ -4253,7 +4328,7 @@
         <v>7</v>
       </c>
       <c r="G114" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="H114">
         <v>93.00000000000001</v>
@@ -4264,7 +4339,7 @@
         <v>14</v>
       </c>
       <c r="B115" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C115">
         <v>90</v>
@@ -4279,7 +4354,7 @@
         <v>7.5</v>
       </c>
       <c r="G115" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="H115">
         <v>99.00000000000001</v>
@@ -4290,7 +4365,7 @@
         <v>14</v>
       </c>
       <c r="B116" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C116">
         <v>100</v>
@@ -4305,7 +4380,7 @@
         <v>8.5</v>
       </c>
       <c r="G116" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="H116">
         <v>110</v>
@@ -4316,7 +4391,7 @@
         <v>14</v>
       </c>
       <c r="B117" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C117">
         <v>110</v>
@@ -4331,7 +4406,7 @@
         <v>9</v>
       </c>
       <c r="G117" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="H117">
         <v>113.6666666666667</v>
@@ -4342,7 +4417,7 @@
         <v>14</v>
       </c>
       <c r="B118" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C118">
         <v>20</v>
@@ -4357,7 +4432,7 @@
         <v>5</v>
       </c>
       <c r="G118" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="H118">
         <v>28</v>
@@ -4368,7 +4443,7 @@
         <v>14</v>
       </c>
       <c r="B119" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C119">
         <v>30</v>
@@ -4383,7 +4458,7 @@
         <v>6</v>
       </c>
       <c r="G119" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="H119">
         <v>36</v>
@@ -4394,7 +4469,7 @@
         <v>14</v>
       </c>
       <c r="B120" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C120">
         <v>40</v>
@@ -4409,7 +4484,7 @@
         <v>7.5</v>
       </c>
       <c r="G120" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H120">
         <v>45.33333333333333</v>
@@ -4420,7 +4495,7 @@
         <v>14</v>
       </c>
       <c r="B121" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C121">
         <v>45</v>
@@ -4435,7 +4510,7 @@
         <v>8.5</v>
       </c>
       <c r="G121" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="H121">
         <v>49.50000000000001</v>
@@ -4446,7 +4521,7 @@
         <v>14</v>
       </c>
       <c r="B122" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C122">
         <v>50</v>
@@ -4461,7 +4536,7 @@
         <v>10</v>
       </c>
       <c r="G122" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="H122">
         <v>50</v>
@@ -4472,7 +4547,7 @@
         <v>14</v>
       </c>
       <c r="B123" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C123">
         <v>70</v>
@@ -4487,7 +4562,7 @@
         <v>6</v>
       </c>
       <c r="G123" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H123">
         <v>77</v>
@@ -4498,7 +4573,7 @@
         <v>14</v>
       </c>
       <c r="B124" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C124">
         <v>120</v>
@@ -4513,7 +4588,7 @@
         <v>8.5</v>
       </c>
       <c r="G124" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="H124">
         <v>124</v>
@@ -4524,7 +4599,7 @@
         <v>14</v>
       </c>
       <c r="B125" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C125">
         <v>120</v>
@@ -4539,7 +4614,7 @@
         <v>9.5</v>
       </c>
       <c r="G125" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H125">
         <v>124</v>
@@ -4550,7 +4625,7 @@
         <v>14</v>
       </c>
       <c r="B126" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C126">
         <v>120</v>
@@ -4565,7 +4640,7 @@
         <v>9.5</v>
       </c>
       <c r="G126" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="H126">
         <v>124</v>
@@ -4576,7 +4651,7 @@
         <v>14</v>
       </c>
       <c r="B127" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C127">
         <v>120</v>
@@ -4591,7 +4666,7 @@
         <v>9.5</v>
       </c>
       <c r="G127" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="H127">
         <v>124</v>
@@ -4602,7 +4677,7 @@
         <v>14</v>
       </c>
       <c r="B128" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C128">
         <v>20</v>
@@ -4617,7 +4692,7 @@
         <v>6.5</v>
       </c>
       <c r="G128" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="H128">
         <v>26.66666666666666</v>
@@ -4628,7 +4703,7 @@
         <v>14</v>
       </c>
       <c r="B129" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C129">
         <v>20</v>
@@ -4643,7 +4718,7 @@
         <v>6.5</v>
       </c>
       <c r="G129" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="H129">
         <v>26.66666666666666</v>
@@ -4654,7 +4729,7 @@
         <v>14</v>
       </c>
       <c r="B130" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C130">
         <v>20</v>
@@ -4669,7 +4744,7 @@
         <v>8</v>
       </c>
       <c r="G130" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="H130">
         <v>26.66666666666666</v>
@@ -4680,7 +4755,7 @@
         <v>14</v>
       </c>
       <c r="B131" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C131">
         <v>20</v>
@@ -4695,7 +4770,7 @@
         <v>8</v>
       </c>
       <c r="G131" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="H131">
         <v>26.66666666666666</v>
@@ -4706,7 +4781,7 @@
         <v>14</v>
       </c>
       <c r="B132" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C132">
         <v>20</v>
@@ -4721,7 +4796,7 @@
         <v>8.5</v>
       </c>
       <c r="G132" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="H132">
         <v>26.66666666666666</v>
@@ -4732,7 +4807,7 @@
         <v>14</v>
       </c>
       <c r="B133" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C133">
         <v>20</v>
@@ -4747,7 +4822,7 @@
         <v>8.5</v>
       </c>
       <c r="G133" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="H133">
         <v>26.66666666666666</v>
@@ -4758,7 +4833,7 @@
         <v>15</v>
       </c>
       <c r="B134" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C134">
         <v>20</v>
@@ -4773,7 +4848,7 @@
         <v>3</v>
       </c>
       <c r="G134" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="H134">
         <v>25.33333333333333</v>
@@ -4784,7 +4859,7 @@
         <v>15</v>
       </c>
       <c r="B135" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C135">
         <v>60</v>
@@ -4799,7 +4874,7 @@
         <v>6</v>
       </c>
       <c r="G135" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="H135">
         <v>72</v>
@@ -4810,7 +4885,7 @@
         <v>15</v>
       </c>
       <c r="B136" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C136">
         <v>80</v>
@@ -4825,7 +4900,7 @@
         <v>7</v>
       </c>
       <c r="G136" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="H136">
         <v>88</v>
@@ -4836,7 +4911,7 @@
         <v>15</v>
       </c>
       <c r="B137" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C137">
         <v>100</v>
@@ -4851,7 +4926,7 @@
         <v>7</v>
       </c>
       <c r="G137" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="H137">
         <v>103.3333333333333</v>
@@ -4862,7 +4937,7 @@
         <v>15</v>
       </c>
       <c r="B138" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C138">
         <v>70</v>
@@ -4877,7 +4952,7 @@
         <v>8</v>
       </c>
       <c r="G138" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="H138">
         <v>98</v>
@@ -4888,7 +4963,7 @@
         <v>15</v>
       </c>
       <c r="B139" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C139">
         <v>80</v>
@@ -4903,7 +4978,7 @@
         <v>8.5</v>
       </c>
       <c r="G139" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="H139">
         <v>101.3333333333333</v>
@@ -4914,7 +4989,7 @@
         <v>15</v>
       </c>
       <c r="B140" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C140">
         <v>20</v>
@@ -4929,7 +5004,7 @@
         <v>5</v>
       </c>
       <c r="G140" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="H140">
         <v>28</v>
@@ -4940,7 +5015,7 @@
         <v>15</v>
       </c>
       <c r="B141" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C141">
         <v>30</v>
@@ -4955,7 +5030,7 @@
         <v>7</v>
       </c>
       <c r="G141" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="H141">
         <v>38</v>
@@ -4966,7 +5041,7 @@
         <v>15</v>
       </c>
       <c r="B142" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C142">
         <v>40</v>
@@ -4981,7 +5056,7 @@
         <v>8</v>
       </c>
       <c r="G142" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="H142">
         <v>48</v>
@@ -4992,7 +5067,7 @@
         <v>15</v>
       </c>
       <c r="B143" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C143">
         <v>40</v>
@@ -5007,7 +5082,7 @@
         <v>9</v>
       </c>
       <c r="G143" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="H143">
         <v>48</v>
@@ -5018,7 +5093,7 @@
         <v>15</v>
       </c>
       <c r="B144" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C144">
         <v>30</v>
@@ -5033,7 +5108,7 @@
         <v>9</v>
       </c>
       <c r="G144" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="H144">
         <v>42</v>
@@ -5044,7 +5119,7 @@
         <v>15</v>
       </c>
       <c r="B145" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C145">
         <v>30</v>
@@ -5059,7 +5134,7 @@
         <v>7</v>
       </c>
       <c r="G145" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="H145">
         <v>45</v>
@@ -5070,7 +5145,7 @@
         <v>15</v>
       </c>
       <c r="B146" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C146">
         <v>50</v>
@@ -5085,7 +5160,7 @@
         <v>7.5</v>
       </c>
       <c r="G146" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="H146">
         <v>63.33333333333333</v>
@@ -5096,7 +5171,7 @@
         <v>15</v>
       </c>
       <c r="B147" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C147">
         <v>50</v>
@@ -5111,7 +5186,7 @@
         <v>8</v>
       </c>
       <c r="G147" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="H147">
         <v>63.33333333333333</v>
@@ -5122,7 +5197,7 @@
         <v>15</v>
       </c>
       <c r="B148" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C148">
         <v>50</v>
@@ -5137,7 +5212,7 @@
         <v>8.5</v>
       </c>
       <c r="G148" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="H148">
         <v>63.33333333333333</v>
@@ -5148,7 +5223,7 @@
         <v>15</v>
       </c>
       <c r="B149" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C149">
         <v>50</v>
@@ -5163,7 +5238,7 @@
         <v>9.5</v>
       </c>
       <c r="G149" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="H149">
         <v>63.33333333333333</v>
@@ -5174,7 +5249,7 @@
         <v>15</v>
       </c>
       <c r="B150" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C150">
         <v>40</v>
@@ -5189,7 +5264,7 @@
         <v>8</v>
       </c>
       <c r="G150" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="H150">
         <v>56</v>
@@ -5200,7 +5275,7 @@
         <v>15</v>
       </c>
       <c r="B151" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C151">
         <v>70</v>
@@ -5215,7 +5290,7 @@
         <v>6</v>
       </c>
       <c r="G151" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="H151">
         <v>84</v>
@@ -5226,7 +5301,7 @@
         <v>15</v>
       </c>
       <c r="B152" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C152">
         <v>120</v>
@@ -5241,7 +5316,7 @@
         <v>6</v>
       </c>
       <c r="G152" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="H152">
         <v>124</v>
@@ -5252,7 +5327,7 @@
         <v>15</v>
       </c>
       <c r="B153" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C153">
         <v>120</v>
@@ -5267,7 +5342,7 @@
         <v>8</v>
       </c>
       <c r="G153" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="H153">
         <v>140</v>
@@ -5278,7 +5353,7 @@
         <v>15</v>
       </c>
       <c r="B154" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C154">
         <v>130</v>
@@ -5293,7 +5368,7 @@
         <v>8.5</v>
       </c>
       <c r="G154" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="H154">
         <v>151.6666666666667</v>
@@ -5304,7 +5379,7 @@
         <v>15</v>
       </c>
       <c r="B155" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C155">
         <v>130</v>
@@ -5319,7 +5394,7 @@
         <v>9</v>
       </c>
       <c r="G155" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="H155">
         <v>151.6666666666667</v>
@@ -5330,7 +5405,7 @@
         <v>16</v>
       </c>
       <c r="B156" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C156">
         <v>20</v>
@@ -5345,7 +5420,7 @@
         <v>4</v>
       </c>
       <c r="G156" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="H156">
         <v>28</v>
@@ -5356,7 +5431,7 @@
         <v>16</v>
       </c>
       <c r="B157" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C157">
         <v>40</v>
@@ -5379,7 +5454,7 @@
         <v>16</v>
       </c>
       <c r="B158" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C158">
         <v>60</v>
@@ -5394,7 +5469,7 @@
         <v>6.5</v>
       </c>
       <c r="G158" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="H158">
         <v>62.00000000000001</v>
@@ -5405,7 +5480,7 @@
         <v>16</v>
       </c>
       <c r="B159" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C159">
         <v>70</v>
@@ -5420,7 +5495,7 @@
         <v>8.5</v>
       </c>
       <c r="G159" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="H159">
         <v>72.33333333333334</v>
@@ -5431,7 +5506,7 @@
         <v>16</v>
       </c>
       <c r="B160" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C160">
         <v>65</v>
@@ -5446,7 +5521,7 @@
         <v>8</v>
       </c>
       <c r="G160" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="H160">
         <v>67.16666666666667</v>
@@ -5457,7 +5532,7 @@
         <v>16</v>
       </c>
       <c r="B161" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C161">
         <v>60</v>
@@ -5480,7 +5555,7 @@
         <v>16</v>
       </c>
       <c r="B162" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C162">
         <v>60</v>
@@ -5495,7 +5570,7 @@
         <v>9</v>
       </c>
       <c r="G162" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="H162">
         <v>66</v>
@@ -5506,7 +5581,7 @@
         <v>16</v>
       </c>
       <c r="B163" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C163">
         <v>45</v>
@@ -5521,7 +5596,7 @@
         <v>8</v>
       </c>
       <c r="G163" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="H163">
         <v>62.99999999999999</v>
@@ -5532,7 +5607,7 @@
         <v>16</v>
       </c>
       <c r="B164" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C164">
         <v>45</v>
@@ -5555,7 +5630,7 @@
         <v>16</v>
       </c>
       <c r="B165" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C165">
         <v>20</v>
@@ -5570,7 +5645,7 @@
         <v>7</v>
       </c>
       <c r="G165" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="H165">
         <v>26.66666666666666</v>
@@ -5581,7 +5656,7 @@
         <v>16</v>
       </c>
       <c r="B166" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C166">
         <v>20</v>
@@ -5596,7 +5671,7 @@
         <v>6</v>
       </c>
       <c r="G166" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="H166">
         <v>28</v>
@@ -5607,7 +5682,7 @@
         <v>16</v>
       </c>
       <c r="B167" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C167">
         <v>20</v>
@@ -5622,7 +5697,7 @@
         <v>7</v>
       </c>
       <c r="G167" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="H167">
         <v>28</v>
@@ -5633,7 +5708,7 @@
         <v>16</v>
       </c>
       <c r="B168" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C168">
         <v>20</v>
@@ -5648,7 +5723,7 @@
         <v>7</v>
       </c>
       <c r="G168" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="H168">
         <v>30</v>
@@ -5659,7 +5734,7 @@
         <v>16</v>
       </c>
       <c r="B169" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C169">
         <v>22.5</v>
@@ -5674,7 +5749,7 @@
         <v>7.5</v>
       </c>
       <c r="G169" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="H169">
         <v>30</v>
@@ -5685,7 +5760,7 @@
         <v>16</v>
       </c>
       <c r="B170" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C170">
         <v>22.5</v>
@@ -5700,7 +5775,7 @@
         <v>7</v>
       </c>
       <c r="G170" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="H170">
         <v>31.5</v>
@@ -5711,7 +5786,7 @@
         <v>16</v>
       </c>
       <c r="B171" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C171">
         <v>25</v>
@@ -5726,7 +5801,7 @@
         <v>8</v>
       </c>
       <c r="G171" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="H171">
         <v>31.66666666666666</v>
@@ -5737,7 +5812,7 @@
         <v>16</v>
       </c>
       <c r="B172" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C172">
         <v>25</v>
@@ -5752,7 +5827,7 @@
         <v>7.5</v>
       </c>
       <c r="G172" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="H172">
         <v>35</v>
@@ -5763,7 +5838,7 @@
         <v>16</v>
       </c>
       <c r="B173" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C173">
         <v>25</v>
@@ -5778,7 +5853,7 @@
         <v>8</v>
       </c>
       <c r="G173" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="H173">
         <v>31.66666666666666</v>
@@ -5789,7 +5864,7 @@
         <v>16</v>
       </c>
       <c r="B174" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C174">
         <v>25</v>
@@ -5804,7 +5879,7 @@
         <v>8</v>
       </c>
       <c r="G174" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="H174">
         <v>37.5</v>
@@ -5815,7 +5890,7 @@
         <v>16</v>
       </c>
       <c r="B175" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C175">
         <v>40</v>
@@ -5830,7 +5905,7 @@
         <v>7.5</v>
       </c>
       <c r="G175" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="H175">
         <v>50.66666666666666</v>
@@ -5841,7 +5916,7 @@
         <v>16</v>
       </c>
       <c r="B176" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C176">
         <v>40</v>
@@ -5856,7 +5931,7 @@
         <v>8.5</v>
       </c>
       <c r="G176" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="H176">
         <v>50.66666666666666</v>
@@ -5867,7 +5942,7 @@
         <v>16</v>
       </c>
       <c r="B177" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C177">
         <v>40</v>
@@ -5882,7 +5957,7 @@
         <v>9</v>
       </c>
       <c r="G177" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="H177">
         <v>48</v>
@@ -5893,7 +5968,7 @@
         <v>16</v>
       </c>
       <c r="B178" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C178">
         <v>22</v>
@@ -5908,7 +5983,7 @@
         <v>7</v>
       </c>
       <c r="G178" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="H178">
         <v>27.86666666666667</v>
@@ -5919,7 +5994,7 @@
         <v>16</v>
       </c>
       <c r="B179" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C179">
         <v>22</v>
@@ -5942,7 +6017,7 @@
         <v>16</v>
       </c>
       <c r="B180" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C180">
         <v>22</v>
@@ -5957,7 +6032,7 @@
         <v>8.5</v>
       </c>
       <c r="G180" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="H180">
         <v>27.86666666666667</v>
@@ -5968,7 +6043,7 @@
         <v>17</v>
       </c>
       <c r="B181" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C181">
         <v>20</v>
@@ -5991,7 +6066,7 @@
         <v>17</v>
       </c>
       <c r="B182" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C182">
         <v>22</v>
@@ -6014,7 +6089,7 @@
         <v>17</v>
       </c>
       <c r="B183" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C183">
         <v>20</v>
@@ -6029,7 +6104,7 @@
         <v>4</v>
       </c>
       <c r="G183" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="H183">
         <v>25.33333333333333</v>
@@ -6040,7 +6115,7 @@
         <v>17</v>
       </c>
       <c r="B184" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C184">
         <v>60</v>
@@ -6063,7 +6138,7 @@
         <v>17</v>
       </c>
       <c r="B185" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C185">
         <v>80</v>
@@ -6086,7 +6161,7 @@
         <v>17</v>
       </c>
       <c r="B186" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C186">
         <v>100</v>
@@ -6109,7 +6184,7 @@
         <v>17</v>
       </c>
       <c r="B187" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C187">
         <v>110</v>
@@ -6132,7 +6207,7 @@
         <v>17</v>
       </c>
       <c r="B188" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C188">
         <v>120</v>
@@ -6147,7 +6222,7 @@
         <v>8.5</v>
       </c>
       <c r="G188" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="H188">
         <v>124</v>
@@ -6158,7 +6233,7 @@
         <v>17</v>
       </c>
       <c r="B189" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C189">
         <v>80</v>
@@ -6173,7 +6248,7 @@
         <v>7.5</v>
       </c>
       <c r="G189" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="H189">
         <v>112</v>
@@ -6184,7 +6259,7 @@
         <v>17</v>
       </c>
       <c r="B190" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C190">
         <v>-30</v>
@@ -6199,7 +6274,7 @@
         <v>6</v>
       </c>
       <c r="G190" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="H190">
         <v>-38</v>
@@ -6210,7 +6285,7 @@
         <v>17</v>
       </c>
       <c r="B191" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C191">
         <v>-30</v>
@@ -6225,7 +6300,7 @@
         <v>6</v>
       </c>
       <c r="G191" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="H191">
         <v>-38</v>
@@ -6236,7 +6311,7 @@
         <v>17</v>
       </c>
       <c r="B192" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C192">
         <v>-25</v>
@@ -6251,7 +6326,7 @@
         <v>7.5</v>
       </c>
       <c r="G192" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="H192">
         <v>-33.33333333333333</v>
@@ -6262,7 +6337,7 @@
         <v>17</v>
       </c>
       <c r="B193" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C193">
         <v>-25</v>
@@ -6277,7 +6352,7 @@
         <v>7.5</v>
       </c>
       <c r="G193" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="H193">
         <v>-33.33333333333333</v>
@@ -6288,7 +6363,7 @@
         <v>17</v>
       </c>
       <c r="B194" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C194">
         <v>-20</v>
@@ -6303,7 +6378,7 @@
         <v>8</v>
       </c>
       <c r="G194" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="H194">
         <v>-25.33333333333333</v>
@@ -6314,7 +6389,7 @@
         <v>17</v>
       </c>
       <c r="B195" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C195">
         <v>-20</v>
@@ -6329,7 +6404,7 @@
         <v>8</v>
       </c>
       <c r="G195" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="H195">
         <v>-25.33333333333333</v>
@@ -6340,7 +6415,7 @@
         <v>17</v>
       </c>
       <c r="B196" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C196">
         <v>35</v>
@@ -6355,7 +6430,7 @@
         <v>7</v>
       </c>
       <c r="G196" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="H196">
         <v>52.5</v>
@@ -6366,7 +6441,7 @@
         <v>17</v>
       </c>
       <c r="B197" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C197">
         <v>25</v>
@@ -6381,7 +6456,7 @@
         <v>7</v>
       </c>
       <c r="G197" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="H197">
         <v>37.5</v>
@@ -6392,7 +6467,7 @@
         <v>17</v>
       </c>
       <c r="B198" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C198">
         <v>35</v>
@@ -6407,7 +6482,7 @@
         <v>7</v>
       </c>
       <c r="G198" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="H198">
         <v>52.5</v>
@@ -6418,7 +6493,7 @@
         <v>17</v>
       </c>
       <c r="B199" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C199">
         <v>25</v>
@@ -6433,7 +6508,7 @@
         <v>7</v>
       </c>
       <c r="G199" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="H199">
         <v>37.5</v>
@@ -6444,7 +6519,7 @@
         <v>18</v>
       </c>
       <c r="B200" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C200">
         <v>70</v>
@@ -6459,7 +6534,7 @@
         <v>6</v>
       </c>
       <c r="G200" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="H200">
         <v>84</v>
@@ -6470,7 +6545,7 @@
         <v>18</v>
       </c>
       <c r="B201" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C201">
         <v>90</v>
@@ -6493,7 +6568,7 @@
         <v>18</v>
       </c>
       <c r="B202" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C202">
         <v>120</v>
@@ -6516,7 +6591,7 @@
         <v>18</v>
       </c>
       <c r="B203" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C203">
         <v>120</v>
@@ -6539,7 +6614,7 @@
         <v>18</v>
       </c>
       <c r="B204" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C204">
         <v>120</v>
@@ -6562,7 +6637,7 @@
         <v>18</v>
       </c>
       <c r="B205" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C205">
         <v>120</v>
@@ -6585,7 +6660,7 @@
         <v>18</v>
       </c>
       <c r="B206" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C206">
         <v>120</v>
@@ -6608,7 +6683,7 @@
         <v>18</v>
       </c>
       <c r="B207" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C207">
         <v>20</v>
@@ -6623,7 +6698,7 @@
         <v>6</v>
       </c>
       <c r="G207" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="H207">
         <v>28</v>
@@ -6634,7 +6709,7 @@
         <v>18</v>
       </c>
       <c r="B208" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C208">
         <v>30</v>
@@ -6657,7 +6732,7 @@
         <v>18</v>
       </c>
       <c r="B209" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C209">
         <v>35</v>
@@ -6680,7 +6755,7 @@
         <v>18</v>
       </c>
       <c r="B210" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C210">
         <v>35</v>
@@ -6703,7 +6778,7 @@
         <v>18</v>
       </c>
       <c r="B211" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C211">
         <v>35</v>
@@ -6726,7 +6801,7 @@
         <v>18</v>
       </c>
       <c r="B212" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C212">
         <v>22</v>
@@ -6741,7 +6816,7 @@
         <v>7.5</v>
       </c>
       <c r="G212" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="H212">
         <v>27.86666666666667</v>
@@ -6752,7 +6827,7 @@
         <v>18</v>
       </c>
       <c r="B213" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C213">
         <v>22</v>
@@ -6767,7 +6842,7 @@
         <v>7.5</v>
       </c>
       <c r="G213" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="H213">
         <v>30.8</v>
@@ -6778,7 +6853,7 @@
         <v>18</v>
       </c>
       <c r="B214" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C214">
         <v>22</v>
@@ -6793,7 +6868,7 @@
         <v>8</v>
       </c>
       <c r="G214" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="H214">
         <v>27.86666666666667</v>
@@ -6804,7 +6879,7 @@
         <v>18</v>
       </c>
       <c r="B215" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C215">
         <v>22</v>
@@ -6819,7 +6894,7 @@
         <v>8</v>
       </c>
       <c r="G215" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="H215">
         <v>30.8</v>
@@ -6830,7 +6905,7 @@
         <v>18</v>
       </c>
       <c r="B216" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C216">
         <v>22</v>
@@ -6845,7 +6920,7 @@
         <v>8.5</v>
       </c>
       <c r="G216" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="H216">
         <v>27.86666666666667</v>
@@ -6856,7 +6931,7 @@
         <v>18</v>
       </c>
       <c r="B217" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C217">
         <v>22</v>
@@ -6871,7 +6946,7 @@
         <v>8</v>
       </c>
       <c r="G217" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="H217">
         <v>30.8</v>
@@ -6882,7 +6957,7 @@
         <v>18</v>
       </c>
       <c r="B218" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C218">
         <v>25</v>
@@ -6897,7 +6972,7 @@
         <v>8</v>
       </c>
       <c r="G218" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="H218">
         <v>31.66666666666666</v>
@@ -6908,7 +6983,7 @@
         <v>18</v>
       </c>
       <c r="B219" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C219">
         <v>25</v>
@@ -6923,7 +6998,7 @@
         <v>6.5</v>
       </c>
       <c r="G219" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="H219">
         <v>31.66666666666666</v>
@@ -6934,7 +7009,7 @@
         <v>18</v>
       </c>
       <c r="B220" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C220">
         <v>25</v>
@@ -6949,7 +7024,7 @@
         <v>8</v>
       </c>
       <c r="G220" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="H220">
         <v>31.66666666666666</v>
@@ -6960,7 +7035,7 @@
         <v>18</v>
       </c>
       <c r="B221" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C221">
         <v>25</v>
@@ -6975,7 +7050,7 @@
         <v>7.5</v>
       </c>
       <c r="G221" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="H221">
         <v>31.66666666666666</v>
@@ -6986,7 +7061,7 @@
         <v>18</v>
       </c>
       <c r="B222" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C222">
         <v>25</v>
@@ -7001,7 +7076,7 @@
         <v>9</v>
       </c>
       <c r="G222" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="H222">
         <v>31.66666666666666</v>
@@ -7012,7 +7087,7 @@
         <v>18</v>
       </c>
       <c r="B223" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C223">
         <v>25</v>
@@ -7027,7 +7102,7 @@
         <v>9</v>
       </c>
       <c r="G223" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="H223">
         <v>31.66666666666666</v>
@@ -7038,7 +7113,7 @@
         <v>19</v>
       </c>
       <c r="B224" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C224">
         <v>70</v>
@@ -7053,7 +7128,7 @@
         <v>6.5</v>
       </c>
       <c r="G224" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="H224">
         <v>84</v>
@@ -7064,7 +7139,7 @@
         <v>19</v>
       </c>
       <c r="B225" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C225">
         <v>85</v>
@@ -7079,7 +7154,7 @@
         <v>8</v>
       </c>
       <c r="G225" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="H225">
         <v>119</v>
@@ -7090,7 +7165,7 @@
         <v>19</v>
       </c>
       <c r="B226" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C226">
         <v>85</v>
@@ -7105,7 +7180,7 @@
         <v>9</v>
       </c>
       <c r="G226" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="H226">
         <v>119</v>
@@ -7116,7 +7191,7 @@
         <v>19</v>
       </c>
       <c r="B227" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C227">
         <v>85</v>
@@ -7131,7 +7206,7 @@
         <v>10</v>
       </c>
       <c r="G227" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="H227">
         <v>113.3333333333333</v>
@@ -7142,7 +7217,7 @@
         <v>19</v>
       </c>
       <c r="B228" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C228">
         <v>30</v>
@@ -7157,7 +7232,7 @@
         <v>6</v>
       </c>
       <c r="G228" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="H228">
         <v>36</v>
@@ -7168,7 +7243,7 @@
         <v>19</v>
       </c>
       <c r="B229" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C229">
         <v>30</v>
@@ -7183,7 +7258,7 @@
         <v>6</v>
       </c>
       <c r="G229" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="H229">
         <v>38</v>
@@ -7194,7 +7269,7 @@
         <v>19</v>
       </c>
       <c r="B230" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C230">
         <v>40</v>
@@ -7209,7 +7284,7 @@
         <v>8</v>
       </c>
       <c r="G230" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="H230">
         <v>50.66666666666666</v>
@@ -7220,7 +7295,7 @@
         <v>19</v>
       </c>
       <c r="B231" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C231">
         <v>40</v>
@@ -7235,7 +7310,7 @@
         <v>9</v>
       </c>
       <c r="G231" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="H231">
         <v>50.66666666666666</v>
@@ -7246,7 +7321,7 @@
         <v>19</v>
       </c>
       <c r="B232" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C232">
         <v>40</v>
@@ -7261,7 +7336,7 @@
         <v>10</v>
       </c>
       <c r="G232" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="H232">
         <v>49.33333333333334</v>
@@ -7272,7 +7347,7 @@
         <v>19</v>
       </c>
       <c r="B233" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C233">
         <v>40</v>
@@ -7287,7 +7362,7 @@
         <v>6.5</v>
       </c>
       <c r="G233" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="H233">
         <v>56</v>
@@ -7298,7 +7373,7 @@
         <v>19</v>
       </c>
       <c r="B234" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C234">
         <v>40</v>
@@ -7313,7 +7388,7 @@
         <v>6.5</v>
       </c>
       <c r="G234" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="H234">
         <v>56</v>
@@ -7324,7 +7399,7 @@
         <v>19</v>
       </c>
       <c r="B235" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C235">
         <v>40</v>
@@ -7339,7 +7414,7 @@
         <v>7.5</v>
       </c>
       <c r="G235" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="H235">
         <v>56</v>
@@ -7350,7 +7425,7 @@
         <v>19</v>
       </c>
       <c r="B236" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C236">
         <v>40</v>
@@ -7365,7 +7440,7 @@
         <v>9</v>
       </c>
       <c r="G236" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="H236">
         <v>56</v>
@@ -7376,7 +7451,7 @@
         <v>19</v>
       </c>
       <c r="B237" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C237">
         <v>60</v>
@@ -7391,7 +7466,7 @@
         <v>8</v>
       </c>
       <c r="G237" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="H237">
         <v>80</v>
@@ -7402,7 +7477,7 @@
         <v>19</v>
       </c>
       <c r="B238" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C238">
         <v>60</v>
@@ -7417,7 +7492,7 @@
         <v>7</v>
       </c>
       <c r="G238" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="H238">
         <v>80</v>
@@ -7428,7 +7503,7 @@
         <v>19</v>
       </c>
       <c r="B239" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C239">
         <v>60</v>
@@ -7443,7 +7518,7 @@
         <v>8.5</v>
       </c>
       <c r="G239" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="H239">
         <v>80</v>
@@ -7454,7 +7529,7 @@
         <v>19</v>
       </c>
       <c r="B240" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C240">
         <v>60</v>
@@ -7469,7 +7544,7 @@
         <v>8</v>
       </c>
       <c r="G240" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="H240">
         <v>80</v>
@@ -7480,7 +7555,7 @@
         <v>19</v>
       </c>
       <c r="B241" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C241">
         <v>60</v>
@@ -7495,7 +7570,7 @@
         <v>9</v>
       </c>
       <c r="G241" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="H241">
         <v>80</v>
@@ -7506,7 +7581,7 @@
         <v>19</v>
       </c>
       <c r="B242" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C242">
         <v>60</v>
@@ -7521,7 +7596,7 @@
         <v>9</v>
       </c>
       <c r="G242" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="H242">
         <v>80</v>
@@ -7532,7 +7607,7 @@
         <v>20</v>
       </c>
       <c r="B243" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C243">
         <v>60</v>
@@ -7547,7 +7622,7 @@
         <v>4</v>
       </c>
       <c r="G243" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="H243">
         <v>76</v>
@@ -7558,7 +7633,7 @@
         <v>20</v>
       </c>
       <c r="B244" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C244">
         <v>100</v>
@@ -7573,7 +7648,7 @@
         <v>6</v>
       </c>
       <c r="G244" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="H244">
         <v>116.6666666666667</v>
@@ -7584,7 +7659,7 @@
         <v>20</v>
       </c>
       <c r="B245" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C245">
         <v>130</v>
@@ -7599,7 +7674,7 @@
         <v>7</v>
       </c>
       <c r="G245" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="H245">
         <v>134.3333333333333</v>
@@ -7610,7 +7685,7 @@
         <v>20</v>
       </c>
       <c r="B246" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C246">
         <v>150</v>
@@ -7625,7 +7700,7 @@
         <v>8.5</v>
       </c>
       <c r="G246" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="H246">
         <v>155</v>
@@ -7636,7 +7711,7 @@
         <v>20</v>
       </c>
       <c r="B247" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C247">
         <v>120</v>
@@ -7651,7 +7726,7 @@
         <v>7.5</v>
       </c>
       <c r="G247" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="H247">
         <v>140</v>
@@ -7662,7 +7737,7 @@
         <v>20</v>
       </c>
       <c r="B248" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C248">
         <v>120</v>
@@ -7677,7 +7752,7 @@
         <v>7.5</v>
       </c>
       <c r="G248" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="H248">
         <v>140</v>
@@ -7688,7 +7763,7 @@
         <v>20</v>
       </c>
       <c r="B249" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C249">
         <v>120</v>
@@ -7703,7 +7778,7 @@
         <v>8</v>
       </c>
       <c r="G249" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="H249">
         <v>140</v>
@@ -7714,7 +7789,7 @@
         <v>20</v>
       </c>
       <c r="B250" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C250">
         <v>120</v>
@@ -7729,7 +7804,7 @@
         <v>8.5</v>
       </c>
       <c r="G250" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="H250">
         <v>140</v>
@@ -7740,7 +7815,7 @@
         <v>20</v>
       </c>
       <c r="B251" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C251">
         <v>120</v>
@@ -7755,7 +7830,7 @@
         <v>9</v>
       </c>
       <c r="G251" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="H251">
         <v>140</v>
@@ -7766,7 +7841,7 @@
         <v>20</v>
       </c>
       <c r="B252" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C252">
         <v>40</v>
@@ -7781,7 +7856,7 @@
         <v>5</v>
       </c>
       <c r="G252" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="H252">
         <v>50.66666666666666</v>
@@ -7792,7 +7867,7 @@
         <v>20</v>
       </c>
       <c r="B253" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C253">
         <v>50</v>
@@ -7807,7 +7882,7 @@
         <v>6</v>
       </c>
       <c r="G253" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="H253">
         <v>58.33333333333334</v>
@@ -7818,7 +7893,7 @@
         <v>20</v>
       </c>
       <c r="B254" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C254">
         <v>60</v>
@@ -7833,7 +7908,7 @@
         <v>7</v>
       </c>
       <c r="G254" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="H254">
         <v>70</v>
@@ -7844,7 +7919,7 @@
         <v>20</v>
       </c>
       <c r="B255" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C255">
         <v>60</v>
@@ -7859,7 +7934,7 @@
         <v>8</v>
       </c>
       <c r="G255" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="H255">
         <v>70</v>
@@ -7870,7 +7945,7 @@
         <v>20</v>
       </c>
       <c r="B256" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C256">
         <v>60</v>
@@ -7885,7 +7960,7 @@
         <v>8.5</v>
       </c>
       <c r="G256" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="H256">
         <v>70</v>
@@ -7896,7 +7971,7 @@
         <v>20</v>
       </c>
       <c r="B257" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C257">
         <v>60</v>
@@ -7911,7 +7986,7 @@
         <v>8.5</v>
       </c>
       <c r="G257" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="H257">
         <v>70</v>
@@ -7922,7 +7997,7 @@
         <v>20</v>
       </c>
       <c r="B258" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C258">
         <v>60</v>
@@ -7937,7 +8012,7 @@
         <v>8</v>
       </c>
       <c r="G258" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="H258">
         <v>70</v>
@@ -7948,7 +8023,7 @@
         <v>20</v>
       </c>
       <c r="B259" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C259">
         <v>40</v>
@@ -7963,7 +8038,7 @@
         <v>5</v>
       </c>
       <c r="G259" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="H259">
         <v>53.33333333333333</v>
@@ -7974,7 +8049,7 @@
         <v>20</v>
       </c>
       <c r="B260" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C260">
         <v>50</v>
@@ -7989,7 +8064,7 @@
         <v>7</v>
       </c>
       <c r="G260" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="H260">
         <v>63.33333333333333</v>
@@ -8000,7 +8075,7 @@
         <v>20</v>
       </c>
       <c r="B261" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C261">
         <v>50</v>
@@ -8015,7 +8090,7 @@
         <v>7</v>
       </c>
       <c r="G261" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="H261">
         <v>63.33333333333333</v>
@@ -8026,7 +8101,7 @@
         <v>20</v>
       </c>
       <c r="B262" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C262">
         <v>50</v>
@@ -8041,7 +8116,7 @@
         <v>7.5</v>
       </c>
       <c r="G262" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="H262">
         <v>63.33333333333333</v>
@@ -8052,7 +8127,7 @@
         <v>20</v>
       </c>
       <c r="B263" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C263">
         <v>50</v>
@@ -8067,7 +8142,7 @@
         <v>8</v>
       </c>
       <c r="G263" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="H263">
         <v>66.66666666666666</v>
@@ -8078,7 +8153,7 @@
         <v>20</v>
       </c>
       <c r="B264" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C264">
         <v>20</v>
@@ -8093,7 +8168,7 @@
         <v>7</v>
       </c>
       <c r="G264" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="H264">
         <v>26.66666666666666</v>
@@ -8104,7 +8179,7 @@
         <v>20</v>
       </c>
       <c r="B265" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C265">
         <v>20</v>
@@ -8119,7 +8194,7 @@
         <v>7</v>
       </c>
       <c r="G265" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="H265">
         <v>28</v>
@@ -8130,7 +8205,7 @@
         <v>20</v>
       </c>
       <c r="B266" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C266">
         <v>25</v>
@@ -8145,7 +8220,7 @@
         <v>8.5</v>
       </c>
       <c r="G266" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H266">
         <v>31.66666666666666</v>
@@ -8156,7 +8231,7 @@
         <v>20</v>
       </c>
       <c r="B267" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C267">
         <v>25</v>
@@ -8171,7 +8246,7 @@
         <v>7.5</v>
       </c>
       <c r="G267" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="H267">
         <v>33.33333333333333</v>
@@ -8182,7 +8257,7 @@
         <v>20</v>
       </c>
       <c r="B268" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C268">
         <v>25</v>
@@ -8197,7 +8272,7 @@
         <v>8.5</v>
       </c>
       <c r="G268" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="H268">
         <v>31.66666666666666</v>
@@ -8208,7 +8283,7 @@
         <v>20</v>
       </c>
       <c r="B269" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C269">
         <v>25</v>
@@ -8223,7 +8298,7 @@
         <v>8</v>
       </c>
       <c r="G269" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="H269">
         <v>35</v>
@@ -8234,7 +8309,7 @@
         <v>20</v>
       </c>
       <c r="B270" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C270">
         <v>25</v>
@@ -8249,7 +8324,7 @@
         <v>9</v>
       </c>
       <c r="G270" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="H270">
         <v>31.66666666666666</v>
@@ -8260,7 +8335,7 @@
         <v>20</v>
       </c>
       <c r="B271" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C271">
         <v>25</v>
@@ -8275,7 +8350,7 @@
         <v>9</v>
       </c>
       <c r="G271" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="H271">
         <v>37.5</v>
@@ -8286,7 +8361,7 @@
         <v>21</v>
       </c>
       <c r="B272" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C272">
         <v>20</v>
@@ -8309,7 +8384,7 @@
         <v>21</v>
       </c>
       <c r="B273" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C273">
         <v>60</v>
@@ -8332,7 +8407,7 @@
         <v>21</v>
       </c>
       <c r="B274" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C274">
         <v>100</v>
@@ -8355,7 +8430,7 @@
         <v>21</v>
       </c>
       <c r="B275" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C275">
         <v>100</v>
@@ -8378,7 +8453,7 @@
         <v>21</v>
       </c>
       <c r="B276" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C276">
         <v>60</v>
@@ -8401,7 +8476,7 @@
         <v>21</v>
       </c>
       <c r="B277" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C277">
         <v>90</v>
@@ -8424,7 +8499,7 @@
         <v>21</v>
       </c>
       <c r="B278" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C278">
         <v>110</v>
@@ -8447,7 +8522,7 @@
         <v>21</v>
       </c>
       <c r="B279" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C279">
         <v>30</v>
@@ -8470,7 +8545,7 @@
         <v>21</v>
       </c>
       <c r="B280" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C280">
         <v>40</v>
@@ -8493,7 +8568,7 @@
         <v>21</v>
       </c>
       <c r="B281" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C281">
         <v>40</v>
@@ -8516,7 +8591,7 @@
         <v>21</v>
       </c>
       <c r="B282" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C282">
         <v>30</v>
@@ -8539,7 +8614,7 @@
         <v>21</v>
       </c>
       <c r="B283" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C283">
         <v>30</v>
@@ -8562,7 +8637,7 @@
         <v>21</v>
       </c>
       <c r="B284" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C284">
         <v>40</v>
@@ -8585,7 +8660,7 @@
         <v>21</v>
       </c>
       <c r="B285" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C285">
         <v>40</v>
@@ -8608,7 +8683,7 @@
         <v>21</v>
       </c>
       <c r="B286" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C286">
         <v>40</v>
@@ -8631,7 +8706,7 @@
         <v>21</v>
       </c>
       <c r="B287" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C287">
         <v>40</v>
@@ -8654,7 +8729,7 @@
         <v>21</v>
       </c>
       <c r="B288" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C288">
         <v>60</v>
@@ -8677,7 +8752,7 @@
         <v>21</v>
       </c>
       <c r="B289" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C289">
         <v>60</v>
@@ -8700,7 +8775,7 @@
         <v>21</v>
       </c>
       <c r="B290" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C290">
         <v>60</v>
@@ -8723,7 +8798,7 @@
         <v>21</v>
       </c>
       <c r="B291" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C291">
         <v>60</v>
@@ -8746,7 +8821,7 @@
         <v>21</v>
       </c>
       <c r="B292" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C292">
         <v>60</v>
@@ -8769,7 +8844,7 @@
         <v>21</v>
       </c>
       <c r="B293" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C293">
         <v>60</v>
@@ -8792,7 +8867,7 @@
         <v>22</v>
       </c>
       <c r="B294" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C294">
         <v>20</v>
@@ -8807,7 +8882,7 @@
         <v>3</v>
       </c>
       <c r="G294" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="H294">
         <v>28</v>
@@ -8818,7 +8893,7 @@
         <v>22</v>
       </c>
       <c r="B295" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C295">
         <v>60</v>
@@ -8833,7 +8908,7 @@
         <v>6</v>
       </c>
       <c r="G295" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="H295">
         <v>76</v>
@@ -8844,7 +8919,7 @@
         <v>22</v>
       </c>
       <c r="B296" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C296">
         <v>110</v>
@@ -8859,7 +8934,7 @@
         <v>7.5</v>
       </c>
       <c r="G296" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="H296">
         <v>121</v>
@@ -8870,7 +8945,7 @@
         <v>22</v>
       </c>
       <c r="B297" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C297">
         <v>70</v>
@@ -8885,7 +8960,7 @@
         <v>8</v>
       </c>
       <c r="G297" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="H297">
         <v>116.6666666666667</v>
@@ -8896,7 +8971,7 @@
         <v>22</v>
       </c>
       <c r="B298" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C298">
         <v>80</v>
@@ -8911,7 +8986,7 @@
         <v>8.5</v>
       </c>
       <c r="G298" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="H298">
         <v>112</v>
@@ -8922,7 +8997,7 @@
         <v>22</v>
       </c>
       <c r="B299" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C299">
         <v>60</v>
@@ -8937,7 +9012,7 @@
         <v>5</v>
       </c>
       <c r="G299" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="H299">
         <v>80</v>
@@ -8948,7 +9023,7 @@
         <v>22</v>
       </c>
       <c r="B300" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C300">
         <v>110</v>
@@ -8963,7 +9038,7 @@
         <v>6.5</v>
       </c>
       <c r="G300" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="H300">
         <v>128.3333333333333</v>
@@ -8974,7 +9049,7 @@
         <v>22</v>
       </c>
       <c r="B301" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C301">
         <v>140</v>
@@ -8989,7 +9064,7 @@
         <v>7</v>
       </c>
       <c r="G301" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="H301">
         <v>144.6666666666667</v>
@@ -9000,7 +9075,7 @@
         <v>22</v>
       </c>
       <c r="B302" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C302">
         <v>160</v>
@@ -9015,7 +9090,7 @@
         <v>8.5</v>
       </c>
       <c r="G302" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="H302">
         <v>165.3333333333333</v>
@@ -9026,7 +9101,7 @@
         <v>22</v>
       </c>
       <c r="B303" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C303">
         <v>170</v>
@@ -9041,7 +9116,7 @@
         <v>9</v>
       </c>
       <c r="G303" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="H303">
         <v>175.6666666666667</v>
@@ -9052,7 +9127,7 @@
         <v>22</v>
       </c>
       <c r="B304" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C304">
         <v>30</v>
@@ -9067,7 +9142,7 @@
         <v>7</v>
       </c>
       <c r="G304" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="H304">
         <v>40</v>
@@ -9078,7 +9153,7 @@
         <v>22</v>
       </c>
       <c r="B305" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C305">
         <v>40</v>
@@ -9093,7 +9168,7 @@
         <v>7</v>
       </c>
       <c r="G305" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="H305">
         <v>44</v>
@@ -9104,7 +9179,7 @@
         <v>22</v>
       </c>
       <c r="B306" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C306">
         <v>50</v>
@@ -9119,7 +9194,7 @@
         <v>9.5</v>
       </c>
       <c r="G306" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="H306">
         <v>53.33333333333334</v>
@@ -9130,7 +9205,7 @@
         <v>22</v>
       </c>
       <c r="B307" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C307">
         <v>40</v>
@@ -9145,7 +9220,7 @@
         <v>8.5</v>
       </c>
       <c r="G307" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="H307">
         <v>53.33333333333333</v>
@@ -9156,7 +9231,7 @@
         <v>23</v>
       </c>
       <c r="B308" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C308">
         <v>70</v>
@@ -9179,7 +9254,7 @@
         <v>23</v>
       </c>
       <c r="B309" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C309">
         <v>120</v>
@@ -9202,7 +9277,7 @@
         <v>23</v>
       </c>
       <c r="B310" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C310">
         <v>140</v>
@@ -9225,7 +9300,7 @@
         <v>23</v>
       </c>
       <c r="B311" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C311">
         <v>140</v>
@@ -9248,7 +9323,7 @@
         <v>23</v>
       </c>
       <c r="B312" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C312">
         <v>120</v>
@@ -9271,7 +9346,7 @@
         <v>23</v>
       </c>
       <c r="B313" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C313">
         <v>20</v>
@@ -9294,7 +9369,7 @@
         <v>23</v>
       </c>
       <c r="B314" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C314">
         <v>40</v>
@@ -9317,7 +9392,7 @@
         <v>23</v>
       </c>
       <c r="B315" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C315">
         <v>60</v>
@@ -9340,7 +9415,7 @@
         <v>23</v>
       </c>
       <c r="B316" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C316">
         <v>70</v>
@@ -9363,7 +9438,7 @@
         <v>23</v>
       </c>
       <c r="B317" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C317">
         <v>80</v>
@@ -9386,7 +9461,7 @@
         <v>23</v>
       </c>
       <c r="B318" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C318">
         <v>75</v>
@@ -9409,7 +9484,7 @@
         <v>23</v>
       </c>
       <c r="B319" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C319">
         <v>60</v>
@@ -9432,7 +9507,7 @@
         <v>23</v>
       </c>
       <c r="B320" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C320">
         <v>60</v>
@@ -9455,7 +9530,7 @@
         <v>23</v>
       </c>
       <c r="B321" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C321">
         <v>60</v>
@@ -9478,7 +9553,7 @@
         <v>23</v>
       </c>
       <c r="B322" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C322">
         <v>65</v>
@@ -9501,7 +9576,7 @@
         <v>23</v>
       </c>
       <c r="B323" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C323">
         <v>65</v>
@@ -9524,7 +9599,7 @@
         <v>23</v>
       </c>
       <c r="B324" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C324">
         <v>65</v>
@@ -9547,7 +9622,7 @@
         <v>23</v>
       </c>
       <c r="B325" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C325">
         <v>65</v>
@@ -9570,7 +9645,7 @@
         <v>23</v>
       </c>
       <c r="B326" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C326">
         <v>65</v>
@@ -9593,7 +9668,7 @@
         <v>23</v>
       </c>
       <c r="B327" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C327">
         <v>65</v>
@@ -9616,7 +9691,7 @@
         <v>23</v>
       </c>
       <c r="B328" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C328">
         <v>65</v>
@@ -9639,7 +9714,7 @@
         <v>23</v>
       </c>
       <c r="B329" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C329">
         <v>65</v>
@@ -9662,7 +9737,7 @@
         <v>24</v>
       </c>
       <c r="B330" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C330">
         <v>20</v>
@@ -9677,7 +9752,7 @@
         <v>3</v>
       </c>
       <c r="G330" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="H330">
         <v>25.33333333333333</v>
@@ -9688,7 +9763,7 @@
         <v>24</v>
       </c>
       <c r="B331" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C331">
         <v>70</v>
@@ -9703,7 +9778,7 @@
         <v>6</v>
       </c>
       <c r="G331" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="H331">
         <v>81.66666666666667</v>
@@ -9714,7 +9789,7 @@
         <v>24</v>
       </c>
       <c r="B332" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C332">
         <v>90</v>
@@ -9729,7 +9804,7 @@
         <v>6</v>
       </c>
       <c r="G332" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="H332">
         <v>93.00000000000001</v>
@@ -9740,7 +9815,7 @@
         <v>24</v>
       </c>
       <c r="B333" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C333">
         <v>120</v>
@@ -9755,7 +9830,7 @@
         <v>7.5</v>
       </c>
       <c r="G333" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="H333">
         <v>124</v>
@@ -9766,7 +9841,7 @@
         <v>24</v>
       </c>
       <c r="B334" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C334">
         <v>140</v>
@@ -9781,7 +9856,7 @@
         <v>10</v>
       </c>
       <c r="G334" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="H334">
         <v>140</v>
@@ -9792,7 +9867,7 @@
         <v>24</v>
       </c>
       <c r="B335" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C335">
         <v>80</v>
@@ -9807,7 +9882,7 @@
         <v>8.5</v>
       </c>
       <c r="G335" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H335">
         <v>133.3333333333333</v>
@@ -9818,7 +9893,7 @@
         <v>24</v>
       </c>
       <c r="B336" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C336">
         <v>80</v>
@@ -9833,7 +9908,7 @@
         <v>10</v>
       </c>
       <c r="G336" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="H336">
         <v>101.3333333333333</v>
@@ -9844,7 +9919,7 @@
         <v>24</v>
       </c>
       <c r="B337" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C337">
         <v>20</v>
@@ -9859,7 +9934,7 @@
         <v>4</v>
       </c>
       <c r="G337" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="H337">
         <v>25.33333333333333</v>
@@ -9870,7 +9945,7 @@
         <v>24</v>
       </c>
       <c r="B338" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C338">
         <v>40</v>
@@ -9885,7 +9960,7 @@
         <v>6</v>
       </c>
       <c r="G338" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="H338">
         <v>50.66666666666666</v>
@@ -9896,7 +9971,7 @@
         <v>24</v>
       </c>
       <c r="B339" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C339">
         <v>60</v>
@@ -9911,7 +9986,7 @@
         <v>7</v>
       </c>
       <c r="G339" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="H339">
         <v>66</v>
@@ -9922,7 +9997,7 @@
         <v>24</v>
       </c>
       <c r="B340" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C340">
         <v>70</v>
@@ -9937,7 +10012,7 @@
         <v>8.5</v>
       </c>
       <c r="G340" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="H340">
         <v>77</v>
@@ -9948,7 +10023,7 @@
         <v>24</v>
       </c>
       <c r="B341" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C341">
         <v>75</v>
@@ -9963,7 +10038,7 @@
         <v>8.75</v>
       </c>
       <c r="G341" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="H341">
         <v>77.50000000000001</v>
@@ -9974,7 +10049,7 @@
         <v>24</v>
       </c>
       <c r="B342" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C342">
         <v>50</v>
@@ -9989,7 +10064,7 @@
         <v>8</v>
       </c>
       <c r="G342" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="H342">
         <v>66.66666666666666</v>
@@ -10000,7 +10075,7 @@
         <v>24</v>
       </c>
       <c r="B343" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C343">
         <v>40</v>
@@ -10015,7 +10090,7 @@
         <v>6</v>
       </c>
       <c r="G343" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="H343">
         <v>50.66666666666666</v>
@@ -10026,7 +10101,7 @@
         <v>24</v>
       </c>
       <c r="B344" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C344">
         <v>50</v>
@@ -10041,7 +10116,7 @@
         <v>6.5</v>
       </c>
       <c r="G344" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="H344">
         <v>63.33333333333333</v>
@@ -10052,7 +10127,7 @@
         <v>24</v>
       </c>
       <c r="B345" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C345">
         <v>63</v>
@@ -10067,7 +10142,7 @@
         <v>8</v>
       </c>
       <c r="G345" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="H345">
         <v>75.59999999999999</v>
@@ -10078,7 +10153,7 @@
         <v>24</v>
       </c>
       <c r="B346" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C346">
         <v>63</v>
@@ -10093,7 +10168,7 @@
         <v>8.5</v>
       </c>
       <c r="G346" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="H346">
         <v>75.59999999999999</v>
@@ -10104,7 +10179,7 @@
         <v>24</v>
       </c>
       <c r="B347" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C347">
         <v>11</v>
@@ -10119,7 +10194,7 @@
         <v>5</v>
       </c>
       <c r="G347" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="H347">
         <v>16.5</v>
@@ -10130,7 +10205,7 @@
         <v>24</v>
       </c>
       <c r="B348" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C348">
         <v>32</v>
@@ -10145,7 +10220,7 @@
         <v>5</v>
       </c>
       <c r="G348" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="H348">
         <v>48</v>
@@ -10156,7 +10231,7 @@
         <v>24</v>
       </c>
       <c r="B349" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C349">
         <v>33</v>
@@ -10171,7 +10246,7 @@
         <v>7</v>
       </c>
       <c r="G349" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="H349">
         <v>49.5</v>
@@ -10182,7 +10257,7 @@
         <v>24</v>
       </c>
       <c r="B350" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C350">
         <v>59</v>
@@ -10197,7 +10272,7 @@
         <v>8</v>
       </c>
       <c r="G350" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="H350">
         <v>82.59999999999999</v>
@@ -10208,7 +10283,7 @@
         <v>24</v>
       </c>
       <c r="B351" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C351">
         <v>39</v>
@@ -10223,7 +10298,7 @@
         <v>9</v>
       </c>
       <c r="G351" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="H351">
         <v>58.5</v>
@@ -10234,7 +10309,7 @@
         <v>24</v>
       </c>
       <c r="B352" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C352">
         <v>66</v>
@@ -10249,7 +10324,7 @@
         <v>9</v>
       </c>
       <c r="G352" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="H352">
         <v>92.39999999999999</v>
@@ -10260,7 +10335,7 @@
         <v>25</v>
       </c>
       <c r="B353" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C353">
         <v>70</v>
@@ -10275,7 +10350,7 @@
         <v>6</v>
       </c>
       <c r="G353" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="H353">
         <v>81.66666666666667</v>
@@ -10286,7 +10361,7 @@
         <v>25</v>
       </c>
       <c r="B354" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C354">
         <v>120</v>
@@ -10301,7 +10376,7 @@
         <v>6</v>
       </c>
       <c r="G354" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="H354">
         <v>124</v>
@@ -10312,7 +10387,7 @@
         <v>25</v>
       </c>
       <c r="B355" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C355">
         <v>140</v>
@@ -10327,7 +10402,7 @@
         <v>6.5</v>
       </c>
       <c r="G355" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="H355">
         <v>144.6666666666667</v>
@@ -10338,7 +10413,7 @@
         <v>25</v>
       </c>
       <c r="B356" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C356">
         <v>160</v>
@@ -10353,7 +10428,7 @@
         <v>8.5</v>
       </c>
       <c r="G356" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="H356">
         <v>165.3333333333333</v>
@@ -10364,7 +10439,7 @@
         <v>25</v>
       </c>
       <c r="B357" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C357">
         <v>140</v>
@@ -10379,7 +10454,7 @@
         <v>8.5</v>
       </c>
       <c r="G357" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="H357">
         <v>163.3333333333333</v>
@@ -10390,7 +10465,7 @@
         <v>25</v>
       </c>
       <c r="B358" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C358">
         <v>140</v>
@@ -10405,7 +10480,7 @@
         <v>9</v>
       </c>
       <c r="G358" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="H358">
         <v>163.3333333333333</v>
@@ -10416,7 +10491,7 @@
         <v>25</v>
       </c>
       <c r="B359" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C359">
         <v>120</v>
@@ -10431,7 +10506,7 @@
         <v>9</v>
       </c>
       <c r="G359" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="H359">
         <v>144</v>
@@ -10442,7 +10517,7 @@
         <v>25</v>
       </c>
       <c r="B360" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C360">
         <v>30</v>
@@ -10457,7 +10532,7 @@
         <v>6</v>
       </c>
       <c r="G360" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="H360">
         <v>38</v>
@@ -10468,7 +10543,7 @@
         <v>25</v>
       </c>
       <c r="B361" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C361">
         <v>40</v>
@@ -10483,7 +10558,7 @@
         <v>7</v>
       </c>
       <c r="G361" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="H361">
         <v>48</v>
@@ -10494,7 +10569,7 @@
         <v>25</v>
       </c>
       <c r="B362" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C362">
         <v>50</v>
@@ -10509,7 +10584,7 @@
         <v>8</v>
       </c>
       <c r="G362" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="H362">
         <v>53.33333333333334</v>
@@ -10520,7 +10595,7 @@
         <v>25</v>
       </c>
       <c r="B363" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C363">
         <v>55</v>
@@ -10535,7 +10610,7 @@
         <v>10</v>
       </c>
       <c r="G363" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="H363">
         <v>56.83333333333334</v>
@@ -10546,7 +10621,7 @@
         <v>25</v>
       </c>
       <c r="B364" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C364">
         <v>45</v>
@@ -10561,7 +10636,7 @@
         <v>9</v>
       </c>
       <c r="G364" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="H364">
         <v>52.5</v>
@@ -10572,7 +10647,7 @@
         <v>25</v>
       </c>
       <c r="B365" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C365">
         <v>45</v>
@@ -10587,7 +10662,7 @@
         <v>9.5</v>
       </c>
       <c r="G365" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="H365">
         <v>52.5</v>
@@ -10598,7 +10673,7 @@
         <v>25</v>
       </c>
       <c r="B366" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C366">
         <v>45</v>
@@ -10613,7 +10688,7 @@
         <v>7</v>
       </c>
       <c r="G366" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="H366">
         <v>57</v>
@@ -10624,7 +10699,7 @@
         <v>25</v>
       </c>
       <c r="B367" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C367">
         <v>50</v>
@@ -10639,7 +10714,7 @@
         <v>8</v>
       </c>
       <c r="G367" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="H367">
         <v>63.33333333333333</v>
@@ -10650,7 +10725,7 @@
         <v>25</v>
       </c>
       <c r="B368" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C368">
         <v>50</v>
@@ -10665,7 +10740,7 @@
         <v>8</v>
       </c>
       <c r="G368" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="H368">
         <v>63.33333333333333</v>
@@ -10676,7 +10751,7 @@
         <v>25</v>
       </c>
       <c r="B369" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C369">
         <v>50</v>
@@ -10691,7 +10766,7 @@
         <v>8</v>
       </c>
       <c r="G369" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="H369">
         <v>63.33333333333333</v>
@@ -10702,7 +10777,7 @@
         <v>25</v>
       </c>
       <c r="B370" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C370">
         <v>40</v>
@@ -10717,7 +10792,7 @@
         <v>8.5</v>
       </c>
       <c r="G370" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="H370">
         <v>60</v>
@@ -10728,7 +10803,7 @@
         <v>26</v>
       </c>
       <c r="B371" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C371">
         <v>20</v>
@@ -10743,7 +10818,7 @@
         <v>5</v>
       </c>
       <c r="G371" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="H371">
         <v>25.33333333333333</v>
@@ -10754,7 +10829,7 @@
         <v>27</v>
       </c>
       <c r="B372" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C372">
         <v>40</v>
@@ -10769,7 +10844,7 @@
         <v>6</v>
       </c>
       <c r="G372" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="H372">
         <v>46.66666666666667</v>
@@ -10780,7 +10855,7 @@
         <v>28</v>
       </c>
       <c r="B373" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C373">
         <v>50</v>
@@ -10795,7 +10870,7 @@
         <v>7</v>
       </c>
       <c r="G373" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="H373">
         <v>60</v>
@@ -10806,7 +10881,7 @@
         <v>29</v>
       </c>
       <c r="B374" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C374">
         <v>50</v>
@@ -10821,7 +10896,7 @@
         <v>6.5</v>
       </c>
       <c r="G374" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="H374">
         <v>63.33333333333333</v>
@@ -10832,7 +10907,7 @@
         <v>30</v>
       </c>
       <c r="B375" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C375">
         <v>60</v>
@@ -10847,7 +10922,7 @@
         <v>7</v>
       </c>
       <c r="G375" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="H375">
         <v>66</v>
@@ -10858,7 +10933,7 @@
         <v>31</v>
       </c>
       <c r="B376" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C376">
         <v>70</v>
@@ -10873,7 +10948,7 @@
         <v>7.75</v>
       </c>
       <c r="G376" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="H376">
         <v>72.33333333333334</v>
@@ -10884,7 +10959,7 @@
         <v>32</v>
       </c>
       <c r="B377" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C377">
         <v>75</v>
@@ -10899,7 +10974,7 @@
         <v>8</v>
       </c>
       <c r="G377" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="H377">
         <v>77.50000000000001</v>
@@ -10910,7 +10985,7 @@
         <v>33</v>
       </c>
       <c r="B378" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C378">
         <v>77.5</v>
@@ -10925,7 +11000,7 @@
         <v>10</v>
       </c>
       <c r="G378" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="H378">
         <v>77.5</v>
@@ -10936,7 +11011,7 @@
         <v>34</v>
       </c>
       <c r="B379" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C379">
         <v>66.25</v>
@@ -10951,7 +11026,7 @@
         <v>9</v>
       </c>
       <c r="G379" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="H379">
         <v>77.29166666666667</v>
@@ -10962,7 +11037,7 @@
         <v>35</v>
       </c>
       <c r="B380" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C380">
         <v>60</v>
@@ -10977,7 +11052,7 @@
         <v>8.25</v>
       </c>
       <c r="G380" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="H380">
         <v>70</v>
@@ -10988,7 +11063,7 @@
         <v>36</v>
       </c>
       <c r="B381" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C381">
         <v>30</v>
@@ -11003,7 +11078,7 @@
         <v>6</v>
       </c>
       <c r="G381" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="H381">
         <v>42</v>
@@ -11014,7 +11089,7 @@
         <v>37</v>
       </c>
       <c r="B382" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C382">
         <v>50</v>
@@ -11029,7 +11104,7 @@
         <v>8.5</v>
       </c>
       <c r="G382" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="H382">
         <v>63.33333333333333</v>
@@ -11040,7 +11115,7 @@
         <v>38</v>
       </c>
       <c r="B383" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C383">
         <v>50</v>
@@ -11055,7 +11130,7 @@
         <v>8</v>
       </c>
       <c r="G383" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="H383">
         <v>63.33333333333333</v>
@@ -11066,7 +11141,7 @@
         <v>39</v>
       </c>
       <c r="B384" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C384">
         <v>50</v>
@@ -11081,7 +11156,7 @@
         <v>10</v>
       </c>
       <c r="G384" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="H384">
         <v>60</v>
@@ -11092,7 +11167,7 @@
         <v>40</v>
       </c>
       <c r="B385" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C385">
         <v>0</v>
@@ -11107,7 +11182,7 @@
         <v>6</v>
       </c>
       <c r="G385" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H385">
         <v>0</v>
@@ -11118,7 +11193,7 @@
         <v>41</v>
       </c>
       <c r="B386" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C386">
         <v>25</v>
@@ -11133,7 +11208,7 @@
         <v>8</v>
       </c>
       <c r="G386" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="H386">
         <v>30</v>
@@ -11144,7 +11219,7 @@
         <v>42</v>
       </c>
       <c r="B387" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C387">
         <v>25</v>
@@ -11159,7 +11234,7 @@
         <v>8</v>
       </c>
       <c r="G387" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H387">
         <v>31.66666666666666</v>
@@ -11170,7 +11245,7 @@
         <v>43</v>
       </c>
       <c r="B388" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C388">
         <v>25</v>
@@ -11185,7 +11260,7 @@
         <v>8.5</v>
       </c>
       <c r="G388" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="H388">
         <v>31.66666666666666</v>
@@ -11196,7 +11271,7 @@
         <v>44</v>
       </c>
       <c r="B389" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C389">
         <v>45</v>
@@ -11211,7 +11286,7 @@
         <v>6.5</v>
       </c>
       <c r="G389" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="H389">
         <v>62.99999999999999</v>
@@ -11222,7 +11297,7 @@
         <v>45</v>
       </c>
       <c r="B390" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C390">
         <v>60</v>
@@ -11237,7 +11312,7 @@
         <v>8</v>
       </c>
       <c r="G390" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="H390">
         <v>76</v>
@@ -11248,7 +11323,7 @@
         <v>46</v>
       </c>
       <c r="B391" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C391">
         <v>60</v>
@@ -11263,7 +11338,7 @@
         <v>7.5</v>
       </c>
       <c r="G391" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="H391">
         <v>76</v>
@@ -11274,7 +11349,7 @@
         <v>47</v>
       </c>
       <c r="B392" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C392">
         <v>60</v>
@@ -11289,7 +11364,7 @@
         <v>7.5</v>
       </c>
       <c r="G392" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="H392">
         <v>76</v>
@@ -11300,7 +11375,7 @@
         <v>48</v>
       </c>
       <c r="B393" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C393">
         <v>60</v>
@@ -11315,7 +11390,7 @@
         <v>9</v>
       </c>
       <c r="G393" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="H393">
         <v>76</v>
@@ -11326,7 +11401,7 @@
         <v>49</v>
       </c>
       <c r="B394" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C394">
         <v>40</v>
@@ -11341,7 +11416,7 @@
         <v>8</v>
       </c>
       <c r="G394" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="H394">
         <v>53.33333333333333</v>
@@ -11352,7 +11427,7 @@
         <v>50</v>
       </c>
       <c r="B395" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C395">
         <v>40</v>
@@ -11367,7 +11442,7 @@
         <v>7.5</v>
       </c>
       <c r="G395" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="H395">
         <v>56</v>
@@ -11378,7 +11453,7 @@
         <v>51</v>
       </c>
       <c r="B396" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C396">
         <v>40</v>
@@ -11393,7 +11468,7 @@
         <v>8</v>
       </c>
       <c r="G396" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="H396">
         <v>56</v>
@@ -11404,7 +11479,7 @@
         <v>52</v>
       </c>
       <c r="B397" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C397">
         <v>40</v>
@@ -11419,7 +11494,7 @@
         <v>8</v>
       </c>
       <c r="G397" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="H397">
         <v>56</v>
@@ -11430,7 +11505,7 @@
         <v>53</v>
       </c>
       <c r="B398" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C398">
         <v>40</v>
@@ -11445,7 +11520,7 @@
         <v>8.5</v>
       </c>
       <c r="G398" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="H398">
         <v>56</v>
@@ -11456,7 +11531,7 @@
         <v>54</v>
       </c>
       <c r="B399" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C399">
         <v>40</v>
@@ -11471,7 +11546,7 @@
         <v>9</v>
       </c>
       <c r="G399" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="H399">
         <v>56</v>
@@ -11482,7 +11557,7 @@
         <v>55</v>
       </c>
       <c r="B400" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C400">
         <v>20</v>
@@ -11497,7 +11572,7 @@
         <v>5</v>
       </c>
       <c r="G400" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="H400">
         <v>25.33333333333333</v>
@@ -11508,7 +11583,7 @@
         <v>56</v>
       </c>
       <c r="B401" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C401">
         <v>70</v>
@@ -11523,7 +11598,7 @@
         <v>6</v>
       </c>
       <c r="G401" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="H401">
         <v>81.66666666666667</v>
@@ -11534,7 +11609,7 @@
         <v>57</v>
       </c>
       <c r="B402" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C402">
         <v>120</v>
@@ -11549,7 +11624,7 @@
         <v>7.5</v>
       </c>
       <c r="G402" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="H402">
         <v>124</v>
@@ -11560,7 +11635,7 @@
         <v>58</v>
       </c>
       <c r="B403" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C403">
         <v>110</v>
@@ -11575,7 +11650,7 @@
         <v>8.5</v>
       </c>
       <c r="G403" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="H403">
         <v>128.3333333333333</v>
@@ -11586,7 +11661,7 @@
         <v>59</v>
       </c>
       <c r="B404" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C404">
         <v>110</v>
@@ -11601,7 +11676,7 @@
         <v>10</v>
       </c>
       <c r="G404" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="H404">
         <v>124.6666666666667</v>
@@ -11612,7 +11687,7 @@
         <v>60</v>
       </c>
       <c r="B405" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C405">
         <v>100</v>
@@ -11627,7 +11702,7 @@
         <v>9.5</v>
       </c>
       <c r="G405" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="H405">
         <v>110</v>
@@ -11638,7 +11713,7 @@
         <v>61</v>
       </c>
       <c r="B406" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C406">
         <v>40</v>
@@ -11653,7 +11728,7 @@
         <v>6</v>
       </c>
       <c r="G406" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="H406">
         <v>60</v>
@@ -11664,7 +11739,7 @@
         <v>62</v>
       </c>
       <c r="B407" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C407">
         <v>50</v>
@@ -11679,7 +11754,7 @@
         <v>7</v>
       </c>
       <c r="G407" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="H407">
         <v>70</v>
@@ -11690,7 +11765,7 @@
         <v>63</v>
       </c>
       <c r="B408" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C408">
         <v>50</v>
@@ -11705,7 +11780,7 @@
         <v>7.5</v>
       </c>
       <c r="G408" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="H408">
         <v>70</v>
@@ -11716,7 +11791,7 @@
         <v>64</v>
       </c>
       <c r="B409" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C409">
         <v>50</v>
@@ -11731,7 +11806,7 @@
         <v>8.5</v>
       </c>
       <c r="G409" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="H409">
         <v>70</v>
@@ -11742,7 +11817,7 @@
         <v>65</v>
       </c>
       <c r="B410" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C410">
         <v>30</v>
@@ -11757,7 +11832,7 @@
         <v>6</v>
       </c>
       <c r="G410" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="H410">
         <v>40</v>
@@ -11768,7 +11843,7 @@
         <v>66</v>
       </c>
       <c r="B411" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C411">
         <v>30</v>
@@ -11783,7 +11858,7 @@
         <v>6.5</v>
       </c>
       <c r="G411" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="H411">
         <v>40</v>
@@ -11794,7 +11869,7 @@
         <v>67</v>
       </c>
       <c r="B412" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C412">
         <v>40</v>
@@ -11809,7 +11884,7 @@
         <v>8.5</v>
       </c>
       <c r="G412" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="H412">
         <v>53.33333333333333</v>
@@ -11820,7 +11895,7 @@
         <v>68</v>
       </c>
       <c r="B413" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C413">
         <v>40</v>
@@ -11835,7 +11910,7 @@
         <v>10</v>
       </c>
       <c r="G413" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="H413">
         <v>50.66666666666666</v>
@@ -11846,7 +11921,7 @@
         <v>69</v>
       </c>
       <c r="B414" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C414">
         <v>40</v>
@@ -11861,7 +11936,7 @@
         <v>9</v>
       </c>
       <c r="G414" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="H414">
         <v>50.66666666666666</v>
@@ -11872,7 +11947,7 @@
         <v>70</v>
       </c>
       <c r="B415" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C415">
         <v>30</v>
@@ -11887,7 +11962,7 @@
         <v>8</v>
       </c>
       <c r="G415" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="H415">
         <v>35</v>
@@ -11898,7 +11973,7 @@
         <v>70</v>
       </c>
       <c r="B416" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C416">
         <v>30</v>
@@ -11913,7 +11988,7 @@
         <v>8</v>
       </c>
       <c r="G416" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="H416">
         <v>42</v>
@@ -11924,7 +11999,7 @@
         <v>71</v>
       </c>
       <c r="B417" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C417">
         <v>30</v>
@@ -11939,7 +12014,7 @@
         <v>8.5</v>
       </c>
       <c r="G417" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="H417">
         <v>36</v>
@@ -11950,7 +12025,7 @@
         <v>71</v>
       </c>
       <c r="B418" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C418">
         <v>30</v>
@@ -11965,7 +12040,7 @@
         <v>8.5</v>
       </c>
       <c r="G418" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="H418">
         <v>42</v>
@@ -11976,7 +12051,7 @@
         <v>72</v>
       </c>
       <c r="B419" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C419">
         <v>30</v>
@@ -11991,7 +12066,7 @@
         <v>9</v>
       </c>
       <c r="G419" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="H419">
         <v>36</v>
@@ -12002,7 +12077,7 @@
         <v>72</v>
       </c>
       <c r="B420" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C420">
         <v>30</v>
@@ -12017,7 +12092,7 @@
         <v>9</v>
       </c>
       <c r="G420" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="H420">
         <v>42</v>
@@ -12028,7 +12103,7 @@
         <v>73</v>
       </c>
       <c r="B421" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C421">
         <v>20</v>
@@ -12040,7 +12115,7 @@
         <v>160</v>
       </c>
       <c r="G421" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="H421">
         <v>25.33333333333333</v>
@@ -12054,7 +12129,7 @@
         <v>73</v>
       </c>
       <c r="B422" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C422">
         <v>70</v>
@@ -12066,7 +12141,7 @@
         <v>350</v>
       </c>
       <c r="G422" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="H422">
         <v>81.66666666666667</v>
@@ -12080,7 +12155,7 @@
         <v>73</v>
       </c>
       <c r="B423" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C423">
         <v>120</v>
@@ -12092,7 +12167,7 @@
         <v>360</v>
       </c>
       <c r="G423" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="H423">
         <v>132</v>
@@ -12106,7 +12181,7 @@
         <v>73</v>
       </c>
       <c r="B424" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C424">
         <v>90</v>
@@ -12118,7 +12193,7 @@
         <v>1800</v>
       </c>
       <c r="G424" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="H424">
         <v>150</v>
@@ -12132,7 +12207,7 @@
         <v>73</v>
       </c>
       <c r="B425" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C425">
         <v>30</v>
@@ -12144,7 +12219,7 @@
         <v>240</v>
       </c>
       <c r="G425" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="H425">
         <v>38</v>
@@ -12158,7 +12233,7 @@
         <v>73</v>
       </c>
       <c r="B426" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C426">
         <v>40</v>
@@ -12170,7 +12245,7 @@
         <v>120</v>
       </c>
       <c r="G426" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="H426">
         <v>44</v>
@@ -12184,7 +12259,7 @@
         <v>73</v>
       </c>
       <c r="B427" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C427">
         <v>45</v>
@@ -12196,7 +12271,7 @@
         <v>135</v>
       </c>
       <c r="G427" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="H427">
         <v>49.50000000000001</v>
@@ -12210,7 +12285,7 @@
         <v>73</v>
       </c>
       <c r="B428" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C428">
         <v>45</v>
@@ -12222,7 +12297,7 @@
         <v>360</v>
       </c>
       <c r="G428" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="H428">
         <v>57</v>
@@ -12236,7 +12311,7 @@
         <v>73</v>
       </c>
       <c r="B429" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C429">
         <v>45</v>
@@ -12248,7 +12323,7 @@
         <v>360</v>
       </c>
       <c r="G429" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="H429">
         <v>57</v>
@@ -12262,7 +12337,7 @@
         <v>73</v>
       </c>
       <c r="B430" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C430">
         <v>45</v>
@@ -12274,7 +12349,7 @@
         <v>360</v>
       </c>
       <c r="G430" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="H430">
         <v>57</v>
@@ -12288,7 +12363,7 @@
         <v>73</v>
       </c>
       <c r="B431" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C431">
         <v>40</v>
@@ -12300,7 +12375,7 @@
         <v>480</v>
       </c>
       <c r="G431" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="H431">
         <v>56</v>
@@ -12314,7 +12389,7 @@
         <v>73</v>
       </c>
       <c r="B432" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C432">
         <v>50</v>
@@ -12326,7 +12401,7 @@
         <v>300</v>
       </c>
       <c r="G432" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="H432">
         <v>60</v>
@@ -12340,7 +12415,7 @@
         <v>73</v>
       </c>
       <c r="B433" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C433">
         <v>60</v>
@@ -12352,7 +12427,7 @@
         <v>360</v>
       </c>
       <c r="G433" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="H433">
         <v>72</v>
@@ -12366,7 +12441,7 @@
         <v>73</v>
       </c>
       <c r="B434" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C434">
         <v>60</v>
@@ -12378,7 +12453,7 @@
         <v>360</v>
       </c>
       <c r="G434" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="H434">
         <v>72</v>
@@ -12392,7 +12467,7 @@
         <v>73</v>
       </c>
       <c r="B435" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C435">
         <v>60</v>
@@ -12404,7 +12479,7 @@
         <v>360</v>
       </c>
       <c r="G435" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="H435">
         <v>72</v>
@@ -12418,7 +12493,7 @@
         <v>73</v>
       </c>
       <c r="B436" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C436">
         <v>60</v>
@@ -12430,7 +12505,7 @@
         <v>360</v>
       </c>
       <c r="G436" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="H436">
         <v>72</v>
@@ -12444,7 +12519,7 @@
         <v>73</v>
       </c>
       <c r="B437" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C437">
         <v>20</v>
@@ -12456,7 +12531,7 @@
         <v>160</v>
       </c>
       <c r="G437" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="H437">
         <v>25.33333333333333</v>
@@ -12470,7 +12545,7 @@
         <v>73</v>
       </c>
       <c r="B438" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C438">
         <v>30</v>
@@ -12482,7 +12557,7 @@
         <v>150</v>
       </c>
       <c r="G438" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="H438">
         <v>35</v>
@@ -12496,7 +12571,7 @@
         <v>73</v>
       </c>
       <c r="B439" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C439">
         <v>20</v>
@@ -12508,7 +12583,7 @@
         <v>240</v>
       </c>
       <c r="G439" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="H439">
         <v>28</v>
@@ -12522,7 +12597,7 @@
         <v>73</v>
       </c>
       <c r="B440" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C440">
         <v>30</v>
@@ -12534,7 +12609,7 @@
         <v>240</v>
       </c>
       <c r="G440" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="H440">
         <v>38</v>
@@ -12548,7 +12623,7 @@
         <v>73</v>
       </c>
       <c r="B441" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C441">
         <v>40</v>
@@ -12560,7 +12635,7 @@
         <v>120</v>
       </c>
       <c r="G441" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="H441">
         <v>44</v>
@@ -12574,7 +12649,7 @@
         <v>73</v>
       </c>
       <c r="B442" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C442">
         <v>30</v>
@@ -12586,7 +12661,7 @@
         <v>240</v>
       </c>
       <c r="G442" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="H442">
         <v>38</v>
@@ -12600,7 +12675,7 @@
         <v>73</v>
       </c>
       <c r="B443" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C443">
         <v>30</v>
@@ -12612,7 +12687,7 @@
         <v>240</v>
       </c>
       <c r="G443" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="H443">
         <v>38</v>
@@ -12626,7 +12701,7 @@
         <v>74</v>
       </c>
       <c r="B444" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C444">
         <v>20</v>
@@ -12641,7 +12716,7 @@
         <v>4</v>
       </c>
       <c r="G444" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="H444">
         <v>25.33333333333333</v>
@@ -12652,7 +12727,7 @@
         <v>74</v>
       </c>
       <c r="B445" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C445">
         <v>70</v>
@@ -12667,7 +12742,7 @@
         <v>6</v>
       </c>
       <c r="G445" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="H445">
         <v>84</v>
@@ -12678,7 +12753,7 @@
         <v>74</v>
       </c>
       <c r="B446" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C446">
         <v>110</v>
@@ -12693,7 +12768,7 @@
         <v>7</v>
       </c>
       <c r="G446" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="H446">
         <v>113.6666666666667</v>
@@ -12704,7 +12779,7 @@
         <v>74</v>
       </c>
       <c r="B447" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C447">
         <v>110</v>
@@ -12719,7 +12794,7 @@
         <v>8.5</v>
       </c>
       <c r="G447" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="H447">
         <v>121</v>
@@ -12730,7 +12805,7 @@
         <v>74</v>
       </c>
       <c r="B448" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C448">
         <v>90</v>
@@ -12745,7 +12820,7 @@
         <v>8</v>
       </c>
       <c r="G448" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="H448">
         <v>120</v>
@@ -12756,7 +12831,7 @@
         <v>74</v>
       </c>
       <c r="B449" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C449">
         <v>90</v>
@@ -12771,7 +12846,7 @@
         <v>8.5</v>
       </c>
       <c r="G449" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="H449">
         <v>120</v>
@@ -12782,7 +12857,7 @@
         <v>74</v>
       </c>
       <c r="B450" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C450">
         <v>30</v>
@@ -12797,7 +12872,7 @@
         <v>5.5</v>
       </c>
       <c r="G450" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="H450">
         <v>38</v>
@@ -12808,7 +12883,7 @@
         <v>74</v>
       </c>
       <c r="B451" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C451">
         <v>40</v>
@@ -12823,7 +12898,7 @@
         <v>6</v>
       </c>
       <c r="G451" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="H451">
         <v>50.66666666666666</v>
@@ -12834,7 +12909,7 @@
         <v>74</v>
       </c>
       <c r="B452" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C452">
         <v>45</v>
@@ -12849,7 +12924,7 @@
         <v>6</v>
       </c>
       <c r="G452" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="H452">
         <v>46.50000000000001</v>
@@ -12860,7 +12935,7 @@
         <v>74</v>
       </c>
       <c r="B453" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C453">
         <v>50</v>
@@ -12875,7 +12950,7 @@
         <v>6.5</v>
       </c>
       <c r="G453" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="H453">
         <v>51.66666666666667</v>
@@ -12886,7 +12961,7 @@
         <v>74</v>
       </c>
       <c r="B454" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C454">
         <v>55</v>
@@ -12901,7 +12976,7 @@
         <v>7</v>
       </c>
       <c r="G454" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="H454">
         <v>56.83333333333334</v>
@@ -12912,7 +12987,7 @@
         <v>74</v>
       </c>
       <c r="B455" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C455">
         <v>60</v>
@@ -12927,7 +13002,7 @@
         <v>10</v>
       </c>
       <c r="G455" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H455">
         <v>60</v>
@@ -12938,7 +13013,7 @@
         <v>74</v>
       </c>
       <c r="B456" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C456">
         <v>50</v>
@@ -12953,7 +13028,7 @@
         <v>8</v>
       </c>
       <c r="G456" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="H456">
         <v>60</v>
@@ -12964,7 +13039,7 @@
         <v>74</v>
       </c>
       <c r="B457" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C457">
         <v>50</v>
@@ -12979,10 +13054,634 @@
         <v>9</v>
       </c>
       <c r="G457" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="H457">
         <v>60</v>
+      </c>
+    </row>
+    <row r="458" spans="1:8">
+      <c r="A458" t="s">
+        <v>75</v>
+      </c>
+      <c r="B458" t="s">
+        <v>106</v>
+      </c>
+      <c r="C458">
+        <v>20</v>
+      </c>
+      <c r="D458">
+        <v>10</v>
+      </c>
+      <c r="E458">
+        <v>200</v>
+      </c>
+      <c r="F458">
+        <v>3</v>
+      </c>
+      <c r="G458" t="s">
+        <v>376</v>
+      </c>
+      <c r="H458">
+        <v>26.66666666666666</v>
+      </c>
+    </row>
+    <row r="459" spans="1:8">
+      <c r="A459" t="s">
+        <v>75</v>
+      </c>
+      <c r="B459" t="s">
+        <v>106</v>
+      </c>
+      <c r="C459">
+        <v>60</v>
+      </c>
+      <c r="D459">
+        <v>8</v>
+      </c>
+      <c r="E459">
+        <v>480</v>
+      </c>
+      <c r="F459">
+        <v>6</v>
+      </c>
+      <c r="G459" t="s">
+        <v>377</v>
+      </c>
+      <c r="H459">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="460" spans="1:8">
+      <c r="A460" t="s">
+        <v>75</v>
+      </c>
+      <c r="B460" t="s">
+        <v>106</v>
+      </c>
+      <c r="C460">
+        <v>100</v>
+      </c>
+      <c r="D460">
+        <v>5</v>
+      </c>
+      <c r="E460">
+        <v>500</v>
+      </c>
+      <c r="F460">
+        <v>7</v>
+      </c>
+      <c r="G460" t="s">
+        <v>378</v>
+      </c>
+      <c r="H460">
+        <v>116.6666666666667</v>
+      </c>
+    </row>
+    <row r="461" spans="1:8">
+      <c r="A461" t="s">
+        <v>75</v>
+      </c>
+      <c r="B461" t="s">
+        <v>106</v>
+      </c>
+      <c r="C461">
+        <v>120</v>
+      </c>
+      <c r="D461">
+        <v>2</v>
+      </c>
+      <c r="E461">
+        <v>240</v>
+      </c>
+      <c r="F461">
+        <v>8</v>
+      </c>
+      <c r="G461" t="s">
+        <v>379</v>
+      </c>
+      <c r="H461">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="462" spans="1:8">
+      <c r="A462" t="s">
+        <v>75</v>
+      </c>
+      <c r="B462" t="s">
+        <v>106</v>
+      </c>
+      <c r="C462">
+        <v>130</v>
+      </c>
+      <c r="D462">
+        <v>1</v>
+      </c>
+      <c r="E462">
+        <v>130</v>
+      </c>
+      <c r="F462">
+        <v>9</v>
+      </c>
+      <c r="G462" t="s">
+        <v>169</v>
+      </c>
+      <c r="H462">
+        <v>134.3333333333333</v>
+      </c>
+    </row>
+    <row r="463" spans="1:8">
+      <c r="A463" t="s">
+        <v>75</v>
+      </c>
+      <c r="B463" t="s">
+        <v>106</v>
+      </c>
+      <c r="C463">
+        <v>100</v>
+      </c>
+      <c r="D463">
+        <v>10</v>
+      </c>
+      <c r="E463">
+        <v>1000</v>
+      </c>
+      <c r="F463">
+        <v>9</v>
+      </c>
+      <c r="G463" t="s">
+        <v>380</v>
+      </c>
+      <c r="H463">
+        <v>133.3333333333333</v>
+      </c>
+    </row>
+    <row r="464" spans="1:8">
+      <c r="A464" t="s">
+        <v>75</v>
+      </c>
+      <c r="B464" t="s">
+        <v>106</v>
+      </c>
+      <c r="C464">
+        <v>100</v>
+      </c>
+      <c r="D464">
+        <v>10</v>
+      </c>
+      <c r="E464">
+        <v>1000</v>
+      </c>
+      <c r="F464">
+        <v>9.5</v>
+      </c>
+      <c r="G464" t="s">
+        <v>381</v>
+      </c>
+      <c r="H464">
+        <v>133.3333333333333</v>
+      </c>
+    </row>
+    <row r="465" spans="1:8">
+      <c r="A465" t="s">
+        <v>75</v>
+      </c>
+      <c r="B465" t="s">
+        <v>119</v>
+      </c>
+      <c r="C465">
+        <v>30</v>
+      </c>
+      <c r="D465">
+        <v>10</v>
+      </c>
+      <c r="E465">
+        <v>300</v>
+      </c>
+      <c r="F465">
+        <v>6</v>
+      </c>
+      <c r="G465" t="s">
+        <v>382</v>
+      </c>
+      <c r="H465">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="466" spans="1:8">
+      <c r="A466" t="s">
+        <v>75</v>
+      </c>
+      <c r="B466" t="s">
+        <v>124</v>
+      </c>
+      <c r="C466">
+        <v>30</v>
+      </c>
+      <c r="D466">
+        <v>10</v>
+      </c>
+      <c r="E466">
+        <v>300</v>
+      </c>
+      <c r="F466">
+        <v>5.5</v>
+      </c>
+      <c r="G466" t="s">
+        <v>383</v>
+      </c>
+      <c r="H466">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="467" spans="1:8">
+      <c r="A467" t="s">
+        <v>75</v>
+      </c>
+      <c r="B467" t="s">
+        <v>124</v>
+      </c>
+      <c r="C467">
+        <v>50</v>
+      </c>
+      <c r="D467">
+        <v>2</v>
+      </c>
+      <c r="E467">
+        <v>100</v>
+      </c>
+      <c r="F467">
+        <v>10</v>
+      </c>
+      <c r="G467" t="s">
+        <v>384</v>
+      </c>
+      <c r="H467">
+        <v>53.33333333333334</v>
+      </c>
+    </row>
+    <row r="468" spans="1:8">
+      <c r="A468" t="s">
+        <v>75</v>
+      </c>
+      <c r="B468" t="s">
+        <v>124</v>
+      </c>
+      <c r="C468">
+        <v>40</v>
+      </c>
+      <c r="D468">
+        <v>8</v>
+      </c>
+      <c r="E468">
+        <v>320</v>
+      </c>
+      <c r="F468">
+        <v>8</v>
+      </c>
+      <c r="G468" t="s">
+        <v>385</v>
+      </c>
+      <c r="H468">
+        <v>50.66666666666666</v>
+      </c>
+    </row>
+    <row r="469" spans="1:8">
+      <c r="A469" t="s">
+        <v>75</v>
+      </c>
+      <c r="B469" t="s">
+        <v>124</v>
+      </c>
+      <c r="C469">
+        <v>40</v>
+      </c>
+      <c r="D469">
+        <v>8</v>
+      </c>
+      <c r="E469">
+        <v>320</v>
+      </c>
+      <c r="F469">
+        <v>8.5</v>
+      </c>
+      <c r="G469" t="s">
+        <v>386</v>
+      </c>
+      <c r="H469">
+        <v>50.66666666666666</v>
+      </c>
+    </row>
+    <row r="470" spans="1:8">
+      <c r="A470" t="s">
+        <v>75</v>
+      </c>
+      <c r="B470" t="s">
+        <v>124</v>
+      </c>
+      <c r="C470">
+        <v>40</v>
+      </c>
+      <c r="D470">
+        <v>6</v>
+      </c>
+      <c r="E470">
+        <v>240</v>
+      </c>
+      <c r="F470">
+        <v>10</v>
+      </c>
+      <c r="G470" t="s">
+        <v>387</v>
+      </c>
+      <c r="H470">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="471" spans="1:8">
+      <c r="A471" t="s">
+        <v>75</v>
+      </c>
+      <c r="B471" t="s">
+        <v>125</v>
+      </c>
+      <c r="C471">
+        <v>40</v>
+      </c>
+      <c r="D471">
+        <v>15</v>
+      </c>
+      <c r="E471">
+        <v>600</v>
+      </c>
+      <c r="F471">
+        <v>7</v>
+      </c>
+      <c r="G471" t="s">
+        <v>388</v>
+      </c>
+      <c r="H471">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="472" spans="1:8">
+      <c r="A472" t="s">
+        <v>75</v>
+      </c>
+      <c r="B472" t="s">
+        <v>125</v>
+      </c>
+      <c r="C472">
+        <v>70</v>
+      </c>
+      <c r="D472">
+        <v>3</v>
+      </c>
+      <c r="E472">
+        <v>210</v>
+      </c>
+      <c r="F472">
+        <v>8.5</v>
+      </c>
+      <c r="G472" t="s">
+        <v>389</v>
+      </c>
+      <c r="H472">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="473" spans="1:8">
+      <c r="A473" t="s">
+        <v>75</v>
+      </c>
+      <c r="B473" t="s">
+        <v>125</v>
+      </c>
+      <c r="C473">
+        <v>60</v>
+      </c>
+      <c r="D473">
+        <v>8</v>
+      </c>
+      <c r="E473">
+        <v>480</v>
+      </c>
+      <c r="F473">
+        <v>8</v>
+      </c>
+      <c r="G473" t="s">
+        <v>390</v>
+      </c>
+      <c r="H473">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="474" spans="1:8">
+      <c r="A474" t="s">
+        <v>75</v>
+      </c>
+      <c r="B474" t="s">
+        <v>125</v>
+      </c>
+      <c r="C474">
+        <v>60</v>
+      </c>
+      <c r="D474">
+        <v>8</v>
+      </c>
+      <c r="E474">
+        <v>480</v>
+      </c>
+      <c r="F474">
+        <v>8</v>
+      </c>
+      <c r="G474" t="s">
+        <v>391</v>
+      </c>
+      <c r="H474">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="475" spans="1:8">
+      <c r="A475" t="s">
+        <v>75</v>
+      </c>
+      <c r="B475" t="s">
+        <v>125</v>
+      </c>
+      <c r="C475">
+        <v>60</v>
+      </c>
+      <c r="D475">
+        <v>8</v>
+      </c>
+      <c r="E475">
+        <v>480</v>
+      </c>
+      <c r="F475">
+        <v>9</v>
+      </c>
+      <c r="G475" t="s">
+        <v>392</v>
+      </c>
+      <c r="H475">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="476" spans="1:8">
+      <c r="A476" t="s">
+        <v>75</v>
+      </c>
+      <c r="B476" t="s">
+        <v>93</v>
+      </c>
+      <c r="C476">
+        <v>25</v>
+      </c>
+      <c r="D476">
+        <v>10</v>
+      </c>
+      <c r="E476">
+        <v>250</v>
+      </c>
+      <c r="F476">
+        <v>9</v>
+      </c>
+      <c r="G476" t="s">
+        <v>393</v>
+      </c>
+      <c r="H476">
+        <v>33.33333333333333</v>
+      </c>
+    </row>
+    <row r="477" spans="1:8">
+      <c r="A477" t="s">
+        <v>75</v>
+      </c>
+      <c r="B477" t="s">
+        <v>140</v>
+      </c>
+      <c r="C477">
+        <v>25</v>
+      </c>
+      <c r="D477">
+        <v>20</v>
+      </c>
+      <c r="E477">
+        <v>500</v>
+      </c>
+      <c r="F477">
+        <v>9</v>
+      </c>
+      <c r="G477" t="s">
+        <v>393</v>
+      </c>
+      <c r="H477">
+        <v>41.66666666666666</v>
+      </c>
+    </row>
+    <row r="478" spans="1:8">
+      <c r="A478" t="s">
+        <v>75</v>
+      </c>
+      <c r="B478" t="s">
+        <v>141</v>
+      </c>
+      <c r="C478">
+        <v>18</v>
+      </c>
+      <c r="D478">
+        <v>12</v>
+      </c>
+      <c r="E478">
+        <v>216</v>
+      </c>
+      <c r="F478">
+        <v>6</v>
+      </c>
+      <c r="G478" t="s">
+        <v>394</v>
+      </c>
+      <c r="H478">
+        <v>25.2</v>
+      </c>
+    </row>
+    <row r="479" spans="1:8">
+      <c r="A479" t="s">
+        <v>75</v>
+      </c>
+      <c r="B479" t="s">
+        <v>141</v>
+      </c>
+      <c r="C479">
+        <v>22</v>
+      </c>
+      <c r="D479">
+        <v>10</v>
+      </c>
+      <c r="E479">
+        <v>220</v>
+      </c>
+      <c r="F479">
+        <v>7.5</v>
+      </c>
+      <c r="G479" t="s">
+        <v>395</v>
+      </c>
+      <c r="H479">
+        <v>29.33333333333333</v>
+      </c>
+    </row>
+    <row r="480" spans="1:8">
+      <c r="A480" t="s">
+        <v>75</v>
+      </c>
+      <c r="B480" t="s">
+        <v>141</v>
+      </c>
+      <c r="C480">
+        <v>22</v>
+      </c>
+      <c r="D480">
+        <v>10</v>
+      </c>
+      <c r="E480">
+        <v>220</v>
+      </c>
+      <c r="F480">
+        <v>8.5</v>
+      </c>
+      <c r="G480" t="s">
+        <v>396</v>
+      </c>
+      <c r="H480">
+        <v>29.33333333333333</v>
+      </c>
+    </row>
+    <row r="481" spans="1:8">
+      <c r="A481" t="s">
+        <v>75</v>
+      </c>
+      <c r="B481" t="s">
+        <v>141</v>
+      </c>
+      <c r="C481">
+        <v>22</v>
+      </c>
+      <c r="D481">
+        <v>10</v>
+      </c>
+      <c r="E481">
+        <v>220</v>
+      </c>
+      <c r="F481">
+        <v>9</v>
+      </c>
+      <c r="G481" t="s">
+        <v>397</v>
+      </c>
+      <c r="H481">
+        <v>29.33333333333333</v>
       </c>
     </row>
   </sheetData>

--- a/data/workout_log.xlsx
+++ b/data/workout_log.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1318" uniqueCount="398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1379" uniqueCount="408">
   <si>
     <t>Timestamp</t>
   </si>
@@ -244,6 +244,9 @@
     <t>2026-03-22</t>
   </si>
   <si>
+    <t>2026-03-24 08:00:00</t>
+  </si>
+  <si>
     <t>Overhead Press</t>
   </si>
   <si>
@@ -442,6 +445,9 @@
     <t>DB Pullover</t>
   </si>
   <si>
+    <t>Tricep Ext.</t>
+  </si>
+  <si>
     <t>Warm-up. Run: 2.75km in 12:30 prior.</t>
   </si>
   <si>
@@ -1208,6 +1214,30 @@
   </si>
   <si>
     <t>Final Century Rep</t>
+  </si>
+  <si>
+    <t>Form check</t>
+  </si>
+  <si>
+    <t>CNS Ramp</t>
+  </si>
+  <si>
+    <t>Felt good</t>
+  </si>
+  <si>
+    <t>Felt decent</t>
+  </si>
+  <si>
+    <t>Grind but inevitable</t>
+  </si>
+  <si>
+    <t>Mobility work</t>
+  </si>
+  <si>
+    <t>Slight R elbow soreness</t>
+  </si>
+  <si>
+    <t>Narrower grip, less discomfort</t>
   </si>
 </sst>
 </file>
@@ -1565,7 +1595,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I481"/>
+  <dimension ref="A1:I505"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -1602,7 +1632,7 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C2">
         <v>30</v>
@@ -1617,7 +1647,7 @@
         <v>4</v>
       </c>
       <c r="G2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H2">
         <v>40</v>
@@ -1628,7 +1658,7 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C3">
         <v>30</v>
@@ -1651,7 +1681,7 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C4">
         <v>30</v>
@@ -1674,7 +1704,7 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C5">
         <v>30</v>
@@ -1697,7 +1727,7 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C6">
         <v>60</v>
@@ -1712,7 +1742,7 @@
         <v>5</v>
       </c>
       <c r="G6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H6">
         <v>76</v>
@@ -1723,7 +1753,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C7">
         <v>100</v>
@@ -1738,7 +1768,7 @@
         <v>6</v>
       </c>
       <c r="G7" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H7">
         <v>110</v>
@@ -1749,7 +1779,7 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C8">
         <v>100</v>
@@ -1772,7 +1802,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C9">
         <v>100</v>
@@ -1795,7 +1825,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C10">
         <v>32</v>
@@ -1810,7 +1840,7 @@
         <v>3</v>
       </c>
       <c r="G10" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H10">
         <v>44.8</v>
@@ -1821,7 +1851,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C11">
         <v>40</v>
@@ -1836,7 +1866,7 @@
         <v>5.5</v>
       </c>
       <c r="G11" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="H11">
         <v>50.66666666666666</v>
@@ -1847,7 +1877,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C12">
         <v>40</v>
@@ -1870,7 +1900,7 @@
         <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C13">
         <v>40</v>
@@ -1885,7 +1915,7 @@
         <v>9</v>
       </c>
       <c r="G13" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="H13">
         <v>48</v>
@@ -1896,7 +1926,7 @@
         <v>9</v>
       </c>
       <c r="B14" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C14">
         <v>20</v>
@@ -1919,7 +1949,7 @@
         <v>9</v>
       </c>
       <c r="B15" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C15">
         <v>20</v>
@@ -1942,7 +1972,7 @@
         <v>9</v>
       </c>
       <c r="B16" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C16">
         <v>20</v>
@@ -1965,7 +1995,7 @@
         <v>9</v>
       </c>
       <c r="B17" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C17">
         <v>20</v>
@@ -1980,7 +2010,7 @@
         <v>8</v>
       </c>
       <c r="G17" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H17">
         <v>26.66666666666666</v>
@@ -1991,7 +2021,7 @@
         <v>9</v>
       </c>
       <c r="B18" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C18">
         <v>20</v>
@@ -2006,7 +2036,7 @@
         <v>8</v>
       </c>
       <c r="G18" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H18">
         <v>26.66666666666666</v>
@@ -2017,7 +2047,7 @@
         <v>9</v>
       </c>
       <c r="B19" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C19">
         <v>20</v>
@@ -2032,7 +2062,7 @@
         <v>8</v>
       </c>
       <c r="G19" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H19">
         <v>25.33333333333333</v>
@@ -2043,7 +2073,7 @@
         <v>9</v>
       </c>
       <c r="B20" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C20">
         <v>20</v>
@@ -2058,7 +2088,7 @@
         <v>8</v>
       </c>
       <c r="G20" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H20">
         <v>25.33333333333333</v>
@@ -2069,7 +2099,7 @@
         <v>10</v>
       </c>
       <c r="B21" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -2084,7 +2114,7 @@
         <v>7</v>
       </c>
       <c r="G21" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="H21">
         <v>0</v>
@@ -2095,7 +2125,7 @@
         <v>10</v>
       </c>
       <c r="B22" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C22">
         <v>30</v>
@@ -2118,7 +2148,7 @@
         <v>10</v>
       </c>
       <c r="B23" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C23">
         <v>30</v>
@@ -2141,7 +2171,7 @@
         <v>10</v>
       </c>
       <c r="B24" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C24">
         <v>30</v>
@@ -2164,7 +2194,7 @@
         <v>10</v>
       </c>
       <c r="B25" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C25">
         <v>30</v>
@@ -2187,7 +2217,7 @@
         <v>10</v>
       </c>
       <c r="B26" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C26">
         <v>30</v>
@@ -2210,7 +2240,7 @@
         <v>10</v>
       </c>
       <c r="B27" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C27">
         <v>30</v>
@@ -2233,7 +2263,7 @@
         <v>10</v>
       </c>
       <c r="B28" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C28">
         <v>30</v>
@@ -2256,7 +2286,7 @@
         <v>10</v>
       </c>
       <c r="B29" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C29">
         <v>30</v>
@@ -2279,7 +2309,7 @@
         <v>10</v>
       </c>
       <c r="B30" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C30">
         <v>30</v>
@@ -2302,7 +2332,7 @@
         <v>10</v>
       </c>
       <c r="B31" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C31">
         <v>70</v>
@@ -2325,7 +2355,7 @@
         <v>10</v>
       </c>
       <c r="B32" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C32">
         <v>70</v>
@@ -2348,7 +2378,7 @@
         <v>10</v>
       </c>
       <c r="B33" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C33">
         <v>70</v>
@@ -2371,7 +2401,7 @@
         <v>10</v>
       </c>
       <c r="B34" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C34">
         <v>23</v>
@@ -2386,7 +2416,7 @@
         <v>7</v>
       </c>
       <c r="G34" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H34">
         <v>38.33333333333333</v>
@@ -2397,7 +2427,7 @@
         <v>10</v>
       </c>
       <c r="B35" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C35">
         <v>23</v>
@@ -2412,7 +2442,7 @@
         <v>7</v>
       </c>
       <c r="G35" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H35">
         <v>38.33333333333333</v>
@@ -2423,7 +2453,7 @@
         <v>10</v>
       </c>
       <c r="B36" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C36">
         <v>23</v>
@@ -2438,7 +2468,7 @@
         <v>9</v>
       </c>
       <c r="G36" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H36">
         <v>38.33333333333333</v>
@@ -2449,7 +2479,7 @@
         <v>10</v>
       </c>
       <c r="B37" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C37">
         <v>23</v>
@@ -2464,7 +2494,7 @@
         <v>10</v>
       </c>
       <c r="G37" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="H37">
         <v>32.2</v>
@@ -2475,7 +2505,7 @@
         <v>10</v>
       </c>
       <c r="B38" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C38">
         <v>20</v>
@@ -2498,7 +2528,7 @@
         <v>10</v>
       </c>
       <c r="B39" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C39">
         <v>20</v>
@@ -2521,7 +2551,7 @@
         <v>10</v>
       </c>
       <c r="B40" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C40">
         <v>20</v>
@@ -2544,7 +2574,7 @@
         <v>11</v>
       </c>
       <c r="B41" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C41">
         <v>36</v>
@@ -2559,7 +2589,7 @@
         <v>5</v>
       </c>
       <c r="G41" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H41">
         <v>48</v>
@@ -2570,7 +2600,7 @@
         <v>11</v>
       </c>
       <c r="B42" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C42">
         <v>44</v>
@@ -2585,7 +2615,7 @@
         <v>7</v>
       </c>
       <c r="G42" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="H42">
         <v>52.8</v>
@@ -2596,7 +2626,7 @@
         <v>11</v>
       </c>
       <c r="B43" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C43">
         <v>44</v>
@@ -2611,7 +2641,7 @@
         <v>7.5</v>
       </c>
       <c r="G43" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="H43">
         <v>52.8</v>
@@ -2622,7 +2652,7 @@
         <v>11</v>
       </c>
       <c r="B44" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C44">
         <v>44</v>
@@ -2637,7 +2667,7 @@
         <v>8</v>
       </c>
       <c r="G44" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="H44">
         <v>52.8</v>
@@ -2648,7 +2678,7 @@
         <v>11</v>
       </c>
       <c r="B45" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C45">
         <v>60</v>
@@ -2671,7 +2701,7 @@
         <v>11</v>
       </c>
       <c r="B46" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C46">
         <v>100</v>
@@ -2694,7 +2724,7 @@
         <v>11</v>
       </c>
       <c r="B47" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C47">
         <v>130</v>
@@ -2717,7 +2747,7 @@
         <v>11</v>
       </c>
       <c r="B48" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C48">
         <v>140</v>
@@ -2732,7 +2762,7 @@
         <v>10</v>
       </c>
       <c r="G48" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="H48">
         <v>144.6666666666667</v>
@@ -2743,7 +2773,7 @@
         <v>11</v>
       </c>
       <c r="B49" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C49">
         <v>130</v>
@@ -2766,7 +2796,7 @@
         <v>11</v>
       </c>
       <c r="B50" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C50">
         <v>100</v>
@@ -2789,7 +2819,7 @@
         <v>11</v>
       </c>
       <c r="B51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C51">
         <v>100</v>
@@ -2804,7 +2834,7 @@
         <v>9</v>
       </c>
       <c r="G51" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H51">
         <v>133.3333333333333</v>
@@ -2815,7 +2845,7 @@
         <v>11</v>
       </c>
       <c r="B52" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C52">
         <v>20</v>
@@ -2830,7 +2860,7 @@
         <v>8</v>
       </c>
       <c r="G52" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H52">
         <v>26.66666666666666</v>
@@ -2841,7 +2871,7 @@
         <v>11</v>
       </c>
       <c r="B53" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C53">
         <v>20</v>
@@ -2856,7 +2886,7 @@
         <v>9</v>
       </c>
       <c r="G53" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="H53">
         <v>26.66666666666666</v>
@@ -2867,7 +2897,7 @@
         <v>11</v>
       </c>
       <c r="B54" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C54">
         <v>30</v>
@@ -2890,7 +2920,7 @@
         <v>11</v>
       </c>
       <c r="B55" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C55">
         <v>40</v>
@@ -2913,7 +2943,7 @@
         <v>11</v>
       </c>
       <c r="B56" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C56">
         <v>40</v>
@@ -2936,7 +2966,7 @@
         <v>11</v>
       </c>
       <c r="B57" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C57">
         <v>40</v>
@@ -2959,7 +2989,7 @@
         <v>11</v>
       </c>
       <c r="B58" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C58">
         <v>45</v>
@@ -2982,7 +3012,7 @@
         <v>11</v>
       </c>
       <c r="B59" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C59">
         <v>45</v>
@@ -3005,7 +3035,7 @@
         <v>11</v>
       </c>
       <c r="B60" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C60">
         <v>50</v>
@@ -3020,7 +3050,7 @@
         <v>7.5</v>
       </c>
       <c r="G60" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="H60">
         <v>63.33333333333333</v>
@@ -3031,7 +3061,7 @@
         <v>11</v>
       </c>
       <c r="B61" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C61">
         <v>50</v>
@@ -3046,7 +3076,7 @@
         <v>7.5</v>
       </c>
       <c r="G61" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="H61">
         <v>63.33333333333333</v>
@@ -3057,7 +3087,7 @@
         <v>11</v>
       </c>
       <c r="B62" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C62">
         <v>50</v>
@@ -3072,7 +3102,7 @@
         <v>8.5</v>
       </c>
       <c r="G62" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="H62">
         <v>63.33333333333333</v>
@@ -3083,7 +3113,7 @@
         <v>11</v>
       </c>
       <c r="B63" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C63">
         <v>50</v>
@@ -3098,7 +3128,7 @@
         <v>8.5</v>
       </c>
       <c r="G63" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="H63">
         <v>63.33333333333333</v>
@@ -3109,7 +3139,7 @@
         <v>11</v>
       </c>
       <c r="B64" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C64">
         <v>50</v>
@@ -3124,7 +3154,7 @@
         <v>9</v>
       </c>
       <c r="G64" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="H64">
         <v>63.33333333333333</v>
@@ -3135,7 +3165,7 @@
         <v>11</v>
       </c>
       <c r="B65" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C65">
         <v>50</v>
@@ -3150,7 +3180,7 @@
         <v>9</v>
       </c>
       <c r="G65" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="H65">
         <v>63.33333333333333</v>
@@ -3161,7 +3191,7 @@
         <v>12</v>
       </c>
       <c r="B66" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C66">
         <v>60</v>
@@ -3184,7 +3214,7 @@
         <v>12</v>
       </c>
       <c r="B67" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C67">
         <v>100</v>
@@ -3207,7 +3237,7 @@
         <v>12</v>
       </c>
       <c r="B68" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C68">
         <v>100</v>
@@ -3230,7 +3260,7 @@
         <v>12</v>
       </c>
       <c r="B69" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C69">
         <v>60</v>
@@ -3253,7 +3283,7 @@
         <v>12</v>
       </c>
       <c r="B70" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C70">
         <v>100</v>
@@ -3276,7 +3306,7 @@
         <v>12</v>
       </c>
       <c r="B71" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C71">
         <v>80</v>
@@ -3299,7 +3329,7 @@
         <v>12</v>
       </c>
       <c r="B72" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C72">
         <v>80</v>
@@ -3322,7 +3352,7 @@
         <v>12</v>
       </c>
       <c r="B73" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C73">
         <v>20</v>
@@ -3345,7 +3375,7 @@
         <v>12</v>
       </c>
       <c r="B74" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C74">
         <v>30</v>
@@ -3368,7 +3398,7 @@
         <v>12</v>
       </c>
       <c r="B75" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C75">
         <v>35</v>
@@ -3391,7 +3421,7 @@
         <v>12</v>
       </c>
       <c r="B76" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C76">
         <v>35</v>
@@ -3406,7 +3436,7 @@
         <v>10</v>
       </c>
       <c r="G76" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="H76">
         <v>43.16666666666667</v>
@@ -3417,7 +3447,7 @@
         <v>12</v>
       </c>
       <c r="B77" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C77">
         <v>30</v>
@@ -3440,7 +3470,7 @@
         <v>12</v>
       </c>
       <c r="B78" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C78">
         <v>30</v>
@@ -3463,7 +3493,7 @@
         <v>12</v>
       </c>
       <c r="B79" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C79">
         <v>50</v>
@@ -3486,7 +3516,7 @@
         <v>12</v>
       </c>
       <c r="B80" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C80">
         <v>40</v>
@@ -3509,7 +3539,7 @@
         <v>12</v>
       </c>
       <c r="B81" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C81">
         <v>22</v>
@@ -3532,7 +3562,7 @@
         <v>12</v>
       </c>
       <c r="B82" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C82">
         <v>22</v>
@@ -3555,7 +3585,7 @@
         <v>12</v>
       </c>
       <c r="B83" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C83">
         <v>22</v>
@@ -3578,7 +3608,7 @@
         <v>13</v>
       </c>
       <c r="B84" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C84">
         <v>20</v>
@@ -3593,7 +3623,7 @@
         <v>4</v>
       </c>
       <c r="G84" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H84">
         <v>28</v>
@@ -3604,7 +3634,7 @@
         <v>13</v>
       </c>
       <c r="B85" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C85">
         <v>40</v>
@@ -3627,7 +3657,7 @@
         <v>13</v>
       </c>
       <c r="B86" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C86">
         <v>50</v>
@@ -3650,7 +3680,7 @@
         <v>13</v>
       </c>
       <c r="B87" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C87">
         <v>60</v>
@@ -3673,7 +3703,7 @@
         <v>13</v>
       </c>
       <c r="B88" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C88">
         <v>60</v>
@@ -3696,7 +3726,7 @@
         <v>13</v>
       </c>
       <c r="B89" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C89">
         <v>60</v>
@@ -3711,7 +3741,7 @@
         <v>9</v>
       </c>
       <c r="G89" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="H89">
         <v>64</v>
@@ -3722,7 +3752,7 @@
         <v>13</v>
       </c>
       <c r="B90" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C90">
         <v>40</v>
@@ -3737,7 +3767,7 @@
         <v>8</v>
       </c>
       <c r="G90" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H90">
         <v>60</v>
@@ -3748,7 +3778,7 @@
         <v>13</v>
       </c>
       <c r="B91" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C91">
         <v>16</v>
@@ -3763,7 +3793,7 @@
         <v>7</v>
       </c>
       <c r="G91" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="H91">
         <v>21.33333333333333</v>
@@ -3774,7 +3804,7 @@
         <v>13</v>
       </c>
       <c r="B92" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C92">
         <v>16</v>
@@ -3789,7 +3819,7 @@
         <v>7</v>
       </c>
       <c r="G92" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="H92">
         <v>21.33333333333333</v>
@@ -3800,7 +3830,7 @@
         <v>13</v>
       </c>
       <c r="B93" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C93">
         <v>16</v>
@@ -3815,7 +3845,7 @@
         <v>8</v>
       </c>
       <c r="G93" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="H93">
         <v>21.33333333333333</v>
@@ -3826,7 +3856,7 @@
         <v>13</v>
       </c>
       <c r="B94" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C94">
         <v>16</v>
@@ -3841,7 +3871,7 @@
         <v>8</v>
       </c>
       <c r="G94" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="H94">
         <v>21.33333333333333</v>
@@ -3852,7 +3882,7 @@
         <v>13</v>
       </c>
       <c r="B95" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C95">
         <v>16</v>
@@ -3867,7 +3897,7 @@
         <v>8.5</v>
       </c>
       <c r="G95" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="H95">
         <v>21.33333333333333</v>
@@ -3878,7 +3908,7 @@
         <v>13</v>
       </c>
       <c r="B96" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C96">
         <v>16</v>
@@ -3893,7 +3923,7 @@
         <v>8.5</v>
       </c>
       <c r="G96" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="H96">
         <v>21.33333333333333</v>
@@ -3904,7 +3934,7 @@
         <v>13</v>
       </c>
       <c r="B97" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C97">
         <v>8</v>
@@ -3927,7 +3957,7 @@
         <v>13</v>
       </c>
       <c r="B98" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C98">
         <v>8</v>
@@ -3950,7 +3980,7 @@
         <v>13</v>
       </c>
       <c r="B99" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C99">
         <v>8</v>
@@ -3973,7 +4003,7 @@
         <v>13</v>
       </c>
       <c r="B100" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C100">
         <v>58</v>
@@ -3988,7 +4018,7 @@
         <v>7</v>
       </c>
       <c r="G100" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="H100">
         <v>77.33333333333333</v>
@@ -3999,7 +4029,7 @@
         <v>13</v>
       </c>
       <c r="B101" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C101">
         <v>58</v>
@@ -4014,7 +4044,7 @@
         <v>7</v>
       </c>
       <c r="G101" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="H101">
         <v>77.33333333333333</v>
@@ -4025,7 +4055,7 @@
         <v>13</v>
       </c>
       <c r="B102" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C102">
         <v>58</v>
@@ -4048,7 +4078,7 @@
         <v>13</v>
       </c>
       <c r="B103" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C103">
         <v>58</v>
@@ -4071,7 +4101,7 @@
         <v>13</v>
       </c>
       <c r="B104" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C104">
         <v>58</v>
@@ -4094,7 +4124,7 @@
         <v>13</v>
       </c>
       <c r="B105" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C105">
         <v>58</v>
@@ -4117,7 +4147,7 @@
         <v>13</v>
       </c>
       <c r="B106" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C106">
         <v>45</v>
@@ -4140,7 +4170,7 @@
         <v>13</v>
       </c>
       <c r="B107" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C107">
         <v>45</v>
@@ -4163,7 +4193,7 @@
         <v>13</v>
       </c>
       <c r="B108" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C108">
         <v>45</v>
@@ -4186,7 +4216,7 @@
         <v>13</v>
       </c>
       <c r="B109" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C109">
         <v>20</v>
@@ -4209,7 +4239,7 @@
         <v>13</v>
       </c>
       <c r="B110" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C110">
         <v>30</v>
@@ -4224,7 +4254,7 @@
         <v>10</v>
       </c>
       <c r="G110" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H110">
         <v>34</v>
@@ -4235,7 +4265,7 @@
         <v>14</v>
       </c>
       <c r="B111" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C111">
         <v>20</v>
@@ -4250,7 +4280,7 @@
         <v>3</v>
       </c>
       <c r="G111" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="H111">
         <v>25.33333333333333</v>
@@ -4261,7 +4291,7 @@
         <v>14</v>
       </c>
       <c r="B112" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C112">
         <v>60</v>
@@ -4276,7 +4306,7 @@
         <v>5</v>
       </c>
       <c r="G112" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="H112">
         <v>66</v>
@@ -4287,7 +4317,7 @@
         <v>14</v>
       </c>
       <c r="B113" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C113">
         <v>80</v>
@@ -4302,7 +4332,7 @@
         <v>7</v>
       </c>
       <c r="G113" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="H113">
         <v>88</v>
@@ -4313,7 +4343,7 @@
         <v>14</v>
       </c>
       <c r="B114" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C114">
         <v>90</v>
@@ -4328,7 +4358,7 @@
         <v>7</v>
       </c>
       <c r="G114" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="H114">
         <v>93.00000000000001</v>
@@ -4339,7 +4369,7 @@
         <v>14</v>
       </c>
       <c r="B115" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C115">
         <v>90</v>
@@ -4354,7 +4384,7 @@
         <v>7.5</v>
       </c>
       <c r="G115" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H115">
         <v>99.00000000000001</v>
@@ -4365,7 +4395,7 @@
         <v>14</v>
       </c>
       <c r="B116" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C116">
         <v>100</v>
@@ -4380,7 +4410,7 @@
         <v>8.5</v>
       </c>
       <c r="G116" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H116">
         <v>110</v>
@@ -4391,7 +4421,7 @@
         <v>14</v>
       </c>
       <c r="B117" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C117">
         <v>110</v>
@@ -4406,7 +4436,7 @@
         <v>9</v>
       </c>
       <c r="G117" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="H117">
         <v>113.6666666666667</v>
@@ -4417,7 +4447,7 @@
         <v>14</v>
       </c>
       <c r="B118" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C118">
         <v>20</v>
@@ -4432,7 +4462,7 @@
         <v>5</v>
       </c>
       <c r="G118" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H118">
         <v>28</v>
@@ -4443,7 +4473,7 @@
         <v>14</v>
       </c>
       <c r="B119" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C119">
         <v>30</v>
@@ -4458,7 +4488,7 @@
         <v>6</v>
       </c>
       <c r="G119" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H119">
         <v>36</v>
@@ -4469,7 +4499,7 @@
         <v>14</v>
       </c>
       <c r="B120" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C120">
         <v>40</v>
@@ -4484,7 +4514,7 @@
         <v>7.5</v>
       </c>
       <c r="G120" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H120">
         <v>45.33333333333333</v>
@@ -4495,7 +4525,7 @@
         <v>14</v>
       </c>
       <c r="B121" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C121">
         <v>45</v>
@@ -4510,7 +4540,7 @@
         <v>8.5</v>
       </c>
       <c r="G121" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H121">
         <v>49.50000000000001</v>
@@ -4521,7 +4551,7 @@
         <v>14</v>
       </c>
       <c r="B122" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C122">
         <v>50</v>
@@ -4536,7 +4566,7 @@
         <v>10</v>
       </c>
       <c r="G122" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="H122">
         <v>50</v>
@@ -4547,7 +4577,7 @@
         <v>14</v>
       </c>
       <c r="B123" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C123">
         <v>70</v>
@@ -4562,7 +4592,7 @@
         <v>6</v>
       </c>
       <c r="G123" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H123">
         <v>77</v>
@@ -4573,7 +4603,7 @@
         <v>14</v>
       </c>
       <c r="B124" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C124">
         <v>120</v>
@@ -4588,7 +4618,7 @@
         <v>8.5</v>
       </c>
       <c r="G124" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="H124">
         <v>124</v>
@@ -4599,7 +4629,7 @@
         <v>14</v>
       </c>
       <c r="B125" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C125">
         <v>120</v>
@@ -4614,7 +4644,7 @@
         <v>9.5</v>
       </c>
       <c r="G125" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="H125">
         <v>124</v>
@@ -4625,7 +4655,7 @@
         <v>14</v>
       </c>
       <c r="B126" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C126">
         <v>120</v>
@@ -4640,7 +4670,7 @@
         <v>9.5</v>
       </c>
       <c r="G126" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="H126">
         <v>124</v>
@@ -4651,7 +4681,7 @@
         <v>14</v>
       </c>
       <c r="B127" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C127">
         <v>120</v>
@@ -4666,7 +4696,7 @@
         <v>9.5</v>
       </c>
       <c r="G127" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H127">
         <v>124</v>
@@ -4677,7 +4707,7 @@
         <v>14</v>
       </c>
       <c r="B128" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C128">
         <v>20</v>
@@ -4692,7 +4722,7 @@
         <v>6.5</v>
       </c>
       <c r="G128" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="H128">
         <v>26.66666666666666</v>
@@ -4703,7 +4733,7 @@
         <v>14</v>
       </c>
       <c r="B129" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C129">
         <v>20</v>
@@ -4718,7 +4748,7 @@
         <v>6.5</v>
       </c>
       <c r="G129" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="H129">
         <v>26.66666666666666</v>
@@ -4729,7 +4759,7 @@
         <v>14</v>
       </c>
       <c r="B130" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C130">
         <v>20</v>
@@ -4744,7 +4774,7 @@
         <v>8</v>
       </c>
       <c r="G130" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="H130">
         <v>26.66666666666666</v>
@@ -4755,7 +4785,7 @@
         <v>14</v>
       </c>
       <c r="B131" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C131">
         <v>20</v>
@@ -4770,7 +4800,7 @@
         <v>8</v>
       </c>
       <c r="G131" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="H131">
         <v>26.66666666666666</v>
@@ -4781,7 +4811,7 @@
         <v>14</v>
       </c>
       <c r="B132" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C132">
         <v>20</v>
@@ -4796,7 +4826,7 @@
         <v>8.5</v>
       </c>
       <c r="G132" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="H132">
         <v>26.66666666666666</v>
@@ -4807,7 +4837,7 @@
         <v>14</v>
       </c>
       <c r="B133" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C133">
         <v>20</v>
@@ -4822,7 +4852,7 @@
         <v>8.5</v>
       </c>
       <c r="G133" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="H133">
         <v>26.66666666666666</v>
@@ -4833,7 +4863,7 @@
         <v>15</v>
       </c>
       <c r="B134" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C134">
         <v>20</v>
@@ -4848,7 +4878,7 @@
         <v>3</v>
       </c>
       <c r="G134" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="H134">
         <v>25.33333333333333</v>
@@ -4859,7 +4889,7 @@
         <v>15</v>
       </c>
       <c r="B135" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C135">
         <v>60</v>
@@ -4874,7 +4904,7 @@
         <v>6</v>
       </c>
       <c r="G135" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="H135">
         <v>72</v>
@@ -4885,7 +4915,7 @@
         <v>15</v>
       </c>
       <c r="B136" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C136">
         <v>80</v>
@@ -4900,7 +4930,7 @@
         <v>7</v>
       </c>
       <c r="G136" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="H136">
         <v>88</v>
@@ -4911,7 +4941,7 @@
         <v>15</v>
       </c>
       <c r="B137" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C137">
         <v>100</v>
@@ -4926,7 +4956,7 @@
         <v>7</v>
       </c>
       <c r="G137" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="H137">
         <v>103.3333333333333</v>
@@ -4937,7 +4967,7 @@
         <v>15</v>
       </c>
       <c r="B138" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C138">
         <v>70</v>
@@ -4952,7 +4982,7 @@
         <v>8</v>
       </c>
       <c r="G138" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H138">
         <v>98</v>
@@ -4963,7 +4993,7 @@
         <v>15</v>
       </c>
       <c r="B139" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C139">
         <v>80</v>
@@ -4978,7 +5008,7 @@
         <v>8.5</v>
       </c>
       <c r="G139" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H139">
         <v>101.3333333333333</v>
@@ -4989,7 +5019,7 @@
         <v>15</v>
       </c>
       <c r="B140" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C140">
         <v>20</v>
@@ -5004,7 +5034,7 @@
         <v>5</v>
       </c>
       <c r="G140" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="H140">
         <v>28</v>
@@ -5015,7 +5045,7 @@
         <v>15</v>
       </c>
       <c r="B141" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C141">
         <v>30</v>
@@ -5030,7 +5060,7 @@
         <v>7</v>
       </c>
       <c r="G141" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="H141">
         <v>38</v>
@@ -5041,7 +5071,7 @@
         <v>15</v>
       </c>
       <c r="B142" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C142">
         <v>40</v>
@@ -5056,7 +5086,7 @@
         <v>8</v>
       </c>
       <c r="G142" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="H142">
         <v>48</v>
@@ -5067,7 +5097,7 @@
         <v>15</v>
       </c>
       <c r="B143" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C143">
         <v>40</v>
@@ -5082,7 +5112,7 @@
         <v>9</v>
       </c>
       <c r="G143" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="H143">
         <v>48</v>
@@ -5093,7 +5123,7 @@
         <v>15</v>
       </c>
       <c r="B144" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C144">
         <v>30</v>
@@ -5108,7 +5138,7 @@
         <v>9</v>
       </c>
       <c r="G144" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="H144">
         <v>42</v>
@@ -5119,7 +5149,7 @@
         <v>15</v>
       </c>
       <c r="B145" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C145">
         <v>30</v>
@@ -5134,7 +5164,7 @@
         <v>7</v>
       </c>
       <c r="G145" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="H145">
         <v>45</v>
@@ -5145,7 +5175,7 @@
         <v>15</v>
       </c>
       <c r="B146" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C146">
         <v>50</v>
@@ -5160,7 +5190,7 @@
         <v>7.5</v>
       </c>
       <c r="G146" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="H146">
         <v>63.33333333333333</v>
@@ -5171,7 +5201,7 @@
         <v>15</v>
       </c>
       <c r="B147" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C147">
         <v>50</v>
@@ -5186,7 +5216,7 @@
         <v>8</v>
       </c>
       <c r="G147" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="H147">
         <v>63.33333333333333</v>
@@ -5197,7 +5227,7 @@
         <v>15</v>
       </c>
       <c r="B148" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C148">
         <v>50</v>
@@ -5212,7 +5242,7 @@
         <v>8.5</v>
       </c>
       <c r="G148" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="H148">
         <v>63.33333333333333</v>
@@ -5223,7 +5253,7 @@
         <v>15</v>
       </c>
       <c r="B149" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C149">
         <v>50</v>
@@ -5238,7 +5268,7 @@
         <v>9.5</v>
       </c>
       <c r="G149" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="H149">
         <v>63.33333333333333</v>
@@ -5249,7 +5279,7 @@
         <v>15</v>
       </c>
       <c r="B150" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C150">
         <v>40</v>
@@ -5264,7 +5294,7 @@
         <v>8</v>
       </c>
       <c r="G150" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="H150">
         <v>56</v>
@@ -5275,7 +5305,7 @@
         <v>15</v>
       </c>
       <c r="B151" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C151">
         <v>70</v>
@@ -5290,7 +5320,7 @@
         <v>6</v>
       </c>
       <c r="G151" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="H151">
         <v>84</v>
@@ -5301,7 +5331,7 @@
         <v>15</v>
       </c>
       <c r="B152" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C152">
         <v>120</v>
@@ -5316,7 +5346,7 @@
         <v>6</v>
       </c>
       <c r="G152" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="H152">
         <v>124</v>
@@ -5327,7 +5357,7 @@
         <v>15</v>
       </c>
       <c r="B153" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C153">
         <v>120</v>
@@ -5342,7 +5372,7 @@
         <v>8</v>
       </c>
       <c r="G153" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="H153">
         <v>140</v>
@@ -5353,7 +5383,7 @@
         <v>15</v>
       </c>
       <c r="B154" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C154">
         <v>130</v>
@@ -5368,7 +5398,7 @@
         <v>8.5</v>
       </c>
       <c r="G154" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="H154">
         <v>151.6666666666667</v>
@@ -5379,7 +5409,7 @@
         <v>15</v>
       </c>
       <c r="B155" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C155">
         <v>130</v>
@@ -5394,7 +5424,7 @@
         <v>9</v>
       </c>
       <c r="G155" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="H155">
         <v>151.6666666666667</v>
@@ -5405,7 +5435,7 @@
         <v>16</v>
       </c>
       <c r="B156" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C156">
         <v>20</v>
@@ -5420,7 +5450,7 @@
         <v>4</v>
       </c>
       <c r="G156" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="H156">
         <v>28</v>
@@ -5431,7 +5461,7 @@
         <v>16</v>
       </c>
       <c r="B157" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C157">
         <v>40</v>
@@ -5454,7 +5484,7 @@
         <v>16</v>
       </c>
       <c r="B158" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C158">
         <v>60</v>
@@ -5469,7 +5499,7 @@
         <v>6.5</v>
       </c>
       <c r="G158" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H158">
         <v>62.00000000000001</v>
@@ -5480,7 +5510,7 @@
         <v>16</v>
       </c>
       <c r="B159" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C159">
         <v>70</v>
@@ -5495,7 +5525,7 @@
         <v>8.5</v>
       </c>
       <c r="G159" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="H159">
         <v>72.33333333333334</v>
@@ -5506,7 +5536,7 @@
         <v>16</v>
       </c>
       <c r="B160" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C160">
         <v>65</v>
@@ -5521,7 +5551,7 @@
         <v>8</v>
       </c>
       <c r="G160" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="H160">
         <v>67.16666666666667</v>
@@ -5532,7 +5562,7 @@
         <v>16</v>
       </c>
       <c r="B161" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C161">
         <v>60</v>
@@ -5555,7 +5585,7 @@
         <v>16</v>
       </c>
       <c r="B162" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C162">
         <v>60</v>
@@ -5570,7 +5600,7 @@
         <v>9</v>
       </c>
       <c r="G162" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H162">
         <v>66</v>
@@ -5581,7 +5611,7 @@
         <v>16</v>
       </c>
       <c r="B163" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C163">
         <v>45</v>
@@ -5596,7 +5626,7 @@
         <v>8</v>
       </c>
       <c r="G163" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="H163">
         <v>62.99999999999999</v>
@@ -5607,7 +5637,7 @@
         <v>16</v>
       </c>
       <c r="B164" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C164">
         <v>45</v>
@@ -5630,7 +5660,7 @@
         <v>16</v>
       </c>
       <c r="B165" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C165">
         <v>20</v>
@@ -5645,7 +5675,7 @@
         <v>7</v>
       </c>
       <c r="G165" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="H165">
         <v>26.66666666666666</v>
@@ -5656,7 +5686,7 @@
         <v>16</v>
       </c>
       <c r="B166" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C166">
         <v>20</v>
@@ -5671,7 +5701,7 @@
         <v>6</v>
       </c>
       <c r="G166" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="H166">
         <v>28</v>
@@ -5682,7 +5712,7 @@
         <v>16</v>
       </c>
       <c r="B167" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C167">
         <v>20</v>
@@ -5697,7 +5727,7 @@
         <v>7</v>
       </c>
       <c r="G167" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="H167">
         <v>28</v>
@@ -5708,7 +5738,7 @@
         <v>16</v>
       </c>
       <c r="B168" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C168">
         <v>20</v>
@@ -5723,7 +5753,7 @@
         <v>7</v>
       </c>
       <c r="G168" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="H168">
         <v>30</v>
@@ -5734,7 +5764,7 @@
         <v>16</v>
       </c>
       <c r="B169" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C169">
         <v>22.5</v>
@@ -5749,7 +5779,7 @@
         <v>7.5</v>
       </c>
       <c r="G169" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H169">
         <v>30</v>
@@ -5760,7 +5790,7 @@
         <v>16</v>
       </c>
       <c r="B170" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C170">
         <v>22.5</v>
@@ -5775,7 +5805,7 @@
         <v>7</v>
       </c>
       <c r="G170" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="H170">
         <v>31.5</v>
@@ -5786,7 +5816,7 @@
         <v>16</v>
       </c>
       <c r="B171" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C171">
         <v>25</v>
@@ -5801,7 +5831,7 @@
         <v>8</v>
       </c>
       <c r="G171" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="H171">
         <v>31.66666666666666</v>
@@ -5812,7 +5842,7 @@
         <v>16</v>
       </c>
       <c r="B172" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C172">
         <v>25</v>
@@ -5827,7 +5857,7 @@
         <v>7.5</v>
       </c>
       <c r="G172" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="H172">
         <v>35</v>
@@ -5838,7 +5868,7 @@
         <v>16</v>
       </c>
       <c r="B173" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C173">
         <v>25</v>
@@ -5853,7 +5883,7 @@
         <v>8</v>
       </c>
       <c r="G173" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="H173">
         <v>31.66666666666666</v>
@@ -5864,7 +5894,7 @@
         <v>16</v>
       </c>
       <c r="B174" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C174">
         <v>25</v>
@@ -5879,7 +5909,7 @@
         <v>8</v>
       </c>
       <c r="G174" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="H174">
         <v>37.5</v>
@@ -5890,7 +5920,7 @@
         <v>16</v>
       </c>
       <c r="B175" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C175">
         <v>40</v>
@@ -5905,7 +5935,7 @@
         <v>7.5</v>
       </c>
       <c r="G175" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="H175">
         <v>50.66666666666666</v>
@@ -5916,7 +5946,7 @@
         <v>16</v>
       </c>
       <c r="B176" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C176">
         <v>40</v>
@@ -5931,7 +5961,7 @@
         <v>8.5</v>
       </c>
       <c r="G176" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="H176">
         <v>50.66666666666666</v>
@@ -5942,7 +5972,7 @@
         <v>16</v>
       </c>
       <c r="B177" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C177">
         <v>40</v>
@@ -5957,7 +5987,7 @@
         <v>9</v>
       </c>
       <c r="G177" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="H177">
         <v>48</v>
@@ -5968,7 +5998,7 @@
         <v>16</v>
       </c>
       <c r="B178" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C178">
         <v>22</v>
@@ -5983,7 +6013,7 @@
         <v>7</v>
       </c>
       <c r="G178" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="H178">
         <v>27.86666666666667</v>
@@ -5994,7 +6024,7 @@
         <v>16</v>
       </c>
       <c r="B179" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C179">
         <v>22</v>
@@ -6017,7 +6047,7 @@
         <v>16</v>
       </c>
       <c r="B180" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C180">
         <v>22</v>
@@ -6032,7 +6062,7 @@
         <v>8.5</v>
       </c>
       <c r="G180" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="H180">
         <v>27.86666666666667</v>
@@ -6043,7 +6073,7 @@
         <v>17</v>
       </c>
       <c r="B181" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C181">
         <v>20</v>
@@ -6066,7 +6096,7 @@
         <v>17</v>
       </c>
       <c r="B182" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C182">
         <v>22</v>
@@ -6089,7 +6119,7 @@
         <v>17</v>
       </c>
       <c r="B183" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C183">
         <v>20</v>
@@ -6104,7 +6134,7 @@
         <v>4</v>
       </c>
       <c r="G183" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="H183">
         <v>25.33333333333333</v>
@@ -6115,7 +6145,7 @@
         <v>17</v>
       </c>
       <c r="B184" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C184">
         <v>60</v>
@@ -6138,7 +6168,7 @@
         <v>17</v>
       </c>
       <c r="B185" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C185">
         <v>80</v>
@@ -6161,7 +6191,7 @@
         <v>17</v>
       </c>
       <c r="B186" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C186">
         <v>100</v>
@@ -6184,7 +6214,7 @@
         <v>17</v>
       </c>
       <c r="B187" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C187">
         <v>110</v>
@@ -6207,7 +6237,7 @@
         <v>17</v>
       </c>
       <c r="B188" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C188">
         <v>120</v>
@@ -6222,7 +6252,7 @@
         <v>8.5</v>
       </c>
       <c r="G188" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="H188">
         <v>124</v>
@@ -6233,7 +6263,7 @@
         <v>17</v>
       </c>
       <c r="B189" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C189">
         <v>80</v>
@@ -6248,7 +6278,7 @@
         <v>7.5</v>
       </c>
       <c r="G189" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="H189">
         <v>112</v>
@@ -6259,7 +6289,7 @@
         <v>17</v>
       </c>
       <c r="B190" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C190">
         <v>-30</v>
@@ -6274,7 +6304,7 @@
         <v>6</v>
       </c>
       <c r="G190" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="H190">
         <v>-38</v>
@@ -6285,7 +6315,7 @@
         <v>17</v>
       </c>
       <c r="B191" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C191">
         <v>-30</v>
@@ -6300,7 +6330,7 @@
         <v>6</v>
       </c>
       <c r="G191" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="H191">
         <v>-38</v>
@@ -6311,7 +6341,7 @@
         <v>17</v>
       </c>
       <c r="B192" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C192">
         <v>-25</v>
@@ -6326,7 +6356,7 @@
         <v>7.5</v>
       </c>
       <c r="G192" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="H192">
         <v>-33.33333333333333</v>
@@ -6337,7 +6367,7 @@
         <v>17</v>
       </c>
       <c r="B193" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C193">
         <v>-25</v>
@@ -6352,7 +6382,7 @@
         <v>7.5</v>
       </c>
       <c r="G193" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="H193">
         <v>-33.33333333333333</v>
@@ -6363,7 +6393,7 @@
         <v>17</v>
       </c>
       <c r="B194" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C194">
         <v>-20</v>
@@ -6378,7 +6408,7 @@
         <v>8</v>
       </c>
       <c r="G194" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="H194">
         <v>-25.33333333333333</v>
@@ -6389,7 +6419,7 @@
         <v>17</v>
       </c>
       <c r="B195" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C195">
         <v>-20</v>
@@ -6404,7 +6434,7 @@
         <v>8</v>
       </c>
       <c r="G195" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="H195">
         <v>-25.33333333333333</v>
@@ -6415,7 +6445,7 @@
         <v>17</v>
       </c>
       <c r="B196" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C196">
         <v>35</v>
@@ -6430,7 +6460,7 @@
         <v>7</v>
       </c>
       <c r="G196" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H196">
         <v>52.5</v>
@@ -6441,7 +6471,7 @@
         <v>17</v>
       </c>
       <c r="B197" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C197">
         <v>25</v>
@@ -6456,7 +6486,7 @@
         <v>7</v>
       </c>
       <c r="G197" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H197">
         <v>37.5</v>
@@ -6467,7 +6497,7 @@
         <v>17</v>
       </c>
       <c r="B198" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C198">
         <v>35</v>
@@ -6482,7 +6512,7 @@
         <v>7</v>
       </c>
       <c r="G198" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="H198">
         <v>52.5</v>
@@ -6493,7 +6523,7 @@
         <v>17</v>
       </c>
       <c r="B199" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C199">
         <v>25</v>
@@ -6508,7 +6538,7 @@
         <v>7</v>
       </c>
       <c r="G199" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="H199">
         <v>37.5</v>
@@ -6519,7 +6549,7 @@
         <v>18</v>
       </c>
       <c r="B200" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C200">
         <v>70</v>
@@ -6534,7 +6564,7 @@
         <v>6</v>
       </c>
       <c r="G200" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="H200">
         <v>84</v>
@@ -6545,7 +6575,7 @@
         <v>18</v>
       </c>
       <c r="B201" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C201">
         <v>90</v>
@@ -6568,7 +6598,7 @@
         <v>18</v>
       </c>
       <c r="B202" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C202">
         <v>120</v>
@@ -6591,7 +6621,7 @@
         <v>18</v>
       </c>
       <c r="B203" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C203">
         <v>120</v>
@@ -6614,7 +6644,7 @@
         <v>18</v>
       </c>
       <c r="B204" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C204">
         <v>120</v>
@@ -6637,7 +6667,7 @@
         <v>18</v>
       </c>
       <c r="B205" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C205">
         <v>120</v>
@@ -6660,7 +6690,7 @@
         <v>18</v>
       </c>
       <c r="B206" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C206">
         <v>120</v>
@@ -6683,7 +6713,7 @@
         <v>18</v>
       </c>
       <c r="B207" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C207">
         <v>20</v>
@@ -6698,7 +6728,7 @@
         <v>6</v>
       </c>
       <c r="G207" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="H207">
         <v>28</v>
@@ -6709,7 +6739,7 @@
         <v>18</v>
       </c>
       <c r="B208" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C208">
         <v>30</v>
@@ -6732,7 +6762,7 @@
         <v>18</v>
       </c>
       <c r="B209" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C209">
         <v>35</v>
@@ -6755,7 +6785,7 @@
         <v>18</v>
       </c>
       <c r="B210" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C210">
         <v>35</v>
@@ -6778,7 +6808,7 @@
         <v>18</v>
       </c>
       <c r="B211" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C211">
         <v>35</v>
@@ -6801,7 +6831,7 @@
         <v>18</v>
       </c>
       <c r="B212" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C212">
         <v>22</v>
@@ -6816,7 +6846,7 @@
         <v>7.5</v>
       </c>
       <c r="G212" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H212">
         <v>27.86666666666667</v>
@@ -6827,7 +6857,7 @@
         <v>18</v>
       </c>
       <c r="B213" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C213">
         <v>22</v>
@@ -6842,7 +6872,7 @@
         <v>7.5</v>
       </c>
       <c r="G213" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H213">
         <v>30.8</v>
@@ -6853,7 +6883,7 @@
         <v>18</v>
       </c>
       <c r="B214" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C214">
         <v>22</v>
@@ -6868,7 +6898,7 @@
         <v>8</v>
       </c>
       <c r="G214" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H214">
         <v>27.86666666666667</v>
@@ -6879,7 +6909,7 @@
         <v>18</v>
       </c>
       <c r="B215" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C215">
         <v>22</v>
@@ -6894,7 +6924,7 @@
         <v>8</v>
       </c>
       <c r="G215" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H215">
         <v>30.8</v>
@@ -6905,7 +6935,7 @@
         <v>18</v>
       </c>
       <c r="B216" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C216">
         <v>22</v>
@@ -6920,7 +6950,7 @@
         <v>8.5</v>
       </c>
       <c r="G216" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H216">
         <v>27.86666666666667</v>
@@ -6931,7 +6961,7 @@
         <v>18</v>
       </c>
       <c r="B217" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C217">
         <v>22</v>
@@ -6946,7 +6976,7 @@
         <v>8</v>
       </c>
       <c r="G217" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H217">
         <v>30.8</v>
@@ -6957,7 +6987,7 @@
         <v>18</v>
       </c>
       <c r="B218" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C218">
         <v>25</v>
@@ -6972,7 +7002,7 @@
         <v>8</v>
       </c>
       <c r="G218" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="H218">
         <v>31.66666666666666</v>
@@ -6983,7 +7013,7 @@
         <v>18</v>
       </c>
       <c r="B219" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C219">
         <v>25</v>
@@ -6998,7 +7028,7 @@
         <v>6.5</v>
       </c>
       <c r="G219" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="H219">
         <v>31.66666666666666</v>
@@ -7009,7 +7039,7 @@
         <v>18</v>
       </c>
       <c r="B220" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C220">
         <v>25</v>
@@ -7024,7 +7054,7 @@
         <v>8</v>
       </c>
       <c r="G220" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="H220">
         <v>31.66666666666666</v>
@@ -7035,7 +7065,7 @@
         <v>18</v>
       </c>
       <c r="B221" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C221">
         <v>25</v>
@@ -7050,7 +7080,7 @@
         <v>7.5</v>
       </c>
       <c r="G221" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="H221">
         <v>31.66666666666666</v>
@@ -7061,7 +7091,7 @@
         <v>18</v>
       </c>
       <c r="B222" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C222">
         <v>25</v>
@@ -7076,7 +7106,7 @@
         <v>9</v>
       </c>
       <c r="G222" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="H222">
         <v>31.66666666666666</v>
@@ -7087,7 +7117,7 @@
         <v>18</v>
       </c>
       <c r="B223" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C223">
         <v>25</v>
@@ -7102,7 +7132,7 @@
         <v>9</v>
       </c>
       <c r="G223" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="H223">
         <v>31.66666666666666</v>
@@ -7113,7 +7143,7 @@
         <v>19</v>
       </c>
       <c r="B224" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C224">
         <v>70</v>
@@ -7128,7 +7158,7 @@
         <v>6.5</v>
       </c>
       <c r="G224" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="H224">
         <v>84</v>
@@ -7139,7 +7169,7 @@
         <v>19</v>
       </c>
       <c r="B225" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C225">
         <v>85</v>
@@ -7154,7 +7184,7 @@
         <v>8</v>
       </c>
       <c r="G225" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="H225">
         <v>119</v>
@@ -7165,7 +7195,7 @@
         <v>19</v>
       </c>
       <c r="B226" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C226">
         <v>85</v>
@@ -7180,7 +7210,7 @@
         <v>9</v>
       </c>
       <c r="G226" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H226">
         <v>119</v>
@@ -7191,7 +7221,7 @@
         <v>19</v>
       </c>
       <c r="B227" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C227">
         <v>85</v>
@@ -7206,7 +7236,7 @@
         <v>10</v>
       </c>
       <c r="G227" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H227">
         <v>113.3333333333333</v>
@@ -7217,7 +7247,7 @@
         <v>19</v>
       </c>
       <c r="B228" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C228">
         <v>30</v>
@@ -7232,7 +7262,7 @@
         <v>6</v>
       </c>
       <c r="G228" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="H228">
         <v>36</v>
@@ -7243,7 +7273,7 @@
         <v>19</v>
       </c>
       <c r="B229" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C229">
         <v>30</v>
@@ -7258,7 +7288,7 @@
         <v>6</v>
       </c>
       <c r="G229" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="H229">
         <v>38</v>
@@ -7269,7 +7299,7 @@
         <v>19</v>
       </c>
       <c r="B230" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C230">
         <v>40</v>
@@ -7284,7 +7314,7 @@
         <v>8</v>
       </c>
       <c r="G230" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="H230">
         <v>50.66666666666666</v>
@@ -7295,7 +7325,7 @@
         <v>19</v>
       </c>
       <c r="B231" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C231">
         <v>40</v>
@@ -7310,7 +7340,7 @@
         <v>9</v>
       </c>
       <c r="G231" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H231">
         <v>50.66666666666666</v>
@@ -7321,7 +7351,7 @@
         <v>19</v>
       </c>
       <c r="B232" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C232">
         <v>40</v>
@@ -7336,7 +7366,7 @@
         <v>10</v>
       </c>
       <c r="G232" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="H232">
         <v>49.33333333333334</v>
@@ -7347,7 +7377,7 @@
         <v>19</v>
       </c>
       <c r="B233" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C233">
         <v>40</v>
@@ -7362,7 +7392,7 @@
         <v>6.5</v>
       </c>
       <c r="G233" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H233">
         <v>56</v>
@@ -7373,7 +7403,7 @@
         <v>19</v>
       </c>
       <c r="B234" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C234">
         <v>40</v>
@@ -7388,7 +7418,7 @@
         <v>6.5</v>
       </c>
       <c r="G234" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H234">
         <v>56</v>
@@ -7399,7 +7429,7 @@
         <v>19</v>
       </c>
       <c r="B235" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C235">
         <v>40</v>
@@ -7414,7 +7444,7 @@
         <v>7.5</v>
       </c>
       <c r="G235" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="H235">
         <v>56</v>
@@ -7425,7 +7455,7 @@
         <v>19</v>
       </c>
       <c r="B236" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C236">
         <v>40</v>
@@ -7440,7 +7470,7 @@
         <v>9</v>
       </c>
       <c r="G236" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="H236">
         <v>56</v>
@@ -7451,7 +7481,7 @@
         <v>19</v>
       </c>
       <c r="B237" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C237">
         <v>60</v>
@@ -7466,7 +7496,7 @@
         <v>8</v>
       </c>
       <c r="G237" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="H237">
         <v>80</v>
@@ -7477,7 +7507,7 @@
         <v>19</v>
       </c>
       <c r="B238" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C238">
         <v>60</v>
@@ -7492,7 +7522,7 @@
         <v>7</v>
       </c>
       <c r="G238" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="H238">
         <v>80</v>
@@ -7503,7 +7533,7 @@
         <v>19</v>
       </c>
       <c r="B239" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C239">
         <v>60</v>
@@ -7518,7 +7548,7 @@
         <v>8.5</v>
       </c>
       <c r="G239" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="H239">
         <v>80</v>
@@ -7529,7 +7559,7 @@
         <v>19</v>
       </c>
       <c r="B240" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C240">
         <v>60</v>
@@ -7544,7 +7574,7 @@
         <v>8</v>
       </c>
       <c r="G240" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="H240">
         <v>80</v>
@@ -7555,7 +7585,7 @@
         <v>19</v>
       </c>
       <c r="B241" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C241">
         <v>60</v>
@@ -7570,7 +7600,7 @@
         <v>9</v>
       </c>
       <c r="G241" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H241">
         <v>80</v>
@@ -7581,7 +7611,7 @@
         <v>19</v>
       </c>
       <c r="B242" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C242">
         <v>60</v>
@@ -7596,7 +7626,7 @@
         <v>9</v>
       </c>
       <c r="G242" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="H242">
         <v>80</v>
@@ -7607,7 +7637,7 @@
         <v>20</v>
       </c>
       <c r="B243" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C243">
         <v>60</v>
@@ -7622,7 +7652,7 @@
         <v>4</v>
       </c>
       <c r="G243" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="H243">
         <v>76</v>
@@ -7633,7 +7663,7 @@
         <v>20</v>
       </c>
       <c r="B244" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C244">
         <v>100</v>
@@ -7648,7 +7678,7 @@
         <v>6</v>
       </c>
       <c r="G244" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="H244">
         <v>116.6666666666667</v>
@@ -7659,7 +7689,7 @@
         <v>20</v>
       </c>
       <c r="B245" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C245">
         <v>130</v>
@@ -7674,7 +7704,7 @@
         <v>7</v>
       </c>
       <c r="G245" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="H245">
         <v>134.3333333333333</v>
@@ -7685,7 +7715,7 @@
         <v>20</v>
       </c>
       <c r="B246" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C246">
         <v>150</v>
@@ -7700,7 +7730,7 @@
         <v>8.5</v>
       </c>
       <c r="G246" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="H246">
         <v>155</v>
@@ -7711,7 +7741,7 @@
         <v>20</v>
       </c>
       <c r="B247" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C247">
         <v>120</v>
@@ -7726,7 +7756,7 @@
         <v>7.5</v>
       </c>
       <c r="G247" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="H247">
         <v>140</v>
@@ -7737,7 +7767,7 @@
         <v>20</v>
       </c>
       <c r="B248" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C248">
         <v>120</v>
@@ -7752,7 +7782,7 @@
         <v>7.5</v>
       </c>
       <c r="G248" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="H248">
         <v>140</v>
@@ -7763,7 +7793,7 @@
         <v>20</v>
       </c>
       <c r="B249" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C249">
         <v>120</v>
@@ -7778,7 +7808,7 @@
         <v>8</v>
       </c>
       <c r="G249" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="H249">
         <v>140</v>
@@ -7789,7 +7819,7 @@
         <v>20</v>
       </c>
       <c r="B250" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C250">
         <v>120</v>
@@ -7804,7 +7834,7 @@
         <v>8.5</v>
       </c>
       <c r="G250" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="H250">
         <v>140</v>
@@ -7815,7 +7845,7 @@
         <v>20</v>
       </c>
       <c r="B251" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C251">
         <v>120</v>
@@ -7830,7 +7860,7 @@
         <v>9</v>
       </c>
       <c r="G251" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="H251">
         <v>140</v>
@@ -7841,7 +7871,7 @@
         <v>20</v>
       </c>
       <c r="B252" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C252">
         <v>40</v>
@@ -7856,7 +7886,7 @@
         <v>5</v>
       </c>
       <c r="G252" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="H252">
         <v>50.66666666666666</v>
@@ -7867,7 +7897,7 @@
         <v>20</v>
       </c>
       <c r="B253" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C253">
         <v>50</v>
@@ -7882,7 +7912,7 @@
         <v>6</v>
       </c>
       <c r="G253" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="H253">
         <v>58.33333333333334</v>
@@ -7893,7 +7923,7 @@
         <v>20</v>
       </c>
       <c r="B254" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C254">
         <v>60</v>
@@ -7908,7 +7938,7 @@
         <v>7</v>
       </c>
       <c r="G254" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="H254">
         <v>70</v>
@@ -7919,7 +7949,7 @@
         <v>20</v>
       </c>
       <c r="B255" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C255">
         <v>60</v>
@@ -7934,7 +7964,7 @@
         <v>8</v>
       </c>
       <c r="G255" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H255">
         <v>70</v>
@@ -7945,7 +7975,7 @@
         <v>20</v>
       </c>
       <c r="B256" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C256">
         <v>60</v>
@@ -7960,7 +7990,7 @@
         <v>8.5</v>
       </c>
       <c r="G256" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="H256">
         <v>70</v>
@@ -7971,7 +8001,7 @@
         <v>20</v>
       </c>
       <c r="B257" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C257">
         <v>60</v>
@@ -7986,7 +8016,7 @@
         <v>8.5</v>
       </c>
       <c r="G257" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="H257">
         <v>70</v>
@@ -7997,7 +8027,7 @@
         <v>20</v>
       </c>
       <c r="B258" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C258">
         <v>60</v>
@@ -8012,7 +8042,7 @@
         <v>8</v>
       </c>
       <c r="G258" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="H258">
         <v>70</v>
@@ -8023,7 +8053,7 @@
         <v>20</v>
       </c>
       <c r="B259" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C259">
         <v>40</v>
@@ -8038,7 +8068,7 @@
         <v>5</v>
       </c>
       <c r="G259" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="H259">
         <v>53.33333333333333</v>
@@ -8049,7 +8079,7 @@
         <v>20</v>
       </c>
       <c r="B260" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C260">
         <v>50</v>
@@ -8064,7 +8094,7 @@
         <v>7</v>
       </c>
       <c r="G260" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="H260">
         <v>63.33333333333333</v>
@@ -8075,7 +8105,7 @@
         <v>20</v>
       </c>
       <c r="B261" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C261">
         <v>50</v>
@@ -8090,7 +8120,7 @@
         <v>7</v>
       </c>
       <c r="G261" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="H261">
         <v>63.33333333333333</v>
@@ -8101,7 +8131,7 @@
         <v>20</v>
       </c>
       <c r="B262" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C262">
         <v>50</v>
@@ -8116,7 +8146,7 @@
         <v>7.5</v>
       </c>
       <c r="G262" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="H262">
         <v>63.33333333333333</v>
@@ -8127,7 +8157,7 @@
         <v>20</v>
       </c>
       <c r="B263" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C263">
         <v>50</v>
@@ -8142,7 +8172,7 @@
         <v>8</v>
       </c>
       <c r="G263" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="H263">
         <v>66.66666666666666</v>
@@ -8153,7 +8183,7 @@
         <v>20</v>
       </c>
       <c r="B264" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C264">
         <v>20</v>
@@ -8168,7 +8198,7 @@
         <v>7</v>
       </c>
       <c r="G264" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="H264">
         <v>26.66666666666666</v>
@@ -8179,7 +8209,7 @@
         <v>20</v>
       </c>
       <c r="B265" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C265">
         <v>20</v>
@@ -8194,7 +8224,7 @@
         <v>7</v>
       </c>
       <c r="G265" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="H265">
         <v>28</v>
@@ -8205,7 +8235,7 @@
         <v>20</v>
       </c>
       <c r="B266" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C266">
         <v>25</v>
@@ -8220,7 +8250,7 @@
         <v>8.5</v>
       </c>
       <c r="G266" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="H266">
         <v>31.66666666666666</v>
@@ -8231,7 +8261,7 @@
         <v>20</v>
       </c>
       <c r="B267" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C267">
         <v>25</v>
@@ -8246,7 +8276,7 @@
         <v>7.5</v>
       </c>
       <c r="G267" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="H267">
         <v>33.33333333333333</v>
@@ -8257,7 +8287,7 @@
         <v>20</v>
       </c>
       <c r="B268" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C268">
         <v>25</v>
@@ -8272,7 +8302,7 @@
         <v>8.5</v>
       </c>
       <c r="G268" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="H268">
         <v>31.66666666666666</v>
@@ -8283,7 +8313,7 @@
         <v>20</v>
       </c>
       <c r="B269" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C269">
         <v>25</v>
@@ -8298,7 +8328,7 @@
         <v>8</v>
       </c>
       <c r="G269" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="H269">
         <v>35</v>
@@ -8309,7 +8339,7 @@
         <v>20</v>
       </c>
       <c r="B270" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C270">
         <v>25</v>
@@ -8324,7 +8354,7 @@
         <v>9</v>
       </c>
       <c r="G270" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="H270">
         <v>31.66666666666666</v>
@@ -8335,7 +8365,7 @@
         <v>20</v>
       </c>
       <c r="B271" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C271">
         <v>25</v>
@@ -8350,7 +8380,7 @@
         <v>9</v>
       </c>
       <c r="G271" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="H271">
         <v>37.5</v>
@@ -8361,7 +8391,7 @@
         <v>21</v>
       </c>
       <c r="B272" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C272">
         <v>20</v>
@@ -8384,7 +8414,7 @@
         <v>21</v>
       </c>
       <c r="B273" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C273">
         <v>60</v>
@@ -8407,7 +8437,7 @@
         <v>21</v>
       </c>
       <c r="B274" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C274">
         <v>100</v>
@@ -8430,7 +8460,7 @@
         <v>21</v>
       </c>
       <c r="B275" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C275">
         <v>100</v>
@@ -8453,7 +8483,7 @@
         <v>21</v>
       </c>
       <c r="B276" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C276">
         <v>60</v>
@@ -8476,7 +8506,7 @@
         <v>21</v>
       </c>
       <c r="B277" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C277">
         <v>90</v>
@@ -8499,7 +8529,7 @@
         <v>21</v>
       </c>
       <c r="B278" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C278">
         <v>110</v>
@@ -8522,7 +8552,7 @@
         <v>21</v>
       </c>
       <c r="B279" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C279">
         <v>30</v>
@@ -8545,7 +8575,7 @@
         <v>21</v>
       </c>
       <c r="B280" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C280">
         <v>40</v>
@@ -8568,7 +8598,7 @@
         <v>21</v>
       </c>
       <c r="B281" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C281">
         <v>40</v>
@@ -8591,7 +8621,7 @@
         <v>21</v>
       </c>
       <c r="B282" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C282">
         <v>30</v>
@@ -8614,7 +8644,7 @@
         <v>21</v>
       </c>
       <c r="B283" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C283">
         <v>30</v>
@@ -8637,7 +8667,7 @@
         <v>21</v>
       </c>
       <c r="B284" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C284">
         <v>40</v>
@@ -8660,7 +8690,7 @@
         <v>21</v>
       </c>
       <c r="B285" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C285">
         <v>40</v>
@@ -8683,7 +8713,7 @@
         <v>21</v>
       </c>
       <c r="B286" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C286">
         <v>40</v>
@@ -8706,7 +8736,7 @@
         <v>21</v>
       </c>
       <c r="B287" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C287">
         <v>40</v>
@@ -8729,7 +8759,7 @@
         <v>21</v>
       </c>
       <c r="B288" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C288">
         <v>60</v>
@@ -8752,7 +8782,7 @@
         <v>21</v>
       </c>
       <c r="B289" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C289">
         <v>60</v>
@@ -8775,7 +8805,7 @@
         <v>21</v>
       </c>
       <c r="B290" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C290">
         <v>60</v>
@@ -8798,7 +8828,7 @@
         <v>21</v>
       </c>
       <c r="B291" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C291">
         <v>60</v>
@@ -8821,7 +8851,7 @@
         <v>21</v>
       </c>
       <c r="B292" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C292">
         <v>60</v>
@@ -8844,7 +8874,7 @@
         <v>21</v>
       </c>
       <c r="B293" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C293">
         <v>60</v>
@@ -8867,7 +8897,7 @@
         <v>22</v>
       </c>
       <c r="B294" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C294">
         <v>20</v>
@@ -8882,7 +8912,7 @@
         <v>3</v>
       </c>
       <c r="G294" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="H294">
         <v>28</v>
@@ -8893,7 +8923,7 @@
         <v>22</v>
       </c>
       <c r="B295" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C295">
         <v>60</v>
@@ -8908,7 +8938,7 @@
         <v>6</v>
       </c>
       <c r="G295" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="H295">
         <v>76</v>
@@ -8919,7 +8949,7 @@
         <v>22</v>
       </c>
       <c r="B296" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C296">
         <v>110</v>
@@ -8934,7 +8964,7 @@
         <v>7.5</v>
       </c>
       <c r="G296" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="H296">
         <v>121</v>
@@ -8945,7 +8975,7 @@
         <v>22</v>
       </c>
       <c r="B297" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C297">
         <v>70</v>
@@ -8960,7 +8990,7 @@
         <v>8</v>
       </c>
       <c r="G297" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="H297">
         <v>116.6666666666667</v>
@@ -8971,7 +9001,7 @@
         <v>22</v>
       </c>
       <c r="B298" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C298">
         <v>80</v>
@@ -8986,7 +9016,7 @@
         <v>8.5</v>
       </c>
       <c r="G298" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="H298">
         <v>112</v>
@@ -8997,7 +9027,7 @@
         <v>22</v>
       </c>
       <c r="B299" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C299">
         <v>60</v>
@@ -9012,7 +9042,7 @@
         <v>5</v>
       </c>
       <c r="G299" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="H299">
         <v>80</v>
@@ -9023,7 +9053,7 @@
         <v>22</v>
       </c>
       <c r="B300" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C300">
         <v>110</v>
@@ -9038,7 +9068,7 @@
         <v>6.5</v>
       </c>
       <c r="G300" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="H300">
         <v>128.3333333333333</v>
@@ -9049,7 +9079,7 @@
         <v>22</v>
       </c>
       <c r="B301" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C301">
         <v>140</v>
@@ -9064,7 +9094,7 @@
         <v>7</v>
       </c>
       <c r="G301" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="H301">
         <v>144.6666666666667</v>
@@ -9075,7 +9105,7 @@
         <v>22</v>
       </c>
       <c r="B302" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C302">
         <v>160</v>
@@ -9090,7 +9120,7 @@
         <v>8.5</v>
       </c>
       <c r="G302" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H302">
         <v>165.3333333333333</v>
@@ -9101,7 +9131,7 @@
         <v>22</v>
       </c>
       <c r="B303" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C303">
         <v>170</v>
@@ -9116,7 +9146,7 @@
         <v>9</v>
       </c>
       <c r="G303" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="H303">
         <v>175.6666666666667</v>
@@ -9127,7 +9157,7 @@
         <v>22</v>
       </c>
       <c r="B304" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C304">
         <v>30</v>
@@ -9142,7 +9172,7 @@
         <v>7</v>
       </c>
       <c r="G304" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="H304">
         <v>40</v>
@@ -9153,7 +9183,7 @@
         <v>22</v>
       </c>
       <c r="B305" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C305">
         <v>40</v>
@@ -9168,7 +9198,7 @@
         <v>7</v>
       </c>
       <c r="G305" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="H305">
         <v>44</v>
@@ -9179,7 +9209,7 @@
         <v>22</v>
       </c>
       <c r="B306" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C306">
         <v>50</v>
@@ -9194,7 +9224,7 @@
         <v>9.5</v>
       </c>
       <c r="G306" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="H306">
         <v>53.33333333333334</v>
@@ -9205,7 +9235,7 @@
         <v>22</v>
       </c>
       <c r="B307" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C307">
         <v>40</v>
@@ -9220,7 +9250,7 @@
         <v>8.5</v>
       </c>
       <c r="G307" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="H307">
         <v>53.33333333333333</v>
@@ -9231,7 +9261,7 @@
         <v>23</v>
       </c>
       <c r="B308" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C308">
         <v>70</v>
@@ -9254,7 +9284,7 @@
         <v>23</v>
       </c>
       <c r="B309" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C309">
         <v>120</v>
@@ -9277,7 +9307,7 @@
         <v>23</v>
       </c>
       <c r="B310" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C310">
         <v>140</v>
@@ -9300,7 +9330,7 @@
         <v>23</v>
       </c>
       <c r="B311" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C311">
         <v>140</v>
@@ -9323,7 +9353,7 @@
         <v>23</v>
       </c>
       <c r="B312" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C312">
         <v>120</v>
@@ -9346,7 +9376,7 @@
         <v>23</v>
       </c>
       <c r="B313" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C313">
         <v>20</v>
@@ -9369,7 +9399,7 @@
         <v>23</v>
       </c>
       <c r="B314" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C314">
         <v>40</v>
@@ -9392,7 +9422,7 @@
         <v>23</v>
       </c>
       <c r="B315" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C315">
         <v>60</v>
@@ -9415,7 +9445,7 @@
         <v>23</v>
       </c>
       <c r="B316" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C316">
         <v>70</v>
@@ -9438,7 +9468,7 @@
         <v>23</v>
       </c>
       <c r="B317" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C317">
         <v>80</v>
@@ -9461,7 +9491,7 @@
         <v>23</v>
       </c>
       <c r="B318" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C318">
         <v>75</v>
@@ -9484,7 +9514,7 @@
         <v>23</v>
       </c>
       <c r="B319" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C319">
         <v>60</v>
@@ -9507,7 +9537,7 @@
         <v>23</v>
       </c>
       <c r="B320" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C320">
         <v>60</v>
@@ -9530,7 +9560,7 @@
         <v>23</v>
       </c>
       <c r="B321" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C321">
         <v>60</v>
@@ -9553,7 +9583,7 @@
         <v>23</v>
       </c>
       <c r="B322" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C322">
         <v>65</v>
@@ -9576,7 +9606,7 @@
         <v>23</v>
       </c>
       <c r="B323" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C323">
         <v>65</v>
@@ -9599,7 +9629,7 @@
         <v>23</v>
       </c>
       <c r="B324" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C324">
         <v>65</v>
@@ -9622,7 +9652,7 @@
         <v>23</v>
       </c>
       <c r="B325" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C325">
         <v>65</v>
@@ -9645,7 +9675,7 @@
         <v>23</v>
       </c>
       <c r="B326" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C326">
         <v>65</v>
@@ -9668,7 +9698,7 @@
         <v>23</v>
       </c>
       <c r="B327" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C327">
         <v>65</v>
@@ -9691,7 +9721,7 @@
         <v>23</v>
       </c>
       <c r="B328" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C328">
         <v>65</v>
@@ -9714,7 +9744,7 @@
         <v>23</v>
       </c>
       <c r="B329" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C329">
         <v>65</v>
@@ -9737,7 +9767,7 @@
         <v>24</v>
       </c>
       <c r="B330" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C330">
         <v>20</v>
@@ -9752,7 +9782,7 @@
         <v>3</v>
       </c>
       <c r="G330" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="H330">
         <v>25.33333333333333</v>
@@ -9763,7 +9793,7 @@
         <v>24</v>
       </c>
       <c r="B331" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C331">
         <v>70</v>
@@ -9778,7 +9808,7 @@
         <v>6</v>
       </c>
       <c r="G331" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="H331">
         <v>81.66666666666667</v>
@@ -9789,7 +9819,7 @@
         <v>24</v>
       </c>
       <c r="B332" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C332">
         <v>90</v>
@@ -9804,7 +9834,7 @@
         <v>6</v>
       </c>
       <c r="G332" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="H332">
         <v>93.00000000000001</v>
@@ -9815,7 +9845,7 @@
         <v>24</v>
       </c>
       <c r="B333" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C333">
         <v>120</v>
@@ -9830,7 +9860,7 @@
         <v>7.5</v>
       </c>
       <c r="G333" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="H333">
         <v>124</v>
@@ -9841,7 +9871,7 @@
         <v>24</v>
       </c>
       <c r="B334" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C334">
         <v>140</v>
@@ -9856,7 +9886,7 @@
         <v>10</v>
       </c>
       <c r="G334" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="H334">
         <v>140</v>
@@ -9867,7 +9897,7 @@
         <v>24</v>
       </c>
       <c r="B335" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C335">
         <v>80</v>
@@ -9882,7 +9912,7 @@
         <v>8.5</v>
       </c>
       <c r="G335" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="H335">
         <v>133.3333333333333</v>
@@ -9893,7 +9923,7 @@
         <v>24</v>
       </c>
       <c r="B336" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C336">
         <v>80</v>
@@ -9908,7 +9938,7 @@
         <v>10</v>
       </c>
       <c r="G336" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="H336">
         <v>101.3333333333333</v>
@@ -9919,7 +9949,7 @@
         <v>24</v>
       </c>
       <c r="B337" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C337">
         <v>20</v>
@@ -9934,7 +9964,7 @@
         <v>4</v>
       </c>
       <c r="G337" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="H337">
         <v>25.33333333333333</v>
@@ -9945,7 +9975,7 @@
         <v>24</v>
       </c>
       <c r="B338" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C338">
         <v>40</v>
@@ -9960,7 +9990,7 @@
         <v>6</v>
       </c>
       <c r="G338" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="H338">
         <v>50.66666666666666</v>
@@ -9971,7 +10001,7 @@
         <v>24</v>
       </c>
       <c r="B339" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C339">
         <v>60</v>
@@ -9986,7 +10016,7 @@
         <v>7</v>
       </c>
       <c r="G339" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H339">
         <v>66</v>
@@ -9997,7 +10027,7 @@
         <v>24</v>
       </c>
       <c r="B340" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C340">
         <v>70</v>
@@ -10012,7 +10042,7 @@
         <v>8.5</v>
       </c>
       <c r="G340" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="H340">
         <v>77</v>
@@ -10023,7 +10053,7 @@
         <v>24</v>
       </c>
       <c r="B341" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C341">
         <v>75</v>
@@ -10038,7 +10068,7 @@
         <v>8.75</v>
       </c>
       <c r="G341" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="H341">
         <v>77.50000000000001</v>
@@ -10049,7 +10079,7 @@
         <v>24</v>
       </c>
       <c r="B342" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C342">
         <v>50</v>
@@ -10064,7 +10094,7 @@
         <v>8</v>
       </c>
       <c r="G342" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="H342">
         <v>66.66666666666666</v>
@@ -10075,7 +10105,7 @@
         <v>24</v>
       </c>
       <c r="B343" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C343">
         <v>40</v>
@@ -10090,7 +10120,7 @@
         <v>6</v>
       </c>
       <c r="G343" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="H343">
         <v>50.66666666666666</v>
@@ -10101,7 +10131,7 @@
         <v>24</v>
       </c>
       <c r="B344" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C344">
         <v>50</v>
@@ -10116,7 +10146,7 @@
         <v>6.5</v>
       </c>
       <c r="G344" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="H344">
         <v>63.33333333333333</v>
@@ -10127,7 +10157,7 @@
         <v>24</v>
       </c>
       <c r="B345" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C345">
         <v>63</v>
@@ -10142,7 +10172,7 @@
         <v>8</v>
       </c>
       <c r="G345" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="H345">
         <v>75.59999999999999</v>
@@ -10153,7 +10183,7 @@
         <v>24</v>
       </c>
       <c r="B346" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C346">
         <v>63</v>
@@ -10168,7 +10198,7 @@
         <v>8.5</v>
       </c>
       <c r="G346" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="H346">
         <v>75.59999999999999</v>
@@ -10179,7 +10209,7 @@
         <v>24</v>
       </c>
       <c r="B347" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C347">
         <v>11</v>
@@ -10194,7 +10224,7 @@
         <v>5</v>
       </c>
       <c r="G347" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="H347">
         <v>16.5</v>
@@ -10205,7 +10235,7 @@
         <v>24</v>
       </c>
       <c r="B348" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C348">
         <v>32</v>
@@ -10220,7 +10250,7 @@
         <v>5</v>
       </c>
       <c r="G348" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="H348">
         <v>48</v>
@@ -10231,7 +10261,7 @@
         <v>24</v>
       </c>
       <c r="B349" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C349">
         <v>33</v>
@@ -10246,7 +10276,7 @@
         <v>7</v>
       </c>
       <c r="G349" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="H349">
         <v>49.5</v>
@@ -10257,7 +10287,7 @@
         <v>24</v>
       </c>
       <c r="B350" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C350">
         <v>59</v>
@@ -10272,7 +10302,7 @@
         <v>8</v>
       </c>
       <c r="G350" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="H350">
         <v>82.59999999999999</v>
@@ -10283,7 +10313,7 @@
         <v>24</v>
       </c>
       <c r="B351" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C351">
         <v>39</v>
@@ -10298,7 +10328,7 @@
         <v>9</v>
       </c>
       <c r="G351" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H351">
         <v>58.5</v>
@@ -10309,7 +10339,7 @@
         <v>24</v>
       </c>
       <c r="B352" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C352">
         <v>66</v>
@@ -10324,7 +10354,7 @@
         <v>9</v>
       </c>
       <c r="G352" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="H352">
         <v>92.39999999999999</v>
@@ -10335,7 +10365,7 @@
         <v>25</v>
       </c>
       <c r="B353" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C353">
         <v>70</v>
@@ -10350,7 +10380,7 @@
         <v>6</v>
       </c>
       <c r="G353" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H353">
         <v>81.66666666666667</v>
@@ -10361,7 +10391,7 @@
         <v>25</v>
       </c>
       <c r="B354" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C354">
         <v>120</v>
@@ -10376,7 +10406,7 @@
         <v>6</v>
       </c>
       <c r="G354" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="H354">
         <v>124</v>
@@ -10387,7 +10417,7 @@
         <v>25</v>
       </c>
       <c r="B355" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C355">
         <v>140</v>
@@ -10402,7 +10432,7 @@
         <v>6.5</v>
       </c>
       <c r="G355" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H355">
         <v>144.6666666666667</v>
@@ -10413,7 +10443,7 @@
         <v>25</v>
       </c>
       <c r="B356" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C356">
         <v>160</v>
@@ -10428,7 +10458,7 @@
         <v>8.5</v>
       </c>
       <c r="G356" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="H356">
         <v>165.3333333333333</v>
@@ -10439,7 +10469,7 @@
         <v>25</v>
       </c>
       <c r="B357" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C357">
         <v>140</v>
@@ -10454,7 +10484,7 @@
         <v>8.5</v>
       </c>
       <c r="G357" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="H357">
         <v>163.3333333333333</v>
@@ -10465,7 +10495,7 @@
         <v>25</v>
       </c>
       <c r="B358" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C358">
         <v>140</v>
@@ -10480,7 +10510,7 @@
         <v>9</v>
       </c>
       <c r="G358" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="H358">
         <v>163.3333333333333</v>
@@ -10491,7 +10521,7 @@
         <v>25</v>
       </c>
       <c r="B359" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C359">
         <v>120</v>
@@ -10506,7 +10536,7 @@
         <v>9</v>
       </c>
       <c r="G359" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="H359">
         <v>144</v>
@@ -10517,7 +10547,7 @@
         <v>25</v>
       </c>
       <c r="B360" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C360">
         <v>30</v>
@@ -10532,7 +10562,7 @@
         <v>6</v>
       </c>
       <c r="G360" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="H360">
         <v>38</v>
@@ -10543,7 +10573,7 @@
         <v>25</v>
       </c>
       <c r="B361" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C361">
         <v>40</v>
@@ -10558,7 +10588,7 @@
         <v>7</v>
       </c>
       <c r="G361" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="H361">
         <v>48</v>
@@ -10569,7 +10599,7 @@
         <v>25</v>
       </c>
       <c r="B362" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C362">
         <v>50</v>
@@ -10584,7 +10614,7 @@
         <v>8</v>
       </c>
       <c r="G362" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="H362">
         <v>53.33333333333334</v>
@@ -10595,7 +10625,7 @@
         <v>25</v>
       </c>
       <c r="B363" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C363">
         <v>55</v>
@@ -10610,7 +10640,7 @@
         <v>10</v>
       </c>
       <c r="G363" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="H363">
         <v>56.83333333333334</v>
@@ -10621,7 +10651,7 @@
         <v>25</v>
       </c>
       <c r="B364" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C364">
         <v>45</v>
@@ -10636,7 +10666,7 @@
         <v>9</v>
       </c>
       <c r="G364" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="H364">
         <v>52.5</v>
@@ -10647,7 +10677,7 @@
         <v>25</v>
       </c>
       <c r="B365" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C365">
         <v>45</v>
@@ -10662,7 +10692,7 @@
         <v>9.5</v>
       </c>
       <c r="G365" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="H365">
         <v>52.5</v>
@@ -10673,7 +10703,7 @@
         <v>25</v>
       </c>
       <c r="B366" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C366">
         <v>45</v>
@@ -10688,7 +10718,7 @@
         <v>7</v>
       </c>
       <c r="G366" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="H366">
         <v>57</v>
@@ -10699,7 +10729,7 @@
         <v>25</v>
       </c>
       <c r="B367" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C367">
         <v>50</v>
@@ -10714,7 +10744,7 @@
         <v>8</v>
       </c>
       <c r="G367" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="H367">
         <v>63.33333333333333</v>
@@ -10725,7 +10755,7 @@
         <v>25</v>
       </c>
       <c r="B368" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C368">
         <v>50</v>
@@ -10740,7 +10770,7 @@
         <v>8</v>
       </c>
       <c r="G368" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="H368">
         <v>63.33333333333333</v>
@@ -10751,7 +10781,7 @@
         <v>25</v>
       </c>
       <c r="B369" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C369">
         <v>50</v>
@@ -10766,7 +10796,7 @@
         <v>8</v>
       </c>
       <c r="G369" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="H369">
         <v>63.33333333333333</v>
@@ -10777,7 +10807,7 @@
         <v>25</v>
       </c>
       <c r="B370" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C370">
         <v>40</v>
@@ -10792,7 +10822,7 @@
         <v>8.5</v>
       </c>
       <c r="G370" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H370">
         <v>60</v>
@@ -10803,7 +10833,7 @@
         <v>26</v>
       </c>
       <c r="B371" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C371">
         <v>20</v>
@@ -10818,7 +10848,7 @@
         <v>5</v>
       </c>
       <c r="G371" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H371">
         <v>25.33333333333333</v>
@@ -10829,7 +10859,7 @@
         <v>27</v>
       </c>
       <c r="B372" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C372">
         <v>40</v>
@@ -10844,7 +10874,7 @@
         <v>6</v>
       </c>
       <c r="G372" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="H372">
         <v>46.66666666666667</v>
@@ -10855,7 +10885,7 @@
         <v>28</v>
       </c>
       <c r="B373" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C373">
         <v>50</v>
@@ -10870,7 +10900,7 @@
         <v>7</v>
       </c>
       <c r="G373" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="H373">
         <v>60</v>
@@ -10881,7 +10911,7 @@
         <v>29</v>
       </c>
       <c r="B374" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C374">
         <v>50</v>
@@ -10896,7 +10926,7 @@
         <v>6.5</v>
       </c>
       <c r="G374" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="H374">
         <v>63.33333333333333</v>
@@ -10907,7 +10937,7 @@
         <v>30</v>
       </c>
       <c r="B375" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C375">
         <v>60</v>
@@ -10922,7 +10952,7 @@
         <v>7</v>
       </c>
       <c r="G375" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="H375">
         <v>66</v>
@@ -10933,7 +10963,7 @@
         <v>31</v>
       </c>
       <c r="B376" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C376">
         <v>70</v>
@@ -10948,7 +10978,7 @@
         <v>7.75</v>
       </c>
       <c r="G376" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="H376">
         <v>72.33333333333334</v>
@@ -10959,7 +10989,7 @@
         <v>32</v>
       </c>
       <c r="B377" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C377">
         <v>75</v>
@@ -10974,7 +11004,7 @@
         <v>8</v>
       </c>
       <c r="G377" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="H377">
         <v>77.50000000000001</v>
@@ -10985,7 +11015,7 @@
         <v>33</v>
       </c>
       <c r="B378" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C378">
         <v>77.5</v>
@@ -11000,7 +11030,7 @@
         <v>10</v>
       </c>
       <c r="G378" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="H378">
         <v>77.5</v>
@@ -11011,7 +11041,7 @@
         <v>34</v>
       </c>
       <c r="B379" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C379">
         <v>66.25</v>
@@ -11026,7 +11056,7 @@
         <v>9</v>
       </c>
       <c r="G379" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="H379">
         <v>77.29166666666667</v>
@@ -11037,7 +11067,7 @@
         <v>35</v>
       </c>
       <c r="B380" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C380">
         <v>60</v>
@@ -11052,7 +11082,7 @@
         <v>8.25</v>
       </c>
       <c r="G380" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="H380">
         <v>70</v>
@@ -11063,7 +11093,7 @@
         <v>36</v>
       </c>
       <c r="B381" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C381">
         <v>30</v>
@@ -11078,7 +11108,7 @@
         <v>6</v>
       </c>
       <c r="G381" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="H381">
         <v>42</v>
@@ -11089,7 +11119,7 @@
         <v>37</v>
       </c>
       <c r="B382" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C382">
         <v>50</v>
@@ -11104,7 +11134,7 @@
         <v>8.5</v>
       </c>
       <c r="G382" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="H382">
         <v>63.33333333333333</v>
@@ -11115,7 +11145,7 @@
         <v>38</v>
       </c>
       <c r="B383" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C383">
         <v>50</v>
@@ -11130,7 +11160,7 @@
         <v>8</v>
       </c>
       <c r="G383" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="H383">
         <v>63.33333333333333</v>
@@ -11141,7 +11171,7 @@
         <v>39</v>
       </c>
       <c r="B384" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C384">
         <v>50</v>
@@ -11156,7 +11186,7 @@
         <v>10</v>
       </c>
       <c r="G384" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="H384">
         <v>60</v>
@@ -11167,7 +11197,7 @@
         <v>40</v>
       </c>
       <c r="B385" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C385">
         <v>0</v>
@@ -11182,7 +11212,7 @@
         <v>6</v>
       </c>
       <c r="G385" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="H385">
         <v>0</v>
@@ -11193,7 +11223,7 @@
         <v>41</v>
       </c>
       <c r="B386" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C386">
         <v>25</v>
@@ -11208,7 +11238,7 @@
         <v>8</v>
       </c>
       <c r="G386" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="H386">
         <v>30</v>
@@ -11219,7 +11249,7 @@
         <v>42</v>
       </c>
       <c r="B387" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C387">
         <v>25</v>
@@ -11234,7 +11264,7 @@
         <v>8</v>
       </c>
       <c r="G387" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="H387">
         <v>31.66666666666666</v>
@@ -11245,7 +11275,7 @@
         <v>43</v>
       </c>
       <c r="B388" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C388">
         <v>25</v>
@@ -11260,7 +11290,7 @@
         <v>8.5</v>
       </c>
       <c r="G388" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="H388">
         <v>31.66666666666666</v>
@@ -11271,7 +11301,7 @@
         <v>44</v>
       </c>
       <c r="B389" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C389">
         <v>45</v>
@@ -11286,7 +11316,7 @@
         <v>6.5</v>
       </c>
       <c r="G389" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="H389">
         <v>62.99999999999999</v>
@@ -11297,7 +11327,7 @@
         <v>45</v>
       </c>
       <c r="B390" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C390">
         <v>60</v>
@@ -11312,7 +11342,7 @@
         <v>8</v>
       </c>
       <c r="G390" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="H390">
         <v>76</v>
@@ -11323,7 +11353,7 @@
         <v>46</v>
       </c>
       <c r="B391" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C391">
         <v>60</v>
@@ -11338,7 +11368,7 @@
         <v>7.5</v>
       </c>
       <c r="G391" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="H391">
         <v>76</v>
@@ -11349,7 +11379,7 @@
         <v>47</v>
       </c>
       <c r="B392" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C392">
         <v>60</v>
@@ -11364,7 +11394,7 @@
         <v>7.5</v>
       </c>
       <c r="G392" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="H392">
         <v>76</v>
@@ -11375,7 +11405,7 @@
         <v>48</v>
       </c>
       <c r="B393" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C393">
         <v>60</v>
@@ -11390,7 +11420,7 @@
         <v>9</v>
       </c>
       <c r="G393" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="H393">
         <v>76</v>
@@ -11401,7 +11431,7 @@
         <v>49</v>
       </c>
       <c r="B394" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C394">
         <v>40</v>
@@ -11416,7 +11446,7 @@
         <v>8</v>
       </c>
       <c r="G394" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="H394">
         <v>53.33333333333333</v>
@@ -11427,7 +11457,7 @@
         <v>50</v>
       </c>
       <c r="B395" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C395">
         <v>40</v>
@@ -11442,7 +11472,7 @@
         <v>7.5</v>
       </c>
       <c r="G395" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="H395">
         <v>56</v>
@@ -11453,7 +11483,7 @@
         <v>51</v>
       </c>
       <c r="B396" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C396">
         <v>40</v>
@@ -11468,7 +11498,7 @@
         <v>8</v>
       </c>
       <c r="G396" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="H396">
         <v>56</v>
@@ -11479,7 +11509,7 @@
         <v>52</v>
       </c>
       <c r="B397" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C397">
         <v>40</v>
@@ -11494,7 +11524,7 @@
         <v>8</v>
       </c>
       <c r="G397" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="H397">
         <v>56</v>
@@ -11505,7 +11535,7 @@
         <v>53</v>
       </c>
       <c r="B398" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C398">
         <v>40</v>
@@ -11520,7 +11550,7 @@
         <v>8.5</v>
       </c>
       <c r="G398" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="H398">
         <v>56</v>
@@ -11531,7 +11561,7 @@
         <v>54</v>
       </c>
       <c r="B399" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C399">
         <v>40</v>
@@ -11546,7 +11576,7 @@
         <v>9</v>
       </c>
       <c r="G399" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="H399">
         <v>56</v>
@@ -11557,7 +11587,7 @@
         <v>55</v>
       </c>
       <c r="B400" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C400">
         <v>20</v>
@@ -11572,7 +11602,7 @@
         <v>5</v>
       </c>
       <c r="G400" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="H400">
         <v>25.33333333333333</v>
@@ -11583,7 +11613,7 @@
         <v>56</v>
       </c>
       <c r="B401" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C401">
         <v>70</v>
@@ -11598,7 +11628,7 @@
         <v>6</v>
       </c>
       <c r="G401" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="H401">
         <v>81.66666666666667</v>
@@ -11609,7 +11639,7 @@
         <v>57</v>
       </c>
       <c r="B402" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C402">
         <v>120</v>
@@ -11624,7 +11654,7 @@
         <v>7.5</v>
       </c>
       <c r="G402" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="H402">
         <v>124</v>
@@ -11635,7 +11665,7 @@
         <v>58</v>
       </c>
       <c r="B403" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C403">
         <v>110</v>
@@ -11650,7 +11680,7 @@
         <v>8.5</v>
       </c>
       <c r="G403" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="H403">
         <v>128.3333333333333</v>
@@ -11661,7 +11691,7 @@
         <v>59</v>
       </c>
       <c r="B404" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C404">
         <v>110</v>
@@ -11676,7 +11706,7 @@
         <v>10</v>
       </c>
       <c r="G404" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="H404">
         <v>124.6666666666667</v>
@@ -11687,7 +11717,7 @@
         <v>60</v>
       </c>
       <c r="B405" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C405">
         <v>100</v>
@@ -11702,7 +11732,7 @@
         <v>9.5</v>
       </c>
       <c r="G405" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="H405">
         <v>110</v>
@@ -11713,7 +11743,7 @@
         <v>61</v>
       </c>
       <c r="B406" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C406">
         <v>40</v>
@@ -11728,7 +11758,7 @@
         <v>6</v>
       </c>
       <c r="G406" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="H406">
         <v>60</v>
@@ -11739,7 +11769,7 @@
         <v>62</v>
       </c>
       <c r="B407" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C407">
         <v>50</v>
@@ -11754,7 +11784,7 @@
         <v>7</v>
       </c>
       <c r="G407" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="H407">
         <v>70</v>
@@ -11765,7 +11795,7 @@
         <v>63</v>
       </c>
       <c r="B408" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C408">
         <v>50</v>
@@ -11780,7 +11810,7 @@
         <v>7.5</v>
       </c>
       <c r="G408" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="H408">
         <v>70</v>
@@ -11791,7 +11821,7 @@
         <v>64</v>
       </c>
       <c r="B409" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C409">
         <v>50</v>
@@ -11806,7 +11836,7 @@
         <v>8.5</v>
       </c>
       <c r="G409" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="H409">
         <v>70</v>
@@ -11817,7 +11847,7 @@
         <v>65</v>
       </c>
       <c r="B410" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C410">
         <v>30</v>
@@ -11832,7 +11862,7 @@
         <v>6</v>
       </c>
       <c r="G410" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="H410">
         <v>40</v>
@@ -11843,7 +11873,7 @@
         <v>66</v>
       </c>
       <c r="B411" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C411">
         <v>30</v>
@@ -11858,7 +11888,7 @@
         <v>6.5</v>
       </c>
       <c r="G411" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H411">
         <v>40</v>
@@ -11869,7 +11899,7 @@
         <v>67</v>
       </c>
       <c r="B412" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C412">
         <v>40</v>
@@ -11884,7 +11914,7 @@
         <v>8.5</v>
       </c>
       <c r="G412" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="H412">
         <v>53.33333333333333</v>
@@ -11895,7 +11925,7 @@
         <v>68</v>
       </c>
       <c r="B413" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C413">
         <v>40</v>
@@ -11910,7 +11940,7 @@
         <v>10</v>
       </c>
       <c r="G413" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="H413">
         <v>50.66666666666666</v>
@@ -11921,7 +11951,7 @@
         <v>69</v>
       </c>
       <c r="B414" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C414">
         <v>40</v>
@@ -11936,7 +11966,7 @@
         <v>9</v>
       </c>
       <c r="G414" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="H414">
         <v>50.66666666666666</v>
@@ -11947,7 +11977,7 @@
         <v>70</v>
       </c>
       <c r="B415" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C415">
         <v>30</v>
@@ -11962,7 +11992,7 @@
         <v>8</v>
       </c>
       <c r="G415" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="H415">
         <v>35</v>
@@ -11973,7 +12003,7 @@
         <v>70</v>
       </c>
       <c r="B416" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C416">
         <v>30</v>
@@ -11988,7 +12018,7 @@
         <v>8</v>
       </c>
       <c r="G416" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="H416">
         <v>42</v>
@@ -11999,7 +12029,7 @@
         <v>71</v>
       </c>
       <c r="B417" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C417">
         <v>30</v>
@@ -12014,7 +12044,7 @@
         <v>8.5</v>
       </c>
       <c r="G417" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="H417">
         <v>36</v>
@@ -12025,7 +12055,7 @@
         <v>71</v>
       </c>
       <c r="B418" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C418">
         <v>30</v>
@@ -12040,7 +12070,7 @@
         <v>8.5</v>
       </c>
       <c r="G418" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="H418">
         <v>42</v>
@@ -12051,7 +12081,7 @@
         <v>72</v>
       </c>
       <c r="B419" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C419">
         <v>30</v>
@@ -12066,7 +12096,7 @@
         <v>9</v>
       </c>
       <c r="G419" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="H419">
         <v>36</v>
@@ -12077,7 +12107,7 @@
         <v>72</v>
       </c>
       <c r="B420" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C420">
         <v>30</v>
@@ -12092,7 +12122,7 @@
         <v>9</v>
       </c>
       <c r="G420" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="H420">
         <v>42</v>
@@ -12103,7 +12133,7 @@
         <v>73</v>
       </c>
       <c r="B421" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C421">
         <v>20</v>
@@ -12115,7 +12145,7 @@
         <v>160</v>
       </c>
       <c r="G421" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="H421">
         <v>25.33333333333333</v>
@@ -12129,7 +12159,7 @@
         <v>73</v>
       </c>
       <c r="B422" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C422">
         <v>70</v>
@@ -12141,7 +12171,7 @@
         <v>350</v>
       </c>
       <c r="G422" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="H422">
         <v>81.66666666666667</v>
@@ -12155,7 +12185,7 @@
         <v>73</v>
       </c>
       <c r="B423" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C423">
         <v>120</v>
@@ -12167,7 +12197,7 @@
         <v>360</v>
       </c>
       <c r="G423" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="H423">
         <v>132</v>
@@ -12181,7 +12211,7 @@
         <v>73</v>
       </c>
       <c r="B424" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C424">
         <v>90</v>
@@ -12193,7 +12223,7 @@
         <v>1800</v>
       </c>
       <c r="G424" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="H424">
         <v>150</v>
@@ -12207,7 +12237,7 @@
         <v>73</v>
       </c>
       <c r="B425" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C425">
         <v>30</v>
@@ -12219,7 +12249,7 @@
         <v>240</v>
       </c>
       <c r="G425" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="H425">
         <v>38</v>
@@ -12233,7 +12263,7 @@
         <v>73</v>
       </c>
       <c r="B426" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C426">
         <v>40</v>
@@ -12245,7 +12275,7 @@
         <v>120</v>
       </c>
       <c r="G426" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="H426">
         <v>44</v>
@@ -12259,7 +12289,7 @@
         <v>73</v>
       </c>
       <c r="B427" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C427">
         <v>45</v>
@@ -12271,7 +12301,7 @@
         <v>135</v>
       </c>
       <c r="G427" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="H427">
         <v>49.50000000000001</v>
@@ -12285,7 +12315,7 @@
         <v>73</v>
       </c>
       <c r="B428" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C428">
         <v>45</v>
@@ -12297,7 +12327,7 @@
         <v>360</v>
       </c>
       <c r="G428" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="H428">
         <v>57</v>
@@ -12311,7 +12341,7 @@
         <v>73</v>
       </c>
       <c r="B429" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C429">
         <v>45</v>
@@ -12323,7 +12353,7 @@
         <v>360</v>
       </c>
       <c r="G429" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="H429">
         <v>57</v>
@@ -12337,7 +12367,7 @@
         <v>73</v>
       </c>
       <c r="B430" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C430">
         <v>45</v>
@@ -12349,7 +12379,7 @@
         <v>360</v>
       </c>
       <c r="G430" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="H430">
         <v>57</v>
@@ -12363,7 +12393,7 @@
         <v>73</v>
       </c>
       <c r="B431" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C431">
         <v>40</v>
@@ -12375,7 +12405,7 @@
         <v>480</v>
       </c>
       <c r="G431" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="H431">
         <v>56</v>
@@ -12389,7 +12419,7 @@
         <v>73</v>
       </c>
       <c r="B432" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C432">
         <v>50</v>
@@ -12401,7 +12431,7 @@
         <v>300</v>
       </c>
       <c r="G432" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="H432">
         <v>60</v>
@@ -12415,7 +12445,7 @@
         <v>73</v>
       </c>
       <c r="B433" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C433">
         <v>60</v>
@@ -12427,7 +12457,7 @@
         <v>360</v>
       </c>
       <c r="G433" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="H433">
         <v>72</v>
@@ -12441,7 +12471,7 @@
         <v>73</v>
       </c>
       <c r="B434" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C434">
         <v>60</v>
@@ -12453,7 +12483,7 @@
         <v>360</v>
       </c>
       <c r="G434" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="H434">
         <v>72</v>
@@ -12467,7 +12497,7 @@
         <v>73</v>
       </c>
       <c r="B435" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C435">
         <v>60</v>
@@ -12479,7 +12509,7 @@
         <v>360</v>
       </c>
       <c r="G435" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="H435">
         <v>72</v>
@@ -12493,7 +12523,7 @@
         <v>73</v>
       </c>
       <c r="B436" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C436">
         <v>60</v>
@@ -12505,7 +12535,7 @@
         <v>360</v>
       </c>
       <c r="G436" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="H436">
         <v>72</v>
@@ -12519,7 +12549,7 @@
         <v>73</v>
       </c>
       <c r="B437" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C437">
         <v>20</v>
@@ -12531,7 +12561,7 @@
         <v>160</v>
       </c>
       <c r="G437" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="H437">
         <v>25.33333333333333</v>
@@ -12545,7 +12575,7 @@
         <v>73</v>
       </c>
       <c r="B438" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C438">
         <v>30</v>
@@ -12557,7 +12587,7 @@
         <v>150</v>
       </c>
       <c r="G438" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="H438">
         <v>35</v>
@@ -12571,7 +12601,7 @@
         <v>73</v>
       </c>
       <c r="B439" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C439">
         <v>20</v>
@@ -12583,7 +12613,7 @@
         <v>240</v>
       </c>
       <c r="G439" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="H439">
         <v>28</v>
@@ -12597,7 +12627,7 @@
         <v>73</v>
       </c>
       <c r="B440" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C440">
         <v>30</v>
@@ -12609,7 +12639,7 @@
         <v>240</v>
       </c>
       <c r="G440" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="H440">
         <v>38</v>
@@ -12623,7 +12653,7 @@
         <v>73</v>
       </c>
       <c r="B441" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C441">
         <v>40</v>
@@ -12635,7 +12665,7 @@
         <v>120</v>
       </c>
       <c r="G441" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="H441">
         <v>44</v>
@@ -12649,7 +12679,7 @@
         <v>73</v>
       </c>
       <c r="B442" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C442">
         <v>30</v>
@@ -12661,7 +12691,7 @@
         <v>240</v>
       </c>
       <c r="G442" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="H442">
         <v>38</v>
@@ -12675,7 +12705,7 @@
         <v>73</v>
       </c>
       <c r="B443" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C443">
         <v>30</v>
@@ -12687,7 +12717,7 @@
         <v>240</v>
       </c>
       <c r="G443" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="H443">
         <v>38</v>
@@ -12701,7 +12731,7 @@
         <v>74</v>
       </c>
       <c r="B444" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C444">
         <v>20</v>
@@ -12716,7 +12746,7 @@
         <v>4</v>
       </c>
       <c r="G444" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="H444">
         <v>25.33333333333333</v>
@@ -12727,7 +12757,7 @@
         <v>74</v>
       </c>
       <c r="B445" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C445">
         <v>70</v>
@@ -12742,7 +12772,7 @@
         <v>6</v>
       </c>
       <c r="G445" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="H445">
         <v>84</v>
@@ -12753,7 +12783,7 @@
         <v>74</v>
       </c>
       <c r="B446" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C446">
         <v>110</v>
@@ -12768,7 +12798,7 @@
         <v>7</v>
       </c>
       <c r="G446" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="H446">
         <v>113.6666666666667</v>
@@ -12779,7 +12809,7 @@
         <v>74</v>
       </c>
       <c r="B447" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C447">
         <v>110</v>
@@ -12794,7 +12824,7 @@
         <v>8.5</v>
       </c>
       <c r="G447" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="H447">
         <v>121</v>
@@ -12805,7 +12835,7 @@
         <v>74</v>
       </c>
       <c r="B448" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C448">
         <v>90</v>
@@ -12820,7 +12850,7 @@
         <v>8</v>
       </c>
       <c r="G448" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="H448">
         <v>120</v>
@@ -12831,7 +12861,7 @@
         <v>74</v>
       </c>
       <c r="B449" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C449">
         <v>90</v>
@@ -12846,7 +12876,7 @@
         <v>8.5</v>
       </c>
       <c r="G449" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="H449">
         <v>120</v>
@@ -12857,7 +12887,7 @@
         <v>74</v>
       </c>
       <c r="B450" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C450">
         <v>30</v>
@@ -12872,7 +12902,7 @@
         <v>5.5</v>
       </c>
       <c r="G450" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="H450">
         <v>38</v>
@@ -12883,7 +12913,7 @@
         <v>74</v>
       </c>
       <c r="B451" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C451">
         <v>40</v>
@@ -12898,7 +12928,7 @@
         <v>6</v>
       </c>
       <c r="G451" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="H451">
         <v>50.66666666666666</v>
@@ -12909,7 +12939,7 @@
         <v>74</v>
       </c>
       <c r="B452" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C452">
         <v>45</v>
@@ -12924,7 +12954,7 @@
         <v>6</v>
       </c>
       <c r="G452" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="H452">
         <v>46.50000000000001</v>
@@ -12935,7 +12965,7 @@
         <v>74</v>
       </c>
       <c r="B453" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C453">
         <v>50</v>
@@ -12950,7 +12980,7 @@
         <v>6.5</v>
       </c>
       <c r="G453" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="H453">
         <v>51.66666666666667</v>
@@ -12961,7 +12991,7 @@
         <v>74</v>
       </c>
       <c r="B454" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C454">
         <v>55</v>
@@ -12976,7 +13006,7 @@
         <v>7</v>
       </c>
       <c r="G454" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="H454">
         <v>56.83333333333334</v>
@@ -12987,7 +13017,7 @@
         <v>74</v>
       </c>
       <c r="B455" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C455">
         <v>60</v>
@@ -13002,7 +13032,7 @@
         <v>10</v>
       </c>
       <c r="G455" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="H455">
         <v>60</v>
@@ -13013,7 +13043,7 @@
         <v>74</v>
       </c>
       <c r="B456" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C456">
         <v>50</v>
@@ -13028,7 +13058,7 @@
         <v>8</v>
       </c>
       <c r="G456" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="H456">
         <v>60</v>
@@ -13039,7 +13069,7 @@
         <v>74</v>
       </c>
       <c r="B457" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C457">
         <v>50</v>
@@ -13054,7 +13084,7 @@
         <v>9</v>
       </c>
       <c r="G457" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="H457">
         <v>60</v>
@@ -13065,7 +13095,7 @@
         <v>75</v>
       </c>
       <c r="B458" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C458">
         <v>20</v>
@@ -13080,7 +13110,7 @@
         <v>3</v>
       </c>
       <c r="G458" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="H458">
         <v>26.66666666666666</v>
@@ -13091,7 +13121,7 @@
         <v>75</v>
       </c>
       <c r="B459" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C459">
         <v>60</v>
@@ -13106,7 +13136,7 @@
         <v>6</v>
       </c>
       <c r="G459" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="H459">
         <v>76</v>
@@ -13117,7 +13147,7 @@
         <v>75</v>
       </c>
       <c r="B460" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C460">
         <v>100</v>
@@ -13132,7 +13162,7 @@
         <v>7</v>
       </c>
       <c r="G460" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="H460">
         <v>116.6666666666667</v>
@@ -13143,7 +13173,7 @@
         <v>75</v>
       </c>
       <c r="B461" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C461">
         <v>120</v>
@@ -13158,7 +13188,7 @@
         <v>8</v>
       </c>
       <c r="G461" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="H461">
         <v>128</v>
@@ -13169,7 +13199,7 @@
         <v>75</v>
       </c>
       <c r="B462" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C462">
         <v>130</v>
@@ -13184,7 +13214,7 @@
         <v>9</v>
       </c>
       <c r="G462" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="H462">
         <v>134.3333333333333</v>
@@ -13195,7 +13225,7 @@
         <v>75</v>
       </c>
       <c r="B463" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C463">
         <v>100</v>
@@ -13210,7 +13240,7 @@
         <v>9</v>
       </c>
       <c r="G463" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="H463">
         <v>133.3333333333333</v>
@@ -13221,7 +13251,7 @@
         <v>75</v>
       </c>
       <c r="B464" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C464">
         <v>100</v>
@@ -13236,7 +13266,7 @@
         <v>9.5</v>
       </c>
       <c r="G464" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="H464">
         <v>133.3333333333333</v>
@@ -13247,7 +13277,7 @@
         <v>75</v>
       </c>
       <c r="B465" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C465">
         <v>30</v>
@@ -13262,7 +13292,7 @@
         <v>6</v>
       </c>
       <c r="G465" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="H465">
         <v>40</v>
@@ -13273,7 +13303,7 @@
         <v>75</v>
       </c>
       <c r="B466" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C466">
         <v>30</v>
@@ -13288,7 +13318,7 @@
         <v>5.5</v>
       </c>
       <c r="G466" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="H466">
         <v>40</v>
@@ -13299,7 +13329,7 @@
         <v>75</v>
       </c>
       <c r="B467" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C467">
         <v>50</v>
@@ -13314,7 +13344,7 @@
         <v>10</v>
       </c>
       <c r="G467" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="H467">
         <v>53.33333333333334</v>
@@ -13325,7 +13355,7 @@
         <v>75</v>
       </c>
       <c r="B468" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C468">
         <v>40</v>
@@ -13340,7 +13370,7 @@
         <v>8</v>
       </c>
       <c r="G468" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="H468">
         <v>50.66666666666666</v>
@@ -13351,7 +13381,7 @@
         <v>75</v>
       </c>
       <c r="B469" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C469">
         <v>40</v>
@@ -13366,7 +13396,7 @@
         <v>8.5</v>
       </c>
       <c r="G469" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="H469">
         <v>50.66666666666666</v>
@@ -13377,7 +13407,7 @@
         <v>75</v>
       </c>
       <c r="B470" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C470">
         <v>40</v>
@@ -13392,7 +13422,7 @@
         <v>10</v>
       </c>
       <c r="G470" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="H470">
         <v>48</v>
@@ -13403,7 +13433,7 @@
         <v>75</v>
       </c>
       <c r="B471" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C471">
         <v>40</v>
@@ -13418,7 +13448,7 @@
         <v>7</v>
       </c>
       <c r="G471" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="H471">
         <v>60</v>
@@ -13429,7 +13459,7 @@
         <v>75</v>
       </c>
       <c r="B472" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C472">
         <v>70</v>
@@ -13444,7 +13474,7 @@
         <v>8.5</v>
       </c>
       <c r="G472" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="H472">
         <v>77</v>
@@ -13455,7 +13485,7 @@
         <v>75</v>
       </c>
       <c r="B473" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C473">
         <v>60</v>
@@ -13470,7 +13500,7 @@
         <v>8</v>
       </c>
       <c r="G473" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="H473">
         <v>76</v>
@@ -13481,7 +13511,7 @@
         <v>75</v>
       </c>
       <c r="B474" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C474">
         <v>60</v>
@@ -13496,7 +13526,7 @@
         <v>8</v>
       </c>
       <c r="G474" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="H474">
         <v>76</v>
@@ -13507,7 +13537,7 @@
         <v>75</v>
       </c>
       <c r="B475" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C475">
         <v>60</v>
@@ -13522,7 +13552,7 @@
         <v>9</v>
       </c>
       <c r="G475" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="H475">
         <v>76</v>
@@ -13533,7 +13563,7 @@
         <v>75</v>
       </c>
       <c r="B476" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C476">
         <v>25</v>
@@ -13548,7 +13578,7 @@
         <v>9</v>
       </c>
       <c r="G476" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="H476">
         <v>33.33333333333333</v>
@@ -13559,7 +13589,7 @@
         <v>75</v>
       </c>
       <c r="B477" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C477">
         <v>25</v>
@@ -13574,7 +13604,7 @@
         <v>9</v>
       </c>
       <c r="G477" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="H477">
         <v>41.66666666666666</v>
@@ -13585,7 +13615,7 @@
         <v>75</v>
       </c>
       <c r="B478" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C478">
         <v>18</v>
@@ -13600,7 +13630,7 @@
         <v>6</v>
       </c>
       <c r="G478" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="H478">
         <v>25.2</v>
@@ -13611,7 +13641,7 @@
         <v>75</v>
       </c>
       <c r="B479" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C479">
         <v>22</v>
@@ -13626,7 +13656,7 @@
         <v>7.5</v>
       </c>
       <c r="G479" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="H479">
         <v>29.33333333333333</v>
@@ -13637,7 +13667,7 @@
         <v>75</v>
       </c>
       <c r="B480" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C480">
         <v>22</v>
@@ -13652,7 +13682,7 @@
         <v>8.5</v>
       </c>
       <c r="G480" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="H480">
         <v>29.33333333333333</v>
@@ -13663,7 +13693,7 @@
         <v>75</v>
       </c>
       <c r="B481" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C481">
         <v>22</v>
@@ -13678,10 +13708,601 @@
         <v>9</v>
       </c>
       <c r="G481" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="H481">
         <v>29.33333333333333</v>
+      </c>
+    </row>
+    <row r="482" spans="1:8">
+      <c r="A482" t="s">
+        <v>76</v>
+      </c>
+      <c r="B482" t="s">
+        <v>100</v>
+      </c>
+      <c r="C482">
+        <v>20</v>
+      </c>
+      <c r="D482">
+        <v>8</v>
+      </c>
+      <c r="E482">
+        <v>160</v>
+      </c>
+      <c r="F482">
+        <v>3</v>
+      </c>
+      <c r="G482" t="s">
+        <v>168</v>
+      </c>
+      <c r="H482">
+        <v>25.33333333333333</v>
+      </c>
+    </row>
+    <row r="483" spans="1:8">
+      <c r="A483" t="s">
+        <v>76</v>
+      </c>
+      <c r="B483" t="s">
+        <v>100</v>
+      </c>
+      <c r="C483">
+        <v>40</v>
+      </c>
+      <c r="D483">
+        <v>10</v>
+      </c>
+      <c r="E483">
+        <v>400</v>
+      </c>
+      <c r="F483">
+        <v>5</v>
+      </c>
+      <c r="G483" t="s">
+        <v>400</v>
+      </c>
+      <c r="H483">
+        <v>53.33333333333333</v>
+      </c>
+    </row>
+    <row r="484" spans="1:8">
+      <c r="A484" t="s">
+        <v>76</v>
+      </c>
+      <c r="B484" t="s">
+        <v>100</v>
+      </c>
+      <c r="C484">
+        <v>60</v>
+      </c>
+      <c r="D484">
+        <v>3</v>
+      </c>
+      <c r="E484">
+        <v>180</v>
+      </c>
+      <c r="F484">
+        <v>6</v>
+      </c>
+      <c r="G484" t="s">
+        <v>401</v>
+      </c>
+      <c r="H484">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="485" spans="1:8">
+      <c r="A485" t="s">
+        <v>76</v>
+      </c>
+      <c r="B485" t="s">
+        <v>100</v>
+      </c>
+      <c r="C485">
+        <v>70</v>
+      </c>
+      <c r="D485">
+        <v>1</v>
+      </c>
+      <c r="E485">
+        <v>70</v>
+      </c>
+      <c r="F485">
+        <v>6.5</v>
+      </c>
+      <c r="G485" t="s">
+        <v>402</v>
+      </c>
+      <c r="H485">
+        <v>72.33333333333334</v>
+      </c>
+    </row>
+    <row r="486" spans="1:8">
+      <c r="A486" t="s">
+        <v>76</v>
+      </c>
+      <c r="B486" t="s">
+        <v>100</v>
+      </c>
+      <c r="C486">
+        <v>75</v>
+      </c>
+      <c r="D486">
+        <v>1</v>
+      </c>
+      <c r="E486">
+        <v>75</v>
+      </c>
+      <c r="F486">
+        <v>7.5</v>
+      </c>
+      <c r="G486" t="s">
+        <v>403</v>
+      </c>
+      <c r="H486">
+        <v>77.50000000000001</v>
+      </c>
+    </row>
+    <row r="487" spans="1:8">
+      <c r="A487" t="s">
+        <v>76</v>
+      </c>
+      <c r="B487" t="s">
+        <v>100</v>
+      </c>
+      <c r="C487">
+        <v>80</v>
+      </c>
+      <c r="D487">
+        <v>1</v>
+      </c>
+      <c r="E487">
+        <v>80</v>
+      </c>
+      <c r="F487">
+        <v>8.5</v>
+      </c>
+      <c r="G487" t="s">
+        <v>404</v>
+      </c>
+      <c r="H487">
+        <v>82.66666666666667</v>
+      </c>
+    </row>
+    <row r="488" spans="1:8">
+      <c r="A488" t="s">
+        <v>76</v>
+      </c>
+      <c r="B488" t="s">
+        <v>100</v>
+      </c>
+      <c r="C488">
+        <v>60</v>
+      </c>
+      <c r="D488">
+        <v>10</v>
+      </c>
+      <c r="E488">
+        <v>600</v>
+      </c>
+      <c r="F488">
+        <v>7.5</v>
+      </c>
+      <c r="G488" t="s">
+        <v>164</v>
+      </c>
+      <c r="H488">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="489" spans="1:8">
+      <c r="A489" t="s">
+        <v>76</v>
+      </c>
+      <c r="B489" t="s">
+        <v>100</v>
+      </c>
+      <c r="C489">
+        <v>60</v>
+      </c>
+      <c r="D489">
+        <v>10</v>
+      </c>
+      <c r="E489">
+        <v>600</v>
+      </c>
+      <c r="F489">
+        <v>8</v>
+      </c>
+      <c r="G489" t="s">
+        <v>164</v>
+      </c>
+      <c r="H489">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="490" spans="1:8">
+      <c r="A490" t="s">
+        <v>76</v>
+      </c>
+      <c r="B490" t="s">
+        <v>100</v>
+      </c>
+      <c r="C490">
+        <v>60</v>
+      </c>
+      <c r="D490">
+        <v>10</v>
+      </c>
+      <c r="E490">
+        <v>600</v>
+      </c>
+      <c r="F490">
+        <v>8.5</v>
+      </c>
+      <c r="G490" t="s">
+        <v>164</v>
+      </c>
+      <c r="H490">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="491" spans="1:8">
+      <c r="A491" t="s">
+        <v>76</v>
+      </c>
+      <c r="B491" t="s">
+        <v>126</v>
+      </c>
+      <c r="C491">
+        <v>40</v>
+      </c>
+      <c r="D491">
+        <v>12</v>
+      </c>
+      <c r="E491">
+        <v>480</v>
+      </c>
+      <c r="F491">
+        <v>6</v>
+      </c>
+      <c r="G491" t="s">
+        <v>405</v>
+      </c>
+      <c r="H491">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="492" spans="1:8">
+      <c r="A492" t="s">
+        <v>76</v>
+      </c>
+      <c r="B492" t="s">
+        <v>126</v>
+      </c>
+      <c r="C492">
+        <v>60</v>
+      </c>
+      <c r="D492">
+        <v>8</v>
+      </c>
+      <c r="E492">
+        <v>480</v>
+      </c>
+      <c r="F492">
+        <v>8</v>
+      </c>
+      <c r="H492">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="493" spans="1:8">
+      <c r="A493" t="s">
+        <v>76</v>
+      </c>
+      <c r="B493" t="s">
+        <v>126</v>
+      </c>
+      <c r="C493">
+        <v>60</v>
+      </c>
+      <c r="D493">
+        <v>8</v>
+      </c>
+      <c r="E493">
+        <v>480</v>
+      </c>
+      <c r="F493">
+        <v>8.5</v>
+      </c>
+      <c r="H493">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="494" spans="1:8">
+      <c r="A494" t="s">
+        <v>76</v>
+      </c>
+      <c r="B494" t="s">
+        <v>126</v>
+      </c>
+      <c r="C494">
+        <v>60</v>
+      </c>
+      <c r="D494">
+        <v>8</v>
+      </c>
+      <c r="E494">
+        <v>480</v>
+      </c>
+      <c r="F494">
+        <v>9</v>
+      </c>
+      <c r="H494">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="495" spans="1:8">
+      <c r="A495" t="s">
+        <v>76</v>
+      </c>
+      <c r="B495" t="s">
+        <v>126</v>
+      </c>
+      <c r="C495">
+        <v>60</v>
+      </c>
+      <c r="D495">
+        <v>8</v>
+      </c>
+      <c r="E495">
+        <v>480</v>
+      </c>
+      <c r="F495">
+        <v>9.5</v>
+      </c>
+      <c r="H495">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="496" spans="1:8">
+      <c r="A496" t="s">
+        <v>76</v>
+      </c>
+      <c r="B496" t="s">
+        <v>113</v>
+      </c>
+      <c r="C496">
+        <v>20</v>
+      </c>
+      <c r="D496">
+        <v>10</v>
+      </c>
+      <c r="E496">
+        <v>200</v>
+      </c>
+      <c r="F496">
+        <v>6</v>
+      </c>
+      <c r="G496" t="s">
+        <v>406</v>
+      </c>
+      <c r="H496">
+        <v>26.66666666666666</v>
+      </c>
+    </row>
+    <row r="497" spans="1:8">
+      <c r="A497" t="s">
+        <v>76</v>
+      </c>
+      <c r="B497" t="s">
+        <v>143</v>
+      </c>
+      <c r="C497">
+        <v>20</v>
+      </c>
+      <c r="D497">
+        <v>15</v>
+      </c>
+      <c r="E497">
+        <v>300</v>
+      </c>
+      <c r="F497">
+        <v>6</v>
+      </c>
+      <c r="G497" t="s">
+        <v>165</v>
+      </c>
+      <c r="H497">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="498" spans="1:8">
+      <c r="A498" t="s">
+        <v>76</v>
+      </c>
+      <c r="B498" t="s">
+        <v>113</v>
+      </c>
+      <c r="C498">
+        <v>25</v>
+      </c>
+      <c r="D498">
+        <v>8</v>
+      </c>
+      <c r="E498">
+        <v>200</v>
+      </c>
+      <c r="F498">
+        <v>7.5</v>
+      </c>
+      <c r="H498">
+        <v>31.66666666666666</v>
+      </c>
+    </row>
+    <row r="499" spans="1:8">
+      <c r="A499" t="s">
+        <v>76</v>
+      </c>
+      <c r="B499" t="s">
+        <v>143</v>
+      </c>
+      <c r="C499">
+        <v>25</v>
+      </c>
+      <c r="D499">
+        <v>15</v>
+      </c>
+      <c r="E499">
+        <v>375</v>
+      </c>
+      <c r="F499">
+        <v>7.5</v>
+      </c>
+      <c r="H499">
+        <v>37.5</v>
+      </c>
+    </row>
+    <row r="500" spans="1:8">
+      <c r="A500" t="s">
+        <v>76</v>
+      </c>
+      <c r="B500" t="s">
+        <v>113</v>
+      </c>
+      <c r="C500">
+        <v>25</v>
+      </c>
+      <c r="D500">
+        <v>8</v>
+      </c>
+      <c r="E500">
+        <v>200</v>
+      </c>
+      <c r="F500">
+        <v>8</v>
+      </c>
+      <c r="G500" t="s">
+        <v>407</v>
+      </c>
+      <c r="H500">
+        <v>31.66666666666666</v>
+      </c>
+    </row>
+    <row r="501" spans="1:8">
+      <c r="A501" t="s">
+        <v>76</v>
+      </c>
+      <c r="B501" t="s">
+        <v>143</v>
+      </c>
+      <c r="C501">
+        <v>25</v>
+      </c>
+      <c r="D501">
+        <v>15</v>
+      </c>
+      <c r="E501">
+        <v>375</v>
+      </c>
+      <c r="F501">
+        <v>8</v>
+      </c>
+      <c r="H501">
+        <v>37.5</v>
+      </c>
+    </row>
+    <row r="502" spans="1:8">
+      <c r="A502" t="s">
+        <v>76</v>
+      </c>
+      <c r="B502" t="s">
+        <v>113</v>
+      </c>
+      <c r="C502">
+        <v>25</v>
+      </c>
+      <c r="D502">
+        <v>8</v>
+      </c>
+      <c r="E502">
+        <v>200</v>
+      </c>
+      <c r="F502">
+        <v>8.5</v>
+      </c>
+      <c r="H502">
+        <v>31.66666666666666</v>
+      </c>
+    </row>
+    <row r="503" spans="1:8">
+      <c r="A503" t="s">
+        <v>76</v>
+      </c>
+      <c r="B503" t="s">
+        <v>143</v>
+      </c>
+      <c r="C503">
+        <v>25</v>
+      </c>
+      <c r="D503">
+        <v>15</v>
+      </c>
+      <c r="E503">
+        <v>375</v>
+      </c>
+      <c r="F503">
+        <v>8.5</v>
+      </c>
+      <c r="H503">
+        <v>37.5</v>
+      </c>
+    </row>
+    <row r="504" spans="1:8">
+      <c r="A504" t="s">
+        <v>76</v>
+      </c>
+      <c r="B504" t="s">
+        <v>113</v>
+      </c>
+      <c r="C504">
+        <v>25</v>
+      </c>
+      <c r="D504">
+        <v>8</v>
+      </c>
+      <c r="E504">
+        <v>200</v>
+      </c>
+      <c r="F504">
+        <v>9</v>
+      </c>
+      <c r="H504">
+        <v>31.66666666666666</v>
+      </c>
+    </row>
+    <row r="505" spans="1:8">
+      <c r="A505" t="s">
+        <v>76</v>
+      </c>
+      <c r="B505" t="s">
+        <v>143</v>
+      </c>
+      <c r="C505">
+        <v>25</v>
+      </c>
+      <c r="D505">
+        <v>15</v>
+      </c>
+      <c r="E505">
+        <v>375</v>
+      </c>
+      <c r="F505">
+        <v>9</v>
+      </c>
+      <c r="H505">
+        <v>37.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/workout_log.xlsx
+++ b/data/workout_log.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1379" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1436" uniqueCount="423">
   <si>
     <t>Timestamp</t>
   </si>
@@ -247,6 +247,9 @@
     <t>2026-03-24 08:00:00</t>
   </si>
   <si>
+    <t>2026-03-25 19:30:00</t>
+  </si>
+  <si>
     <t>Overhead Press</t>
   </si>
   <si>
@@ -1238,6 +1241,48 @@
   </si>
   <si>
     <t>Narrower grip, less discomfort</t>
+  </si>
+  <si>
+    <t>CNS Check</t>
+  </si>
+  <si>
+    <t>Butter</t>
+  </si>
+  <si>
+    <t>Easy</t>
+  </si>
+  <si>
+    <t>Felt great</t>
+  </si>
+  <si>
+    <t>Smooth finish</t>
+  </si>
+  <si>
+    <t>Fail (Lockout)</t>
+  </si>
+  <si>
+    <t>Fail (Floor)</t>
+  </si>
+  <si>
+    <t>High fatigue</t>
+  </si>
+  <si>
+    <t>That sucked</t>
+  </si>
+  <si>
+    <t>Snappy</t>
+  </si>
+  <si>
+    <t>Controlled</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>Recovery triple</t>
+  </si>
+  <si>
+    <t>Fatigue limit</t>
   </si>
 </sst>
 </file>
@@ -1595,7 +1640,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I505"/>
+  <dimension ref="A1:I524"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -1632,7 +1677,7 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C2">
         <v>30</v>
@@ -1647,7 +1692,7 @@
         <v>4</v>
       </c>
       <c r="G2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H2">
         <v>40</v>
@@ -1658,7 +1703,7 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C3">
         <v>30</v>
@@ -1681,7 +1726,7 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C4">
         <v>30</v>
@@ -1704,7 +1749,7 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C5">
         <v>30</v>
@@ -1727,7 +1772,7 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C6">
         <v>60</v>
@@ -1742,7 +1787,7 @@
         <v>5</v>
       </c>
       <c r="G6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H6">
         <v>76</v>
@@ -1753,7 +1798,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C7">
         <v>100</v>
@@ -1768,7 +1813,7 @@
         <v>6</v>
       </c>
       <c r="G7" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H7">
         <v>110</v>
@@ -1779,7 +1824,7 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C8">
         <v>100</v>
@@ -1802,7 +1847,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C9">
         <v>100</v>
@@ -1825,7 +1870,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C10">
         <v>32</v>
@@ -1840,7 +1885,7 @@
         <v>3</v>
       </c>
       <c r="G10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H10">
         <v>44.8</v>
@@ -1851,7 +1896,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C11">
         <v>40</v>
@@ -1866,7 +1911,7 @@
         <v>5.5</v>
       </c>
       <c r="G11" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H11">
         <v>50.66666666666666</v>
@@ -1877,7 +1922,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C12">
         <v>40</v>
@@ -1900,7 +1945,7 @@
         <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C13">
         <v>40</v>
@@ -1915,7 +1960,7 @@
         <v>9</v>
       </c>
       <c r="G13" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H13">
         <v>48</v>
@@ -1926,7 +1971,7 @@
         <v>9</v>
       </c>
       <c r="B14" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C14">
         <v>20</v>
@@ -1949,7 +1994,7 @@
         <v>9</v>
       </c>
       <c r="B15" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C15">
         <v>20</v>
@@ -1972,7 +2017,7 @@
         <v>9</v>
       </c>
       <c r="B16" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C16">
         <v>20</v>
@@ -1995,7 +2040,7 @@
         <v>9</v>
       </c>
       <c r="B17" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C17">
         <v>20</v>
@@ -2010,7 +2055,7 @@
         <v>8</v>
       </c>
       <c r="G17" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H17">
         <v>26.66666666666666</v>
@@ -2021,7 +2066,7 @@
         <v>9</v>
       </c>
       <c r="B18" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C18">
         <v>20</v>
@@ -2036,7 +2081,7 @@
         <v>8</v>
       </c>
       <c r="G18" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H18">
         <v>26.66666666666666</v>
@@ -2047,7 +2092,7 @@
         <v>9</v>
       </c>
       <c r="B19" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C19">
         <v>20</v>
@@ -2062,7 +2107,7 @@
         <v>8</v>
       </c>
       <c r="G19" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H19">
         <v>25.33333333333333</v>
@@ -2073,7 +2118,7 @@
         <v>9</v>
       </c>
       <c r="B20" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C20">
         <v>20</v>
@@ -2088,7 +2133,7 @@
         <v>8</v>
       </c>
       <c r="G20" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H20">
         <v>25.33333333333333</v>
@@ -2099,7 +2144,7 @@
         <v>10</v>
       </c>
       <c r="B21" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -2114,7 +2159,7 @@
         <v>7</v>
       </c>
       <c r="G21" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H21">
         <v>0</v>
@@ -2125,7 +2170,7 @@
         <v>10</v>
       </c>
       <c r="B22" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C22">
         <v>30</v>
@@ -2148,7 +2193,7 @@
         <v>10</v>
       </c>
       <c r="B23" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C23">
         <v>30</v>
@@ -2171,7 +2216,7 @@
         <v>10</v>
       </c>
       <c r="B24" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C24">
         <v>30</v>
@@ -2194,7 +2239,7 @@
         <v>10</v>
       </c>
       <c r="B25" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C25">
         <v>30</v>
@@ -2217,7 +2262,7 @@
         <v>10</v>
       </c>
       <c r="B26" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C26">
         <v>30</v>
@@ -2240,7 +2285,7 @@
         <v>10</v>
       </c>
       <c r="B27" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C27">
         <v>30</v>
@@ -2263,7 +2308,7 @@
         <v>10</v>
       </c>
       <c r="B28" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C28">
         <v>30</v>
@@ -2286,7 +2331,7 @@
         <v>10</v>
       </c>
       <c r="B29" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C29">
         <v>30</v>
@@ -2309,7 +2354,7 @@
         <v>10</v>
       </c>
       <c r="B30" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C30">
         <v>30</v>
@@ -2332,7 +2377,7 @@
         <v>10</v>
       </c>
       <c r="B31" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C31">
         <v>70</v>
@@ -2355,7 +2400,7 @@
         <v>10</v>
       </c>
       <c r="B32" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C32">
         <v>70</v>
@@ -2378,7 +2423,7 @@
         <v>10</v>
       </c>
       <c r="B33" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C33">
         <v>70</v>
@@ -2401,7 +2446,7 @@
         <v>10</v>
       </c>
       <c r="B34" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C34">
         <v>23</v>
@@ -2416,7 +2461,7 @@
         <v>7</v>
       </c>
       <c r="G34" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H34">
         <v>38.33333333333333</v>
@@ -2427,7 +2472,7 @@
         <v>10</v>
       </c>
       <c r="B35" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C35">
         <v>23</v>
@@ -2442,7 +2487,7 @@
         <v>7</v>
       </c>
       <c r="G35" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H35">
         <v>38.33333333333333</v>
@@ -2453,7 +2498,7 @@
         <v>10</v>
       </c>
       <c r="B36" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C36">
         <v>23</v>
@@ -2468,7 +2513,7 @@
         <v>9</v>
       </c>
       <c r="G36" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H36">
         <v>38.33333333333333</v>
@@ -2479,7 +2524,7 @@
         <v>10</v>
       </c>
       <c r="B37" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C37">
         <v>23</v>
@@ -2494,7 +2539,7 @@
         <v>10</v>
       </c>
       <c r="G37" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H37">
         <v>32.2</v>
@@ -2505,7 +2550,7 @@
         <v>10</v>
       </c>
       <c r="B38" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C38">
         <v>20</v>
@@ -2528,7 +2573,7 @@
         <v>10</v>
       </c>
       <c r="B39" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C39">
         <v>20</v>
@@ -2551,7 +2596,7 @@
         <v>10</v>
       </c>
       <c r="B40" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C40">
         <v>20</v>
@@ -2574,7 +2619,7 @@
         <v>11</v>
       </c>
       <c r="B41" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C41">
         <v>36</v>
@@ -2589,7 +2634,7 @@
         <v>5</v>
       </c>
       <c r="G41" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H41">
         <v>48</v>
@@ -2600,7 +2645,7 @@
         <v>11</v>
       </c>
       <c r="B42" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C42">
         <v>44</v>
@@ -2615,7 +2660,7 @@
         <v>7</v>
       </c>
       <c r="G42" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H42">
         <v>52.8</v>
@@ -2626,7 +2671,7 @@
         <v>11</v>
       </c>
       <c r="B43" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C43">
         <v>44</v>
@@ -2641,7 +2686,7 @@
         <v>7.5</v>
       </c>
       <c r="G43" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H43">
         <v>52.8</v>
@@ -2652,7 +2697,7 @@
         <v>11</v>
       </c>
       <c r="B44" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C44">
         <v>44</v>
@@ -2667,7 +2712,7 @@
         <v>8</v>
       </c>
       <c r="G44" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H44">
         <v>52.8</v>
@@ -2678,7 +2723,7 @@
         <v>11</v>
       </c>
       <c r="B45" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C45">
         <v>60</v>
@@ -2701,7 +2746,7 @@
         <v>11</v>
       </c>
       <c r="B46" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C46">
         <v>100</v>
@@ -2724,7 +2769,7 @@
         <v>11</v>
       </c>
       <c r="B47" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C47">
         <v>130</v>
@@ -2747,7 +2792,7 @@
         <v>11</v>
       </c>
       <c r="B48" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C48">
         <v>140</v>
@@ -2762,7 +2807,7 @@
         <v>10</v>
       </c>
       <c r="G48" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H48">
         <v>144.6666666666667</v>
@@ -2773,7 +2818,7 @@
         <v>11</v>
       </c>
       <c r="B49" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C49">
         <v>130</v>
@@ -2796,7 +2841,7 @@
         <v>11</v>
       </c>
       <c r="B50" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C50">
         <v>100</v>
@@ -2819,7 +2864,7 @@
         <v>11</v>
       </c>
       <c r="B51" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C51">
         <v>100</v>
@@ -2834,7 +2879,7 @@
         <v>9</v>
       </c>
       <c r="G51" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H51">
         <v>133.3333333333333</v>
@@ -2845,7 +2890,7 @@
         <v>11</v>
       </c>
       <c r="B52" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C52">
         <v>20</v>
@@ -2860,7 +2905,7 @@
         <v>8</v>
       </c>
       <c r="G52" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H52">
         <v>26.66666666666666</v>
@@ -2871,7 +2916,7 @@
         <v>11</v>
       </c>
       <c r="B53" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C53">
         <v>20</v>
@@ -2886,7 +2931,7 @@
         <v>9</v>
       </c>
       <c r="G53" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H53">
         <v>26.66666666666666</v>
@@ -2897,7 +2942,7 @@
         <v>11</v>
       </c>
       <c r="B54" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C54">
         <v>30</v>
@@ -2920,7 +2965,7 @@
         <v>11</v>
       </c>
       <c r="B55" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C55">
         <v>40</v>
@@ -2943,7 +2988,7 @@
         <v>11</v>
       </c>
       <c r="B56" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C56">
         <v>40</v>
@@ -2966,7 +3011,7 @@
         <v>11</v>
       </c>
       <c r="B57" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C57">
         <v>40</v>
@@ -2989,7 +3034,7 @@
         <v>11</v>
       </c>
       <c r="B58" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C58">
         <v>45</v>
@@ -3012,7 +3057,7 @@
         <v>11</v>
       </c>
       <c r="B59" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C59">
         <v>45</v>
@@ -3035,7 +3080,7 @@
         <v>11</v>
       </c>
       <c r="B60" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C60">
         <v>50</v>
@@ -3050,7 +3095,7 @@
         <v>7.5</v>
       </c>
       <c r="G60" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H60">
         <v>63.33333333333333</v>
@@ -3061,7 +3106,7 @@
         <v>11</v>
       </c>
       <c r="B61" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C61">
         <v>50</v>
@@ -3076,7 +3121,7 @@
         <v>7.5</v>
       </c>
       <c r="G61" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H61">
         <v>63.33333333333333</v>
@@ -3087,7 +3132,7 @@
         <v>11</v>
       </c>
       <c r="B62" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C62">
         <v>50</v>
@@ -3102,7 +3147,7 @@
         <v>8.5</v>
       </c>
       <c r="G62" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H62">
         <v>63.33333333333333</v>
@@ -3113,7 +3158,7 @@
         <v>11</v>
       </c>
       <c r="B63" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C63">
         <v>50</v>
@@ -3128,7 +3173,7 @@
         <v>8.5</v>
       </c>
       <c r="G63" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H63">
         <v>63.33333333333333</v>
@@ -3139,7 +3184,7 @@
         <v>11</v>
       </c>
       <c r="B64" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C64">
         <v>50</v>
@@ -3154,7 +3199,7 @@
         <v>9</v>
       </c>
       <c r="G64" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H64">
         <v>63.33333333333333</v>
@@ -3165,7 +3210,7 @@
         <v>11</v>
       </c>
       <c r="B65" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C65">
         <v>50</v>
@@ -3180,7 +3225,7 @@
         <v>9</v>
       </c>
       <c r="G65" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H65">
         <v>63.33333333333333</v>
@@ -3191,7 +3236,7 @@
         <v>12</v>
       </c>
       <c r="B66" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C66">
         <v>60</v>
@@ -3214,7 +3259,7 @@
         <v>12</v>
       </c>
       <c r="B67" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C67">
         <v>100</v>
@@ -3237,7 +3282,7 @@
         <v>12</v>
       </c>
       <c r="B68" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C68">
         <v>100</v>
@@ -3260,7 +3305,7 @@
         <v>12</v>
       </c>
       <c r="B69" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C69">
         <v>60</v>
@@ -3283,7 +3328,7 @@
         <v>12</v>
       </c>
       <c r="B70" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C70">
         <v>100</v>
@@ -3306,7 +3351,7 @@
         <v>12</v>
       </c>
       <c r="B71" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C71">
         <v>80</v>
@@ -3329,7 +3374,7 @@
         <v>12</v>
       </c>
       <c r="B72" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C72">
         <v>80</v>
@@ -3352,7 +3397,7 @@
         <v>12</v>
       </c>
       <c r="B73" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C73">
         <v>20</v>
@@ -3375,7 +3420,7 @@
         <v>12</v>
       </c>
       <c r="B74" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C74">
         <v>30</v>
@@ -3398,7 +3443,7 @@
         <v>12</v>
       </c>
       <c r="B75" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C75">
         <v>35</v>
@@ -3421,7 +3466,7 @@
         <v>12</v>
       </c>
       <c r="B76" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C76">
         <v>35</v>
@@ -3436,7 +3481,7 @@
         <v>10</v>
       </c>
       <c r="G76" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H76">
         <v>43.16666666666667</v>
@@ -3447,7 +3492,7 @@
         <v>12</v>
       </c>
       <c r="B77" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C77">
         <v>30</v>
@@ -3470,7 +3515,7 @@
         <v>12</v>
       </c>
       <c r="B78" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C78">
         <v>30</v>
@@ -3493,7 +3538,7 @@
         <v>12</v>
       </c>
       <c r="B79" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C79">
         <v>50</v>
@@ -3516,7 +3561,7 @@
         <v>12</v>
       </c>
       <c r="B80" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C80">
         <v>40</v>
@@ -3539,7 +3584,7 @@
         <v>12</v>
       </c>
       <c r="B81" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C81">
         <v>22</v>
@@ -3562,7 +3607,7 @@
         <v>12</v>
       </c>
       <c r="B82" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C82">
         <v>22</v>
@@ -3585,7 +3630,7 @@
         <v>12</v>
       </c>
       <c r="B83" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C83">
         <v>22</v>
@@ -3608,7 +3653,7 @@
         <v>13</v>
       </c>
       <c r="B84" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C84">
         <v>20</v>
@@ -3623,7 +3668,7 @@
         <v>4</v>
       </c>
       <c r="G84" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H84">
         <v>28</v>
@@ -3634,7 +3679,7 @@
         <v>13</v>
       </c>
       <c r="B85" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C85">
         <v>40</v>
@@ -3657,7 +3702,7 @@
         <v>13</v>
       </c>
       <c r="B86" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C86">
         <v>50</v>
@@ -3680,7 +3725,7 @@
         <v>13</v>
       </c>
       <c r="B87" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C87">
         <v>60</v>
@@ -3703,7 +3748,7 @@
         <v>13</v>
       </c>
       <c r="B88" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C88">
         <v>60</v>
@@ -3726,7 +3771,7 @@
         <v>13</v>
       </c>
       <c r="B89" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C89">
         <v>60</v>
@@ -3741,7 +3786,7 @@
         <v>9</v>
       </c>
       <c r="G89" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H89">
         <v>64</v>
@@ -3752,7 +3797,7 @@
         <v>13</v>
       </c>
       <c r="B90" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C90">
         <v>40</v>
@@ -3767,7 +3812,7 @@
         <v>8</v>
       </c>
       <c r="G90" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H90">
         <v>60</v>
@@ -3778,7 +3823,7 @@
         <v>13</v>
       </c>
       <c r="B91" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C91">
         <v>16</v>
@@ -3793,7 +3838,7 @@
         <v>7</v>
       </c>
       <c r="G91" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H91">
         <v>21.33333333333333</v>
@@ -3804,7 +3849,7 @@
         <v>13</v>
       </c>
       <c r="B92" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C92">
         <v>16</v>
@@ -3819,7 +3864,7 @@
         <v>7</v>
       </c>
       <c r="G92" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H92">
         <v>21.33333333333333</v>
@@ -3830,7 +3875,7 @@
         <v>13</v>
       </c>
       <c r="B93" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C93">
         <v>16</v>
@@ -3845,7 +3890,7 @@
         <v>8</v>
       </c>
       <c r="G93" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H93">
         <v>21.33333333333333</v>
@@ -3856,7 +3901,7 @@
         <v>13</v>
       </c>
       <c r="B94" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C94">
         <v>16</v>
@@ -3871,7 +3916,7 @@
         <v>8</v>
       </c>
       <c r="G94" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H94">
         <v>21.33333333333333</v>
@@ -3882,7 +3927,7 @@
         <v>13</v>
       </c>
       <c r="B95" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C95">
         <v>16</v>
@@ -3897,7 +3942,7 @@
         <v>8.5</v>
       </c>
       <c r="G95" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H95">
         <v>21.33333333333333</v>
@@ -3908,7 +3953,7 @@
         <v>13</v>
       </c>
       <c r="B96" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C96">
         <v>16</v>
@@ -3923,7 +3968,7 @@
         <v>8.5</v>
       </c>
       <c r="G96" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H96">
         <v>21.33333333333333</v>
@@ -3934,7 +3979,7 @@
         <v>13</v>
       </c>
       <c r="B97" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C97">
         <v>8</v>
@@ -3957,7 +4002,7 @@
         <v>13</v>
       </c>
       <c r="B98" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C98">
         <v>8</v>
@@ -3980,7 +4025,7 @@
         <v>13</v>
       </c>
       <c r="B99" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C99">
         <v>8</v>
@@ -4003,7 +4048,7 @@
         <v>13</v>
       </c>
       <c r="B100" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C100">
         <v>58</v>
@@ -4018,7 +4063,7 @@
         <v>7</v>
       </c>
       <c r="G100" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H100">
         <v>77.33333333333333</v>
@@ -4029,7 +4074,7 @@
         <v>13</v>
       </c>
       <c r="B101" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C101">
         <v>58</v>
@@ -4044,7 +4089,7 @@
         <v>7</v>
       </c>
       <c r="G101" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H101">
         <v>77.33333333333333</v>
@@ -4055,7 +4100,7 @@
         <v>13</v>
       </c>
       <c r="B102" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C102">
         <v>58</v>
@@ -4078,7 +4123,7 @@
         <v>13</v>
       </c>
       <c r="B103" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C103">
         <v>58</v>
@@ -4101,7 +4146,7 @@
         <v>13</v>
       </c>
       <c r="B104" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C104">
         <v>58</v>
@@ -4124,7 +4169,7 @@
         <v>13</v>
       </c>
       <c r="B105" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C105">
         <v>58</v>
@@ -4147,7 +4192,7 @@
         <v>13</v>
       </c>
       <c r="B106" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C106">
         <v>45</v>
@@ -4170,7 +4215,7 @@
         <v>13</v>
       </c>
       <c r="B107" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C107">
         <v>45</v>
@@ -4193,7 +4238,7 @@
         <v>13</v>
       </c>
       <c r="B108" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C108">
         <v>45</v>
@@ -4216,7 +4261,7 @@
         <v>13</v>
       </c>
       <c r="B109" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C109">
         <v>20</v>
@@ -4239,7 +4284,7 @@
         <v>13</v>
       </c>
       <c r="B110" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C110">
         <v>30</v>
@@ -4254,7 +4299,7 @@
         <v>10</v>
       </c>
       <c r="G110" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H110">
         <v>34</v>
@@ -4265,7 +4310,7 @@
         <v>14</v>
       </c>
       <c r="B111" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C111">
         <v>20</v>
@@ -4280,7 +4325,7 @@
         <v>3</v>
       </c>
       <c r="G111" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H111">
         <v>25.33333333333333</v>
@@ -4291,7 +4336,7 @@
         <v>14</v>
       </c>
       <c r="B112" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C112">
         <v>60</v>
@@ -4306,7 +4351,7 @@
         <v>5</v>
       </c>
       <c r="G112" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H112">
         <v>66</v>
@@ -4317,7 +4362,7 @@
         <v>14</v>
       </c>
       <c r="B113" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C113">
         <v>80</v>
@@ -4332,7 +4377,7 @@
         <v>7</v>
       </c>
       <c r="G113" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H113">
         <v>88</v>
@@ -4343,7 +4388,7 @@
         <v>14</v>
       </c>
       <c r="B114" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C114">
         <v>90</v>
@@ -4358,7 +4403,7 @@
         <v>7</v>
       </c>
       <c r="G114" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H114">
         <v>93.00000000000001</v>
@@ -4369,7 +4414,7 @@
         <v>14</v>
       </c>
       <c r="B115" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C115">
         <v>90</v>
@@ -4384,7 +4429,7 @@
         <v>7.5</v>
       </c>
       <c r="G115" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H115">
         <v>99.00000000000001</v>
@@ -4395,7 +4440,7 @@
         <v>14</v>
       </c>
       <c r="B116" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C116">
         <v>100</v>
@@ -4410,7 +4455,7 @@
         <v>8.5</v>
       </c>
       <c r="G116" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H116">
         <v>110</v>
@@ -4421,7 +4466,7 @@
         <v>14</v>
       </c>
       <c r="B117" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C117">
         <v>110</v>
@@ -4436,7 +4481,7 @@
         <v>9</v>
       </c>
       <c r="G117" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H117">
         <v>113.6666666666667</v>
@@ -4447,7 +4492,7 @@
         <v>14</v>
       </c>
       <c r="B118" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C118">
         <v>20</v>
@@ -4462,7 +4507,7 @@
         <v>5</v>
       </c>
       <c r="G118" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H118">
         <v>28</v>
@@ -4473,7 +4518,7 @@
         <v>14</v>
       </c>
       <c r="B119" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C119">
         <v>30</v>
@@ -4488,7 +4533,7 @@
         <v>6</v>
       </c>
       <c r="G119" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H119">
         <v>36</v>
@@ -4499,7 +4544,7 @@
         <v>14</v>
       </c>
       <c r="B120" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C120">
         <v>40</v>
@@ -4514,7 +4559,7 @@
         <v>7.5</v>
       </c>
       <c r="G120" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H120">
         <v>45.33333333333333</v>
@@ -4525,7 +4570,7 @@
         <v>14</v>
       </c>
       <c r="B121" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C121">
         <v>45</v>
@@ -4540,7 +4585,7 @@
         <v>8.5</v>
       </c>
       <c r="G121" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H121">
         <v>49.50000000000001</v>
@@ -4551,7 +4596,7 @@
         <v>14</v>
       </c>
       <c r="B122" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C122">
         <v>50</v>
@@ -4566,7 +4611,7 @@
         <v>10</v>
       </c>
       <c r="G122" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H122">
         <v>50</v>
@@ -4577,7 +4622,7 @@
         <v>14</v>
       </c>
       <c r="B123" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C123">
         <v>70</v>
@@ -4592,7 +4637,7 @@
         <v>6</v>
       </c>
       <c r="G123" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H123">
         <v>77</v>
@@ -4603,7 +4648,7 @@
         <v>14</v>
       </c>
       <c r="B124" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C124">
         <v>120</v>
@@ -4618,7 +4663,7 @@
         <v>8.5</v>
       </c>
       <c r="G124" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H124">
         <v>124</v>
@@ -4629,7 +4674,7 @@
         <v>14</v>
       </c>
       <c r="B125" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C125">
         <v>120</v>
@@ -4644,7 +4689,7 @@
         <v>9.5</v>
       </c>
       <c r="G125" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H125">
         <v>124</v>
@@ -4655,7 +4700,7 @@
         <v>14</v>
       </c>
       <c r="B126" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C126">
         <v>120</v>
@@ -4670,7 +4715,7 @@
         <v>9.5</v>
       </c>
       <c r="G126" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H126">
         <v>124</v>
@@ -4681,7 +4726,7 @@
         <v>14</v>
       </c>
       <c r="B127" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C127">
         <v>120</v>
@@ -4696,7 +4741,7 @@
         <v>9.5</v>
       </c>
       <c r="G127" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H127">
         <v>124</v>
@@ -4707,7 +4752,7 @@
         <v>14</v>
       </c>
       <c r="B128" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C128">
         <v>20</v>
@@ -4722,7 +4767,7 @@
         <v>6.5</v>
       </c>
       <c r="G128" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H128">
         <v>26.66666666666666</v>
@@ -4733,7 +4778,7 @@
         <v>14</v>
       </c>
       <c r="B129" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C129">
         <v>20</v>
@@ -4748,7 +4793,7 @@
         <v>6.5</v>
       </c>
       <c r="G129" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H129">
         <v>26.66666666666666</v>
@@ -4759,7 +4804,7 @@
         <v>14</v>
       </c>
       <c r="B130" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C130">
         <v>20</v>
@@ -4774,7 +4819,7 @@
         <v>8</v>
       </c>
       <c r="G130" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H130">
         <v>26.66666666666666</v>
@@ -4785,7 +4830,7 @@
         <v>14</v>
       </c>
       <c r="B131" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C131">
         <v>20</v>
@@ -4800,7 +4845,7 @@
         <v>8</v>
       </c>
       <c r="G131" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H131">
         <v>26.66666666666666</v>
@@ -4811,7 +4856,7 @@
         <v>14</v>
       </c>
       <c r="B132" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C132">
         <v>20</v>
@@ -4826,7 +4871,7 @@
         <v>8.5</v>
       </c>
       <c r="G132" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H132">
         <v>26.66666666666666</v>
@@ -4837,7 +4882,7 @@
         <v>14</v>
       </c>
       <c r="B133" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C133">
         <v>20</v>
@@ -4852,7 +4897,7 @@
         <v>8.5</v>
       </c>
       <c r="G133" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H133">
         <v>26.66666666666666</v>
@@ -4863,7 +4908,7 @@
         <v>15</v>
       </c>
       <c r="B134" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C134">
         <v>20</v>
@@ -4878,7 +4923,7 @@
         <v>3</v>
       </c>
       <c r="G134" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H134">
         <v>25.33333333333333</v>
@@ -4889,7 +4934,7 @@
         <v>15</v>
       </c>
       <c r="B135" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C135">
         <v>60</v>
@@ -4904,7 +4949,7 @@
         <v>6</v>
       </c>
       <c r="G135" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H135">
         <v>72</v>
@@ -4915,7 +4960,7 @@
         <v>15</v>
       </c>
       <c r="B136" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C136">
         <v>80</v>
@@ -4930,7 +4975,7 @@
         <v>7</v>
       </c>
       <c r="G136" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H136">
         <v>88</v>
@@ -4941,7 +4986,7 @@
         <v>15</v>
       </c>
       <c r="B137" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C137">
         <v>100</v>
@@ -4956,7 +5001,7 @@
         <v>7</v>
       </c>
       <c r="G137" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H137">
         <v>103.3333333333333</v>
@@ -4967,7 +5012,7 @@
         <v>15</v>
       </c>
       <c r="B138" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C138">
         <v>70</v>
@@ -4982,7 +5027,7 @@
         <v>8</v>
       </c>
       <c r="G138" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H138">
         <v>98</v>
@@ -4993,7 +5038,7 @@
         <v>15</v>
       </c>
       <c r="B139" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C139">
         <v>80</v>
@@ -5008,7 +5053,7 @@
         <v>8.5</v>
       </c>
       <c r="G139" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H139">
         <v>101.3333333333333</v>
@@ -5019,7 +5064,7 @@
         <v>15</v>
       </c>
       <c r="B140" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C140">
         <v>20</v>
@@ -5034,7 +5079,7 @@
         <v>5</v>
       </c>
       <c r="G140" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H140">
         <v>28</v>
@@ -5045,7 +5090,7 @@
         <v>15</v>
       </c>
       <c r="B141" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C141">
         <v>30</v>
@@ -5060,7 +5105,7 @@
         <v>7</v>
       </c>
       <c r="G141" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H141">
         <v>38</v>
@@ -5071,7 +5116,7 @@
         <v>15</v>
       </c>
       <c r="B142" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C142">
         <v>40</v>
@@ -5086,7 +5131,7 @@
         <v>8</v>
       </c>
       <c r="G142" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H142">
         <v>48</v>
@@ -5097,7 +5142,7 @@
         <v>15</v>
       </c>
       <c r="B143" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C143">
         <v>40</v>
@@ -5112,7 +5157,7 @@
         <v>9</v>
       </c>
       <c r="G143" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H143">
         <v>48</v>
@@ -5123,7 +5168,7 @@
         <v>15</v>
       </c>
       <c r="B144" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C144">
         <v>30</v>
@@ -5138,7 +5183,7 @@
         <v>9</v>
       </c>
       <c r="G144" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H144">
         <v>42</v>
@@ -5149,7 +5194,7 @@
         <v>15</v>
       </c>
       <c r="B145" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C145">
         <v>30</v>
@@ -5164,7 +5209,7 @@
         <v>7</v>
       </c>
       <c r="G145" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H145">
         <v>45</v>
@@ -5175,7 +5220,7 @@
         <v>15</v>
       </c>
       <c r="B146" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C146">
         <v>50</v>
@@ -5190,7 +5235,7 @@
         <v>7.5</v>
       </c>
       <c r="G146" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H146">
         <v>63.33333333333333</v>
@@ -5201,7 +5246,7 @@
         <v>15</v>
       </c>
       <c r="B147" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C147">
         <v>50</v>
@@ -5216,7 +5261,7 @@
         <v>8</v>
       </c>
       <c r="G147" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H147">
         <v>63.33333333333333</v>
@@ -5227,7 +5272,7 @@
         <v>15</v>
       </c>
       <c r="B148" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C148">
         <v>50</v>
@@ -5242,7 +5287,7 @@
         <v>8.5</v>
       </c>
       <c r="G148" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H148">
         <v>63.33333333333333</v>
@@ -5253,7 +5298,7 @@
         <v>15</v>
       </c>
       <c r="B149" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C149">
         <v>50</v>
@@ -5268,7 +5313,7 @@
         <v>9.5</v>
       </c>
       <c r="G149" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H149">
         <v>63.33333333333333</v>
@@ -5279,7 +5324,7 @@
         <v>15</v>
       </c>
       <c r="B150" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C150">
         <v>40</v>
@@ -5294,7 +5339,7 @@
         <v>8</v>
       </c>
       <c r="G150" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H150">
         <v>56</v>
@@ -5305,7 +5350,7 @@
         <v>15</v>
       </c>
       <c r="B151" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C151">
         <v>70</v>
@@ -5320,7 +5365,7 @@
         <v>6</v>
       </c>
       <c r="G151" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H151">
         <v>84</v>
@@ -5331,7 +5376,7 @@
         <v>15</v>
       </c>
       <c r="B152" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C152">
         <v>120</v>
@@ -5346,7 +5391,7 @@
         <v>6</v>
       </c>
       <c r="G152" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H152">
         <v>124</v>
@@ -5357,7 +5402,7 @@
         <v>15</v>
       </c>
       <c r="B153" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C153">
         <v>120</v>
@@ -5372,7 +5417,7 @@
         <v>8</v>
       </c>
       <c r="G153" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H153">
         <v>140</v>
@@ -5383,7 +5428,7 @@
         <v>15</v>
       </c>
       <c r="B154" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C154">
         <v>130</v>
@@ -5398,7 +5443,7 @@
         <v>8.5</v>
       </c>
       <c r="G154" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H154">
         <v>151.6666666666667</v>
@@ -5409,7 +5454,7 @@
         <v>15</v>
       </c>
       <c r="B155" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C155">
         <v>130</v>
@@ -5424,7 +5469,7 @@
         <v>9</v>
       </c>
       <c r="G155" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H155">
         <v>151.6666666666667</v>
@@ -5435,7 +5480,7 @@
         <v>16</v>
       </c>
       <c r="B156" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C156">
         <v>20</v>
@@ -5450,7 +5495,7 @@
         <v>4</v>
       </c>
       <c r="G156" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H156">
         <v>28</v>
@@ -5461,7 +5506,7 @@
         <v>16</v>
       </c>
       <c r="B157" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C157">
         <v>40</v>
@@ -5484,7 +5529,7 @@
         <v>16</v>
       </c>
       <c r="B158" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C158">
         <v>60</v>
@@ -5499,7 +5544,7 @@
         <v>6.5</v>
       </c>
       <c r="G158" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H158">
         <v>62.00000000000001</v>
@@ -5510,7 +5555,7 @@
         <v>16</v>
       </c>
       <c r="B159" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C159">
         <v>70</v>
@@ -5525,7 +5570,7 @@
         <v>8.5</v>
       </c>
       <c r="G159" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H159">
         <v>72.33333333333334</v>
@@ -5536,7 +5581,7 @@
         <v>16</v>
       </c>
       <c r="B160" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C160">
         <v>65</v>
@@ -5551,7 +5596,7 @@
         <v>8</v>
       </c>
       <c r="G160" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H160">
         <v>67.16666666666667</v>
@@ -5562,7 +5607,7 @@
         <v>16</v>
       </c>
       <c r="B161" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C161">
         <v>60</v>
@@ -5585,7 +5630,7 @@
         <v>16</v>
       </c>
       <c r="B162" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C162">
         <v>60</v>
@@ -5600,7 +5645,7 @@
         <v>9</v>
       </c>
       <c r="G162" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H162">
         <v>66</v>
@@ -5611,7 +5656,7 @@
         <v>16</v>
       </c>
       <c r="B163" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C163">
         <v>45</v>
@@ -5626,7 +5671,7 @@
         <v>8</v>
       </c>
       <c r="G163" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H163">
         <v>62.99999999999999</v>
@@ -5637,7 +5682,7 @@
         <v>16</v>
       </c>
       <c r="B164" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C164">
         <v>45</v>
@@ -5660,7 +5705,7 @@
         <v>16</v>
       </c>
       <c r="B165" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C165">
         <v>20</v>
@@ -5675,7 +5720,7 @@
         <v>7</v>
       </c>
       <c r="G165" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H165">
         <v>26.66666666666666</v>
@@ -5686,7 +5731,7 @@
         <v>16</v>
       </c>
       <c r="B166" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C166">
         <v>20</v>
@@ -5701,7 +5746,7 @@
         <v>6</v>
       </c>
       <c r="G166" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H166">
         <v>28</v>
@@ -5712,7 +5757,7 @@
         <v>16</v>
       </c>
       <c r="B167" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C167">
         <v>20</v>
@@ -5727,7 +5772,7 @@
         <v>7</v>
       </c>
       <c r="G167" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H167">
         <v>28</v>
@@ -5738,7 +5783,7 @@
         <v>16</v>
       </c>
       <c r="B168" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C168">
         <v>20</v>
@@ -5753,7 +5798,7 @@
         <v>7</v>
       </c>
       <c r="G168" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H168">
         <v>30</v>
@@ -5764,7 +5809,7 @@
         <v>16</v>
       </c>
       <c r="B169" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C169">
         <v>22.5</v>
@@ -5779,7 +5824,7 @@
         <v>7.5</v>
       </c>
       <c r="G169" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H169">
         <v>30</v>
@@ -5790,7 +5835,7 @@
         <v>16</v>
       </c>
       <c r="B170" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C170">
         <v>22.5</v>
@@ -5805,7 +5850,7 @@
         <v>7</v>
       </c>
       <c r="G170" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H170">
         <v>31.5</v>
@@ -5816,7 +5861,7 @@
         <v>16</v>
       </c>
       <c r="B171" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C171">
         <v>25</v>
@@ -5831,7 +5876,7 @@
         <v>8</v>
       </c>
       <c r="G171" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H171">
         <v>31.66666666666666</v>
@@ -5842,7 +5887,7 @@
         <v>16</v>
       </c>
       <c r="B172" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C172">
         <v>25</v>
@@ -5857,7 +5902,7 @@
         <v>7.5</v>
       </c>
       <c r="G172" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H172">
         <v>35</v>
@@ -5868,7 +5913,7 @@
         <v>16</v>
       </c>
       <c r="B173" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C173">
         <v>25</v>
@@ -5883,7 +5928,7 @@
         <v>8</v>
       </c>
       <c r="G173" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H173">
         <v>31.66666666666666</v>
@@ -5894,7 +5939,7 @@
         <v>16</v>
       </c>
       <c r="B174" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C174">
         <v>25</v>
@@ -5909,7 +5954,7 @@
         <v>8</v>
       </c>
       <c r="G174" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H174">
         <v>37.5</v>
@@ -5920,7 +5965,7 @@
         <v>16</v>
       </c>
       <c r="B175" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C175">
         <v>40</v>
@@ -5935,7 +5980,7 @@
         <v>7.5</v>
       </c>
       <c r="G175" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H175">
         <v>50.66666666666666</v>
@@ -5946,7 +5991,7 @@
         <v>16</v>
       </c>
       <c r="B176" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C176">
         <v>40</v>
@@ -5961,7 +6006,7 @@
         <v>8.5</v>
       </c>
       <c r="G176" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H176">
         <v>50.66666666666666</v>
@@ -5972,7 +6017,7 @@
         <v>16</v>
       </c>
       <c r="B177" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C177">
         <v>40</v>
@@ -5987,7 +6032,7 @@
         <v>9</v>
       </c>
       <c r="G177" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H177">
         <v>48</v>
@@ -5998,7 +6043,7 @@
         <v>16</v>
       </c>
       <c r="B178" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C178">
         <v>22</v>
@@ -6013,7 +6058,7 @@
         <v>7</v>
       </c>
       <c r="G178" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H178">
         <v>27.86666666666667</v>
@@ -6024,7 +6069,7 @@
         <v>16</v>
       </c>
       <c r="B179" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C179">
         <v>22</v>
@@ -6047,7 +6092,7 @@
         <v>16</v>
       </c>
       <c r="B180" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C180">
         <v>22</v>
@@ -6062,7 +6107,7 @@
         <v>8.5</v>
       </c>
       <c r="G180" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H180">
         <v>27.86666666666667</v>
@@ -6073,7 +6118,7 @@
         <v>17</v>
       </c>
       <c r="B181" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C181">
         <v>20</v>
@@ -6096,7 +6141,7 @@
         <v>17</v>
       </c>
       <c r="B182" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C182">
         <v>22</v>
@@ -6119,7 +6164,7 @@
         <v>17</v>
       </c>
       <c r="B183" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C183">
         <v>20</v>
@@ -6134,7 +6179,7 @@
         <v>4</v>
       </c>
       <c r="G183" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H183">
         <v>25.33333333333333</v>
@@ -6145,7 +6190,7 @@
         <v>17</v>
       </c>
       <c r="B184" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C184">
         <v>60</v>
@@ -6168,7 +6213,7 @@
         <v>17</v>
       </c>
       <c r="B185" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C185">
         <v>80</v>
@@ -6191,7 +6236,7 @@
         <v>17</v>
       </c>
       <c r="B186" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C186">
         <v>100</v>
@@ -6214,7 +6259,7 @@
         <v>17</v>
       </c>
       <c r="B187" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C187">
         <v>110</v>
@@ -6237,7 +6282,7 @@
         <v>17</v>
       </c>
       <c r="B188" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C188">
         <v>120</v>
@@ -6252,7 +6297,7 @@
         <v>8.5</v>
       </c>
       <c r="G188" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H188">
         <v>124</v>
@@ -6263,7 +6308,7 @@
         <v>17</v>
       </c>
       <c r="B189" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C189">
         <v>80</v>
@@ -6278,7 +6323,7 @@
         <v>7.5</v>
       </c>
       <c r="G189" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H189">
         <v>112</v>
@@ -6289,7 +6334,7 @@
         <v>17</v>
       </c>
       <c r="B190" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C190">
         <v>-30</v>
@@ -6304,7 +6349,7 @@
         <v>6</v>
       </c>
       <c r="G190" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H190">
         <v>-38</v>
@@ -6315,7 +6360,7 @@
         <v>17</v>
       </c>
       <c r="B191" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C191">
         <v>-30</v>
@@ -6330,7 +6375,7 @@
         <v>6</v>
       </c>
       <c r="G191" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H191">
         <v>-38</v>
@@ -6341,7 +6386,7 @@
         <v>17</v>
       </c>
       <c r="B192" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C192">
         <v>-25</v>
@@ -6356,7 +6401,7 @@
         <v>7.5</v>
       </c>
       <c r="G192" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H192">
         <v>-33.33333333333333</v>
@@ -6367,7 +6412,7 @@
         <v>17</v>
       </c>
       <c r="B193" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C193">
         <v>-25</v>
@@ -6382,7 +6427,7 @@
         <v>7.5</v>
       </c>
       <c r="G193" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H193">
         <v>-33.33333333333333</v>
@@ -6393,7 +6438,7 @@
         <v>17</v>
       </c>
       <c r="B194" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C194">
         <v>-20</v>
@@ -6408,7 +6453,7 @@
         <v>8</v>
       </c>
       <c r="G194" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H194">
         <v>-25.33333333333333</v>
@@ -6419,7 +6464,7 @@
         <v>17</v>
       </c>
       <c r="B195" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C195">
         <v>-20</v>
@@ -6434,7 +6479,7 @@
         <v>8</v>
       </c>
       <c r="G195" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H195">
         <v>-25.33333333333333</v>
@@ -6445,7 +6490,7 @@
         <v>17</v>
       </c>
       <c r="B196" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C196">
         <v>35</v>
@@ -6460,7 +6505,7 @@
         <v>7</v>
       </c>
       <c r="G196" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H196">
         <v>52.5</v>
@@ -6471,7 +6516,7 @@
         <v>17</v>
       </c>
       <c r="B197" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C197">
         <v>25</v>
@@ -6486,7 +6531,7 @@
         <v>7</v>
       </c>
       <c r="G197" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H197">
         <v>37.5</v>
@@ -6497,7 +6542,7 @@
         <v>17</v>
       </c>
       <c r="B198" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C198">
         <v>35</v>
@@ -6512,7 +6557,7 @@
         <v>7</v>
       </c>
       <c r="G198" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H198">
         <v>52.5</v>
@@ -6523,7 +6568,7 @@
         <v>17</v>
       </c>
       <c r="B199" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C199">
         <v>25</v>
@@ -6538,7 +6583,7 @@
         <v>7</v>
       </c>
       <c r="G199" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H199">
         <v>37.5</v>
@@ -6549,7 +6594,7 @@
         <v>18</v>
       </c>
       <c r="B200" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C200">
         <v>70</v>
@@ -6564,7 +6609,7 @@
         <v>6</v>
       </c>
       <c r="G200" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H200">
         <v>84</v>
@@ -6575,7 +6620,7 @@
         <v>18</v>
       </c>
       <c r="B201" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C201">
         <v>90</v>
@@ -6598,7 +6643,7 @@
         <v>18</v>
       </c>
       <c r="B202" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C202">
         <v>120</v>
@@ -6621,7 +6666,7 @@
         <v>18</v>
       </c>
       <c r="B203" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C203">
         <v>120</v>
@@ -6644,7 +6689,7 @@
         <v>18</v>
       </c>
       <c r="B204" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C204">
         <v>120</v>
@@ -6667,7 +6712,7 @@
         <v>18</v>
       </c>
       <c r="B205" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C205">
         <v>120</v>
@@ -6690,7 +6735,7 @@
         <v>18</v>
       </c>
       <c r="B206" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C206">
         <v>120</v>
@@ -6713,7 +6758,7 @@
         <v>18</v>
       </c>
       <c r="B207" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C207">
         <v>20</v>
@@ -6728,7 +6773,7 @@
         <v>6</v>
       </c>
       <c r="G207" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H207">
         <v>28</v>
@@ -6739,7 +6784,7 @@
         <v>18</v>
       </c>
       <c r="B208" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C208">
         <v>30</v>
@@ -6762,7 +6807,7 @@
         <v>18</v>
       </c>
       <c r="B209" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C209">
         <v>35</v>
@@ -6785,7 +6830,7 @@
         <v>18</v>
       </c>
       <c r="B210" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C210">
         <v>35</v>
@@ -6808,7 +6853,7 @@
         <v>18</v>
       </c>
       <c r="B211" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C211">
         <v>35</v>
@@ -6831,7 +6876,7 @@
         <v>18</v>
       </c>
       <c r="B212" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C212">
         <v>22</v>
@@ -6846,7 +6891,7 @@
         <v>7.5</v>
       </c>
       <c r="G212" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H212">
         <v>27.86666666666667</v>
@@ -6857,7 +6902,7 @@
         <v>18</v>
       </c>
       <c r="B213" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C213">
         <v>22</v>
@@ -6872,7 +6917,7 @@
         <v>7.5</v>
       </c>
       <c r="G213" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H213">
         <v>30.8</v>
@@ -6883,7 +6928,7 @@
         <v>18</v>
       </c>
       <c r="B214" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C214">
         <v>22</v>
@@ -6898,7 +6943,7 @@
         <v>8</v>
       </c>
       <c r="G214" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H214">
         <v>27.86666666666667</v>
@@ -6909,7 +6954,7 @@
         <v>18</v>
       </c>
       <c r="B215" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C215">
         <v>22</v>
@@ -6924,7 +6969,7 @@
         <v>8</v>
       </c>
       <c r="G215" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H215">
         <v>30.8</v>
@@ -6935,7 +6980,7 @@
         <v>18</v>
       </c>
       <c r="B216" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C216">
         <v>22</v>
@@ -6950,7 +6995,7 @@
         <v>8.5</v>
       </c>
       <c r="G216" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H216">
         <v>27.86666666666667</v>
@@ -6961,7 +7006,7 @@
         <v>18</v>
       </c>
       <c r="B217" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C217">
         <v>22</v>
@@ -6976,7 +7021,7 @@
         <v>8</v>
       </c>
       <c r="G217" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H217">
         <v>30.8</v>
@@ -6987,7 +7032,7 @@
         <v>18</v>
       </c>
       <c r="B218" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C218">
         <v>25</v>
@@ -7002,7 +7047,7 @@
         <v>8</v>
       </c>
       <c r="G218" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H218">
         <v>31.66666666666666</v>
@@ -7013,7 +7058,7 @@
         <v>18</v>
       </c>
       <c r="B219" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C219">
         <v>25</v>
@@ -7028,7 +7073,7 @@
         <v>6.5</v>
       </c>
       <c r="G219" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H219">
         <v>31.66666666666666</v>
@@ -7039,7 +7084,7 @@
         <v>18</v>
       </c>
       <c r="B220" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C220">
         <v>25</v>
@@ -7054,7 +7099,7 @@
         <v>8</v>
       </c>
       <c r="G220" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H220">
         <v>31.66666666666666</v>
@@ -7065,7 +7110,7 @@
         <v>18</v>
       </c>
       <c r="B221" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C221">
         <v>25</v>
@@ -7080,7 +7125,7 @@
         <v>7.5</v>
       </c>
       <c r="G221" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H221">
         <v>31.66666666666666</v>
@@ -7091,7 +7136,7 @@
         <v>18</v>
       </c>
       <c r="B222" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C222">
         <v>25</v>
@@ -7106,7 +7151,7 @@
         <v>9</v>
       </c>
       <c r="G222" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H222">
         <v>31.66666666666666</v>
@@ -7117,7 +7162,7 @@
         <v>18</v>
       </c>
       <c r="B223" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C223">
         <v>25</v>
@@ -7132,7 +7177,7 @@
         <v>9</v>
       </c>
       <c r="G223" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H223">
         <v>31.66666666666666</v>
@@ -7143,7 +7188,7 @@
         <v>19</v>
       </c>
       <c r="B224" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C224">
         <v>70</v>
@@ -7158,7 +7203,7 @@
         <v>6.5</v>
       </c>
       <c r="G224" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H224">
         <v>84</v>
@@ -7169,7 +7214,7 @@
         <v>19</v>
       </c>
       <c r="B225" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C225">
         <v>85</v>
@@ -7184,7 +7229,7 @@
         <v>8</v>
       </c>
       <c r="G225" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H225">
         <v>119</v>
@@ -7195,7 +7240,7 @@
         <v>19</v>
       </c>
       <c r="B226" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C226">
         <v>85</v>
@@ -7210,7 +7255,7 @@
         <v>9</v>
       </c>
       <c r="G226" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H226">
         <v>119</v>
@@ -7221,7 +7266,7 @@
         <v>19</v>
       </c>
       <c r="B227" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C227">
         <v>85</v>
@@ -7236,7 +7281,7 @@
         <v>10</v>
       </c>
       <c r="G227" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H227">
         <v>113.3333333333333</v>
@@ -7247,7 +7292,7 @@
         <v>19</v>
       </c>
       <c r="B228" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C228">
         <v>30</v>
@@ -7262,7 +7307,7 @@
         <v>6</v>
       </c>
       <c r="G228" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H228">
         <v>36</v>
@@ -7273,7 +7318,7 @@
         <v>19</v>
       </c>
       <c r="B229" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C229">
         <v>30</v>
@@ -7288,7 +7333,7 @@
         <v>6</v>
       </c>
       <c r="G229" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H229">
         <v>38</v>
@@ -7299,7 +7344,7 @@
         <v>19</v>
       </c>
       <c r="B230" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C230">
         <v>40</v>
@@ -7314,7 +7359,7 @@
         <v>8</v>
       </c>
       <c r="G230" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H230">
         <v>50.66666666666666</v>
@@ -7325,7 +7370,7 @@
         <v>19</v>
       </c>
       <c r="B231" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C231">
         <v>40</v>
@@ -7340,7 +7385,7 @@
         <v>9</v>
       </c>
       <c r="G231" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H231">
         <v>50.66666666666666</v>
@@ -7351,7 +7396,7 @@
         <v>19</v>
       </c>
       <c r="B232" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C232">
         <v>40</v>
@@ -7366,7 +7411,7 @@
         <v>10</v>
       </c>
       <c r="G232" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H232">
         <v>49.33333333333334</v>
@@ -7377,7 +7422,7 @@
         <v>19</v>
       </c>
       <c r="B233" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C233">
         <v>40</v>
@@ -7392,7 +7437,7 @@
         <v>6.5</v>
       </c>
       <c r="G233" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H233">
         <v>56</v>
@@ -7403,7 +7448,7 @@
         <v>19</v>
       </c>
       <c r="B234" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C234">
         <v>40</v>
@@ -7418,7 +7463,7 @@
         <v>6.5</v>
       </c>
       <c r="G234" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H234">
         <v>56</v>
@@ -7429,7 +7474,7 @@
         <v>19</v>
       </c>
       <c r="B235" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C235">
         <v>40</v>
@@ -7444,7 +7489,7 @@
         <v>7.5</v>
       </c>
       <c r="G235" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H235">
         <v>56</v>
@@ -7455,7 +7500,7 @@
         <v>19</v>
       </c>
       <c r="B236" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C236">
         <v>40</v>
@@ -7470,7 +7515,7 @@
         <v>9</v>
       </c>
       <c r="G236" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H236">
         <v>56</v>
@@ -7481,7 +7526,7 @@
         <v>19</v>
       </c>
       <c r="B237" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C237">
         <v>60</v>
@@ -7496,7 +7541,7 @@
         <v>8</v>
       </c>
       <c r="G237" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H237">
         <v>80</v>
@@ -7507,7 +7552,7 @@
         <v>19</v>
       </c>
       <c r="B238" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C238">
         <v>60</v>
@@ -7522,7 +7567,7 @@
         <v>7</v>
       </c>
       <c r="G238" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H238">
         <v>80</v>
@@ -7533,7 +7578,7 @@
         <v>19</v>
       </c>
       <c r="B239" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C239">
         <v>60</v>
@@ -7548,7 +7593,7 @@
         <v>8.5</v>
       </c>
       <c r="G239" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H239">
         <v>80</v>
@@ -7559,7 +7604,7 @@
         <v>19</v>
       </c>
       <c r="B240" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C240">
         <v>60</v>
@@ -7574,7 +7619,7 @@
         <v>8</v>
       </c>
       <c r="G240" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H240">
         <v>80</v>
@@ -7585,7 +7630,7 @@
         <v>19</v>
       </c>
       <c r="B241" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C241">
         <v>60</v>
@@ -7600,7 +7645,7 @@
         <v>9</v>
       </c>
       <c r="G241" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H241">
         <v>80</v>
@@ -7611,7 +7656,7 @@
         <v>19</v>
       </c>
       <c r="B242" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C242">
         <v>60</v>
@@ -7626,7 +7671,7 @@
         <v>9</v>
       </c>
       <c r="G242" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H242">
         <v>80</v>
@@ -7637,7 +7682,7 @@
         <v>20</v>
       </c>
       <c r="B243" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C243">
         <v>60</v>
@@ -7652,7 +7697,7 @@
         <v>4</v>
       </c>
       <c r="G243" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H243">
         <v>76</v>
@@ -7663,7 +7708,7 @@
         <v>20</v>
       </c>
       <c r="B244" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C244">
         <v>100</v>
@@ -7678,7 +7723,7 @@
         <v>6</v>
       </c>
       <c r="G244" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H244">
         <v>116.6666666666667</v>
@@ -7689,7 +7734,7 @@
         <v>20</v>
       </c>
       <c r="B245" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C245">
         <v>130</v>
@@ -7704,7 +7749,7 @@
         <v>7</v>
       </c>
       <c r="G245" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H245">
         <v>134.3333333333333</v>
@@ -7715,7 +7760,7 @@
         <v>20</v>
       </c>
       <c r="B246" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C246">
         <v>150</v>
@@ -7730,7 +7775,7 @@
         <v>8.5</v>
       </c>
       <c r="G246" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H246">
         <v>155</v>
@@ -7741,7 +7786,7 @@
         <v>20</v>
       </c>
       <c r="B247" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C247">
         <v>120</v>
@@ -7756,7 +7801,7 @@
         <v>7.5</v>
       </c>
       <c r="G247" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H247">
         <v>140</v>
@@ -7767,7 +7812,7 @@
         <v>20</v>
       </c>
       <c r="B248" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C248">
         <v>120</v>
@@ -7782,7 +7827,7 @@
         <v>7.5</v>
       </c>
       <c r="G248" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H248">
         <v>140</v>
@@ -7793,7 +7838,7 @@
         <v>20</v>
       </c>
       <c r="B249" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C249">
         <v>120</v>
@@ -7808,7 +7853,7 @@
         <v>8</v>
       </c>
       <c r="G249" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H249">
         <v>140</v>
@@ -7819,7 +7864,7 @@
         <v>20</v>
       </c>
       <c r="B250" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C250">
         <v>120</v>
@@ -7834,7 +7879,7 @@
         <v>8.5</v>
       </c>
       <c r="G250" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H250">
         <v>140</v>
@@ -7845,7 +7890,7 @@
         <v>20</v>
       </c>
       <c r="B251" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C251">
         <v>120</v>
@@ -7860,7 +7905,7 @@
         <v>9</v>
       </c>
       <c r="G251" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H251">
         <v>140</v>
@@ -7871,7 +7916,7 @@
         <v>20</v>
       </c>
       <c r="B252" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C252">
         <v>40</v>
@@ -7886,7 +7931,7 @@
         <v>5</v>
       </c>
       <c r="G252" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H252">
         <v>50.66666666666666</v>
@@ -7897,7 +7942,7 @@
         <v>20</v>
       </c>
       <c r="B253" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C253">
         <v>50</v>
@@ -7912,7 +7957,7 @@
         <v>6</v>
       </c>
       <c r="G253" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H253">
         <v>58.33333333333334</v>
@@ -7923,7 +7968,7 @@
         <v>20</v>
       </c>
       <c r="B254" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C254">
         <v>60</v>
@@ -7938,7 +7983,7 @@
         <v>7</v>
       </c>
       <c r="G254" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H254">
         <v>70</v>
@@ -7949,7 +7994,7 @@
         <v>20</v>
       </c>
       <c r="B255" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C255">
         <v>60</v>
@@ -7964,7 +8009,7 @@
         <v>8</v>
       </c>
       <c r="G255" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H255">
         <v>70</v>
@@ -7975,7 +8020,7 @@
         <v>20</v>
       </c>
       <c r="B256" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C256">
         <v>60</v>
@@ -7990,7 +8035,7 @@
         <v>8.5</v>
       </c>
       <c r="G256" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H256">
         <v>70</v>
@@ -8001,7 +8046,7 @@
         <v>20</v>
       </c>
       <c r="B257" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C257">
         <v>60</v>
@@ -8016,7 +8061,7 @@
         <v>8.5</v>
       </c>
       <c r="G257" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H257">
         <v>70</v>
@@ -8027,7 +8072,7 @@
         <v>20</v>
       </c>
       <c r="B258" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C258">
         <v>60</v>
@@ -8042,7 +8087,7 @@
         <v>8</v>
       </c>
       <c r="G258" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H258">
         <v>70</v>
@@ -8053,7 +8098,7 @@
         <v>20</v>
       </c>
       <c r="B259" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C259">
         <v>40</v>
@@ -8068,7 +8113,7 @@
         <v>5</v>
       </c>
       <c r="G259" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H259">
         <v>53.33333333333333</v>
@@ -8079,7 +8124,7 @@
         <v>20</v>
       </c>
       <c r="B260" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C260">
         <v>50</v>
@@ -8094,7 +8139,7 @@
         <v>7</v>
       </c>
       <c r="G260" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H260">
         <v>63.33333333333333</v>
@@ -8105,7 +8150,7 @@
         <v>20</v>
       </c>
       <c r="B261" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C261">
         <v>50</v>
@@ -8120,7 +8165,7 @@
         <v>7</v>
       </c>
       <c r="G261" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H261">
         <v>63.33333333333333</v>
@@ -8131,7 +8176,7 @@
         <v>20</v>
       </c>
       <c r="B262" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C262">
         <v>50</v>
@@ -8146,7 +8191,7 @@
         <v>7.5</v>
       </c>
       <c r="G262" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H262">
         <v>63.33333333333333</v>
@@ -8157,7 +8202,7 @@
         <v>20</v>
       </c>
       <c r="B263" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C263">
         <v>50</v>
@@ -8172,7 +8217,7 @@
         <v>8</v>
       </c>
       <c r="G263" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H263">
         <v>66.66666666666666</v>
@@ -8183,7 +8228,7 @@
         <v>20</v>
       </c>
       <c r="B264" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C264">
         <v>20</v>
@@ -8198,7 +8243,7 @@
         <v>7</v>
       </c>
       <c r="G264" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H264">
         <v>26.66666666666666</v>
@@ -8209,7 +8254,7 @@
         <v>20</v>
       </c>
       <c r="B265" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C265">
         <v>20</v>
@@ -8224,7 +8269,7 @@
         <v>7</v>
       </c>
       <c r="G265" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H265">
         <v>28</v>
@@ -8235,7 +8280,7 @@
         <v>20</v>
       </c>
       <c r="B266" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C266">
         <v>25</v>
@@ -8250,7 +8295,7 @@
         <v>8.5</v>
       </c>
       <c r="G266" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H266">
         <v>31.66666666666666</v>
@@ -8261,7 +8306,7 @@
         <v>20</v>
       </c>
       <c r="B267" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C267">
         <v>25</v>
@@ -8276,7 +8321,7 @@
         <v>7.5</v>
       </c>
       <c r="G267" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H267">
         <v>33.33333333333333</v>
@@ -8287,7 +8332,7 @@
         <v>20</v>
       </c>
       <c r="B268" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C268">
         <v>25</v>
@@ -8302,7 +8347,7 @@
         <v>8.5</v>
       </c>
       <c r="G268" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H268">
         <v>31.66666666666666</v>
@@ -8313,7 +8358,7 @@
         <v>20</v>
       </c>
       <c r="B269" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C269">
         <v>25</v>
@@ -8328,7 +8373,7 @@
         <v>8</v>
       </c>
       <c r="G269" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H269">
         <v>35</v>
@@ -8339,7 +8384,7 @@
         <v>20</v>
       </c>
       <c r="B270" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C270">
         <v>25</v>
@@ -8354,7 +8399,7 @@
         <v>9</v>
       </c>
       <c r="G270" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H270">
         <v>31.66666666666666</v>
@@ -8365,7 +8410,7 @@
         <v>20</v>
       </c>
       <c r="B271" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C271">
         <v>25</v>
@@ -8380,7 +8425,7 @@
         <v>9</v>
       </c>
       <c r="G271" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H271">
         <v>37.5</v>
@@ -8391,7 +8436,7 @@
         <v>21</v>
       </c>
       <c r="B272" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C272">
         <v>20</v>
@@ -8414,7 +8459,7 @@
         <v>21</v>
       </c>
       <c r="B273" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C273">
         <v>60</v>
@@ -8437,7 +8482,7 @@
         <v>21</v>
       </c>
       <c r="B274" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C274">
         <v>100</v>
@@ -8460,7 +8505,7 @@
         <v>21</v>
       </c>
       <c r="B275" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C275">
         <v>100</v>
@@ -8483,7 +8528,7 @@
         <v>21</v>
       </c>
       <c r="B276" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C276">
         <v>60</v>
@@ -8506,7 +8551,7 @@
         <v>21</v>
       </c>
       <c r="B277" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C277">
         <v>90</v>
@@ -8529,7 +8574,7 @@
         <v>21</v>
       </c>
       <c r="B278" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C278">
         <v>110</v>
@@ -8552,7 +8597,7 @@
         <v>21</v>
       </c>
       <c r="B279" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C279">
         <v>30</v>
@@ -8575,7 +8620,7 @@
         <v>21</v>
       </c>
       <c r="B280" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C280">
         <v>40</v>
@@ -8598,7 +8643,7 @@
         <v>21</v>
       </c>
       <c r="B281" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C281">
         <v>40</v>
@@ -8621,7 +8666,7 @@
         <v>21</v>
       </c>
       <c r="B282" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C282">
         <v>30</v>
@@ -8644,7 +8689,7 @@
         <v>21</v>
       </c>
       <c r="B283" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C283">
         <v>30</v>
@@ -8667,7 +8712,7 @@
         <v>21</v>
       </c>
       <c r="B284" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C284">
         <v>40</v>
@@ -8690,7 +8735,7 @@
         <v>21</v>
       </c>
       <c r="B285" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C285">
         <v>40</v>
@@ -8713,7 +8758,7 @@
         <v>21</v>
       </c>
       <c r="B286" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C286">
         <v>40</v>
@@ -8736,7 +8781,7 @@
         <v>21</v>
       </c>
       <c r="B287" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C287">
         <v>40</v>
@@ -8759,7 +8804,7 @@
         <v>21</v>
       </c>
       <c r="B288" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C288">
         <v>60</v>
@@ -8782,7 +8827,7 @@
         <v>21</v>
       </c>
       <c r="B289" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C289">
         <v>60</v>
@@ -8805,7 +8850,7 @@
         <v>21</v>
       </c>
       <c r="B290" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C290">
         <v>60</v>
@@ -8828,7 +8873,7 @@
         <v>21</v>
       </c>
       <c r="B291" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C291">
         <v>60</v>
@@ -8851,7 +8896,7 @@
         <v>21</v>
       </c>
       <c r="B292" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C292">
         <v>60</v>
@@ -8874,7 +8919,7 @@
         <v>21</v>
       </c>
       <c r="B293" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C293">
         <v>60</v>
@@ -8897,7 +8942,7 @@
         <v>22</v>
       </c>
       <c r="B294" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C294">
         <v>20</v>
@@ -8912,7 +8957,7 @@
         <v>3</v>
       </c>
       <c r="G294" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H294">
         <v>28</v>
@@ -8923,7 +8968,7 @@
         <v>22</v>
       </c>
       <c r="B295" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C295">
         <v>60</v>
@@ -8938,7 +8983,7 @@
         <v>6</v>
       </c>
       <c r="G295" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H295">
         <v>76</v>
@@ -8949,7 +8994,7 @@
         <v>22</v>
       </c>
       <c r="B296" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C296">
         <v>110</v>
@@ -8964,7 +9009,7 @@
         <v>7.5</v>
       </c>
       <c r="G296" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H296">
         <v>121</v>
@@ -8975,7 +9020,7 @@
         <v>22</v>
       </c>
       <c r="B297" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C297">
         <v>70</v>
@@ -8990,7 +9035,7 @@
         <v>8</v>
       </c>
       <c r="G297" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H297">
         <v>116.6666666666667</v>
@@ -9001,7 +9046,7 @@
         <v>22</v>
       </c>
       <c r="B298" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C298">
         <v>80</v>
@@ -9016,7 +9061,7 @@
         <v>8.5</v>
       </c>
       <c r="G298" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H298">
         <v>112</v>
@@ -9027,7 +9072,7 @@
         <v>22</v>
       </c>
       <c r="B299" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C299">
         <v>60</v>
@@ -9042,7 +9087,7 @@
         <v>5</v>
       </c>
       <c r="G299" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H299">
         <v>80</v>
@@ -9053,7 +9098,7 @@
         <v>22</v>
       </c>
       <c r="B300" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C300">
         <v>110</v>
@@ -9068,7 +9113,7 @@
         <v>6.5</v>
       </c>
       <c r="G300" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H300">
         <v>128.3333333333333</v>
@@ -9079,7 +9124,7 @@
         <v>22</v>
       </c>
       <c r="B301" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C301">
         <v>140</v>
@@ -9094,7 +9139,7 @@
         <v>7</v>
       </c>
       <c r="G301" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H301">
         <v>144.6666666666667</v>
@@ -9105,7 +9150,7 @@
         <v>22</v>
       </c>
       <c r="B302" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C302">
         <v>160</v>
@@ -9120,7 +9165,7 @@
         <v>8.5</v>
       </c>
       <c r="G302" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H302">
         <v>165.3333333333333</v>
@@ -9131,7 +9176,7 @@
         <v>22</v>
       </c>
       <c r="B303" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C303">
         <v>170</v>
@@ -9146,7 +9191,7 @@
         <v>9</v>
       </c>
       <c r="G303" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H303">
         <v>175.6666666666667</v>
@@ -9157,7 +9202,7 @@
         <v>22</v>
       </c>
       <c r="B304" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C304">
         <v>30</v>
@@ -9172,7 +9217,7 @@
         <v>7</v>
       </c>
       <c r="G304" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H304">
         <v>40</v>
@@ -9183,7 +9228,7 @@
         <v>22</v>
       </c>
       <c r="B305" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C305">
         <v>40</v>
@@ -9198,7 +9243,7 @@
         <v>7</v>
       </c>
       <c r="G305" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H305">
         <v>44</v>
@@ -9209,7 +9254,7 @@
         <v>22</v>
       </c>
       <c r="B306" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C306">
         <v>50</v>
@@ -9224,7 +9269,7 @@
         <v>9.5</v>
       </c>
       <c r="G306" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H306">
         <v>53.33333333333334</v>
@@ -9235,7 +9280,7 @@
         <v>22</v>
       </c>
       <c r="B307" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C307">
         <v>40</v>
@@ -9250,7 +9295,7 @@
         <v>8.5</v>
       </c>
       <c r="G307" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H307">
         <v>53.33333333333333</v>
@@ -9261,7 +9306,7 @@
         <v>23</v>
       </c>
       <c r="B308" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C308">
         <v>70</v>
@@ -9284,7 +9329,7 @@
         <v>23</v>
       </c>
       <c r="B309" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C309">
         <v>120</v>
@@ -9307,7 +9352,7 @@
         <v>23</v>
       </c>
       <c r="B310" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C310">
         <v>140</v>
@@ -9330,7 +9375,7 @@
         <v>23</v>
       </c>
       <c r="B311" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C311">
         <v>140</v>
@@ -9353,7 +9398,7 @@
         <v>23</v>
       </c>
       <c r="B312" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C312">
         <v>120</v>
@@ -9376,7 +9421,7 @@
         <v>23</v>
       </c>
       <c r="B313" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C313">
         <v>20</v>
@@ -9399,7 +9444,7 @@
         <v>23</v>
       </c>
       <c r="B314" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C314">
         <v>40</v>
@@ -9422,7 +9467,7 @@
         <v>23</v>
       </c>
       <c r="B315" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C315">
         <v>60</v>
@@ -9445,7 +9490,7 @@
         <v>23</v>
       </c>
       <c r="B316" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C316">
         <v>70</v>
@@ -9468,7 +9513,7 @@
         <v>23</v>
       </c>
       <c r="B317" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C317">
         <v>80</v>
@@ -9491,7 +9536,7 @@
         <v>23</v>
       </c>
       <c r="B318" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C318">
         <v>75</v>
@@ -9514,7 +9559,7 @@
         <v>23</v>
       </c>
       <c r="B319" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C319">
         <v>60</v>
@@ -9537,7 +9582,7 @@
         <v>23</v>
       </c>
       <c r="B320" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C320">
         <v>60</v>
@@ -9560,7 +9605,7 @@
         <v>23</v>
       </c>
       <c r="B321" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C321">
         <v>60</v>
@@ -9583,7 +9628,7 @@
         <v>23</v>
       </c>
       <c r="B322" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C322">
         <v>65</v>
@@ -9606,7 +9651,7 @@
         <v>23</v>
       </c>
       <c r="B323" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C323">
         <v>65</v>
@@ -9629,7 +9674,7 @@
         <v>23</v>
       </c>
       <c r="B324" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C324">
         <v>65</v>
@@ -9652,7 +9697,7 @@
         <v>23</v>
       </c>
       <c r="B325" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C325">
         <v>65</v>
@@ -9675,7 +9720,7 @@
         <v>23</v>
       </c>
       <c r="B326" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C326">
         <v>65</v>
@@ -9698,7 +9743,7 @@
         <v>23</v>
       </c>
       <c r="B327" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C327">
         <v>65</v>
@@ -9721,7 +9766,7 @@
         <v>23</v>
       </c>
       <c r="B328" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C328">
         <v>65</v>
@@ -9744,7 +9789,7 @@
         <v>23</v>
       </c>
       <c r="B329" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C329">
         <v>65</v>
@@ -9767,7 +9812,7 @@
         <v>24</v>
       </c>
       <c r="B330" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C330">
         <v>20</v>
@@ -9782,7 +9827,7 @@
         <v>3</v>
       </c>
       <c r="G330" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H330">
         <v>25.33333333333333</v>
@@ -9793,7 +9838,7 @@
         <v>24</v>
       </c>
       <c r="B331" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C331">
         <v>70</v>
@@ -9808,7 +9853,7 @@
         <v>6</v>
       </c>
       <c r="G331" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H331">
         <v>81.66666666666667</v>
@@ -9819,7 +9864,7 @@
         <v>24</v>
       </c>
       <c r="B332" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C332">
         <v>90</v>
@@ -9834,7 +9879,7 @@
         <v>6</v>
       </c>
       <c r="G332" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H332">
         <v>93.00000000000001</v>
@@ -9845,7 +9890,7 @@
         <v>24</v>
       </c>
       <c r="B333" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C333">
         <v>120</v>
@@ -9860,7 +9905,7 @@
         <v>7.5</v>
       </c>
       <c r="G333" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H333">
         <v>124</v>
@@ -9871,7 +9916,7 @@
         <v>24</v>
       </c>
       <c r="B334" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C334">
         <v>140</v>
@@ -9886,7 +9931,7 @@
         <v>10</v>
       </c>
       <c r="G334" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H334">
         <v>140</v>
@@ -9897,7 +9942,7 @@
         <v>24</v>
       </c>
       <c r="B335" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C335">
         <v>80</v>
@@ -9912,7 +9957,7 @@
         <v>8.5</v>
       </c>
       <c r="G335" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H335">
         <v>133.3333333333333</v>
@@ -9923,7 +9968,7 @@
         <v>24</v>
       </c>
       <c r="B336" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C336">
         <v>80</v>
@@ -9938,7 +9983,7 @@
         <v>10</v>
       </c>
       <c r="G336" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H336">
         <v>101.3333333333333</v>
@@ -9949,7 +9994,7 @@
         <v>24</v>
       </c>
       <c r="B337" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C337">
         <v>20</v>
@@ -9964,7 +10009,7 @@
         <v>4</v>
       </c>
       <c r="G337" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H337">
         <v>25.33333333333333</v>
@@ -9975,7 +10020,7 @@
         <v>24</v>
       </c>
       <c r="B338" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C338">
         <v>40</v>
@@ -9990,7 +10035,7 @@
         <v>6</v>
       </c>
       <c r="G338" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H338">
         <v>50.66666666666666</v>
@@ -10001,7 +10046,7 @@
         <v>24</v>
       </c>
       <c r="B339" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C339">
         <v>60</v>
@@ -10016,7 +10061,7 @@
         <v>7</v>
       </c>
       <c r="G339" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H339">
         <v>66</v>
@@ -10027,7 +10072,7 @@
         <v>24</v>
       </c>
       <c r="B340" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C340">
         <v>70</v>
@@ -10042,7 +10087,7 @@
         <v>8.5</v>
       </c>
       <c r="G340" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H340">
         <v>77</v>
@@ -10053,7 +10098,7 @@
         <v>24</v>
       </c>
       <c r="B341" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C341">
         <v>75</v>
@@ -10068,7 +10113,7 @@
         <v>8.75</v>
       </c>
       <c r="G341" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H341">
         <v>77.50000000000001</v>
@@ -10079,7 +10124,7 @@
         <v>24</v>
       </c>
       <c r="B342" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C342">
         <v>50</v>
@@ -10094,7 +10139,7 @@
         <v>8</v>
       </c>
       <c r="G342" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H342">
         <v>66.66666666666666</v>
@@ -10105,7 +10150,7 @@
         <v>24</v>
       </c>
       <c r="B343" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C343">
         <v>40</v>
@@ -10120,7 +10165,7 @@
         <v>6</v>
       </c>
       <c r="G343" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H343">
         <v>50.66666666666666</v>
@@ -10131,7 +10176,7 @@
         <v>24</v>
       </c>
       <c r="B344" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C344">
         <v>50</v>
@@ -10146,7 +10191,7 @@
         <v>6.5</v>
       </c>
       <c r="G344" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H344">
         <v>63.33333333333333</v>
@@ -10157,7 +10202,7 @@
         <v>24</v>
       </c>
       <c r="B345" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C345">
         <v>63</v>
@@ -10172,7 +10217,7 @@
         <v>8</v>
       </c>
       <c r="G345" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H345">
         <v>75.59999999999999</v>
@@ -10183,7 +10228,7 @@
         <v>24</v>
       </c>
       <c r="B346" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C346">
         <v>63</v>
@@ -10198,7 +10243,7 @@
         <v>8.5</v>
       </c>
       <c r="G346" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H346">
         <v>75.59999999999999</v>
@@ -10209,7 +10254,7 @@
         <v>24</v>
       </c>
       <c r="B347" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C347">
         <v>11</v>
@@ -10224,7 +10269,7 @@
         <v>5</v>
       </c>
       <c r="G347" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H347">
         <v>16.5</v>
@@ -10235,7 +10280,7 @@
         <v>24</v>
       </c>
       <c r="B348" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C348">
         <v>32</v>
@@ -10250,7 +10295,7 @@
         <v>5</v>
       </c>
       <c r="G348" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H348">
         <v>48</v>
@@ -10261,7 +10306,7 @@
         <v>24</v>
       </c>
       <c r="B349" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C349">
         <v>33</v>
@@ -10276,7 +10321,7 @@
         <v>7</v>
       </c>
       <c r="G349" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H349">
         <v>49.5</v>
@@ -10287,7 +10332,7 @@
         <v>24</v>
       </c>
       <c r="B350" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C350">
         <v>59</v>
@@ -10302,7 +10347,7 @@
         <v>8</v>
       </c>
       <c r="G350" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H350">
         <v>82.59999999999999</v>
@@ -10313,7 +10358,7 @@
         <v>24</v>
       </c>
       <c r="B351" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C351">
         <v>39</v>
@@ -10328,7 +10373,7 @@
         <v>9</v>
       </c>
       <c r="G351" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H351">
         <v>58.5</v>
@@ -10339,7 +10384,7 @@
         <v>24</v>
       </c>
       <c r="B352" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C352">
         <v>66</v>
@@ -10354,7 +10399,7 @@
         <v>9</v>
       </c>
       <c r="G352" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H352">
         <v>92.39999999999999</v>
@@ -10365,7 +10410,7 @@
         <v>25</v>
       </c>
       <c r="B353" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C353">
         <v>70</v>
@@ -10380,7 +10425,7 @@
         <v>6</v>
       </c>
       <c r="G353" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H353">
         <v>81.66666666666667</v>
@@ -10391,7 +10436,7 @@
         <v>25</v>
       </c>
       <c r="B354" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C354">
         <v>120</v>
@@ -10406,7 +10451,7 @@
         <v>6</v>
       </c>
       <c r="G354" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H354">
         <v>124</v>
@@ -10417,7 +10462,7 @@
         <v>25</v>
       </c>
       <c r="B355" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C355">
         <v>140</v>
@@ -10432,7 +10477,7 @@
         <v>6.5</v>
       </c>
       <c r="G355" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H355">
         <v>144.6666666666667</v>
@@ -10443,7 +10488,7 @@
         <v>25</v>
       </c>
       <c r="B356" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C356">
         <v>160</v>
@@ -10458,7 +10503,7 @@
         <v>8.5</v>
       </c>
       <c r="G356" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H356">
         <v>165.3333333333333</v>
@@ -10469,7 +10514,7 @@
         <v>25</v>
       </c>
       <c r="B357" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C357">
         <v>140</v>
@@ -10484,7 +10529,7 @@
         <v>8.5</v>
       </c>
       <c r="G357" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H357">
         <v>163.3333333333333</v>
@@ -10495,7 +10540,7 @@
         <v>25</v>
       </c>
       <c r="B358" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C358">
         <v>140</v>
@@ -10510,7 +10555,7 @@
         <v>9</v>
       </c>
       <c r="G358" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H358">
         <v>163.3333333333333</v>
@@ -10521,7 +10566,7 @@
         <v>25</v>
       </c>
       <c r="B359" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C359">
         <v>120</v>
@@ -10536,7 +10581,7 @@
         <v>9</v>
       </c>
       <c r="G359" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H359">
         <v>144</v>
@@ -10547,7 +10592,7 @@
         <v>25</v>
       </c>
       <c r="B360" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C360">
         <v>30</v>
@@ -10562,7 +10607,7 @@
         <v>6</v>
       </c>
       <c r="G360" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H360">
         <v>38</v>
@@ -10573,7 +10618,7 @@
         <v>25</v>
       </c>
       <c r="B361" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C361">
         <v>40</v>
@@ -10588,7 +10633,7 @@
         <v>7</v>
       </c>
       <c r="G361" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H361">
         <v>48</v>
@@ -10599,7 +10644,7 @@
         <v>25</v>
       </c>
       <c r="B362" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C362">
         <v>50</v>
@@ -10614,7 +10659,7 @@
         <v>8</v>
       </c>
       <c r="G362" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H362">
         <v>53.33333333333334</v>
@@ -10625,7 +10670,7 @@
         <v>25</v>
       </c>
       <c r="B363" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C363">
         <v>55</v>
@@ -10640,7 +10685,7 @@
         <v>10</v>
       </c>
       <c r="G363" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H363">
         <v>56.83333333333334</v>
@@ -10651,7 +10696,7 @@
         <v>25</v>
       </c>
       <c r="B364" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C364">
         <v>45</v>
@@ -10666,7 +10711,7 @@
         <v>9</v>
       </c>
       <c r="G364" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H364">
         <v>52.5</v>
@@ -10677,7 +10722,7 @@
         <v>25</v>
       </c>
       <c r="B365" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C365">
         <v>45</v>
@@ -10692,7 +10737,7 @@
         <v>9.5</v>
       </c>
       <c r="G365" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H365">
         <v>52.5</v>
@@ -10703,7 +10748,7 @@
         <v>25</v>
       </c>
       <c r="B366" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C366">
         <v>45</v>
@@ -10718,7 +10763,7 @@
         <v>7</v>
       </c>
       <c r="G366" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H366">
         <v>57</v>
@@ -10729,7 +10774,7 @@
         <v>25</v>
       </c>
       <c r="B367" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C367">
         <v>50</v>
@@ -10744,7 +10789,7 @@
         <v>8</v>
       </c>
       <c r="G367" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H367">
         <v>63.33333333333333</v>
@@ -10755,7 +10800,7 @@
         <v>25</v>
       </c>
       <c r="B368" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C368">
         <v>50</v>
@@ -10770,7 +10815,7 @@
         <v>8</v>
       </c>
       <c r="G368" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H368">
         <v>63.33333333333333</v>
@@ -10781,7 +10826,7 @@
         <v>25</v>
       </c>
       <c r="B369" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C369">
         <v>50</v>
@@ -10796,7 +10841,7 @@
         <v>8</v>
       </c>
       <c r="G369" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H369">
         <v>63.33333333333333</v>
@@ -10807,7 +10852,7 @@
         <v>25</v>
       </c>
       <c r="B370" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C370">
         <v>40</v>
@@ -10822,7 +10867,7 @@
         <v>8.5</v>
       </c>
       <c r="G370" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H370">
         <v>60</v>
@@ -10833,7 +10878,7 @@
         <v>26</v>
       </c>
       <c r="B371" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C371">
         <v>20</v>
@@ -10848,7 +10893,7 @@
         <v>5</v>
       </c>
       <c r="G371" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H371">
         <v>25.33333333333333</v>
@@ -10859,7 +10904,7 @@
         <v>27</v>
       </c>
       <c r="B372" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C372">
         <v>40</v>
@@ -10874,7 +10919,7 @@
         <v>6</v>
       </c>
       <c r="G372" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H372">
         <v>46.66666666666667</v>
@@ -10885,7 +10930,7 @@
         <v>28</v>
       </c>
       <c r="B373" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C373">
         <v>50</v>
@@ -10900,7 +10945,7 @@
         <v>7</v>
       </c>
       <c r="G373" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H373">
         <v>60</v>
@@ -10911,7 +10956,7 @@
         <v>29</v>
       </c>
       <c r="B374" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C374">
         <v>50</v>
@@ -10926,7 +10971,7 @@
         <v>6.5</v>
       </c>
       <c r="G374" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H374">
         <v>63.33333333333333</v>
@@ -10937,7 +10982,7 @@
         <v>30</v>
       </c>
       <c r="B375" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C375">
         <v>60</v>
@@ -10952,7 +10997,7 @@
         <v>7</v>
       </c>
       <c r="G375" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H375">
         <v>66</v>
@@ -10963,7 +11008,7 @@
         <v>31</v>
       </c>
       <c r="B376" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C376">
         <v>70</v>
@@ -10978,7 +11023,7 @@
         <v>7.75</v>
       </c>
       <c r="G376" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H376">
         <v>72.33333333333334</v>
@@ -10989,7 +11034,7 @@
         <v>32</v>
       </c>
       <c r="B377" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C377">
         <v>75</v>
@@ -11004,7 +11049,7 @@
         <v>8</v>
       </c>
       <c r="G377" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H377">
         <v>77.50000000000001</v>
@@ -11015,7 +11060,7 @@
         <v>33</v>
       </c>
       <c r="B378" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C378">
         <v>77.5</v>
@@ -11030,7 +11075,7 @@
         <v>10</v>
       </c>
       <c r="G378" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H378">
         <v>77.5</v>
@@ -11041,7 +11086,7 @@
         <v>34</v>
       </c>
       <c r="B379" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C379">
         <v>66.25</v>
@@ -11056,7 +11101,7 @@
         <v>9</v>
       </c>
       <c r="G379" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H379">
         <v>77.29166666666667</v>
@@ -11067,7 +11112,7 @@
         <v>35</v>
       </c>
       <c r="B380" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C380">
         <v>60</v>
@@ -11082,7 +11127,7 @@
         <v>8.25</v>
       </c>
       <c r="G380" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H380">
         <v>70</v>
@@ -11093,7 +11138,7 @@
         <v>36</v>
       </c>
       <c r="B381" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C381">
         <v>30</v>
@@ -11108,7 +11153,7 @@
         <v>6</v>
       </c>
       <c r="G381" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H381">
         <v>42</v>
@@ -11119,7 +11164,7 @@
         <v>37</v>
       </c>
       <c r="B382" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C382">
         <v>50</v>
@@ -11134,7 +11179,7 @@
         <v>8.5</v>
       </c>
       <c r="G382" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H382">
         <v>63.33333333333333</v>
@@ -11145,7 +11190,7 @@
         <v>38</v>
       </c>
       <c r="B383" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C383">
         <v>50</v>
@@ -11160,7 +11205,7 @@
         <v>8</v>
       </c>
       <c r="G383" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H383">
         <v>63.33333333333333</v>
@@ -11171,7 +11216,7 @@
         <v>39</v>
       </c>
       <c r="B384" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C384">
         <v>50</v>
@@ -11186,7 +11231,7 @@
         <v>10</v>
       </c>
       <c r="G384" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H384">
         <v>60</v>
@@ -11197,7 +11242,7 @@
         <v>40</v>
       </c>
       <c r="B385" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C385">
         <v>0</v>
@@ -11212,7 +11257,7 @@
         <v>6</v>
       </c>
       <c r="G385" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H385">
         <v>0</v>
@@ -11223,7 +11268,7 @@
         <v>41</v>
       </c>
       <c r="B386" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C386">
         <v>25</v>
@@ -11238,7 +11283,7 @@
         <v>8</v>
       </c>
       <c r="G386" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H386">
         <v>30</v>
@@ -11249,7 +11294,7 @@
         <v>42</v>
       </c>
       <c r="B387" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C387">
         <v>25</v>
@@ -11264,7 +11309,7 @@
         <v>8</v>
       </c>
       <c r="G387" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H387">
         <v>31.66666666666666</v>
@@ -11275,7 +11320,7 @@
         <v>43</v>
       </c>
       <c r="B388" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C388">
         <v>25</v>
@@ -11290,7 +11335,7 @@
         <v>8.5</v>
       </c>
       <c r="G388" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H388">
         <v>31.66666666666666</v>
@@ -11301,7 +11346,7 @@
         <v>44</v>
       </c>
       <c r="B389" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C389">
         <v>45</v>
@@ -11316,7 +11361,7 @@
         <v>6.5</v>
       </c>
       <c r="G389" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H389">
         <v>62.99999999999999</v>
@@ -11327,7 +11372,7 @@
         <v>45</v>
       </c>
       <c r="B390" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C390">
         <v>60</v>
@@ -11342,7 +11387,7 @@
         <v>8</v>
       </c>
       <c r="G390" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H390">
         <v>76</v>
@@ -11353,7 +11398,7 @@
         <v>46</v>
       </c>
       <c r="B391" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C391">
         <v>60</v>
@@ -11368,7 +11413,7 @@
         <v>7.5</v>
       </c>
       <c r="G391" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H391">
         <v>76</v>
@@ -11379,7 +11424,7 @@
         <v>47</v>
       </c>
       <c r="B392" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C392">
         <v>60</v>
@@ -11394,7 +11439,7 @@
         <v>7.5</v>
       </c>
       <c r="G392" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H392">
         <v>76</v>
@@ -11405,7 +11450,7 @@
         <v>48</v>
       </c>
       <c r="B393" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C393">
         <v>60</v>
@@ -11420,7 +11465,7 @@
         <v>9</v>
       </c>
       <c r="G393" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H393">
         <v>76</v>
@@ -11431,7 +11476,7 @@
         <v>49</v>
       </c>
       <c r="B394" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C394">
         <v>40</v>
@@ -11446,7 +11491,7 @@
         <v>8</v>
       </c>
       <c r="G394" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H394">
         <v>53.33333333333333</v>
@@ -11457,7 +11502,7 @@
         <v>50</v>
       </c>
       <c r="B395" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C395">
         <v>40</v>
@@ -11472,7 +11517,7 @@
         <v>7.5</v>
       </c>
       <c r="G395" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H395">
         <v>56</v>
@@ -11483,7 +11528,7 @@
         <v>51</v>
       </c>
       <c r="B396" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C396">
         <v>40</v>
@@ -11498,7 +11543,7 @@
         <v>8</v>
       </c>
       <c r="G396" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H396">
         <v>56</v>
@@ -11509,7 +11554,7 @@
         <v>52</v>
       </c>
       <c r="B397" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C397">
         <v>40</v>
@@ -11524,7 +11569,7 @@
         <v>8</v>
       </c>
       <c r="G397" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H397">
         <v>56</v>
@@ -11535,7 +11580,7 @@
         <v>53</v>
       </c>
       <c r="B398" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C398">
         <v>40</v>
@@ -11550,7 +11595,7 @@
         <v>8.5</v>
       </c>
       <c r="G398" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H398">
         <v>56</v>
@@ -11561,7 +11606,7 @@
         <v>54</v>
       </c>
       <c r="B399" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C399">
         <v>40</v>
@@ -11576,7 +11621,7 @@
         <v>9</v>
       </c>
       <c r="G399" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H399">
         <v>56</v>
@@ -11587,7 +11632,7 @@
         <v>55</v>
       </c>
       <c r="B400" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C400">
         <v>20</v>
@@ -11602,7 +11647,7 @@
         <v>5</v>
       </c>
       <c r="G400" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H400">
         <v>25.33333333333333</v>
@@ -11613,7 +11658,7 @@
         <v>56</v>
       </c>
       <c r="B401" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C401">
         <v>70</v>
@@ -11628,7 +11673,7 @@
         <v>6</v>
       </c>
       <c r="G401" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H401">
         <v>81.66666666666667</v>
@@ -11639,7 +11684,7 @@
         <v>57</v>
       </c>
       <c r="B402" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C402">
         <v>120</v>
@@ -11654,7 +11699,7 @@
         <v>7.5</v>
       </c>
       <c r="G402" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H402">
         <v>124</v>
@@ -11665,7 +11710,7 @@
         <v>58</v>
       </c>
       <c r="B403" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C403">
         <v>110</v>
@@ -11680,7 +11725,7 @@
         <v>8.5</v>
       </c>
       <c r="G403" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H403">
         <v>128.3333333333333</v>
@@ -11691,7 +11736,7 @@
         <v>59</v>
       </c>
       <c r="B404" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C404">
         <v>110</v>
@@ -11706,7 +11751,7 @@
         <v>10</v>
       </c>
       <c r="G404" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H404">
         <v>124.6666666666667</v>
@@ -11717,7 +11762,7 @@
         <v>60</v>
       </c>
       <c r="B405" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C405">
         <v>100</v>
@@ -11732,7 +11777,7 @@
         <v>9.5</v>
       </c>
       <c r="G405" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H405">
         <v>110</v>
@@ -11743,7 +11788,7 @@
         <v>61</v>
       </c>
       <c r="B406" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C406">
         <v>40</v>
@@ -11758,7 +11803,7 @@
         <v>6</v>
       </c>
       <c r="G406" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H406">
         <v>60</v>
@@ -11769,7 +11814,7 @@
         <v>62</v>
       </c>
       <c r="B407" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C407">
         <v>50</v>
@@ -11784,7 +11829,7 @@
         <v>7</v>
       </c>
       <c r="G407" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H407">
         <v>70</v>
@@ -11795,7 +11840,7 @@
         <v>63</v>
       </c>
       <c r="B408" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C408">
         <v>50</v>
@@ -11810,7 +11855,7 @@
         <v>7.5</v>
       </c>
       <c r="G408" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H408">
         <v>70</v>
@@ -11821,7 +11866,7 @@
         <v>64</v>
       </c>
       <c r="B409" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C409">
         <v>50</v>
@@ -11836,7 +11881,7 @@
         <v>8.5</v>
       </c>
       <c r="G409" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H409">
         <v>70</v>
@@ -11847,7 +11892,7 @@
         <v>65</v>
       </c>
       <c r="B410" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C410">
         <v>30</v>
@@ -11862,7 +11907,7 @@
         <v>6</v>
       </c>
       <c r="G410" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H410">
         <v>40</v>
@@ -11873,7 +11918,7 @@
         <v>66</v>
       </c>
       <c r="B411" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C411">
         <v>30</v>
@@ -11888,7 +11933,7 @@
         <v>6.5</v>
       </c>
       <c r="G411" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H411">
         <v>40</v>
@@ -11899,7 +11944,7 @@
         <v>67</v>
       </c>
       <c r="B412" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C412">
         <v>40</v>
@@ -11914,7 +11959,7 @@
         <v>8.5</v>
       </c>
       <c r="G412" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H412">
         <v>53.33333333333333</v>
@@ -11925,7 +11970,7 @@
         <v>68</v>
       </c>
       <c r="B413" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C413">
         <v>40</v>
@@ -11940,7 +11985,7 @@
         <v>10</v>
       </c>
       <c r="G413" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H413">
         <v>50.66666666666666</v>
@@ -11951,7 +11996,7 @@
         <v>69</v>
       </c>
       <c r="B414" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C414">
         <v>40</v>
@@ -11966,7 +12011,7 @@
         <v>9</v>
       </c>
       <c r="G414" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H414">
         <v>50.66666666666666</v>
@@ -11977,7 +12022,7 @@
         <v>70</v>
       </c>
       <c r="B415" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C415">
         <v>30</v>
@@ -11992,7 +12037,7 @@
         <v>8</v>
       </c>
       <c r="G415" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H415">
         <v>35</v>
@@ -12003,7 +12048,7 @@
         <v>70</v>
       </c>
       <c r="B416" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C416">
         <v>30</v>
@@ -12018,7 +12063,7 @@
         <v>8</v>
       </c>
       <c r="G416" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H416">
         <v>42</v>
@@ -12029,7 +12074,7 @@
         <v>71</v>
       </c>
       <c r="B417" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C417">
         <v>30</v>
@@ -12044,7 +12089,7 @@
         <v>8.5</v>
       </c>
       <c r="G417" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H417">
         <v>36</v>
@@ -12055,7 +12100,7 @@
         <v>71</v>
       </c>
       <c r="B418" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C418">
         <v>30</v>
@@ -12070,7 +12115,7 @@
         <v>8.5</v>
       </c>
       <c r="G418" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H418">
         <v>42</v>
@@ -12081,7 +12126,7 @@
         <v>72</v>
       </c>
       <c r="B419" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C419">
         <v>30</v>
@@ -12096,7 +12141,7 @@
         <v>9</v>
       </c>
       <c r="G419" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H419">
         <v>36</v>
@@ -12107,7 +12152,7 @@
         <v>72</v>
       </c>
       <c r="B420" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C420">
         <v>30</v>
@@ -12122,7 +12167,7 @@
         <v>9</v>
       </c>
       <c r="G420" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H420">
         <v>42</v>
@@ -12133,7 +12178,7 @@
         <v>73</v>
       </c>
       <c r="B421" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C421">
         <v>20</v>
@@ -12145,7 +12190,7 @@
         <v>160</v>
       </c>
       <c r="G421" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H421">
         <v>25.33333333333333</v>
@@ -12159,7 +12204,7 @@
         <v>73</v>
       </c>
       <c r="B422" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C422">
         <v>70</v>
@@ -12171,7 +12216,7 @@
         <v>350</v>
       </c>
       <c r="G422" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H422">
         <v>81.66666666666667</v>
@@ -12185,7 +12230,7 @@
         <v>73</v>
       </c>
       <c r="B423" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C423">
         <v>120</v>
@@ -12197,7 +12242,7 @@
         <v>360</v>
       </c>
       <c r="G423" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H423">
         <v>132</v>
@@ -12211,7 +12256,7 @@
         <v>73</v>
       </c>
       <c r="B424" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C424">
         <v>90</v>
@@ -12223,7 +12268,7 @@
         <v>1800</v>
       </c>
       <c r="G424" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H424">
         <v>150</v>
@@ -12237,7 +12282,7 @@
         <v>73</v>
       </c>
       <c r="B425" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C425">
         <v>30</v>
@@ -12249,7 +12294,7 @@
         <v>240</v>
       </c>
       <c r="G425" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H425">
         <v>38</v>
@@ -12263,7 +12308,7 @@
         <v>73</v>
       </c>
       <c r="B426" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C426">
         <v>40</v>
@@ -12275,7 +12320,7 @@
         <v>120</v>
       </c>
       <c r="G426" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H426">
         <v>44</v>
@@ -12289,7 +12334,7 @@
         <v>73</v>
       </c>
       <c r="B427" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C427">
         <v>45</v>
@@ -12301,7 +12346,7 @@
         <v>135</v>
       </c>
       <c r="G427" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H427">
         <v>49.50000000000001</v>
@@ -12315,7 +12360,7 @@
         <v>73</v>
       </c>
       <c r="B428" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C428">
         <v>45</v>
@@ -12327,7 +12372,7 @@
         <v>360</v>
       </c>
       <c r="G428" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H428">
         <v>57</v>
@@ -12341,7 +12386,7 @@
         <v>73</v>
       </c>
       <c r="B429" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C429">
         <v>45</v>
@@ -12353,7 +12398,7 @@
         <v>360</v>
       </c>
       <c r="G429" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H429">
         <v>57</v>
@@ -12367,7 +12412,7 @@
         <v>73</v>
       </c>
       <c r="B430" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C430">
         <v>45</v>
@@ -12379,7 +12424,7 @@
         <v>360</v>
       </c>
       <c r="G430" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H430">
         <v>57</v>
@@ -12393,7 +12438,7 @@
         <v>73</v>
       </c>
       <c r="B431" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C431">
         <v>40</v>
@@ -12405,7 +12450,7 @@
         <v>480</v>
       </c>
       <c r="G431" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H431">
         <v>56</v>
@@ -12419,7 +12464,7 @@
         <v>73</v>
       </c>
       <c r="B432" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C432">
         <v>50</v>
@@ -12431,7 +12476,7 @@
         <v>300</v>
       </c>
       <c r="G432" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H432">
         <v>60</v>
@@ -12445,7 +12490,7 @@
         <v>73</v>
       </c>
       <c r="B433" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C433">
         <v>60</v>
@@ -12457,7 +12502,7 @@
         <v>360</v>
       </c>
       <c r="G433" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H433">
         <v>72</v>
@@ -12471,7 +12516,7 @@
         <v>73</v>
       </c>
       <c r="B434" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C434">
         <v>60</v>
@@ -12483,7 +12528,7 @@
         <v>360</v>
       </c>
       <c r="G434" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H434">
         <v>72</v>
@@ -12497,7 +12542,7 @@
         <v>73</v>
       </c>
       <c r="B435" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C435">
         <v>60</v>
@@ -12509,7 +12554,7 @@
         <v>360</v>
       </c>
       <c r="G435" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H435">
         <v>72</v>
@@ -12523,7 +12568,7 @@
         <v>73</v>
       </c>
       <c r="B436" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C436">
         <v>60</v>
@@ -12535,7 +12580,7 @@
         <v>360</v>
       </c>
       <c r="G436" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H436">
         <v>72</v>
@@ -12549,7 +12594,7 @@
         <v>73</v>
       </c>
       <c r="B437" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C437">
         <v>20</v>
@@ -12561,7 +12606,7 @@
         <v>160</v>
       </c>
       <c r="G437" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H437">
         <v>25.33333333333333</v>
@@ -12575,7 +12620,7 @@
         <v>73</v>
       </c>
       <c r="B438" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C438">
         <v>30</v>
@@ -12587,7 +12632,7 @@
         <v>150</v>
       </c>
       <c r="G438" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H438">
         <v>35</v>
@@ -12601,7 +12646,7 @@
         <v>73</v>
       </c>
       <c r="B439" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C439">
         <v>20</v>
@@ -12613,7 +12658,7 @@
         <v>240</v>
       </c>
       <c r="G439" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H439">
         <v>28</v>
@@ -12627,7 +12672,7 @@
         <v>73</v>
       </c>
       <c r="B440" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C440">
         <v>30</v>
@@ -12639,7 +12684,7 @@
         <v>240</v>
       </c>
       <c r="G440" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H440">
         <v>38</v>
@@ -12653,7 +12698,7 @@
         <v>73</v>
       </c>
       <c r="B441" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C441">
         <v>40</v>
@@ -12665,7 +12710,7 @@
         <v>120</v>
       </c>
       <c r="G441" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H441">
         <v>44</v>
@@ -12679,7 +12724,7 @@
         <v>73</v>
       </c>
       <c r="B442" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C442">
         <v>30</v>
@@ -12691,7 +12736,7 @@
         <v>240</v>
       </c>
       <c r="G442" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H442">
         <v>38</v>
@@ -12705,7 +12750,7 @@
         <v>73</v>
       </c>
       <c r="B443" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C443">
         <v>30</v>
@@ -12717,7 +12762,7 @@
         <v>240</v>
       </c>
       <c r="G443" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H443">
         <v>38</v>
@@ -12731,7 +12776,7 @@
         <v>74</v>
       </c>
       <c r="B444" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C444">
         <v>20</v>
@@ -12746,7 +12791,7 @@
         <v>4</v>
       </c>
       <c r="G444" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H444">
         <v>25.33333333333333</v>
@@ -12757,7 +12802,7 @@
         <v>74</v>
       </c>
       <c r="B445" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C445">
         <v>70</v>
@@ -12772,7 +12817,7 @@
         <v>6</v>
       </c>
       <c r="G445" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H445">
         <v>84</v>
@@ -12783,7 +12828,7 @@
         <v>74</v>
       </c>
       <c r="B446" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C446">
         <v>110</v>
@@ -12798,7 +12843,7 @@
         <v>7</v>
       </c>
       <c r="G446" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H446">
         <v>113.6666666666667</v>
@@ -12809,7 +12854,7 @@
         <v>74</v>
       </c>
       <c r="B447" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C447">
         <v>110</v>
@@ -12824,7 +12869,7 @@
         <v>8.5</v>
       </c>
       <c r="G447" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H447">
         <v>121</v>
@@ -12835,7 +12880,7 @@
         <v>74</v>
       </c>
       <c r="B448" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C448">
         <v>90</v>
@@ -12850,7 +12895,7 @@
         <v>8</v>
       </c>
       <c r="G448" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H448">
         <v>120</v>
@@ -12861,7 +12906,7 @@
         <v>74</v>
       </c>
       <c r="B449" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C449">
         <v>90</v>
@@ -12876,7 +12921,7 @@
         <v>8.5</v>
       </c>
       <c r="G449" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H449">
         <v>120</v>
@@ -12887,7 +12932,7 @@
         <v>74</v>
       </c>
       <c r="B450" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C450">
         <v>30</v>
@@ -12902,7 +12947,7 @@
         <v>5.5</v>
       </c>
       <c r="G450" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H450">
         <v>38</v>
@@ -12913,7 +12958,7 @@
         <v>74</v>
       </c>
       <c r="B451" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C451">
         <v>40</v>
@@ -12928,7 +12973,7 @@
         <v>6</v>
       </c>
       <c r="G451" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H451">
         <v>50.66666666666666</v>
@@ -12939,7 +12984,7 @@
         <v>74</v>
       </c>
       <c r="B452" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C452">
         <v>45</v>
@@ -12954,7 +12999,7 @@
         <v>6</v>
       </c>
       <c r="G452" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H452">
         <v>46.50000000000001</v>
@@ -12965,7 +13010,7 @@
         <v>74</v>
       </c>
       <c r="B453" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C453">
         <v>50</v>
@@ -12980,7 +13025,7 @@
         <v>6.5</v>
       </c>
       <c r="G453" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H453">
         <v>51.66666666666667</v>
@@ -12991,7 +13036,7 @@
         <v>74</v>
       </c>
       <c r="B454" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C454">
         <v>55</v>
@@ -13006,7 +13051,7 @@
         <v>7</v>
       </c>
       <c r="G454" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H454">
         <v>56.83333333333334</v>
@@ -13017,7 +13062,7 @@
         <v>74</v>
       </c>
       <c r="B455" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C455">
         <v>60</v>
@@ -13032,7 +13077,7 @@
         <v>10</v>
       </c>
       <c r="G455" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H455">
         <v>60</v>
@@ -13043,7 +13088,7 @@
         <v>74</v>
       </c>
       <c r="B456" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C456">
         <v>50</v>
@@ -13058,7 +13103,7 @@
         <v>8</v>
       </c>
       <c r="G456" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H456">
         <v>60</v>
@@ -13069,7 +13114,7 @@
         <v>74</v>
       </c>
       <c r="B457" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C457">
         <v>50</v>
@@ -13084,7 +13129,7 @@
         <v>9</v>
       </c>
       <c r="G457" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H457">
         <v>60</v>
@@ -13095,7 +13140,7 @@
         <v>75</v>
       </c>
       <c r="B458" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C458">
         <v>20</v>
@@ -13110,7 +13155,7 @@
         <v>3</v>
       </c>
       <c r="G458" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H458">
         <v>26.66666666666666</v>
@@ -13121,7 +13166,7 @@
         <v>75</v>
       </c>
       <c r="B459" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C459">
         <v>60</v>
@@ -13136,7 +13181,7 @@
         <v>6</v>
       </c>
       <c r="G459" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H459">
         <v>76</v>
@@ -13147,7 +13192,7 @@
         <v>75</v>
       </c>
       <c r="B460" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C460">
         <v>100</v>
@@ -13162,7 +13207,7 @@
         <v>7</v>
       </c>
       <c r="G460" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H460">
         <v>116.6666666666667</v>
@@ -13173,7 +13218,7 @@
         <v>75</v>
       </c>
       <c r="B461" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C461">
         <v>120</v>
@@ -13188,7 +13233,7 @@
         <v>8</v>
       </c>
       <c r="G461" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H461">
         <v>128</v>
@@ -13199,7 +13244,7 @@
         <v>75</v>
       </c>
       <c r="B462" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C462">
         <v>130</v>
@@ -13214,7 +13259,7 @@
         <v>9</v>
       </c>
       <c r="G462" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H462">
         <v>134.3333333333333</v>
@@ -13225,7 +13270,7 @@
         <v>75</v>
       </c>
       <c r="B463" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C463">
         <v>100</v>
@@ -13240,7 +13285,7 @@
         <v>9</v>
       </c>
       <c r="G463" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H463">
         <v>133.3333333333333</v>
@@ -13251,7 +13296,7 @@
         <v>75</v>
       </c>
       <c r="B464" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C464">
         <v>100</v>
@@ -13266,7 +13311,7 @@
         <v>9.5</v>
       </c>
       <c r="G464" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H464">
         <v>133.3333333333333</v>
@@ -13277,7 +13322,7 @@
         <v>75</v>
       </c>
       <c r="B465" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C465">
         <v>30</v>
@@ -13292,7 +13337,7 @@
         <v>6</v>
       </c>
       <c r="G465" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H465">
         <v>40</v>
@@ -13303,7 +13348,7 @@
         <v>75</v>
       </c>
       <c r="B466" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C466">
         <v>30</v>
@@ -13318,7 +13363,7 @@
         <v>5.5</v>
       </c>
       <c r="G466" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H466">
         <v>40</v>
@@ -13329,7 +13374,7 @@
         <v>75</v>
       </c>
       <c r="B467" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C467">
         <v>50</v>
@@ -13344,7 +13389,7 @@
         <v>10</v>
       </c>
       <c r="G467" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H467">
         <v>53.33333333333334</v>
@@ -13355,7 +13400,7 @@
         <v>75</v>
       </c>
       <c r="B468" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C468">
         <v>40</v>
@@ -13370,7 +13415,7 @@
         <v>8</v>
       </c>
       <c r="G468" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H468">
         <v>50.66666666666666</v>
@@ -13381,7 +13426,7 @@
         <v>75</v>
       </c>
       <c r="B469" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C469">
         <v>40</v>
@@ -13396,7 +13441,7 @@
         <v>8.5</v>
       </c>
       <c r="G469" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H469">
         <v>50.66666666666666</v>
@@ -13407,7 +13452,7 @@
         <v>75</v>
       </c>
       <c r="B470" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C470">
         <v>40</v>
@@ -13422,7 +13467,7 @@
         <v>10</v>
       </c>
       <c r="G470" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H470">
         <v>48</v>
@@ -13433,7 +13478,7 @@
         <v>75</v>
       </c>
       <c r="B471" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C471">
         <v>40</v>
@@ -13448,7 +13493,7 @@
         <v>7</v>
       </c>
       <c r="G471" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H471">
         <v>60</v>
@@ -13459,7 +13504,7 @@
         <v>75</v>
       </c>
       <c r="B472" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C472">
         <v>70</v>
@@ -13474,7 +13519,7 @@
         <v>8.5</v>
       </c>
       <c r="G472" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H472">
         <v>77</v>
@@ -13485,7 +13530,7 @@
         <v>75</v>
       </c>
       <c r="B473" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C473">
         <v>60</v>
@@ -13500,7 +13545,7 @@
         <v>8</v>
       </c>
       <c r="G473" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H473">
         <v>76</v>
@@ -13511,7 +13556,7 @@
         <v>75</v>
       </c>
       <c r="B474" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C474">
         <v>60</v>
@@ -13526,7 +13571,7 @@
         <v>8</v>
       </c>
       <c r="G474" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H474">
         <v>76</v>
@@ -13537,7 +13582,7 @@
         <v>75</v>
       </c>
       <c r="B475" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C475">
         <v>60</v>
@@ -13552,7 +13597,7 @@
         <v>9</v>
       </c>
       <c r="G475" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H475">
         <v>76</v>
@@ -13563,7 +13608,7 @@
         <v>75</v>
       </c>
       <c r="B476" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C476">
         <v>25</v>
@@ -13578,7 +13623,7 @@
         <v>9</v>
       </c>
       <c r="G476" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H476">
         <v>33.33333333333333</v>
@@ -13589,7 +13634,7 @@
         <v>75</v>
       </c>
       <c r="B477" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C477">
         <v>25</v>
@@ -13604,7 +13649,7 @@
         <v>9</v>
       </c>
       <c r="G477" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H477">
         <v>41.66666666666666</v>
@@ -13615,7 +13660,7 @@
         <v>75</v>
       </c>
       <c r="B478" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C478">
         <v>18</v>
@@ -13630,7 +13675,7 @@
         <v>6</v>
       </c>
       <c r="G478" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H478">
         <v>25.2</v>
@@ -13641,7 +13686,7 @@
         <v>75</v>
       </c>
       <c r="B479" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C479">
         <v>22</v>
@@ -13656,7 +13701,7 @@
         <v>7.5</v>
       </c>
       <c r="G479" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H479">
         <v>29.33333333333333</v>
@@ -13667,7 +13712,7 @@
         <v>75</v>
       </c>
       <c r="B480" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C480">
         <v>22</v>
@@ -13682,7 +13727,7 @@
         <v>8.5</v>
       </c>
       <c r="G480" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H480">
         <v>29.33333333333333</v>
@@ -13693,7 +13738,7 @@
         <v>75</v>
       </c>
       <c r="B481" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C481">
         <v>22</v>
@@ -13708,7 +13753,7 @@
         <v>9</v>
       </c>
       <c r="G481" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H481">
         <v>29.33333333333333</v>
@@ -13719,7 +13764,7 @@
         <v>76</v>
       </c>
       <c r="B482" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C482">
         <v>20</v>
@@ -13734,7 +13779,7 @@
         <v>3</v>
       </c>
       <c r="G482" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H482">
         <v>25.33333333333333</v>
@@ -13745,7 +13790,7 @@
         <v>76</v>
       </c>
       <c r="B483" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C483">
         <v>40</v>
@@ -13760,7 +13805,7 @@
         <v>5</v>
       </c>
       <c r="G483" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H483">
         <v>53.33333333333333</v>
@@ -13771,7 +13816,7 @@
         <v>76</v>
       </c>
       <c r="B484" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C484">
         <v>60</v>
@@ -13786,7 +13831,7 @@
         <v>6</v>
       </c>
       <c r="G484" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H484">
         <v>66</v>
@@ -13797,7 +13842,7 @@
         <v>76</v>
       </c>
       <c r="B485" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C485">
         <v>70</v>
@@ -13812,7 +13857,7 @@
         <v>6.5</v>
       </c>
       <c r="G485" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H485">
         <v>72.33333333333334</v>
@@ -13823,7 +13868,7 @@
         <v>76</v>
       </c>
       <c r="B486" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C486">
         <v>75</v>
@@ -13838,7 +13883,7 @@
         <v>7.5</v>
       </c>
       <c r="G486" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H486">
         <v>77.50000000000001</v>
@@ -13849,7 +13894,7 @@
         <v>76</v>
       </c>
       <c r="B487" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C487">
         <v>80</v>
@@ -13864,7 +13909,7 @@
         <v>8.5</v>
       </c>
       <c r="G487" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H487">
         <v>82.66666666666667</v>
@@ -13875,7 +13920,7 @@
         <v>76</v>
       </c>
       <c r="B488" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C488">
         <v>60</v>
@@ -13890,7 +13935,7 @@
         <v>7.5</v>
       </c>
       <c r="G488" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H488">
         <v>80</v>
@@ -13901,7 +13946,7 @@
         <v>76</v>
       </c>
       <c r="B489" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C489">
         <v>60</v>
@@ -13916,7 +13961,7 @@
         <v>8</v>
       </c>
       <c r="G489" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H489">
         <v>80</v>
@@ -13927,7 +13972,7 @@
         <v>76</v>
       </c>
       <c r="B490" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C490">
         <v>60</v>
@@ -13942,7 +13987,7 @@
         <v>8.5</v>
       </c>
       <c r="G490" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H490">
         <v>80</v>
@@ -13953,7 +13998,7 @@
         <v>76</v>
       </c>
       <c r="B491" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C491">
         <v>40</v>
@@ -13968,7 +14013,7 @@
         <v>6</v>
       </c>
       <c r="G491" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H491">
         <v>56</v>
@@ -13979,7 +14024,7 @@
         <v>76</v>
       </c>
       <c r="B492" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C492">
         <v>60</v>
@@ -14002,7 +14047,7 @@
         <v>76</v>
       </c>
       <c r="B493" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C493">
         <v>60</v>
@@ -14025,7 +14070,7 @@
         <v>76</v>
       </c>
       <c r="B494" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C494">
         <v>60</v>
@@ -14048,7 +14093,7 @@
         <v>76</v>
       </c>
       <c r="B495" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C495">
         <v>60</v>
@@ -14071,7 +14116,7 @@
         <v>76</v>
       </c>
       <c r="B496" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C496">
         <v>20</v>
@@ -14086,7 +14131,7 @@
         <v>6</v>
       </c>
       <c r="G496" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H496">
         <v>26.66666666666666</v>
@@ -14097,7 +14142,7 @@
         <v>76</v>
       </c>
       <c r="B497" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C497">
         <v>20</v>
@@ -14112,7 +14157,7 @@
         <v>6</v>
       </c>
       <c r="G497" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H497">
         <v>30</v>
@@ -14123,7 +14168,7 @@
         <v>76</v>
       </c>
       <c r="B498" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C498">
         <v>25</v>
@@ -14146,7 +14191,7 @@
         <v>76</v>
       </c>
       <c r="B499" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C499">
         <v>25</v>
@@ -14169,7 +14214,7 @@
         <v>76</v>
       </c>
       <c r="B500" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C500">
         <v>25</v>
@@ -14184,7 +14229,7 @@
         <v>8</v>
       </c>
       <c r="G500" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H500">
         <v>31.66666666666666</v>
@@ -14195,7 +14240,7 @@
         <v>76</v>
       </c>
       <c r="B501" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C501">
         <v>25</v>
@@ -14218,7 +14263,7 @@
         <v>76</v>
       </c>
       <c r="B502" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C502">
         <v>25</v>
@@ -14241,7 +14286,7 @@
         <v>76</v>
       </c>
       <c r="B503" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C503">
         <v>25</v>
@@ -14264,7 +14309,7 @@
         <v>76</v>
       </c>
       <c r="B504" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C504">
         <v>25</v>
@@ -14287,7 +14332,7 @@
         <v>76</v>
       </c>
       <c r="B505" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C505">
         <v>25</v>
@@ -14303,6 +14348,500 @@
       </c>
       <c r="H505">
         <v>37.5</v>
+      </c>
+    </row>
+    <row r="506" spans="1:8">
+      <c r="A506" t="s">
+        <v>77</v>
+      </c>
+      <c r="B506" t="s">
+        <v>92</v>
+      </c>
+      <c r="C506">
+        <v>70</v>
+      </c>
+      <c r="D506">
+        <v>10</v>
+      </c>
+      <c r="E506">
+        <v>700</v>
+      </c>
+      <c r="F506">
+        <v>4.5</v>
+      </c>
+      <c r="G506" t="s">
+        <v>409</v>
+      </c>
+      <c r="H506">
+        <v>93.33333333333333</v>
+      </c>
+    </row>
+    <row r="507" spans="1:8">
+      <c r="A507" t="s">
+        <v>77</v>
+      </c>
+      <c r="B507" t="s">
+        <v>92</v>
+      </c>
+      <c r="C507">
+        <v>120</v>
+      </c>
+      <c r="D507">
+        <v>1</v>
+      </c>
+      <c r="E507">
+        <v>120</v>
+      </c>
+      <c r="F507">
+        <v>5</v>
+      </c>
+      <c r="G507" t="s">
+        <v>410</v>
+      </c>
+      <c r="H507">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="508" spans="1:8">
+      <c r="A508" t="s">
+        <v>77</v>
+      </c>
+      <c r="B508" t="s">
+        <v>92</v>
+      </c>
+      <c r="C508">
+        <v>160</v>
+      </c>
+      <c r="D508">
+        <v>1</v>
+      </c>
+      <c r="E508">
+        <v>160</v>
+      </c>
+      <c r="F508">
+        <v>7.5</v>
+      </c>
+      <c r="G508" t="s">
+        <v>411</v>
+      </c>
+      <c r="H508">
+        <v>165.3333333333333</v>
+      </c>
+    </row>
+    <row r="509" spans="1:8">
+      <c r="A509" t="s">
+        <v>77</v>
+      </c>
+      <c r="B509" t="s">
+        <v>92</v>
+      </c>
+      <c r="C509">
+        <v>160</v>
+      </c>
+      <c r="D509">
+        <v>3</v>
+      </c>
+      <c r="E509">
+        <v>480</v>
+      </c>
+      <c r="F509">
+        <v>8.5</v>
+      </c>
+      <c r="G509" t="s">
+        <v>412</v>
+      </c>
+      <c r="H509">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="510" spans="1:8">
+      <c r="A510" t="s">
+        <v>77</v>
+      </c>
+      <c r="B510" t="s">
+        <v>92</v>
+      </c>
+      <c r="C510">
+        <v>170</v>
+      </c>
+      <c r="D510">
+        <v>1</v>
+      </c>
+      <c r="E510">
+        <v>170</v>
+      </c>
+      <c r="F510">
+        <v>8.5</v>
+      </c>
+      <c r="G510" t="s">
+        <v>413</v>
+      </c>
+      <c r="H510">
+        <v>175.6666666666667</v>
+      </c>
+    </row>
+    <row r="511" spans="1:8">
+      <c r="A511" t="s">
+        <v>77</v>
+      </c>
+      <c r="B511" t="s">
+        <v>92</v>
+      </c>
+      <c r="C511">
+        <v>180</v>
+      </c>
+      <c r="D511">
+        <v>0</v>
+      </c>
+      <c r="E511">
+        <v>0</v>
+      </c>
+      <c r="F511">
+        <v>10</v>
+      </c>
+      <c r="G511" t="s">
+        <v>414</v>
+      </c>
+      <c r="H511">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="512" spans="1:8">
+      <c r="A512" t="s">
+        <v>77</v>
+      </c>
+      <c r="B512" t="s">
+        <v>92</v>
+      </c>
+      <c r="C512">
+        <v>180</v>
+      </c>
+      <c r="D512">
+        <v>0</v>
+      </c>
+      <c r="E512">
+        <v>0</v>
+      </c>
+      <c r="F512">
+        <v>10</v>
+      </c>
+      <c r="G512" t="s">
+        <v>415</v>
+      </c>
+      <c r="H512">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="513" spans="1:8">
+      <c r="A513" t="s">
+        <v>77</v>
+      </c>
+      <c r="B513" t="s">
+        <v>92</v>
+      </c>
+      <c r="C513">
+        <v>140</v>
+      </c>
+      <c r="D513">
+        <v>5</v>
+      </c>
+      <c r="E513">
+        <v>700</v>
+      </c>
+      <c r="F513">
+        <v>8.5</v>
+      </c>
+      <c r="G513" t="s">
+        <v>165</v>
+      </c>
+      <c r="H513">
+        <v>163.3333333333333</v>
+      </c>
+    </row>
+    <row r="514" spans="1:8">
+      <c r="A514" t="s">
+        <v>77</v>
+      </c>
+      <c r="B514" t="s">
+        <v>92</v>
+      </c>
+      <c r="C514">
+        <v>140</v>
+      </c>
+      <c r="D514">
+        <v>5</v>
+      </c>
+      <c r="E514">
+        <v>700</v>
+      </c>
+      <c r="F514">
+        <v>9.5</v>
+      </c>
+      <c r="G514" t="s">
+        <v>416</v>
+      </c>
+      <c r="H514">
+        <v>163.3333333333333</v>
+      </c>
+    </row>
+    <row r="515" spans="1:8">
+      <c r="A515" t="s">
+        <v>77</v>
+      </c>
+      <c r="B515" t="s">
+        <v>92</v>
+      </c>
+      <c r="C515">
+        <v>140</v>
+      </c>
+      <c r="D515">
+        <v>5</v>
+      </c>
+      <c r="E515">
+        <v>700</v>
+      </c>
+      <c r="F515">
+        <v>9.5</v>
+      </c>
+      <c r="G515" t="s">
+        <v>417</v>
+      </c>
+      <c r="H515">
+        <v>163.3333333333333</v>
+      </c>
+    </row>
+    <row r="516" spans="1:8">
+      <c r="A516" t="s">
+        <v>77</v>
+      </c>
+      <c r="B516" t="s">
+        <v>101</v>
+      </c>
+      <c r="C516">
+        <v>20</v>
+      </c>
+      <c r="D516">
+        <v>10</v>
+      </c>
+      <c r="E516">
+        <v>200</v>
+      </c>
+      <c r="F516">
+        <v>4</v>
+      </c>
+      <c r="G516" t="s">
+        <v>169</v>
+      </c>
+      <c r="H516">
+        <v>26.66666666666666</v>
+      </c>
+    </row>
+    <row r="517" spans="1:8">
+      <c r="A517" t="s">
+        <v>77</v>
+      </c>
+      <c r="B517" t="s">
+        <v>101</v>
+      </c>
+      <c r="C517">
+        <v>40</v>
+      </c>
+      <c r="D517">
+        <v>10</v>
+      </c>
+      <c r="E517">
+        <v>400</v>
+      </c>
+      <c r="F517">
+        <v>5</v>
+      </c>
+      <c r="G517" t="s">
+        <v>169</v>
+      </c>
+      <c r="H517">
+        <v>53.33333333333333</v>
+      </c>
+    </row>
+    <row r="518" spans="1:8">
+      <c r="A518" t="s">
+        <v>77</v>
+      </c>
+      <c r="B518" t="s">
+        <v>101</v>
+      </c>
+      <c r="C518">
+        <v>60</v>
+      </c>
+      <c r="D518">
+        <v>3</v>
+      </c>
+      <c r="E518">
+        <v>180</v>
+      </c>
+      <c r="F518">
+        <v>6</v>
+      </c>
+      <c r="G518" t="s">
+        <v>418</v>
+      </c>
+      <c r="H518">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="519" spans="1:8">
+      <c r="A519" t="s">
+        <v>77</v>
+      </c>
+      <c r="B519" t="s">
+        <v>101</v>
+      </c>
+      <c r="C519">
+        <v>70</v>
+      </c>
+      <c r="D519">
+        <v>1</v>
+      </c>
+      <c r="E519">
+        <v>70</v>
+      </c>
+      <c r="F519">
+        <v>7</v>
+      </c>
+      <c r="G519" t="s">
+        <v>419</v>
+      </c>
+      <c r="H519">
+        <v>72.33333333333334</v>
+      </c>
+    </row>
+    <row r="520" spans="1:8">
+      <c r="A520" t="s">
+        <v>77</v>
+      </c>
+      <c r="B520" t="s">
+        <v>101</v>
+      </c>
+      <c r="C520">
+        <v>80</v>
+      </c>
+      <c r="D520">
+        <v>0</v>
+      </c>
+      <c r="E520">
+        <v>0</v>
+      </c>
+      <c r="F520">
+        <v>10</v>
+      </c>
+      <c r="G520" t="s">
+        <v>420</v>
+      </c>
+      <c r="H520">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="521" spans="1:8">
+      <c r="A521" t="s">
+        <v>77</v>
+      </c>
+      <c r="B521" t="s">
+        <v>101</v>
+      </c>
+      <c r="C521">
+        <v>70</v>
+      </c>
+      <c r="D521">
+        <v>3</v>
+      </c>
+      <c r="E521">
+        <v>210</v>
+      </c>
+      <c r="F521">
+        <v>8.5</v>
+      </c>
+      <c r="G521" t="s">
+        <v>421</v>
+      </c>
+      <c r="H521">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="522" spans="1:8">
+      <c r="A522" t="s">
+        <v>77</v>
+      </c>
+      <c r="B522" t="s">
+        <v>101</v>
+      </c>
+      <c r="C522">
+        <v>65</v>
+      </c>
+      <c r="D522">
+        <v>5</v>
+      </c>
+      <c r="E522">
+        <v>325</v>
+      </c>
+      <c r="F522">
+        <v>8</v>
+      </c>
+      <c r="G522" t="s">
+        <v>269</v>
+      </c>
+      <c r="H522">
+        <v>75.83333333333334</v>
+      </c>
+    </row>
+    <row r="523" spans="1:8">
+      <c r="A523" t="s">
+        <v>77</v>
+      </c>
+      <c r="B523" t="s">
+        <v>101</v>
+      </c>
+      <c r="C523">
+        <v>65</v>
+      </c>
+      <c r="D523">
+        <v>5</v>
+      </c>
+      <c r="E523">
+        <v>325</v>
+      </c>
+      <c r="F523">
+        <v>8.5</v>
+      </c>
+      <c r="G523" t="s">
+        <v>269</v>
+      </c>
+      <c r="H523">
+        <v>75.83333333333334</v>
+      </c>
+    </row>
+    <row r="524" spans="1:8">
+      <c r="A524" t="s">
+        <v>77</v>
+      </c>
+      <c r="B524" t="s">
+        <v>101</v>
+      </c>
+      <c r="C524">
+        <v>65</v>
+      </c>
+      <c r="D524">
+        <v>5</v>
+      </c>
+      <c r="E524">
+        <v>325</v>
+      </c>
+      <c r="F524">
+        <v>9.5</v>
+      </c>
+      <c r="G524" t="s">
+        <v>422</v>
+      </c>
+      <c r="H524">
+        <v>75.83333333333334</v>
       </c>
     </row>
   </sheetData>

--- a/data/workout_log.xlsx
+++ b/data/workout_log.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1436" uniqueCount="423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1487" uniqueCount="437">
   <si>
     <t>Timestamp</t>
   </si>
@@ -250,6 +250,9 @@
     <t>2026-03-25 19:30:00</t>
   </si>
   <si>
+    <t>2026-03-30 20:00:00</t>
+  </si>
+  <si>
     <t>Overhead Press</t>
   </si>
   <si>
@@ -1283,6 +1286,45 @@
   </si>
   <si>
     <t>Fatigue limit</t>
+  </si>
+  <si>
+    <t>Progressive warm-up / feeder set</t>
+  </si>
+  <si>
+    <t>High-intensity technical set</t>
+  </si>
+  <si>
+    <t>Heavy single; technical peak</t>
+  </si>
+  <si>
+    <t>Volume accumulation at target weight</t>
+  </si>
+  <si>
+    <t>Volume accumulation set 2</t>
+  </si>
+  <si>
+    <t>High volume set; restricted breathing (belt)</t>
+  </si>
+  <si>
+    <t>Progressive warm-up set</t>
+  </si>
+  <si>
+    <t>Moderate-intensity working set</t>
+  </si>
+  <si>
+    <t>High-intensity working set</t>
+  </si>
+  <si>
+    <t>Back-off volume set</t>
+  </si>
+  <si>
+    <t>Accessory volume</t>
+  </si>
+  <si>
+    <t>Accessory volume set 2</t>
+  </si>
+  <si>
+    <t>R-Shoulder instability noted</t>
   </si>
 </sst>
 </file>
@@ -1640,7 +1682,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I524"/>
+  <dimension ref="A1:I541"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -1677,7 +1719,7 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C2">
         <v>30</v>
@@ -1692,7 +1734,7 @@
         <v>4</v>
       </c>
       <c r="G2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H2">
         <v>40</v>
@@ -1703,7 +1745,7 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C3">
         <v>30</v>
@@ -1726,7 +1768,7 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C4">
         <v>30</v>
@@ -1749,7 +1791,7 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C5">
         <v>30</v>
@@ -1772,7 +1814,7 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C6">
         <v>60</v>
@@ -1787,7 +1829,7 @@
         <v>5</v>
       </c>
       <c r="G6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H6">
         <v>76</v>
@@ -1798,7 +1840,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C7">
         <v>100</v>
@@ -1813,7 +1855,7 @@
         <v>6</v>
       </c>
       <c r="G7" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H7">
         <v>110</v>
@@ -1824,7 +1866,7 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C8">
         <v>100</v>
@@ -1847,7 +1889,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C9">
         <v>100</v>
@@ -1870,7 +1912,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C10">
         <v>32</v>
@@ -1885,7 +1927,7 @@
         <v>3</v>
       </c>
       <c r="G10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H10">
         <v>44.8</v>
@@ -1896,7 +1938,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C11">
         <v>40</v>
@@ -1911,7 +1953,7 @@
         <v>5.5</v>
       </c>
       <c r="G11" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H11">
         <v>50.66666666666666</v>
@@ -1922,7 +1964,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C12">
         <v>40</v>
@@ -1945,7 +1987,7 @@
         <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C13">
         <v>40</v>
@@ -1960,7 +2002,7 @@
         <v>9</v>
       </c>
       <c r="G13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H13">
         <v>48</v>
@@ -1971,7 +2013,7 @@
         <v>9</v>
       </c>
       <c r="B14" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C14">
         <v>20</v>
@@ -1994,7 +2036,7 @@
         <v>9</v>
       </c>
       <c r="B15" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C15">
         <v>20</v>
@@ -2017,7 +2059,7 @@
         <v>9</v>
       </c>
       <c r="B16" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C16">
         <v>20</v>
@@ -2040,7 +2082,7 @@
         <v>9</v>
       </c>
       <c r="B17" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C17">
         <v>20</v>
@@ -2055,7 +2097,7 @@
         <v>8</v>
       </c>
       <c r="G17" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H17">
         <v>26.66666666666666</v>
@@ -2066,7 +2108,7 @@
         <v>9</v>
       </c>
       <c r="B18" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C18">
         <v>20</v>
@@ -2081,7 +2123,7 @@
         <v>8</v>
       </c>
       <c r="G18" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H18">
         <v>26.66666666666666</v>
@@ -2092,7 +2134,7 @@
         <v>9</v>
       </c>
       <c r="B19" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C19">
         <v>20</v>
@@ -2107,7 +2149,7 @@
         <v>8</v>
       </c>
       <c r="G19" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H19">
         <v>25.33333333333333</v>
@@ -2118,7 +2160,7 @@
         <v>9</v>
       </c>
       <c r="B20" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C20">
         <v>20</v>
@@ -2133,7 +2175,7 @@
         <v>8</v>
       </c>
       <c r="G20" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H20">
         <v>25.33333333333333</v>
@@ -2144,7 +2186,7 @@
         <v>10</v>
       </c>
       <c r="B21" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -2159,7 +2201,7 @@
         <v>7</v>
       </c>
       <c r="G21" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H21">
         <v>0</v>
@@ -2170,7 +2212,7 @@
         <v>10</v>
       </c>
       <c r="B22" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C22">
         <v>30</v>
@@ -2193,7 +2235,7 @@
         <v>10</v>
       </c>
       <c r="B23" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C23">
         <v>30</v>
@@ -2216,7 +2258,7 @@
         <v>10</v>
       </c>
       <c r="B24" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C24">
         <v>30</v>
@@ -2239,7 +2281,7 @@
         <v>10</v>
       </c>
       <c r="B25" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C25">
         <v>30</v>
@@ -2262,7 +2304,7 @@
         <v>10</v>
       </c>
       <c r="B26" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C26">
         <v>30</v>
@@ -2285,7 +2327,7 @@
         <v>10</v>
       </c>
       <c r="B27" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C27">
         <v>30</v>
@@ -2308,7 +2350,7 @@
         <v>10</v>
       </c>
       <c r="B28" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C28">
         <v>30</v>
@@ -2331,7 +2373,7 @@
         <v>10</v>
       </c>
       <c r="B29" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C29">
         <v>30</v>
@@ -2354,7 +2396,7 @@
         <v>10</v>
       </c>
       <c r="B30" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C30">
         <v>30</v>
@@ -2377,7 +2419,7 @@
         <v>10</v>
       </c>
       <c r="B31" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C31">
         <v>70</v>
@@ -2400,7 +2442,7 @@
         <v>10</v>
       </c>
       <c r="B32" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C32">
         <v>70</v>
@@ -2423,7 +2465,7 @@
         <v>10</v>
       </c>
       <c r="B33" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C33">
         <v>70</v>
@@ -2446,7 +2488,7 @@
         <v>10</v>
       </c>
       <c r="B34" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C34">
         <v>23</v>
@@ -2461,7 +2503,7 @@
         <v>7</v>
       </c>
       <c r="G34" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H34">
         <v>38.33333333333333</v>
@@ -2472,7 +2514,7 @@
         <v>10</v>
       </c>
       <c r="B35" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C35">
         <v>23</v>
@@ -2487,7 +2529,7 @@
         <v>7</v>
       </c>
       <c r="G35" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H35">
         <v>38.33333333333333</v>
@@ -2498,7 +2540,7 @@
         <v>10</v>
       </c>
       <c r="B36" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C36">
         <v>23</v>
@@ -2513,7 +2555,7 @@
         <v>9</v>
       </c>
       <c r="G36" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H36">
         <v>38.33333333333333</v>
@@ -2524,7 +2566,7 @@
         <v>10</v>
       </c>
       <c r="B37" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C37">
         <v>23</v>
@@ -2539,7 +2581,7 @@
         <v>10</v>
       </c>
       <c r="G37" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H37">
         <v>32.2</v>
@@ -2550,7 +2592,7 @@
         <v>10</v>
       </c>
       <c r="B38" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C38">
         <v>20</v>
@@ -2573,7 +2615,7 @@
         <v>10</v>
       </c>
       <c r="B39" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C39">
         <v>20</v>
@@ -2596,7 +2638,7 @@
         <v>10</v>
       </c>
       <c r="B40" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C40">
         <v>20</v>
@@ -2619,7 +2661,7 @@
         <v>11</v>
       </c>
       <c r="B41" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C41">
         <v>36</v>
@@ -2634,7 +2676,7 @@
         <v>5</v>
       </c>
       <c r="G41" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H41">
         <v>48</v>
@@ -2645,7 +2687,7 @@
         <v>11</v>
       </c>
       <c r="B42" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C42">
         <v>44</v>
@@ -2660,7 +2702,7 @@
         <v>7</v>
       </c>
       <c r="G42" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H42">
         <v>52.8</v>
@@ -2671,7 +2713,7 @@
         <v>11</v>
       </c>
       <c r="B43" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C43">
         <v>44</v>
@@ -2686,7 +2728,7 @@
         <v>7.5</v>
       </c>
       <c r="G43" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H43">
         <v>52.8</v>
@@ -2697,7 +2739,7 @@
         <v>11</v>
       </c>
       <c r="B44" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C44">
         <v>44</v>
@@ -2712,7 +2754,7 @@
         <v>8</v>
       </c>
       <c r="G44" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H44">
         <v>52.8</v>
@@ -2723,7 +2765,7 @@
         <v>11</v>
       </c>
       <c r="B45" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C45">
         <v>60</v>
@@ -2746,7 +2788,7 @@
         <v>11</v>
       </c>
       <c r="B46" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C46">
         <v>100</v>
@@ -2769,7 +2811,7 @@
         <v>11</v>
       </c>
       <c r="B47" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C47">
         <v>130</v>
@@ -2792,7 +2834,7 @@
         <v>11</v>
       </c>
       <c r="B48" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C48">
         <v>140</v>
@@ -2807,7 +2849,7 @@
         <v>10</v>
       </c>
       <c r="G48" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H48">
         <v>144.6666666666667</v>
@@ -2818,7 +2860,7 @@
         <v>11</v>
       </c>
       <c r="B49" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C49">
         <v>130</v>
@@ -2841,7 +2883,7 @@
         <v>11</v>
       </c>
       <c r="B50" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C50">
         <v>100</v>
@@ -2864,7 +2906,7 @@
         <v>11</v>
       </c>
       <c r="B51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C51">
         <v>100</v>
@@ -2879,7 +2921,7 @@
         <v>9</v>
       </c>
       <c r="G51" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H51">
         <v>133.3333333333333</v>
@@ -2890,7 +2932,7 @@
         <v>11</v>
       </c>
       <c r="B52" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C52">
         <v>20</v>
@@ -2905,7 +2947,7 @@
         <v>8</v>
       </c>
       <c r="G52" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H52">
         <v>26.66666666666666</v>
@@ -2916,7 +2958,7 @@
         <v>11</v>
       </c>
       <c r="B53" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C53">
         <v>20</v>
@@ -2931,7 +2973,7 @@
         <v>9</v>
       </c>
       <c r="G53" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H53">
         <v>26.66666666666666</v>
@@ -2942,7 +2984,7 @@
         <v>11</v>
       </c>
       <c r="B54" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C54">
         <v>30</v>
@@ -2965,7 +3007,7 @@
         <v>11</v>
       </c>
       <c r="B55" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C55">
         <v>40</v>
@@ -2988,7 +3030,7 @@
         <v>11</v>
       </c>
       <c r="B56" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C56">
         <v>40</v>
@@ -3011,7 +3053,7 @@
         <v>11</v>
       </c>
       <c r="B57" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C57">
         <v>40</v>
@@ -3034,7 +3076,7 @@
         <v>11</v>
       </c>
       <c r="B58" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C58">
         <v>45</v>
@@ -3057,7 +3099,7 @@
         <v>11</v>
       </c>
       <c r="B59" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C59">
         <v>45</v>
@@ -3080,7 +3122,7 @@
         <v>11</v>
       </c>
       <c r="B60" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C60">
         <v>50</v>
@@ -3095,7 +3137,7 @@
         <v>7.5</v>
       </c>
       <c r="G60" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H60">
         <v>63.33333333333333</v>
@@ -3106,7 +3148,7 @@
         <v>11</v>
       </c>
       <c r="B61" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C61">
         <v>50</v>
@@ -3121,7 +3163,7 @@
         <v>7.5</v>
       </c>
       <c r="G61" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H61">
         <v>63.33333333333333</v>
@@ -3132,7 +3174,7 @@
         <v>11</v>
       </c>
       <c r="B62" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C62">
         <v>50</v>
@@ -3147,7 +3189,7 @@
         <v>8.5</v>
       </c>
       <c r="G62" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H62">
         <v>63.33333333333333</v>
@@ -3158,7 +3200,7 @@
         <v>11</v>
       </c>
       <c r="B63" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C63">
         <v>50</v>
@@ -3173,7 +3215,7 @@
         <v>8.5</v>
       </c>
       <c r="G63" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H63">
         <v>63.33333333333333</v>
@@ -3184,7 +3226,7 @@
         <v>11</v>
       </c>
       <c r="B64" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C64">
         <v>50</v>
@@ -3199,7 +3241,7 @@
         <v>9</v>
       </c>
       <c r="G64" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H64">
         <v>63.33333333333333</v>
@@ -3210,7 +3252,7 @@
         <v>11</v>
       </c>
       <c r="B65" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C65">
         <v>50</v>
@@ -3225,7 +3267,7 @@
         <v>9</v>
       </c>
       <c r="G65" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H65">
         <v>63.33333333333333</v>
@@ -3236,7 +3278,7 @@
         <v>12</v>
       </c>
       <c r="B66" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C66">
         <v>60</v>
@@ -3259,7 +3301,7 @@
         <v>12</v>
       </c>
       <c r="B67" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C67">
         <v>100</v>
@@ -3282,7 +3324,7 @@
         <v>12</v>
       </c>
       <c r="B68" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C68">
         <v>100</v>
@@ -3305,7 +3347,7 @@
         <v>12</v>
       </c>
       <c r="B69" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C69">
         <v>60</v>
@@ -3328,7 +3370,7 @@
         <v>12</v>
       </c>
       <c r="B70" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C70">
         <v>100</v>
@@ -3351,7 +3393,7 @@
         <v>12</v>
       </c>
       <c r="B71" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C71">
         <v>80</v>
@@ -3374,7 +3416,7 @@
         <v>12</v>
       </c>
       <c r="B72" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C72">
         <v>80</v>
@@ -3397,7 +3439,7 @@
         <v>12</v>
       </c>
       <c r="B73" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C73">
         <v>20</v>
@@ -3420,7 +3462,7 @@
         <v>12</v>
       </c>
       <c r="B74" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C74">
         <v>30</v>
@@ -3443,7 +3485,7 @@
         <v>12</v>
       </c>
       <c r="B75" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C75">
         <v>35</v>
@@ -3466,7 +3508,7 @@
         <v>12</v>
       </c>
       <c r="B76" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C76">
         <v>35</v>
@@ -3481,7 +3523,7 @@
         <v>10</v>
       </c>
       <c r="G76" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H76">
         <v>43.16666666666667</v>
@@ -3492,7 +3534,7 @@
         <v>12</v>
       </c>
       <c r="B77" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C77">
         <v>30</v>
@@ -3515,7 +3557,7 @@
         <v>12</v>
       </c>
       <c r="B78" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C78">
         <v>30</v>
@@ -3538,7 +3580,7 @@
         <v>12</v>
       </c>
       <c r="B79" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C79">
         <v>50</v>
@@ -3561,7 +3603,7 @@
         <v>12</v>
       </c>
       <c r="B80" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C80">
         <v>40</v>
@@ -3584,7 +3626,7 @@
         <v>12</v>
       </c>
       <c r="B81" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C81">
         <v>22</v>
@@ -3607,7 +3649,7 @@
         <v>12</v>
       </c>
       <c r="B82" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C82">
         <v>22</v>
@@ -3630,7 +3672,7 @@
         <v>12</v>
       </c>
       <c r="B83" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C83">
         <v>22</v>
@@ -3653,7 +3695,7 @@
         <v>13</v>
       </c>
       <c r="B84" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C84">
         <v>20</v>
@@ -3668,7 +3710,7 @@
         <v>4</v>
       </c>
       <c r="G84" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H84">
         <v>28</v>
@@ -3679,7 +3721,7 @@
         <v>13</v>
       </c>
       <c r="B85" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C85">
         <v>40</v>
@@ -3702,7 +3744,7 @@
         <v>13</v>
       </c>
       <c r="B86" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C86">
         <v>50</v>
@@ -3725,7 +3767,7 @@
         <v>13</v>
       </c>
       <c r="B87" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C87">
         <v>60</v>
@@ -3748,7 +3790,7 @@
         <v>13</v>
       </c>
       <c r="B88" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C88">
         <v>60</v>
@@ -3771,7 +3813,7 @@
         <v>13</v>
       </c>
       <c r="B89" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C89">
         <v>60</v>
@@ -3786,7 +3828,7 @@
         <v>9</v>
       </c>
       <c r="G89" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H89">
         <v>64</v>
@@ -3797,7 +3839,7 @@
         <v>13</v>
       </c>
       <c r="B90" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C90">
         <v>40</v>
@@ -3812,7 +3854,7 @@
         <v>8</v>
       </c>
       <c r="G90" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H90">
         <v>60</v>
@@ -3823,7 +3865,7 @@
         <v>13</v>
       </c>
       <c r="B91" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C91">
         <v>16</v>
@@ -3838,7 +3880,7 @@
         <v>7</v>
       </c>
       <c r="G91" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H91">
         <v>21.33333333333333</v>
@@ -3849,7 +3891,7 @@
         <v>13</v>
       </c>
       <c r="B92" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C92">
         <v>16</v>
@@ -3864,7 +3906,7 @@
         <v>7</v>
       </c>
       <c r="G92" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H92">
         <v>21.33333333333333</v>
@@ -3875,7 +3917,7 @@
         <v>13</v>
       </c>
       <c r="B93" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C93">
         <v>16</v>
@@ -3890,7 +3932,7 @@
         <v>8</v>
       </c>
       <c r="G93" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H93">
         <v>21.33333333333333</v>
@@ -3901,7 +3943,7 @@
         <v>13</v>
       </c>
       <c r="B94" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C94">
         <v>16</v>
@@ -3916,7 +3958,7 @@
         <v>8</v>
       </c>
       <c r="G94" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H94">
         <v>21.33333333333333</v>
@@ -3927,7 +3969,7 @@
         <v>13</v>
       </c>
       <c r="B95" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C95">
         <v>16</v>
@@ -3942,7 +3984,7 @@
         <v>8.5</v>
       </c>
       <c r="G95" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H95">
         <v>21.33333333333333</v>
@@ -3953,7 +3995,7 @@
         <v>13</v>
       </c>
       <c r="B96" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C96">
         <v>16</v>
@@ -3968,7 +4010,7 @@
         <v>8.5</v>
       </c>
       <c r="G96" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H96">
         <v>21.33333333333333</v>
@@ -3979,7 +4021,7 @@
         <v>13</v>
       </c>
       <c r="B97" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C97">
         <v>8</v>
@@ -4002,7 +4044,7 @@
         <v>13</v>
       </c>
       <c r="B98" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C98">
         <v>8</v>
@@ -4025,7 +4067,7 @@
         <v>13</v>
       </c>
       <c r="B99" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C99">
         <v>8</v>
@@ -4048,7 +4090,7 @@
         <v>13</v>
       </c>
       <c r="B100" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C100">
         <v>58</v>
@@ -4063,7 +4105,7 @@
         <v>7</v>
       </c>
       <c r="G100" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H100">
         <v>77.33333333333333</v>
@@ -4074,7 +4116,7 @@
         <v>13</v>
       </c>
       <c r="B101" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C101">
         <v>58</v>
@@ -4089,7 +4131,7 @@
         <v>7</v>
       </c>
       <c r="G101" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H101">
         <v>77.33333333333333</v>
@@ -4100,7 +4142,7 @@
         <v>13</v>
       </c>
       <c r="B102" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C102">
         <v>58</v>
@@ -4123,7 +4165,7 @@
         <v>13</v>
       </c>
       <c r="B103" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C103">
         <v>58</v>
@@ -4146,7 +4188,7 @@
         <v>13</v>
       </c>
       <c r="B104" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C104">
         <v>58</v>
@@ -4169,7 +4211,7 @@
         <v>13</v>
       </c>
       <c r="B105" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C105">
         <v>58</v>
@@ -4192,7 +4234,7 @@
         <v>13</v>
       </c>
       <c r="B106" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C106">
         <v>45</v>
@@ -4215,7 +4257,7 @@
         <v>13</v>
       </c>
       <c r="B107" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C107">
         <v>45</v>
@@ -4238,7 +4280,7 @@
         <v>13</v>
       </c>
       <c r="B108" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C108">
         <v>45</v>
@@ -4261,7 +4303,7 @@
         <v>13</v>
       </c>
       <c r="B109" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C109">
         <v>20</v>
@@ -4284,7 +4326,7 @@
         <v>13</v>
       </c>
       <c r="B110" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C110">
         <v>30</v>
@@ -4299,7 +4341,7 @@
         <v>10</v>
       </c>
       <c r="G110" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H110">
         <v>34</v>
@@ -4310,7 +4352,7 @@
         <v>14</v>
       </c>
       <c r="B111" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C111">
         <v>20</v>
@@ -4325,7 +4367,7 @@
         <v>3</v>
       </c>
       <c r="G111" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H111">
         <v>25.33333333333333</v>
@@ -4336,7 +4378,7 @@
         <v>14</v>
       </c>
       <c r="B112" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C112">
         <v>60</v>
@@ -4351,7 +4393,7 @@
         <v>5</v>
       </c>
       <c r="G112" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H112">
         <v>66</v>
@@ -4362,7 +4404,7 @@
         <v>14</v>
       </c>
       <c r="B113" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C113">
         <v>80</v>
@@ -4377,7 +4419,7 @@
         <v>7</v>
       </c>
       <c r="G113" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H113">
         <v>88</v>
@@ -4388,7 +4430,7 @@
         <v>14</v>
       </c>
       <c r="B114" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C114">
         <v>90</v>
@@ -4403,7 +4445,7 @@
         <v>7</v>
       </c>
       <c r="G114" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H114">
         <v>93.00000000000001</v>
@@ -4414,7 +4456,7 @@
         <v>14</v>
       </c>
       <c r="B115" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C115">
         <v>90</v>
@@ -4429,7 +4471,7 @@
         <v>7.5</v>
       </c>
       <c r="G115" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H115">
         <v>99.00000000000001</v>
@@ -4440,7 +4482,7 @@
         <v>14</v>
       </c>
       <c r="B116" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C116">
         <v>100</v>
@@ -4455,7 +4497,7 @@
         <v>8.5</v>
       </c>
       <c r="G116" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H116">
         <v>110</v>
@@ -4466,7 +4508,7 @@
         <v>14</v>
       </c>
       <c r="B117" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C117">
         <v>110</v>
@@ -4481,7 +4523,7 @@
         <v>9</v>
       </c>
       <c r="G117" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H117">
         <v>113.6666666666667</v>
@@ -4492,7 +4534,7 @@
         <v>14</v>
       </c>
       <c r="B118" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C118">
         <v>20</v>
@@ -4507,7 +4549,7 @@
         <v>5</v>
       </c>
       <c r="G118" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H118">
         <v>28</v>
@@ -4518,7 +4560,7 @@
         <v>14</v>
       </c>
       <c r="B119" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C119">
         <v>30</v>
@@ -4533,7 +4575,7 @@
         <v>6</v>
       </c>
       <c r="G119" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H119">
         <v>36</v>
@@ -4544,7 +4586,7 @@
         <v>14</v>
       </c>
       <c r="B120" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C120">
         <v>40</v>
@@ -4559,7 +4601,7 @@
         <v>7.5</v>
       </c>
       <c r="G120" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H120">
         <v>45.33333333333333</v>
@@ -4570,7 +4612,7 @@
         <v>14</v>
       </c>
       <c r="B121" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C121">
         <v>45</v>
@@ -4585,7 +4627,7 @@
         <v>8.5</v>
       </c>
       <c r="G121" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H121">
         <v>49.50000000000001</v>
@@ -4596,7 +4638,7 @@
         <v>14</v>
       </c>
       <c r="B122" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C122">
         <v>50</v>
@@ -4611,7 +4653,7 @@
         <v>10</v>
       </c>
       <c r="G122" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H122">
         <v>50</v>
@@ -4622,7 +4664,7 @@
         <v>14</v>
       </c>
       <c r="B123" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C123">
         <v>70</v>
@@ -4637,7 +4679,7 @@
         <v>6</v>
       </c>
       <c r="G123" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H123">
         <v>77</v>
@@ -4648,7 +4690,7 @@
         <v>14</v>
       </c>
       <c r="B124" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C124">
         <v>120</v>
@@ -4663,7 +4705,7 @@
         <v>8.5</v>
       </c>
       <c r="G124" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H124">
         <v>124</v>
@@ -4674,7 +4716,7 @@
         <v>14</v>
       </c>
       <c r="B125" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C125">
         <v>120</v>
@@ -4689,7 +4731,7 @@
         <v>9.5</v>
       </c>
       <c r="G125" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H125">
         <v>124</v>
@@ -4700,7 +4742,7 @@
         <v>14</v>
       </c>
       <c r="B126" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C126">
         <v>120</v>
@@ -4715,7 +4757,7 @@
         <v>9.5</v>
       </c>
       <c r="G126" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H126">
         <v>124</v>
@@ -4726,7 +4768,7 @@
         <v>14</v>
       </c>
       <c r="B127" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C127">
         <v>120</v>
@@ -4741,7 +4783,7 @@
         <v>9.5</v>
       </c>
       <c r="G127" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H127">
         <v>124</v>
@@ -4752,7 +4794,7 @@
         <v>14</v>
       </c>
       <c r="B128" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C128">
         <v>20</v>
@@ -4767,7 +4809,7 @@
         <v>6.5</v>
       </c>
       <c r="G128" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H128">
         <v>26.66666666666666</v>
@@ -4778,7 +4820,7 @@
         <v>14</v>
       </c>
       <c r="B129" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C129">
         <v>20</v>
@@ -4793,7 +4835,7 @@
         <v>6.5</v>
       </c>
       <c r="G129" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H129">
         <v>26.66666666666666</v>
@@ -4804,7 +4846,7 @@
         <v>14</v>
       </c>
       <c r="B130" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C130">
         <v>20</v>
@@ -4819,7 +4861,7 @@
         <v>8</v>
       </c>
       <c r="G130" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H130">
         <v>26.66666666666666</v>
@@ -4830,7 +4872,7 @@
         <v>14</v>
       </c>
       <c r="B131" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C131">
         <v>20</v>
@@ -4845,7 +4887,7 @@
         <v>8</v>
       </c>
       <c r="G131" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H131">
         <v>26.66666666666666</v>
@@ -4856,7 +4898,7 @@
         <v>14</v>
       </c>
       <c r="B132" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C132">
         <v>20</v>
@@ -4871,7 +4913,7 @@
         <v>8.5</v>
       </c>
       <c r="G132" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H132">
         <v>26.66666666666666</v>
@@ -4882,7 +4924,7 @@
         <v>14</v>
       </c>
       <c r="B133" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C133">
         <v>20</v>
@@ -4897,7 +4939,7 @@
         <v>8.5</v>
       </c>
       <c r="G133" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H133">
         <v>26.66666666666666</v>
@@ -4908,7 +4950,7 @@
         <v>15</v>
       </c>
       <c r="B134" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C134">
         <v>20</v>
@@ -4923,7 +4965,7 @@
         <v>3</v>
       </c>
       <c r="G134" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H134">
         <v>25.33333333333333</v>
@@ -4934,7 +4976,7 @@
         <v>15</v>
       </c>
       <c r="B135" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C135">
         <v>60</v>
@@ -4949,7 +4991,7 @@
         <v>6</v>
       </c>
       <c r="G135" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H135">
         <v>72</v>
@@ -4960,7 +5002,7 @@
         <v>15</v>
       </c>
       <c r="B136" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C136">
         <v>80</v>
@@ -4975,7 +5017,7 @@
         <v>7</v>
       </c>
       <c r="G136" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H136">
         <v>88</v>
@@ -4986,7 +5028,7 @@
         <v>15</v>
       </c>
       <c r="B137" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C137">
         <v>100</v>
@@ -5001,7 +5043,7 @@
         <v>7</v>
       </c>
       <c r="G137" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H137">
         <v>103.3333333333333</v>
@@ -5012,7 +5054,7 @@
         <v>15</v>
       </c>
       <c r="B138" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C138">
         <v>70</v>
@@ -5027,7 +5069,7 @@
         <v>8</v>
       </c>
       <c r="G138" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H138">
         <v>98</v>
@@ -5038,7 +5080,7 @@
         <v>15</v>
       </c>
       <c r="B139" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C139">
         <v>80</v>
@@ -5053,7 +5095,7 @@
         <v>8.5</v>
       </c>
       <c r="G139" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H139">
         <v>101.3333333333333</v>
@@ -5064,7 +5106,7 @@
         <v>15</v>
       </c>
       <c r="B140" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C140">
         <v>20</v>
@@ -5079,7 +5121,7 @@
         <v>5</v>
       </c>
       <c r="G140" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H140">
         <v>28</v>
@@ -5090,7 +5132,7 @@
         <v>15</v>
       </c>
       <c r="B141" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C141">
         <v>30</v>
@@ -5105,7 +5147,7 @@
         <v>7</v>
       </c>
       <c r="G141" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H141">
         <v>38</v>
@@ -5116,7 +5158,7 @@
         <v>15</v>
       </c>
       <c r="B142" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C142">
         <v>40</v>
@@ -5131,7 +5173,7 @@
         <v>8</v>
       </c>
       <c r="G142" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H142">
         <v>48</v>
@@ -5142,7 +5184,7 @@
         <v>15</v>
       </c>
       <c r="B143" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C143">
         <v>40</v>
@@ -5157,7 +5199,7 @@
         <v>9</v>
       </c>
       <c r="G143" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H143">
         <v>48</v>
@@ -5168,7 +5210,7 @@
         <v>15</v>
       </c>
       <c r="B144" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C144">
         <v>30</v>
@@ -5183,7 +5225,7 @@
         <v>9</v>
       </c>
       <c r="G144" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H144">
         <v>42</v>
@@ -5194,7 +5236,7 @@
         <v>15</v>
       </c>
       <c r="B145" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C145">
         <v>30</v>
@@ -5209,7 +5251,7 @@
         <v>7</v>
       </c>
       <c r="G145" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H145">
         <v>45</v>
@@ -5220,7 +5262,7 @@
         <v>15</v>
       </c>
       <c r="B146" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C146">
         <v>50</v>
@@ -5235,7 +5277,7 @@
         <v>7.5</v>
       </c>
       <c r="G146" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H146">
         <v>63.33333333333333</v>
@@ -5246,7 +5288,7 @@
         <v>15</v>
       </c>
       <c r="B147" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C147">
         <v>50</v>
@@ -5261,7 +5303,7 @@
         <v>8</v>
       </c>
       <c r="G147" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H147">
         <v>63.33333333333333</v>
@@ -5272,7 +5314,7 @@
         <v>15</v>
       </c>
       <c r="B148" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C148">
         <v>50</v>
@@ -5287,7 +5329,7 @@
         <v>8.5</v>
       </c>
       <c r="G148" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H148">
         <v>63.33333333333333</v>
@@ -5298,7 +5340,7 @@
         <v>15</v>
       </c>
       <c r="B149" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C149">
         <v>50</v>
@@ -5313,7 +5355,7 @@
         <v>9.5</v>
       </c>
       <c r="G149" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H149">
         <v>63.33333333333333</v>
@@ -5324,7 +5366,7 @@
         <v>15</v>
       </c>
       <c r="B150" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C150">
         <v>40</v>
@@ -5339,7 +5381,7 @@
         <v>8</v>
       </c>
       <c r="G150" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H150">
         <v>56</v>
@@ -5350,7 +5392,7 @@
         <v>15</v>
       </c>
       <c r="B151" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C151">
         <v>70</v>
@@ -5365,7 +5407,7 @@
         <v>6</v>
       </c>
       <c r="G151" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H151">
         <v>84</v>
@@ -5376,7 +5418,7 @@
         <v>15</v>
       </c>
       <c r="B152" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C152">
         <v>120</v>
@@ -5391,7 +5433,7 @@
         <v>6</v>
       </c>
       <c r="G152" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H152">
         <v>124</v>
@@ -5402,7 +5444,7 @@
         <v>15</v>
       </c>
       <c r="B153" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C153">
         <v>120</v>
@@ -5417,7 +5459,7 @@
         <v>8</v>
       </c>
       <c r="G153" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H153">
         <v>140</v>
@@ -5428,7 +5470,7 @@
         <v>15</v>
       </c>
       <c r="B154" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C154">
         <v>130</v>
@@ -5443,7 +5485,7 @@
         <v>8.5</v>
       </c>
       <c r="G154" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H154">
         <v>151.6666666666667</v>
@@ -5454,7 +5496,7 @@
         <v>15</v>
       </c>
       <c r="B155" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C155">
         <v>130</v>
@@ -5469,7 +5511,7 @@
         <v>9</v>
       </c>
       <c r="G155" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H155">
         <v>151.6666666666667</v>
@@ -5480,7 +5522,7 @@
         <v>16</v>
       </c>
       <c r="B156" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C156">
         <v>20</v>
@@ -5495,7 +5537,7 @@
         <v>4</v>
       </c>
       <c r="G156" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H156">
         <v>28</v>
@@ -5506,7 +5548,7 @@
         <v>16</v>
       </c>
       <c r="B157" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C157">
         <v>40</v>
@@ -5529,7 +5571,7 @@
         <v>16</v>
       </c>
       <c r="B158" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C158">
         <v>60</v>
@@ -5544,7 +5586,7 @@
         <v>6.5</v>
       </c>
       <c r="G158" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H158">
         <v>62.00000000000001</v>
@@ -5555,7 +5597,7 @@
         <v>16</v>
       </c>
       <c r="B159" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C159">
         <v>70</v>
@@ -5570,7 +5612,7 @@
         <v>8.5</v>
       </c>
       <c r="G159" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H159">
         <v>72.33333333333334</v>
@@ -5581,7 +5623,7 @@
         <v>16</v>
       </c>
       <c r="B160" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C160">
         <v>65</v>
@@ -5596,7 +5638,7 @@
         <v>8</v>
       </c>
       <c r="G160" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H160">
         <v>67.16666666666667</v>
@@ -5607,7 +5649,7 @@
         <v>16</v>
       </c>
       <c r="B161" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C161">
         <v>60</v>
@@ -5630,7 +5672,7 @@
         <v>16</v>
       </c>
       <c r="B162" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C162">
         <v>60</v>
@@ -5645,7 +5687,7 @@
         <v>9</v>
       </c>
       <c r="G162" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H162">
         <v>66</v>
@@ -5656,7 +5698,7 @@
         <v>16</v>
       </c>
       <c r="B163" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C163">
         <v>45</v>
@@ -5671,7 +5713,7 @@
         <v>8</v>
       </c>
       <c r="G163" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H163">
         <v>62.99999999999999</v>
@@ -5682,7 +5724,7 @@
         <v>16</v>
       </c>
       <c r="B164" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C164">
         <v>45</v>
@@ -5705,7 +5747,7 @@
         <v>16</v>
       </c>
       <c r="B165" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C165">
         <v>20</v>
@@ -5720,7 +5762,7 @@
         <v>7</v>
       </c>
       <c r="G165" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H165">
         <v>26.66666666666666</v>
@@ -5731,7 +5773,7 @@
         <v>16</v>
       </c>
       <c r="B166" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C166">
         <v>20</v>
@@ -5746,7 +5788,7 @@
         <v>6</v>
       </c>
       <c r="G166" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H166">
         <v>28</v>
@@ -5757,7 +5799,7 @@
         <v>16</v>
       </c>
       <c r="B167" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C167">
         <v>20</v>
@@ -5772,7 +5814,7 @@
         <v>7</v>
       </c>
       <c r="G167" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H167">
         <v>28</v>
@@ -5783,7 +5825,7 @@
         <v>16</v>
       </c>
       <c r="B168" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C168">
         <v>20</v>
@@ -5798,7 +5840,7 @@
         <v>7</v>
       </c>
       <c r="G168" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H168">
         <v>30</v>
@@ -5809,7 +5851,7 @@
         <v>16</v>
       </c>
       <c r="B169" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C169">
         <v>22.5</v>
@@ -5824,7 +5866,7 @@
         <v>7.5</v>
       </c>
       <c r="G169" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H169">
         <v>30</v>
@@ -5835,7 +5877,7 @@
         <v>16</v>
       </c>
       <c r="B170" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C170">
         <v>22.5</v>
@@ -5850,7 +5892,7 @@
         <v>7</v>
       </c>
       <c r="G170" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H170">
         <v>31.5</v>
@@ -5861,7 +5903,7 @@
         <v>16</v>
       </c>
       <c r="B171" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C171">
         <v>25</v>
@@ -5876,7 +5918,7 @@
         <v>8</v>
       </c>
       <c r="G171" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H171">
         <v>31.66666666666666</v>
@@ -5887,7 +5929,7 @@
         <v>16</v>
       </c>
       <c r="B172" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C172">
         <v>25</v>
@@ -5902,7 +5944,7 @@
         <v>7.5</v>
       </c>
       <c r="G172" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H172">
         <v>35</v>
@@ -5913,7 +5955,7 @@
         <v>16</v>
       </c>
       <c r="B173" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C173">
         <v>25</v>
@@ -5928,7 +5970,7 @@
         <v>8</v>
       </c>
       <c r="G173" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H173">
         <v>31.66666666666666</v>
@@ -5939,7 +5981,7 @@
         <v>16</v>
       </c>
       <c r="B174" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C174">
         <v>25</v>
@@ -5954,7 +5996,7 @@
         <v>8</v>
       </c>
       <c r="G174" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H174">
         <v>37.5</v>
@@ -5965,7 +6007,7 @@
         <v>16</v>
       </c>
       <c r="B175" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C175">
         <v>40</v>
@@ -5980,7 +6022,7 @@
         <v>7.5</v>
       </c>
       <c r="G175" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H175">
         <v>50.66666666666666</v>
@@ -5991,7 +6033,7 @@
         <v>16</v>
       </c>
       <c r="B176" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C176">
         <v>40</v>
@@ -6006,7 +6048,7 @@
         <v>8.5</v>
       </c>
       <c r="G176" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H176">
         <v>50.66666666666666</v>
@@ -6017,7 +6059,7 @@
         <v>16</v>
       </c>
       <c r="B177" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C177">
         <v>40</v>
@@ -6032,7 +6074,7 @@
         <v>9</v>
       </c>
       <c r="G177" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H177">
         <v>48</v>
@@ -6043,7 +6085,7 @@
         <v>16</v>
       </c>
       <c r="B178" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C178">
         <v>22</v>
@@ -6058,7 +6100,7 @@
         <v>7</v>
       </c>
       <c r="G178" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H178">
         <v>27.86666666666667</v>
@@ -6069,7 +6111,7 @@
         <v>16</v>
       </c>
       <c r="B179" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C179">
         <v>22</v>
@@ -6092,7 +6134,7 @@
         <v>16</v>
       </c>
       <c r="B180" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C180">
         <v>22</v>
@@ -6107,7 +6149,7 @@
         <v>8.5</v>
       </c>
       <c r="G180" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H180">
         <v>27.86666666666667</v>
@@ -6118,7 +6160,7 @@
         <v>17</v>
       </c>
       <c r="B181" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C181">
         <v>20</v>
@@ -6141,7 +6183,7 @@
         <v>17</v>
       </c>
       <c r="B182" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C182">
         <v>22</v>
@@ -6164,7 +6206,7 @@
         <v>17</v>
       </c>
       <c r="B183" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C183">
         <v>20</v>
@@ -6179,7 +6221,7 @@
         <v>4</v>
       </c>
       <c r="G183" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H183">
         <v>25.33333333333333</v>
@@ -6190,7 +6232,7 @@
         <v>17</v>
       </c>
       <c r="B184" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C184">
         <v>60</v>
@@ -6213,7 +6255,7 @@
         <v>17</v>
       </c>
       <c r="B185" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C185">
         <v>80</v>
@@ -6236,7 +6278,7 @@
         <v>17</v>
       </c>
       <c r="B186" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C186">
         <v>100</v>
@@ -6259,7 +6301,7 @@
         <v>17</v>
       </c>
       <c r="B187" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C187">
         <v>110</v>
@@ -6282,7 +6324,7 @@
         <v>17</v>
       </c>
       <c r="B188" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C188">
         <v>120</v>
@@ -6297,7 +6339,7 @@
         <v>8.5</v>
       </c>
       <c r="G188" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H188">
         <v>124</v>
@@ -6308,7 +6350,7 @@
         <v>17</v>
       </c>
       <c r="B189" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C189">
         <v>80</v>
@@ -6323,7 +6365,7 @@
         <v>7.5</v>
       </c>
       <c r="G189" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H189">
         <v>112</v>
@@ -6334,7 +6376,7 @@
         <v>17</v>
       </c>
       <c r="B190" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C190">
         <v>-30</v>
@@ -6349,7 +6391,7 @@
         <v>6</v>
       </c>
       <c r="G190" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H190">
         <v>-38</v>
@@ -6360,7 +6402,7 @@
         <v>17</v>
       </c>
       <c r="B191" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C191">
         <v>-30</v>
@@ -6375,7 +6417,7 @@
         <v>6</v>
       </c>
       <c r="G191" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H191">
         <v>-38</v>
@@ -6386,7 +6428,7 @@
         <v>17</v>
       </c>
       <c r="B192" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C192">
         <v>-25</v>
@@ -6401,7 +6443,7 @@
         <v>7.5</v>
       </c>
       <c r="G192" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H192">
         <v>-33.33333333333333</v>
@@ -6412,7 +6454,7 @@
         <v>17</v>
       </c>
       <c r="B193" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C193">
         <v>-25</v>
@@ -6427,7 +6469,7 @@
         <v>7.5</v>
       </c>
       <c r="G193" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H193">
         <v>-33.33333333333333</v>
@@ -6438,7 +6480,7 @@
         <v>17</v>
       </c>
       <c r="B194" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C194">
         <v>-20</v>
@@ -6453,7 +6495,7 @@
         <v>8</v>
       </c>
       <c r="G194" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H194">
         <v>-25.33333333333333</v>
@@ -6464,7 +6506,7 @@
         <v>17</v>
       </c>
       <c r="B195" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C195">
         <v>-20</v>
@@ -6479,7 +6521,7 @@
         <v>8</v>
       </c>
       <c r="G195" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H195">
         <v>-25.33333333333333</v>
@@ -6490,7 +6532,7 @@
         <v>17</v>
       </c>
       <c r="B196" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C196">
         <v>35</v>
@@ -6505,7 +6547,7 @@
         <v>7</v>
       </c>
       <c r="G196" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H196">
         <v>52.5</v>
@@ -6516,7 +6558,7 @@
         <v>17</v>
       </c>
       <c r="B197" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C197">
         <v>25</v>
@@ -6531,7 +6573,7 @@
         <v>7</v>
       </c>
       <c r="G197" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H197">
         <v>37.5</v>
@@ -6542,7 +6584,7 @@
         <v>17</v>
       </c>
       <c r="B198" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C198">
         <v>35</v>
@@ -6557,7 +6599,7 @@
         <v>7</v>
       </c>
       <c r="G198" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H198">
         <v>52.5</v>
@@ -6568,7 +6610,7 @@
         <v>17</v>
       </c>
       <c r="B199" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C199">
         <v>25</v>
@@ -6583,7 +6625,7 @@
         <v>7</v>
       </c>
       <c r="G199" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H199">
         <v>37.5</v>
@@ -6594,7 +6636,7 @@
         <v>18</v>
       </c>
       <c r="B200" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C200">
         <v>70</v>
@@ -6609,7 +6651,7 @@
         <v>6</v>
       </c>
       <c r="G200" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H200">
         <v>84</v>
@@ -6620,7 +6662,7 @@
         <v>18</v>
       </c>
       <c r="B201" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C201">
         <v>90</v>
@@ -6643,7 +6685,7 @@
         <v>18</v>
       </c>
       <c r="B202" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C202">
         <v>120</v>
@@ -6666,7 +6708,7 @@
         <v>18</v>
       </c>
       <c r="B203" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C203">
         <v>120</v>
@@ -6689,7 +6731,7 @@
         <v>18</v>
       </c>
       <c r="B204" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C204">
         <v>120</v>
@@ -6712,7 +6754,7 @@
         <v>18</v>
       </c>
       <c r="B205" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C205">
         <v>120</v>
@@ -6735,7 +6777,7 @@
         <v>18</v>
       </c>
       <c r="B206" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C206">
         <v>120</v>
@@ -6758,7 +6800,7 @@
         <v>18</v>
       </c>
       <c r="B207" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C207">
         <v>20</v>
@@ -6773,7 +6815,7 @@
         <v>6</v>
       </c>
       <c r="G207" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H207">
         <v>28</v>
@@ -6784,7 +6826,7 @@
         <v>18</v>
       </c>
       <c r="B208" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C208">
         <v>30</v>
@@ -6807,7 +6849,7 @@
         <v>18</v>
       </c>
       <c r="B209" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C209">
         <v>35</v>
@@ -6830,7 +6872,7 @@
         <v>18</v>
       </c>
       <c r="B210" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C210">
         <v>35</v>
@@ -6853,7 +6895,7 @@
         <v>18</v>
       </c>
       <c r="B211" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C211">
         <v>35</v>
@@ -6876,7 +6918,7 @@
         <v>18</v>
       </c>
       <c r="B212" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C212">
         <v>22</v>
@@ -6891,7 +6933,7 @@
         <v>7.5</v>
       </c>
       <c r="G212" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H212">
         <v>27.86666666666667</v>
@@ -6902,7 +6944,7 @@
         <v>18</v>
       </c>
       <c r="B213" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C213">
         <v>22</v>
@@ -6917,7 +6959,7 @@
         <v>7.5</v>
       </c>
       <c r="G213" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H213">
         <v>30.8</v>
@@ -6928,7 +6970,7 @@
         <v>18</v>
       </c>
       <c r="B214" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C214">
         <v>22</v>
@@ -6943,7 +6985,7 @@
         <v>8</v>
       </c>
       <c r="G214" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H214">
         <v>27.86666666666667</v>
@@ -6954,7 +6996,7 @@
         <v>18</v>
       </c>
       <c r="B215" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C215">
         <v>22</v>
@@ -6969,7 +7011,7 @@
         <v>8</v>
       </c>
       <c r="G215" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H215">
         <v>30.8</v>
@@ -6980,7 +7022,7 @@
         <v>18</v>
       </c>
       <c r="B216" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C216">
         <v>22</v>
@@ -6995,7 +7037,7 @@
         <v>8.5</v>
       </c>
       <c r="G216" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H216">
         <v>27.86666666666667</v>
@@ -7006,7 +7048,7 @@
         <v>18</v>
       </c>
       <c r="B217" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C217">
         <v>22</v>
@@ -7021,7 +7063,7 @@
         <v>8</v>
       </c>
       <c r="G217" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H217">
         <v>30.8</v>
@@ -7032,7 +7074,7 @@
         <v>18</v>
       </c>
       <c r="B218" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C218">
         <v>25</v>
@@ -7047,7 +7089,7 @@
         <v>8</v>
       </c>
       <c r="G218" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H218">
         <v>31.66666666666666</v>
@@ -7058,7 +7100,7 @@
         <v>18</v>
       </c>
       <c r="B219" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C219">
         <v>25</v>
@@ -7073,7 +7115,7 @@
         <v>6.5</v>
       </c>
       <c r="G219" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H219">
         <v>31.66666666666666</v>
@@ -7084,7 +7126,7 @@
         <v>18</v>
       </c>
       <c r="B220" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C220">
         <v>25</v>
@@ -7099,7 +7141,7 @@
         <v>8</v>
       </c>
       <c r="G220" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H220">
         <v>31.66666666666666</v>
@@ -7110,7 +7152,7 @@
         <v>18</v>
       </c>
       <c r="B221" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C221">
         <v>25</v>
@@ -7125,7 +7167,7 @@
         <v>7.5</v>
       </c>
       <c r="G221" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H221">
         <v>31.66666666666666</v>
@@ -7136,7 +7178,7 @@
         <v>18</v>
       </c>
       <c r="B222" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C222">
         <v>25</v>
@@ -7151,7 +7193,7 @@
         <v>9</v>
       </c>
       <c r="G222" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H222">
         <v>31.66666666666666</v>
@@ -7162,7 +7204,7 @@
         <v>18</v>
       </c>
       <c r="B223" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C223">
         <v>25</v>
@@ -7177,7 +7219,7 @@
         <v>9</v>
       </c>
       <c r="G223" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H223">
         <v>31.66666666666666</v>
@@ -7188,7 +7230,7 @@
         <v>19</v>
       </c>
       <c r="B224" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C224">
         <v>70</v>
@@ -7203,7 +7245,7 @@
         <v>6.5</v>
       </c>
       <c r="G224" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H224">
         <v>84</v>
@@ -7214,7 +7256,7 @@
         <v>19</v>
       </c>
       <c r="B225" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C225">
         <v>85</v>
@@ -7229,7 +7271,7 @@
         <v>8</v>
       </c>
       <c r="G225" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H225">
         <v>119</v>
@@ -7240,7 +7282,7 @@
         <v>19</v>
       </c>
       <c r="B226" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C226">
         <v>85</v>
@@ -7255,7 +7297,7 @@
         <v>9</v>
       </c>
       <c r="G226" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H226">
         <v>119</v>
@@ -7266,7 +7308,7 @@
         <v>19</v>
       </c>
       <c r="B227" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C227">
         <v>85</v>
@@ -7281,7 +7323,7 @@
         <v>10</v>
       </c>
       <c r="G227" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H227">
         <v>113.3333333333333</v>
@@ -7292,7 +7334,7 @@
         <v>19</v>
       </c>
       <c r="B228" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C228">
         <v>30</v>
@@ -7307,7 +7349,7 @@
         <v>6</v>
       </c>
       <c r="G228" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H228">
         <v>36</v>
@@ -7318,7 +7360,7 @@
         <v>19</v>
       </c>
       <c r="B229" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C229">
         <v>30</v>
@@ -7333,7 +7375,7 @@
         <v>6</v>
       </c>
       <c r="G229" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H229">
         <v>38</v>
@@ -7344,7 +7386,7 @@
         <v>19</v>
       </c>
       <c r="B230" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C230">
         <v>40</v>
@@ -7359,7 +7401,7 @@
         <v>8</v>
       </c>
       <c r="G230" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H230">
         <v>50.66666666666666</v>
@@ -7370,7 +7412,7 @@
         <v>19</v>
       </c>
       <c r="B231" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C231">
         <v>40</v>
@@ -7385,7 +7427,7 @@
         <v>9</v>
       </c>
       <c r="G231" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H231">
         <v>50.66666666666666</v>
@@ -7396,7 +7438,7 @@
         <v>19</v>
       </c>
       <c r="B232" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C232">
         <v>40</v>
@@ -7411,7 +7453,7 @@
         <v>10</v>
       </c>
       <c r="G232" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H232">
         <v>49.33333333333334</v>
@@ -7422,7 +7464,7 @@
         <v>19</v>
       </c>
       <c r="B233" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C233">
         <v>40</v>
@@ -7437,7 +7479,7 @@
         <v>6.5</v>
       </c>
       <c r="G233" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H233">
         <v>56</v>
@@ -7448,7 +7490,7 @@
         <v>19</v>
       </c>
       <c r="B234" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C234">
         <v>40</v>
@@ -7463,7 +7505,7 @@
         <v>6.5</v>
       </c>
       <c r="G234" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H234">
         <v>56</v>
@@ -7474,7 +7516,7 @@
         <v>19</v>
       </c>
       <c r="B235" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C235">
         <v>40</v>
@@ -7489,7 +7531,7 @@
         <v>7.5</v>
       </c>
       <c r="G235" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H235">
         <v>56</v>
@@ -7500,7 +7542,7 @@
         <v>19</v>
       </c>
       <c r="B236" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C236">
         <v>40</v>
@@ -7515,7 +7557,7 @@
         <v>9</v>
       </c>
       <c r="G236" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H236">
         <v>56</v>
@@ -7526,7 +7568,7 @@
         <v>19</v>
       </c>
       <c r="B237" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C237">
         <v>60</v>
@@ -7541,7 +7583,7 @@
         <v>8</v>
       </c>
       <c r="G237" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H237">
         <v>80</v>
@@ -7552,7 +7594,7 @@
         <v>19</v>
       </c>
       <c r="B238" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C238">
         <v>60</v>
@@ -7567,7 +7609,7 @@
         <v>7</v>
       </c>
       <c r="G238" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H238">
         <v>80</v>
@@ -7578,7 +7620,7 @@
         <v>19</v>
       </c>
       <c r="B239" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C239">
         <v>60</v>
@@ -7593,7 +7635,7 @@
         <v>8.5</v>
       </c>
       <c r="G239" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H239">
         <v>80</v>
@@ -7604,7 +7646,7 @@
         <v>19</v>
       </c>
       <c r="B240" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C240">
         <v>60</v>
@@ -7619,7 +7661,7 @@
         <v>8</v>
       </c>
       <c r="G240" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H240">
         <v>80</v>
@@ -7630,7 +7672,7 @@
         <v>19</v>
       </c>
       <c r="B241" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C241">
         <v>60</v>
@@ -7645,7 +7687,7 @@
         <v>9</v>
       </c>
       <c r="G241" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H241">
         <v>80</v>
@@ -7656,7 +7698,7 @@
         <v>19</v>
       </c>
       <c r="B242" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C242">
         <v>60</v>
@@ -7671,7 +7713,7 @@
         <v>9</v>
       </c>
       <c r="G242" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H242">
         <v>80</v>
@@ -7682,7 +7724,7 @@
         <v>20</v>
       </c>
       <c r="B243" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C243">
         <v>60</v>
@@ -7697,7 +7739,7 @@
         <v>4</v>
       </c>
       <c r="G243" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H243">
         <v>76</v>
@@ -7708,7 +7750,7 @@
         <v>20</v>
       </c>
       <c r="B244" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C244">
         <v>100</v>
@@ -7723,7 +7765,7 @@
         <v>6</v>
       </c>
       <c r="G244" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H244">
         <v>116.6666666666667</v>
@@ -7734,7 +7776,7 @@
         <v>20</v>
       </c>
       <c r="B245" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C245">
         <v>130</v>
@@ -7749,7 +7791,7 @@
         <v>7</v>
       </c>
       <c r="G245" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H245">
         <v>134.3333333333333</v>
@@ -7760,7 +7802,7 @@
         <v>20</v>
       </c>
       <c r="B246" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C246">
         <v>150</v>
@@ -7775,7 +7817,7 @@
         <v>8.5</v>
       </c>
       <c r="G246" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H246">
         <v>155</v>
@@ -7786,7 +7828,7 @@
         <v>20</v>
       </c>
       <c r="B247" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C247">
         <v>120</v>
@@ -7801,7 +7843,7 @@
         <v>7.5</v>
       </c>
       <c r="G247" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H247">
         <v>140</v>
@@ -7812,7 +7854,7 @@
         <v>20</v>
       </c>
       <c r="B248" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C248">
         <v>120</v>
@@ -7827,7 +7869,7 @@
         <v>7.5</v>
       </c>
       <c r="G248" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H248">
         <v>140</v>
@@ -7838,7 +7880,7 @@
         <v>20</v>
       </c>
       <c r="B249" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C249">
         <v>120</v>
@@ -7853,7 +7895,7 @@
         <v>8</v>
       </c>
       <c r="G249" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H249">
         <v>140</v>
@@ -7864,7 +7906,7 @@
         <v>20</v>
       </c>
       <c r="B250" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C250">
         <v>120</v>
@@ -7879,7 +7921,7 @@
         <v>8.5</v>
       </c>
       <c r="G250" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H250">
         <v>140</v>
@@ -7890,7 +7932,7 @@
         <v>20</v>
       </c>
       <c r="B251" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C251">
         <v>120</v>
@@ -7905,7 +7947,7 @@
         <v>9</v>
       </c>
       <c r="G251" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H251">
         <v>140</v>
@@ -7916,7 +7958,7 @@
         <v>20</v>
       </c>
       <c r="B252" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C252">
         <v>40</v>
@@ -7931,7 +7973,7 @@
         <v>5</v>
       </c>
       <c r="G252" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H252">
         <v>50.66666666666666</v>
@@ -7942,7 +7984,7 @@
         <v>20</v>
       </c>
       <c r="B253" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C253">
         <v>50</v>
@@ -7957,7 +7999,7 @@
         <v>6</v>
       </c>
       <c r="G253" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H253">
         <v>58.33333333333334</v>
@@ -7968,7 +8010,7 @@
         <v>20</v>
       </c>
       <c r="B254" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C254">
         <v>60</v>
@@ -7983,7 +8025,7 @@
         <v>7</v>
       </c>
       <c r="G254" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H254">
         <v>70</v>
@@ -7994,7 +8036,7 @@
         <v>20</v>
       </c>
       <c r="B255" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C255">
         <v>60</v>
@@ -8009,7 +8051,7 @@
         <v>8</v>
       </c>
       <c r="G255" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H255">
         <v>70</v>
@@ -8020,7 +8062,7 @@
         <v>20</v>
       </c>
       <c r="B256" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C256">
         <v>60</v>
@@ -8035,7 +8077,7 @@
         <v>8.5</v>
       </c>
       <c r="G256" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H256">
         <v>70</v>
@@ -8046,7 +8088,7 @@
         <v>20</v>
       </c>
       <c r="B257" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C257">
         <v>60</v>
@@ -8061,7 +8103,7 @@
         <v>8.5</v>
       </c>
       <c r="G257" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H257">
         <v>70</v>
@@ -8072,7 +8114,7 @@
         <v>20</v>
       </c>
       <c r="B258" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C258">
         <v>60</v>
@@ -8087,7 +8129,7 @@
         <v>8</v>
       </c>
       <c r="G258" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H258">
         <v>70</v>
@@ -8098,7 +8140,7 @@
         <v>20</v>
       </c>
       <c r="B259" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C259">
         <v>40</v>
@@ -8113,7 +8155,7 @@
         <v>5</v>
       </c>
       <c r="G259" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H259">
         <v>53.33333333333333</v>
@@ -8124,7 +8166,7 @@
         <v>20</v>
       </c>
       <c r="B260" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C260">
         <v>50</v>
@@ -8139,7 +8181,7 @@
         <v>7</v>
       </c>
       <c r="G260" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H260">
         <v>63.33333333333333</v>
@@ -8150,7 +8192,7 @@
         <v>20</v>
       </c>
       <c r="B261" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C261">
         <v>50</v>
@@ -8165,7 +8207,7 @@
         <v>7</v>
       </c>
       <c r="G261" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H261">
         <v>63.33333333333333</v>
@@ -8176,7 +8218,7 @@
         <v>20</v>
       </c>
       <c r="B262" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C262">
         <v>50</v>
@@ -8191,7 +8233,7 @@
         <v>7.5</v>
       </c>
       <c r="G262" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H262">
         <v>63.33333333333333</v>
@@ -8202,7 +8244,7 @@
         <v>20</v>
       </c>
       <c r="B263" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C263">
         <v>50</v>
@@ -8217,7 +8259,7 @@
         <v>8</v>
       </c>
       <c r="G263" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H263">
         <v>66.66666666666666</v>
@@ -8228,7 +8270,7 @@
         <v>20</v>
       </c>
       <c r="B264" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C264">
         <v>20</v>
@@ -8243,7 +8285,7 @@
         <v>7</v>
       </c>
       <c r="G264" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H264">
         <v>26.66666666666666</v>
@@ -8254,7 +8296,7 @@
         <v>20</v>
       </c>
       <c r="B265" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C265">
         <v>20</v>
@@ -8269,7 +8311,7 @@
         <v>7</v>
       </c>
       <c r="G265" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H265">
         <v>28</v>
@@ -8280,7 +8322,7 @@
         <v>20</v>
       </c>
       <c r="B266" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C266">
         <v>25</v>
@@ -8295,7 +8337,7 @@
         <v>8.5</v>
       </c>
       <c r="G266" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H266">
         <v>31.66666666666666</v>
@@ -8306,7 +8348,7 @@
         <v>20</v>
       </c>
       <c r="B267" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C267">
         <v>25</v>
@@ -8321,7 +8363,7 @@
         <v>7.5</v>
       </c>
       <c r="G267" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H267">
         <v>33.33333333333333</v>
@@ -8332,7 +8374,7 @@
         <v>20</v>
       </c>
       <c r="B268" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C268">
         <v>25</v>
@@ -8347,7 +8389,7 @@
         <v>8.5</v>
       </c>
       <c r="G268" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H268">
         <v>31.66666666666666</v>
@@ -8358,7 +8400,7 @@
         <v>20</v>
       </c>
       <c r="B269" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C269">
         <v>25</v>
@@ -8373,7 +8415,7 @@
         <v>8</v>
       </c>
       <c r="G269" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H269">
         <v>35</v>
@@ -8384,7 +8426,7 @@
         <v>20</v>
       </c>
       <c r="B270" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C270">
         <v>25</v>
@@ -8399,7 +8441,7 @@
         <v>9</v>
       </c>
       <c r="G270" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H270">
         <v>31.66666666666666</v>
@@ -8410,7 +8452,7 @@
         <v>20</v>
       </c>
       <c r="B271" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C271">
         <v>25</v>
@@ -8425,7 +8467,7 @@
         <v>9</v>
       </c>
       <c r="G271" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H271">
         <v>37.5</v>
@@ -8436,7 +8478,7 @@
         <v>21</v>
       </c>
       <c r="B272" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C272">
         <v>20</v>
@@ -8459,7 +8501,7 @@
         <v>21</v>
       </c>
       <c r="B273" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C273">
         <v>60</v>
@@ -8482,7 +8524,7 @@
         <v>21</v>
       </c>
       <c r="B274" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C274">
         <v>100</v>
@@ -8505,7 +8547,7 @@
         <v>21</v>
       </c>
       <c r="B275" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C275">
         <v>100</v>
@@ -8528,7 +8570,7 @@
         <v>21</v>
       </c>
       <c r="B276" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C276">
         <v>60</v>
@@ -8551,7 +8593,7 @@
         <v>21</v>
       </c>
       <c r="B277" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C277">
         <v>90</v>
@@ -8574,7 +8616,7 @@
         <v>21</v>
       </c>
       <c r="B278" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C278">
         <v>110</v>
@@ -8597,7 +8639,7 @@
         <v>21</v>
       </c>
       <c r="B279" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C279">
         <v>30</v>
@@ -8620,7 +8662,7 @@
         <v>21</v>
       </c>
       <c r="B280" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C280">
         <v>40</v>
@@ -8643,7 +8685,7 @@
         <v>21</v>
       </c>
       <c r="B281" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C281">
         <v>40</v>
@@ -8666,7 +8708,7 @@
         <v>21</v>
       </c>
       <c r="B282" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C282">
         <v>30</v>
@@ -8689,7 +8731,7 @@
         <v>21</v>
       </c>
       <c r="B283" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C283">
         <v>30</v>
@@ -8712,7 +8754,7 @@
         <v>21</v>
       </c>
       <c r="B284" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C284">
         <v>40</v>
@@ -8735,7 +8777,7 @@
         <v>21</v>
       </c>
       <c r="B285" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C285">
         <v>40</v>
@@ -8758,7 +8800,7 @@
         <v>21</v>
       </c>
       <c r="B286" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C286">
         <v>40</v>
@@ -8781,7 +8823,7 @@
         <v>21</v>
       </c>
       <c r="B287" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C287">
         <v>40</v>
@@ -8804,7 +8846,7 @@
         <v>21</v>
       </c>
       <c r="B288" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C288">
         <v>60</v>
@@ -8827,7 +8869,7 @@
         <v>21</v>
       </c>
       <c r="B289" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C289">
         <v>60</v>
@@ -8850,7 +8892,7 @@
         <v>21</v>
       </c>
       <c r="B290" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C290">
         <v>60</v>
@@ -8873,7 +8915,7 @@
         <v>21</v>
       </c>
       <c r="B291" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C291">
         <v>60</v>
@@ -8896,7 +8938,7 @@
         <v>21</v>
       </c>
       <c r="B292" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C292">
         <v>60</v>
@@ -8919,7 +8961,7 @@
         <v>21</v>
       </c>
       <c r="B293" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C293">
         <v>60</v>
@@ -8942,7 +8984,7 @@
         <v>22</v>
       </c>
       <c r="B294" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C294">
         <v>20</v>
@@ -8957,7 +8999,7 @@
         <v>3</v>
       </c>
       <c r="G294" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H294">
         <v>28</v>
@@ -8968,7 +9010,7 @@
         <v>22</v>
       </c>
       <c r="B295" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C295">
         <v>60</v>
@@ -8983,7 +9025,7 @@
         <v>6</v>
       </c>
       <c r="G295" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H295">
         <v>76</v>
@@ -8994,7 +9036,7 @@
         <v>22</v>
       </c>
       <c r="B296" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C296">
         <v>110</v>
@@ -9009,7 +9051,7 @@
         <v>7.5</v>
       </c>
       <c r="G296" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H296">
         <v>121</v>
@@ -9020,7 +9062,7 @@
         <v>22</v>
       </c>
       <c r="B297" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C297">
         <v>70</v>
@@ -9035,7 +9077,7 @@
         <v>8</v>
       </c>
       <c r="G297" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H297">
         <v>116.6666666666667</v>
@@ -9046,7 +9088,7 @@
         <v>22</v>
       </c>
       <c r="B298" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C298">
         <v>80</v>
@@ -9061,7 +9103,7 @@
         <v>8.5</v>
       </c>
       <c r="G298" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H298">
         <v>112</v>
@@ -9072,7 +9114,7 @@
         <v>22</v>
       </c>
       <c r="B299" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C299">
         <v>60</v>
@@ -9087,7 +9129,7 @@
         <v>5</v>
       </c>
       <c r="G299" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H299">
         <v>80</v>
@@ -9098,7 +9140,7 @@
         <v>22</v>
       </c>
       <c r="B300" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C300">
         <v>110</v>
@@ -9113,7 +9155,7 @@
         <v>6.5</v>
       </c>
       <c r="G300" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H300">
         <v>128.3333333333333</v>
@@ -9124,7 +9166,7 @@
         <v>22</v>
       </c>
       <c r="B301" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C301">
         <v>140</v>
@@ -9139,7 +9181,7 @@
         <v>7</v>
       </c>
       <c r="G301" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H301">
         <v>144.6666666666667</v>
@@ -9150,7 +9192,7 @@
         <v>22</v>
       </c>
       <c r="B302" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C302">
         <v>160</v>
@@ -9165,7 +9207,7 @@
         <v>8.5</v>
       </c>
       <c r="G302" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H302">
         <v>165.3333333333333</v>
@@ -9176,7 +9218,7 @@
         <v>22</v>
       </c>
       <c r="B303" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C303">
         <v>170</v>
@@ -9191,7 +9233,7 @@
         <v>9</v>
       </c>
       <c r="G303" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H303">
         <v>175.6666666666667</v>
@@ -9202,7 +9244,7 @@
         <v>22</v>
       </c>
       <c r="B304" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C304">
         <v>30</v>
@@ -9217,7 +9259,7 @@
         <v>7</v>
       </c>
       <c r="G304" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H304">
         <v>40</v>
@@ -9228,7 +9270,7 @@
         <v>22</v>
       </c>
       <c r="B305" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C305">
         <v>40</v>
@@ -9243,7 +9285,7 @@
         <v>7</v>
       </c>
       <c r="G305" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H305">
         <v>44</v>
@@ -9254,7 +9296,7 @@
         <v>22</v>
       </c>
       <c r="B306" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C306">
         <v>50</v>
@@ -9269,7 +9311,7 @@
         <v>9.5</v>
       </c>
       <c r="G306" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H306">
         <v>53.33333333333334</v>
@@ -9280,7 +9322,7 @@
         <v>22</v>
       </c>
       <c r="B307" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C307">
         <v>40</v>
@@ -9295,7 +9337,7 @@
         <v>8.5</v>
       </c>
       <c r="G307" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H307">
         <v>53.33333333333333</v>
@@ -9306,7 +9348,7 @@
         <v>23</v>
       </c>
       <c r="B308" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C308">
         <v>70</v>
@@ -9329,7 +9371,7 @@
         <v>23</v>
       </c>
       <c r="B309" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C309">
         <v>120</v>
@@ -9352,7 +9394,7 @@
         <v>23</v>
       </c>
       <c r="B310" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C310">
         <v>140</v>
@@ -9375,7 +9417,7 @@
         <v>23</v>
       </c>
       <c r="B311" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C311">
         <v>140</v>
@@ -9398,7 +9440,7 @@
         <v>23</v>
       </c>
       <c r="B312" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C312">
         <v>120</v>
@@ -9421,7 +9463,7 @@
         <v>23</v>
       </c>
       <c r="B313" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C313">
         <v>20</v>
@@ -9444,7 +9486,7 @@
         <v>23</v>
       </c>
       <c r="B314" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C314">
         <v>40</v>
@@ -9467,7 +9509,7 @@
         <v>23</v>
       </c>
       <c r="B315" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C315">
         <v>60</v>
@@ -9490,7 +9532,7 @@
         <v>23</v>
       </c>
       <c r="B316" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C316">
         <v>70</v>
@@ -9513,7 +9555,7 @@
         <v>23</v>
       </c>
       <c r="B317" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C317">
         <v>80</v>
@@ -9536,7 +9578,7 @@
         <v>23</v>
       </c>
       <c r="B318" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C318">
         <v>75</v>
@@ -9559,7 +9601,7 @@
         <v>23</v>
       </c>
       <c r="B319" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C319">
         <v>60</v>
@@ -9582,7 +9624,7 @@
         <v>23</v>
       </c>
       <c r="B320" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C320">
         <v>60</v>
@@ -9605,7 +9647,7 @@
         <v>23</v>
       </c>
       <c r="B321" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C321">
         <v>60</v>
@@ -9628,7 +9670,7 @@
         <v>23</v>
       </c>
       <c r="B322" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C322">
         <v>65</v>
@@ -9651,7 +9693,7 @@
         <v>23</v>
       </c>
       <c r="B323" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C323">
         <v>65</v>
@@ -9674,7 +9716,7 @@
         <v>23</v>
       </c>
       <c r="B324" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C324">
         <v>65</v>
@@ -9697,7 +9739,7 @@
         <v>23</v>
       </c>
       <c r="B325" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C325">
         <v>65</v>
@@ -9720,7 +9762,7 @@
         <v>23</v>
       </c>
       <c r="B326" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C326">
         <v>65</v>
@@ -9743,7 +9785,7 @@
         <v>23</v>
       </c>
       <c r="B327" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C327">
         <v>65</v>
@@ -9766,7 +9808,7 @@
         <v>23</v>
       </c>
       <c r="B328" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C328">
         <v>65</v>
@@ -9789,7 +9831,7 @@
         <v>23</v>
       </c>
       <c r="B329" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C329">
         <v>65</v>
@@ -9812,7 +9854,7 @@
         <v>24</v>
       </c>
       <c r="B330" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C330">
         <v>20</v>
@@ -9827,7 +9869,7 @@
         <v>3</v>
       </c>
       <c r="G330" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H330">
         <v>25.33333333333333</v>
@@ -9838,7 +9880,7 @@
         <v>24</v>
       </c>
       <c r="B331" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C331">
         <v>70</v>
@@ -9853,7 +9895,7 @@
         <v>6</v>
       </c>
       <c r="G331" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H331">
         <v>81.66666666666667</v>
@@ -9864,7 +9906,7 @@
         <v>24</v>
       </c>
       <c r="B332" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C332">
         <v>90</v>
@@ -9879,7 +9921,7 @@
         <v>6</v>
       </c>
       <c r="G332" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H332">
         <v>93.00000000000001</v>
@@ -9890,7 +9932,7 @@
         <v>24</v>
       </c>
       <c r="B333" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C333">
         <v>120</v>
@@ -9905,7 +9947,7 @@
         <v>7.5</v>
       </c>
       <c r="G333" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H333">
         <v>124</v>
@@ -9916,7 +9958,7 @@
         <v>24</v>
       </c>
       <c r="B334" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C334">
         <v>140</v>
@@ -9931,7 +9973,7 @@
         <v>10</v>
       </c>
       <c r="G334" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H334">
         <v>140</v>
@@ -9942,7 +9984,7 @@
         <v>24</v>
       </c>
       <c r="B335" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C335">
         <v>80</v>
@@ -9957,7 +9999,7 @@
         <v>8.5</v>
       </c>
       <c r="G335" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H335">
         <v>133.3333333333333</v>
@@ -9968,7 +10010,7 @@
         <v>24</v>
       </c>
       <c r="B336" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C336">
         <v>80</v>
@@ -9983,7 +10025,7 @@
         <v>10</v>
       </c>
       <c r="G336" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H336">
         <v>101.3333333333333</v>
@@ -9994,7 +10036,7 @@
         <v>24</v>
       </c>
       <c r="B337" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C337">
         <v>20</v>
@@ -10009,7 +10051,7 @@
         <v>4</v>
       </c>
       <c r="G337" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H337">
         <v>25.33333333333333</v>
@@ -10020,7 +10062,7 @@
         <v>24</v>
       </c>
       <c r="B338" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C338">
         <v>40</v>
@@ -10035,7 +10077,7 @@
         <v>6</v>
       </c>
       <c r="G338" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H338">
         <v>50.66666666666666</v>
@@ -10046,7 +10088,7 @@
         <v>24</v>
       </c>
       <c r="B339" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C339">
         <v>60</v>
@@ -10061,7 +10103,7 @@
         <v>7</v>
       </c>
       <c r="G339" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H339">
         <v>66</v>
@@ -10072,7 +10114,7 @@
         <v>24</v>
       </c>
       <c r="B340" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C340">
         <v>70</v>
@@ -10087,7 +10129,7 @@
         <v>8.5</v>
       </c>
       <c r="G340" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H340">
         <v>77</v>
@@ -10098,7 +10140,7 @@
         <v>24</v>
       </c>
       <c r="B341" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C341">
         <v>75</v>
@@ -10113,7 +10155,7 @@
         <v>8.75</v>
       </c>
       <c r="G341" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H341">
         <v>77.50000000000001</v>
@@ -10124,7 +10166,7 @@
         <v>24</v>
       </c>
       <c r="B342" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C342">
         <v>50</v>
@@ -10139,7 +10181,7 @@
         <v>8</v>
       </c>
       <c r="G342" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H342">
         <v>66.66666666666666</v>
@@ -10150,7 +10192,7 @@
         <v>24</v>
       </c>
       <c r="B343" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C343">
         <v>40</v>
@@ -10165,7 +10207,7 @@
         <v>6</v>
       </c>
       <c r="G343" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H343">
         <v>50.66666666666666</v>
@@ -10176,7 +10218,7 @@
         <v>24</v>
       </c>
       <c r="B344" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C344">
         <v>50</v>
@@ -10191,7 +10233,7 @@
         <v>6.5</v>
       </c>
       <c r="G344" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H344">
         <v>63.33333333333333</v>
@@ -10202,7 +10244,7 @@
         <v>24</v>
       </c>
       <c r="B345" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C345">
         <v>63</v>
@@ -10217,7 +10259,7 @@
         <v>8</v>
       </c>
       <c r="G345" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H345">
         <v>75.59999999999999</v>
@@ -10228,7 +10270,7 @@
         <v>24</v>
       </c>
       <c r="B346" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C346">
         <v>63</v>
@@ -10243,7 +10285,7 @@
         <v>8.5</v>
       </c>
       <c r="G346" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H346">
         <v>75.59999999999999</v>
@@ -10254,7 +10296,7 @@
         <v>24</v>
       </c>
       <c r="B347" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C347">
         <v>11</v>
@@ -10269,7 +10311,7 @@
         <v>5</v>
       </c>
       <c r="G347" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H347">
         <v>16.5</v>
@@ -10280,7 +10322,7 @@
         <v>24</v>
       </c>
       <c r="B348" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C348">
         <v>32</v>
@@ -10295,7 +10337,7 @@
         <v>5</v>
       </c>
       <c r="G348" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H348">
         <v>48</v>
@@ -10306,7 +10348,7 @@
         <v>24</v>
       </c>
       <c r="B349" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C349">
         <v>33</v>
@@ -10321,7 +10363,7 @@
         <v>7</v>
       </c>
       <c r="G349" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H349">
         <v>49.5</v>
@@ -10332,7 +10374,7 @@
         <v>24</v>
       </c>
       <c r="B350" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C350">
         <v>59</v>
@@ -10347,7 +10389,7 @@
         <v>8</v>
       </c>
       <c r="G350" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H350">
         <v>82.59999999999999</v>
@@ -10358,7 +10400,7 @@
         <v>24</v>
       </c>
       <c r="B351" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C351">
         <v>39</v>
@@ -10373,7 +10415,7 @@
         <v>9</v>
       </c>
       <c r="G351" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H351">
         <v>58.5</v>
@@ -10384,7 +10426,7 @@
         <v>24</v>
       </c>
       <c r="B352" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C352">
         <v>66</v>
@@ -10399,7 +10441,7 @@
         <v>9</v>
       </c>
       <c r="G352" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H352">
         <v>92.39999999999999</v>
@@ -10410,7 +10452,7 @@
         <v>25</v>
       </c>
       <c r="B353" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C353">
         <v>70</v>
@@ -10425,7 +10467,7 @@
         <v>6</v>
       </c>
       <c r="G353" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H353">
         <v>81.66666666666667</v>
@@ -10436,7 +10478,7 @@
         <v>25</v>
       </c>
       <c r="B354" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C354">
         <v>120</v>
@@ -10451,7 +10493,7 @@
         <v>6</v>
       </c>
       <c r="G354" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H354">
         <v>124</v>
@@ -10462,7 +10504,7 @@
         <v>25</v>
       </c>
       <c r="B355" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C355">
         <v>140</v>
@@ -10477,7 +10519,7 @@
         <v>6.5</v>
       </c>
       <c r="G355" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H355">
         <v>144.6666666666667</v>
@@ -10488,7 +10530,7 @@
         <v>25</v>
       </c>
       <c r="B356" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C356">
         <v>160</v>
@@ -10503,7 +10545,7 @@
         <v>8.5</v>
       </c>
       <c r="G356" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H356">
         <v>165.3333333333333</v>
@@ -10514,7 +10556,7 @@
         <v>25</v>
       </c>
       <c r="B357" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C357">
         <v>140</v>
@@ -10529,7 +10571,7 @@
         <v>8.5</v>
       </c>
       <c r="G357" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H357">
         <v>163.3333333333333</v>
@@ -10540,7 +10582,7 @@
         <v>25</v>
       </c>
       <c r="B358" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C358">
         <v>140</v>
@@ -10555,7 +10597,7 @@
         <v>9</v>
       </c>
       <c r="G358" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H358">
         <v>163.3333333333333</v>
@@ -10566,7 +10608,7 @@
         <v>25</v>
       </c>
       <c r="B359" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C359">
         <v>120</v>
@@ -10581,7 +10623,7 @@
         <v>9</v>
       </c>
       <c r="G359" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H359">
         <v>144</v>
@@ -10592,7 +10634,7 @@
         <v>25</v>
       </c>
       <c r="B360" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C360">
         <v>30</v>
@@ -10607,7 +10649,7 @@
         <v>6</v>
       </c>
       <c r="G360" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H360">
         <v>38</v>
@@ -10618,7 +10660,7 @@
         <v>25</v>
       </c>
       <c r="B361" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C361">
         <v>40</v>
@@ -10633,7 +10675,7 @@
         <v>7</v>
       </c>
       <c r="G361" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H361">
         <v>48</v>
@@ -10644,7 +10686,7 @@
         <v>25</v>
       </c>
       <c r="B362" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C362">
         <v>50</v>
@@ -10659,7 +10701,7 @@
         <v>8</v>
       </c>
       <c r="G362" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H362">
         <v>53.33333333333334</v>
@@ -10670,7 +10712,7 @@
         <v>25</v>
       </c>
       <c r="B363" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C363">
         <v>55</v>
@@ -10685,7 +10727,7 @@
         <v>10</v>
       </c>
       <c r="G363" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H363">
         <v>56.83333333333334</v>
@@ -10696,7 +10738,7 @@
         <v>25</v>
       </c>
       <c r="B364" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C364">
         <v>45</v>
@@ -10711,7 +10753,7 @@
         <v>9</v>
       </c>
       <c r="G364" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H364">
         <v>52.5</v>
@@ -10722,7 +10764,7 @@
         <v>25</v>
       </c>
       <c r="B365" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C365">
         <v>45</v>
@@ -10737,7 +10779,7 @@
         <v>9.5</v>
       </c>
       <c r="G365" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H365">
         <v>52.5</v>
@@ -10748,7 +10790,7 @@
         <v>25</v>
       </c>
       <c r="B366" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C366">
         <v>45</v>
@@ -10763,7 +10805,7 @@
         <v>7</v>
       </c>
       <c r="G366" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H366">
         <v>57</v>
@@ -10774,7 +10816,7 @@
         <v>25</v>
       </c>
       <c r="B367" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C367">
         <v>50</v>
@@ -10789,7 +10831,7 @@
         <v>8</v>
       </c>
       <c r="G367" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H367">
         <v>63.33333333333333</v>
@@ -10800,7 +10842,7 @@
         <v>25</v>
       </c>
       <c r="B368" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C368">
         <v>50</v>
@@ -10815,7 +10857,7 @@
         <v>8</v>
       </c>
       <c r="G368" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H368">
         <v>63.33333333333333</v>
@@ -10826,7 +10868,7 @@
         <v>25</v>
       </c>
       <c r="B369" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C369">
         <v>50</v>
@@ -10841,7 +10883,7 @@
         <v>8</v>
       </c>
       <c r="G369" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H369">
         <v>63.33333333333333</v>
@@ -10852,7 +10894,7 @@
         <v>25</v>
       </c>
       <c r="B370" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C370">
         <v>40</v>
@@ -10867,7 +10909,7 @@
         <v>8.5</v>
       </c>
       <c r="G370" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H370">
         <v>60</v>
@@ -10878,7 +10920,7 @@
         <v>26</v>
       </c>
       <c r="B371" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C371">
         <v>20</v>
@@ -10893,7 +10935,7 @@
         <v>5</v>
       </c>
       <c r="G371" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H371">
         <v>25.33333333333333</v>
@@ -10904,7 +10946,7 @@
         <v>27</v>
       </c>
       <c r="B372" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C372">
         <v>40</v>
@@ -10919,7 +10961,7 @@
         <v>6</v>
       </c>
       <c r="G372" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H372">
         <v>46.66666666666667</v>
@@ -10930,7 +10972,7 @@
         <v>28</v>
       </c>
       <c r="B373" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C373">
         <v>50</v>
@@ -10945,7 +10987,7 @@
         <v>7</v>
       </c>
       <c r="G373" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H373">
         <v>60</v>
@@ -10956,7 +10998,7 @@
         <v>29</v>
       </c>
       <c r="B374" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C374">
         <v>50</v>
@@ -10971,7 +11013,7 @@
         <v>6.5</v>
       </c>
       <c r="G374" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H374">
         <v>63.33333333333333</v>
@@ -10982,7 +11024,7 @@
         <v>30</v>
       </c>
       <c r="B375" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C375">
         <v>60</v>
@@ -10997,7 +11039,7 @@
         <v>7</v>
       </c>
       <c r="G375" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H375">
         <v>66</v>
@@ -11008,7 +11050,7 @@
         <v>31</v>
       </c>
       <c r="B376" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C376">
         <v>70</v>
@@ -11023,7 +11065,7 @@
         <v>7.75</v>
       </c>
       <c r="G376" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H376">
         <v>72.33333333333334</v>
@@ -11034,7 +11076,7 @@
         <v>32</v>
       </c>
       <c r="B377" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C377">
         <v>75</v>
@@ -11049,7 +11091,7 @@
         <v>8</v>
       </c>
       <c r="G377" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H377">
         <v>77.50000000000001</v>
@@ -11060,7 +11102,7 @@
         <v>33</v>
       </c>
       <c r="B378" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C378">
         <v>77.5</v>
@@ -11075,7 +11117,7 @@
         <v>10</v>
       </c>
       <c r="G378" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H378">
         <v>77.5</v>
@@ -11086,7 +11128,7 @@
         <v>34</v>
       </c>
       <c r="B379" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C379">
         <v>66.25</v>
@@ -11101,7 +11143,7 @@
         <v>9</v>
       </c>
       <c r="G379" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H379">
         <v>77.29166666666667</v>
@@ -11112,7 +11154,7 @@
         <v>35</v>
       </c>
       <c r="B380" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C380">
         <v>60</v>
@@ -11127,7 +11169,7 @@
         <v>8.25</v>
       </c>
       <c r="G380" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H380">
         <v>70</v>
@@ -11138,7 +11180,7 @@
         <v>36</v>
       </c>
       <c r="B381" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C381">
         <v>30</v>
@@ -11153,7 +11195,7 @@
         <v>6</v>
       </c>
       <c r="G381" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H381">
         <v>42</v>
@@ -11164,7 +11206,7 @@
         <v>37</v>
       </c>
       <c r="B382" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C382">
         <v>50</v>
@@ -11179,7 +11221,7 @@
         <v>8.5</v>
       </c>
       <c r="G382" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H382">
         <v>63.33333333333333</v>
@@ -11190,7 +11232,7 @@
         <v>38</v>
       </c>
       <c r="B383" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C383">
         <v>50</v>
@@ -11205,7 +11247,7 @@
         <v>8</v>
       </c>
       <c r="G383" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H383">
         <v>63.33333333333333</v>
@@ -11216,7 +11258,7 @@
         <v>39</v>
       </c>
       <c r="B384" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C384">
         <v>50</v>
@@ -11231,7 +11273,7 @@
         <v>10</v>
       </c>
       <c r="G384" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H384">
         <v>60</v>
@@ -11242,7 +11284,7 @@
         <v>40</v>
       </c>
       <c r="B385" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C385">
         <v>0</v>
@@ -11257,7 +11299,7 @@
         <v>6</v>
       </c>
       <c r="G385" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H385">
         <v>0</v>
@@ -11268,7 +11310,7 @@
         <v>41</v>
       </c>
       <c r="B386" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C386">
         <v>25</v>
@@ -11283,7 +11325,7 @@
         <v>8</v>
       </c>
       <c r="G386" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H386">
         <v>30</v>
@@ -11294,7 +11336,7 @@
         <v>42</v>
       </c>
       <c r="B387" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C387">
         <v>25</v>
@@ -11309,7 +11351,7 @@
         <v>8</v>
       </c>
       <c r="G387" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H387">
         <v>31.66666666666666</v>
@@ -11320,7 +11362,7 @@
         <v>43</v>
       </c>
       <c r="B388" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C388">
         <v>25</v>
@@ -11335,7 +11377,7 @@
         <v>8.5</v>
       </c>
       <c r="G388" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H388">
         <v>31.66666666666666</v>
@@ -11346,7 +11388,7 @@
         <v>44</v>
       </c>
       <c r="B389" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C389">
         <v>45</v>
@@ -11361,7 +11403,7 @@
         <v>6.5</v>
       </c>
       <c r="G389" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H389">
         <v>62.99999999999999</v>
@@ -11372,7 +11414,7 @@
         <v>45</v>
       </c>
       <c r="B390" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C390">
         <v>60</v>
@@ -11387,7 +11429,7 @@
         <v>8</v>
       </c>
       <c r="G390" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H390">
         <v>76</v>
@@ -11398,7 +11440,7 @@
         <v>46</v>
       </c>
       <c r="B391" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C391">
         <v>60</v>
@@ -11413,7 +11455,7 @@
         <v>7.5</v>
       </c>
       <c r="G391" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H391">
         <v>76</v>
@@ -11424,7 +11466,7 @@
         <v>47</v>
       </c>
       <c r="B392" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C392">
         <v>60</v>
@@ -11439,7 +11481,7 @@
         <v>7.5</v>
       </c>
       <c r="G392" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H392">
         <v>76</v>
@@ -11450,7 +11492,7 @@
         <v>48</v>
       </c>
       <c r="B393" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C393">
         <v>60</v>
@@ -11465,7 +11507,7 @@
         <v>9</v>
       </c>
       <c r="G393" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H393">
         <v>76</v>
@@ -11476,7 +11518,7 @@
         <v>49</v>
       </c>
       <c r="B394" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C394">
         <v>40</v>
@@ -11491,7 +11533,7 @@
         <v>8</v>
       </c>
       <c r="G394" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H394">
         <v>53.33333333333333</v>
@@ -11502,7 +11544,7 @@
         <v>50</v>
       </c>
       <c r="B395" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C395">
         <v>40</v>
@@ -11517,7 +11559,7 @@
         <v>7.5</v>
       </c>
       <c r="G395" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H395">
         <v>56</v>
@@ -11528,7 +11570,7 @@
         <v>51</v>
       </c>
       <c r="B396" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C396">
         <v>40</v>
@@ -11543,7 +11585,7 @@
         <v>8</v>
       </c>
       <c r="G396" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H396">
         <v>56</v>
@@ -11554,7 +11596,7 @@
         <v>52</v>
       </c>
       <c r="B397" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C397">
         <v>40</v>
@@ -11569,7 +11611,7 @@
         <v>8</v>
       </c>
       <c r="G397" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H397">
         <v>56</v>
@@ -11580,7 +11622,7 @@
         <v>53</v>
       </c>
       <c r="B398" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C398">
         <v>40</v>
@@ -11595,7 +11637,7 @@
         <v>8.5</v>
       </c>
       <c r="G398" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H398">
         <v>56</v>
@@ -11606,7 +11648,7 @@
         <v>54</v>
       </c>
       <c r="B399" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C399">
         <v>40</v>
@@ -11621,7 +11663,7 @@
         <v>9</v>
       </c>
       <c r="G399" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H399">
         <v>56</v>
@@ -11632,7 +11674,7 @@
         <v>55</v>
       </c>
       <c r="B400" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C400">
         <v>20</v>
@@ -11647,7 +11689,7 @@
         <v>5</v>
       </c>
       <c r="G400" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H400">
         <v>25.33333333333333</v>
@@ -11658,7 +11700,7 @@
         <v>56</v>
       </c>
       <c r="B401" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C401">
         <v>70</v>
@@ -11673,7 +11715,7 @@
         <v>6</v>
       </c>
       <c r="G401" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H401">
         <v>81.66666666666667</v>
@@ -11684,7 +11726,7 @@
         <v>57</v>
       </c>
       <c r="B402" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C402">
         <v>120</v>
@@ -11699,7 +11741,7 @@
         <v>7.5</v>
       </c>
       <c r="G402" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H402">
         <v>124</v>
@@ -11710,7 +11752,7 @@
         <v>58</v>
       </c>
       <c r="B403" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C403">
         <v>110</v>
@@ -11725,7 +11767,7 @@
         <v>8.5</v>
       </c>
       <c r="G403" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H403">
         <v>128.3333333333333</v>
@@ -11736,7 +11778,7 @@
         <v>59</v>
       </c>
       <c r="B404" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C404">
         <v>110</v>
@@ -11751,7 +11793,7 @@
         <v>10</v>
       </c>
       <c r="G404" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H404">
         <v>124.6666666666667</v>
@@ -11762,7 +11804,7 @@
         <v>60</v>
       </c>
       <c r="B405" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C405">
         <v>100</v>
@@ -11777,7 +11819,7 @@
         <v>9.5</v>
       </c>
       <c r="G405" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H405">
         <v>110</v>
@@ -11788,7 +11830,7 @@
         <v>61</v>
       </c>
       <c r="B406" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C406">
         <v>40</v>
@@ -11803,7 +11845,7 @@
         <v>6</v>
       </c>
       <c r="G406" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H406">
         <v>60</v>
@@ -11814,7 +11856,7 @@
         <v>62</v>
       </c>
       <c r="B407" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C407">
         <v>50</v>
@@ -11829,7 +11871,7 @@
         <v>7</v>
       </c>
       <c r="G407" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H407">
         <v>70</v>
@@ -11840,7 +11882,7 @@
         <v>63</v>
       </c>
       <c r="B408" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C408">
         <v>50</v>
@@ -11855,7 +11897,7 @@
         <v>7.5</v>
       </c>
       <c r="G408" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H408">
         <v>70</v>
@@ -11866,7 +11908,7 @@
         <v>64</v>
       </c>
       <c r="B409" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C409">
         <v>50</v>
@@ -11881,7 +11923,7 @@
         <v>8.5</v>
       </c>
       <c r="G409" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H409">
         <v>70</v>
@@ -11892,7 +11934,7 @@
         <v>65</v>
       </c>
       <c r="B410" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C410">
         <v>30</v>
@@ -11907,7 +11949,7 @@
         <v>6</v>
       </c>
       <c r="G410" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H410">
         <v>40</v>
@@ -11918,7 +11960,7 @@
         <v>66</v>
       </c>
       <c r="B411" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C411">
         <v>30</v>
@@ -11933,7 +11975,7 @@
         <v>6.5</v>
       </c>
       <c r="G411" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H411">
         <v>40</v>
@@ -11944,7 +11986,7 @@
         <v>67</v>
       </c>
       <c r="B412" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C412">
         <v>40</v>
@@ -11959,7 +12001,7 @@
         <v>8.5</v>
       </c>
       <c r="G412" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H412">
         <v>53.33333333333333</v>
@@ -11970,7 +12012,7 @@
         <v>68</v>
       </c>
       <c r="B413" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C413">
         <v>40</v>
@@ -11985,7 +12027,7 @@
         <v>10</v>
       </c>
       <c r="G413" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H413">
         <v>50.66666666666666</v>
@@ -11996,7 +12038,7 @@
         <v>69</v>
       </c>
       <c r="B414" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C414">
         <v>40</v>
@@ -12011,7 +12053,7 @@
         <v>9</v>
       </c>
       <c r="G414" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H414">
         <v>50.66666666666666</v>
@@ -12022,7 +12064,7 @@
         <v>70</v>
       </c>
       <c r="B415" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C415">
         <v>30</v>
@@ -12037,7 +12079,7 @@
         <v>8</v>
       </c>
       <c r="G415" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H415">
         <v>35</v>
@@ -12048,7 +12090,7 @@
         <v>70</v>
       </c>
       <c r="B416" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C416">
         <v>30</v>
@@ -12063,7 +12105,7 @@
         <v>8</v>
       </c>
       <c r="G416" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H416">
         <v>42</v>
@@ -12074,7 +12116,7 @@
         <v>71</v>
       </c>
       <c r="B417" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C417">
         <v>30</v>
@@ -12089,7 +12131,7 @@
         <v>8.5</v>
       </c>
       <c r="G417" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H417">
         <v>36</v>
@@ -12100,7 +12142,7 @@
         <v>71</v>
       </c>
       <c r="B418" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C418">
         <v>30</v>
@@ -12115,7 +12157,7 @@
         <v>8.5</v>
       </c>
       <c r="G418" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H418">
         <v>42</v>
@@ -12126,7 +12168,7 @@
         <v>72</v>
       </c>
       <c r="B419" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C419">
         <v>30</v>
@@ -12141,7 +12183,7 @@
         <v>9</v>
       </c>
       <c r="G419" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H419">
         <v>36</v>
@@ -12152,7 +12194,7 @@
         <v>72</v>
       </c>
       <c r="B420" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C420">
         <v>30</v>
@@ -12167,7 +12209,7 @@
         <v>9</v>
       </c>
       <c r="G420" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H420">
         <v>42</v>
@@ -12178,7 +12220,7 @@
         <v>73</v>
       </c>
       <c r="B421" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C421">
         <v>20</v>
@@ -12190,7 +12232,7 @@
         <v>160</v>
       </c>
       <c r="G421" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H421">
         <v>25.33333333333333</v>
@@ -12204,7 +12246,7 @@
         <v>73</v>
       </c>
       <c r="B422" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C422">
         <v>70</v>
@@ -12216,7 +12258,7 @@
         <v>350</v>
       </c>
       <c r="G422" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H422">
         <v>81.66666666666667</v>
@@ -12230,7 +12272,7 @@
         <v>73</v>
       </c>
       <c r="B423" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C423">
         <v>120</v>
@@ -12242,7 +12284,7 @@
         <v>360</v>
       </c>
       <c r="G423" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H423">
         <v>132</v>
@@ -12256,7 +12298,7 @@
         <v>73</v>
       </c>
       <c r="B424" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C424">
         <v>90</v>
@@ -12268,7 +12310,7 @@
         <v>1800</v>
       </c>
       <c r="G424" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H424">
         <v>150</v>
@@ -12282,7 +12324,7 @@
         <v>73</v>
       </c>
       <c r="B425" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C425">
         <v>30</v>
@@ -12294,7 +12336,7 @@
         <v>240</v>
       </c>
       <c r="G425" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H425">
         <v>38</v>
@@ -12308,7 +12350,7 @@
         <v>73</v>
       </c>
       <c r="B426" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C426">
         <v>40</v>
@@ -12320,7 +12362,7 @@
         <v>120</v>
       </c>
       <c r="G426" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H426">
         <v>44</v>
@@ -12334,7 +12376,7 @@
         <v>73</v>
       </c>
       <c r="B427" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C427">
         <v>45</v>
@@ -12346,7 +12388,7 @@
         <v>135</v>
       </c>
       <c r="G427" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H427">
         <v>49.50000000000001</v>
@@ -12360,7 +12402,7 @@
         <v>73</v>
       </c>
       <c r="B428" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C428">
         <v>45</v>
@@ -12372,7 +12414,7 @@
         <v>360</v>
       </c>
       <c r="G428" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H428">
         <v>57</v>
@@ -12386,7 +12428,7 @@
         <v>73</v>
       </c>
       <c r="B429" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C429">
         <v>45</v>
@@ -12398,7 +12440,7 @@
         <v>360</v>
       </c>
       <c r="G429" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H429">
         <v>57</v>
@@ -12412,7 +12454,7 @@
         <v>73</v>
       </c>
       <c r="B430" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C430">
         <v>45</v>
@@ -12424,7 +12466,7 @@
         <v>360</v>
       </c>
       <c r="G430" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H430">
         <v>57</v>
@@ -12438,7 +12480,7 @@
         <v>73</v>
       </c>
       <c r="B431" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C431">
         <v>40</v>
@@ -12450,7 +12492,7 @@
         <v>480</v>
       </c>
       <c r="G431" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H431">
         <v>56</v>
@@ -12464,7 +12506,7 @@
         <v>73</v>
       </c>
       <c r="B432" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C432">
         <v>50</v>
@@ -12476,7 +12518,7 @@
         <v>300</v>
       </c>
       <c r="G432" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H432">
         <v>60</v>
@@ -12490,7 +12532,7 @@
         <v>73</v>
       </c>
       <c r="B433" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C433">
         <v>60</v>
@@ -12502,7 +12544,7 @@
         <v>360</v>
       </c>
       <c r="G433" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H433">
         <v>72</v>
@@ -12516,7 +12558,7 @@
         <v>73</v>
       </c>
       <c r="B434" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C434">
         <v>60</v>
@@ -12528,7 +12570,7 @@
         <v>360</v>
       </c>
       <c r="G434" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H434">
         <v>72</v>
@@ -12542,7 +12584,7 @@
         <v>73</v>
       </c>
       <c r="B435" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C435">
         <v>60</v>
@@ -12554,7 +12596,7 @@
         <v>360</v>
       </c>
       <c r="G435" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H435">
         <v>72</v>
@@ -12568,7 +12610,7 @@
         <v>73</v>
       </c>
       <c r="B436" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C436">
         <v>60</v>
@@ -12580,7 +12622,7 @@
         <v>360</v>
       </c>
       <c r="G436" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H436">
         <v>72</v>
@@ -12594,7 +12636,7 @@
         <v>73</v>
       </c>
       <c r="B437" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C437">
         <v>20</v>
@@ -12606,7 +12648,7 @@
         <v>160</v>
       </c>
       <c r="G437" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H437">
         <v>25.33333333333333</v>
@@ -12620,7 +12662,7 @@
         <v>73</v>
       </c>
       <c r="B438" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C438">
         <v>30</v>
@@ -12632,7 +12674,7 @@
         <v>150</v>
       </c>
       <c r="G438" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H438">
         <v>35</v>
@@ -12646,7 +12688,7 @@
         <v>73</v>
       </c>
       <c r="B439" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C439">
         <v>20</v>
@@ -12658,7 +12700,7 @@
         <v>240</v>
       </c>
       <c r="G439" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H439">
         <v>28</v>
@@ -12672,7 +12714,7 @@
         <v>73</v>
       </c>
       <c r="B440" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C440">
         <v>30</v>
@@ -12684,7 +12726,7 @@
         <v>240</v>
       </c>
       <c r="G440" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H440">
         <v>38</v>
@@ -12698,7 +12740,7 @@
         <v>73</v>
       </c>
       <c r="B441" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C441">
         <v>40</v>
@@ -12710,7 +12752,7 @@
         <v>120</v>
       </c>
       <c r="G441" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H441">
         <v>44</v>
@@ -12724,7 +12766,7 @@
         <v>73</v>
       </c>
       <c r="B442" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C442">
         <v>30</v>
@@ -12736,7 +12778,7 @@
         <v>240</v>
       </c>
       <c r="G442" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H442">
         <v>38</v>
@@ -12750,7 +12792,7 @@
         <v>73</v>
       </c>
       <c r="B443" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C443">
         <v>30</v>
@@ -12762,7 +12804,7 @@
         <v>240</v>
       </c>
       <c r="G443" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H443">
         <v>38</v>
@@ -12776,7 +12818,7 @@
         <v>74</v>
       </c>
       <c r="B444" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C444">
         <v>20</v>
@@ -12791,7 +12833,7 @@
         <v>4</v>
       </c>
       <c r="G444" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H444">
         <v>25.33333333333333</v>
@@ -12802,7 +12844,7 @@
         <v>74</v>
       </c>
       <c r="B445" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C445">
         <v>70</v>
@@ -12817,7 +12859,7 @@
         <v>6</v>
       </c>
       <c r="G445" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H445">
         <v>84</v>
@@ -12828,7 +12870,7 @@
         <v>74</v>
       </c>
       <c r="B446" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C446">
         <v>110</v>
@@ -12843,7 +12885,7 @@
         <v>7</v>
       </c>
       <c r="G446" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H446">
         <v>113.6666666666667</v>
@@ -12854,7 +12896,7 @@
         <v>74</v>
       </c>
       <c r="B447" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C447">
         <v>110</v>
@@ -12869,7 +12911,7 @@
         <v>8.5</v>
       </c>
       <c r="G447" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H447">
         <v>121</v>
@@ -12880,7 +12922,7 @@
         <v>74</v>
       </c>
       <c r="B448" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C448">
         <v>90</v>
@@ -12895,7 +12937,7 @@
         <v>8</v>
       </c>
       <c r="G448" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H448">
         <v>120</v>
@@ -12906,7 +12948,7 @@
         <v>74</v>
       </c>
       <c r="B449" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C449">
         <v>90</v>
@@ -12921,7 +12963,7 @@
         <v>8.5</v>
       </c>
       <c r="G449" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H449">
         <v>120</v>
@@ -12932,7 +12974,7 @@
         <v>74</v>
       </c>
       <c r="B450" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C450">
         <v>30</v>
@@ -12947,7 +12989,7 @@
         <v>5.5</v>
       </c>
       <c r="G450" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H450">
         <v>38</v>
@@ -12958,7 +13000,7 @@
         <v>74</v>
       </c>
       <c r="B451" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C451">
         <v>40</v>
@@ -12973,7 +13015,7 @@
         <v>6</v>
       </c>
       <c r="G451" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H451">
         <v>50.66666666666666</v>
@@ -12984,7 +13026,7 @@
         <v>74</v>
       </c>
       <c r="B452" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C452">
         <v>45</v>
@@ -12999,7 +13041,7 @@
         <v>6</v>
       </c>
       <c r="G452" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H452">
         <v>46.50000000000001</v>
@@ -13010,7 +13052,7 @@
         <v>74</v>
       </c>
       <c r="B453" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C453">
         <v>50</v>
@@ -13025,7 +13067,7 @@
         <v>6.5</v>
       </c>
       <c r="G453" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H453">
         <v>51.66666666666667</v>
@@ -13036,7 +13078,7 @@
         <v>74</v>
       </c>
       <c r="B454" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C454">
         <v>55</v>
@@ -13051,7 +13093,7 @@
         <v>7</v>
       </c>
       <c r="G454" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H454">
         <v>56.83333333333334</v>
@@ -13062,7 +13104,7 @@
         <v>74</v>
       </c>
       <c r="B455" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C455">
         <v>60</v>
@@ -13077,7 +13119,7 @@
         <v>10</v>
       </c>
       <c r="G455" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H455">
         <v>60</v>
@@ -13088,7 +13130,7 @@
         <v>74</v>
       </c>
       <c r="B456" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C456">
         <v>50</v>
@@ -13103,7 +13145,7 @@
         <v>8</v>
       </c>
       <c r="G456" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H456">
         <v>60</v>
@@ -13114,7 +13156,7 @@
         <v>74</v>
       </c>
       <c r="B457" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C457">
         <v>50</v>
@@ -13129,7 +13171,7 @@
         <v>9</v>
       </c>
       <c r="G457" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H457">
         <v>60</v>
@@ -13140,7 +13182,7 @@
         <v>75</v>
       </c>
       <c r="B458" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C458">
         <v>20</v>
@@ -13155,7 +13197,7 @@
         <v>3</v>
       </c>
       <c r="G458" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H458">
         <v>26.66666666666666</v>
@@ -13166,7 +13208,7 @@
         <v>75</v>
       </c>
       <c r="B459" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C459">
         <v>60</v>
@@ -13181,7 +13223,7 @@
         <v>6</v>
       </c>
       <c r="G459" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H459">
         <v>76</v>
@@ -13192,7 +13234,7 @@
         <v>75</v>
       </c>
       <c r="B460" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C460">
         <v>100</v>
@@ -13207,7 +13249,7 @@
         <v>7</v>
       </c>
       <c r="G460" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H460">
         <v>116.6666666666667</v>
@@ -13218,7 +13260,7 @@
         <v>75</v>
       </c>
       <c r="B461" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C461">
         <v>120</v>
@@ -13233,7 +13275,7 @@
         <v>8</v>
       </c>
       <c r="G461" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H461">
         <v>128</v>
@@ -13244,7 +13286,7 @@
         <v>75</v>
       </c>
       <c r="B462" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C462">
         <v>130</v>
@@ -13259,7 +13301,7 @@
         <v>9</v>
       </c>
       <c r="G462" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H462">
         <v>134.3333333333333</v>
@@ -13270,7 +13312,7 @@
         <v>75</v>
       </c>
       <c r="B463" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C463">
         <v>100</v>
@@ -13285,7 +13327,7 @@
         <v>9</v>
       </c>
       <c r="G463" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H463">
         <v>133.3333333333333</v>
@@ -13296,7 +13338,7 @@
         <v>75</v>
       </c>
       <c r="B464" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C464">
         <v>100</v>
@@ -13311,7 +13353,7 @@
         <v>9.5</v>
       </c>
       <c r="G464" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H464">
         <v>133.3333333333333</v>
@@ -13322,7 +13364,7 @@
         <v>75</v>
       </c>
       <c r="B465" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C465">
         <v>30</v>
@@ -13337,7 +13379,7 @@
         <v>6</v>
       </c>
       <c r="G465" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H465">
         <v>40</v>
@@ -13348,7 +13390,7 @@
         <v>75</v>
       </c>
       <c r="B466" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C466">
         <v>30</v>
@@ -13363,7 +13405,7 @@
         <v>5.5</v>
       </c>
       <c r="G466" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H466">
         <v>40</v>
@@ -13374,7 +13416,7 @@
         <v>75</v>
       </c>
       <c r="B467" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C467">
         <v>50</v>
@@ -13389,7 +13431,7 @@
         <v>10</v>
       </c>
       <c r="G467" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H467">
         <v>53.33333333333334</v>
@@ -13400,7 +13442,7 @@
         <v>75</v>
       </c>
       <c r="B468" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C468">
         <v>40</v>
@@ -13415,7 +13457,7 @@
         <v>8</v>
       </c>
       <c r="G468" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H468">
         <v>50.66666666666666</v>
@@ -13426,7 +13468,7 @@
         <v>75</v>
       </c>
       <c r="B469" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C469">
         <v>40</v>
@@ -13441,7 +13483,7 @@
         <v>8.5</v>
       </c>
       <c r="G469" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H469">
         <v>50.66666666666666</v>
@@ -13452,7 +13494,7 @@
         <v>75</v>
       </c>
       <c r="B470" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C470">
         <v>40</v>
@@ -13467,7 +13509,7 @@
         <v>10</v>
       </c>
       <c r="G470" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H470">
         <v>48</v>
@@ -13478,7 +13520,7 @@
         <v>75</v>
       </c>
       <c r="B471" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C471">
         <v>40</v>
@@ -13493,7 +13535,7 @@
         <v>7</v>
       </c>
       <c r="G471" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H471">
         <v>60</v>
@@ -13504,7 +13546,7 @@
         <v>75</v>
       </c>
       <c r="B472" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C472">
         <v>70</v>
@@ -13519,7 +13561,7 @@
         <v>8.5</v>
       </c>
       <c r="G472" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H472">
         <v>77</v>
@@ -13530,7 +13572,7 @@
         <v>75</v>
       </c>
       <c r="B473" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C473">
         <v>60</v>
@@ -13545,7 +13587,7 @@
         <v>8</v>
       </c>
       <c r="G473" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H473">
         <v>76</v>
@@ -13556,7 +13598,7 @@
         <v>75</v>
       </c>
       <c r="B474" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C474">
         <v>60</v>
@@ -13571,7 +13613,7 @@
         <v>8</v>
       </c>
       <c r="G474" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H474">
         <v>76</v>
@@ -13582,7 +13624,7 @@
         <v>75</v>
       </c>
       <c r="B475" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C475">
         <v>60</v>
@@ -13597,7 +13639,7 @@
         <v>9</v>
       </c>
       <c r="G475" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H475">
         <v>76</v>
@@ -13608,7 +13650,7 @@
         <v>75</v>
       </c>
       <c r="B476" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C476">
         <v>25</v>
@@ -13623,7 +13665,7 @@
         <v>9</v>
       </c>
       <c r="G476" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H476">
         <v>33.33333333333333</v>
@@ -13634,7 +13676,7 @@
         <v>75</v>
       </c>
       <c r="B477" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C477">
         <v>25</v>
@@ -13649,7 +13691,7 @@
         <v>9</v>
       </c>
       <c r="G477" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H477">
         <v>41.66666666666666</v>
@@ -13660,7 +13702,7 @@
         <v>75</v>
       </c>
       <c r="B478" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C478">
         <v>18</v>
@@ -13675,7 +13717,7 @@
         <v>6</v>
       </c>
       <c r="G478" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H478">
         <v>25.2</v>
@@ -13686,7 +13728,7 @@
         <v>75</v>
       </c>
       <c r="B479" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C479">
         <v>22</v>
@@ -13701,7 +13743,7 @@
         <v>7.5</v>
       </c>
       <c r="G479" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H479">
         <v>29.33333333333333</v>
@@ -13712,7 +13754,7 @@
         <v>75</v>
       </c>
       <c r="B480" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C480">
         <v>22</v>
@@ -13727,7 +13769,7 @@
         <v>8.5</v>
       </c>
       <c r="G480" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H480">
         <v>29.33333333333333</v>
@@ -13738,7 +13780,7 @@
         <v>75</v>
       </c>
       <c r="B481" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C481">
         <v>22</v>
@@ -13753,7 +13795,7 @@
         <v>9</v>
       </c>
       <c r="G481" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H481">
         <v>29.33333333333333</v>
@@ -13764,7 +13806,7 @@
         <v>76</v>
       </c>
       <c r="B482" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C482">
         <v>20</v>
@@ -13779,7 +13821,7 @@
         <v>3</v>
       </c>
       <c r="G482" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H482">
         <v>25.33333333333333</v>
@@ -13790,7 +13832,7 @@
         <v>76</v>
       </c>
       <c r="B483" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C483">
         <v>40</v>
@@ -13805,7 +13847,7 @@
         <v>5</v>
       </c>
       <c r="G483" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H483">
         <v>53.33333333333333</v>
@@ -13816,7 +13858,7 @@
         <v>76</v>
       </c>
       <c r="B484" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C484">
         <v>60</v>
@@ -13831,7 +13873,7 @@
         <v>6</v>
       </c>
       <c r="G484" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H484">
         <v>66</v>
@@ -13842,7 +13884,7 @@
         <v>76</v>
       </c>
       <c r="B485" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C485">
         <v>70</v>
@@ -13857,7 +13899,7 @@
         <v>6.5</v>
       </c>
       <c r="G485" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H485">
         <v>72.33333333333334</v>
@@ -13868,7 +13910,7 @@
         <v>76</v>
       </c>
       <c r="B486" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C486">
         <v>75</v>
@@ -13883,7 +13925,7 @@
         <v>7.5</v>
       </c>
       <c r="G486" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H486">
         <v>77.50000000000001</v>
@@ -13894,7 +13936,7 @@
         <v>76</v>
       </c>
       <c r="B487" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C487">
         <v>80</v>
@@ -13909,7 +13951,7 @@
         <v>8.5</v>
       </c>
       <c r="G487" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H487">
         <v>82.66666666666667</v>
@@ -13920,7 +13962,7 @@
         <v>76</v>
       </c>
       <c r="B488" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C488">
         <v>60</v>
@@ -13935,7 +13977,7 @@
         <v>7.5</v>
       </c>
       <c r="G488" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H488">
         <v>80</v>
@@ -13946,7 +13988,7 @@
         <v>76</v>
       </c>
       <c r="B489" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C489">
         <v>60</v>
@@ -13961,7 +14003,7 @@
         <v>8</v>
       </c>
       <c r="G489" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H489">
         <v>80</v>
@@ -13972,7 +14014,7 @@
         <v>76</v>
       </c>
       <c r="B490" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C490">
         <v>60</v>
@@ -13987,7 +14029,7 @@
         <v>8.5</v>
       </c>
       <c r="G490" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H490">
         <v>80</v>
@@ -13998,7 +14040,7 @@
         <v>76</v>
       </c>
       <c r="B491" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C491">
         <v>40</v>
@@ -14013,7 +14055,7 @@
         <v>6</v>
       </c>
       <c r="G491" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H491">
         <v>56</v>
@@ -14024,7 +14066,7 @@
         <v>76</v>
       </c>
       <c r="B492" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C492">
         <v>60</v>
@@ -14047,7 +14089,7 @@
         <v>76</v>
       </c>
       <c r="B493" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C493">
         <v>60</v>
@@ -14070,7 +14112,7 @@
         <v>76</v>
       </c>
       <c r="B494" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C494">
         <v>60</v>
@@ -14093,7 +14135,7 @@
         <v>76</v>
       </c>
       <c r="B495" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C495">
         <v>60</v>
@@ -14116,7 +14158,7 @@
         <v>76</v>
       </c>
       <c r="B496" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C496">
         <v>20</v>
@@ -14131,7 +14173,7 @@
         <v>6</v>
       </c>
       <c r="G496" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H496">
         <v>26.66666666666666</v>
@@ -14142,7 +14184,7 @@
         <v>76</v>
       </c>
       <c r="B497" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C497">
         <v>20</v>
@@ -14157,7 +14199,7 @@
         <v>6</v>
       </c>
       <c r="G497" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H497">
         <v>30</v>
@@ -14168,7 +14210,7 @@
         <v>76</v>
       </c>
       <c r="B498" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C498">
         <v>25</v>
@@ -14191,7 +14233,7 @@
         <v>76</v>
       </c>
       <c r="B499" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C499">
         <v>25</v>
@@ -14214,7 +14256,7 @@
         <v>76</v>
       </c>
       <c r="B500" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C500">
         <v>25</v>
@@ -14229,7 +14271,7 @@
         <v>8</v>
       </c>
       <c r="G500" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H500">
         <v>31.66666666666666</v>
@@ -14240,7 +14282,7 @@
         <v>76</v>
       </c>
       <c r="B501" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C501">
         <v>25</v>
@@ -14263,7 +14305,7 @@
         <v>76</v>
       </c>
       <c r="B502" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C502">
         <v>25</v>
@@ -14286,7 +14328,7 @@
         <v>76</v>
       </c>
       <c r="B503" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C503">
         <v>25</v>
@@ -14309,7 +14351,7 @@
         <v>76</v>
       </c>
       <c r="B504" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C504">
         <v>25</v>
@@ -14332,7 +14374,7 @@
         <v>76</v>
       </c>
       <c r="B505" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C505">
         <v>25</v>
@@ -14355,7 +14397,7 @@
         <v>77</v>
       </c>
       <c r="B506" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C506">
         <v>70</v>
@@ -14370,7 +14412,7 @@
         <v>4.5</v>
       </c>
       <c r="G506" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H506">
         <v>93.33333333333333</v>
@@ -14381,7 +14423,7 @@
         <v>77</v>
       </c>
       <c r="B507" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C507">
         <v>120</v>
@@ -14396,7 +14438,7 @@
         <v>5</v>
       </c>
       <c r="G507" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H507">
         <v>124</v>
@@ -14407,7 +14449,7 @@
         <v>77</v>
       </c>
       <c r="B508" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C508">
         <v>160</v>
@@ -14422,7 +14464,7 @@
         <v>7.5</v>
       </c>
       <c r="G508" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H508">
         <v>165.3333333333333</v>
@@ -14433,7 +14475,7 @@
         <v>77</v>
       </c>
       <c r="B509" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C509">
         <v>160</v>
@@ -14448,7 +14490,7 @@
         <v>8.5</v>
       </c>
       <c r="G509" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H509">
         <v>176</v>
@@ -14459,7 +14501,7 @@
         <v>77</v>
       </c>
       <c r="B510" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C510">
         <v>170</v>
@@ -14474,7 +14516,7 @@
         <v>8.5</v>
       </c>
       <c r="G510" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H510">
         <v>175.6666666666667</v>
@@ -14485,7 +14527,7 @@
         <v>77</v>
       </c>
       <c r="B511" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C511">
         <v>180</v>
@@ -14500,7 +14542,7 @@
         <v>10</v>
       </c>
       <c r="G511" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H511">
         <v>180</v>
@@ -14511,7 +14553,7 @@
         <v>77</v>
       </c>
       <c r="B512" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C512">
         <v>180</v>
@@ -14526,7 +14568,7 @@
         <v>10</v>
       </c>
       <c r="G512" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H512">
         <v>180</v>
@@ -14537,7 +14579,7 @@
         <v>77</v>
       </c>
       <c r="B513" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C513">
         <v>140</v>
@@ -14552,7 +14594,7 @@
         <v>8.5</v>
       </c>
       <c r="G513" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H513">
         <v>163.3333333333333</v>
@@ -14563,7 +14605,7 @@
         <v>77</v>
       </c>
       <c r="B514" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C514">
         <v>140</v>
@@ -14578,7 +14620,7 @@
         <v>9.5</v>
       </c>
       <c r="G514" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H514">
         <v>163.3333333333333</v>
@@ -14589,7 +14631,7 @@
         <v>77</v>
       </c>
       <c r="B515" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C515">
         <v>140</v>
@@ -14604,7 +14646,7 @@
         <v>9.5</v>
       </c>
       <c r="G515" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H515">
         <v>163.3333333333333</v>
@@ -14615,7 +14657,7 @@
         <v>77</v>
       </c>
       <c r="B516" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C516">
         <v>20</v>
@@ -14630,7 +14672,7 @@
         <v>4</v>
       </c>
       <c r="G516" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H516">
         <v>26.66666666666666</v>
@@ -14641,7 +14683,7 @@
         <v>77</v>
       </c>
       <c r="B517" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C517">
         <v>40</v>
@@ -14656,7 +14698,7 @@
         <v>5</v>
       </c>
       <c r="G517" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H517">
         <v>53.33333333333333</v>
@@ -14667,7 +14709,7 @@
         <v>77</v>
       </c>
       <c r="B518" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C518">
         <v>60</v>
@@ -14682,7 +14724,7 @@
         <v>6</v>
       </c>
       <c r="G518" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H518">
         <v>66</v>
@@ -14693,7 +14735,7 @@
         <v>77</v>
       </c>
       <c r="B519" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C519">
         <v>70</v>
@@ -14708,7 +14750,7 @@
         <v>7</v>
       </c>
       <c r="G519" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H519">
         <v>72.33333333333334</v>
@@ -14719,7 +14761,7 @@
         <v>77</v>
       </c>
       <c r="B520" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C520">
         <v>80</v>
@@ -14734,7 +14776,7 @@
         <v>10</v>
       </c>
       <c r="G520" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H520">
         <v>80</v>
@@ -14745,7 +14787,7 @@
         <v>77</v>
       </c>
       <c r="B521" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C521">
         <v>70</v>
@@ -14760,7 +14802,7 @@
         <v>8.5</v>
       </c>
       <c r="G521" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H521">
         <v>77</v>
@@ -14771,7 +14813,7 @@
         <v>77</v>
       </c>
       <c r="B522" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C522">
         <v>65</v>
@@ -14786,7 +14828,7 @@
         <v>8</v>
       </c>
       <c r="G522" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H522">
         <v>75.83333333333334</v>
@@ -14797,7 +14839,7 @@
         <v>77</v>
       </c>
       <c r="B523" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C523">
         <v>65</v>
@@ -14812,7 +14854,7 @@
         <v>8.5</v>
       </c>
       <c r="G523" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H523">
         <v>75.83333333333334</v>
@@ -14823,7 +14865,7 @@
         <v>77</v>
       </c>
       <c r="B524" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C524">
         <v>65</v>
@@ -14838,10 +14880,452 @@
         <v>9.5</v>
       </c>
       <c r="G524" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H524">
         <v>75.83333333333334</v>
+      </c>
+    </row>
+    <row r="525" spans="1:8">
+      <c r="A525" t="s">
+        <v>78</v>
+      </c>
+      <c r="B525" t="s">
+        <v>114</v>
+      </c>
+      <c r="C525">
+        <v>20</v>
+      </c>
+      <c r="D525">
+        <v>8</v>
+      </c>
+      <c r="E525">
+        <v>160</v>
+      </c>
+      <c r="F525">
+        <v>3</v>
+      </c>
+      <c r="G525" t="s">
+        <v>347</v>
+      </c>
+      <c r="H525">
+        <v>25.33333333333333</v>
+      </c>
+    </row>
+    <row r="526" spans="1:8">
+      <c r="A526" t="s">
+        <v>78</v>
+      </c>
+      <c r="B526" t="s">
+        <v>99</v>
+      </c>
+      <c r="C526">
+        <v>70</v>
+      </c>
+      <c r="D526">
+        <v>6</v>
+      </c>
+      <c r="E526">
+        <v>420</v>
+      </c>
+      <c r="F526">
+        <v>5</v>
+      </c>
+      <c r="G526" t="s">
+        <v>424</v>
+      </c>
+      <c r="H526">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="527" spans="1:8">
+      <c r="A527" t="s">
+        <v>78</v>
+      </c>
+      <c r="B527" t="s">
+        <v>99</v>
+      </c>
+      <c r="C527">
+        <v>120</v>
+      </c>
+      <c r="D527">
+        <v>3</v>
+      </c>
+      <c r="E527">
+        <v>360</v>
+      </c>
+      <c r="F527">
+        <v>8</v>
+      </c>
+      <c r="G527" t="s">
+        <v>425</v>
+      </c>
+      <c r="H527">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="528" spans="1:8">
+      <c r="A528" t="s">
+        <v>78</v>
+      </c>
+      <c r="B528" t="s">
+        <v>99</v>
+      </c>
+      <c r="C528">
+        <v>130</v>
+      </c>
+      <c r="D528">
+        <v>1</v>
+      </c>
+      <c r="E528">
+        <v>130</v>
+      </c>
+      <c r="F528">
+        <v>8.5</v>
+      </c>
+      <c r="G528" t="s">
+        <v>426</v>
+      </c>
+      <c r="H528">
+        <v>134.3333333333333</v>
+      </c>
+    </row>
+    <row r="529" spans="1:8">
+      <c r="A529" t="s">
+        <v>78</v>
+      </c>
+      <c r="B529" t="s">
+        <v>99</v>
+      </c>
+      <c r="C529">
+        <v>100</v>
+      </c>
+      <c r="D529">
+        <v>8</v>
+      </c>
+      <c r="E529">
+        <v>800</v>
+      </c>
+      <c r="F529">
+        <v>8.5</v>
+      </c>
+      <c r="G529" t="s">
+        <v>427</v>
+      </c>
+      <c r="H529">
+        <v>126.6666666666667</v>
+      </c>
+    </row>
+    <row r="530" spans="1:8">
+      <c r="A530" t="s">
+        <v>78</v>
+      </c>
+      <c r="B530" t="s">
+        <v>99</v>
+      </c>
+      <c r="C530">
+        <v>100</v>
+      </c>
+      <c r="D530">
+        <v>8</v>
+      </c>
+      <c r="E530">
+        <v>800</v>
+      </c>
+      <c r="F530">
+        <v>8.5</v>
+      </c>
+      <c r="G530" t="s">
+        <v>428</v>
+      </c>
+      <c r="H530">
+        <v>126.6666666666667</v>
+      </c>
+    </row>
+    <row r="531" spans="1:8">
+      <c r="A531" t="s">
+        <v>78</v>
+      </c>
+      <c r="B531" t="s">
+        <v>99</v>
+      </c>
+      <c r="C531">
+        <v>70</v>
+      </c>
+      <c r="D531">
+        <v>20</v>
+      </c>
+      <c r="E531">
+        <v>1400</v>
+      </c>
+      <c r="F531">
+        <v>7.5</v>
+      </c>
+      <c r="G531" t="s">
+        <v>429</v>
+      </c>
+      <c r="H531">
+        <v>116.6666666666667</v>
+      </c>
+    </row>
+    <row r="532" spans="1:8">
+      <c r="A532" t="s">
+        <v>78</v>
+      </c>
+      <c r="B532" t="s">
+        <v>102</v>
+      </c>
+      <c r="C532">
+        <v>20</v>
+      </c>
+      <c r="D532">
+        <v>8</v>
+      </c>
+      <c r="E532">
+        <v>160</v>
+      </c>
+      <c r="F532">
+        <v>3</v>
+      </c>
+      <c r="G532" t="s">
+        <v>347</v>
+      </c>
+      <c r="H532">
+        <v>25.33333333333333</v>
+      </c>
+    </row>
+    <row r="533" spans="1:8">
+      <c r="A533" t="s">
+        <v>78</v>
+      </c>
+      <c r="B533" t="s">
+        <v>102</v>
+      </c>
+      <c r="C533">
+        <v>50</v>
+      </c>
+      <c r="D533">
+        <v>6</v>
+      </c>
+      <c r="E533">
+        <v>300</v>
+      </c>
+      <c r="F533">
+        <v>6</v>
+      </c>
+      <c r="G533" t="s">
+        <v>430</v>
+      </c>
+      <c r="H533">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="534" spans="1:8">
+      <c r="A534" t="s">
+        <v>78</v>
+      </c>
+      <c r="B534" t="s">
+        <v>102</v>
+      </c>
+      <c r="C534">
+        <v>60</v>
+      </c>
+      <c r="D534">
+        <v>6</v>
+      </c>
+      <c r="E534">
+        <v>360</v>
+      </c>
+      <c r="F534">
+        <v>7</v>
+      </c>
+      <c r="G534" t="s">
+        <v>431</v>
+      </c>
+      <c r="H534">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="535" spans="1:8">
+      <c r="A535" t="s">
+        <v>78</v>
+      </c>
+      <c r="B535" t="s">
+        <v>102</v>
+      </c>
+      <c r="C535">
+        <v>70</v>
+      </c>
+      <c r="D535">
+        <v>5</v>
+      </c>
+      <c r="E535">
+        <v>350</v>
+      </c>
+      <c r="F535">
+        <v>8</v>
+      </c>
+      <c r="G535" t="s">
+        <v>432</v>
+      </c>
+      <c r="H535">
+        <v>81.66666666666667</v>
+      </c>
+    </row>
+    <row r="536" spans="1:8">
+      <c r="A536" t="s">
+        <v>78</v>
+      </c>
+      <c r="B536" t="s">
+        <v>102</v>
+      </c>
+      <c r="C536">
+        <v>70</v>
+      </c>
+      <c r="D536">
+        <v>5</v>
+      </c>
+      <c r="E536">
+        <v>350</v>
+      </c>
+      <c r="F536">
+        <v>9</v>
+      </c>
+      <c r="G536" t="s">
+        <v>432</v>
+      </c>
+      <c r="H536">
+        <v>81.66666666666667</v>
+      </c>
+    </row>
+    <row r="537" spans="1:8">
+      <c r="A537" t="s">
+        <v>78</v>
+      </c>
+      <c r="B537" t="s">
+        <v>102</v>
+      </c>
+      <c r="C537">
+        <v>60</v>
+      </c>
+      <c r="D537">
+        <v>10</v>
+      </c>
+      <c r="E537">
+        <v>600</v>
+      </c>
+      <c r="F537">
+        <v>8.5</v>
+      </c>
+      <c r="G537" t="s">
+        <v>433</v>
+      </c>
+      <c r="H537">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="538" spans="1:8">
+      <c r="A538" t="s">
+        <v>78</v>
+      </c>
+      <c r="B538" t="s">
+        <v>102</v>
+      </c>
+      <c r="C538">
+        <v>60</v>
+      </c>
+      <c r="D538">
+        <v>10</v>
+      </c>
+      <c r="E538">
+        <v>600</v>
+      </c>
+      <c r="F538">
+        <v>9.5</v>
+      </c>
+      <c r="G538" t="s">
+        <v>428</v>
+      </c>
+      <c r="H538">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="539" spans="1:8">
+      <c r="A539" t="s">
+        <v>78</v>
+      </c>
+      <c r="B539" t="s">
+        <v>83</v>
+      </c>
+      <c r="C539">
+        <v>22</v>
+      </c>
+      <c r="D539">
+        <v>12</v>
+      </c>
+      <c r="E539">
+        <v>264</v>
+      </c>
+      <c r="F539">
+        <v>7.5</v>
+      </c>
+      <c r="G539" t="s">
+        <v>434</v>
+      </c>
+      <c r="H539">
+        <v>30.8</v>
+      </c>
+    </row>
+    <row r="540" spans="1:8">
+      <c r="A540" t="s">
+        <v>78</v>
+      </c>
+      <c r="B540" t="s">
+        <v>83</v>
+      </c>
+      <c r="C540">
+        <v>22</v>
+      </c>
+      <c r="D540">
+        <v>12</v>
+      </c>
+      <c r="E540">
+        <v>264</v>
+      </c>
+      <c r="F540">
+        <v>8</v>
+      </c>
+      <c r="G540" t="s">
+        <v>435</v>
+      </c>
+      <c r="H540">
+        <v>30.8</v>
+      </c>
+    </row>
+    <row r="541" spans="1:8">
+      <c r="A541" t="s">
+        <v>78</v>
+      </c>
+      <c r="B541" t="s">
+        <v>83</v>
+      </c>
+      <c r="C541">
+        <v>22</v>
+      </c>
+      <c r="D541">
+        <v>12</v>
+      </c>
+      <c r="E541">
+        <v>264</v>
+      </c>
+      <c r="F541">
+        <v>9</v>
+      </c>
+      <c r="G541" t="s">
+        <v>436</v>
+      </c>
+      <c r="H541">
+        <v>30.8</v>
       </c>
     </row>
   </sheetData>
